--- a/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
+++ b/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\Fossil Replenishment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0066332-46D1-47C0-B8CF-E5704BAAFBD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A11E5234-568C-476A-A65A-AEA4DD2E43AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6662473D-6E1F-42FD-999B-28162E22D4B5}"/>
   </bookViews>

--- a/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
+++ b/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\Fossil Replenishment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A11E5234-568C-476A-A65A-AEA4DD2E43AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{583391EB-E811-484B-BA36-E8300917055D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6662473D-6E1F-42FD-999B-28162E22D4B5}"/>
   </bookViews>

--- a/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
+++ b/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\Fossil Replenishment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D2F3DE0-9962-4782-A163-2CCB9B80748E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD860362-0F4E-4DE6-9A82-898793CE9777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6662473D-6E1F-42FD-999B-28162E22D4B5}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$T$343</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$T$374</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2756" uniqueCount="1071">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2942" uniqueCount="1134">
   <si>
     <t>In Transit PO</t>
   </si>
@@ -3250,6 +3250,195 @@
   </si>
   <si>
     <t>Y-Liq</t>
+  </si>
+  <si>
+    <t>FS5237</t>
+  </si>
+  <si>
+    <t>CH2885</t>
+  </si>
+  <si>
+    <t>AX1343</t>
+  </si>
+  <si>
+    <t>AX1746</t>
+  </si>
+  <si>
+    <t>FS5665</t>
+  </si>
+  <si>
+    <t>FS5061</t>
+  </si>
+  <si>
+    <t>AX2761</t>
+  </si>
+  <si>
+    <t>AR11606</t>
+  </si>
+  <si>
+    <t>MK9165</t>
+  </si>
+  <si>
+    <t>AR1828</t>
+  </si>
+  <si>
+    <t>AX4614</t>
+  </si>
+  <si>
+    <t>DZ4548</t>
+  </si>
+  <si>
+    <t>MK9146</t>
+  </si>
+  <si>
+    <t>AX4611</t>
+  </si>
+  <si>
+    <t>AX5385</t>
+  </si>
+  <si>
+    <t>MK4823</t>
+  </si>
+  <si>
+    <t>MK7303</t>
+  </si>
+  <si>
+    <t>AR11589</t>
+  </si>
+  <si>
+    <t>AX5616</t>
+  </si>
+  <si>
+    <t>FS5151</t>
+  </si>
+  <si>
+    <t>FS5855</t>
+  </si>
+  <si>
+    <t>AX2101</t>
+  </si>
+  <si>
+    <t>MK4967</t>
+  </si>
+  <si>
+    <t>ES5362</t>
+  </si>
+  <si>
+    <t>ME3154</t>
+  </si>
+  <si>
+    <t>AR11692</t>
+  </si>
+  <si>
+    <t>DZ2234</t>
+  </si>
+  <si>
+    <t>AR11755</t>
+  </si>
+  <si>
+    <t>MK7570SET</t>
+  </si>
+  <si>
+    <t>MK7582</t>
+  </si>
+  <si>
+    <t>FS6062</t>
+  </si>
+  <si>
+    <t>B01KNMEVDG</t>
+  </si>
+  <si>
+    <t>B00EVZ83J0</t>
+  </si>
+  <si>
+    <t>B0846PJPW9</t>
+  </si>
+  <si>
+    <t>B0CHXGWVZJ</t>
+  </si>
+  <si>
+    <t>B07WQ9WRJ9</t>
+  </si>
+  <si>
+    <t>B00STAYV6C</t>
+  </si>
+  <si>
+    <t>B0CR5JQFD5</t>
+  </si>
+  <si>
+    <t>B0CYNH9X11</t>
+  </si>
+  <si>
+    <t>B0CZ93BN92</t>
+  </si>
+  <si>
+    <t>B00VATDB10</t>
+  </si>
+  <si>
+    <t>B0D85F9QCK</t>
+  </si>
+  <si>
+    <t>B08SW1LBDF</t>
+  </si>
+  <si>
+    <t>B0CFVK4PYT</t>
+  </si>
+  <si>
+    <t>B0CR5G3NRL</t>
+  </si>
+  <si>
+    <t>B0CWR5S3R7</t>
+  </si>
+  <si>
+    <t>B0CZ9BTN24</t>
+  </si>
+  <si>
+    <t>B0BG17DJQS</t>
+  </si>
+  <si>
+    <t>B0CR5RZRMH</t>
+  </si>
+  <si>
+    <t>B0CYN8F826</t>
+  </si>
+  <si>
+    <t>B017SN1OI8</t>
+  </si>
+  <si>
+    <t>B0975TDMW6</t>
+  </si>
+  <si>
+    <t>B00786VY22</t>
+  </si>
+  <si>
+    <t>B0FS6N1YT5</t>
+  </si>
+  <si>
+    <t>B0D93652ZY</t>
+  </si>
+  <si>
+    <t>B0769YW2KN</t>
+  </si>
+  <si>
+    <t>B0FFJ4N8BK</t>
+  </si>
+  <si>
+    <t>B07SV6Q9QX</t>
+  </si>
+  <si>
+    <t>B0GDJJ86QY</t>
+  </si>
+  <si>
+    <t>B0GF7BSTKP</t>
+  </si>
+  <si>
+    <t>B0GF73VZZ2</t>
+  </si>
+  <si>
+    <t>B0CZSF6LVY</t>
+  </si>
+  <si>
+    <t>N</t>
   </si>
 </sst>
 </file>
@@ -3879,29 +4068,26 @@
         <v>12</v>
       </c>
       <c r="I2" s="8">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="J2" s="8">
         <v>0</v>
       </c>
       <c r="K2" s="8">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="L2" s="8">
         <v>0</v>
       </c>
       <c r="M2" s="8">
         <f>I2+J2+K2+L2</f>
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="N2" s="8">
-        <v>2039</v>
+        <v>2457</v>
       </c>
       <c r="O2" s="8"/>
-      <c r="P2" s="8">
-        <f>O2/12</f>
-        <v>0</v>
-      </c>
+      <c r="P2" s="8"/>
       <c r="Q2" s="8"/>
       <c r="R2" s="8"/>
       <c r="S2" s="8"/>
@@ -3933,7 +4119,7 @@
         <v>12</v>
       </c>
       <c r="I3" s="8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J3" s="8">
         <v>0</v>
@@ -3946,7 +4132,7 @@
       </c>
       <c r="M3" s="8">
         <f t="shared" ref="M3:M66" si="0">I3+J3+K3+L3</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N3" s="8">
         <v>0</v>
@@ -3984,7 +4170,7 @@
         <v>12</v>
       </c>
       <c r="I4" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="8">
         <v>0</v>
@@ -3997,7 +4183,7 @@
       </c>
       <c r="M4" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" s="8">
         <v>0</v>
@@ -4035,23 +4221,23 @@
         <v>12</v>
       </c>
       <c r="I5" s="8">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="J5" s="8">
         <v>0</v>
       </c>
       <c r="K5" s="8">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="L5" s="8">
         <v>0</v>
       </c>
       <c r="M5" s="8">
         <f t="shared" si="0"/>
-        <v>355</v>
+        <v>303</v>
       </c>
       <c r="N5" s="8">
-        <v>0</v>
+        <v>509</v>
       </c>
       <c r="O5" s="8"/>
       <c r="P5" s="8"/>
@@ -4086,23 +4272,23 @@
         <v>12</v>
       </c>
       <c r="I6" s="8">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="J6" s="8">
         <v>0</v>
       </c>
       <c r="K6" s="8">
-        <v>40</v>
+        <v>240</v>
       </c>
       <c r="L6" s="8">
         <v>0</v>
       </c>
       <c r="M6" s="8">
         <f t="shared" si="0"/>
-        <v>306</v>
+        <v>519</v>
       </c>
       <c r="N6" s="8">
-        <v>1143</v>
+        <v>1182</v>
       </c>
       <c r="O6" s="8"/>
       <c r="P6" s="8"/>
@@ -4137,7 +4323,7 @@
         <v>12</v>
       </c>
       <c r="I7" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="8">
         <v>0</v>
@@ -4150,10 +4336,10 @@
       </c>
       <c r="M7" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" s="8">
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
@@ -4188,23 +4374,23 @@
         <v>12</v>
       </c>
       <c r="I8" s="8">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="J8" s="8">
         <v>0</v>
       </c>
       <c r="K8" s="8">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="L8" s="8">
         <v>0</v>
       </c>
       <c r="M8" s="8">
         <f t="shared" si="0"/>
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="N8" s="8">
-        <v>1288</v>
+        <v>1196</v>
       </c>
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
@@ -4239,7 +4425,7 @@
         <v>12</v>
       </c>
       <c r="I9" s="8">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="J9" s="8">
         <v>0</v>
@@ -4252,10 +4438,10 @@
       </c>
       <c r="M9" s="8">
         <f t="shared" si="0"/>
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="N9" s="8">
-        <v>539</v>
+        <v>910</v>
       </c>
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
@@ -4290,23 +4476,23 @@
         <v>12</v>
       </c>
       <c r="I10" s="8">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J10" s="8">
         <v>0</v>
       </c>
       <c r="K10" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L10" s="8">
         <v>0</v>
       </c>
       <c r="M10" s="8">
         <f t="shared" si="0"/>
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N10" s="8">
-        <v>864</v>
+        <v>846</v>
       </c>
       <c r="O10" s="8"/>
       <c r="P10" s="8"/>
@@ -4341,23 +4527,23 @@
         <v>12</v>
       </c>
       <c r="I11" s="8">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="J11" s="8">
         <v>0</v>
       </c>
       <c r="K11" s="8">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L11" s="8">
         <v>0</v>
       </c>
       <c r="M11" s="8">
         <f t="shared" si="0"/>
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="N11" s="8">
-        <v>529</v>
+        <v>488</v>
       </c>
       <c r="O11" s="8"/>
       <c r="P11" s="8"/>
@@ -4398,17 +4584,17 @@
         <v>0</v>
       </c>
       <c r="K12" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L12" s="8">
         <v>0</v>
       </c>
       <c r="M12" s="8">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N12" s="8">
-        <v>265</v>
+        <v>801</v>
       </c>
       <c r="O12" s="8"/>
       <c r="P12" s="8"/>
@@ -4443,23 +4629,23 @@
         <v>12</v>
       </c>
       <c r="I13" s="8">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="J13" s="8">
         <v>0</v>
       </c>
       <c r="K13" s="8">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="L13" s="8">
         <v>0</v>
       </c>
       <c r="M13" s="8">
         <f t="shared" si="0"/>
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="N13" s="8">
-        <v>491</v>
+        <v>443</v>
       </c>
       <c r="O13" s="8"/>
       <c r="P13" s="8"/>
@@ -4494,23 +4680,23 @@
         <v>12</v>
       </c>
       <c r="I14" s="8">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J14" s="8">
         <v>0</v>
       </c>
       <c r="K14" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L14" s="8">
         <v>0</v>
       </c>
       <c r="M14" s="8">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N14" s="8">
-        <v>1727</v>
+        <v>1688</v>
       </c>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
@@ -4545,7 +4731,7 @@
         <v>12</v>
       </c>
       <c r="I15" s="8">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J15" s="8">
         <v>0</v>
@@ -4558,7 +4744,7 @@
       </c>
       <c r="M15" s="8">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="N15" s="8">
         <v>0</v>
@@ -4596,7 +4782,7 @@
         <v>12</v>
       </c>
       <c r="I16" s="8">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J16" s="8">
         <v>0</v>
@@ -4609,10 +4795,10 @@
       </c>
       <c r="M16" s="8">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N16" s="8">
-        <v>1125</v>
+        <v>1098</v>
       </c>
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
@@ -4647,23 +4833,23 @@
         <v>12</v>
       </c>
       <c r="I17" s="8">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="J17" s="8">
         <v>0</v>
       </c>
       <c r="K17" s="8">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="L17" s="8">
         <v>0</v>
       </c>
       <c r="M17" s="8">
         <f t="shared" si="0"/>
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N17" s="8">
-        <v>303</v>
+        <v>284</v>
       </c>
       <c r="O17" s="8"/>
       <c r="P17" s="8"/>
@@ -4698,7 +4884,7 @@
         <v>12</v>
       </c>
       <c r="I18" s="8">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="J18" s="8">
         <v>0</v>
@@ -4711,10 +4897,10 @@
       </c>
       <c r="M18" s="8">
         <f t="shared" si="0"/>
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="N18" s="8">
-        <v>894</v>
+        <v>743</v>
       </c>
       <c r="O18" s="8"/>
       <c r="P18" s="8"/>
@@ -4749,23 +4935,23 @@
         <v>13</v>
       </c>
       <c r="I19" s="8">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="J19" s="8">
         <v>0</v>
       </c>
       <c r="K19" s="8">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="L19" s="8">
         <v>0</v>
       </c>
       <c r="M19" s="8">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="N19" s="8">
-        <v>0</v>
+        <v>778</v>
       </c>
       <c r="O19" s="8"/>
       <c r="P19" s="8"/>
@@ -4800,23 +4986,23 @@
         <v>14</v>
       </c>
       <c r="I20" s="8">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J20" s="8">
         <v>0</v>
       </c>
       <c r="K20" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L20" s="8">
         <v>0</v>
       </c>
       <c r="M20" s="8">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N20" s="8">
-        <v>290</v>
+        <v>195</v>
       </c>
       <c r="O20" s="8"/>
       <c r="P20" s="8"/>
@@ -4851,23 +5037,23 @@
         <v>13</v>
       </c>
       <c r="I21" s="8">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="J21" s="8">
         <v>0</v>
       </c>
       <c r="K21" s="8">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="L21" s="8">
         <v>0</v>
       </c>
       <c r="M21" s="8">
         <f t="shared" si="0"/>
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="N21" s="8">
-        <v>285</v>
+        <v>1161</v>
       </c>
       <c r="O21" s="8"/>
       <c r="P21" s="8"/>
@@ -4959,17 +5145,17 @@
         <v>0</v>
       </c>
       <c r="K23" s="8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L23" s="8">
         <v>0</v>
       </c>
       <c r="M23" s="8">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N23" s="8">
-        <v>579</v>
+        <v>740</v>
       </c>
       <c r="O23" s="8"/>
       <c r="P23" s="8"/>
@@ -5020,7 +5206,7 @@
         <v>14</v>
       </c>
       <c r="N24" s="8">
-        <v>268</v>
+        <v>173</v>
       </c>
       <c r="O24" s="8"/>
       <c r="P24" s="8"/>
@@ -5055,7 +5241,7 @@
         <v>12</v>
       </c>
       <c r="I25" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" s="8">
         <v>0</v>
@@ -5068,7 +5254,7 @@
       </c>
       <c r="M25" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" s="8">
         <v>0</v>
@@ -5106,23 +5292,23 @@
         <v>12</v>
       </c>
       <c r="I26" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J26" s="8">
         <v>0</v>
       </c>
       <c r="K26" s="8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L26" s="8">
         <v>0</v>
       </c>
       <c r="M26" s="8">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="N26" s="8">
-        <v>1719</v>
+        <v>1597</v>
       </c>
       <c r="O26" s="8"/>
       <c r="P26" s="8"/>
@@ -5173,7 +5359,7 @@
         <v>35</v>
       </c>
       <c r="N27" s="8">
-        <v>837</v>
+        <v>810</v>
       </c>
       <c r="O27" s="8"/>
       <c r="P27" s="8"/>
@@ -5208,7 +5394,7 @@
         <v>12</v>
       </c>
       <c r="I28" s="8">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="J28" s="8">
         <v>0</v>
@@ -5221,7 +5407,7 @@
       </c>
       <c r="M28" s="8">
         <f t="shared" si="0"/>
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="N28" s="8">
         <v>0</v>
@@ -5259,23 +5445,23 @@
         <v>13</v>
       </c>
       <c r="I29" s="8">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J29" s="8">
         <v>0</v>
       </c>
       <c r="K29" s="8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L29" s="8">
         <v>0</v>
       </c>
       <c r="M29" s="8">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="N29" s="8">
-        <v>969</v>
+        <v>932</v>
       </c>
       <c r="O29" s="8"/>
       <c r="P29" s="8"/>
@@ -5310,23 +5496,23 @@
         <v>14</v>
       </c>
       <c r="I30" s="8">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J30" s="8">
         <v>0</v>
       </c>
       <c r="K30" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L30" s="8">
         <v>0</v>
       </c>
       <c r="M30" s="8">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="N30" s="8">
-        <v>1156</v>
+        <v>1109</v>
       </c>
       <c r="O30" s="8"/>
       <c r="P30" s="8"/>
@@ -5361,7 +5547,7 @@
         <v>13</v>
       </c>
       <c r="I31" s="8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J31" s="8">
         <v>0</v>
@@ -5374,7 +5560,7 @@
       </c>
       <c r="M31" s="8">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N31" s="8">
         <v>0</v>
@@ -5412,23 +5598,23 @@
         <v>12</v>
       </c>
       <c r="I32" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J32" s="8">
         <v>0</v>
       </c>
       <c r="K32" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L32" s="8">
         <v>0</v>
       </c>
       <c r="M32" s="8">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N32" s="8">
-        <v>1037</v>
+        <v>1023</v>
       </c>
       <c r="O32" s="8"/>
       <c r="P32" s="8"/>
@@ -5469,17 +5655,17 @@
         <v>0</v>
       </c>
       <c r="K33" s="8">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="L33" s="8">
         <v>0</v>
       </c>
       <c r="M33" s="8">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="N33" s="8">
-        <v>210</v>
+        <v>182</v>
       </c>
       <c r="O33" s="8"/>
       <c r="P33" s="8"/>
@@ -5514,23 +5700,23 @@
         <v>12</v>
       </c>
       <c r="I34" s="8">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J34" s="8">
         <v>0</v>
       </c>
       <c r="K34" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L34" s="8">
         <v>0</v>
       </c>
       <c r="M34" s="8">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="N34" s="8">
-        <v>1207</v>
+        <v>1195</v>
       </c>
       <c r="O34" s="8"/>
       <c r="P34" s="8"/>
@@ -5565,13 +5751,13 @@
         <v>12</v>
       </c>
       <c r="I35" s="8">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J35" s="8">
         <v>0</v>
       </c>
       <c r="K35" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L35" s="8">
         <v>0</v>
@@ -5581,7 +5767,7 @@
         <v>17</v>
       </c>
       <c r="N35" s="8">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="O35" s="8"/>
       <c r="P35" s="8"/>
@@ -5632,7 +5818,7 @@
         <v>15</v>
       </c>
       <c r="N36" s="8">
-        <v>408</v>
+        <v>386</v>
       </c>
       <c r="O36" s="8"/>
       <c r="P36" s="8"/>
@@ -5667,7 +5853,7 @@
         <v>13</v>
       </c>
       <c r="I37" s="8">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J37" s="8">
         <v>0</v>
@@ -5680,10 +5866,10 @@
       </c>
       <c r="M37" s="8">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N37" s="8">
-        <v>212</v>
+        <v>36</v>
       </c>
       <c r="O37" s="8"/>
       <c r="P37" s="8"/>
@@ -5724,17 +5910,17 @@
         <v>0</v>
       </c>
       <c r="K38" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38" s="8">
         <v>0</v>
       </c>
       <c r="M38" s="8">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N38" s="8">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="O38" s="8"/>
       <c r="P38" s="8"/>
@@ -5769,7 +5955,7 @@
         <v>12</v>
       </c>
       <c r="I39" s="8">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J39" s="8">
         <v>0</v>
@@ -5782,10 +5968,10 @@
       </c>
       <c r="M39" s="8">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N39" s="8">
-        <v>2519</v>
+        <v>2429</v>
       </c>
       <c r="O39" s="8"/>
       <c r="P39" s="8"/>
@@ -5826,17 +6012,17 @@
         <v>0</v>
       </c>
       <c r="K40" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L40" s="8">
         <v>0</v>
       </c>
       <c r="M40" s="8">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="N40" s="8">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="O40" s="8"/>
       <c r="P40" s="8"/>
@@ -5871,23 +6057,23 @@
         <v>12</v>
       </c>
       <c r="I41" s="8">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J41" s="8">
         <v>0</v>
       </c>
       <c r="K41" s="8">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L41" s="8">
         <v>0</v>
       </c>
       <c r="M41" s="8">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N41" s="8">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="O41" s="8"/>
       <c r="P41" s="8"/>
@@ -5922,23 +6108,23 @@
         <v>13</v>
       </c>
       <c r="I42" s="8">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J42" s="8">
         <v>0</v>
       </c>
       <c r="K42" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L42" s="8">
         <v>0</v>
       </c>
       <c r="M42" s="8">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N42" s="8">
-        <v>1180</v>
+        <v>1069</v>
       </c>
       <c r="O42" s="8"/>
       <c r="P42" s="8"/>
@@ -5973,23 +6159,23 @@
         <v>12</v>
       </c>
       <c r="I43" s="8">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J43" s="8">
         <v>0</v>
       </c>
       <c r="K43" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L43" s="8">
         <v>0</v>
       </c>
       <c r="M43" s="8">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="N43" s="8">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="O43" s="8"/>
       <c r="P43" s="8"/>
@@ -6024,13 +6210,13 @@
         <v>12</v>
       </c>
       <c r="I44" s="8">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J44" s="8">
         <v>0</v>
       </c>
       <c r="K44" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L44" s="8">
         <v>0</v>
@@ -6040,7 +6226,7 @@
         <v>12</v>
       </c>
       <c r="N44" s="8">
-        <v>732</v>
+        <v>719</v>
       </c>
       <c r="O44" s="8"/>
       <c r="P44" s="8"/>
@@ -6078,20 +6264,20 @@
         <v>3</v>
       </c>
       <c r="J45" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K45" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L45" s="8">
         <v>0</v>
       </c>
       <c r="M45" s="8">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N45" s="8">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="O45" s="8"/>
       <c r="P45" s="8"/>
@@ -6126,13 +6312,13 @@
         <v>12</v>
       </c>
       <c r="I46" s="8">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J46" s="8">
         <v>0</v>
       </c>
       <c r="K46" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L46" s="8">
         <v>0</v>
@@ -6142,7 +6328,7 @@
         <v>19</v>
       </c>
       <c r="N46" s="8">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="O46" s="8"/>
       <c r="P46" s="8"/>
@@ -6177,23 +6363,23 @@
         <v>13</v>
       </c>
       <c r="I47" s="8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J47" s="8">
         <v>0</v>
       </c>
       <c r="K47" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" s="8">
         <v>0</v>
       </c>
       <c r="M47" s="8">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N47" s="8">
-        <v>355</v>
+        <v>332</v>
       </c>
       <c r="O47" s="8"/>
       <c r="P47" s="8"/>
@@ -6228,7 +6414,7 @@
         <v>12</v>
       </c>
       <c r="I48" s="8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J48" s="8">
         <v>0</v>
@@ -6241,10 +6427,10 @@
       </c>
       <c r="M48" s="8">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N48" s="8">
-        <v>2040</v>
+        <v>1906</v>
       </c>
       <c r="O48" s="8"/>
       <c r="P48" s="8"/>
@@ -6295,7 +6481,7 @@
         <v>18</v>
       </c>
       <c r="N49" s="8">
-        <v>675</v>
+        <v>657</v>
       </c>
       <c r="O49" s="8"/>
       <c r="P49" s="8"/>
@@ -6330,13 +6516,13 @@
         <v>15</v>
       </c>
       <c r="I50" s="8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J50" s="8">
         <v>0</v>
       </c>
       <c r="K50" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" s="8">
         <v>0</v>
@@ -6381,23 +6567,23 @@
         <v>12</v>
       </c>
       <c r="I51" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J51" s="8">
         <v>0</v>
       </c>
       <c r="K51" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L51" s="8">
         <v>0</v>
       </c>
       <c r="M51" s="8">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N51" s="8">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="O51" s="8"/>
       <c r="P51" s="8"/>
@@ -6432,23 +6618,23 @@
         <v>12</v>
       </c>
       <c r="I52" s="8">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="J52" s="8">
         <v>0</v>
       </c>
       <c r="K52" s="8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L52" s="8">
         <v>0</v>
       </c>
       <c r="M52" s="8">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N52" s="8">
-        <v>2961</v>
+        <v>2592</v>
       </c>
       <c r="O52" s="8"/>
       <c r="P52" s="8"/>
@@ -6483,7 +6669,7 @@
         <v>12</v>
       </c>
       <c r="I53" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J53" s="8">
         <v>0</v>
@@ -6496,10 +6682,10 @@
       </c>
       <c r="M53" s="8">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N53" s="8">
-        <v>301</v>
+        <v>279</v>
       </c>
       <c r="O53" s="8"/>
       <c r="P53" s="8"/>
@@ -6534,23 +6720,23 @@
         <v>12</v>
       </c>
       <c r="I54" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J54" s="8">
         <v>0</v>
       </c>
       <c r="K54" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54" s="8">
         <v>0</v>
       </c>
       <c r="M54" s="8">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N54" s="8">
-        <v>745</v>
+        <v>647</v>
       </c>
       <c r="O54" s="8"/>
       <c r="P54" s="8"/>
@@ -6585,7 +6771,7 @@
         <v>12</v>
       </c>
       <c r="I55" s="8">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J55" s="8">
         <v>0</v>
@@ -6598,10 +6784,10 @@
       </c>
       <c r="M55" s="8">
         <f t="shared" si="0"/>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N55" s="8">
-        <v>342</v>
+        <v>784</v>
       </c>
       <c r="O55" s="8"/>
       <c r="P55" s="8"/>
@@ -6652,7 +6838,7 @@
         <v>7</v>
       </c>
       <c r="N56" s="8">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="O56" s="8"/>
       <c r="P56" s="8"/>
@@ -6687,20 +6873,20 @@
         <v>12</v>
       </c>
       <c r="I57" s="8">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J57" s="8">
         <v>0</v>
       </c>
       <c r="K57" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L57" s="8">
         <v>0</v>
       </c>
       <c r="M57" s="8">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="N57" s="8">
         <v>845</v>
@@ -6754,7 +6940,7 @@
         <v>7</v>
       </c>
       <c r="N58" s="8">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="O58" s="8"/>
       <c r="P58" s="8"/>
@@ -6805,7 +6991,7 @@
         <v>10</v>
       </c>
       <c r="N59" s="8">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="O59" s="8"/>
       <c r="P59" s="8"/>
@@ -6856,7 +7042,7 @@
         <v>6</v>
       </c>
       <c r="N60" s="8">
-        <v>642</v>
+        <v>625</v>
       </c>
       <c r="O60" s="8"/>
       <c r="P60" s="8"/>
@@ -6891,13 +7077,13 @@
         <v>12</v>
       </c>
       <c r="I61" s="8">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J61" s="8">
         <v>0</v>
       </c>
       <c r="K61" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L61" s="8">
         <v>0</v>
@@ -6907,7 +7093,7 @@
         <v>14</v>
       </c>
       <c r="N61" s="8">
-        <v>335</v>
+        <v>240</v>
       </c>
       <c r="O61" s="8"/>
       <c r="P61" s="8"/>
@@ -6958,7 +7144,7 @@
         <v>11</v>
       </c>
       <c r="N62" s="8">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="O62" s="8"/>
       <c r="P62" s="8"/>
@@ -6993,7 +7179,7 @@
         <v>12</v>
       </c>
       <c r="I63" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J63" s="8">
         <v>0</v>
@@ -7006,10 +7192,10 @@
       </c>
       <c r="M63" s="8">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N63" s="8">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="O63" s="8"/>
       <c r="P63" s="8"/>
@@ -7044,23 +7230,23 @@
         <v>13</v>
       </c>
       <c r="I64" s="8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J64" s="8">
         <v>0</v>
       </c>
       <c r="K64" s="8">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L64" s="8">
         <v>0</v>
       </c>
       <c r="M64" s="8">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="N64" s="8">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="O64" s="8"/>
       <c r="P64" s="8"/>
@@ -7095,7 +7281,7 @@
         <v>12</v>
       </c>
       <c r="I65" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J65" s="8">
         <v>0</v>
@@ -7108,10 +7294,10 @@
       </c>
       <c r="M65" s="8">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N65" s="8">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="O65" s="8"/>
       <c r="P65" s="8"/>
@@ -7197,10 +7383,10 @@
         <v>12</v>
       </c>
       <c r="I67" s="8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J67" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K67" s="8">
         <v>0</v>
@@ -7213,7 +7399,7 @@
         <v>7</v>
       </c>
       <c r="N67" s="8">
-        <v>587</v>
+        <v>476</v>
       </c>
       <c r="O67" s="8"/>
       <c r="P67" s="8"/>
@@ -7264,7 +7450,7 @@
         <v>7</v>
       </c>
       <c r="N68" s="8">
-        <v>889</v>
+        <v>881</v>
       </c>
       <c r="O68" s="8"/>
       <c r="P68" s="8"/>
@@ -7299,23 +7485,23 @@
         <v>12</v>
       </c>
       <c r="I69" s="8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J69" s="8">
         <v>0</v>
       </c>
       <c r="K69" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L69" s="8">
         <v>0</v>
       </c>
       <c r="M69" s="8">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N69" s="8">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="O69" s="8"/>
       <c r="P69" s="8"/>
@@ -7350,10 +7536,10 @@
         <v>16</v>
       </c>
       <c r="I70" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J70" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K70" s="8">
         <v>0</v>
@@ -7363,10 +7549,10 @@
       </c>
       <c r="M70" s="8">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N70" s="8">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="O70" s="8"/>
       <c r="P70" s="8"/>
@@ -7401,7 +7587,7 @@
         <v>12</v>
       </c>
       <c r="I71" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J71" s="8">
         <v>0</v>
@@ -7414,10 +7600,10 @@
       </c>
       <c r="M71" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N71" s="8">
-        <v>281</v>
+        <v>221</v>
       </c>
       <c r="O71" s="8"/>
       <c r="P71" s="8"/>
@@ -7468,7 +7654,7 @@
         <v>13</v>
       </c>
       <c r="N72" s="8">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O72" s="8"/>
       <c r="P72" s="8"/>
@@ -7503,23 +7689,23 @@
         <v>12</v>
       </c>
       <c r="I73" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J73" s="8">
         <v>0</v>
       </c>
       <c r="K73" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L73" s="8">
         <v>0</v>
       </c>
       <c r="M73" s="8">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N73" s="8">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="O73" s="8"/>
       <c r="P73" s="8"/>
@@ -7554,7 +7740,7 @@
         <v>14</v>
       </c>
       <c r="I74" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J74" s="8">
         <v>0</v>
@@ -7567,10 +7753,10 @@
       </c>
       <c r="M74" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N74" s="8">
-        <v>498</v>
+        <v>480</v>
       </c>
       <c r="O74" s="8"/>
       <c r="P74" s="8"/>
@@ -7605,10 +7791,10 @@
         <v>13</v>
       </c>
       <c r="I75" s="8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J75" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K75" s="8">
         <v>0</v>
@@ -7621,7 +7807,7 @@
         <v>8</v>
       </c>
       <c r="N75" s="8">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O75" s="8"/>
       <c r="P75" s="8"/>
@@ -7656,10 +7842,10 @@
         <v>13</v>
       </c>
       <c r="I76" s="8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J76" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K76" s="8">
         <v>0</v>
@@ -7672,7 +7858,7 @@
         <v>7</v>
       </c>
       <c r="N76" s="8">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="O76" s="8"/>
       <c r="P76" s="8"/>
@@ -7707,10 +7893,10 @@
         <v>12</v>
       </c>
       <c r="I77" s="8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J77" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K77" s="8">
         <v>0</v>
@@ -7723,7 +7909,7 @@
         <v>7</v>
       </c>
       <c r="N77" s="8">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="O77" s="8"/>
       <c r="P77" s="8"/>
@@ -7758,13 +7944,13 @@
         <v>12</v>
       </c>
       <c r="I78" s="8">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J78" s="8">
         <v>0</v>
       </c>
       <c r="K78" s="8">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L78" s="8">
         <v>0</v>
@@ -7774,7 +7960,7 @@
         <v>15</v>
       </c>
       <c r="N78" s="8">
-        <v>1037</v>
+        <v>997</v>
       </c>
       <c r="O78" s="8"/>
       <c r="P78" s="8"/>
@@ -7825,7 +8011,7 @@
         <v>11</v>
       </c>
       <c r="N79" s="8">
-        <v>271</v>
+        <v>196</v>
       </c>
       <c r="O79" s="8"/>
       <c r="P79" s="8"/>
@@ -7876,7 +8062,7 @@
         <v>6</v>
       </c>
       <c r="N80" s="8">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="O80" s="8"/>
       <c r="P80" s="8"/>
@@ -7911,13 +8097,13 @@
         <v>15</v>
       </c>
       <c r="I81" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J81" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K81" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L81" s="8">
         <v>0</v>
@@ -7962,13 +8148,13 @@
         <v>15</v>
       </c>
       <c r="I82" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J82" s="8">
         <v>0</v>
       </c>
       <c r="K82" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82" s="8">
         <v>0</v>
@@ -7978,7 +8164,7 @@
         <v>5</v>
       </c>
       <c r="N82" s="8">
-        <v>518</v>
+        <v>505</v>
       </c>
       <c r="O82" s="8"/>
       <c r="P82" s="8"/>
@@ -8013,10 +8199,10 @@
         <v>15</v>
       </c>
       <c r="I83" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J83" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K83" s="8">
         <v>0</v>
@@ -8029,7 +8215,7 @@
         <v>6</v>
       </c>
       <c r="N83" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O83" s="8"/>
       <c r="P83" s="8"/>
@@ -8064,7 +8250,7 @@
         <v>13</v>
       </c>
       <c r="I84" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J84" s="8">
         <v>0</v>
@@ -8077,7 +8263,7 @@
       </c>
       <c r="M84" s="8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N84" s="8">
         <v>0</v>
@@ -8131,7 +8317,7 @@
         <v>7</v>
       </c>
       <c r="N85" s="8">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O85" s="8"/>
       <c r="P85" s="8"/>
@@ -8166,13 +8352,13 @@
         <v>12</v>
       </c>
       <c r="I86" s="8">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J86" s="8">
         <v>0</v>
       </c>
       <c r="K86" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L86" s="8">
         <v>0</v>
@@ -8182,7 +8368,7 @@
         <v>19</v>
       </c>
       <c r="N86" s="8">
-        <v>503</v>
+        <v>782</v>
       </c>
       <c r="O86" s="8"/>
       <c r="P86" s="8"/>
@@ -8217,23 +8403,23 @@
         <v>13</v>
       </c>
       <c r="I87" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J87" s="8">
         <v>0</v>
       </c>
       <c r="K87" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L87" s="8">
         <v>0</v>
       </c>
       <c r="M87" s="8">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N87" s="8">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O87" s="8"/>
       <c r="P87" s="8"/>
@@ -8268,13 +8454,13 @@
         <v>12</v>
       </c>
       <c r="I88" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J88" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K88" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L88" s="8">
         <v>0</v>
@@ -8284,7 +8470,7 @@
         <v>5</v>
       </c>
       <c r="N88" s="8">
-        <v>454</v>
+        <v>391</v>
       </c>
       <c r="O88" s="8"/>
       <c r="P88" s="8"/>
@@ -8319,23 +8505,23 @@
         <v>12</v>
       </c>
       <c r="I89" s="8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J89" s="8">
         <v>0</v>
       </c>
       <c r="K89" s="8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L89" s="8">
         <v>0</v>
       </c>
       <c r="M89" s="8">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N89" s="8">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="O89" s="8"/>
       <c r="P89" s="8"/>
@@ -8370,10 +8556,10 @@
         <v>12</v>
       </c>
       <c r="I90" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J90" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K90" s="8">
         <v>0</v>
@@ -8386,7 +8572,7 @@
         <v>7</v>
       </c>
       <c r="N90" s="8">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O90" s="8"/>
       <c r="P90" s="8"/>
@@ -8421,10 +8607,10 @@
         <v>12</v>
       </c>
       <c r="I91" s="8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J91" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K91" s="8">
         <v>0</v>
@@ -8437,7 +8623,7 @@
         <v>6</v>
       </c>
       <c r="N91" s="8">
-        <v>1103</v>
+        <v>1095</v>
       </c>
       <c r="O91" s="8"/>
       <c r="P91" s="8"/>
@@ -8472,7 +8658,7 @@
         <v>12</v>
       </c>
       <c r="I92" s="8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J92" s="8">
         <v>0</v>
@@ -8485,10 +8671,10 @@
       </c>
       <c r="M92" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N92" s="8">
-        <v>624</v>
+        <v>535</v>
       </c>
       <c r="O92" s="8"/>
       <c r="P92" s="8"/>
@@ -8529,17 +8715,17 @@
         <v>0</v>
       </c>
       <c r="K93" s="8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L93" s="8">
         <v>0</v>
       </c>
       <c r="M93" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="N93" s="8">
-        <v>240</v>
+        <v>201</v>
       </c>
       <c r="O93" s="8"/>
       <c r="P93" s="8"/>
@@ -8641,7 +8827,7 @@
         <v>9</v>
       </c>
       <c r="N95" s="8">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="O95" s="8"/>
       <c r="P95" s="8"/>
@@ -8682,17 +8868,17 @@
         <v>0</v>
       </c>
       <c r="K96" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L96" s="8">
         <v>0</v>
       </c>
       <c r="M96" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N96" s="8">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="O96" s="8"/>
       <c r="P96" s="8"/>
@@ -8727,23 +8913,23 @@
         <v>14</v>
       </c>
       <c r="I97" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J97" s="8">
         <v>0</v>
       </c>
       <c r="K97" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L97" s="8">
         <v>0</v>
       </c>
       <c r="M97" s="8">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N97" s="8">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="O97" s="8"/>
       <c r="P97" s="8"/>
@@ -8896,7 +9082,7 @@
         <v>7</v>
       </c>
       <c r="N100" s="8">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="O100" s="8"/>
       <c r="P100" s="8"/>
@@ -8982,23 +9168,23 @@
         <v>14</v>
       </c>
       <c r="I102" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J102" s="8">
         <v>0</v>
       </c>
       <c r="K102" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L102" s="8">
         <v>0</v>
       </c>
       <c r="M102" s="8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N102" s="8">
-        <v>772</v>
+        <v>730</v>
       </c>
       <c r="O102" s="8"/>
       <c r="P102" s="8"/>
@@ -9049,7 +9235,7 @@
         <v>4</v>
       </c>
       <c r="N103" s="8">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="O103" s="8"/>
       <c r="P103" s="8"/>
@@ -9151,7 +9337,7 @@
         <v>6</v>
       </c>
       <c r="N105" s="8">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="O105" s="8"/>
       <c r="P105" s="8"/>
@@ -9202,7 +9388,7 @@
         <v>6</v>
       </c>
       <c r="N106" s="8">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="O106" s="8"/>
       <c r="P106" s="8"/>
@@ -9253,7 +9439,7 @@
         <v>4</v>
       </c>
       <c r="N107" s="8">
-        <v>176</v>
+        <v>135</v>
       </c>
       <c r="O107" s="8"/>
       <c r="P107" s="8"/>
@@ -9339,7 +9525,7 @@
         <v>13</v>
       </c>
       <c r="I109" s="8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J109" s="8">
         <v>0</v>
@@ -9352,10 +9538,10 @@
       </c>
       <c r="M109" s="8">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N109" s="8">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="O109" s="8"/>
       <c r="P109" s="8"/>
@@ -9390,7 +9576,7 @@
         <v>13</v>
       </c>
       <c r="I110" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J110" s="8">
         <v>0</v>
@@ -9403,10 +9589,10 @@
       </c>
       <c r="M110" s="8">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N110" s="8">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="O110" s="8"/>
       <c r="P110" s="8"/>
@@ -9441,7 +9627,7 @@
         <v>13</v>
       </c>
       <c r="I111" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J111" s="8">
         <v>0</v>
@@ -9454,7 +9640,7 @@
       </c>
       <c r="M111" s="8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N111" s="8">
         <v>0</v>
@@ -9492,7 +9678,7 @@
         <v>12</v>
       </c>
       <c r="I112" s="8">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="J112" s="8">
         <v>0</v>
@@ -9505,7 +9691,7 @@
       </c>
       <c r="M112" s="8">
         <f t="shared" si="1"/>
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="N112" s="8">
         <v>0</v>
@@ -9543,23 +9729,23 @@
         <v>12</v>
       </c>
       <c r="I113" s="8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J113" s="8">
         <v>0</v>
       </c>
       <c r="K113" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L113" s="8">
         <v>0</v>
       </c>
       <c r="M113" s="8">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N113" s="8">
-        <v>1154</v>
+        <v>1050</v>
       </c>
       <c r="O113" s="8"/>
       <c r="P113" s="8"/>
@@ -9600,17 +9786,17 @@
         <v>0</v>
       </c>
       <c r="K114" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L114" s="8">
         <v>0</v>
       </c>
       <c r="M114" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N114" s="8">
-        <v>410</v>
+        <v>294</v>
       </c>
       <c r="O114" s="8"/>
       <c r="P114" s="8"/>
@@ -9661,7 +9847,7 @@
         <v>10</v>
       </c>
       <c r="N115" s="8">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="O115" s="8"/>
       <c r="P115" s="8"/>
@@ -9702,17 +9888,17 @@
         <v>0</v>
       </c>
       <c r="K116" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L116" s="8">
         <v>0</v>
       </c>
       <c r="M116" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N116" s="8">
-        <v>967</v>
+        <v>956</v>
       </c>
       <c r="O116" s="8"/>
       <c r="P116" s="8"/>
@@ -9763,7 +9949,7 @@
         <v>9</v>
       </c>
       <c r="N117" s="8">
-        <v>107</v>
+        <v>63</v>
       </c>
       <c r="O117" s="8"/>
       <c r="P117" s="8"/>
@@ -9804,14 +9990,14 @@
         <v>0</v>
       </c>
       <c r="K118" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L118" s="8">
         <v>0</v>
       </c>
       <c r="M118" s="8">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N118" s="8">
         <v>77</v>
@@ -9849,13 +10035,13 @@
         <v>14</v>
       </c>
       <c r="I119" s="8">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J119" s="8">
         <v>0</v>
       </c>
       <c r="K119" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L119" s="8">
         <v>0</v>
@@ -9865,7 +10051,7 @@
         <v>15</v>
       </c>
       <c r="N119" s="8">
-        <v>409</v>
+        <v>379</v>
       </c>
       <c r="O119" s="8"/>
       <c r="P119" s="8"/>
@@ -9906,17 +10092,17 @@
         <v>0</v>
       </c>
       <c r="K120" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L120" s="8">
         <v>0</v>
       </c>
       <c r="M120" s="8">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="N120" s="8">
-        <v>488</v>
+        <v>419</v>
       </c>
       <c r="O120" s="8"/>
       <c r="P120" s="8"/>
@@ -9967,7 +10153,7 @@
         <v>8</v>
       </c>
       <c r="N121" s="8">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="O121" s="8"/>
       <c r="P121" s="8"/>
@@ -10008,17 +10194,17 @@
         <v>0</v>
       </c>
       <c r="K122" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L122" s="8">
         <v>0</v>
       </c>
       <c r="M122" s="8">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N122" s="8">
-        <v>1137</v>
+        <v>1132</v>
       </c>
       <c r="O122" s="8"/>
       <c r="P122" s="8"/>
@@ -10053,10 +10239,10 @@
         <v>14</v>
       </c>
       <c r="I123" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J123" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K123" s="8">
         <v>0</v>
@@ -10155,7 +10341,7 @@
         <v>13</v>
       </c>
       <c r="I125" s="8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J125" s="8">
         <v>0</v>
@@ -10168,10 +10354,10 @@
       </c>
       <c r="M125" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N125" s="8">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="O125" s="8"/>
       <c r="P125" s="8"/>
@@ -10206,10 +10392,10 @@
         <v>17</v>
       </c>
       <c r="I126" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J126" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K126" s="8">
         <v>0</v>
@@ -10273,7 +10459,7 @@
         <v>3</v>
       </c>
       <c r="N127" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O127" s="8"/>
       <c r="P127" s="8"/>
@@ -10324,7 +10510,7 @@
         <v>3</v>
       </c>
       <c r="N128" s="8">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="O128" s="8"/>
       <c r="P128" s="8"/>
@@ -10410,23 +10596,23 @@
         <v>12</v>
       </c>
       <c r="I130" s="8">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J130" s="8">
         <v>0</v>
       </c>
       <c r="K130" s="8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L130" s="8">
         <v>0</v>
       </c>
       <c r="M130" s="8">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N130" s="8">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="O130" s="8"/>
       <c r="P130" s="8"/>
@@ -10477,7 +10663,7 @@
         <v>5</v>
       </c>
       <c r="N131" s="8">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="O131" s="8"/>
       <c r="P131" s="8"/>
@@ -10512,23 +10698,23 @@
         <v>12</v>
       </c>
       <c r="I132" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J132" s="8">
         <v>0</v>
       </c>
       <c r="K132" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L132" s="8">
         <v>0</v>
       </c>
       <c r="M132" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N132" s="8">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="O132" s="8"/>
       <c r="P132" s="8"/>
@@ -10563,7 +10749,7 @@
         <v>12</v>
       </c>
       <c r="I133" s="8">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J133" s="8">
         <v>0</v>
@@ -10576,10 +10762,10 @@
       </c>
       <c r="M133" s="8">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N133" s="8">
-        <v>365</v>
+        <v>180</v>
       </c>
       <c r="O133" s="8"/>
       <c r="P133" s="8"/>
@@ -10614,10 +10800,10 @@
         <v>15</v>
       </c>
       <c r="I134" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J134" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K134" s="8">
         <v>0</v>
@@ -10630,7 +10816,7 @@
         <v>4</v>
       </c>
       <c r="N134" s="8">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="O134" s="8"/>
       <c r="P134" s="8"/>
@@ -10681,7 +10867,7 @@
         <v>4</v>
       </c>
       <c r="N135" s="8">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="O135" s="8"/>
       <c r="P135" s="8"/>
@@ -10732,7 +10918,7 @@
         <v>3</v>
       </c>
       <c r="N136" s="8">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="O136" s="8"/>
       <c r="P136" s="8"/>
@@ -10767,7 +10953,7 @@
         <v>15</v>
       </c>
       <c r="I137" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J137" s="8">
         <v>0</v>
@@ -10780,10 +10966,10 @@
       </c>
       <c r="M137" s="8">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N137" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O137" s="8"/>
       <c r="P137" s="8"/>
@@ -10869,10 +11055,10 @@
         <v>15</v>
       </c>
       <c r="I139" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J139" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K139" s="8">
         <v>0</v>
@@ -10882,7 +11068,7 @@
       </c>
       <c r="M139" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N139" s="8">
         <v>0</v>
@@ -10920,10 +11106,10 @@
         <v>15</v>
       </c>
       <c r="I140" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J140" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K140" s="8">
         <v>0</v>
@@ -10936,7 +11122,7 @@
         <v>5</v>
       </c>
       <c r="N140" s="8">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="O140" s="8"/>
       <c r="P140" s="8"/>
@@ -10971,13 +11157,13 @@
         <v>13</v>
       </c>
       <c r="I141" s="8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J141" s="8">
         <v>0</v>
       </c>
       <c r="K141" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L141" s="8">
         <v>0</v>
@@ -11079,17 +11265,17 @@
         <v>0</v>
       </c>
       <c r="K143" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L143" s="8">
         <v>0</v>
       </c>
       <c r="M143" s="8">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N143" s="8">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O143" s="8"/>
       <c r="P143" s="8"/>
@@ -11175,10 +11361,10 @@
         <v>14</v>
       </c>
       <c r="I145" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J145" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K145" s="8">
         <v>0</v>
@@ -11191,7 +11377,7 @@
         <v>5</v>
       </c>
       <c r="N145" s="8">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="O145" s="8"/>
       <c r="P145" s="8"/>
@@ -11293,7 +11479,7 @@
         <v>4</v>
       </c>
       <c r="N147" s="8">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="O147" s="8"/>
       <c r="P147" s="8"/>
@@ -11379,10 +11565,10 @@
         <v>12</v>
       </c>
       <c r="I149" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J149" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K149" s="8">
         <v>0</v>
@@ -11395,7 +11581,7 @@
         <v>4</v>
       </c>
       <c r="N149" s="8">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="O149" s="8"/>
       <c r="P149" s="8"/>
@@ -11446,7 +11632,7 @@
         <v>3</v>
       </c>
       <c r="N150" s="8">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="O150" s="8"/>
       <c r="P150" s="8"/>
@@ -11481,23 +11667,23 @@
         <v>13</v>
       </c>
       <c r="I151" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J151" s="8">
         <v>0</v>
       </c>
       <c r="K151" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L151" s="8">
         <v>0</v>
       </c>
       <c r="M151" s="8">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N151" s="8">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O151" s="8"/>
       <c r="P151" s="8"/>
@@ -11532,10 +11718,10 @@
         <v>15</v>
       </c>
       <c r="I152" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J152" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K152" s="8">
         <v>0</v>
@@ -11548,7 +11734,7 @@
         <v>5</v>
       </c>
       <c r="N152" s="8">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="O152" s="8"/>
       <c r="P152" s="8"/>
@@ -11589,17 +11775,17 @@
         <v>0</v>
       </c>
       <c r="K153" s="8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L153" s="8">
         <v>0</v>
       </c>
       <c r="M153" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N153" s="8">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="O153" s="8"/>
       <c r="P153" s="8"/>
@@ -11634,10 +11820,10 @@
         <v>15</v>
       </c>
       <c r="I154" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J154" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K154" s="8">
         <v>0</v>
@@ -11650,7 +11836,7 @@
         <v>5</v>
       </c>
       <c r="N154" s="8">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="O154" s="8"/>
       <c r="P154" s="8"/>
@@ -11889,10 +12075,10 @@
         <v>15</v>
       </c>
       <c r="I159" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J159" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K159" s="8">
         <v>0</v>
@@ -11940,10 +12126,10 @@
         <v>15</v>
       </c>
       <c r="I160" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J160" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K160" s="8">
         <v>0</v>
@@ -11956,7 +12142,7 @@
         <v>5</v>
       </c>
       <c r="N160" s="8">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="O160" s="8"/>
       <c r="P160" s="8"/>
@@ -11991,23 +12177,23 @@
         <v>13</v>
       </c>
       <c r="I161" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J161" s="8">
         <v>0</v>
       </c>
       <c r="K161" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L161" s="8">
         <v>0</v>
       </c>
       <c r="M161" s="8">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N161" s="8">
-        <v>530</v>
+        <v>474</v>
       </c>
       <c r="O161" s="8"/>
       <c r="P161" s="8"/>
@@ -12042,10 +12228,10 @@
         <v>13</v>
       </c>
       <c r="I162" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J162" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K162" s="8">
         <v>0</v>
@@ -12058,7 +12244,7 @@
         <v>4</v>
       </c>
       <c r="N162" s="8">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="O162" s="8"/>
       <c r="P162" s="8"/>
@@ -12093,7 +12279,7 @@
         <v>16</v>
       </c>
       <c r="I163" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J163" s="8">
         <v>0</v>
@@ -12106,7 +12292,7 @@
       </c>
       <c r="M163" s="8">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N163" s="8">
         <v>0</v>
@@ -12211,7 +12397,7 @@
         <v>3</v>
       </c>
       <c r="N165" s="8">
-        <v>1699</v>
+        <v>1673</v>
       </c>
       <c r="O165" s="8"/>
       <c r="P165" s="8"/>
@@ -12246,10 +12432,10 @@
         <v>14</v>
       </c>
       <c r="I166" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J166" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K166" s="8">
         <v>0</v>
@@ -12262,7 +12448,7 @@
         <v>5</v>
       </c>
       <c r="N166" s="8">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="O166" s="8"/>
       <c r="P166" s="8"/>
@@ -12348,20 +12534,20 @@
         <v>14</v>
       </c>
       <c r="I168" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J168" s="8">
         <v>0</v>
       </c>
       <c r="K168" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L168" s="8">
         <v>0</v>
       </c>
       <c r="M168" s="8">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N168" s="8">
         <v>493</v>
@@ -12450,10 +12636,10 @@
         <v>14</v>
       </c>
       <c r="I170" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J170" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K170" s="8">
         <v>0</v>
@@ -12466,7 +12652,7 @@
         <v>5</v>
       </c>
       <c r="N170" s="8">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="O170" s="8"/>
       <c r="P170" s="8"/>
@@ -12501,7 +12687,7 @@
         <v>16</v>
       </c>
       <c r="I171" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J171" s="8">
         <v>0</v>
@@ -12514,7 +12700,7 @@
       </c>
       <c r="M171" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N171" s="8">
         <v>0</v>
@@ -12603,10 +12789,10 @@
         <v>14</v>
       </c>
       <c r="I173" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J173" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K173" s="8">
         <v>0</v>
@@ -12619,7 +12805,7 @@
         <v>4</v>
       </c>
       <c r="N173" s="8">
-        <v>718</v>
+        <v>675</v>
       </c>
       <c r="O173" s="8"/>
       <c r="P173" s="8"/>
@@ -12772,7 +12958,7 @@
         <v>3</v>
       </c>
       <c r="N176" s="8">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="O176" s="8"/>
       <c r="P176" s="8"/>
@@ -12925,7 +13111,7 @@
         <v>4</v>
       </c>
       <c r="N179" s="8">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="O179" s="8"/>
       <c r="P179" s="8"/>
@@ -12960,23 +13146,23 @@
         <v>13</v>
       </c>
       <c r="I180" s="8">
+        <v>1</v>
+      </c>
+      <c r="J180" s="8">
+        <v>0</v>
+      </c>
+      <c r="K180" s="8">
         <v>3</v>
-      </c>
-      <c r="J180" s="8">
-        <v>0</v>
-      </c>
-      <c r="K180" s="8">
-        <v>0</v>
       </c>
       <c r="L180" s="8">
         <v>0</v>
       </c>
       <c r="M180" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N180" s="8">
-        <v>382</v>
+        <v>330</v>
       </c>
       <c r="O180" s="8"/>
       <c r="P180" s="8"/>
@@ -13027,7 +13213,7 @@
         <v>5</v>
       </c>
       <c r="N181" s="8">
-        <v>345</v>
+        <v>315</v>
       </c>
       <c r="O181" s="8"/>
       <c r="P181" s="8"/>
@@ -13129,7 +13315,7 @@
         <v>7</v>
       </c>
       <c r="N183" s="8">
-        <v>288</v>
+        <v>263</v>
       </c>
       <c r="O183" s="8"/>
       <c r="P183" s="8"/>
@@ -13167,7 +13353,7 @@
         <v>2</v>
       </c>
       <c r="J184" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K184" s="8">
         <v>0</v>
@@ -13177,10 +13363,10 @@
       </c>
       <c r="M184" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N184" s="8">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="O184" s="8"/>
       <c r="P184" s="8"/>
@@ -13215,23 +13401,23 @@
         <v>12</v>
       </c>
       <c r="I185" s="8">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="J185" s="8">
         <v>0</v>
       </c>
       <c r="K185" s="8">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L185" s="8">
         <v>0</v>
       </c>
       <c r="M185" s="8">
         <f t="shared" si="2"/>
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="N185" s="8">
-        <v>1515</v>
+        <v>1502</v>
       </c>
       <c r="O185" s="8"/>
       <c r="P185" s="8"/>
@@ -13266,23 +13452,23 @@
         <v>12</v>
       </c>
       <c r="I186" s="8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J186" s="8">
         <v>0</v>
       </c>
       <c r="K186" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L186" s="8">
         <v>0</v>
       </c>
       <c r="M186" s="8">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N186" s="8">
-        <v>1115</v>
+        <v>1122</v>
       </c>
       <c r="O186" s="8"/>
       <c r="P186" s="8"/>
@@ -13333,7 +13519,7 @@
         <v>2</v>
       </c>
       <c r="N187" s="8">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="O187" s="8"/>
       <c r="P187" s="8"/>
@@ -13419,7 +13605,7 @@
         <v>12</v>
       </c>
       <c r="I189" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J189" s="8">
         <v>0</v>
@@ -13432,7 +13618,7 @@
       </c>
       <c r="M189" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N189" s="8">
         <v>0</v>
@@ -13470,23 +13656,23 @@
         <v>12</v>
       </c>
       <c r="I190" s="8">
+        <v>2</v>
+      </c>
+      <c r="J190" s="8">
+        <v>0</v>
+      </c>
+      <c r="K190" s="8">
         <v>3</v>
-      </c>
-      <c r="J190" s="8">
-        <v>0</v>
-      </c>
-      <c r="K190" s="8">
-        <v>0</v>
       </c>
       <c r="L190" s="8">
         <v>0</v>
       </c>
       <c r="M190" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N190" s="8">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="O190" s="8"/>
       <c r="P190" s="8"/>
@@ -13527,17 +13713,17 @@
         <v>0</v>
       </c>
       <c r="K191" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L191" s="8">
         <v>0</v>
       </c>
       <c r="M191" s="8">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N191" s="8">
-        <v>1330</v>
+        <v>1282</v>
       </c>
       <c r="O191" s="8"/>
       <c r="P191" s="8"/>
@@ -13680,14 +13866,14 @@
         <v>0</v>
       </c>
       <c r="K194" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L194" s="8">
         <v>0</v>
       </c>
       <c r="M194" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N194" s="8">
         <v>333</v>
@@ -13827,10 +14013,10 @@
         <v>12</v>
       </c>
       <c r="I197" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J197" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K197" s="8">
         <v>0</v>
@@ -13843,7 +14029,7 @@
         <v>5</v>
       </c>
       <c r="N197" s="8">
-        <v>353</v>
+        <v>287</v>
       </c>
       <c r="O197" s="8"/>
       <c r="P197" s="8"/>
@@ -13878,23 +14064,23 @@
         <v>12</v>
       </c>
       <c r="I198" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J198" s="8">
         <v>0</v>
       </c>
       <c r="K198" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L198" s="8">
         <v>0</v>
       </c>
       <c r="M198" s="8">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N198" s="8">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="O198" s="8"/>
       <c r="P198" s="8"/>
@@ -13945,7 +14131,7 @@
         <v>2</v>
       </c>
       <c r="N199" s="8">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="O199" s="8"/>
       <c r="P199" s="8"/>
@@ -14037,17 +14223,17 @@
         <v>0</v>
       </c>
       <c r="K201" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L201" s="8">
         <v>0</v>
       </c>
       <c r="M201" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N201" s="8">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O201" s="8"/>
       <c r="P201" s="8"/>
@@ -14235,10 +14421,10 @@
         <v>16</v>
       </c>
       <c r="I205" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J205" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K205" s="8">
         <v>0</v>
@@ -14251,7 +14437,7 @@
         <v>6</v>
       </c>
       <c r="N205" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O205" s="8"/>
       <c r="P205" s="8"/>
@@ -14286,10 +14472,10 @@
         <v>15</v>
       </c>
       <c r="I206" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J206" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K206" s="8">
         <v>0</v>
@@ -14302,7 +14488,7 @@
         <v>2</v>
       </c>
       <c r="N206" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O206" s="8"/>
       <c r="P206" s="8"/>
@@ -14353,7 +14539,7 @@
         <v>4</v>
       </c>
       <c r="N207" s="8">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="O207" s="8"/>
       <c r="P207" s="8"/>
@@ -14388,7 +14574,7 @@
         <v>14</v>
       </c>
       <c r="I208" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J208" s="8">
         <v>0</v>
@@ -14401,10 +14587,10 @@
       </c>
       <c r="M208" s="8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N208" s="8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O208" s="8"/>
       <c r="P208" s="8"/>
@@ -14455,7 +14641,7 @@
         <v>4</v>
       </c>
       <c r="N209" s="8">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O209" s="8"/>
       <c r="P209" s="8"/>
@@ -14490,7 +14676,7 @@
         <v>13</v>
       </c>
       <c r="I210" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J210" s="8">
         <v>0</v>
@@ -14503,7 +14689,7 @@
       </c>
       <c r="M210" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N210" s="8">
         <v>0</v>
@@ -14557,7 +14743,7 @@
         <v>4</v>
       </c>
       <c r="N211" s="8">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="O211" s="8"/>
       <c r="P211" s="8"/>
@@ -14643,23 +14829,23 @@
         <v>14</v>
       </c>
       <c r="I213" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J213" s="8">
         <v>0</v>
       </c>
       <c r="K213" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L213" s="8">
         <v>0</v>
       </c>
       <c r="M213" s="8">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="N213" s="8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O213" s="8"/>
       <c r="P213" s="8"/>
@@ -14694,23 +14880,23 @@
         <v>14</v>
       </c>
       <c r="I214" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J214" s="8">
         <v>0</v>
       </c>
       <c r="K214" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L214" s="8">
         <v>0</v>
       </c>
       <c r="M214" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N214" s="8">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="O214" s="8"/>
       <c r="P214" s="8"/>
@@ -14745,13 +14931,13 @@
         <v>14</v>
       </c>
       <c r="I215" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J215" s="8">
         <v>0</v>
       </c>
       <c r="K215" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L215" s="8">
         <v>0</v>
@@ -14761,7 +14947,7 @@
         <v>6</v>
       </c>
       <c r="N215" s="8">
-        <v>795</v>
+        <v>788</v>
       </c>
       <c r="O215" s="8"/>
       <c r="P215" s="8"/>
@@ -14802,17 +14988,17 @@
         <v>0</v>
       </c>
       <c r="K216" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L216" s="8">
         <v>0</v>
       </c>
       <c r="M216" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N216" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O216" s="8"/>
       <c r="P216" s="8"/>
@@ -14847,10 +15033,10 @@
         <v>13</v>
       </c>
       <c r="I217" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J217" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K217" s="8">
         <v>0</v>
@@ -14898,10 +15084,10 @@
         <v>13</v>
       </c>
       <c r="I218" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J218" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K218" s="8">
         <v>0</v>
@@ -14949,10 +15135,10 @@
         <v>13</v>
       </c>
       <c r="I219" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J219" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K219" s="8">
         <v>0</v>
@@ -14965,7 +15151,7 @@
         <v>6</v>
       </c>
       <c r="N219" s="8">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="O219" s="8"/>
       <c r="P219" s="8"/>
@@ -15016,7 +15202,7 @@
         <v>4</v>
       </c>
       <c r="N220" s="8">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="O220" s="8"/>
       <c r="P220" s="8"/>
@@ -15067,7 +15253,7 @@
         <v>4</v>
       </c>
       <c r="N221" s="8">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O221" s="8"/>
       <c r="P221" s="8"/>
@@ -15118,7 +15304,7 @@
         <v>2</v>
       </c>
       <c r="N222" s="8">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="O222" s="8"/>
       <c r="P222" s="8"/>
@@ -15169,7 +15355,7 @@
         <v>3</v>
       </c>
       <c r="N223" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O223" s="8"/>
       <c r="P223" s="8"/>
@@ -15204,10 +15390,10 @@
         <v>13</v>
       </c>
       <c r="I224" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J224" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K224" s="8">
         <v>0</v>
@@ -15255,10 +15441,10 @@
         <v>12</v>
       </c>
       <c r="I225" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J225" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K225" s="8">
         <v>0</v>
@@ -15271,7 +15457,7 @@
         <v>4</v>
       </c>
       <c r="N225" s="8">
-        <v>602</v>
+        <v>585</v>
       </c>
       <c r="O225" s="8"/>
       <c r="P225" s="8"/>
@@ -15306,7 +15492,7 @@
         <v>14</v>
       </c>
       <c r="I226" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J226" s="8">
         <v>0</v>
@@ -15319,10 +15505,10 @@
       </c>
       <c r="M226" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N226" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O226" s="8"/>
       <c r="P226" s="8"/>
@@ -15363,17 +15549,17 @@
         <v>0</v>
       </c>
       <c r="K227" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L227" s="8">
         <v>0</v>
       </c>
       <c r="M227" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N227" s="8">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="O227" s="8"/>
       <c r="P227" s="8"/>
@@ -15408,13 +15594,13 @@
         <v>15</v>
       </c>
       <c r="I228" s="8">
+        <v>0</v>
+      </c>
+      <c r="J228" s="8">
+        <v>0</v>
+      </c>
+      <c r="K228" s="8">
         <v>1</v>
-      </c>
-      <c r="J228" s="8">
-        <v>0</v>
-      </c>
-      <c r="K228" s="8">
-        <v>0</v>
       </c>
       <c r="L228" s="8">
         <v>0</v>
@@ -15424,7 +15610,7 @@
         <v>1</v>
       </c>
       <c r="N228" s="8">
-        <v>417</v>
+        <v>300</v>
       </c>
       <c r="O228" s="8"/>
       <c r="P228" s="8"/>
@@ -15475,7 +15661,7 @@
         <v>4</v>
       </c>
       <c r="N229" s="8">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="O229" s="8"/>
       <c r="P229" s="8"/>
@@ -15510,13 +15696,13 @@
         <v>15</v>
       </c>
       <c r="I230" s="8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J230" s="8">
         <v>0</v>
       </c>
       <c r="K230" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L230" s="8">
         <v>0</v>
@@ -15526,7 +15712,7 @@
         <v>5</v>
       </c>
       <c r="N230" s="8">
-        <v>149</v>
+        <v>4</v>
       </c>
       <c r="O230" s="8"/>
       <c r="P230" s="8"/>
@@ -15628,7 +15814,7 @@
         <v>16</v>
       </c>
       <c r="N232" s="8">
-        <v>995</v>
+        <v>957</v>
       </c>
       <c r="O232" s="8"/>
       <c r="P232" s="8"/>
@@ -15663,7 +15849,7 @@
         <v>15</v>
       </c>
       <c r="I233" s="8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J233" s="8">
         <v>0</v>
@@ -15676,10 +15862,10 @@
       </c>
       <c r="M233" s="8">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N233" s="8">
-        <v>909</v>
+        <v>896</v>
       </c>
       <c r="O233" s="8"/>
       <c r="P233" s="8"/>
@@ -15714,10 +15900,10 @@
         <v>15</v>
       </c>
       <c r="I234" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J234" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K234" s="8">
         <v>0</v>
@@ -15730,7 +15916,7 @@
         <v>2</v>
       </c>
       <c r="N234" s="8">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O234" s="8"/>
       <c r="P234" s="8"/>
@@ -15781,7 +15967,7 @@
         <v>3</v>
       </c>
       <c r="N235" s="8">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="O235" s="8"/>
       <c r="P235" s="8"/>
@@ -15883,7 +16069,7 @@
         <v>4</v>
       </c>
       <c r="N237" s="8">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="O237" s="8"/>
       <c r="P237" s="8"/>
@@ -15934,7 +16120,7 @@
         <v>7</v>
       </c>
       <c r="N238" s="8">
-        <v>370</v>
+        <v>344</v>
       </c>
       <c r="O238" s="8"/>
       <c r="P238" s="8"/>
@@ -15969,10 +16155,10 @@
         <v>15</v>
       </c>
       <c r="I239" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J239" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K239" s="8">
         <v>0</v>
@@ -15985,7 +16171,7 @@
         <v>5</v>
       </c>
       <c r="N239" s="8">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="O239" s="8"/>
       <c r="P239" s="8"/>
@@ -16020,23 +16206,23 @@
         <v>13</v>
       </c>
       <c r="I240" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J240" s="8">
         <v>0</v>
       </c>
       <c r="K240" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L240" s="8">
         <v>0</v>
       </c>
       <c r="M240" s="8">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N240" s="8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O240" s="8"/>
       <c r="P240" s="8"/>
@@ -16071,23 +16257,23 @@
         <v>14</v>
       </c>
       <c r="I241" s="8">
+        <v>2</v>
+      </c>
+      <c r="J241" s="8">
+        <v>0</v>
+      </c>
+      <c r="K241" s="8">
         <v>1</v>
-      </c>
-      <c r="J241" s="8">
-        <v>1</v>
-      </c>
-      <c r="K241" s="8">
-        <v>0</v>
       </c>
       <c r="L241" s="8">
         <v>0</v>
       </c>
       <c r="M241" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N241" s="8">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="O241" s="8"/>
       <c r="P241" s="8"/>
@@ -16138,7 +16324,7 @@
         <v>2</v>
       </c>
       <c r="N242" s="8">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O242" s="8"/>
       <c r="P242" s="8"/>
@@ -16173,13 +16359,13 @@
         <v>15</v>
       </c>
       <c r="I243" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J243" s="8">
         <v>0</v>
       </c>
       <c r="K243" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L243" s="8">
         <v>0</v>
@@ -16189,7 +16375,7 @@
         <v>3</v>
       </c>
       <c r="N243" s="8">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="O243" s="8"/>
       <c r="P243" s="8"/>
@@ -16224,7 +16410,7 @@
         <v>14</v>
       </c>
       <c r="I244" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J244" s="8">
         <v>0</v>
@@ -16237,7 +16423,7 @@
       </c>
       <c r="M244" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N244" s="8">
         <v>0</v>
@@ -16326,10 +16512,10 @@
         <v>15</v>
       </c>
       <c r="I246" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J246" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K246" s="8">
         <v>0</v>
@@ -16342,7 +16528,7 @@
         <v>4</v>
       </c>
       <c r="N246" s="8">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="O246" s="8"/>
       <c r="P246" s="8"/>
@@ -16393,7 +16579,7 @@
         <v>3</v>
       </c>
       <c r="N247" s="8">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="O247" s="8"/>
       <c r="P247" s="8"/>
@@ -16428,10 +16614,10 @@
         <v>12</v>
       </c>
       <c r="I248" s="8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J248" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K248" s="8">
         <v>0</v>
@@ -16546,7 +16732,7 @@
         <v>3</v>
       </c>
       <c r="N250" s="8">
-        <v>1540</v>
+        <v>1535</v>
       </c>
       <c r="O250" s="8"/>
       <c r="P250" s="8"/>
@@ -16597,7 +16783,7 @@
         <v>3</v>
       </c>
       <c r="N251" s="8">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="O251" s="8"/>
       <c r="P251" s="8"/>
@@ -16638,17 +16824,17 @@
         <v>0</v>
       </c>
       <c r="K252" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L252" s="8">
         <v>0</v>
       </c>
       <c r="M252" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N252" s="8">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="O252" s="8"/>
       <c r="P252" s="8"/>
@@ -16699,7 +16885,7 @@
         <v>3</v>
       </c>
       <c r="N253" s="8">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="O253" s="8"/>
       <c r="P253" s="8"/>
@@ -16750,7 +16936,7 @@
         <v>3</v>
       </c>
       <c r="N254" s="8">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="O254" s="8"/>
       <c r="P254" s="8"/>
@@ -16801,7 +16987,7 @@
         <v>3</v>
       </c>
       <c r="N255" s="8">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="O255" s="8"/>
       <c r="P255" s="8"/>
@@ -16852,7 +17038,7 @@
         <v>3</v>
       </c>
       <c r="N256" s="8">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="O256" s="8"/>
       <c r="P256" s="8"/>
@@ -16887,7 +17073,7 @@
         <v>14</v>
       </c>
       <c r="I257" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J257" s="8">
         <v>0</v>
@@ -16900,10 +17086,10 @@
       </c>
       <c r="M257" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N257" s="8">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="O257" s="8"/>
       <c r="P257" s="8"/>
@@ -17005,7 +17191,7 @@
         <v>3</v>
       </c>
       <c r="N259" s="8">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O259" s="8"/>
       <c r="P259" s="8"/>
@@ -17056,7 +17242,7 @@
         <v>7</v>
       </c>
       <c r="N260" s="8">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="O260" s="8"/>
       <c r="P260" s="8"/>
@@ -17107,7 +17293,7 @@
         <v>13</v>
       </c>
       <c r="N261" s="8">
-        <v>1321</v>
+        <v>1547</v>
       </c>
       <c r="O261" s="8"/>
       <c r="P261" s="8"/>
@@ -17148,17 +17334,17 @@
         <v>0</v>
       </c>
       <c r="K262" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L262" s="8">
         <v>0</v>
       </c>
       <c r="M262" s="8">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N262" s="8">
-        <v>446</v>
+        <v>419</v>
       </c>
       <c r="O262" s="8"/>
       <c r="P262" s="8"/>
@@ -17199,17 +17385,17 @@
         <v>0</v>
       </c>
       <c r="K263" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L263" s="8">
         <v>0</v>
       </c>
       <c r="M263" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="N263" s="8">
-        <v>958</v>
+        <v>784</v>
       </c>
       <c r="O263" s="8"/>
       <c r="P263" s="8"/>
@@ -17260,7 +17446,7 @@
         <v>3</v>
       </c>
       <c r="N264" s="8">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="O264" s="8"/>
       <c r="P264" s="8"/>
@@ -17346,7 +17532,7 @@
         <v>14</v>
       </c>
       <c r="I266" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J266" s="8">
         <v>0</v>
@@ -17359,10 +17545,10 @@
       </c>
       <c r="M266" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N266" s="8">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="O266" s="8"/>
       <c r="P266" s="8"/>
@@ -17413,7 +17599,7 @@
         <v>2</v>
       </c>
       <c r="N267" s="8">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="O267" s="8"/>
       <c r="P267" s="8"/>
@@ -17448,7 +17634,7 @@
         <v>15</v>
       </c>
       <c r="I268" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J268" s="8">
         <v>0</v>
@@ -17461,10 +17647,10 @@
       </c>
       <c r="M268" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N268" s="8">
-        <v>218</v>
+        <v>193</v>
       </c>
       <c r="O268" s="8"/>
       <c r="P268" s="8"/>
@@ -17505,17 +17691,17 @@
         <v>0</v>
       </c>
       <c r="K269" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L269" s="8">
         <v>0</v>
       </c>
       <c r="M269" s="8">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N269" s="8">
-        <v>286</v>
+        <v>246</v>
       </c>
       <c r="O269" s="8"/>
       <c r="P269" s="8"/>
@@ -17754,23 +17940,23 @@
         <v>16</v>
       </c>
       <c r="I274" s="8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J274" s="8">
         <v>0</v>
       </c>
       <c r="K274" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L274" s="8">
         <v>0</v>
       </c>
       <c r="M274" s="8">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N274" s="8">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="O274" s="8"/>
       <c r="P274" s="8"/>
@@ -17805,10 +17991,10 @@
         <v>15</v>
       </c>
       <c r="I275" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J275" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K275" s="8">
         <v>0</v>
@@ -17821,7 +18007,7 @@
         <v>4</v>
       </c>
       <c r="N275" s="8">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O275" s="8"/>
       <c r="P275" s="8"/>
@@ -17856,13 +18042,13 @@
         <v>15</v>
       </c>
       <c r="I276" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J276" s="8">
         <v>0</v>
       </c>
       <c r="K276" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L276" s="8">
         <v>0</v>
@@ -17872,7 +18058,7 @@
         <v>4</v>
       </c>
       <c r="N276" s="8">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="O276" s="8"/>
       <c r="P276" s="8"/>
@@ -17913,17 +18099,17 @@
         <v>0</v>
       </c>
       <c r="K277" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L277" s="8">
         <v>0</v>
       </c>
       <c r="M277" s="8">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N277" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O277" s="8"/>
       <c r="P277" s="8"/>
@@ -17958,23 +18144,23 @@
         <v>12</v>
       </c>
       <c r="I278" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J278" s="8">
         <v>0</v>
       </c>
       <c r="K278" s="8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L278" s="8">
         <v>0</v>
       </c>
       <c r="M278" s="8">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="N278" s="8">
-        <v>382</v>
+        <v>862</v>
       </c>
       <c r="O278" s="8"/>
       <c r="P278" s="8"/>
@@ -18025,7 +18211,7 @@
         <v>3</v>
       </c>
       <c r="N279" s="8">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="O279" s="8"/>
       <c r="P279" s="8"/>
@@ -18076,7 +18262,7 @@
         <v>3</v>
       </c>
       <c r="N280" s="8">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="O280" s="8"/>
       <c r="P280" s="8"/>
@@ -18117,17 +18303,17 @@
         <v>0</v>
       </c>
       <c r="K281" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L281" s="8">
         <v>0</v>
       </c>
       <c r="M281" s="8">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N281" s="8">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="O281" s="8"/>
       <c r="P281" s="8"/>
@@ -18213,23 +18399,23 @@
         <v>12</v>
       </c>
       <c r="I283" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J283" s="8">
         <v>0</v>
       </c>
       <c r="K283" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L283" s="8">
         <v>0</v>
       </c>
       <c r="M283" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N283" s="8">
-        <v>570</v>
+        <v>495</v>
       </c>
       <c r="O283" s="8"/>
       <c r="P283" s="8"/>
@@ -18264,23 +18450,23 @@
         <v>12</v>
       </c>
       <c r="I284" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J284" s="8">
         <v>0</v>
       </c>
       <c r="K284" s="8">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L284" s="8">
         <v>0</v>
       </c>
       <c r="M284" s="8">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="N284" s="8">
-        <v>924</v>
+        <v>664</v>
       </c>
       <c r="O284" s="8"/>
       <c r="P284" s="8"/>
@@ -18315,7 +18501,7 @@
         <v>13</v>
       </c>
       <c r="I285" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J285" s="8">
         <v>0</v>
@@ -18328,10 +18514,10 @@
       </c>
       <c r="M285" s="8">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N285" s="8">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="O285" s="8"/>
       <c r="P285" s="8"/>
@@ -18366,7 +18552,7 @@
         <v>12</v>
       </c>
       <c r="I286" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J286" s="8">
         <v>0</v>
@@ -18379,10 +18565,10 @@
       </c>
       <c r="M286" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N286" s="8">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="O286" s="8"/>
       <c r="P286" s="8"/>
@@ -18433,7 +18619,7 @@
         <v>8</v>
       </c>
       <c r="N287" s="8">
-        <v>86</v>
+        <v>485</v>
       </c>
       <c r="O287" s="8"/>
       <c r="P287" s="8"/>
@@ -18484,7 +18670,7 @@
         <v>6</v>
       </c>
       <c r="N288" s="8">
-        <v>1769</v>
+        <v>1723</v>
       </c>
       <c r="O288" s="8"/>
       <c r="P288" s="8"/>
@@ -18535,7 +18721,7 @@
         <v>3</v>
       </c>
       <c r="N289" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O289" s="8"/>
       <c r="P289" s="8"/>
@@ -18621,23 +18807,23 @@
         <v>12</v>
       </c>
       <c r="I291" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J291" s="8">
         <v>0</v>
       </c>
       <c r="K291" s="8">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L291" s="8">
         <v>0</v>
       </c>
       <c r="M291" s="8">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="N291" s="8">
-        <v>1103</v>
+        <v>805</v>
       </c>
       <c r="O291" s="8"/>
       <c r="P291" s="8"/>
@@ -18688,7 +18874,7 @@
         <v>4</v>
       </c>
       <c r="N292" s="8">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="O292" s="8"/>
       <c r="P292" s="8"/>
@@ -18723,7 +18909,7 @@
         <v>12</v>
       </c>
       <c r="I293" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J293" s="8">
         <v>0</v>
@@ -18736,7 +18922,7 @@
       </c>
       <c r="M293" s="8">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N293" s="8">
         <v>0</v>
@@ -18774,23 +18960,23 @@
         <v>12</v>
       </c>
       <c r="I294" s="8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J294" s="8">
         <v>0</v>
       </c>
       <c r="K294" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L294" s="8">
         <v>0</v>
       </c>
       <c r="M294" s="8">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N294" s="8">
-        <v>488</v>
+        <v>1467</v>
       </c>
       <c r="O294" s="8"/>
       <c r="P294" s="8"/>
@@ -18892,7 +19078,7 @@
         <v>1</v>
       </c>
       <c r="N296" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O296" s="8"/>
       <c r="P296" s="8"/>
@@ -18978,7 +19164,7 @@
         <v>14</v>
       </c>
       <c r="I298" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J298" s="8">
         <v>0</v>
@@ -18991,7 +19177,7 @@
       </c>
       <c r="M298" s="8">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N298" s="8">
         <v>0</v>
@@ -19086,17 +19272,17 @@
         <v>0</v>
       </c>
       <c r="K300" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L300" s="8">
         <v>0</v>
       </c>
       <c r="M300" s="8">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N300" s="8">
-        <v>268</v>
+        <v>205</v>
       </c>
       <c r="O300" s="8"/>
       <c r="P300" s="8"/>
@@ -19147,7 +19333,7 @@
         <v>7</v>
       </c>
       <c r="N301" s="8">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="O301" s="8"/>
       <c r="P301" s="8"/>
@@ -19198,7 +19384,7 @@
         <v>7</v>
       </c>
       <c r="N302" s="8">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="O302" s="8"/>
       <c r="P302" s="8"/>
@@ -19249,7 +19435,7 @@
         <v>4</v>
       </c>
       <c r="N303" s="8">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="O303" s="8"/>
       <c r="P303" s="8"/>
@@ -19300,7 +19486,7 @@
         <v>4</v>
       </c>
       <c r="N304" s="8">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="O304" s="8"/>
       <c r="P304" s="8"/>
@@ -19351,7 +19537,7 @@
         <v>10</v>
       </c>
       <c r="N305" s="8">
-        <v>220</v>
+        <v>184</v>
       </c>
       <c r="O305" s="8"/>
       <c r="P305" s="8"/>
@@ -19402,7 +19588,7 @@
         <v>12</v>
       </c>
       <c r="N306" s="8">
-        <v>1048</v>
+        <v>1466</v>
       </c>
       <c r="O306" s="8"/>
       <c r="P306" s="8"/>
@@ -19453,7 +19639,7 @@
         <v>12</v>
       </c>
       <c r="N307" s="8">
-        <v>1272</v>
+        <v>1209</v>
       </c>
       <c r="O307" s="8"/>
       <c r="P307" s="8"/>
@@ -19488,7 +19674,7 @@
         <v>13</v>
       </c>
       <c r="I308" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J308" s="8">
         <v>0</v>
@@ -19501,10 +19687,10 @@
       </c>
       <c r="M308" s="8">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N308" s="8">
-        <v>975</v>
+        <v>890</v>
       </c>
       <c r="O308" s="8"/>
       <c r="P308" s="8"/>
@@ -19657,7 +19843,7 @@
         <v>3</v>
       </c>
       <c r="N311" s="8">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="O311" s="8"/>
       <c r="P311" s="8"/>
@@ -19692,7 +19878,7 @@
         <v>13</v>
       </c>
       <c r="I312" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J312" s="8">
         <v>0</v>
@@ -19705,10 +19891,10 @@
       </c>
       <c r="M312" s="8">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N312" s="8">
-        <v>400</v>
+        <v>353</v>
       </c>
       <c r="O312" s="8"/>
       <c r="P312" s="8"/>
@@ -19759,7 +19945,7 @@
         <v>3</v>
       </c>
       <c r="N313" s="8">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="O313" s="8"/>
       <c r="P313" s="8"/>
@@ -19810,7 +19996,7 @@
         <v>3</v>
       </c>
       <c r="N314" s="8">
-        <v>518</v>
+        <v>447</v>
       </c>
       <c r="O314" s="8"/>
       <c r="P314" s="8"/>
@@ -19861,7 +20047,7 @@
         <v>8</v>
       </c>
       <c r="N315" s="8">
-        <v>122</v>
+        <v>41</v>
       </c>
       <c r="O315" s="8"/>
       <c r="P315" s="8"/>
@@ -19896,7 +20082,7 @@
         <v>12</v>
       </c>
       <c r="I316" s="8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J316" s="8">
         <v>0</v>
@@ -19909,10 +20095,10 @@
       </c>
       <c r="M316" s="8">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N316" s="8">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="O316" s="8"/>
       <c r="P316" s="8"/>
@@ -19947,7 +20133,7 @@
         <v>12</v>
       </c>
       <c r="I317" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J317" s="8">
         <v>0</v>
@@ -19960,10 +20146,10 @@
       </c>
       <c r="M317" s="8">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N317" s="8">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="O317" s="8"/>
       <c r="P317" s="8"/>
@@ -20014,7 +20200,7 @@
         <v>7</v>
       </c>
       <c r="N318" s="8">
-        <v>1196</v>
+        <v>1462</v>
       </c>
       <c r="O318" s="8"/>
       <c r="P318" s="8"/>
@@ -20116,7 +20302,7 @@
         <v>4</v>
       </c>
       <c r="N320" s="8">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="O320" s="8"/>
       <c r="P320" s="8"/>
@@ -20151,7 +20337,7 @@
         <v>14</v>
       </c>
       <c r="I321" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J321" s="8">
         <v>0</v>
@@ -20164,10 +20350,10 @@
       </c>
       <c r="M321" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N321" s="8">
-        <v>696</v>
+        <v>679</v>
       </c>
       <c r="O321" s="8"/>
       <c r="P321" s="8"/>
@@ -20218,7 +20404,7 @@
         <v>3</v>
       </c>
       <c r="N322" s="8">
-        <v>131</v>
+        <v>321</v>
       </c>
       <c r="O322" s="8"/>
       <c r="P322" s="8"/>
@@ -20265,11 +20451,11 @@
         <v>0</v>
       </c>
       <c r="M323" s="8">
-        <f t="shared" ref="M323:M343" si="5">I323+J323+K323+L323</f>
+        <f t="shared" ref="M323:M374" si="5">I323+J323+K323+L323</f>
         <v>4</v>
       </c>
       <c r="N323" s="8">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="O323" s="8"/>
       <c r="P323" s="8"/>
@@ -20320,7 +20506,7 @@
         <v>0</v>
       </c>
       <c r="N324" s="8">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O324" s="8"/>
       <c r="P324" s="8"/>
@@ -20371,7 +20557,7 @@
         <v>4</v>
       </c>
       <c r="N325" s="8">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="O325" s="8"/>
       <c r="P325" s="8"/>
@@ -20422,7 +20608,7 @@
         <v>3</v>
       </c>
       <c r="N326" s="8">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="O326" s="8"/>
       <c r="P326" s="8"/>
@@ -20473,7 +20659,7 @@
         <v>3</v>
       </c>
       <c r="N327" s="8">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="O327" s="8"/>
       <c r="P327" s="8"/>
@@ -20524,7 +20710,7 @@
         <v>1</v>
       </c>
       <c r="N328" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O328" s="8"/>
       <c r="P328" s="8"/>
@@ -20575,7 +20761,7 @@
         <v>4</v>
       </c>
       <c r="N329" s="8">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="O329" s="8"/>
       <c r="P329" s="8"/>
@@ -20677,7 +20863,7 @@
         <v>4</v>
       </c>
       <c r="N331" s="8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O331" s="8"/>
       <c r="P331" s="8"/>
@@ -20728,7 +20914,7 @@
         <v>1</v>
       </c>
       <c r="N332" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O332" s="8"/>
       <c r="P332" s="8"/>
@@ -20763,7 +20949,7 @@
         <v>13</v>
       </c>
       <c r="I333" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J333" s="8">
         <v>0</v>
@@ -20776,7 +20962,7 @@
       </c>
       <c r="M333" s="8">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N333" s="8">
         <v>370</v>
@@ -20830,7 +21016,7 @@
         <v>5</v>
       </c>
       <c r="N334" s="8">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="O334" s="8"/>
       <c r="P334" s="8"/>
@@ -20881,7 +21067,7 @@
         <v>1</v>
       </c>
       <c r="N335" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O335" s="8"/>
       <c r="P335" s="8"/>
@@ -20932,7 +21118,7 @@
         <v>6</v>
       </c>
       <c r="N336" s="8">
-        <v>856</v>
+        <v>849</v>
       </c>
       <c r="O336" s="8"/>
       <c r="P336" s="8"/>
@@ -20967,7 +21153,7 @@
         <v>12</v>
       </c>
       <c r="I337" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J337" s="8">
         <v>0</v>
@@ -20980,10 +21166,10 @@
       </c>
       <c r="M337" s="8">
         <f t="shared" si="5"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N337" s="8">
-        <v>1015</v>
+        <v>1133</v>
       </c>
       <c r="O337" s="8"/>
       <c r="P337" s="8"/>
@@ -21034,7 +21220,7 @@
         <v>8</v>
       </c>
       <c r="N338" s="8">
-        <v>1311</v>
+        <v>1543</v>
       </c>
       <c r="O338" s="8"/>
       <c r="P338" s="8"/>
@@ -21085,7 +21271,7 @@
         <v>5</v>
       </c>
       <c r="N339" s="8">
-        <v>1037</v>
+        <v>1015</v>
       </c>
       <c r="O339" s="8"/>
       <c r="P339" s="8"/>
@@ -21120,13 +21306,13 @@
         <v>14</v>
       </c>
       <c r="I340" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J340" s="8">
         <v>0</v>
       </c>
       <c r="K340" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L340" s="8">
         <v>0</v>
@@ -21136,7 +21322,7 @@
         <v>2</v>
       </c>
       <c r="N340" s="8">
-        <v>1078</v>
+        <v>1037</v>
       </c>
       <c r="O340" s="8"/>
       <c r="P340" s="8"/>
@@ -21187,7 +21373,7 @@
         <v>5</v>
       </c>
       <c r="N341" s="8">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="O341" s="8"/>
       <c r="P341" s="8"/>
@@ -21238,7 +21424,7 @@
         <v>4</v>
       </c>
       <c r="N342" s="8">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="O342" s="8"/>
       <c r="P342" s="8"/>
@@ -21279,17 +21465,17 @@
         <v>0</v>
       </c>
       <c r="K343" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L343" s="8">
         <v>0</v>
       </c>
       <c r="M343" s="8">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N343" s="8">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="O343" s="8"/>
       <c r="P343" s="8"/>
@@ -21300,19 +21486,44 @@
     </row>
     <row r="344" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="7"/>
-      <c r="B344" s="7"/>
-      <c r="C344" s="7"/>
+      <c r="B344" s="7" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C344" s="7" t="s">
+        <v>1071</v>
+      </c>
       <c r="D344" s="7"/>
-      <c r="E344" s="7"/>
-      <c r="F344" s="7"/>
-      <c r="G344" s="7"/>
-      <c r="H344" s="7"/>
-      <c r="I344" s="7"/>
-      <c r="J344" s="7"/>
-      <c r="K344" s="7"/>
-      <c r="L344" s="7"/>
-      <c r="M344" s="7"/>
-      <c r="N344" s="7"/>
+      <c r="E344" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F344" s="7" t="s">
+        <v>1067</v>
+      </c>
+      <c r="G344" s="8" t="s">
+        <v>1060</v>
+      </c>
+      <c r="H344" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I344" s="7">
+        <v>1</v>
+      </c>
+      <c r="J344" s="8">
+        <v>0</v>
+      </c>
+      <c r="K344" s="8">
+        <v>0</v>
+      </c>
+      <c r="L344" s="8">
+        <v>0</v>
+      </c>
+      <c r="M344" s="8">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="N344" s="7">
+        <v>0</v>
+      </c>
       <c r="O344" s="7"/>
       <c r="P344" s="7"/>
       <c r="Q344" s="7"/>
@@ -21322,19 +21533,44 @@
     </row>
     <row r="345" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="7"/>
-      <c r="B345" s="7"/>
-      <c r="C345" s="7"/>
+      <c r="B345" s="7" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C345" s="7" t="s">
+        <v>1072</v>
+      </c>
       <c r="D345" s="7"/>
-      <c r="E345" s="7"/>
-      <c r="F345" s="7"/>
-      <c r="G345" s="7"/>
-      <c r="H345" s="7"/>
-      <c r="I345" s="7"/>
-      <c r="J345" s="7"/>
-      <c r="K345" s="7"/>
-      <c r="L345" s="7"/>
-      <c r="M345" s="7"/>
-      <c r="N345" s="7"/>
+      <c r="E345" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F345" s="7" t="s">
+        <v>1067</v>
+      </c>
+      <c r="G345" s="8" t="s">
+        <v>1060</v>
+      </c>
+      <c r="H345" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I345" s="7">
+        <v>3</v>
+      </c>
+      <c r="J345" s="8">
+        <v>0</v>
+      </c>
+      <c r="K345" s="8">
+        <v>0</v>
+      </c>
+      <c r="L345" s="8">
+        <v>0</v>
+      </c>
+      <c r="M345" s="8">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="N345" s="7">
+        <v>0</v>
+      </c>
       <c r="O345" s="7"/>
       <c r="P345" s="7"/>
       <c r="Q345" s="7"/>
@@ -21344,19 +21580,44 @@
     </row>
     <row r="346" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="7"/>
-      <c r="B346" s="7"/>
-      <c r="C346" s="7"/>
+      <c r="B346" s="7" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C346" s="7" t="s">
+        <v>1073</v>
+      </c>
       <c r="D346" s="7"/>
-      <c r="E346" s="7"/>
-      <c r="F346" s="7"/>
-      <c r="G346" s="7"/>
-      <c r="H346" s="7"/>
-      <c r="I346" s="7"/>
-      <c r="J346" s="7"/>
-      <c r="K346" s="7"/>
-      <c r="L346" s="7"/>
-      <c r="M346" s="7"/>
-      <c r="N346" s="7"/>
+      <c r="E346" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F346" s="7" t="s">
+        <v>1067</v>
+      </c>
+      <c r="G346" s="8" t="s">
+        <v>1060</v>
+      </c>
+      <c r="H346" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I346" s="7">
+        <v>304</v>
+      </c>
+      <c r="J346" s="8">
+        <v>0</v>
+      </c>
+      <c r="K346" s="8">
+        <v>0</v>
+      </c>
+      <c r="L346" s="8">
+        <v>0</v>
+      </c>
+      <c r="M346" s="8">
+        <f t="shared" si="5"/>
+        <v>304</v>
+      </c>
+      <c r="N346" s="7">
+        <v>0</v>
+      </c>
       <c r="O346" s="7"/>
       <c r="P346" s="7"/>
       <c r="Q346" s="7"/>
@@ -21366,19 +21627,44 @@
     </row>
     <row r="347" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="7"/>
-      <c r="B347" s="7"/>
-      <c r="C347" s="7"/>
+      <c r="B347" s="7" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C347" s="7" t="s">
+        <v>1074</v>
+      </c>
       <c r="D347" s="7"/>
-      <c r="E347" s="7"/>
-      <c r="F347" s="7"/>
-      <c r="G347" s="7"/>
-      <c r="H347" s="7"/>
-      <c r="I347" s="7"/>
-      <c r="J347" s="7"/>
-      <c r="K347" s="7"/>
-      <c r="L347" s="7"/>
-      <c r="M347" s="7"/>
-      <c r="N347" s="7"/>
+      <c r="E347" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F347" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G347" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H347" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I347" s="7">
+        <v>1</v>
+      </c>
+      <c r="J347" s="8">
+        <v>0</v>
+      </c>
+      <c r="K347" s="8">
+        <v>3</v>
+      </c>
+      <c r="L347" s="8">
+        <v>0</v>
+      </c>
+      <c r="M347" s="8">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="N347" s="7">
+        <v>396</v>
+      </c>
       <c r="O347" s="7"/>
       <c r="P347" s="7"/>
       <c r="Q347" s="7"/>
@@ -21388,19 +21674,44 @@
     </row>
     <row r="348" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="7"/>
-      <c r="B348" s="7"/>
-      <c r="C348" s="7"/>
+      <c r="B348" s="7" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C348" s="7" t="s">
+        <v>1075</v>
+      </c>
       <c r="D348" s="7"/>
-      <c r="E348" s="7"/>
-      <c r="F348" s="7"/>
-      <c r="G348" s="7"/>
-      <c r="H348" s="7"/>
-      <c r="I348" s="7"/>
-      <c r="J348" s="7"/>
-      <c r="K348" s="7"/>
-      <c r="L348" s="7"/>
-      <c r="M348" s="7"/>
-      <c r="N348" s="7"/>
+      <c r="E348" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F348" s="7" t="s">
+        <v>1067</v>
+      </c>
+      <c r="G348" s="8" t="s">
+        <v>1060</v>
+      </c>
+      <c r="H348" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I348" s="7">
+        <v>64</v>
+      </c>
+      <c r="J348" s="8">
+        <v>0</v>
+      </c>
+      <c r="K348" s="8">
+        <v>24</v>
+      </c>
+      <c r="L348" s="8">
+        <v>0</v>
+      </c>
+      <c r="M348" s="8">
+        <f t="shared" si="5"/>
+        <v>88</v>
+      </c>
+      <c r="N348" s="7">
+        <v>189</v>
+      </c>
       <c r="O348" s="7"/>
       <c r="P348" s="7"/>
       <c r="Q348" s="7"/>
@@ -21410,19 +21721,44 @@
     </row>
     <row r="349" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="7"/>
-      <c r="B349" s="7"/>
-      <c r="C349" s="7"/>
+      <c r="B349" s="7" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C349" s="7" t="s">
+        <v>1076</v>
+      </c>
       <c r="D349" s="7"/>
-      <c r="E349" s="7"/>
-      <c r="F349" s="7"/>
-      <c r="G349" s="7"/>
-      <c r="H349" s="7"/>
-      <c r="I349" s="7"/>
-      <c r="J349" s="7"/>
-      <c r="K349" s="7"/>
-      <c r="L349" s="7"/>
-      <c r="M349" s="7"/>
-      <c r="N349" s="7"/>
+      <c r="E349" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F349" s="7" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G349" s="7" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H349" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I349" s="7">
+        <v>0</v>
+      </c>
+      <c r="J349" s="8">
+        <v>0</v>
+      </c>
+      <c r="K349" s="8">
+        <v>3</v>
+      </c>
+      <c r="L349" s="8">
+        <v>0</v>
+      </c>
+      <c r="M349" s="8">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="N349" s="7">
+        <v>2</v>
+      </c>
       <c r="O349" s="7"/>
       <c r="P349" s="7"/>
       <c r="Q349" s="7"/>
@@ -21432,19 +21768,44 @@
     </row>
     <row r="350" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="7"/>
-      <c r="B350" s="7"/>
-      <c r="C350" s="7"/>
+      <c r="B350" s="7" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C350" s="7" t="s">
+        <v>1077</v>
+      </c>
       <c r="D350" s="7"/>
-      <c r="E350" s="7"/>
-      <c r="F350" s="7"/>
-      <c r="G350" s="7"/>
-      <c r="H350" s="7"/>
-      <c r="I350" s="7"/>
-      <c r="J350" s="7"/>
-      <c r="K350" s="7"/>
-      <c r="L350" s="7"/>
-      <c r="M350" s="7"/>
-      <c r="N350" s="7"/>
+      <c r="E350" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F350" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G350" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H350" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I350" s="7">
+        <v>0</v>
+      </c>
+      <c r="J350" s="8">
+        <v>0</v>
+      </c>
+      <c r="K350" s="8">
+        <v>1</v>
+      </c>
+      <c r="L350" s="8">
+        <v>0</v>
+      </c>
+      <c r="M350" s="8">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="N350" s="7">
+        <v>0</v>
+      </c>
       <c r="O350" s="7"/>
       <c r="P350" s="7"/>
       <c r="Q350" s="7"/>
@@ -21454,19 +21815,44 @@
     </row>
     <row r="351" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="7"/>
-      <c r="B351" s="7"/>
-      <c r="C351" s="7"/>
+      <c r="B351" s="7" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C351" s="7" t="s">
+        <v>1078</v>
+      </c>
       <c r="D351" s="7"/>
-      <c r="E351" s="7"/>
-      <c r="F351" s="7"/>
-      <c r="G351" s="7"/>
-      <c r="H351" s="7"/>
-      <c r="I351" s="7"/>
-      <c r="J351" s="7"/>
-      <c r="K351" s="7"/>
-      <c r="L351" s="7"/>
-      <c r="M351" s="7"/>
-      <c r="N351" s="7"/>
+      <c r="E351" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F351" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G351" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H351" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I351" s="7">
+        <v>1</v>
+      </c>
+      <c r="J351" s="8">
+        <v>0</v>
+      </c>
+      <c r="K351" s="8">
+        <v>0</v>
+      </c>
+      <c r="L351" s="8">
+        <v>0</v>
+      </c>
+      <c r="M351" s="8">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="N351" s="7">
+        <v>0</v>
+      </c>
       <c r="O351" s="7"/>
       <c r="P351" s="7"/>
       <c r="Q351" s="7"/>
@@ -21476,19 +21862,44 @@
     </row>
     <row r="352" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="7"/>
-      <c r="B352" s="7"/>
-      <c r="C352" s="7"/>
+      <c r="B352" s="7" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C352" s="7" t="s">
+        <v>1079</v>
+      </c>
       <c r="D352" s="7"/>
-      <c r="E352" s="7"/>
-      <c r="F352" s="7"/>
-      <c r="G352" s="7"/>
-      <c r="H352" s="7"/>
-      <c r="I352" s="7"/>
-      <c r="J352" s="7"/>
-      <c r="K352" s="7"/>
-      <c r="L352" s="7"/>
-      <c r="M352" s="7"/>
-      <c r="N352" s="7"/>
+      <c r="E352" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F352" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G352" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H352" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I352" s="7">
+        <v>3</v>
+      </c>
+      <c r="J352" s="8">
+        <v>0</v>
+      </c>
+      <c r="K352" s="8">
+        <v>0</v>
+      </c>
+      <c r="L352" s="8">
+        <v>0</v>
+      </c>
+      <c r="M352" s="8">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="N352" s="7">
+        <v>592</v>
+      </c>
       <c r="O352" s="7"/>
       <c r="P352" s="7"/>
       <c r="Q352" s="7"/>
@@ -21498,19 +21909,44 @@
     </row>
     <row r="353" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="7"/>
-      <c r="B353" s="7"/>
-      <c r="C353" s="7"/>
+      <c r="B353" s="7" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C353" s="7" t="s">
+        <v>1080</v>
+      </c>
       <c r="D353" s="7"/>
-      <c r="E353" s="7"/>
-      <c r="F353" s="7"/>
-      <c r="G353" s="7"/>
-      <c r="H353" s="7"/>
-      <c r="I353" s="7"/>
-      <c r="J353" s="7"/>
-      <c r="K353" s="7"/>
-      <c r="L353" s="7"/>
-      <c r="M353" s="7"/>
-      <c r="N353" s="7"/>
+      <c r="E353" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F353" s="7" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G353" s="7" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H353" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I353" s="7">
+        <v>0</v>
+      </c>
+      <c r="J353" s="8">
+        <v>0</v>
+      </c>
+      <c r="K353" s="8">
+        <v>1</v>
+      </c>
+      <c r="L353" s="8">
+        <v>0</v>
+      </c>
+      <c r="M353" s="8">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="N353" s="7">
+        <v>0</v>
+      </c>
       <c r="O353" s="7"/>
       <c r="P353" s="7"/>
       <c r="Q353" s="7"/>
@@ -21520,19 +21956,44 @@
     </row>
     <row r="354" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="7"/>
-      <c r="B354" s="7"/>
-      <c r="C354" s="7"/>
+      <c r="B354" s="7" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C354" s="7" t="s">
+        <v>1081</v>
+      </c>
       <c r="D354" s="7"/>
-      <c r="E354" s="7"/>
-      <c r="F354" s="7"/>
-      <c r="G354" s="7"/>
-      <c r="H354" s="7"/>
-      <c r="I354" s="7"/>
-      <c r="J354" s="7"/>
-      <c r="K354" s="7"/>
-      <c r="L354" s="7"/>
-      <c r="M354" s="7"/>
-      <c r="N354" s="7"/>
+      <c r="E354" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F354" s="7" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G354" s="7" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H354" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I354" s="7">
+        <v>0</v>
+      </c>
+      <c r="J354" s="8">
+        <v>0</v>
+      </c>
+      <c r="K354" s="8">
+        <v>0</v>
+      </c>
+      <c r="L354" s="8">
+        <v>0</v>
+      </c>
+      <c r="M354" s="8">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N354" s="7">
+        <v>0</v>
+      </c>
       <c r="O354" s="7"/>
       <c r="P354" s="7"/>
       <c r="Q354" s="7"/>
@@ -21542,19 +22003,44 @@
     </row>
     <row r="355" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="7"/>
-      <c r="B355" s="7"/>
-      <c r="C355" s="7"/>
+      <c r="B355" s="7" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C355" s="7" t="s">
+        <v>1082</v>
+      </c>
       <c r="D355" s="7"/>
-      <c r="E355" s="7"/>
-      <c r="F355" s="7"/>
-      <c r="G355" s="7"/>
-      <c r="H355" s="7"/>
-      <c r="I355" s="7"/>
-      <c r="J355" s="7"/>
-      <c r="K355" s="7"/>
-      <c r="L355" s="7"/>
-      <c r="M355" s="7"/>
-      <c r="N355" s="7"/>
+      <c r="E355" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F355" s="7" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G355" s="7" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H355" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I355" s="7">
+        <v>1</v>
+      </c>
+      <c r="J355" s="8">
+        <v>0</v>
+      </c>
+      <c r="K355" s="8">
+        <v>2</v>
+      </c>
+      <c r="L355" s="8">
+        <v>0</v>
+      </c>
+      <c r="M355" s="8">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="N355" s="7">
+        <v>13</v>
+      </c>
       <c r="O355" s="7"/>
       <c r="P355" s="7"/>
       <c r="Q355" s="7"/>
@@ -21564,19 +22050,44 @@
     </row>
     <row r="356" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="7"/>
-      <c r="B356" s="7"/>
-      <c r="C356" s="7"/>
+      <c r="B356" s="7" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C356" s="7" t="s">
+        <v>1083</v>
+      </c>
       <c r="D356" s="7"/>
-      <c r="E356" s="7"/>
-      <c r="F356" s="7"/>
-      <c r="G356" s="7"/>
-      <c r="H356" s="7"/>
-      <c r="I356" s="7"/>
-      <c r="J356" s="7"/>
-      <c r="K356" s="7"/>
-      <c r="L356" s="7"/>
-      <c r="M356" s="7"/>
-      <c r="N356" s="7"/>
+      <c r="E356" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F356" s="7" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G356" s="7" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H356" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I356" s="7">
+        <v>0</v>
+      </c>
+      <c r="J356" s="8">
+        <v>0</v>
+      </c>
+      <c r="K356" s="8">
+        <v>0</v>
+      </c>
+      <c r="L356" s="8">
+        <v>0</v>
+      </c>
+      <c r="M356" s="8">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N356" s="7">
+        <v>0</v>
+      </c>
       <c r="O356" s="7"/>
       <c r="P356" s="7"/>
       <c r="Q356" s="7"/>
@@ -21586,19 +22097,44 @@
     </row>
     <row r="357" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="7"/>
-      <c r="B357" s="7"/>
-      <c r="C357" s="7"/>
+      <c r="B357" s="7" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C357" s="7" t="s">
+        <v>1084</v>
+      </c>
       <c r="D357" s="7"/>
-      <c r="E357" s="7"/>
-      <c r="F357" s="7"/>
-      <c r="G357" s="7"/>
-      <c r="H357" s="7"/>
-      <c r="I357" s="7"/>
-      <c r="J357" s="7"/>
-      <c r="K357" s="7"/>
-      <c r="L357" s="7"/>
-      <c r="M357" s="7"/>
-      <c r="N357" s="7"/>
+      <c r="E357" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F357" s="7" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G357" s="7" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H357" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I357" s="7">
+        <v>0</v>
+      </c>
+      <c r="J357" s="8">
+        <v>0</v>
+      </c>
+      <c r="K357" s="8">
+        <v>0</v>
+      </c>
+      <c r="L357" s="8">
+        <v>0</v>
+      </c>
+      <c r="M357" s="8">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N357" s="7">
+        <v>0</v>
+      </c>
       <c r="O357" s="7"/>
       <c r="P357" s="7"/>
       <c r="Q357" s="7"/>
@@ -21608,19 +22144,44 @@
     </row>
     <row r="358" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="7"/>
-      <c r="B358" s="7"/>
-      <c r="C358" s="7"/>
+      <c r="B358" s="7" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C358" s="7" t="s">
+        <v>1085</v>
+      </c>
       <c r="D358" s="7"/>
-      <c r="E358" s="7"/>
-      <c r="F358" s="7"/>
-      <c r="G358" s="7"/>
-      <c r="H358" s="7"/>
-      <c r="I358" s="7"/>
-      <c r="J358" s="7"/>
-      <c r="K358" s="7"/>
-      <c r="L358" s="7"/>
-      <c r="M358" s="7"/>
-      <c r="N358" s="7"/>
+      <c r="E358" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F358" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G358" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H358" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I358" s="7">
+        <v>0</v>
+      </c>
+      <c r="J358" s="8">
+        <v>0</v>
+      </c>
+      <c r="K358" s="8">
+        <v>0</v>
+      </c>
+      <c r="L358" s="8">
+        <v>0</v>
+      </c>
+      <c r="M358" s="8">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N358" s="7">
+        <v>0</v>
+      </c>
       <c r="O358" s="7"/>
       <c r="P358" s="7"/>
       <c r="Q358" s="7"/>
@@ -21630,19 +22191,44 @@
     </row>
     <row r="359" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="7"/>
-      <c r="B359" s="7"/>
-      <c r="C359" s="7"/>
+      <c r="B359" s="7" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C359" s="7" t="s">
+        <v>1086</v>
+      </c>
       <c r="D359" s="7"/>
-      <c r="E359" s="7"/>
-      <c r="F359" s="7"/>
-      <c r="G359" s="7"/>
-      <c r="H359" s="7"/>
-      <c r="I359" s="7"/>
-      <c r="J359" s="7"/>
-      <c r="K359" s="7"/>
-      <c r="L359" s="7"/>
-      <c r="M359" s="7"/>
-      <c r="N359" s="7"/>
+      <c r="E359" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F359" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G359" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H359" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I359" s="7">
+        <v>0</v>
+      </c>
+      <c r="J359" s="8">
+        <v>0</v>
+      </c>
+      <c r="K359" s="8">
+        <v>3</v>
+      </c>
+      <c r="L359" s="8">
+        <v>0</v>
+      </c>
+      <c r="M359" s="8">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="N359" s="7">
+        <v>1</v>
+      </c>
       <c r="O359" s="7"/>
       <c r="P359" s="7"/>
       <c r="Q359" s="7"/>
@@ -21652,19 +22238,44 @@
     </row>
     <row r="360" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="7"/>
-      <c r="B360" s="7"/>
-      <c r="C360" s="7"/>
+      <c r="B360" s="7" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C360" s="7" t="s">
+        <v>1087</v>
+      </c>
       <c r="D360" s="7"/>
-      <c r="E360" s="7"/>
-      <c r="F360" s="7"/>
-      <c r="G360" s="7"/>
-      <c r="H360" s="7"/>
-      <c r="I360" s="7"/>
-      <c r="J360" s="7"/>
-      <c r="K360" s="7"/>
-      <c r="L360" s="7"/>
-      <c r="M360" s="7"/>
-      <c r="N360" s="7"/>
+      <c r="E360" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F360" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G360" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H360" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I360" s="7">
+        <v>0</v>
+      </c>
+      <c r="J360" s="8">
+        <v>0</v>
+      </c>
+      <c r="K360" s="8">
+        <v>0</v>
+      </c>
+      <c r="L360" s="8">
+        <v>0</v>
+      </c>
+      <c r="M360" s="8">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N360" s="7">
+        <v>0</v>
+      </c>
       <c r="O360" s="7"/>
       <c r="P360" s="7"/>
       <c r="Q360" s="7"/>
@@ -21674,19 +22285,44 @@
     </row>
     <row r="361" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="7"/>
-      <c r="B361" s="7"/>
-      <c r="C361" s="7"/>
+      <c r="B361" s="7" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C361" s="7" t="s">
+        <v>1088</v>
+      </c>
       <c r="D361" s="7"/>
-      <c r="E361" s="7"/>
-      <c r="F361" s="7"/>
-      <c r="G361" s="7"/>
-      <c r="H361" s="7"/>
-      <c r="I361" s="7"/>
-      <c r="J361" s="7"/>
-      <c r="K361" s="7"/>
-      <c r="L361" s="7"/>
-      <c r="M361" s="7"/>
-      <c r="N361" s="7"/>
+      <c r="E361" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F361" s="7" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G361" s="7" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H361" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I361" s="7">
+        <v>0</v>
+      </c>
+      <c r="J361" s="8">
+        <v>0</v>
+      </c>
+      <c r="K361" s="8">
+        <v>1</v>
+      </c>
+      <c r="L361" s="8">
+        <v>0</v>
+      </c>
+      <c r="M361" s="8">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="N361" s="7">
+        <v>0</v>
+      </c>
       <c r="O361" s="7"/>
       <c r="P361" s="7"/>
       <c r="Q361" s="7"/>
@@ -21696,19 +22332,44 @@
     </row>
     <row r="362" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="7"/>
-      <c r="B362" s="7"/>
-      <c r="C362" s="7"/>
+      <c r="B362" s="7" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C362" s="7" t="s">
+        <v>1089</v>
+      </c>
       <c r="D362" s="7"/>
-      <c r="E362" s="7"/>
-      <c r="F362" s="7"/>
-      <c r="G362" s="7"/>
-      <c r="H362" s="7"/>
-      <c r="I362" s="7"/>
-      <c r="J362" s="7"/>
-      <c r="K362" s="7"/>
-      <c r="L362" s="7"/>
-      <c r="M362" s="7"/>
-      <c r="N362" s="7"/>
+      <c r="E362" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F362" s="7" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G362" s="7" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H362" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I362" s="7">
+        <v>0</v>
+      </c>
+      <c r="J362" s="8">
+        <v>0</v>
+      </c>
+      <c r="K362" s="8">
+        <v>0</v>
+      </c>
+      <c r="L362" s="8">
+        <v>0</v>
+      </c>
+      <c r="M362" s="8">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N362" s="7">
+        <v>0</v>
+      </c>
       <c r="O362" s="7"/>
       <c r="P362" s="7"/>
       <c r="Q362" s="7"/>
@@ -21718,19 +22379,44 @@
     </row>
     <row r="363" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="7"/>
-      <c r="B363" s="7"/>
-      <c r="C363" s="7"/>
+      <c r="B363" s="7" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C363" s="7" t="s">
+        <v>1090</v>
+      </c>
       <c r="D363" s="7"/>
-      <c r="E363" s="7"/>
-      <c r="F363" s="7"/>
-      <c r="G363" s="7"/>
-      <c r="H363" s="7"/>
-      <c r="I363" s="7"/>
-      <c r="J363" s="7"/>
-      <c r="K363" s="7"/>
-      <c r="L363" s="7"/>
-      <c r="M363" s="7"/>
-      <c r="N363" s="7"/>
+      <c r="E363" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F363" s="7" t="s">
+        <v>1067</v>
+      </c>
+      <c r="G363" s="8" t="s">
+        <v>1060</v>
+      </c>
+      <c r="H363" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I363" s="7">
+        <v>0</v>
+      </c>
+      <c r="J363" s="8">
+        <v>0</v>
+      </c>
+      <c r="K363" s="8">
+        <v>48</v>
+      </c>
+      <c r="L363" s="8">
+        <v>0</v>
+      </c>
+      <c r="M363" s="8">
+        <f t="shared" si="5"/>
+        <v>48</v>
+      </c>
+      <c r="N363" s="7">
+        <v>240</v>
+      </c>
       <c r="O363" s="7"/>
       <c r="P363" s="7"/>
       <c r="Q363" s="7"/>
@@ -21740,19 +22426,44 @@
     </row>
     <row r="364" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="7"/>
-      <c r="B364" s="7"/>
-      <c r="C364" s="7"/>
+      <c r="B364" s="7" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C364" s="7" t="s">
+        <v>1091</v>
+      </c>
       <c r="D364" s="7"/>
-      <c r="E364" s="7"/>
-      <c r="F364" s="7"/>
-      <c r="G364" s="7"/>
-      <c r="H364" s="7"/>
-      <c r="I364" s="7"/>
-      <c r="J364" s="7"/>
-      <c r="K364" s="7"/>
-      <c r="L364" s="7"/>
-      <c r="M364" s="7"/>
-      <c r="N364" s="7"/>
+      <c r="E364" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F364" s="7" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G364" s="7" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H364" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I364" s="7">
+        <v>0</v>
+      </c>
+      <c r="J364" s="8">
+        <v>0</v>
+      </c>
+      <c r="K364" s="8">
+        <v>15</v>
+      </c>
+      <c r="L364" s="8">
+        <v>0</v>
+      </c>
+      <c r="M364" s="8">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="N364" s="7">
+        <v>195</v>
+      </c>
       <c r="O364" s="7"/>
       <c r="P364" s="7"/>
       <c r="Q364" s="7"/>
@@ -21762,19 +22473,44 @@
     </row>
     <row r="365" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="7"/>
-      <c r="B365" s="7"/>
-      <c r="C365" s="7"/>
+      <c r="B365" s="7" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C365" s="7" t="s">
+        <v>1092</v>
+      </c>
       <c r="D365" s="7"/>
-      <c r="E365" s="7"/>
-      <c r="F365" s="7"/>
-      <c r="G365" s="7"/>
-      <c r="H365" s="7"/>
-      <c r="I365" s="7"/>
-      <c r="J365" s="7"/>
-      <c r="K365" s="7"/>
-      <c r="L365" s="7"/>
-      <c r="M365" s="7"/>
-      <c r="N365" s="7"/>
+      <c r="E365" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F365" s="7" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G365" s="7" t="s">
+        <v>1133</v>
+      </c>
+      <c r="H365" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I365" s="7">
+        <v>1</v>
+      </c>
+      <c r="J365" s="8">
+        <v>0</v>
+      </c>
+      <c r="K365" s="8">
+        <v>0</v>
+      </c>
+      <c r="L365" s="8">
+        <v>0</v>
+      </c>
+      <c r="M365" s="8">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="N365" s="7">
+        <v>0</v>
+      </c>
       <c r="O365" s="7"/>
       <c r="P365" s="7"/>
       <c r="Q365" s="7"/>
@@ -21784,19 +22520,44 @@
     </row>
     <row r="366" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="7"/>
-      <c r="B366" s="7"/>
-      <c r="C366" s="7"/>
+      <c r="B366" s="7" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C366" s="7" t="s">
+        <v>1093</v>
+      </c>
       <c r="D366" s="7"/>
-      <c r="E366" s="7"/>
-      <c r="F366" s="7"/>
-      <c r="G366" s="7"/>
-      <c r="H366" s="7"/>
-      <c r="I366" s="7"/>
-      <c r="J366" s="7"/>
-      <c r="K366" s="7"/>
-      <c r="L366" s="7"/>
-      <c r="M366" s="7"/>
-      <c r="N366" s="7"/>
+      <c r="E366" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F366" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G366" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H366" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I366" s="7">
+        <v>0</v>
+      </c>
+      <c r="J366" s="8">
+        <v>0</v>
+      </c>
+      <c r="K366" s="8">
+        <v>3</v>
+      </c>
+      <c r="L366" s="8">
+        <v>0</v>
+      </c>
+      <c r="M366" s="8">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="N366" s="7">
+        <v>4</v>
+      </c>
       <c r="O366" s="7"/>
       <c r="P366" s="7"/>
       <c r="Q366" s="7"/>
@@ -21806,19 +22567,44 @@
     </row>
     <row r="367" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" s="7"/>
-      <c r="B367" s="7"/>
-      <c r="C367" s="7"/>
+      <c r="B367" s="7" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C367" s="7" t="s">
+        <v>1094</v>
+      </c>
       <c r="D367" s="7"/>
-      <c r="E367" s="7"/>
-      <c r="F367" s="7"/>
-      <c r="G367" s="7"/>
-      <c r="H367" s="7"/>
-      <c r="I367" s="7"/>
-      <c r="J367" s="7"/>
-      <c r="K367" s="7"/>
-      <c r="L367" s="7"/>
-      <c r="M367" s="7"/>
-      <c r="N367" s="7"/>
+      <c r="E367" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F367" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G367" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H367" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I367" s="7">
+        <v>0</v>
+      </c>
+      <c r="J367" s="8">
+        <v>0</v>
+      </c>
+      <c r="K367" s="8">
+        <v>30</v>
+      </c>
+      <c r="L367" s="8">
+        <v>0</v>
+      </c>
+      <c r="M367" s="8">
+        <f t="shared" si="5"/>
+        <v>30</v>
+      </c>
+      <c r="N367" s="7">
+        <v>3141</v>
+      </c>
       <c r="O367" s="7"/>
       <c r="P367" s="7"/>
       <c r="Q367" s="7"/>
@@ -21828,19 +22614,44 @@
     </row>
     <row r="368" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A368" s="7"/>
-      <c r="B368" s="7"/>
-      <c r="C368" s="7"/>
+      <c r="B368" s="7" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C368" s="7" t="s">
+        <v>1095</v>
+      </c>
       <c r="D368" s="7"/>
-      <c r="E368" s="7"/>
-      <c r="F368" s="7"/>
-      <c r="G368" s="7"/>
-      <c r="H368" s="7"/>
-      <c r="I368" s="7"/>
-      <c r="J368" s="7"/>
-      <c r="K368" s="7"/>
-      <c r="L368" s="7"/>
-      <c r="M368" s="7"/>
-      <c r="N368" s="7"/>
+      <c r="E368" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F368" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G368" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H368" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I368" s="7">
+        <v>0</v>
+      </c>
+      <c r="J368" s="8">
+        <v>0</v>
+      </c>
+      <c r="K368" s="8">
+        <v>6</v>
+      </c>
+      <c r="L368" s="8">
+        <v>0</v>
+      </c>
+      <c r="M368" s="8">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="N368" s="7">
+        <v>253</v>
+      </c>
       <c r="O368" s="7"/>
       <c r="P368" s="7"/>
       <c r="Q368" s="7"/>
@@ -21850,19 +22661,44 @@
     </row>
     <row r="369" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A369" s="7"/>
-      <c r="B369" s="7"/>
-      <c r="C369" s="7"/>
+      <c r="B369" s="7" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C369" s="7" t="s">
+        <v>1096</v>
+      </c>
       <c r="D369" s="7"/>
-      <c r="E369" s="7"/>
-      <c r="F369" s="7"/>
-      <c r="G369" s="7"/>
-      <c r="H369" s="7"/>
-      <c r="I369" s="7"/>
-      <c r="J369" s="7"/>
-      <c r="K369" s="7"/>
-      <c r="L369" s="7"/>
-      <c r="M369" s="7"/>
-      <c r="N369" s="7"/>
+      <c r="E369" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F369" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G369" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H369" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I369" s="7">
+        <v>0</v>
+      </c>
+      <c r="J369" s="8">
+        <v>0</v>
+      </c>
+      <c r="K369" s="8">
+        <v>3</v>
+      </c>
+      <c r="L369" s="8">
+        <v>0</v>
+      </c>
+      <c r="M369" s="8">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="N369" s="7">
+        <v>404</v>
+      </c>
       <c r="O369" s="7"/>
       <c r="P369" s="7"/>
       <c r="Q369" s="7"/>
@@ -21872,19 +22708,44 @@
     </row>
     <row r="370" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A370" s="7"/>
-      <c r="B370" s="7"/>
-      <c r="C370" s="7"/>
+      <c r="B370" s="7" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C370" s="7" t="s">
+        <v>1097</v>
+      </c>
       <c r="D370" s="7"/>
-      <c r="E370" s="7"/>
-      <c r="F370" s="7"/>
-      <c r="G370" s="7"/>
-      <c r="H370" s="7"/>
-      <c r="I370" s="7"/>
-      <c r="J370" s="7"/>
-      <c r="K370" s="7"/>
-      <c r="L370" s="7"/>
-      <c r="M370" s="7"/>
-      <c r="N370" s="7"/>
+      <c r="E370" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F370" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G370" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H370" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I370" s="7">
+        <v>0</v>
+      </c>
+      <c r="J370" s="8">
+        <v>0</v>
+      </c>
+      <c r="K370" s="8">
+        <v>2</v>
+      </c>
+      <c r="L370" s="8">
+        <v>0</v>
+      </c>
+      <c r="M370" s="8">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="N370" s="7">
+        <v>56</v>
+      </c>
       <c r="O370" s="7"/>
       <c r="P370" s="7"/>
       <c r="Q370" s="7"/>
@@ -21894,19 +22755,44 @@
     </row>
     <row r="371" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A371" s="7"/>
-      <c r="B371" s="7"/>
-      <c r="C371" s="7"/>
+      <c r="B371" s="7" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C371" s="7" t="s">
+        <v>1098</v>
+      </c>
       <c r="D371" s="7"/>
-      <c r="E371" s="7"/>
-      <c r="F371" s="7"/>
-      <c r="G371" s="7"/>
-      <c r="H371" s="7"/>
-      <c r="I371" s="7"/>
-      <c r="J371" s="7"/>
-      <c r="K371" s="7"/>
-      <c r="L371" s="7"/>
-      <c r="M371" s="7"/>
-      <c r="N371" s="7"/>
+      <c r="E371" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F371" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G371" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H371" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I371" s="7">
+        <v>0</v>
+      </c>
+      <c r="J371" s="8">
+        <v>0</v>
+      </c>
+      <c r="K371" s="8">
+        <v>0</v>
+      </c>
+      <c r="L371" s="8">
+        <v>0</v>
+      </c>
+      <c r="M371" s="8">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N371" s="7">
+        <v>0</v>
+      </c>
       <c r="O371" s="7"/>
       <c r="P371" s="7"/>
       <c r="Q371" s="7"/>
@@ -21916,19 +22802,44 @@
     </row>
     <row r="372" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A372" s="7"/>
-      <c r="B372" s="7"/>
-      <c r="C372" s="7"/>
+      <c r="B372" s="7" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C372" s="7" t="s">
+        <v>1099</v>
+      </c>
       <c r="D372" s="7"/>
-      <c r="E372" s="7"/>
-      <c r="F372" s="7"/>
-      <c r="G372" s="7"/>
-      <c r="H372" s="7"/>
-      <c r="I372" s="7"/>
-      <c r="J372" s="7"/>
-      <c r="K372" s="7"/>
-      <c r="L372" s="7"/>
-      <c r="M372" s="7"/>
-      <c r="N372" s="7"/>
+      <c r="E372" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F372" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G372" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H372" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I372" s="7">
+        <v>0</v>
+      </c>
+      <c r="J372" s="8">
+        <v>0</v>
+      </c>
+      <c r="K372" s="8">
+        <v>3</v>
+      </c>
+      <c r="L372" s="8">
+        <v>0</v>
+      </c>
+      <c r="M372" s="8">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="N372" s="7">
+        <v>50</v>
+      </c>
       <c r="O372" s="7"/>
       <c r="P372" s="7"/>
       <c r="Q372" s="7"/>
@@ -21938,19 +22849,44 @@
     </row>
     <row r="373" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A373" s="7"/>
-      <c r="B373" s="7"/>
-      <c r="C373" s="7"/>
+      <c r="B373" s="7" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C373" s="7" t="s">
+        <v>1100</v>
+      </c>
       <c r="D373" s="7"/>
-      <c r="E373" s="7"/>
-      <c r="F373" s="7"/>
-      <c r="G373" s="7"/>
-      <c r="H373" s="7"/>
-      <c r="I373" s="7"/>
-      <c r="J373" s="7"/>
-      <c r="K373" s="7"/>
-      <c r="L373" s="7"/>
-      <c r="M373" s="7"/>
-      <c r="N373" s="7"/>
+      <c r="E373" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F373" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G373" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H373" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I373" s="7">
+        <v>0</v>
+      </c>
+      <c r="J373" s="8">
+        <v>0</v>
+      </c>
+      <c r="K373" s="8">
+        <v>5</v>
+      </c>
+      <c r="L373" s="8">
+        <v>0</v>
+      </c>
+      <c r="M373" s="8">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="N373" s="7">
+        <v>108</v>
+      </c>
       <c r="O373" s="7"/>
       <c r="P373" s="7"/>
       <c r="Q373" s="7"/>
@@ -21960,19 +22896,44 @@
     </row>
     <row r="374" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A374" s="7"/>
-      <c r="B374" s="7"/>
-      <c r="C374" s="7"/>
+      <c r="B374" s="7" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C374" s="7" t="s">
+        <v>1101</v>
+      </c>
       <c r="D374" s="7"/>
-      <c r="E374" s="7"/>
-      <c r="F374" s="7"/>
-      <c r="G374" s="7"/>
-      <c r="H374" s="7"/>
-      <c r="I374" s="7"/>
-      <c r="J374" s="7"/>
-      <c r="K374" s="7"/>
-      <c r="L374" s="7"/>
-      <c r="M374" s="7"/>
-      <c r="N374" s="7"/>
+      <c r="E374" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F374" s="7" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G374" s="7" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H374" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I374" s="7">
+        <v>0</v>
+      </c>
+      <c r="J374" s="8">
+        <v>0</v>
+      </c>
+      <c r="K374" s="8">
+        <v>0</v>
+      </c>
+      <c r="L374" s="8">
+        <v>0</v>
+      </c>
+      <c r="M374" s="8">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N374" s="7">
+        <v>855</v>
+      </c>
       <c r="O374" s="7"/>
       <c r="P374" s="7"/>
       <c r="Q374" s="7"/>
@@ -30605,7 +31566,7 @@
       <c r="T766" s="7"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T343" xr:uid="{AF55B7BF-85DC-4082-9A73-200B4D79A598}"/>
+  <autoFilter ref="A1:T374" xr:uid="{AF55B7BF-85DC-4082-9A73-200B4D79A598}"/>
   <conditionalFormatting sqref="A1:B1">
     <cfRule type="duplicateValues" dxfId="5" priority="5"/>
     <cfRule type="duplicateValues" dxfId="4" priority="6"/>

--- a/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
+++ b/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\Fossil Replenishment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD860362-0F4E-4DE6-9A82-898793CE9777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D0C406E-7606-4000-99F8-756B018A1E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6662473D-6E1F-42FD-999B-28162E22D4B5}"/>
   </bookViews>
@@ -4521,7 +4521,7 @@
         <v>1069</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>12</v>
@@ -8346,7 +8346,7 @@
         <v>1070</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="H86" s="8" t="s">
         <v>12</v>
@@ -31566,7 +31566,6 @@
       <c r="T766" s="7"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T374" xr:uid="{AF55B7BF-85DC-4082-9A73-200B4D79A598}"/>
   <conditionalFormatting sqref="A1:B1">
     <cfRule type="duplicateValues" dxfId="5" priority="5"/>
     <cfRule type="duplicateValues" dxfId="4" priority="6"/>

--- a/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
+++ b/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\Fossil Replenishment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D0C406E-7606-4000-99F8-756B018A1E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C96EE8F8-6F96-4864-9A65-BBB2E96831FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6662473D-6E1F-42FD-999B-28162E22D4B5}"/>
   </bookViews>

--- a/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
+++ b/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\Fossil Replenishment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C96EE8F8-6F96-4864-9A65-BBB2E96831FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F81491C7-E2C3-4EEB-AEEC-52C360FD7C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6662473D-6E1F-42FD-999B-28162E22D4B5}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$T$374</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$T$384</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2942" uniqueCount="1134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3084" uniqueCount="1195">
   <si>
     <t>In Transit PO</t>
   </si>
@@ -3439,6 +3439,189 @@
   </si>
   <si>
     <t>N</t>
+  </si>
+  <si>
+    <t>FS5164</t>
+  </si>
+  <si>
+    <t>BQ3502</t>
+  </si>
+  <si>
+    <t>AX2429</t>
+  </si>
+  <si>
+    <t>MK3197</t>
+  </si>
+  <si>
+    <t>MK9185</t>
+  </si>
+  <si>
+    <t>FS4656</t>
+  </si>
+  <si>
+    <t>SKW6355</t>
+  </si>
+  <si>
+    <t>AX5729</t>
+  </si>
+  <si>
+    <t>ES5402</t>
+  </si>
+  <si>
+    <t>FS5822</t>
+  </si>
+  <si>
+    <t>B0183NW5H6</t>
+  </si>
+  <si>
+    <t>B07RPQWF6B</t>
+  </si>
+  <si>
+    <t>B09GYMBKMQ</t>
+  </si>
+  <si>
+    <t>B00Z52HG6O</t>
+  </si>
+  <si>
+    <t>B0D955H882</t>
+  </si>
+  <si>
+    <t>B00DH9NPBM</t>
+  </si>
+  <si>
+    <t>B01MZWUN47</t>
+  </si>
+  <si>
+    <t>B0DSBPCW8R</t>
+  </si>
+  <si>
+    <t>B0DSBSVS4X</t>
+  </si>
+  <si>
+    <t>B08QTW81S9</t>
+  </si>
+  <si>
+    <t>FBA74358</t>
+  </si>
+  <si>
+    <t>FBA73952</t>
+  </si>
+  <si>
+    <t>FBA75372</t>
+  </si>
+  <si>
+    <t>FBA80095</t>
+  </si>
+  <si>
+    <t>FBA80096</t>
+  </si>
+  <si>
+    <t>FBA66968</t>
+  </si>
+  <si>
+    <t>FBA79321</t>
+  </si>
+  <si>
+    <t>FBA79417</t>
+  </si>
+  <si>
+    <t>FBA79428</t>
+  </si>
+  <si>
+    <t>FBA69542</t>
+  </si>
+  <si>
+    <t>FBA79516</t>
+  </si>
+  <si>
+    <t>FBA74343</t>
+  </si>
+  <si>
+    <t>FBA79136</t>
+  </si>
+  <si>
+    <t>FBA79286</t>
+  </si>
+  <si>
+    <t>FBA79407</t>
+  </si>
+  <si>
+    <t>FBA79424</t>
+  </si>
+  <si>
+    <t>FBA76805</t>
+  </si>
+  <si>
+    <t>FBA79303</t>
+  </si>
+  <si>
+    <t>FBA79408</t>
+  </si>
+  <si>
+    <t>FBA66987</t>
+  </si>
+  <si>
+    <t>FBA75153</t>
+  </si>
+  <si>
+    <t>FBA69567</t>
+  </si>
+  <si>
+    <t>FBA79947</t>
+  </si>
+  <si>
+    <t>FBA79528</t>
+  </si>
+  <si>
+    <t>FBA76876</t>
+  </si>
+  <si>
+    <t>FBA79858</t>
+  </si>
+  <si>
+    <t>FBA80035</t>
+  </si>
+  <si>
+    <t>FBA80038</t>
+  </si>
+  <si>
+    <t>FBA80051</t>
+  </si>
+  <si>
+    <t>FBA80053</t>
+  </si>
+  <si>
+    <t>FBA79419</t>
+  </si>
+  <si>
+    <t>FBA75262</t>
+  </si>
+  <si>
+    <t>FBA75458</t>
+  </si>
+  <si>
+    <t>FBA74950</t>
+  </si>
+  <si>
+    <t>FBA77065</t>
+  </si>
+  <si>
+    <t>FBA79561</t>
+  </si>
+  <si>
+    <t>FBA66628</t>
+  </si>
+  <si>
+    <t>FBA72029</t>
+  </si>
+  <si>
+    <t>FBA79736</t>
+  </si>
+  <si>
+    <t>FBA79745</t>
+  </si>
+  <si>
+    <t>FBA74415</t>
   </si>
 </sst>
 </file>
@@ -3534,7 +3717,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3558,6 +3741,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4068,23 +4254,23 @@
         <v>12</v>
       </c>
       <c r="I2" s="8">
-        <v>117</v>
+        <v>166</v>
       </c>
       <c r="J2" s="8">
         <v>0</v>
       </c>
       <c r="K2" s="8">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="L2" s="8">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="M2" s="8">
         <f>I2+J2+K2+L2</f>
-        <v>189</v>
+        <v>550</v>
       </c>
       <c r="N2" s="8">
-        <v>2457</v>
+        <v>2439</v>
       </c>
       <c r="O2" s="8"/>
       <c r="P2" s="8"/>
@@ -4170,7 +4356,7 @@
         <v>12</v>
       </c>
       <c r="I4" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="8">
         <v>0</v>
@@ -4183,7 +4369,7 @@
       </c>
       <c r="M4" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" s="8">
         <v>0</v>
@@ -4221,23 +4407,23 @@
         <v>12</v>
       </c>
       <c r="I5" s="8">
-        <v>298</v>
+        <v>268</v>
       </c>
       <c r="J5" s="8">
         <v>0</v>
       </c>
       <c r="K5" s="8">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="L5" s="8">
         <v>0</v>
       </c>
       <c r="M5" s="8">
         <f t="shared" si="0"/>
-        <v>303</v>
+        <v>368</v>
       </c>
       <c r="N5" s="8">
-        <v>509</v>
+        <v>89</v>
       </c>
       <c r="O5" s="8"/>
       <c r="P5" s="8"/>
@@ -4272,23 +4458,23 @@
         <v>12</v>
       </c>
       <c r="I6" s="8">
-        <v>279</v>
+        <v>539</v>
       </c>
       <c r="J6" s="8">
         <v>0</v>
       </c>
       <c r="K6" s="8">
-        <v>240</v>
+        <v>72</v>
       </c>
       <c r="L6" s="8">
         <v>0</v>
       </c>
       <c r="M6" s="8">
         <f t="shared" si="0"/>
-        <v>519</v>
+        <v>611</v>
       </c>
       <c r="N6" s="8">
-        <v>1182</v>
+        <v>1110</v>
       </c>
       <c r="O6" s="8"/>
       <c r="P6" s="8"/>
@@ -4323,23 +4509,23 @@
         <v>12</v>
       </c>
       <c r="I7" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J7" s="8">
         <v>0</v>
       </c>
       <c r="K7" s="8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L7" s="8">
         <v>0</v>
       </c>
       <c r="M7" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>103</v>
       </c>
       <c r="N7" s="8">
-        <v>540</v>
+        <v>297</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
@@ -4374,23 +4560,23 @@
         <v>12</v>
       </c>
       <c r="I8" s="8">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="J8" s="8">
         <v>0</v>
       </c>
       <c r="K8" s="8">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="L8" s="8">
         <v>0</v>
       </c>
       <c r="M8" s="8">
         <f t="shared" si="0"/>
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="N8" s="8">
-        <v>1196</v>
+        <v>1045</v>
       </c>
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
@@ -4441,7 +4627,7 @@
         <v>54</v>
       </c>
       <c r="N9" s="8">
-        <v>910</v>
+        <v>852</v>
       </c>
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
@@ -4476,7 +4662,7 @@
         <v>12</v>
       </c>
       <c r="I10" s="8">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="J10" s="8">
         <v>0</v>
@@ -4489,10 +4675,10 @@
       </c>
       <c r="M10" s="8">
         <f t="shared" si="0"/>
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="N10" s="8">
-        <v>846</v>
+        <v>819</v>
       </c>
       <c r="O10" s="8"/>
       <c r="P10" s="8"/>
@@ -4518,7 +4704,7 @@
         <v>19</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>1062</v>
@@ -4527,23 +4713,23 @@
         <v>12</v>
       </c>
       <c r="I11" s="8">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="J11" s="8">
         <v>0</v>
       </c>
       <c r="K11" s="8">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L11" s="8">
         <v>0</v>
       </c>
       <c r="M11" s="8">
         <f t="shared" si="0"/>
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="N11" s="8">
-        <v>488</v>
+        <v>453</v>
       </c>
       <c r="O11" s="8"/>
       <c r="P11" s="8"/>
@@ -4578,23 +4764,23 @@
         <v>12</v>
       </c>
       <c r="I12" s="8">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J12" s="8">
         <v>0</v>
       </c>
       <c r="K12" s="8">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="L12" s="8">
         <v>0</v>
       </c>
       <c r="M12" s="8">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="N12" s="8">
-        <v>801</v>
+        <v>565</v>
       </c>
       <c r="O12" s="8"/>
       <c r="P12" s="8"/>
@@ -4629,23 +4815,23 @@
         <v>12</v>
       </c>
       <c r="I13" s="8">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="J13" s="8">
         <v>0</v>
       </c>
       <c r="K13" s="8">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="L13" s="8">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="M13" s="8">
         <f t="shared" si="0"/>
-        <v>162</v>
+        <v>332</v>
       </c>
       <c r="N13" s="8">
-        <v>443</v>
+        <v>419</v>
       </c>
       <c r="O13" s="8"/>
       <c r="P13" s="8"/>
@@ -4686,17 +4872,17 @@
         <v>0</v>
       </c>
       <c r="K14" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" s="8">
         <v>0</v>
       </c>
       <c r="M14" s="8">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N14" s="8">
-        <v>1688</v>
+        <v>1626</v>
       </c>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
@@ -4731,7 +4917,7 @@
         <v>12</v>
       </c>
       <c r="I15" s="8">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J15" s="8">
         <v>0</v>
@@ -4744,7 +4930,7 @@
       </c>
       <c r="M15" s="8">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="N15" s="8">
         <v>0</v>
@@ -4782,7 +4968,7 @@
         <v>12</v>
       </c>
       <c r="I16" s="8">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J16" s="8">
         <v>0</v>
@@ -4795,10 +4981,10 @@
       </c>
       <c r="M16" s="8">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="N16" s="8">
-        <v>1098</v>
+        <v>1033</v>
       </c>
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
@@ -4833,23 +5019,23 @@
         <v>12</v>
       </c>
       <c r="I17" s="8">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="J17" s="8">
         <v>0</v>
       </c>
       <c r="K17" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L17" s="8">
         <v>0</v>
       </c>
       <c r="M17" s="8">
         <f t="shared" si="0"/>
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="N17" s="8">
-        <v>284</v>
+        <v>256</v>
       </c>
       <c r="O17" s="8"/>
       <c r="P17" s="8"/>
@@ -4884,7 +5070,7 @@
         <v>12</v>
       </c>
       <c r="I18" s="8">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="J18" s="8">
         <v>0</v>
@@ -4897,10 +5083,10 @@
       </c>
       <c r="M18" s="8">
         <f t="shared" si="0"/>
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="N18" s="8">
-        <v>743</v>
+        <v>666</v>
       </c>
       <c r="O18" s="8"/>
       <c r="P18" s="8"/>
@@ -4935,23 +5121,23 @@
         <v>13</v>
       </c>
       <c r="I19" s="8">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J19" s="8">
         <v>0</v>
       </c>
       <c r="K19" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L19" s="8">
         <v>0</v>
       </c>
       <c r="M19" s="8">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="N19" s="8">
-        <v>778</v>
+        <v>532</v>
       </c>
       <c r="O19" s="8"/>
       <c r="P19" s="8"/>
@@ -4992,17 +5178,17 @@
         <v>0</v>
       </c>
       <c r="K20" s="8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L20" s="8">
         <v>0</v>
       </c>
       <c r="M20" s="8">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="N20" s="8">
-        <v>195</v>
+        <v>610</v>
       </c>
       <c r="O20" s="8"/>
       <c r="P20" s="8"/>
@@ -5037,23 +5223,23 @@
         <v>13</v>
       </c>
       <c r="I21" s="8">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="J21" s="8">
         <v>0</v>
       </c>
       <c r="K21" s="8">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L21" s="8">
         <v>0</v>
       </c>
       <c r="M21" s="8">
         <f t="shared" si="0"/>
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="N21" s="8">
-        <v>1161</v>
+        <v>893</v>
       </c>
       <c r="O21" s="8"/>
       <c r="P21" s="8"/>
@@ -5088,7 +5274,7 @@
         <v>12</v>
       </c>
       <c r="I22" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" s="8">
         <v>0</v>
@@ -5101,7 +5287,7 @@
       </c>
       <c r="M22" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N22" s="8">
         <v>0</v>
@@ -5139,13 +5325,13 @@
         <v>12</v>
       </c>
       <c r="I23" s="8">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J23" s="8">
         <v>0</v>
       </c>
       <c r="K23" s="8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L23" s="8">
         <v>0</v>
@@ -5155,7 +5341,7 @@
         <v>47</v>
       </c>
       <c r="N23" s="8">
-        <v>740</v>
+        <v>817</v>
       </c>
       <c r="O23" s="8"/>
       <c r="P23" s="8"/>
@@ -5206,7 +5392,7 @@
         <v>14</v>
       </c>
       <c r="N24" s="8">
-        <v>173</v>
+        <v>90</v>
       </c>
       <c r="O24" s="8"/>
       <c r="P24" s="8"/>
@@ -5292,23 +5478,23 @@
         <v>12</v>
       </c>
       <c r="I26" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J26" s="8">
         <v>0</v>
       </c>
       <c r="K26" s="8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L26" s="8">
         <v>0</v>
       </c>
       <c r="M26" s="8">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N26" s="8">
-        <v>1597</v>
+        <v>1783</v>
       </c>
       <c r="O26" s="8"/>
       <c r="P26" s="8"/>
@@ -5343,7 +5529,7 @@
         <v>12</v>
       </c>
       <c r="I27" s="8">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="J27" s="8">
         <v>0</v>
@@ -5356,10 +5542,10 @@
       </c>
       <c r="M27" s="8">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="N27" s="8">
-        <v>810</v>
+        <v>950</v>
       </c>
       <c r="O27" s="8"/>
       <c r="P27" s="8"/>
@@ -5394,7 +5580,7 @@
         <v>12</v>
       </c>
       <c r="I28" s="8">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J28" s="8">
         <v>0</v>
@@ -5407,7 +5593,7 @@
       </c>
       <c r="M28" s="8">
         <f t="shared" si="0"/>
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N28" s="8">
         <v>0</v>
@@ -5451,17 +5637,17 @@
         <v>0</v>
       </c>
       <c r="K29" s="8">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L29" s="8">
         <v>0</v>
       </c>
       <c r="M29" s="8">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="N29" s="8">
-        <v>932</v>
+        <v>910</v>
       </c>
       <c r="O29" s="8"/>
       <c r="P29" s="8"/>
@@ -5496,23 +5682,23 @@
         <v>14</v>
       </c>
       <c r="I30" s="8">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J30" s="8">
         <v>0</v>
       </c>
       <c r="K30" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L30" s="8">
         <v>0</v>
       </c>
       <c r="M30" s="8">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="N30" s="8">
-        <v>1109</v>
+        <v>1346</v>
       </c>
       <c r="O30" s="8"/>
       <c r="P30" s="8"/>
@@ -5547,7 +5733,7 @@
         <v>13</v>
       </c>
       <c r="I31" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J31" s="8">
         <v>0</v>
@@ -5560,7 +5746,7 @@
       </c>
       <c r="M31" s="8">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N31" s="8">
         <v>0</v>
@@ -5598,23 +5784,23 @@
         <v>12</v>
       </c>
       <c r="I32" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J32" s="8">
         <v>0</v>
       </c>
       <c r="K32" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L32" s="8">
         <v>0</v>
       </c>
       <c r="M32" s="8">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N32" s="8">
-        <v>1023</v>
+        <v>1002</v>
       </c>
       <c r="O32" s="8"/>
       <c r="P32" s="8"/>
@@ -5649,23 +5835,23 @@
         <v>12</v>
       </c>
       <c r="I33" s="8">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J33" s="8">
         <v>0</v>
       </c>
       <c r="K33" s="8">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="L33" s="8">
         <v>0</v>
       </c>
       <c r="M33" s="8">
         <f t="shared" si="0"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N33" s="8">
-        <v>182</v>
+        <v>85</v>
       </c>
       <c r="O33" s="8"/>
       <c r="P33" s="8"/>
@@ -5706,17 +5892,17 @@
         <v>0</v>
       </c>
       <c r="K34" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L34" s="8">
         <v>0</v>
       </c>
       <c r="M34" s="8">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N34" s="8">
-        <v>1195</v>
+        <v>1181</v>
       </c>
       <c r="O34" s="8"/>
       <c r="P34" s="8"/>
@@ -5767,7 +5953,7 @@
         <v>17</v>
       </c>
       <c r="N35" s="8">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="O35" s="8"/>
       <c r="P35" s="8"/>
@@ -5818,7 +6004,7 @@
         <v>15</v>
       </c>
       <c r="N36" s="8">
-        <v>386</v>
+        <v>373</v>
       </c>
       <c r="O36" s="8"/>
       <c r="P36" s="8"/>
@@ -5853,7 +6039,7 @@
         <v>13</v>
       </c>
       <c r="I37" s="8">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J37" s="8">
         <v>0</v>
@@ -5866,10 +6052,10 @@
       </c>
       <c r="M37" s="8">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="N37" s="8">
-        <v>36</v>
+        <v>490</v>
       </c>
       <c r="O37" s="8"/>
       <c r="P37" s="8"/>
@@ -5904,13 +6090,13 @@
         <v>12</v>
       </c>
       <c r="I38" s="8">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J38" s="8">
         <v>0</v>
       </c>
       <c r="K38" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L38" s="8">
         <v>0</v>
@@ -5920,7 +6106,7 @@
         <v>19</v>
       </c>
       <c r="N38" s="8">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="O38" s="8"/>
       <c r="P38" s="8"/>
@@ -5955,23 +6141,23 @@
         <v>12</v>
       </c>
       <c r="I39" s="8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J39" s="8">
         <v>0</v>
       </c>
       <c r="K39" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L39" s="8">
         <v>0</v>
       </c>
       <c r="M39" s="8">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N39" s="8">
-        <v>2429</v>
+        <v>2304</v>
       </c>
       <c r="O39" s="8"/>
       <c r="P39" s="8"/>
@@ -6012,17 +6198,17 @@
         <v>0</v>
       </c>
       <c r="K40" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L40" s="8">
         <v>0</v>
       </c>
       <c r="M40" s="8">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N40" s="8">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="O40" s="8"/>
       <c r="P40" s="8"/>
@@ -6057,13 +6243,13 @@
         <v>12</v>
       </c>
       <c r="I41" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J41" s="8">
         <v>0</v>
       </c>
       <c r="K41" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" s="8">
         <v>0</v>
@@ -6073,7 +6259,7 @@
         <v>20</v>
       </c>
       <c r="N41" s="8">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="O41" s="8"/>
       <c r="P41" s="8"/>
@@ -6108,23 +6294,23 @@
         <v>13</v>
       </c>
       <c r="I42" s="8">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J42" s="8">
         <v>0</v>
       </c>
       <c r="K42" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" s="8">
         <v>0</v>
       </c>
       <c r="M42" s="8">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="N42" s="8">
-        <v>1069</v>
+        <v>940</v>
       </c>
       <c r="O42" s="8"/>
       <c r="P42" s="8"/>
@@ -6159,23 +6345,23 @@
         <v>12</v>
       </c>
       <c r="I43" s="8">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J43" s="8">
         <v>0</v>
       </c>
       <c r="K43" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L43" s="8">
         <v>0</v>
       </c>
       <c r="M43" s="8">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N43" s="8">
-        <v>294</v>
+        <v>252</v>
       </c>
       <c r="O43" s="8"/>
       <c r="P43" s="8"/>
@@ -6210,13 +6396,13 @@
         <v>12</v>
       </c>
       <c r="I44" s="8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J44" s="8">
         <v>0</v>
       </c>
       <c r="K44" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L44" s="8">
         <v>0</v>
@@ -6226,7 +6412,7 @@
         <v>12</v>
       </c>
       <c r="N44" s="8">
-        <v>719</v>
+        <v>697</v>
       </c>
       <c r="O44" s="8"/>
       <c r="P44" s="8"/>
@@ -6261,23 +6447,23 @@
         <v>12</v>
       </c>
       <c r="I45" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J45" s="8">
         <v>0</v>
       </c>
       <c r="K45" s="8">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L45" s="8">
         <v>0</v>
       </c>
       <c r="M45" s="8">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="N45" s="8">
-        <v>574</v>
+        <v>544</v>
       </c>
       <c r="O45" s="8"/>
       <c r="P45" s="8"/>
@@ -6312,7 +6498,7 @@
         <v>12</v>
       </c>
       <c r="I46" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J46" s="8">
         <v>0</v>
@@ -6325,10 +6511,10 @@
       </c>
       <c r="M46" s="8">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N46" s="8">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="O46" s="8"/>
       <c r="P46" s="8"/>
@@ -6363,7 +6549,7 @@
         <v>13</v>
       </c>
       <c r="I47" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J47" s="8">
         <v>0</v>
@@ -6376,10 +6562,10 @@
       </c>
       <c r="M47" s="8">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N47" s="8">
-        <v>332</v>
+        <v>309</v>
       </c>
       <c r="O47" s="8"/>
       <c r="P47" s="8"/>
@@ -6414,7 +6600,7 @@
         <v>12</v>
       </c>
       <c r="I48" s="8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J48" s="8">
         <v>0</v>
@@ -6427,10 +6613,10 @@
       </c>
       <c r="M48" s="8">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N48" s="8">
-        <v>1906</v>
+        <v>1796</v>
       </c>
       <c r="O48" s="8"/>
       <c r="P48" s="8"/>
@@ -6481,7 +6667,7 @@
         <v>18</v>
       </c>
       <c r="N49" s="8">
-        <v>657</v>
+        <v>924</v>
       </c>
       <c r="O49" s="8"/>
       <c r="P49" s="8"/>
@@ -6516,7 +6702,7 @@
         <v>15</v>
       </c>
       <c r="I50" s="8">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J50" s="8">
         <v>0</v>
@@ -6529,10 +6715,10 @@
       </c>
       <c r="M50" s="8">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N50" s="8">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="O50" s="8"/>
       <c r="P50" s="8"/>
@@ -6573,17 +6759,17 @@
         <v>0</v>
       </c>
       <c r="K51" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L51" s="8">
         <v>0</v>
       </c>
       <c r="M51" s="8">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N51" s="8">
-        <v>96</v>
+        <v>554</v>
       </c>
       <c r="O51" s="8"/>
       <c r="P51" s="8"/>
@@ -6618,23 +6804,23 @@
         <v>12</v>
       </c>
       <c r="I52" s="8">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J52" s="8">
         <v>0</v>
       </c>
       <c r="K52" s="8">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L52" s="8">
         <v>0</v>
       </c>
       <c r="M52" s="8">
         <f t="shared" si="0"/>
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="N52" s="8">
-        <v>2592</v>
+        <v>2314</v>
       </c>
       <c r="O52" s="8"/>
       <c r="P52" s="8"/>
@@ -6669,7 +6855,7 @@
         <v>12</v>
       </c>
       <c r="I53" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J53" s="8">
         <v>0</v>
@@ -6682,10 +6868,10 @@
       </c>
       <c r="M53" s="8">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N53" s="8">
-        <v>279</v>
+        <v>256</v>
       </c>
       <c r="O53" s="8"/>
       <c r="P53" s="8"/>
@@ -6726,17 +6912,17 @@
         <v>0</v>
       </c>
       <c r="K54" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L54" s="8">
         <v>0</v>
       </c>
       <c r="M54" s="8">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N54" s="8">
-        <v>647</v>
+        <v>579</v>
       </c>
       <c r="O54" s="8"/>
       <c r="P54" s="8"/>
@@ -6771,23 +6957,23 @@
         <v>12</v>
       </c>
       <c r="I55" s="8">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="J55" s="8">
         <v>0</v>
       </c>
       <c r="K55" s="8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L55" s="8">
         <v>0</v>
       </c>
       <c r="M55" s="8">
         <f t="shared" si="0"/>
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N55" s="8">
-        <v>784</v>
+        <v>709</v>
       </c>
       <c r="O55" s="8"/>
       <c r="P55" s="8"/>
@@ -6822,7 +7008,7 @@
         <v>14</v>
       </c>
       <c r="I56" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J56" s="8">
         <v>0</v>
@@ -6835,10 +7021,10 @@
       </c>
       <c r="M56" s="8">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N56" s="8">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="O56" s="8"/>
       <c r="P56" s="8"/>
@@ -6879,17 +7065,17 @@
         <v>0</v>
       </c>
       <c r="K57" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" s="8">
         <v>0</v>
       </c>
       <c r="M57" s="8">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N57" s="8">
-        <v>845</v>
+        <v>812</v>
       </c>
       <c r="O57" s="8"/>
       <c r="P57" s="8"/>
@@ -6940,7 +7126,7 @@
         <v>7</v>
       </c>
       <c r="N58" s="8">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="O58" s="8"/>
       <c r="P58" s="8"/>
@@ -6991,7 +7177,7 @@
         <v>10</v>
       </c>
       <c r="N59" s="8">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="O59" s="8"/>
       <c r="P59" s="8"/>
@@ -7042,7 +7228,7 @@
         <v>6</v>
       </c>
       <c r="N60" s="8">
-        <v>625</v>
+        <v>900</v>
       </c>
       <c r="O60" s="8"/>
       <c r="P60" s="8"/>
@@ -7077,23 +7263,23 @@
         <v>12</v>
       </c>
       <c r="I61" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J61" s="8">
         <v>0</v>
       </c>
       <c r="K61" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L61" s="8">
         <v>0</v>
       </c>
       <c r="M61" s="8">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N61" s="8">
-        <v>240</v>
+        <v>130</v>
       </c>
       <c r="O61" s="8"/>
       <c r="P61" s="8"/>
@@ -7128,7 +7314,7 @@
         <v>12</v>
       </c>
       <c r="I62" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J62" s="8">
         <v>0</v>
@@ -7141,10 +7327,10 @@
       </c>
       <c r="M62" s="8">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N62" s="8">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="O62" s="8"/>
       <c r="P62" s="8"/>
@@ -7179,7 +7365,7 @@
         <v>12</v>
       </c>
       <c r="I63" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J63" s="8">
         <v>0</v>
@@ -7192,10 +7378,10 @@
       </c>
       <c r="M63" s="8">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N63" s="8">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="O63" s="8"/>
       <c r="P63" s="8"/>
@@ -7230,23 +7416,23 @@
         <v>13</v>
       </c>
       <c r="I64" s="8">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J64" s="8">
         <v>0</v>
       </c>
       <c r="K64" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" s="8">
         <v>0</v>
       </c>
       <c r="M64" s="8">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N64" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O64" s="8"/>
       <c r="P64" s="8"/>
@@ -7297,7 +7483,7 @@
         <v>10</v>
       </c>
       <c r="N65" s="8">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="O65" s="8"/>
       <c r="P65" s="8"/>
@@ -7383,7 +7569,7 @@
         <v>12</v>
       </c>
       <c r="I67" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J67" s="8">
         <v>0</v>
@@ -7396,10 +7582,10 @@
       </c>
       <c r="M67" s="8">
         <f t="shared" ref="M67:M130" si="1">I67+J67+K67+L67</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N67" s="8">
-        <v>476</v>
+        <v>359</v>
       </c>
       <c r="O67" s="8"/>
       <c r="P67" s="8"/>
@@ -7450,7 +7636,7 @@
         <v>7</v>
       </c>
       <c r="N68" s="8">
-        <v>881</v>
+        <v>1067</v>
       </c>
       <c r="O68" s="8"/>
       <c r="P68" s="8"/>
@@ -7485,23 +7671,23 @@
         <v>12</v>
       </c>
       <c r="I69" s="8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J69" s="8">
         <v>0</v>
       </c>
       <c r="K69" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L69" s="8">
         <v>0</v>
       </c>
       <c r="M69" s="8">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N69" s="8">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="O69" s="8"/>
       <c r="P69" s="8"/>
@@ -7552,7 +7738,7 @@
         <v>4</v>
       </c>
       <c r="N70" s="8">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="O70" s="8"/>
       <c r="P70" s="8"/>
@@ -7593,17 +7779,17 @@
         <v>0</v>
       </c>
       <c r="K71" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L71" s="8">
         <v>0</v>
       </c>
       <c r="M71" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N71" s="8">
-        <v>221</v>
+        <v>155</v>
       </c>
       <c r="O71" s="8"/>
       <c r="P71" s="8"/>
@@ -7638,7 +7824,7 @@
         <v>12</v>
       </c>
       <c r="I72" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J72" s="8">
         <v>0</v>
@@ -7651,10 +7837,10 @@
       </c>
       <c r="M72" s="8">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N72" s="8">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="O72" s="8"/>
       <c r="P72" s="8"/>
@@ -7689,23 +7875,23 @@
         <v>12</v>
       </c>
       <c r="I73" s="8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J73" s="8">
         <v>0</v>
       </c>
       <c r="K73" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L73" s="8">
         <v>0</v>
       </c>
       <c r="M73" s="8">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N73" s="8">
-        <v>1205</v>
+        <v>1141</v>
       </c>
       <c r="O73" s="8"/>
       <c r="P73" s="8"/>
@@ -7740,7 +7926,7 @@
         <v>14</v>
       </c>
       <c r="I74" s="8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J74" s="8">
         <v>0</v>
@@ -7753,10 +7939,10 @@
       </c>
       <c r="M74" s="8">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N74" s="8">
-        <v>480</v>
+        <v>448</v>
       </c>
       <c r="O74" s="8"/>
       <c r="P74" s="8"/>
@@ -7807,7 +7993,7 @@
         <v>8</v>
       </c>
       <c r="N75" s="8">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O75" s="8"/>
       <c r="P75" s="8"/>
@@ -7858,7 +8044,7 @@
         <v>7</v>
       </c>
       <c r="N76" s="8">
-        <v>506</v>
+        <v>493</v>
       </c>
       <c r="O76" s="8"/>
       <c r="P76" s="8"/>
@@ -7893,7 +8079,7 @@
         <v>12</v>
       </c>
       <c r="I77" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J77" s="8">
         <v>0</v>
@@ -7906,10 +8092,10 @@
       </c>
       <c r="M77" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N77" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O77" s="8"/>
       <c r="P77" s="8"/>
@@ -7944,23 +8130,23 @@
         <v>12</v>
       </c>
       <c r="I78" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J78" s="8">
         <v>0</v>
       </c>
       <c r="K78" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L78" s="8">
         <v>0</v>
       </c>
       <c r="M78" s="8">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N78" s="8">
-        <v>997</v>
+        <v>956</v>
       </c>
       <c r="O78" s="8"/>
       <c r="P78" s="8"/>
@@ -8011,7 +8197,7 @@
         <v>11</v>
       </c>
       <c r="N79" s="8">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="O79" s="8"/>
       <c r="P79" s="8"/>
@@ -8062,7 +8248,7 @@
         <v>6</v>
       </c>
       <c r="N80" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O80" s="8"/>
       <c r="P80" s="8"/>
@@ -8164,7 +8350,7 @@
         <v>5</v>
       </c>
       <c r="N82" s="8">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="O82" s="8"/>
       <c r="P82" s="8"/>
@@ -8215,7 +8401,7 @@
         <v>6</v>
       </c>
       <c r="N83" s="8">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="O83" s="8"/>
       <c r="P83" s="8"/>
@@ -8250,7 +8436,7 @@
         <v>13</v>
       </c>
       <c r="I84" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J84" s="8">
         <v>0</v>
@@ -8263,7 +8449,7 @@
       </c>
       <c r="M84" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N84" s="8">
         <v>0</v>
@@ -8317,7 +8503,7 @@
         <v>7</v>
       </c>
       <c r="N85" s="8">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="O85" s="8"/>
       <c r="P85" s="8"/>
@@ -8343,7 +8529,7 @@
         <v>19</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="G86" s="8" t="s">
         <v>1061</v>
@@ -8352,13 +8538,13 @@
         <v>12</v>
       </c>
       <c r="I86" s="8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J86" s="8">
         <v>0</v>
       </c>
       <c r="K86" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L86" s="8">
         <v>0</v>
@@ -8368,7 +8554,7 @@
         <v>19</v>
       </c>
       <c r="N86" s="8">
-        <v>782</v>
+        <v>770</v>
       </c>
       <c r="O86" s="8"/>
       <c r="P86" s="8"/>
@@ -8403,7 +8589,7 @@
         <v>13</v>
       </c>
       <c r="I87" s="8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J87" s="8">
         <v>0</v>
@@ -8416,10 +8602,10 @@
       </c>
       <c r="M87" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N87" s="8">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="O87" s="8"/>
       <c r="P87" s="8"/>
@@ -8470,7 +8656,7 @@
         <v>5</v>
       </c>
       <c r="N88" s="8">
-        <v>391</v>
+        <v>369</v>
       </c>
       <c r="O88" s="8"/>
       <c r="P88" s="8"/>
@@ -8505,23 +8691,23 @@
         <v>12</v>
       </c>
       <c r="I89" s="8">
+        <v>14</v>
+      </c>
+      <c r="J89" s="8">
+        <v>0</v>
+      </c>
+      <c r="K89" s="8">
         <v>11</v>
-      </c>
-      <c r="J89" s="8">
-        <v>0</v>
-      </c>
-      <c r="K89" s="8">
-        <v>9</v>
       </c>
       <c r="L89" s="8">
         <v>0</v>
       </c>
       <c r="M89" s="8">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N89" s="8">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="O89" s="8"/>
       <c r="P89" s="8"/>
@@ -8572,7 +8758,7 @@
         <v>7</v>
       </c>
       <c r="N90" s="8">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="O90" s="8"/>
       <c r="P90" s="8"/>
@@ -8623,7 +8809,7 @@
         <v>6</v>
       </c>
       <c r="N91" s="8">
-        <v>1095</v>
+        <v>1062</v>
       </c>
       <c r="O91" s="8"/>
       <c r="P91" s="8"/>
@@ -8658,23 +8844,23 @@
         <v>12</v>
       </c>
       <c r="I92" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J92" s="8">
         <v>0</v>
       </c>
       <c r="K92" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L92" s="8">
         <v>0</v>
       </c>
       <c r="M92" s="8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N92" s="8">
-        <v>535</v>
+        <v>477</v>
       </c>
       <c r="O92" s="8"/>
       <c r="P92" s="8"/>
@@ -8709,23 +8895,23 @@
         <v>13</v>
       </c>
       <c r="I93" s="8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J93" s="8">
         <v>0</v>
       </c>
       <c r="K93" s="8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L93" s="8">
         <v>0</v>
       </c>
       <c r="M93" s="8">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N93" s="8">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="O93" s="8"/>
       <c r="P93" s="8"/>
@@ -8827,7 +9013,7 @@
         <v>9</v>
       </c>
       <c r="N95" s="8">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="O95" s="8"/>
       <c r="P95" s="8"/>
@@ -8868,17 +9054,17 @@
         <v>0</v>
       </c>
       <c r="K96" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L96" s="8">
         <v>0</v>
       </c>
       <c r="M96" s="8">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N96" s="8">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="O96" s="8"/>
       <c r="P96" s="8"/>
@@ -8929,7 +9115,7 @@
         <v>7</v>
       </c>
       <c r="N97" s="8">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="O97" s="8"/>
       <c r="P97" s="8"/>
@@ -9066,23 +9252,23 @@
         <v>15</v>
       </c>
       <c r="I100" s="8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J100" s="8">
         <v>0</v>
       </c>
       <c r="K100" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L100" s="8">
         <v>0</v>
       </c>
       <c r="M100" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="N100" s="8">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="O100" s="8"/>
       <c r="P100" s="8"/>
@@ -9133,7 +9319,7 @@
         <v>4</v>
       </c>
       <c r="N101" s="8">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="O101" s="8"/>
       <c r="P101" s="8"/>
@@ -9184,7 +9370,7 @@
         <v>3</v>
       </c>
       <c r="N102" s="8">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="O102" s="8"/>
       <c r="P102" s="8"/>
@@ -9219,7 +9405,7 @@
         <v>15</v>
       </c>
       <c r="I103" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J103" s="8">
         <v>0</v>
@@ -9232,10 +9418,10 @@
       </c>
       <c r="M103" s="8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N103" s="8">
-        <v>109</v>
+        <v>622</v>
       </c>
       <c r="O103" s="8"/>
       <c r="P103" s="8"/>
@@ -9321,7 +9507,7 @@
         <v>12</v>
       </c>
       <c r="I105" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J105" s="8">
         <v>0</v>
@@ -9334,10 +9520,10 @@
       </c>
       <c r="M105" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N105" s="8">
-        <v>453</v>
+        <v>439</v>
       </c>
       <c r="O105" s="8"/>
       <c r="P105" s="8"/>
@@ -9388,7 +9574,7 @@
         <v>6</v>
       </c>
       <c r="N106" s="8">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O106" s="8"/>
       <c r="P106" s="8"/>
@@ -9439,7 +9625,7 @@
         <v>4</v>
       </c>
       <c r="N107" s="8">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="O107" s="8"/>
       <c r="P107" s="8"/>
@@ -9474,7 +9660,7 @@
         <v>15</v>
       </c>
       <c r="I108" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J108" s="8">
         <v>0</v>
@@ -9487,7 +9673,7 @@
       </c>
       <c r="M108" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N108" s="8">
         <v>0</v>
@@ -9525,7 +9711,7 @@
         <v>13</v>
       </c>
       <c r="I109" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J109" s="8">
         <v>0</v>
@@ -9538,10 +9724,10 @@
       </c>
       <c r="M109" s="8">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N109" s="8">
-        <v>362</v>
+        <v>341</v>
       </c>
       <c r="O109" s="8"/>
       <c r="P109" s="8"/>
@@ -9582,17 +9768,17 @@
         <v>0</v>
       </c>
       <c r="K110" s="8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L110" s="8">
         <v>0</v>
       </c>
       <c r="M110" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N110" s="8">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="O110" s="8"/>
       <c r="P110" s="8"/>
@@ -9627,7 +9813,7 @@
         <v>13</v>
       </c>
       <c r="I111" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J111" s="8">
         <v>0</v>
@@ -9640,7 +9826,7 @@
       </c>
       <c r="M111" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N111" s="8">
         <v>0</v>
@@ -9678,7 +9864,7 @@
         <v>12</v>
       </c>
       <c r="I112" s="8">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="J112" s="8">
         <v>0</v>
@@ -9691,10 +9877,10 @@
       </c>
       <c r="M112" s="8">
         <f t="shared" si="1"/>
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="N112" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O112" s="8"/>
       <c r="P112" s="8"/>
@@ -9729,23 +9915,23 @@
         <v>12</v>
       </c>
       <c r="I113" s="8">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J113" s="8">
         <v>0</v>
       </c>
       <c r="K113" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L113" s="8">
         <v>0</v>
       </c>
       <c r="M113" s="8">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N113" s="8">
-        <v>1050</v>
+        <v>1027</v>
       </c>
       <c r="O113" s="8"/>
       <c r="P113" s="8"/>
@@ -9780,7 +9966,7 @@
         <v>13</v>
       </c>
       <c r="I114" s="8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J114" s="8">
         <v>0</v>
@@ -9793,10 +9979,10 @@
       </c>
       <c r="M114" s="8">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N114" s="8">
-        <v>294</v>
+        <v>208</v>
       </c>
       <c r="O114" s="8"/>
       <c r="P114" s="8"/>
@@ -9831,7 +10017,7 @@
         <v>13</v>
       </c>
       <c r="I115" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J115" s="8">
         <v>0</v>
@@ -9844,10 +10030,10 @@
       </c>
       <c r="M115" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N115" s="8">
-        <v>368</v>
+        <v>338</v>
       </c>
       <c r="O115" s="8"/>
       <c r="P115" s="8"/>
@@ -9898,7 +10084,7 @@
         <v>9</v>
       </c>
       <c r="N116" s="8">
-        <v>956</v>
+        <v>938</v>
       </c>
       <c r="O116" s="8"/>
       <c r="P116" s="8"/>
@@ -9933,23 +10119,23 @@
         <v>12</v>
       </c>
       <c r="I117" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J117" s="8">
         <v>0</v>
       </c>
       <c r="K117" s="8">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L117" s="8">
         <v>0</v>
       </c>
       <c r="M117" s="8">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="N117" s="8">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="O117" s="8"/>
       <c r="P117" s="8"/>
@@ -9990,17 +10176,17 @@
         <v>0</v>
       </c>
       <c r="K118" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L118" s="8">
         <v>0</v>
       </c>
       <c r="M118" s="8">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N118" s="8">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="O118" s="8"/>
       <c r="P118" s="8"/>
@@ -10035,7 +10221,7 @@
         <v>14</v>
       </c>
       <c r="I119" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J119" s="8">
         <v>0</v>
@@ -10048,10 +10234,10 @@
       </c>
       <c r="M119" s="8">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N119" s="8">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="O119" s="8"/>
       <c r="P119" s="8"/>
@@ -10086,23 +10272,23 @@
         <v>14</v>
       </c>
       <c r="I120" s="8">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J120" s="8">
         <v>0</v>
       </c>
       <c r="K120" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L120" s="8">
         <v>0</v>
       </c>
       <c r="M120" s="8">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N120" s="8">
-        <v>419</v>
+        <v>375</v>
       </c>
       <c r="O120" s="8"/>
       <c r="P120" s="8"/>
@@ -10153,7 +10339,7 @@
         <v>8</v>
       </c>
       <c r="N121" s="8">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="O121" s="8"/>
       <c r="P121" s="8"/>
@@ -10188,13 +10374,13 @@
         <v>13</v>
       </c>
       <c r="I122" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J122" s="8">
         <v>0</v>
       </c>
       <c r="K122" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L122" s="8">
         <v>0</v>
@@ -10204,7 +10390,7 @@
         <v>3</v>
       </c>
       <c r="N122" s="8">
-        <v>1132</v>
+        <v>1127</v>
       </c>
       <c r="O122" s="8"/>
       <c r="P122" s="8"/>
@@ -10341,7 +10527,7 @@
         <v>13</v>
       </c>
       <c r="I125" s="8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J125" s="8">
         <v>0</v>
@@ -10354,10 +10540,10 @@
       </c>
       <c r="M125" s="8">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N125" s="8">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="O125" s="8"/>
       <c r="P125" s="8"/>
@@ -10510,7 +10696,7 @@
         <v>3</v>
       </c>
       <c r="N128" s="8">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="O128" s="8"/>
       <c r="P128" s="8"/>
@@ -10545,7 +10731,7 @@
         <v>15</v>
       </c>
       <c r="I129" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J129" s="8">
         <v>0</v>
@@ -10558,7 +10744,7 @@
       </c>
       <c r="M129" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N129" s="8">
         <v>0</v>
@@ -10596,23 +10782,23 @@
         <v>12</v>
       </c>
       <c r="I130" s="8">
+        <v>2</v>
+      </c>
+      <c r="J130" s="8">
+        <v>0</v>
+      </c>
+      <c r="K130" s="8">
         <v>3</v>
-      </c>
-      <c r="J130" s="8">
-        <v>0</v>
-      </c>
-      <c r="K130" s="8">
-        <v>5</v>
       </c>
       <c r="L130" s="8">
         <v>0</v>
       </c>
       <c r="M130" s="8">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N130" s="8">
-        <v>583</v>
+        <v>549</v>
       </c>
       <c r="O130" s="8"/>
       <c r="P130" s="8"/>
@@ -10663,7 +10849,7 @@
         <v>5</v>
       </c>
       <c r="N131" s="8">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="O131" s="8"/>
       <c r="P131" s="8"/>
@@ -10698,7 +10884,7 @@
         <v>12</v>
       </c>
       <c r="I132" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J132" s="8">
         <v>0</v>
@@ -10711,10 +10897,10 @@
       </c>
       <c r="M132" s="8">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N132" s="8">
-        <v>899</v>
+        <v>881</v>
       </c>
       <c r="O132" s="8"/>
       <c r="P132" s="8"/>
@@ -10749,13 +10935,13 @@
         <v>12</v>
       </c>
       <c r="I133" s="8">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J133" s="8">
         <v>0</v>
       </c>
       <c r="K133" s="8">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L133" s="8">
         <v>0</v>
@@ -10765,7 +10951,7 @@
         <v>19</v>
       </c>
       <c r="N133" s="8">
-        <v>180</v>
+        <v>22</v>
       </c>
       <c r="O133" s="8"/>
       <c r="P133" s="8"/>
@@ -10816,7 +11002,7 @@
         <v>4</v>
       </c>
       <c r="N134" s="8">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O134" s="8"/>
       <c r="P134" s="8"/>
@@ -10867,7 +11053,7 @@
         <v>4</v>
       </c>
       <c r="N135" s="8">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="O135" s="8"/>
       <c r="P135" s="8"/>
@@ -10902,7 +11088,7 @@
         <v>14</v>
       </c>
       <c r="I136" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J136" s="8">
         <v>0</v>
@@ -10915,10 +11101,10 @@
       </c>
       <c r="M136" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N136" s="8">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="O136" s="8"/>
       <c r="P136" s="8"/>
@@ -10969,7 +11155,7 @@
         <v>6</v>
       </c>
       <c r="N137" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O137" s="8"/>
       <c r="P137" s="8"/>
@@ -11020,7 +11206,7 @@
         <v>6</v>
       </c>
       <c r="N138" s="8">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="O138" s="8"/>
       <c r="P138" s="8"/>
@@ -11122,7 +11308,7 @@
         <v>5</v>
       </c>
       <c r="N140" s="8">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="O140" s="8"/>
       <c r="P140" s="8"/>
@@ -11259,13 +11445,13 @@
         <v>13</v>
       </c>
       <c r="I143" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J143" s="8">
         <v>0</v>
       </c>
       <c r="K143" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L143" s="8">
         <v>0</v>
@@ -11275,7 +11461,7 @@
         <v>4</v>
       </c>
       <c r="N143" s="8">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="O143" s="8"/>
       <c r="P143" s="8"/>
@@ -11377,7 +11563,7 @@
         <v>5</v>
       </c>
       <c r="N145" s="8">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="O145" s="8"/>
       <c r="P145" s="8"/>
@@ -11479,7 +11665,7 @@
         <v>4</v>
       </c>
       <c r="N147" s="8">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="O147" s="8"/>
       <c r="P147" s="8"/>
@@ -11581,7 +11767,7 @@
         <v>4</v>
       </c>
       <c r="N149" s="8">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="O149" s="8"/>
       <c r="P149" s="8"/>
@@ -11632,7 +11818,7 @@
         <v>3</v>
       </c>
       <c r="N150" s="8">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="O150" s="8"/>
       <c r="P150" s="8"/>
@@ -11667,13 +11853,13 @@
         <v>13</v>
       </c>
       <c r="I151" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J151" s="8">
         <v>0</v>
       </c>
       <c r="K151" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L151" s="8">
         <v>0</v>
@@ -11683,7 +11869,7 @@
         <v>6</v>
       </c>
       <c r="N151" s="8">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="O151" s="8"/>
       <c r="P151" s="8"/>
@@ -11734,7 +11920,7 @@
         <v>5</v>
       </c>
       <c r="N152" s="8">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="O152" s="8"/>
       <c r="P152" s="8"/>
@@ -11769,13 +11955,13 @@
         <v>13</v>
       </c>
       <c r="I153" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J153" s="8">
         <v>0</v>
       </c>
       <c r="K153" s="8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L153" s="8">
         <v>0</v>
@@ -11785,7 +11971,7 @@
         <v>10</v>
       </c>
       <c r="N153" s="8">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="O153" s="8"/>
       <c r="P153" s="8"/>
@@ -11836,7 +12022,7 @@
         <v>5</v>
       </c>
       <c r="N154" s="8">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="O154" s="8"/>
       <c r="P154" s="8"/>
@@ -12091,7 +12277,7 @@
         <v>5</v>
       </c>
       <c r="N159" s="8">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O159" s="8"/>
       <c r="P159" s="8"/>
@@ -12142,7 +12328,7 @@
         <v>5</v>
       </c>
       <c r="N160" s="8">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="O160" s="8"/>
       <c r="P160" s="8"/>
@@ -12177,7 +12363,7 @@
         <v>13</v>
       </c>
       <c r="I161" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J161" s="8">
         <v>0</v>
@@ -12190,10 +12376,10 @@
       </c>
       <c r="M161" s="8">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N161" s="8">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="O161" s="8"/>
       <c r="P161" s="8"/>
@@ -12244,7 +12430,7 @@
         <v>4</v>
       </c>
       <c r="N162" s="8">
-        <v>423</v>
+        <v>399</v>
       </c>
       <c r="O162" s="8"/>
       <c r="P162" s="8"/>
@@ -12279,7 +12465,7 @@
         <v>16</v>
       </c>
       <c r="I163" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J163" s="8">
         <v>0</v>
@@ -12292,7 +12478,7 @@
       </c>
       <c r="M163" s="8">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N163" s="8">
         <v>0</v>
@@ -12330,7 +12516,7 @@
         <v>16</v>
       </c>
       <c r="I164" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J164" s="8">
         <v>0</v>
@@ -12343,10 +12529,10 @@
       </c>
       <c r="M164" s="8">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N164" s="8">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="O164" s="8"/>
       <c r="P164" s="8"/>
@@ -12397,7 +12583,7 @@
         <v>3</v>
       </c>
       <c r="N165" s="8">
-        <v>1673</v>
+        <v>1658</v>
       </c>
       <c r="O165" s="8"/>
       <c r="P165" s="8"/>
@@ -12448,7 +12634,7 @@
         <v>5</v>
       </c>
       <c r="N166" s="8">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="O166" s="8"/>
       <c r="P166" s="8"/>
@@ -12483,7 +12669,7 @@
         <v>14</v>
       </c>
       <c r="I167" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J167" s="8">
         <v>0</v>
@@ -12496,7 +12682,7 @@
       </c>
       <c r="M167" s="8">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N167" s="8">
         <v>0</v>
@@ -12652,7 +12838,7 @@
         <v>5</v>
       </c>
       <c r="N170" s="8">
-        <v>366</v>
+        <v>558</v>
       </c>
       <c r="O170" s="8"/>
       <c r="P170" s="8"/>
@@ -12805,7 +12991,7 @@
         <v>4</v>
       </c>
       <c r="N173" s="8">
-        <v>675</v>
+        <v>662</v>
       </c>
       <c r="O173" s="8"/>
       <c r="P173" s="8"/>
@@ -12958,7 +13144,7 @@
         <v>3</v>
       </c>
       <c r="N176" s="8">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O176" s="8"/>
       <c r="P176" s="8"/>
@@ -13095,7 +13281,7 @@
         <v>15</v>
       </c>
       <c r="I179" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J179" s="8">
         <v>0</v>
@@ -13108,10 +13294,10 @@
       </c>
       <c r="M179" s="8">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N179" s="8">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="O179" s="8"/>
       <c r="P179" s="8"/>
@@ -13146,23 +13332,23 @@
         <v>13</v>
       </c>
       <c r="I180" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J180" s="8">
         <v>0</v>
       </c>
       <c r="K180" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L180" s="8">
         <v>0</v>
       </c>
       <c r="M180" s="8">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N180" s="8">
-        <v>330</v>
+        <v>285</v>
       </c>
       <c r="O180" s="8"/>
       <c r="P180" s="8"/>
@@ -13213,7 +13399,7 @@
         <v>5</v>
       </c>
       <c r="N181" s="8">
-        <v>315</v>
+        <v>287</v>
       </c>
       <c r="O181" s="8"/>
       <c r="P181" s="8"/>
@@ -13315,7 +13501,7 @@
         <v>7</v>
       </c>
       <c r="N183" s="8">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="O183" s="8"/>
       <c r="P183" s="8"/>
@@ -13350,23 +13536,23 @@
         <v>14</v>
       </c>
       <c r="I184" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J184" s="8">
         <v>0</v>
       </c>
       <c r="K184" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L184" s="8">
         <v>0</v>
       </c>
       <c r="M184" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N184" s="8">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="O184" s="8"/>
       <c r="P184" s="8"/>
@@ -13401,7 +13587,7 @@
         <v>12</v>
       </c>
       <c r="I185" s="8">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="J185" s="8">
         <v>0</v>
@@ -13410,14 +13596,14 @@
         <v>24</v>
       </c>
       <c r="L185" s="8">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="M185" s="8">
         <f t="shared" si="2"/>
-        <v>133</v>
+        <v>324</v>
       </c>
       <c r="N185" s="8">
-        <v>1502</v>
+        <v>1479</v>
       </c>
       <c r="O185" s="8"/>
       <c r="P185" s="8"/>
@@ -13452,23 +13638,23 @@
         <v>12</v>
       </c>
       <c r="I186" s="8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J186" s="8">
         <v>0</v>
       </c>
       <c r="K186" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L186" s="8">
         <v>0</v>
       </c>
       <c r="M186" s="8">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N186" s="8">
-        <v>1122</v>
+        <v>1089</v>
       </c>
       <c r="O186" s="8"/>
       <c r="P186" s="8"/>
@@ -13519,7 +13705,7 @@
         <v>2</v>
       </c>
       <c r="N187" s="8">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="O187" s="8"/>
       <c r="P187" s="8"/>
@@ -13605,7 +13791,7 @@
         <v>12</v>
       </c>
       <c r="I189" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J189" s="8">
         <v>0</v>
@@ -13618,7 +13804,7 @@
       </c>
       <c r="M189" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N189" s="8">
         <v>0</v>
@@ -13662,17 +13848,17 @@
         <v>0</v>
       </c>
       <c r="K190" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L190" s="8">
         <v>0</v>
       </c>
       <c r="M190" s="8">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N190" s="8">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="O190" s="8"/>
       <c r="P190" s="8"/>
@@ -13713,17 +13899,17 @@
         <v>0</v>
       </c>
       <c r="K191" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L191" s="8">
         <v>0</v>
       </c>
       <c r="M191" s="8">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N191" s="8">
-        <v>1282</v>
+        <v>1228</v>
       </c>
       <c r="O191" s="8"/>
       <c r="P191" s="8"/>
@@ -13825,7 +14011,7 @@
         <v>4</v>
       </c>
       <c r="N193" s="8">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="O193" s="8"/>
       <c r="P193" s="8"/>
@@ -13876,7 +14062,7 @@
         <v>5</v>
       </c>
       <c r="N194" s="8">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="O194" s="8"/>
       <c r="P194" s="8"/>
@@ -14029,7 +14215,7 @@
         <v>5</v>
       </c>
       <c r="N197" s="8">
-        <v>287</v>
+        <v>252</v>
       </c>
       <c r="O197" s="8"/>
       <c r="P197" s="8"/>
@@ -14064,13 +14250,13 @@
         <v>12</v>
       </c>
       <c r="I198" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J198" s="8">
         <v>0</v>
       </c>
       <c r="K198" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L198" s="8">
         <v>0</v>
@@ -14080,7 +14266,7 @@
         <v>11</v>
       </c>
       <c r="N198" s="8">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="O198" s="8"/>
       <c r="P198" s="8"/>
@@ -14131,7 +14317,7 @@
         <v>2</v>
       </c>
       <c r="N199" s="8">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="O199" s="8"/>
       <c r="P199" s="8"/>
@@ -14217,13 +14403,13 @@
         <v>12</v>
       </c>
       <c r="I201" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J201" s="8">
         <v>0</v>
       </c>
       <c r="K201" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L201" s="8">
         <v>0</v>
@@ -14233,7 +14419,7 @@
         <v>5</v>
       </c>
       <c r="N201" s="8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O201" s="8"/>
       <c r="P201" s="8"/>
@@ -14284,7 +14470,7 @@
         <v>3</v>
       </c>
       <c r="N202" s="8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O202" s="8"/>
       <c r="P202" s="8"/>
@@ -14437,7 +14623,7 @@
         <v>6</v>
       </c>
       <c r="N205" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O205" s="8"/>
       <c r="P205" s="8"/>
@@ -14539,7 +14725,7 @@
         <v>4</v>
       </c>
       <c r="N207" s="8">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="O207" s="8"/>
       <c r="P207" s="8"/>
@@ -14590,7 +14776,7 @@
         <v>3</v>
       </c>
       <c r="N208" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O208" s="8"/>
       <c r="P208" s="8"/>
@@ -14641,7 +14827,7 @@
         <v>4</v>
       </c>
       <c r="N209" s="8">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="O209" s="8"/>
       <c r="P209" s="8"/>
@@ -14743,7 +14929,7 @@
         <v>4</v>
       </c>
       <c r="N211" s="8">
-        <v>826</v>
+        <v>821</v>
       </c>
       <c r="O211" s="8"/>
       <c r="P211" s="8"/>
@@ -14829,7 +15015,7 @@
         <v>14</v>
       </c>
       <c r="I213" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J213" s="8">
         <v>0</v>
@@ -14842,7 +15028,7 @@
       </c>
       <c r="M213" s="8">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N213" s="8">
         <v>0</v>
@@ -14896,7 +15082,7 @@
         <v>4</v>
       </c>
       <c r="N214" s="8">
-        <v>498</v>
+        <v>484</v>
       </c>
       <c r="O214" s="8"/>
       <c r="P214" s="8"/>
@@ -14931,13 +15117,13 @@
         <v>14</v>
       </c>
       <c r="I215" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J215" s="8">
         <v>0</v>
       </c>
       <c r="K215" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L215" s="8">
         <v>0</v>
@@ -14947,7 +15133,7 @@
         <v>6</v>
       </c>
       <c r="N215" s="8">
-        <v>788</v>
+        <v>779</v>
       </c>
       <c r="O215" s="8"/>
       <c r="P215" s="8"/>
@@ -14982,13 +15168,13 @@
         <v>14</v>
       </c>
       <c r="I216" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J216" s="8">
         <v>0</v>
       </c>
       <c r="K216" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L216" s="8">
         <v>0</v>
@@ -15049,7 +15235,7 @@
         <v>4</v>
       </c>
       <c r="N217" s="8">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="O217" s="8"/>
       <c r="P217" s="8"/>
@@ -15100,7 +15286,7 @@
         <v>6</v>
       </c>
       <c r="N218" s="8">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O218" s="8"/>
       <c r="P218" s="8"/>
@@ -15151,7 +15337,7 @@
         <v>6</v>
       </c>
       <c r="N219" s="8">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="O219" s="8"/>
       <c r="P219" s="8"/>
@@ -15304,7 +15490,7 @@
         <v>2</v>
       </c>
       <c r="N222" s="8">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="O222" s="8"/>
       <c r="P222" s="8"/>
@@ -15355,7 +15541,7 @@
         <v>3</v>
       </c>
       <c r="N223" s="8">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="O223" s="8"/>
       <c r="P223" s="8"/>
@@ -15406,7 +15592,7 @@
         <v>3</v>
       </c>
       <c r="N224" s="8">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="O224" s="8"/>
       <c r="P224" s="8"/>
@@ -15457,7 +15643,7 @@
         <v>4</v>
       </c>
       <c r="N225" s="8">
-        <v>585</v>
+        <v>560</v>
       </c>
       <c r="O225" s="8"/>
       <c r="P225" s="8"/>
@@ -15492,7 +15678,7 @@
         <v>14</v>
       </c>
       <c r="I226" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J226" s="8">
         <v>0</v>
@@ -15505,7 +15691,7 @@
       </c>
       <c r="M226" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N226" s="8">
         <v>0</v>
@@ -15543,13 +15729,13 @@
         <v>16</v>
       </c>
       <c r="I227" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J227" s="8">
         <v>0</v>
       </c>
       <c r="K227" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L227" s="8">
         <v>0</v>
@@ -15559,7 +15745,7 @@
         <v>2</v>
       </c>
       <c r="N227" s="8">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="O227" s="8"/>
       <c r="P227" s="8"/>
@@ -15600,17 +15786,17 @@
         <v>0</v>
       </c>
       <c r="K228" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L228" s="8">
         <v>0</v>
       </c>
       <c r="M228" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N228" s="8">
-        <v>300</v>
+        <v>248</v>
       </c>
       <c r="O228" s="8"/>
       <c r="P228" s="8"/>
@@ -15645,7 +15831,7 @@
         <v>15</v>
       </c>
       <c r="I229" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J229" s="8">
         <v>0</v>
@@ -15658,10 +15844,10 @@
       </c>
       <c r="M229" s="8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N229" s="8">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="O229" s="8"/>
       <c r="P229" s="8"/>
@@ -15712,7 +15898,7 @@
         <v>5</v>
       </c>
       <c r="N230" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O230" s="8"/>
       <c r="P230" s="8"/>
@@ -15814,7 +16000,7 @@
         <v>16</v>
       </c>
       <c r="N232" s="8">
-        <v>957</v>
+        <v>903</v>
       </c>
       <c r="O232" s="8"/>
       <c r="P232" s="8"/>
@@ -15849,7 +16035,7 @@
         <v>15</v>
       </c>
       <c r="I233" s="8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J233" s="8">
         <v>0</v>
@@ -15862,10 +16048,10 @@
       </c>
       <c r="M233" s="8">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N233" s="8">
-        <v>896</v>
+        <v>872</v>
       </c>
       <c r="O233" s="8"/>
       <c r="P233" s="8"/>
@@ -15916,7 +16102,7 @@
         <v>2</v>
       </c>
       <c r="N234" s="8">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="O234" s="8"/>
       <c r="P234" s="8"/>
@@ -15951,7 +16137,7 @@
         <v>14</v>
       </c>
       <c r="I235" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J235" s="8">
         <v>0</v>
@@ -15964,10 +16150,10 @@
       </c>
       <c r="M235" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N235" s="8">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="O235" s="8"/>
       <c r="P235" s="8"/>
@@ -16069,7 +16255,7 @@
         <v>4</v>
       </c>
       <c r="N237" s="8">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="O237" s="8"/>
       <c r="P237" s="8"/>
@@ -16120,7 +16306,7 @@
         <v>7</v>
       </c>
       <c r="N238" s="8">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="O238" s="8"/>
       <c r="P238" s="8"/>
@@ -16171,7 +16357,7 @@
         <v>5</v>
       </c>
       <c r="N239" s="8">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="O239" s="8"/>
       <c r="P239" s="8"/>
@@ -16222,7 +16408,7 @@
         <v>4</v>
       </c>
       <c r="N240" s="8">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O240" s="8"/>
       <c r="P240" s="8"/>
@@ -16273,7 +16459,7 @@
         <v>3</v>
       </c>
       <c r="N241" s="8">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="O241" s="8"/>
       <c r="P241" s="8"/>
@@ -16308,7 +16494,7 @@
         <v>12</v>
       </c>
       <c r="I242" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J242" s="8">
         <v>0</v>
@@ -16321,10 +16507,10 @@
       </c>
       <c r="M242" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N242" s="8">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="O242" s="8"/>
       <c r="P242" s="8"/>
@@ -16365,17 +16551,17 @@
         <v>0</v>
       </c>
       <c r="K243" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L243" s="8">
         <v>0</v>
       </c>
       <c r="M243" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N243" s="8">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="O243" s="8"/>
       <c r="P243" s="8"/>
@@ -16512,7 +16698,7 @@
         <v>15</v>
       </c>
       <c r="I246" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J246" s="8">
         <v>0</v>
@@ -16525,10 +16711,10 @@
       </c>
       <c r="M246" s="8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N246" s="8">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="O246" s="8"/>
       <c r="P246" s="8"/>
@@ -16579,7 +16765,7 @@
         <v>3</v>
       </c>
       <c r="N247" s="8">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="O247" s="8"/>
       <c r="P247" s="8"/>
@@ -16732,7 +16918,7 @@
         <v>3</v>
       </c>
       <c r="N250" s="8">
-        <v>1535</v>
+        <v>1524</v>
       </c>
       <c r="O250" s="8"/>
       <c r="P250" s="8"/>
@@ -16783,7 +16969,7 @@
         <v>3</v>
       </c>
       <c r="N251" s="8">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="O251" s="8"/>
       <c r="P251" s="8"/>
@@ -16834,7 +17020,7 @@
         <v>3</v>
       </c>
       <c r="N252" s="8">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="O252" s="8"/>
       <c r="P252" s="8"/>
@@ -16885,7 +17071,7 @@
         <v>3</v>
       </c>
       <c r="N253" s="8">
-        <v>787</v>
+        <v>1082</v>
       </c>
       <c r="O253" s="8"/>
       <c r="P253" s="8"/>
@@ -16936,7 +17122,7 @@
         <v>3</v>
       </c>
       <c r="N254" s="8">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="O254" s="8"/>
       <c r="P254" s="8"/>
@@ -16987,7 +17173,7 @@
         <v>3</v>
       </c>
       <c r="N255" s="8">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O255" s="8"/>
       <c r="P255" s="8"/>
@@ -17038,7 +17224,7 @@
         <v>3</v>
       </c>
       <c r="N256" s="8">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="O256" s="8"/>
       <c r="P256" s="8"/>
@@ -17073,23 +17259,23 @@
         <v>14</v>
       </c>
       <c r="I257" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J257" s="8">
         <v>0</v>
       </c>
       <c r="K257" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L257" s="8">
         <v>0</v>
       </c>
       <c r="M257" s="8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N257" s="8">
-        <v>458</v>
+        <v>439</v>
       </c>
       <c r="O257" s="8"/>
       <c r="P257" s="8"/>
@@ -17242,7 +17428,7 @@
         <v>7</v>
       </c>
       <c r="N260" s="8">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="O260" s="8"/>
       <c r="P260" s="8"/>
@@ -17277,7 +17463,7 @@
         <v>12</v>
       </c>
       <c r="I261" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J261" s="8">
         <v>0</v>
@@ -17290,10 +17476,10 @@
       </c>
       <c r="M261" s="8">
         <f t="shared" si="4"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N261" s="8">
-        <v>1547</v>
+        <v>1470</v>
       </c>
       <c r="O261" s="8"/>
       <c r="P261" s="8"/>
@@ -17328,23 +17514,23 @@
         <v>12</v>
       </c>
       <c r="I262" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J262" s="8">
         <v>0</v>
       </c>
       <c r="K262" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L262" s="8">
         <v>0</v>
       </c>
       <c r="M262" s="8">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N262" s="8">
-        <v>419</v>
+        <v>395</v>
       </c>
       <c r="O262" s="8"/>
       <c r="P262" s="8"/>
@@ -17379,23 +17565,23 @@
         <v>12</v>
       </c>
       <c r="I263" s="8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J263" s="8">
         <v>0</v>
       </c>
       <c r="K263" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L263" s="8">
         <v>0</v>
       </c>
       <c r="M263" s="8">
         <f t="shared" si="4"/>
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="N263" s="8">
-        <v>784</v>
+        <v>705</v>
       </c>
       <c r="O263" s="8"/>
       <c r="P263" s="8"/>
@@ -17532,7 +17718,7 @@
         <v>14</v>
       </c>
       <c r="I266" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J266" s="8">
         <v>0</v>
@@ -17545,10 +17731,10 @@
       </c>
       <c r="M266" s="8">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N266" s="8">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="O266" s="8"/>
       <c r="P266" s="8"/>
@@ -17599,7 +17785,7 @@
         <v>2</v>
       </c>
       <c r="N267" s="8">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O267" s="8"/>
       <c r="P267" s="8"/>
@@ -17640,17 +17826,17 @@
         <v>0</v>
       </c>
       <c r="K268" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L268" s="8">
         <v>0</v>
       </c>
       <c r="M268" s="8">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N268" s="8">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="O268" s="8"/>
       <c r="P268" s="8"/>
@@ -17701,7 +17887,7 @@
         <v>9</v>
       </c>
       <c r="N269" s="8">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="O269" s="8"/>
       <c r="P269" s="8"/>
@@ -17803,7 +17989,7 @@
         <v>3</v>
       </c>
       <c r="N271" s="8">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="O271" s="8"/>
       <c r="P271" s="8"/>
@@ -17940,13 +18126,13 @@
         <v>16</v>
       </c>
       <c r="I274" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J274" s="8">
         <v>0</v>
       </c>
       <c r="K274" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L274" s="8">
         <v>0</v>
@@ -17956,7 +18142,7 @@
         <v>5</v>
       </c>
       <c r="N274" s="8">
-        <v>140</v>
+        <v>111</v>
       </c>
       <c r="O274" s="8"/>
       <c r="P274" s="8"/>
@@ -18007,7 +18193,7 @@
         <v>4</v>
       </c>
       <c r="N275" s="8">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O275" s="8"/>
       <c r="P275" s="8"/>
@@ -18058,7 +18244,7 @@
         <v>4</v>
       </c>
       <c r="N276" s="8">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="O276" s="8"/>
       <c r="P276" s="8"/>
@@ -18093,20 +18279,20 @@
         <v>13</v>
       </c>
       <c r="I277" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J277" s="8">
         <v>0</v>
       </c>
       <c r="K277" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L277" s="8">
         <v>0</v>
       </c>
       <c r="M277" s="8">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N277" s="8">
         <v>0</v>
@@ -18144,23 +18330,23 @@
         <v>12</v>
       </c>
       <c r="I278" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J278" s="8">
         <v>0</v>
       </c>
       <c r="K278" s="8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L278" s="8">
         <v>0</v>
       </c>
       <c r="M278" s="8">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N278" s="8">
-        <v>862</v>
+        <v>686</v>
       </c>
       <c r="O278" s="8"/>
       <c r="P278" s="8"/>
@@ -18211,7 +18397,7 @@
         <v>3</v>
       </c>
       <c r="N279" s="8">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O279" s="8"/>
       <c r="P279" s="8"/>
@@ -18297,13 +18483,13 @@
         <v>16</v>
       </c>
       <c r="I281" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J281" s="8">
         <v>0</v>
       </c>
       <c r="K281" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L281" s="8">
         <v>0</v>
@@ -18399,13 +18585,13 @@
         <v>12</v>
       </c>
       <c r="I283" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J283" s="8">
         <v>0</v>
       </c>
       <c r="K283" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L283" s="8">
         <v>0</v>
@@ -18415,7 +18601,7 @@
         <v>4</v>
       </c>
       <c r="N283" s="8">
-        <v>495</v>
+        <v>440</v>
       </c>
       <c r="O283" s="8"/>
       <c r="P283" s="8"/>
@@ -18450,23 +18636,23 @@
         <v>12</v>
       </c>
       <c r="I284" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J284" s="8">
         <v>0</v>
       </c>
       <c r="K284" s="8">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="L284" s="8">
         <v>0</v>
       </c>
       <c r="M284" s="8">
         <f t="shared" si="4"/>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N284" s="8">
-        <v>664</v>
+        <v>487</v>
       </c>
       <c r="O284" s="8"/>
       <c r="P284" s="8"/>
@@ -18558,17 +18744,17 @@
         <v>0</v>
       </c>
       <c r="K286" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L286" s="8">
         <v>0</v>
       </c>
       <c r="M286" s="8">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N286" s="8">
-        <v>792</v>
+        <v>776</v>
       </c>
       <c r="O286" s="8"/>
       <c r="P286" s="8"/>
@@ -18603,7 +18789,7 @@
         <v>12</v>
       </c>
       <c r="I287" s="8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J287" s="8">
         <v>0</v>
@@ -18616,10 +18802,10 @@
       </c>
       <c r="M287" s="8">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N287" s="8">
-        <v>485</v>
+        <v>885</v>
       </c>
       <c r="O287" s="8"/>
       <c r="P287" s="8"/>
@@ -18670,7 +18856,7 @@
         <v>6</v>
       </c>
       <c r="N288" s="8">
-        <v>1723</v>
+        <v>1687</v>
       </c>
       <c r="O288" s="8"/>
       <c r="P288" s="8"/>
@@ -18705,7 +18891,7 @@
         <v>14</v>
       </c>
       <c r="I289" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J289" s="8">
         <v>0</v>
@@ -18718,10 +18904,10 @@
       </c>
       <c r="M289" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N289" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O289" s="8"/>
       <c r="P289" s="8"/>
@@ -18772,7 +18958,7 @@
         <v>3</v>
       </c>
       <c r="N290" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O290" s="8"/>
       <c r="P290" s="8"/>
@@ -18807,23 +18993,23 @@
         <v>12</v>
       </c>
       <c r="I291" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J291" s="8">
         <v>0</v>
       </c>
       <c r="K291" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L291" s="8">
         <v>0</v>
       </c>
       <c r="M291" s="8">
         <f t="shared" si="4"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N291" s="8">
-        <v>805</v>
+        <v>576</v>
       </c>
       <c r="O291" s="8"/>
       <c r="P291" s="8"/>
@@ -18874,7 +19060,7 @@
         <v>4</v>
       </c>
       <c r="N292" s="8">
-        <v>36</v>
+        <v>226</v>
       </c>
       <c r="O292" s="8"/>
       <c r="P292" s="8"/>
@@ -18960,23 +19146,23 @@
         <v>12</v>
       </c>
       <c r="I294" s="8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J294" s="8">
         <v>0</v>
       </c>
       <c r="K294" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L294" s="8">
         <v>0</v>
       </c>
       <c r="M294" s="8">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N294" s="8">
-        <v>1467</v>
+        <v>1443</v>
       </c>
       <c r="O294" s="8"/>
       <c r="P294" s="8"/>
@@ -19113,7 +19299,7 @@
         <v>17</v>
       </c>
       <c r="I297" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J297" s="8">
         <v>0</v>
@@ -19126,7 +19312,7 @@
       </c>
       <c r="M297" s="8">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N297" s="8">
         <v>0</v>
@@ -19272,17 +19458,17 @@
         <v>0</v>
       </c>
       <c r="K300" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L300" s="8">
         <v>0</v>
       </c>
       <c r="M300" s="8">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N300" s="8">
-        <v>205</v>
+        <v>176</v>
       </c>
       <c r="O300" s="8"/>
       <c r="P300" s="8"/>
@@ -19384,7 +19570,7 @@
         <v>7</v>
       </c>
       <c r="N302" s="8">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O302" s="8"/>
       <c r="P302" s="8"/>
@@ -19435,7 +19621,7 @@
         <v>4</v>
       </c>
       <c r="N303" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O303" s="8"/>
       <c r="P303" s="8"/>
@@ -19486,7 +19672,7 @@
         <v>4</v>
       </c>
       <c r="N304" s="8">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O304" s="8"/>
       <c r="P304" s="8"/>
@@ -19537,7 +19723,7 @@
         <v>10</v>
       </c>
       <c r="N305" s="8">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="O305" s="8"/>
       <c r="P305" s="8"/>
@@ -19572,7 +19758,7 @@
         <v>13</v>
       </c>
       <c r="I306" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J306" s="8">
         <v>0</v>
@@ -19585,10 +19771,10 @@
       </c>
       <c r="M306" s="8">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N306" s="8">
-        <v>1466</v>
+        <v>1400</v>
       </c>
       <c r="O306" s="8"/>
       <c r="P306" s="8"/>
@@ -19639,7 +19825,7 @@
         <v>12</v>
       </c>
       <c r="N307" s="8">
-        <v>1209</v>
+        <v>1196</v>
       </c>
       <c r="O307" s="8"/>
       <c r="P307" s="8"/>
@@ -19674,7 +19860,7 @@
         <v>13</v>
       </c>
       <c r="I308" s="8">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J308" s="8">
         <v>0</v>
@@ -19687,10 +19873,10 @@
       </c>
       <c r="M308" s="8">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N308" s="8">
-        <v>890</v>
+        <v>828</v>
       </c>
       <c r="O308" s="8"/>
       <c r="P308" s="8"/>
@@ -19792,7 +19978,7 @@
         <v>4</v>
       </c>
       <c r="N310" s="8">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="O310" s="8"/>
       <c r="P310" s="8"/>
@@ -19843,7 +20029,7 @@
         <v>3</v>
       </c>
       <c r="N311" s="8">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="O311" s="8"/>
       <c r="P311" s="8"/>
@@ -19894,7 +20080,7 @@
         <v>3</v>
       </c>
       <c r="N312" s="8">
-        <v>353</v>
+        <v>318</v>
       </c>
       <c r="O312" s="8"/>
       <c r="P312" s="8"/>
@@ -19945,7 +20131,7 @@
         <v>3</v>
       </c>
       <c r="N313" s="8">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O313" s="8"/>
       <c r="P313" s="8"/>
@@ -19980,7 +20166,7 @@
         <v>12</v>
       </c>
       <c r="I314" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J314" s="8">
         <v>0</v>
@@ -19993,10 +20179,10 @@
       </c>
       <c r="M314" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N314" s="8">
-        <v>447</v>
+        <v>416</v>
       </c>
       <c r="O314" s="8"/>
       <c r="P314" s="8"/>
@@ -20047,7 +20233,7 @@
         <v>8</v>
       </c>
       <c r="N315" s="8">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="O315" s="8"/>
       <c r="P315" s="8"/>
@@ -20082,7 +20268,7 @@
         <v>12</v>
       </c>
       <c r="I316" s="8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J316" s="8">
         <v>0</v>
@@ -20095,10 +20281,10 @@
       </c>
       <c r="M316" s="8">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N316" s="8">
-        <v>313</v>
+        <v>279</v>
       </c>
       <c r="O316" s="8"/>
       <c r="P316" s="8"/>
@@ -20149,7 +20335,7 @@
         <v>3</v>
       </c>
       <c r="N317" s="8">
-        <v>111</v>
+        <v>395</v>
       </c>
       <c r="O317" s="8"/>
       <c r="P317" s="8"/>
@@ -20184,7 +20370,7 @@
         <v>12</v>
       </c>
       <c r="I318" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J318" s="8">
         <v>0</v>
@@ -20197,10 +20383,10 @@
       </c>
       <c r="M318" s="8">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N318" s="8">
-        <v>1462</v>
+        <v>1239</v>
       </c>
       <c r="O318" s="8"/>
       <c r="P318" s="8"/>
@@ -20251,7 +20437,7 @@
         <v>4</v>
       </c>
       <c r="N319" s="8">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="O319" s="8"/>
       <c r="P319" s="8"/>
@@ -20302,7 +20488,7 @@
         <v>4</v>
       </c>
       <c r="N320" s="8">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="O320" s="8"/>
       <c r="P320" s="8"/>
@@ -20353,7 +20539,7 @@
         <v>2</v>
       </c>
       <c r="N321" s="8">
-        <v>679</v>
+        <v>649</v>
       </c>
       <c r="O321" s="8"/>
       <c r="P321" s="8"/>
@@ -20404,7 +20590,7 @@
         <v>3</v>
       </c>
       <c r="N322" s="8">
-        <v>321</v>
+        <v>522</v>
       </c>
       <c r="O322" s="8"/>
       <c r="P322" s="8"/>
@@ -20451,11 +20637,11 @@
         <v>0</v>
       </c>
       <c r="M323" s="8">
-        <f t="shared" ref="M323:M374" si="5">I323+J323+K323+L323</f>
+        <f t="shared" ref="M323:M384" si="5">I323+J323+K323+L323</f>
         <v>4</v>
       </c>
       <c r="N323" s="8">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="O323" s="8"/>
       <c r="P323" s="8"/>
@@ -20557,7 +20743,7 @@
         <v>4</v>
       </c>
       <c r="N325" s="8">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="O325" s="8"/>
       <c r="P325" s="8"/>
@@ -20608,7 +20794,7 @@
         <v>3</v>
       </c>
       <c r="N326" s="8">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="O326" s="8"/>
       <c r="P326" s="8"/>
@@ -20659,7 +20845,7 @@
         <v>3</v>
       </c>
       <c r="N327" s="8">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O327" s="8"/>
       <c r="P327" s="8"/>
@@ -20761,7 +20947,7 @@
         <v>4</v>
       </c>
       <c r="N329" s="8">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="O329" s="8"/>
       <c r="P329" s="8"/>
@@ -20847,7 +21033,7 @@
         <v>13</v>
       </c>
       <c r="I331" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J331" s="8">
         <v>0</v>
@@ -20860,7 +21046,7 @@
       </c>
       <c r="M331" s="8">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N331" s="8">
         <v>0</v>
@@ -20949,7 +21135,7 @@
         <v>13</v>
       </c>
       <c r="I333" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J333" s="8">
         <v>0</v>
@@ -20962,7 +21148,7 @@
       </c>
       <c r="M333" s="8">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N333" s="8">
         <v>370</v>
@@ -21118,7 +21304,7 @@
         <v>6</v>
       </c>
       <c r="N336" s="8">
-        <v>849</v>
+        <v>825</v>
       </c>
       <c r="O336" s="8"/>
       <c r="P336" s="8"/>
@@ -21153,7 +21339,7 @@
         <v>12</v>
       </c>
       <c r="I337" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J337" s="8">
         <v>0</v>
@@ -21166,10 +21352,10 @@
       </c>
       <c r="M337" s="8">
         <f t="shared" si="5"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N337" s="8">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="O337" s="8"/>
       <c r="P337" s="8"/>
@@ -21220,7 +21406,7 @@
         <v>8</v>
       </c>
       <c r="N338" s="8">
-        <v>1543</v>
+        <v>1491</v>
       </c>
       <c r="O338" s="8"/>
       <c r="P338" s="8"/>
@@ -21271,7 +21457,7 @@
         <v>5</v>
       </c>
       <c r="N339" s="8">
-        <v>1015</v>
+        <v>988</v>
       </c>
       <c r="O339" s="8"/>
       <c r="P339" s="8"/>
@@ -21306,13 +21492,13 @@
         <v>14</v>
       </c>
       <c r="I340" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J340" s="8">
         <v>0</v>
       </c>
       <c r="K340" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L340" s="8">
         <v>0</v>
@@ -21322,7 +21508,7 @@
         <v>2</v>
       </c>
       <c r="N340" s="8">
-        <v>1037</v>
+        <v>976</v>
       </c>
       <c r="O340" s="8"/>
       <c r="P340" s="8"/>
@@ -21373,7 +21559,7 @@
         <v>5</v>
       </c>
       <c r="N341" s="8">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="O341" s="8"/>
       <c r="P341" s="8"/>
@@ -21424,7 +21610,7 @@
         <v>4</v>
       </c>
       <c r="N342" s="8">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="O342" s="8"/>
       <c r="P342" s="8"/>
@@ -21459,13 +21645,13 @@
         <v>14</v>
       </c>
       <c r="I343" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J343" s="8">
         <v>0</v>
       </c>
       <c r="K343" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L343" s="8">
         <v>0</v>
@@ -21475,7 +21661,7 @@
         <v>4</v>
       </c>
       <c r="N343" s="8">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="O343" s="8"/>
       <c r="P343" s="8"/>
@@ -21485,18 +21671,22 @@
       <c r="T343" s="8"/>
     </row>
     <row r="344" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A344" s="7"/>
-      <c r="B344" s="7" t="s">
+      <c r="A344" s="9" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B344" s="9" t="s">
         <v>1102</v>
       </c>
-      <c r="C344" s="7" t="s">
+      <c r="C344" s="9" t="s">
         <v>1071</v>
       </c>
-      <c r="D344" s="7"/>
+      <c r="D344" s="8" t="s">
+        <v>20</v>
+      </c>
       <c r="E344" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F344" s="7" t="s">
+      <c r="F344" s="8" t="s">
         <v>1067</v>
       </c>
       <c r="G344" s="8" t="s">
@@ -21505,8 +21695,8 @@
       <c r="H344" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="I344" s="7">
-        <v>1</v>
+      <c r="I344" s="8">
+        <v>2</v>
       </c>
       <c r="J344" s="8">
         <v>0</v>
@@ -21519,31 +21709,35 @@
       </c>
       <c r="M344" s="8">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="N344" s="7">
-        <v>0</v>
-      </c>
-      <c r="O344" s="7"/>
-      <c r="P344" s="7"/>
-      <c r="Q344" s="7"/>
-      <c r="R344" s="7"/>
-      <c r="S344" s="7"/>
-      <c r="T344" s="7"/>
+        <v>2</v>
+      </c>
+      <c r="N344" s="8">
+        <v>0</v>
+      </c>
+      <c r="O344" s="8"/>
+      <c r="P344" s="9"/>
+      <c r="Q344" s="9"/>
+      <c r="R344" s="9"/>
+      <c r="S344" s="9"/>
+      <c r="T344" s="9"/>
     </row>
     <row r="345" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A345" s="7"/>
-      <c r="B345" s="7" t="s">
+      <c r="A345" s="9" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B345" s="9" t="s">
         <v>1103</v>
       </c>
-      <c r="C345" s="7" t="s">
+      <c r="C345" s="9" t="s">
         <v>1072</v>
       </c>
-      <c r="D345" s="7"/>
+      <c r="D345" s="8" t="s">
+        <v>20</v>
+      </c>
       <c r="E345" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F345" s="7" t="s">
+      <c r="F345" s="8" t="s">
         <v>1067</v>
       </c>
       <c r="G345" s="8" t="s">
@@ -21552,8 +21746,8 @@
       <c r="H345" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="I345" s="7">
-        <v>3</v>
+      <c r="I345" s="8">
+        <v>12</v>
       </c>
       <c r="J345" s="8">
         <v>0</v>
@@ -21566,31 +21760,35 @@
       </c>
       <c r="M345" s="8">
         <f t="shared" si="5"/>
-        <v>3</v>
-      </c>
-      <c r="N345" s="7">
-        <v>0</v>
-      </c>
-      <c r="O345" s="7"/>
-      <c r="P345" s="7"/>
-      <c r="Q345" s="7"/>
-      <c r="R345" s="7"/>
-      <c r="S345" s="7"/>
-      <c r="T345" s="7"/>
+        <v>12</v>
+      </c>
+      <c r="N345" s="8">
+        <v>0</v>
+      </c>
+      <c r="O345" s="8"/>
+      <c r="P345" s="9"/>
+      <c r="Q345" s="9"/>
+      <c r="R345" s="9"/>
+      <c r="S345" s="9"/>
+      <c r="T345" s="9"/>
     </row>
     <row r="346" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A346" s="7"/>
-      <c r="B346" s="7" t="s">
+      <c r="A346" s="9" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B346" s="9" t="s">
         <v>1104</v>
       </c>
-      <c r="C346" s="7" t="s">
+      <c r="C346" s="9" t="s">
         <v>1073</v>
       </c>
-      <c r="D346" s="7"/>
+      <c r="D346" s="8" t="s">
+        <v>20</v>
+      </c>
       <c r="E346" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F346" s="7" t="s">
+      <c r="F346" s="8" t="s">
         <v>1067</v>
       </c>
       <c r="G346" s="8" t="s">
@@ -21599,8 +21797,8 @@
       <c r="H346" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="I346" s="7">
-        <v>304</v>
+      <c r="I346" s="8">
+        <v>312</v>
       </c>
       <c r="J346" s="8">
         <v>0</v>
@@ -21613,78 +21811,86 @@
       </c>
       <c r="M346" s="8">
         <f t="shared" si="5"/>
-        <v>304</v>
-      </c>
-      <c r="N346" s="7">
-        <v>0</v>
-      </c>
-      <c r="O346" s="7"/>
-      <c r="P346" s="7"/>
-      <c r="Q346" s="7"/>
-      <c r="R346" s="7"/>
-      <c r="S346" s="7"/>
-      <c r="T346" s="7"/>
+        <v>312</v>
+      </c>
+      <c r="N346" s="8">
+        <v>0</v>
+      </c>
+      <c r="O346" s="8"/>
+      <c r="P346" s="9"/>
+      <c r="Q346" s="9"/>
+      <c r="R346" s="9"/>
+      <c r="S346" s="9"/>
+      <c r="T346" s="9"/>
     </row>
     <row r="347" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A347" s="7"/>
-      <c r="B347" s="7" t="s">
+      <c r="A347" s="9" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B347" s="9" t="s">
         <v>1105</v>
       </c>
-      <c r="C347" s="7" t="s">
+      <c r="C347" s="9" t="s">
         <v>1074</v>
       </c>
-      <c r="D347" s="7"/>
+      <c r="D347" s="8" t="s">
+        <v>701</v>
+      </c>
       <c r="E347" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F347" s="7" t="s">
+      <c r="F347" s="9" t="s">
         <v>1068</v>
       </c>
-      <c r="G347" s="7" t="s">
+      <c r="G347" s="8" t="s">
         <v>1061</v>
       </c>
       <c r="H347" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="I347" s="7">
-        <v>1</v>
+      <c r="I347" s="8">
+        <v>2</v>
       </c>
       <c r="J347" s="8">
         <v>0</v>
       </c>
       <c r="K347" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L347" s="8">
         <v>0</v>
       </c>
       <c r="M347" s="8">
         <f t="shared" si="5"/>
-        <v>4</v>
-      </c>
-      <c r="N347" s="7">
-        <v>396</v>
-      </c>
-      <c r="O347" s="7"/>
-      <c r="P347" s="7"/>
-      <c r="Q347" s="7"/>
-      <c r="R347" s="7"/>
-      <c r="S347" s="7"/>
-      <c r="T347" s="7"/>
+        <v>7</v>
+      </c>
+      <c r="N347" s="8">
+        <v>337</v>
+      </c>
+      <c r="O347" s="8"/>
+      <c r="P347" s="9"/>
+      <c r="Q347" s="9"/>
+      <c r="R347" s="9"/>
+      <c r="S347" s="9"/>
+      <c r="T347" s="9"/>
     </row>
     <row r="348" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A348" s="7"/>
-      <c r="B348" s="7" t="s">
+      <c r="A348" s="9" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B348" s="9" t="s">
         <v>1106</v>
       </c>
-      <c r="C348" s="7" t="s">
+      <c r="C348" s="9" t="s">
         <v>1075</v>
       </c>
-      <c r="D348" s="7"/>
+      <c r="D348" s="8" t="s">
+        <v>701</v>
+      </c>
       <c r="E348" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F348" s="7" t="s">
+      <c r="F348" s="8" t="s">
         <v>1067</v>
       </c>
       <c r="G348" s="8" t="s">
@@ -21693,61 +21899,65 @@
       <c r="H348" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="I348" s="7">
-        <v>64</v>
+      <c r="I348" s="8">
+        <v>85</v>
       </c>
       <c r="J348" s="8">
         <v>0</v>
       </c>
       <c r="K348" s="8">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="L348" s="8">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M348" s="8">
         <f t="shared" si="5"/>
-        <v>88</v>
-      </c>
-      <c r="N348" s="7">
+        <v>97</v>
+      </c>
+      <c r="N348" s="8">
         <v>189</v>
       </c>
-      <c r="O348" s="7"/>
-      <c r="P348" s="7"/>
-      <c r="Q348" s="7"/>
-      <c r="R348" s="7"/>
-      <c r="S348" s="7"/>
-      <c r="T348" s="7"/>
+      <c r="O348" s="8"/>
+      <c r="P348" s="9"/>
+      <c r="Q348" s="9"/>
+      <c r="R348" s="9"/>
+      <c r="S348" s="9"/>
+      <c r="T348" s="9"/>
     </row>
     <row r="349" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A349" s="7"/>
-      <c r="B349" s="7" t="s">
+      <c r="A349" s="9" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B349" s="9" t="s">
         <v>1107</v>
       </c>
-      <c r="C349" s="7" t="s">
+      <c r="C349" s="9" t="s">
         <v>1076</v>
       </c>
-      <c r="D349" s="7"/>
+      <c r="D349" s="8" t="s">
+        <v>30</v>
+      </c>
       <c r="E349" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F349" s="7" t="s">
+      <c r="F349" s="9" t="s">
         <v>1070</v>
       </c>
-      <c r="G349" s="7" t="s">
+      <c r="G349" s="9" t="s">
         <v>1062</v>
       </c>
       <c r="H349" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="I349" s="7">
-        <v>0</v>
+      <c r="I349" s="8">
+        <v>1</v>
       </c>
       <c r="J349" s="8">
         <v>0</v>
       </c>
       <c r="K349" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L349" s="8">
         <v>0</v>
@@ -21756,38 +21966,42 @@
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="N349" s="7">
-        <v>2</v>
-      </c>
-      <c r="O349" s="7"/>
-      <c r="P349" s="7"/>
-      <c r="Q349" s="7"/>
-      <c r="R349" s="7"/>
-      <c r="S349" s="7"/>
-      <c r="T349" s="7"/>
+      <c r="N349" s="8">
+        <v>0</v>
+      </c>
+      <c r="O349" s="8"/>
+      <c r="P349" s="9"/>
+      <c r="Q349" s="9"/>
+      <c r="R349" s="9"/>
+      <c r="S349" s="9"/>
+      <c r="T349" s="9"/>
     </row>
     <row r="350" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A350" s="7"/>
-      <c r="B350" s="7" t="s">
+      <c r="A350" s="9" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B350" s="9" t="s">
         <v>1108</v>
       </c>
-      <c r="C350" s="7" t="s">
+      <c r="C350" s="9" t="s">
         <v>1077</v>
       </c>
-      <c r="D350" s="7"/>
+      <c r="D350" s="8" t="s">
+        <v>75</v>
+      </c>
       <c r="E350" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F350" s="7" t="s">
+      <c r="F350" s="9" t="s">
         <v>1068</v>
       </c>
-      <c r="G350" s="7" t="s">
+      <c r="G350" s="8" t="s">
         <v>1061</v>
       </c>
       <c r="H350" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="I350" s="7">
+      <c r="I350" s="8">
         <v>0</v>
       </c>
       <c r="J350" s="8">
@@ -21803,39 +22017,43 @@
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="N350" s="7">
-        <v>0</v>
-      </c>
-      <c r="O350" s="7"/>
-      <c r="P350" s="7"/>
-      <c r="Q350" s="7"/>
-      <c r="R350" s="7"/>
-      <c r="S350" s="7"/>
-      <c r="T350" s="7"/>
+      <c r="N350" s="8">
+        <v>0</v>
+      </c>
+      <c r="O350" s="8"/>
+      <c r="P350" s="9"/>
+      <c r="Q350" s="9"/>
+      <c r="R350" s="9"/>
+      <c r="S350" s="9"/>
+      <c r="T350" s="9"/>
     </row>
     <row r="351" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A351" s="7"/>
-      <c r="B351" s="7" t="s">
+      <c r="A351" s="9" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B351" s="9" t="s">
         <v>1109</v>
       </c>
-      <c r="C351" s="7" t="s">
+      <c r="C351" s="9" t="s">
         <v>1078</v>
       </c>
-      <c r="D351" s="7"/>
+      <c r="D351" s="8" t="s">
+        <v>75</v>
+      </c>
       <c r="E351" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F351" s="7" t="s">
+      <c r="F351" s="9" t="s">
         <v>1068</v>
       </c>
-      <c r="G351" s="7" t="s">
+      <c r="G351" s="8" t="s">
         <v>1061</v>
       </c>
       <c r="H351" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I351" s="7">
-        <v>1</v>
+      <c r="I351" s="8">
+        <v>0</v>
       </c>
       <c r="J351" s="8">
         <v>0</v>
@@ -21848,40 +22066,44 @@
       </c>
       <c r="M351" s="8">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="N351" s="7">
-        <v>0</v>
-      </c>
-      <c r="O351" s="7"/>
-      <c r="P351" s="7"/>
-      <c r="Q351" s="7"/>
-      <c r="R351" s="7"/>
-      <c r="S351" s="7"/>
-      <c r="T351" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="N351" s="8">
+        <v>0</v>
+      </c>
+      <c r="O351" s="8"/>
+      <c r="P351" s="9"/>
+      <c r="Q351" s="9"/>
+      <c r="R351" s="9"/>
+      <c r="S351" s="9"/>
+      <c r="T351" s="9"/>
     </row>
     <row r="352" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A352" s="7"/>
-      <c r="B352" s="7" t="s">
+      <c r="A352" s="9" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B352" s="9" t="s">
         <v>1110</v>
       </c>
-      <c r="C352" s="7" t="s">
+      <c r="C352" s="9" t="s">
         <v>1079</v>
       </c>
-      <c r="D352" s="7"/>
+      <c r="D352" s="8" t="s">
+        <v>75</v>
+      </c>
       <c r="E352" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F352" s="7" t="s">
+      <c r="F352" s="9" t="s">
         <v>1068</v>
       </c>
-      <c r="G352" s="7" t="s">
+      <c r="G352" s="8" t="s">
         <v>1061</v>
       </c>
       <c r="H352" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I352" s="7">
+      <c r="I352" s="8">
         <v>3</v>
       </c>
       <c r="J352" s="8">
@@ -21897,45 +22119,49 @@
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="N352" s="7">
-        <v>592</v>
-      </c>
-      <c r="O352" s="7"/>
-      <c r="P352" s="7"/>
-      <c r="Q352" s="7"/>
-      <c r="R352" s="7"/>
-      <c r="S352" s="7"/>
-      <c r="T352" s="7"/>
+      <c r="N352" s="8">
+        <v>578</v>
+      </c>
+      <c r="O352" s="8"/>
+      <c r="P352" s="9"/>
+      <c r="Q352" s="9"/>
+      <c r="R352" s="9"/>
+      <c r="S352" s="9"/>
+      <c r="T352" s="9"/>
     </row>
     <row r="353" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A353" s="7"/>
-      <c r="B353" s="7" t="s">
+      <c r="A353" s="9" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B353" s="9" t="s">
         <v>1111</v>
       </c>
-      <c r="C353" s="7" t="s">
+      <c r="C353" s="9" t="s">
         <v>1080</v>
       </c>
-      <c r="D353" s="7"/>
+      <c r="D353" s="8" t="s">
+        <v>30</v>
+      </c>
       <c r="E353" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F353" s="7" t="s">
+      <c r="F353" s="9" t="s">
         <v>1070</v>
       </c>
-      <c r="G353" s="7" t="s">
+      <c r="G353" s="9" t="s">
         <v>1062</v>
       </c>
       <c r="H353" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I353" s="7">
-        <v>0</v>
+      <c r="I353" s="8">
+        <v>1</v>
       </c>
       <c r="J353" s="8">
         <v>0</v>
       </c>
       <c r="K353" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L353" s="8">
         <v>0</v>
@@ -21944,38 +22170,42 @@
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="N353" s="7">
-        <v>0</v>
-      </c>
-      <c r="O353" s="7"/>
-      <c r="P353" s="7"/>
-      <c r="Q353" s="7"/>
-      <c r="R353" s="7"/>
-      <c r="S353" s="7"/>
-      <c r="T353" s="7"/>
+      <c r="N353" s="8">
+        <v>0</v>
+      </c>
+      <c r="O353" s="8"/>
+      <c r="P353" s="9"/>
+      <c r="Q353" s="9"/>
+      <c r="R353" s="9"/>
+      <c r="S353" s="9"/>
+      <c r="T353" s="9"/>
     </row>
     <row r="354" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A354" s="7"/>
-      <c r="B354" s="7" t="s">
+      <c r="A354" s="9" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B354" s="9" t="s">
         <v>1112</v>
       </c>
-      <c r="C354" s="7" t="s">
+      <c r="C354" s="9" t="s">
         <v>1081</v>
       </c>
-      <c r="D354" s="7"/>
+      <c r="D354" s="8" t="s">
+        <v>75</v>
+      </c>
       <c r="E354" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F354" s="7" t="s">
+      <c r="F354" s="9" t="s">
         <v>1070</v>
       </c>
-      <c r="G354" s="7" t="s">
+      <c r="G354" s="9" t="s">
         <v>1062</v>
       </c>
       <c r="H354" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="I354" s="7">
+      <c r="I354" s="8">
         <v>0</v>
       </c>
       <c r="J354" s="8">
@@ -21991,85 +22221,93 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N354" s="7">
-        <v>0</v>
-      </c>
-      <c r="O354" s="7"/>
-      <c r="P354" s="7"/>
-      <c r="Q354" s="7"/>
-      <c r="R354" s="7"/>
-      <c r="S354" s="7"/>
-      <c r="T354" s="7"/>
+      <c r="N354" s="8">
+        <v>0</v>
+      </c>
+      <c r="O354" s="8"/>
+      <c r="P354" s="9"/>
+      <c r="Q354" s="9"/>
+      <c r="R354" s="9"/>
+      <c r="S354" s="9"/>
+      <c r="T354" s="9"/>
     </row>
     <row r="355" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A355" s="7"/>
-      <c r="B355" s="7" t="s">
+      <c r="A355" s="9" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B355" s="9" t="s">
         <v>1113</v>
       </c>
-      <c r="C355" s="7" t="s">
+      <c r="C355" s="9" t="s">
         <v>1082</v>
       </c>
-      <c r="D355" s="7"/>
+      <c r="D355" s="8" t="s">
+        <v>30</v>
+      </c>
       <c r="E355" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F355" s="7" t="s">
+      <c r="F355" s="9" t="s">
         <v>1070</v>
       </c>
-      <c r="G355" s="7" t="s">
+      <c r="G355" s="9" t="s">
         <v>1062</v>
       </c>
       <c r="H355" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I355" s="7">
+      <c r="I355" s="8">
         <v>1</v>
       </c>
       <c r="J355" s="8">
         <v>0</v>
       </c>
       <c r="K355" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L355" s="8">
         <v>0</v>
       </c>
       <c r="M355" s="8">
         <f t="shared" si="5"/>
-        <v>3</v>
-      </c>
-      <c r="N355" s="7">
-        <v>13</v>
-      </c>
-      <c r="O355" s="7"/>
-      <c r="P355" s="7"/>
-      <c r="Q355" s="7"/>
-      <c r="R355" s="7"/>
-      <c r="S355" s="7"/>
-      <c r="T355" s="7"/>
+        <v>2</v>
+      </c>
+      <c r="N355" s="8">
+        <v>7</v>
+      </c>
+      <c r="O355" s="8"/>
+      <c r="P355" s="9"/>
+      <c r="Q355" s="9"/>
+      <c r="R355" s="9"/>
+      <c r="S355" s="9"/>
+      <c r="T355" s="9"/>
     </row>
     <row r="356" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A356" s="7"/>
-      <c r="B356" s="7" t="s">
+      <c r="A356" s="9" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B356" s="9" t="s">
         <v>1114</v>
       </c>
-      <c r="C356" s="7" t="s">
+      <c r="C356" s="9" t="s">
         <v>1083</v>
       </c>
-      <c r="D356" s="7"/>
+      <c r="D356" s="8" t="s">
+        <v>75</v>
+      </c>
       <c r="E356" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F356" s="7" t="s">
+      <c r="F356" s="9" t="s">
         <v>1070</v>
       </c>
-      <c r="G356" s="7" t="s">
+      <c r="G356" s="9" t="s">
         <v>1062</v>
       </c>
       <c r="H356" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I356" s="7">
+      <c r="I356" s="8">
         <v>0</v>
       </c>
       <c r="J356" s="8">
@@ -22085,38 +22323,42 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N356" s="7">
-        <v>0</v>
-      </c>
-      <c r="O356" s="7"/>
-      <c r="P356" s="7"/>
-      <c r="Q356" s="7"/>
-      <c r="R356" s="7"/>
-      <c r="S356" s="7"/>
-      <c r="T356" s="7"/>
+      <c r="N356" s="8">
+        <v>0</v>
+      </c>
+      <c r="O356" s="8"/>
+      <c r="P356" s="9"/>
+      <c r="Q356" s="9"/>
+      <c r="R356" s="9"/>
+      <c r="S356" s="9"/>
+      <c r="T356" s="9"/>
     </row>
     <row r="357" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A357" s="7"/>
-      <c r="B357" s="7" t="s">
+      <c r="A357" s="9" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B357" s="9" t="s">
         <v>1115</v>
       </c>
-      <c r="C357" s="7" t="s">
+      <c r="C357" s="9" t="s">
         <v>1084</v>
       </c>
-      <c r="D357" s="7"/>
+      <c r="D357" s="8" t="s">
+        <v>75</v>
+      </c>
       <c r="E357" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F357" s="7" t="s">
+      <c r="F357" s="9" t="s">
         <v>1070</v>
       </c>
-      <c r="G357" s="7" t="s">
+      <c r="G357" s="9" t="s">
         <v>1062</v>
       </c>
       <c r="H357" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="I357" s="7">
+      <c r="I357" s="8">
         <v>0</v>
       </c>
       <c r="J357" s="8">
@@ -22132,38 +22374,42 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N357" s="7">
-        <v>0</v>
-      </c>
-      <c r="O357" s="7"/>
-      <c r="P357" s="7"/>
-      <c r="Q357" s="7"/>
-      <c r="R357" s="7"/>
-      <c r="S357" s="7"/>
-      <c r="T357" s="7"/>
+      <c r="N357" s="8">
+        <v>0</v>
+      </c>
+      <c r="O357" s="8"/>
+      <c r="P357" s="9"/>
+      <c r="Q357" s="9"/>
+      <c r="R357" s="9"/>
+      <c r="S357" s="9"/>
+      <c r="T357" s="9"/>
     </row>
     <row r="358" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A358" s="7"/>
-      <c r="B358" s="7" t="s">
+      <c r="A358" s="9" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B358" s="9" t="s">
         <v>1116</v>
       </c>
-      <c r="C358" s="7" t="s">
+      <c r="C358" s="9" t="s">
         <v>1085</v>
       </c>
-      <c r="D358" s="7"/>
+      <c r="D358" s="8" t="s">
+        <v>75</v>
+      </c>
       <c r="E358" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F358" s="7" t="s">
+      <c r="F358" s="9" t="s">
         <v>1068</v>
       </c>
-      <c r="G358" s="7" t="s">
+      <c r="G358" s="8" t="s">
         <v>1061</v>
       </c>
       <c r="H358" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="I358" s="7">
+      <c r="I358" s="8">
         <v>0</v>
       </c>
       <c r="J358" s="8">
@@ -22179,45 +22425,49 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N358" s="7">
-        <v>0</v>
-      </c>
-      <c r="O358" s="7"/>
-      <c r="P358" s="7"/>
-      <c r="Q358" s="7"/>
-      <c r="R358" s="7"/>
-      <c r="S358" s="7"/>
-      <c r="T358" s="7"/>
+      <c r="N358" s="8">
+        <v>0</v>
+      </c>
+      <c r="O358" s="8"/>
+      <c r="P358" s="9"/>
+      <c r="Q358" s="9"/>
+      <c r="R358" s="9"/>
+      <c r="S358" s="9"/>
+      <c r="T358" s="9"/>
     </row>
     <row r="359" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A359" s="7"/>
-      <c r="B359" s="7" t="s">
+      <c r="A359" s="9" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B359" s="9" t="s">
         <v>1117</v>
       </c>
-      <c r="C359" s="7" t="s">
+      <c r="C359" s="9" t="s">
         <v>1086</v>
       </c>
-      <c r="D359" s="7"/>
+      <c r="D359" s="8" t="s">
+        <v>75</v>
+      </c>
       <c r="E359" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F359" s="7" t="s">
+      <c r="F359" s="9" t="s">
         <v>1068</v>
       </c>
-      <c r="G359" s="7" t="s">
+      <c r="G359" s="8" t="s">
         <v>1061</v>
       </c>
       <c r="H359" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I359" s="7">
-        <v>0</v>
+      <c r="I359" s="8">
+        <v>1</v>
       </c>
       <c r="J359" s="8">
         <v>0</v>
       </c>
       <c r="K359" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L359" s="8">
         <v>0</v>
@@ -22226,38 +22476,42 @@
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="N359" s="7">
-        <v>1</v>
-      </c>
-      <c r="O359" s="7"/>
-      <c r="P359" s="7"/>
-      <c r="Q359" s="7"/>
-      <c r="R359" s="7"/>
-      <c r="S359" s="7"/>
-      <c r="T359" s="7"/>
+      <c r="N359" s="8">
+        <v>0</v>
+      </c>
+      <c r="O359" s="8"/>
+      <c r="P359" s="9"/>
+      <c r="Q359" s="9"/>
+      <c r="R359" s="9"/>
+      <c r="S359" s="9"/>
+      <c r="T359" s="9"/>
     </row>
     <row r="360" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A360" s="7"/>
-      <c r="B360" s="7" t="s">
+      <c r="A360" s="9" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B360" s="9" t="s">
         <v>1118</v>
       </c>
-      <c r="C360" s="7" t="s">
+      <c r="C360" s="9" t="s">
         <v>1087</v>
       </c>
-      <c r="D360" s="7"/>
+      <c r="D360" s="8" t="s">
+        <v>30</v>
+      </c>
       <c r="E360" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F360" s="7" t="s">
+      <c r="F360" s="9" t="s">
         <v>1068</v>
       </c>
-      <c r="G360" s="7" t="s">
+      <c r="G360" s="8" t="s">
         <v>1061</v>
       </c>
       <c r="H360" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I360" s="7">
+      <c r="I360" s="8">
         <v>0</v>
       </c>
       <c r="J360" s="8">
@@ -22273,38 +22527,42 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N360" s="7">
-        <v>0</v>
-      </c>
-      <c r="O360" s="7"/>
-      <c r="P360" s="7"/>
-      <c r="Q360" s="7"/>
-      <c r="R360" s="7"/>
-      <c r="S360" s="7"/>
-      <c r="T360" s="7"/>
+      <c r="N360" s="8">
+        <v>0</v>
+      </c>
+      <c r="O360" s="8"/>
+      <c r="P360" s="9"/>
+      <c r="Q360" s="9"/>
+      <c r="R360" s="9"/>
+      <c r="S360" s="9"/>
+      <c r="T360" s="9"/>
     </row>
     <row r="361" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A361" s="7"/>
-      <c r="B361" s="7" t="s">
+      <c r="A361" s="9" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B361" s="9" t="s">
         <v>1119</v>
       </c>
-      <c r="C361" s="7" t="s">
+      <c r="C361" s="9" t="s">
         <v>1088</v>
       </c>
-      <c r="D361" s="7"/>
+      <c r="D361" s="8" t="s">
+        <v>75</v>
+      </c>
       <c r="E361" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F361" s="7" t="s">
+      <c r="F361" s="9" t="s">
         <v>1070</v>
       </c>
-      <c r="G361" s="7" t="s">
+      <c r="G361" s="9" t="s">
         <v>1062</v>
       </c>
       <c r="H361" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I361" s="7">
+      <c r="I361" s="8">
         <v>0</v>
       </c>
       <c r="J361" s="8">
@@ -22320,38 +22578,42 @@
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="N361" s="7">
-        <v>0</v>
-      </c>
-      <c r="O361" s="7"/>
-      <c r="P361" s="7"/>
-      <c r="Q361" s="7"/>
-      <c r="R361" s="7"/>
-      <c r="S361" s="7"/>
-      <c r="T361" s="7"/>
+      <c r="N361" s="8">
+        <v>0</v>
+      </c>
+      <c r="O361" s="8"/>
+      <c r="P361" s="9"/>
+      <c r="Q361" s="9"/>
+      <c r="R361" s="9"/>
+      <c r="S361" s="9"/>
+      <c r="T361" s="9"/>
     </row>
     <row r="362" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A362" s="7"/>
-      <c r="B362" s="7" t="s">
+      <c r="A362" s="9" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B362" s="9" t="s">
         <v>1120</v>
       </c>
-      <c r="C362" s="7" t="s">
+      <c r="C362" s="9" t="s">
         <v>1089</v>
       </c>
-      <c r="D362" s="7"/>
+      <c r="D362" s="8" t="s">
+        <v>75</v>
+      </c>
       <c r="E362" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F362" s="7" t="s">
+      <c r="F362" s="9" t="s">
         <v>1070</v>
       </c>
-      <c r="G362" s="7" t="s">
+      <c r="G362" s="9" t="s">
         <v>1062</v>
       </c>
       <c r="H362" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="I362" s="7">
+      <c r="I362" s="8">
         <v>0</v>
       </c>
       <c r="J362" s="8">
@@ -22367,29 +22629,33 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N362" s="7">
-        <v>0</v>
-      </c>
-      <c r="O362" s="7"/>
-      <c r="P362" s="7"/>
-      <c r="Q362" s="7"/>
-      <c r="R362" s="7"/>
-      <c r="S362" s="7"/>
-      <c r="T362" s="7"/>
+      <c r="N362" s="8">
+        <v>0</v>
+      </c>
+      <c r="O362" s="8"/>
+      <c r="P362" s="9"/>
+      <c r="Q362" s="9"/>
+      <c r="R362" s="9"/>
+      <c r="S362" s="9"/>
+      <c r="T362" s="9"/>
     </row>
     <row r="363" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A363" s="7"/>
-      <c r="B363" s="7" t="s">
+      <c r="A363" s="9" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B363" s="9" t="s">
         <v>1121</v>
       </c>
-      <c r="C363" s="7" t="s">
+      <c r="C363" s="9" t="s">
         <v>1090</v>
       </c>
-      <c r="D363" s="7"/>
+      <c r="D363" s="8" t="s">
+        <v>418</v>
+      </c>
       <c r="E363" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F363" s="7" t="s">
+      <c r="F363" s="8" t="s">
         <v>1067</v>
       </c>
       <c r="G363" s="8" t="s">
@@ -22398,61 +22664,65 @@
       <c r="H363" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="I363" s="7">
-        <v>0</v>
+      <c r="I363" s="8">
+        <v>48</v>
       </c>
       <c r="J363" s="8">
         <v>0</v>
       </c>
       <c r="K363" s="8">
+        <v>0</v>
+      </c>
+      <c r="L363" s="8">
         <v>48</v>
-      </c>
-      <c r="L363" s="8">
-        <v>0</v>
       </c>
       <c r="M363" s="8">
         <f t="shared" si="5"/>
-        <v>48</v>
-      </c>
-      <c r="N363" s="7">
+        <v>96</v>
+      </c>
+      <c r="N363" s="8">
         <v>240</v>
       </c>
-      <c r="O363" s="7"/>
-      <c r="P363" s="7"/>
-      <c r="Q363" s="7"/>
-      <c r="R363" s="7"/>
-      <c r="S363" s="7"/>
-      <c r="T363" s="7"/>
+      <c r="O363" s="8"/>
+      <c r="P363" s="9"/>
+      <c r="Q363" s="9"/>
+      <c r="R363" s="9"/>
+      <c r="S363" s="9"/>
+      <c r="T363" s="9"/>
     </row>
     <row r="364" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A364" s="7"/>
-      <c r="B364" s="7" t="s">
+      <c r="A364" s="9" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B364" s="9" t="s">
         <v>1122</v>
       </c>
-      <c r="C364" s="7" t="s">
+      <c r="C364" s="9" t="s">
         <v>1091</v>
       </c>
-      <c r="D364" s="7"/>
+      <c r="D364" s="8" t="s">
+        <v>418</v>
+      </c>
       <c r="E364" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F364" s="7" t="s">
+      <c r="F364" s="9" t="s">
         <v>1070</v>
       </c>
-      <c r="G364" s="7" t="s">
+      <c r="G364" s="9" t="s">
         <v>1062</v>
       </c>
       <c r="H364" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="I364" s="7">
-        <v>0</v>
+      <c r="I364" s="8">
+        <v>3</v>
       </c>
       <c r="J364" s="8">
         <v>0</v>
       </c>
       <c r="K364" s="8">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L364" s="8">
         <v>0</v>
@@ -22461,38 +22731,42 @@
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="N364" s="7">
-        <v>195</v>
-      </c>
-      <c r="O364" s="7"/>
-      <c r="P364" s="7"/>
-      <c r="Q364" s="7"/>
-      <c r="R364" s="7"/>
-      <c r="S364" s="7"/>
-      <c r="T364" s="7"/>
+      <c r="N364" s="8">
+        <v>183</v>
+      </c>
+      <c r="O364" s="8"/>
+      <c r="P364" s="9"/>
+      <c r="Q364" s="9"/>
+      <c r="R364" s="9"/>
+      <c r="S364" s="9"/>
+      <c r="T364" s="9"/>
     </row>
     <row r="365" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A365" s="7"/>
-      <c r="B365" s="7" t="s">
+      <c r="A365" s="9" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B365" s="9" t="s">
         <v>1123</v>
       </c>
-      <c r="C365" s="7" t="s">
+      <c r="C365" s="9" t="s">
         <v>1092</v>
       </c>
-      <c r="D365" s="7"/>
+      <c r="D365" s="8" t="s">
+        <v>30</v>
+      </c>
       <c r="E365" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F365" s="7" t="s">
+      <c r="F365" s="9" t="s">
         <v>1133</v>
       </c>
-      <c r="G365" s="7" t="s">
+      <c r="G365" s="9" t="s">
         <v>1133</v>
       </c>
       <c r="H365" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="I365" s="7">
+      <c r="I365" s="8">
         <v>1</v>
       </c>
       <c r="J365" s="8">
@@ -22508,45 +22782,49 @@
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="N365" s="7">
-        <v>0</v>
-      </c>
-      <c r="O365" s="7"/>
-      <c r="P365" s="7"/>
-      <c r="Q365" s="7"/>
-      <c r="R365" s="7"/>
-      <c r="S365" s="7"/>
-      <c r="T365" s="7"/>
+      <c r="N365" s="8">
+        <v>0</v>
+      </c>
+      <c r="O365" s="8"/>
+      <c r="P365" s="9"/>
+      <c r="Q365" s="9"/>
+      <c r="R365" s="9"/>
+      <c r="S365" s="9"/>
+      <c r="T365" s="9"/>
     </row>
     <row r="366" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A366" s="7"/>
-      <c r="B366" s="7" t="s">
+      <c r="A366" s="9" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B366" s="9" t="s">
         <v>1124</v>
       </c>
-      <c r="C366" s="7" t="s">
+      <c r="C366" s="9" t="s">
         <v>1093</v>
       </c>
-      <c r="D366" s="7"/>
+      <c r="D366" s="8" t="s">
+        <v>127</v>
+      </c>
       <c r="E366" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F366" s="7" t="s">
+      <c r="F366" s="9" t="s">
         <v>1068</v>
       </c>
-      <c r="G366" s="7" t="s">
+      <c r="G366" s="8" t="s">
         <v>1061</v>
       </c>
       <c r="H366" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I366" s="7">
-        <v>0</v>
+      <c r="I366" s="8">
+        <v>1</v>
       </c>
       <c r="J366" s="8">
         <v>0</v>
       </c>
       <c r="K366" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L366" s="8">
         <v>0</v>
@@ -22555,45 +22833,49 @@
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="N366" s="7">
-        <v>4</v>
-      </c>
-      <c r="O366" s="7"/>
-      <c r="P366" s="7"/>
-      <c r="Q366" s="7"/>
-      <c r="R366" s="7"/>
-      <c r="S366" s="7"/>
-      <c r="T366" s="7"/>
+      <c r="N366" s="8">
+        <v>3</v>
+      </c>
+      <c r="O366" s="8"/>
+      <c r="P366" s="9"/>
+      <c r="Q366" s="9"/>
+      <c r="R366" s="9"/>
+      <c r="S366" s="9"/>
+      <c r="T366" s="9"/>
     </row>
     <row r="367" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A367" s="7"/>
-      <c r="B367" s="7" t="s">
+      <c r="A367" s="9" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B367" s="9" t="s">
         <v>1125</v>
       </c>
-      <c r="C367" s="7" t="s">
+      <c r="C367" s="9" t="s">
         <v>1094</v>
       </c>
-      <c r="D367" s="7"/>
+      <c r="D367" s="8" t="s">
+        <v>75</v>
+      </c>
       <c r="E367" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F367" s="7" t="s">
+      <c r="F367" s="9" t="s">
         <v>1068</v>
       </c>
-      <c r="G367" s="7" t="s">
+      <c r="G367" s="8" t="s">
         <v>1061</v>
       </c>
       <c r="H367" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="I367" s="7">
-        <v>0</v>
+      <c r="I367" s="8">
+        <v>8</v>
       </c>
       <c r="J367" s="8">
         <v>0</v>
       </c>
       <c r="K367" s="8">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L367" s="8">
         <v>0</v>
@@ -22602,45 +22884,49 @@
         <f t="shared" si="5"/>
         <v>30</v>
       </c>
-      <c r="N367" s="7">
-        <v>3141</v>
-      </c>
-      <c r="O367" s="7"/>
-      <c r="P367" s="7"/>
-      <c r="Q367" s="7"/>
-      <c r="R367" s="7"/>
-      <c r="S367" s="7"/>
-      <c r="T367" s="7"/>
+      <c r="N367" s="8">
+        <v>2592</v>
+      </c>
+      <c r="O367" s="8"/>
+      <c r="P367" s="9"/>
+      <c r="Q367" s="9"/>
+      <c r="R367" s="9"/>
+      <c r="S367" s="9"/>
+      <c r="T367" s="9"/>
     </row>
     <row r="368" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A368" s="7"/>
-      <c r="B368" s="7" t="s">
+      <c r="A368" s="9" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B368" s="9" t="s">
         <v>1126</v>
       </c>
-      <c r="C368" s="7" t="s">
+      <c r="C368" s="9" t="s">
         <v>1095</v>
       </c>
-      <c r="D368" s="7"/>
+      <c r="D368" s="8" t="s">
+        <v>418</v>
+      </c>
       <c r="E368" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F368" s="7" t="s">
+      <c r="F368" s="9" t="s">
         <v>1068</v>
       </c>
-      <c r="G368" s="7" t="s">
+      <c r="G368" s="8" t="s">
         <v>1061</v>
       </c>
       <c r="H368" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="I368" s="7">
-        <v>0</v>
+      <c r="I368" s="8">
+        <v>2</v>
       </c>
       <c r="J368" s="8">
         <v>0</v>
       </c>
       <c r="K368" s="8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L368" s="8">
         <v>0</v>
@@ -22649,45 +22935,49 @@
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="N368" s="7">
-        <v>253</v>
-      </c>
-      <c r="O368" s="7"/>
-      <c r="P368" s="7"/>
-      <c r="Q368" s="7"/>
-      <c r="R368" s="7"/>
-      <c r="S368" s="7"/>
-      <c r="T368" s="7"/>
+      <c r="N368" s="8">
+        <v>263</v>
+      </c>
+      <c r="O368" s="8"/>
+      <c r="P368" s="9"/>
+      <c r="Q368" s="9"/>
+      <c r="R368" s="9"/>
+      <c r="S368" s="9"/>
+      <c r="T368" s="9"/>
     </row>
     <row r="369" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A369" s="7"/>
-      <c r="B369" s="7" t="s">
+      <c r="A369" s="9" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B369" s="9" t="s">
         <v>1127</v>
       </c>
-      <c r="C369" s="7" t="s">
+      <c r="C369" s="9" t="s">
         <v>1096</v>
       </c>
-      <c r="D369" s="7"/>
+      <c r="D369" s="8" t="s">
+        <v>194</v>
+      </c>
       <c r="E369" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F369" s="7" t="s">
+      <c r="F369" s="9" t="s">
         <v>1068</v>
       </c>
-      <c r="G369" s="7" t="s">
+      <c r="G369" s="8" t="s">
         <v>1061</v>
       </c>
       <c r="H369" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I369" s="7">
-        <v>0</v>
+      <c r="I369" s="8">
+        <v>1</v>
       </c>
       <c r="J369" s="8">
         <v>0</v>
       </c>
       <c r="K369" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L369" s="8">
         <v>0</v>
@@ -22696,45 +22986,49 @@
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="N369" s="7">
-        <v>404</v>
-      </c>
-      <c r="O369" s="7"/>
-      <c r="P369" s="7"/>
-      <c r="Q369" s="7"/>
-      <c r="R369" s="7"/>
-      <c r="S369" s="7"/>
-      <c r="T369" s="7"/>
+      <c r="N369" s="8">
+        <v>317</v>
+      </c>
+      <c r="O369" s="8"/>
+      <c r="P369" s="9"/>
+      <c r="Q369" s="9"/>
+      <c r="R369" s="9"/>
+      <c r="S369" s="9"/>
+      <c r="T369" s="9"/>
     </row>
     <row r="370" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A370" s="7"/>
-      <c r="B370" s="7" t="s">
+      <c r="A370" s="9" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B370" s="9" t="s">
         <v>1128</v>
       </c>
-      <c r="C370" s="7" t="s">
+      <c r="C370" s="9" t="s">
         <v>1097</v>
       </c>
-      <c r="D370" s="7"/>
+      <c r="D370" s="8" t="s">
+        <v>921</v>
+      </c>
       <c r="E370" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F370" s="7" t="s">
+      <c r="F370" s="9" t="s">
         <v>1068</v>
       </c>
-      <c r="G370" s="7" t="s">
+      <c r="G370" s="8" t="s">
         <v>1061</v>
       </c>
       <c r="H370" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I370" s="7">
-        <v>0</v>
+      <c r="I370" s="8">
+        <v>1</v>
       </c>
       <c r="J370" s="8">
         <v>0</v>
       </c>
       <c r="K370" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L370" s="8">
         <v>0</v>
@@ -22743,38 +23037,42 @@
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="N370" s="7">
-        <v>56</v>
-      </c>
-      <c r="O370" s="7"/>
-      <c r="P370" s="7"/>
-      <c r="Q370" s="7"/>
-      <c r="R370" s="7"/>
-      <c r="S370" s="7"/>
-      <c r="T370" s="7"/>
+      <c r="N370" s="8">
+        <v>53</v>
+      </c>
+      <c r="O370" s="8"/>
+      <c r="P370" s="9"/>
+      <c r="Q370" s="9"/>
+      <c r="R370" s="9"/>
+      <c r="S370" s="9"/>
+      <c r="T370" s="9"/>
     </row>
     <row r="371" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A371" s="7"/>
-      <c r="B371" s="7" t="s">
+      <c r="A371" s="9" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B371" s="9" t="s">
         <v>1129</v>
       </c>
-      <c r="C371" s="7" t="s">
+      <c r="C371" s="9" t="s">
         <v>1098</v>
       </c>
-      <c r="D371" s="7"/>
+      <c r="D371" s="8" t="s">
+        <v>921</v>
+      </c>
       <c r="E371" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F371" s="7" t="s">
+      <c r="F371" s="9" t="s">
         <v>1068</v>
       </c>
-      <c r="G371" s="7" t="s">
+      <c r="G371" s="8" t="s">
         <v>1061</v>
       </c>
       <c r="H371" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="I371" s="7">
+      <c r="I371" s="8">
         <v>0</v>
       </c>
       <c r="J371" s="8">
@@ -22790,45 +23088,49 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N371" s="7">
-        <v>0</v>
-      </c>
-      <c r="O371" s="7"/>
-      <c r="P371" s="7"/>
-      <c r="Q371" s="7"/>
-      <c r="R371" s="7"/>
-      <c r="S371" s="7"/>
-      <c r="T371" s="7"/>
+      <c r="N371" s="8">
+        <v>0</v>
+      </c>
+      <c r="O371" s="8"/>
+      <c r="P371" s="9"/>
+      <c r="Q371" s="9"/>
+      <c r="R371" s="9"/>
+      <c r="S371" s="9"/>
+      <c r="T371" s="9"/>
     </row>
     <row r="372" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A372" s="7"/>
-      <c r="B372" s="7" t="s">
+      <c r="A372" s="9" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B372" s="9" t="s">
         <v>1130</v>
       </c>
-      <c r="C372" s="7" t="s">
+      <c r="C372" s="9" t="s">
         <v>1099</v>
       </c>
-      <c r="D372" s="7"/>
+      <c r="D372" s="8" t="s">
+        <v>921</v>
+      </c>
       <c r="E372" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F372" s="7" t="s">
+      <c r="F372" s="9" t="s">
         <v>1068</v>
       </c>
-      <c r="G372" s="7" t="s">
+      <c r="G372" s="8" t="s">
         <v>1061</v>
       </c>
       <c r="H372" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I372" s="7">
-        <v>0</v>
+      <c r="I372" s="8">
+        <v>1</v>
       </c>
       <c r="J372" s="8">
         <v>0</v>
       </c>
       <c r="K372" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L372" s="8">
         <v>0</v>
@@ -22837,45 +23139,49 @@
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="N372" s="7">
-        <v>50</v>
-      </c>
-      <c r="O372" s="7"/>
-      <c r="P372" s="7"/>
-      <c r="Q372" s="7"/>
-      <c r="R372" s="7"/>
-      <c r="S372" s="7"/>
-      <c r="T372" s="7"/>
+      <c r="N372" s="8">
+        <v>48</v>
+      </c>
+      <c r="O372" s="8"/>
+      <c r="P372" s="9"/>
+      <c r="Q372" s="9"/>
+      <c r="R372" s="9"/>
+      <c r="S372" s="9"/>
+      <c r="T372" s="9"/>
     </row>
     <row r="373" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A373" s="7"/>
-      <c r="B373" s="7" t="s">
+      <c r="A373" s="9" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B373" s="9" t="s">
         <v>1131</v>
       </c>
-      <c r="C373" s="7" t="s">
+      <c r="C373" s="9" t="s">
         <v>1100</v>
       </c>
-      <c r="D373" s="7"/>
+      <c r="D373" s="8" t="s">
+        <v>921</v>
+      </c>
       <c r="E373" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F373" s="7" t="s">
+      <c r="F373" s="9" t="s">
         <v>1068</v>
       </c>
-      <c r="G373" s="7" t="s">
+      <c r="G373" s="8" t="s">
         <v>1061</v>
       </c>
       <c r="H373" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I373" s="7">
-        <v>0</v>
+      <c r="I373" s="8">
+        <v>1</v>
       </c>
       <c r="J373" s="8">
         <v>0</v>
       </c>
       <c r="K373" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L373" s="8">
         <v>0</v>
@@ -22884,38 +23190,42 @@
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="N373" s="7">
-        <v>108</v>
-      </c>
-      <c r="O373" s="7"/>
-      <c r="P373" s="7"/>
-      <c r="Q373" s="7"/>
-      <c r="R373" s="7"/>
-      <c r="S373" s="7"/>
-      <c r="T373" s="7"/>
+      <c r="N373" s="8">
+        <v>96</v>
+      </c>
+      <c r="O373" s="8"/>
+      <c r="P373" s="9"/>
+      <c r="Q373" s="9"/>
+      <c r="R373" s="9"/>
+      <c r="S373" s="9"/>
+      <c r="T373" s="9"/>
     </row>
     <row r="374" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A374" s="7"/>
-      <c r="B374" s="7" t="s">
+      <c r="A374" s="9" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B374" s="9" t="s">
         <v>1132</v>
       </c>
-      <c r="C374" s="7" t="s">
+      <c r="C374" s="9" t="s">
         <v>1101</v>
       </c>
-      <c r="D374" s="7"/>
+      <c r="D374" s="8" t="s">
+        <v>75</v>
+      </c>
       <c r="E374" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F374" s="7" t="s">
+      <c r="F374" s="9" t="s">
         <v>1070</v>
       </c>
-      <c r="G374" s="7" t="s">
+      <c r="G374" s="9" t="s">
         <v>1062</v>
       </c>
       <c r="H374" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="I374" s="7">
+      <c r="I374" s="8">
         <v>0</v>
       </c>
       <c r="J374" s="8">
@@ -22931,235 +23241,525 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N374" s="7">
-        <v>855</v>
-      </c>
-      <c r="O374" s="7"/>
-      <c r="P374" s="7"/>
-      <c r="Q374" s="7"/>
-      <c r="R374" s="7"/>
-      <c r="S374" s="7"/>
-      <c r="T374" s="7"/>
+      <c r="N374" s="8">
+        <v>846</v>
+      </c>
+      <c r="O374" s="8"/>
+      <c r="P374" s="9"/>
+      <c r="Q374" s="9"/>
+      <c r="R374" s="9"/>
+      <c r="S374" s="9"/>
+      <c r="T374" s="9"/>
     </row>
     <row r="375" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A375" s="7"/>
-      <c r="B375" s="7"/>
-      <c r="C375" s="7"/>
-      <c r="D375" s="7"/>
-      <c r="E375" s="7"/>
-      <c r="F375" s="7"/>
-      <c r="G375" s="7"/>
-      <c r="H375" s="7"/>
-      <c r="I375" s="7"/>
-      <c r="J375" s="7"/>
-      <c r="K375" s="7"/>
-      <c r="L375" s="7"/>
-      <c r="M375" s="7"/>
-      <c r="N375" s="7"/>
-      <c r="O375" s="7"/>
-      <c r="P375" s="7"/>
-      <c r="Q375" s="7"/>
-      <c r="R375" s="7"/>
-      <c r="S375" s="7"/>
-      <c r="T375" s="7"/>
+      <c r="A375" s="9" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B375" s="9" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C375" s="9" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D375" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E375" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F375" s="8" t="s">
+        <v>1067</v>
+      </c>
+      <c r="G375" s="8" t="s">
+        <v>1060</v>
+      </c>
+      <c r="H375" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I375" s="8">
+        <v>1</v>
+      </c>
+      <c r="J375" s="8">
+        <v>0</v>
+      </c>
+      <c r="K375" s="8">
+        <v>0</v>
+      </c>
+      <c r="L375" s="8">
+        <v>0</v>
+      </c>
+      <c r="M375" s="8">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="N375" s="8">
+        <v>0</v>
+      </c>
+      <c r="O375" s="8"/>
+      <c r="P375" s="9"/>
+      <c r="Q375" s="9"/>
+      <c r="R375" s="9"/>
+      <c r="S375" s="9"/>
+      <c r="T375" s="9"/>
     </row>
     <row r="376" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A376" s="7"/>
-      <c r="B376" s="7"/>
-      <c r="C376" s="7"/>
-      <c r="D376" s="7"/>
-      <c r="E376" s="7"/>
-      <c r="F376" s="7"/>
-      <c r="G376" s="7"/>
-      <c r="H376" s="7"/>
-      <c r="I376" s="7"/>
-      <c r="J376" s="7"/>
-      <c r="K376" s="7"/>
-      <c r="L376" s="7"/>
-      <c r="M376" s="7"/>
-      <c r="N376" s="7"/>
-      <c r="O376" s="7"/>
-      <c r="P376" s="7"/>
-      <c r="Q376" s="7"/>
-      <c r="R376" s="7"/>
-      <c r="S376" s="7"/>
-      <c r="T376" s="7"/>
+      <c r="A376" s="9" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B376" s="9" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C376" s="9" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D376" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E376" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F376" s="8" t="s">
+        <v>1067</v>
+      </c>
+      <c r="G376" s="8" t="s">
+        <v>1060</v>
+      </c>
+      <c r="H376" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I376" s="8">
+        <v>1</v>
+      </c>
+      <c r="J376" s="8">
+        <v>0</v>
+      </c>
+      <c r="K376" s="8">
+        <v>0</v>
+      </c>
+      <c r="L376" s="8">
+        <v>0</v>
+      </c>
+      <c r="M376" s="8">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="N376" s="8">
+        <v>0</v>
+      </c>
+      <c r="O376" s="8"/>
+      <c r="P376" s="9"/>
+      <c r="Q376" s="9"/>
+      <c r="R376" s="9"/>
+      <c r="S376" s="9"/>
+      <c r="T376" s="9"/>
     </row>
     <row r="377" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A377" s="7"/>
-      <c r="B377" s="7"/>
-      <c r="C377" s="7"/>
-      <c r="D377" s="7"/>
-      <c r="E377" s="7"/>
-      <c r="F377" s="7"/>
-      <c r="G377" s="7"/>
-      <c r="H377" s="7"/>
-      <c r="I377" s="7"/>
-      <c r="J377" s="7"/>
-      <c r="K377" s="7"/>
-      <c r="L377" s="7"/>
-      <c r="M377" s="7"/>
-      <c r="N377" s="7"/>
-      <c r="O377" s="7"/>
-      <c r="P377" s="7"/>
-      <c r="Q377" s="7"/>
-      <c r="R377" s="7"/>
-      <c r="S377" s="7"/>
-      <c r="T377" s="7"/>
+      <c r="A377" s="9" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B377" s="9" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C377" s="9" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D377" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E377" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F377" s="9" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G377" s="9" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H377" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I377" s="8">
+        <v>1</v>
+      </c>
+      <c r="J377" s="8">
+        <v>0</v>
+      </c>
+      <c r="K377" s="8">
+        <v>0</v>
+      </c>
+      <c r="L377" s="8">
+        <v>0</v>
+      </c>
+      <c r="M377" s="8">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="N377" s="8">
+        <v>0</v>
+      </c>
+      <c r="O377" s="8"/>
+      <c r="P377" s="9"/>
+      <c r="Q377" s="9"/>
+      <c r="R377" s="9"/>
+      <c r="S377" s="9"/>
+      <c r="T377" s="9"/>
     </row>
     <row r="378" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A378" s="7"/>
-      <c r="B378" s="7"/>
-      <c r="C378" s="7"/>
-      <c r="D378" s="7"/>
-      <c r="E378" s="7"/>
-      <c r="F378" s="7"/>
-      <c r="G378" s="7"/>
-      <c r="H378" s="7"/>
-      <c r="I378" s="7"/>
-      <c r="J378" s="7"/>
-      <c r="K378" s="7"/>
-      <c r="L378" s="7"/>
-      <c r="M378" s="7"/>
-      <c r="N378" s="7"/>
-      <c r="O378" s="7"/>
-      <c r="P378" s="7"/>
-      <c r="Q378" s="7"/>
-      <c r="R378" s="7"/>
-      <c r="S378" s="7"/>
-      <c r="T378" s="7"/>
+      <c r="A378" s="9" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B378" s="9" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C378" s="9" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D378" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E378" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F378" s="9" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G378" s="9" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H378" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I378" s="8">
+        <v>1</v>
+      </c>
+      <c r="J378" s="8">
+        <v>0</v>
+      </c>
+      <c r="K378" s="8">
+        <v>0</v>
+      </c>
+      <c r="L378" s="8">
+        <v>0</v>
+      </c>
+      <c r="M378" s="8">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="N378" s="8">
+        <v>0</v>
+      </c>
+      <c r="O378" s="8"/>
+      <c r="P378" s="9"/>
+      <c r="Q378" s="9"/>
+      <c r="R378" s="9"/>
+      <c r="S378" s="9"/>
+      <c r="T378" s="9"/>
     </row>
     <row r="379" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A379" s="7"/>
-      <c r="B379" s="7"/>
-      <c r="C379" s="7"/>
-      <c r="D379" s="7"/>
-      <c r="E379" s="7"/>
-      <c r="F379" s="7"/>
-      <c r="G379" s="7"/>
-      <c r="H379" s="7"/>
-      <c r="I379" s="7"/>
-      <c r="J379" s="7"/>
-      <c r="K379" s="7"/>
-      <c r="L379" s="7"/>
-      <c r="M379" s="7"/>
-      <c r="N379" s="7"/>
-      <c r="O379" s="7"/>
-      <c r="P379" s="7"/>
-      <c r="Q379" s="7"/>
-      <c r="R379" s="7"/>
-      <c r="S379" s="7"/>
-      <c r="T379" s="7"/>
+      <c r="A379" s="9" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B379" s="9" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C379" s="9" t="s">
+        <v>1138</v>
+      </c>
+      <c r="D379" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E379" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F379" s="9" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G379" s="9" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H379" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I379" s="8">
+        <v>1</v>
+      </c>
+      <c r="J379" s="8">
+        <v>0</v>
+      </c>
+      <c r="K379" s="8">
+        <v>0</v>
+      </c>
+      <c r="L379" s="8">
+        <v>0</v>
+      </c>
+      <c r="M379" s="8">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="N379" s="8">
+        <v>0</v>
+      </c>
+      <c r="O379" s="8"/>
+      <c r="P379" s="9"/>
+      <c r="Q379" s="9"/>
+      <c r="R379" s="9"/>
+      <c r="S379" s="9"/>
+      <c r="T379" s="9"/>
     </row>
     <row r="380" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A380" s="7"/>
-      <c r="B380" s="7"/>
-      <c r="C380" s="7"/>
-      <c r="D380" s="7"/>
-      <c r="E380" s="7"/>
-      <c r="F380" s="7"/>
-      <c r="G380" s="7"/>
-      <c r="H380" s="7"/>
-      <c r="I380" s="7"/>
-      <c r="J380" s="7"/>
-      <c r="K380" s="7"/>
-      <c r="L380" s="7"/>
-      <c r="M380" s="7"/>
-      <c r="N380" s="7"/>
-      <c r="O380" s="7"/>
-      <c r="P380" s="7"/>
-      <c r="Q380" s="7"/>
-      <c r="R380" s="7"/>
-      <c r="S380" s="7"/>
-      <c r="T380" s="7"/>
+      <c r="A380" s="9" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B380" s="9" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C380" s="9" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D380" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E380" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F380" s="9" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G380" s="8" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H380" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I380" s="8">
+        <v>1</v>
+      </c>
+      <c r="J380" s="8">
+        <v>0</v>
+      </c>
+      <c r="K380" s="8">
+        <v>0</v>
+      </c>
+      <c r="L380" s="8">
+        <v>0</v>
+      </c>
+      <c r="M380" s="8">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="N380" s="8">
+        <v>0</v>
+      </c>
+      <c r="O380" s="8"/>
+      <c r="P380" s="9"/>
+      <c r="Q380" s="9"/>
+      <c r="R380" s="9"/>
+      <c r="S380" s="9"/>
+      <c r="T380" s="9"/>
     </row>
     <row r="381" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A381" s="7"/>
-      <c r="B381" s="7"/>
-      <c r="C381" s="7"/>
-      <c r="D381" s="7"/>
-      <c r="E381" s="7"/>
-      <c r="F381" s="7"/>
-      <c r="G381" s="7"/>
-      <c r="H381" s="7"/>
-      <c r="I381" s="7"/>
-      <c r="J381" s="7"/>
-      <c r="K381" s="7"/>
-      <c r="L381" s="7"/>
-      <c r="M381" s="7"/>
-      <c r="N381" s="7"/>
-      <c r="O381" s="7"/>
-      <c r="P381" s="7"/>
-      <c r="Q381" s="7"/>
-      <c r="R381" s="7"/>
-      <c r="S381" s="7"/>
-      <c r="T381" s="7"/>
+      <c r="A381" s="9" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B381" s="9" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C381" s="9" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D381" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E381" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F381" s="9" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G381" s="8" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H381" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I381" s="8">
+        <v>1</v>
+      </c>
+      <c r="J381" s="8">
+        <v>0</v>
+      </c>
+      <c r="K381" s="8">
+        <v>0</v>
+      </c>
+      <c r="L381" s="8">
+        <v>0</v>
+      </c>
+      <c r="M381" s="8">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="N381" s="8">
+        <v>0</v>
+      </c>
+      <c r="O381" s="8"/>
+      <c r="P381" s="9"/>
+      <c r="Q381" s="9"/>
+      <c r="R381" s="9"/>
+      <c r="S381" s="9"/>
+      <c r="T381" s="9"/>
     </row>
     <row r="382" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A382" s="7"/>
-      <c r="B382" s="7"/>
-      <c r="C382" s="7"/>
-      <c r="D382" s="7"/>
-      <c r="E382" s="7"/>
-      <c r="F382" s="7"/>
-      <c r="G382" s="7"/>
-      <c r="H382" s="7"/>
-      <c r="I382" s="7"/>
-      <c r="J382" s="7"/>
-      <c r="K382" s="7"/>
-      <c r="L382" s="7"/>
-      <c r="M382" s="7"/>
-      <c r="N382" s="7"/>
-      <c r="O382" s="7"/>
-      <c r="P382" s="7"/>
-      <c r="Q382" s="7"/>
-      <c r="R382" s="7"/>
-      <c r="S382" s="7"/>
-      <c r="T382" s="7"/>
+      <c r="A382" s="9" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B382" s="9" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C382" s="9" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D382" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E382" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F382" s="9" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G382" s="8" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H382" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I382" s="8">
+        <v>1</v>
+      </c>
+      <c r="J382" s="8">
+        <v>0</v>
+      </c>
+      <c r="K382" s="8">
+        <v>0</v>
+      </c>
+      <c r="L382" s="8">
+        <v>0</v>
+      </c>
+      <c r="M382" s="8">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="N382" s="8">
+        <v>0</v>
+      </c>
+      <c r="O382" s="8"/>
+      <c r="P382" s="9"/>
+      <c r="Q382" s="9"/>
+      <c r="R382" s="9"/>
+      <c r="S382" s="9"/>
+      <c r="T382" s="9"/>
     </row>
     <row r="383" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A383" s="7"/>
-      <c r="B383" s="7"/>
-      <c r="C383" s="7"/>
-      <c r="D383" s="7"/>
-      <c r="E383" s="7"/>
-      <c r="F383" s="7"/>
-      <c r="G383" s="7"/>
-      <c r="H383" s="7"/>
-      <c r="I383" s="7"/>
-      <c r="J383" s="7"/>
-      <c r="K383" s="7"/>
-      <c r="L383" s="7"/>
-      <c r="M383" s="7"/>
-      <c r="N383" s="7"/>
-      <c r="O383" s="7"/>
-      <c r="P383" s="7"/>
-      <c r="Q383" s="7"/>
-      <c r="R383" s="7"/>
-      <c r="S383" s="7"/>
-      <c r="T383" s="7"/>
+      <c r="A383" s="9" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B383" s="9" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C383" s="9" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D383" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E383" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F383" s="9" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G383" s="9" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H383" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I383" s="8">
+        <v>1</v>
+      </c>
+      <c r="J383" s="8">
+        <v>0</v>
+      </c>
+      <c r="K383" s="8">
+        <v>0</v>
+      </c>
+      <c r="L383" s="8">
+        <v>0</v>
+      </c>
+      <c r="M383" s="8">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="N383" s="8">
+        <v>0</v>
+      </c>
+      <c r="O383" s="8"/>
+      <c r="P383" s="9"/>
+      <c r="Q383" s="9"/>
+      <c r="R383" s="9"/>
+      <c r="S383" s="9"/>
+      <c r="T383" s="9"/>
     </row>
     <row r="384" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A384" s="7"/>
-      <c r="B384" s="7"/>
-      <c r="C384" s="7"/>
-      <c r="D384" s="7"/>
-      <c r="E384" s="7"/>
-      <c r="F384" s="7"/>
-      <c r="G384" s="7"/>
-      <c r="H384" s="7"/>
-      <c r="I384" s="7"/>
-      <c r="J384" s="7"/>
-      <c r="K384" s="7"/>
-      <c r="L384" s="7"/>
-      <c r="M384" s="7"/>
-      <c r="N384" s="7"/>
-      <c r="O384" s="7"/>
-      <c r="P384" s="7"/>
-      <c r="Q384" s="7"/>
-      <c r="R384" s="7"/>
-      <c r="S384" s="7"/>
-      <c r="T384" s="7"/>
+      <c r="A384" s="9" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B384" s="9" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C384" s="9" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D384" s="8" t="s">
+        <v>418</v>
+      </c>
+      <c r="E384" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F384" s="9" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G384" s="8" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H384" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I384" s="8">
+        <v>0</v>
+      </c>
+      <c r="J384" s="8">
+        <v>0</v>
+      </c>
+      <c r="K384" s="8">
+        <v>0</v>
+      </c>
+      <c r="L384" s="8">
+        <v>0</v>
+      </c>
+      <c r="M384" s="8">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N384" s="8">
+        <v>262</v>
+      </c>
+      <c r="O384" s="8"/>
+      <c r="P384" s="9"/>
+      <c r="Q384" s="9"/>
+      <c r="R384" s="9"/>
+      <c r="S384" s="9"/>
+      <c r="T384" s="9"/>
     </row>
     <row r="385" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A385" s="7"/>
@@ -31566,15 +32166,16 @@
       <c r="T766" s="7"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:T384" xr:uid="{AF55B7BF-85DC-4082-9A73-200B4D79A598}"/>
+  <conditionalFormatting sqref="C1">
+    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="10"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
+++ b/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
@@ -32167,15 +32167,15 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:T384" xr:uid="{AF55B7BF-85DC-4082-9A73-200B4D79A598}"/>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="duplicateValues" dxfId="5" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="14"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="1" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
+++ b/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
@@ -19,6 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$T$384</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>

--- a/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
+++ b/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\Fossil Replenishment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C096FD1-0220-4A86-91CF-B20161D5B2C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686BF969-B84B-4BAE-9370-EE22639DAD16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6662473D-6E1F-42FD-999B-28162E22D4B5}"/>
   </bookViews>
@@ -37870,7 +37870,7 @@
         <v>433</v>
       </c>
       <c r="N5" s="8">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="O5" s="8"/>
       <c r="P5" s="8"/>
@@ -37974,7 +37974,7 @@
         <v>126</v>
       </c>
       <c r="N7" s="8">
-        <v>286</v>
+        <v>262</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
@@ -38026,7 +38026,7 @@
         <v>144</v>
       </c>
       <c r="N8" s="8">
-        <v>1021</v>
+        <v>981</v>
       </c>
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
@@ -38182,7 +38182,7 @@
         <v>62</v>
       </c>
       <c r="N11" s="8">
-        <v>439</v>
+        <v>403</v>
       </c>
       <c r="O11" s="8"/>
       <c r="P11" s="8"/>
@@ -38234,7 +38234,7 @@
         <v>43</v>
       </c>
       <c r="N12" s="8">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="O12" s="8"/>
       <c r="P12" s="8"/>
@@ -38546,7 +38546,7 @@
         <v>44</v>
       </c>
       <c r="N18" s="8">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="O18" s="8"/>
       <c r="P18" s="8"/>
@@ -38650,7 +38650,7 @@
         <v>24</v>
       </c>
       <c r="N20" s="8">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="O20" s="8"/>
       <c r="P20" s="8"/>
@@ -38961,7 +38961,7 @@
         <v>21</v>
       </c>
       <c r="N26" s="8">
-        <v>1779</v>
+        <v>1777</v>
       </c>
       <c r="O26" s="8"/>
       <c r="P26" s="8"/>
@@ -39169,7 +39169,7 @@
         <v>21</v>
       </c>
       <c r="N30" s="8">
-        <v>1356</v>
+        <v>1352</v>
       </c>
       <c r="O30" s="8"/>
       <c r="P30" s="8"/>
@@ -39377,7 +39377,7 @@
         <v>16</v>
       </c>
       <c r="N34" s="8">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="O34" s="8"/>
       <c r="P34" s="8"/>
@@ -39637,7 +39637,7 @@
         <v>29</v>
       </c>
       <c r="N39" s="8">
-        <v>2299</v>
+        <v>2296</v>
       </c>
       <c r="O39" s="8"/>
       <c r="P39" s="8"/>
@@ -39793,7 +39793,7 @@
         <v>17</v>
       </c>
       <c r="N42" s="8">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="O42" s="8"/>
       <c r="P42" s="8"/>
@@ -39845,7 +39845,7 @@
         <v>17</v>
       </c>
       <c r="N43" s="8">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O43" s="8"/>
       <c r="P43" s="8"/>
@@ -40261,7 +40261,7 @@
         <v>16</v>
       </c>
       <c r="N51" s="8">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="O51" s="8"/>
       <c r="P51" s="8"/>
@@ -40313,7 +40313,7 @@
         <v>61</v>
       </c>
       <c r="N52" s="8">
-        <v>2290</v>
+        <v>2280</v>
       </c>
       <c r="O52" s="8"/>
       <c r="P52" s="8"/>
@@ -40417,7 +40417,7 @@
         <v>14</v>
       </c>
       <c r="N54" s="8">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="O54" s="8"/>
       <c r="P54" s="8"/>
@@ -40469,7 +40469,7 @@
         <v>47</v>
       </c>
       <c r="N55" s="8">
-        <v>703</v>
+        <v>695</v>
       </c>
       <c r="O55" s="8"/>
       <c r="P55" s="8"/>
@@ -40573,7 +40573,7 @@
         <v>19</v>
       </c>
       <c r="N57" s="8">
-        <v>811</v>
+        <v>803</v>
       </c>
       <c r="O57" s="8"/>
       <c r="P57" s="8"/>
@@ -40781,7 +40781,7 @@
         <v>16</v>
       </c>
       <c r="N61" s="8">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="O61" s="8"/>
       <c r="P61" s="8"/>
@@ -40885,7 +40885,7 @@
         <v>5</v>
       </c>
       <c r="N63" s="8">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O63" s="8"/>
       <c r="P63" s="8"/>
@@ -41301,7 +41301,7 @@
         <v>11</v>
       </c>
       <c r="N71" s="8">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="O71" s="8"/>
       <c r="P71" s="8"/>
@@ -41405,7 +41405,7 @@
         <v>14</v>
       </c>
       <c r="N73" s="8">
-        <v>1138</v>
+        <v>1133</v>
       </c>
       <c r="O73" s="8"/>
       <c r="P73" s="8"/>
@@ -41457,7 +41457,7 @@
         <v>6</v>
       </c>
       <c r="N74" s="8">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="O74" s="8"/>
       <c r="P74" s="8"/>
@@ -41665,7 +41665,7 @@
         <v>14</v>
       </c>
       <c r="N78" s="8">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="O78" s="8"/>
       <c r="P78" s="8"/>
@@ -42393,7 +42393,7 @@
         <v>8</v>
       </c>
       <c r="N92" s="8">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="O92" s="8"/>
       <c r="P92" s="8"/>
@@ -42601,7 +42601,7 @@
         <v>7</v>
       </c>
       <c r="N96" s="8">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O96" s="8"/>
       <c r="P96" s="8"/>
@@ -42912,7 +42912,7 @@
         <v>6</v>
       </c>
       <c r="N102" s="8">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="O102" s="8"/>
       <c r="P102" s="8"/>
@@ -42964,7 +42964,7 @@
         <v>4</v>
       </c>
       <c r="N103" s="8">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="O103" s="8"/>
       <c r="P103" s="8"/>
@@ -43275,7 +43275,7 @@
         <v>4</v>
       </c>
       <c r="N109" s="8">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="O109" s="8"/>
       <c r="P109" s="8"/>
@@ -43431,7 +43431,7 @@
         <v>19</v>
       </c>
       <c r="N112" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O112" s="8"/>
       <c r="P112" s="8"/>
@@ -43483,7 +43483,7 @@
         <v>16</v>
       </c>
       <c r="N113" s="8">
-        <v>1016</v>
+        <v>1010</v>
       </c>
       <c r="O113" s="8"/>
       <c r="P113" s="8"/>
@@ -43535,7 +43535,7 @@
         <v>10</v>
       </c>
       <c r="N114" s="8">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="O114" s="8"/>
       <c r="P114" s="8"/>
@@ -43587,7 +43587,7 @@
         <v>12</v>
       </c>
       <c r="N115" s="8">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="O115" s="8"/>
       <c r="P115" s="8"/>
@@ -43743,7 +43743,7 @@
         <v>10</v>
       </c>
       <c r="N118" s="8">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="O118" s="8"/>
       <c r="P118" s="8"/>
@@ -44367,7 +44367,7 @@
         <v>11</v>
       </c>
       <c r="N130" s="8">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="O130" s="8"/>
       <c r="P130" s="8"/>
@@ -44471,7 +44471,7 @@
         <v>5</v>
       </c>
       <c r="N132" s="8">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="O132" s="8"/>
       <c r="P132" s="8"/>
@@ -46186,7 +46186,7 @@
         <v>2</v>
       </c>
       <c r="N165" s="8">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="O165" s="8"/>
       <c r="P165" s="8"/>
@@ -46913,7 +46913,7 @@
         <v>4</v>
       </c>
       <c r="N179" s="8">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O179" s="8"/>
       <c r="P179" s="8"/>
@@ -46965,7 +46965,7 @@
         <v>10</v>
       </c>
       <c r="N180" s="8">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="O180" s="8"/>
       <c r="P180" s="8"/>
@@ -47277,7 +47277,7 @@
         <v>10</v>
       </c>
       <c r="N186" s="8">
-        <v>1087</v>
+        <v>1084</v>
       </c>
       <c r="O186" s="8"/>
       <c r="P186" s="8"/>
@@ -47484,7 +47484,7 @@
         <v>8</v>
       </c>
       <c r="N190" s="8">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="O190" s="8"/>
       <c r="P190" s="8"/>
@@ -47536,7 +47536,7 @@
         <v>8</v>
       </c>
       <c r="N191" s="8">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="O191" s="8"/>
       <c r="P191" s="8"/>
@@ -49459,7 +49459,7 @@
         <v>4</v>
       </c>
       <c r="N228" s="8">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="O228" s="8"/>
       <c r="P228" s="8"/>
@@ -49823,7 +49823,7 @@
         <v>3</v>
       </c>
       <c r="N235" s="8">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O235" s="8"/>
       <c r="P235" s="8"/>
@@ -50187,7 +50187,7 @@
         <v>3</v>
       </c>
       <c r="N242" s="8">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="O242" s="8"/>
       <c r="P242" s="8"/>
@@ -51174,7 +51174,7 @@
         <v>11</v>
       </c>
       <c r="N261" s="8">
-        <v>1458</v>
+        <v>1453</v>
       </c>
       <c r="O261" s="8"/>
       <c r="P261" s="8"/>
@@ -51226,7 +51226,7 @@
         <v>10</v>
       </c>
       <c r="N262" s="8">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="O262" s="8"/>
       <c r="P262" s="8"/>
@@ -51278,7 +51278,7 @@
         <v>23</v>
       </c>
       <c r="N263" s="8">
-        <v>697</v>
+        <v>682</v>
       </c>
       <c r="O263" s="8"/>
       <c r="P263" s="8"/>
@@ -52058,7 +52058,7 @@
         <v>9</v>
       </c>
       <c r="N278" s="8">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="O278" s="8"/>
       <c r="P278" s="8"/>
@@ -52318,7 +52318,7 @@
         <v>3</v>
       </c>
       <c r="N283" s="8">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="O283" s="8"/>
       <c r="P283" s="8"/>
@@ -52370,7 +52370,7 @@
         <v>19</v>
       </c>
       <c r="N284" s="8">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="O284" s="8"/>
       <c r="P284" s="8"/>
@@ -52526,7 +52526,7 @@
         <v>8</v>
       </c>
       <c r="N287" s="8">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="O287" s="8"/>
       <c r="P287" s="8"/>
@@ -52734,7 +52734,7 @@
         <v>18</v>
       </c>
       <c r="N291" s="8">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="O291" s="8"/>
       <c r="P291" s="8"/>
@@ -52890,7 +52890,7 @@
         <v>15</v>
       </c>
       <c r="N294" s="8">
-        <v>1442</v>
+        <v>1439</v>
       </c>
       <c r="O294" s="8"/>
       <c r="P294" s="8"/>
@@ -53200,7 +53200,7 @@
         <v>4</v>
       </c>
       <c r="N300" s="8">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="O300" s="8"/>
       <c r="P300" s="8"/>
@@ -54032,7 +54032,7 @@
         <v>4</v>
       </c>
       <c r="N316" s="8">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="O316" s="8"/>
       <c r="P316" s="8"/>
@@ -54914,7 +54914,7 @@
         <v>3</v>
       </c>
       <c r="N333" s="8">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="O333" s="8"/>
       <c r="P333" s="8"/>
@@ -55278,7 +55278,7 @@
         <v>3</v>
       </c>
       <c r="N340" s="8">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="O340" s="8"/>
       <c r="P340" s="8"/>
@@ -55642,7 +55642,7 @@
         <v>5</v>
       </c>
       <c r="N347" s="8">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="O347" s="8"/>
       <c r="P347" s="9"/>
@@ -56055,7 +56055,7 @@
         <v>3</v>
       </c>
       <c r="N355" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O355" s="8"/>
       <c r="P355" s="9"/>
@@ -56518,7 +56518,7 @@
         <v>11</v>
       </c>
       <c r="N364" s="8">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="O364" s="8"/>
       <c r="P364" s="9"/>
@@ -57037,7 +57037,7 @@
         <v>5</v>
       </c>
       <c r="N374" s="8">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="O374" s="8"/>
       <c r="P374" s="9"/>
@@ -57557,7 +57557,7 @@
         <v>5</v>
       </c>
       <c r="N384" s="8">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="O384" s="8"/>
       <c r="P384" s="9"/>
@@ -57613,7 +57613,7 @@
       <c r="N385" s="8">
         <v>466</v>
       </c>
-      <c r="O385" s="7"/>
+      <c r="O385" s="8"/>
       <c r="P385" s="7"/>
       <c r="Q385" s="7"/>
       <c r="R385" s="7"/>
@@ -57667,7 +57667,7 @@
       <c r="N386" s="8">
         <v>1</v>
       </c>
-      <c r="O386" s="7"/>
+      <c r="O386" s="8"/>
       <c r="P386" s="7"/>
       <c r="Q386" s="7"/>
       <c r="R386" s="7"/>
@@ -57721,7 +57721,7 @@
       <c r="N387" s="8">
         <v>1</v>
       </c>
-      <c r="O387" s="7"/>
+      <c r="O387" s="8"/>
       <c r="P387" s="7"/>
       <c r="Q387" s="7"/>
       <c r="R387" s="7"/>
@@ -57775,7 +57775,7 @@
       <c r="N388" s="8">
         <v>1</v>
       </c>
-      <c r="O388" s="7"/>
+      <c r="O388" s="8"/>
       <c r="P388" s="7"/>
       <c r="Q388" s="7"/>
       <c r="R388" s="7"/>
@@ -57829,7 +57829,7 @@
       <c r="N389" s="8">
         <v>1</v>
       </c>
-      <c r="O389" s="7"/>
+      <c r="O389" s="8"/>
       <c r="P389" s="7"/>
       <c r="Q389" s="7"/>
       <c r="R389" s="7"/>
@@ -66131,6 +66131,7 @@
       <c r="T766" s="7"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:T389" xr:uid="{AF55B7BF-85DC-4082-9A73-200B4D79A598}"/>
   <conditionalFormatting sqref="A1:B1">
     <cfRule type="duplicateValues" dxfId="5" priority="13"/>
     <cfRule type="duplicateValues" dxfId="4" priority="14"/>

--- a/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
+++ b/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
@@ -8,18 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\Fossil Replenishment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBCBBB4B-0E8C-4621-92C8-A16BF404DDF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3302EB5-14A2-4A41-A106-F49943D5FEA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6662473D-6E1F-42FD-999B-28162E22D4B5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$T$401</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$T$402</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3220" uniqueCount="1246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3228" uniqueCount="1249">
   <si>
     <t>In Transit PO</t>
   </si>
@@ -3778,6 +3775,15 @@
   </si>
   <si>
     <t>FBA79726</t>
+  </si>
+  <si>
+    <t>MK7529</t>
+  </si>
+  <si>
+    <t>B0DT37Y5FY</t>
+  </si>
+  <si>
+    <t>FBA79902</t>
   </si>
 </sst>
 </file>
@@ -3909,7 +3915,37 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3981,2855 +4017,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="SOH"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="1">
-          <cell r="A1" t="str">
-            <v>Base Style</v>
-          </cell>
-          <cell r="F1" t="str">
-            <v>Fossil SOH</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="A2" t="str">
-            <v>FS5237</v>
-          </cell>
-          <cell r="F2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3" t="str">
-            <v>FS4867</v>
-          </cell>
-          <cell r="F3">
-            <v>1911</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4" t="str">
-            <v>FS5661</v>
-          </cell>
-          <cell r="F4">
-            <v>353</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5" t="str">
-            <v>CH2882</v>
-          </cell>
-          <cell r="F5">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6" t="str">
-            <v>CH2885</v>
-          </cell>
-          <cell r="F6">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7" t="str">
-            <v>BQ3181</v>
-          </cell>
-          <cell r="F7">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8" t="str">
-            <v>FS4795</v>
-          </cell>
-          <cell r="F8">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9" t="str">
-            <v>AX1343</v>
-          </cell>
-          <cell r="F9">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10" t="str">
-            <v>FS5164</v>
-          </cell>
-          <cell r="F10">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11" t="str">
-            <v>JR1401</v>
-          </cell>
-          <cell r="F11">
-            <v>2414</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12" t="str">
-            <v>ES2811</v>
-          </cell>
-          <cell r="F12">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13" t="str">
-            <v>ES4433</v>
-          </cell>
-          <cell r="F13">
-            <v>900</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14" t="str">
-            <v>FS4735</v>
-          </cell>
-          <cell r="F14">
-            <v>667</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15" t="str">
-            <v>FS4813</v>
-          </cell>
-          <cell r="F15">
-            <v>638</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16" t="str">
-            <v>AX1746</v>
-          </cell>
-          <cell r="F16">
-            <v>218</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17" t="str">
-            <v>FS5665</v>
-          </cell>
-          <cell r="F17">
-            <v>92</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="A18" t="str">
-            <v>ES3843</v>
-          </cell>
-          <cell r="F18">
-            <v>526</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="A19" t="str">
-            <v>FS6106</v>
-          </cell>
-          <cell r="F19">
-            <v>774</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="A20" t="str">
-            <v>JR1487</v>
-          </cell>
-          <cell r="F20">
-            <v>1043</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="A21" t="str">
-            <v>ES4628</v>
-          </cell>
-          <cell r="F21">
-            <v>1416</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="A22" t="str">
-            <v>FS5792</v>
-          </cell>
-          <cell r="F22">
-            <v>764</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="A23" t="str">
-            <v>FS5308</v>
-          </cell>
-          <cell r="F23">
-            <v>513</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="A24" t="str">
-            <v>BQ3502</v>
-          </cell>
-          <cell r="F24">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="A25" t="str">
-            <v>ES3020</v>
-          </cell>
-          <cell r="F25">
-            <v>535</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="A26" t="str">
-            <v>AX4182</v>
-          </cell>
-          <cell r="F26">
-            <v>892</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="A27" t="str">
-            <v>MK6485</v>
-          </cell>
-          <cell r="F27">
-            <v>241</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="A28" t="str">
-            <v>AX4184</v>
-          </cell>
-          <cell r="F28">
-            <v>187</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="A29" t="str">
-            <v>FS4812</v>
-          </cell>
-          <cell r="F29">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="A30" t="str">
-            <v>FS6111</v>
-          </cell>
-          <cell r="F30">
-            <v>449</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="A31" t="str">
-            <v>MK4842</v>
-          </cell>
-          <cell r="F31">
-            <v>242</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="A32" t="str">
-            <v>AX2429</v>
-          </cell>
-          <cell r="F32">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="A33" t="str">
-            <v>FS5525</v>
-          </cell>
-          <cell r="F33">
-            <v>1283</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="A34" t="str">
-            <v>FS5963</v>
-          </cell>
-          <cell r="F34">
-            <v>953</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="A35" t="str">
-            <v>ES4519</v>
-          </cell>
-          <cell r="F35">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="A36" t="str">
-            <v>AX2463</v>
-          </cell>
-          <cell r="F36">
-            <v>726</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="A37" t="str">
-            <v>MK5491</v>
-          </cell>
-          <cell r="F37">
-            <v>1223</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="A38" t="str">
-            <v>AX5176</v>
-          </cell>
-          <cell r="F38">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="A39" t="str">
-            <v>FS5512</v>
-          </cell>
-          <cell r="F39">
-            <v>863</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="A40" t="str">
-            <v>ES5364</v>
-          </cell>
-          <cell r="F40">
-            <v>474</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="A41" t="str">
-            <v>FS6113</v>
-          </cell>
-          <cell r="F41">
-            <v>1110</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="A42" t="str">
-            <v>FS6029</v>
-          </cell>
-          <cell r="F42">
-            <v>226</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="A43" t="str">
-            <v>AX1769</v>
-          </cell>
-          <cell r="F43">
-            <v>313</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="A44" t="str">
-            <v>AX4180</v>
-          </cell>
-          <cell r="F44">
-            <v>269</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="A45" t="str">
-            <v>ES5358</v>
-          </cell>
-          <cell r="F45">
-            <v>105</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="A46" t="str">
-            <v>ME3098</v>
-          </cell>
-          <cell r="F46">
-            <v>2080</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="A47" t="str">
-            <v>ES5310</v>
-          </cell>
-          <cell r="F47">
-            <v>50</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="A48" t="str">
-            <v>FS6048</v>
-          </cell>
-          <cell r="F48">
-            <v>286</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="A49" t="str">
-            <v>AX4183</v>
-          </cell>
-          <cell r="F49">
-            <v>921</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="A50" t="str">
-            <v>ES5349</v>
-          </cell>
-          <cell r="F50">
-            <v>174</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="A51" t="str">
-            <v>FS6090</v>
-          </cell>
-          <cell r="F51">
-            <v>577</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="A52" t="str">
-            <v>ME3254</v>
-          </cell>
-          <cell r="F52">
-            <v>934</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="A53" t="str">
-            <v>ME3260</v>
-          </cell>
-          <cell r="F53">
-            <v>206</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="A54" t="str">
-            <v>AX5901</v>
-          </cell>
-          <cell r="F54">
-            <v>149</v>
-          </cell>
-        </row>
-        <row r="55">
-          <cell r="A55" t="str">
-            <v>ES3284</v>
-          </cell>
-          <cell r="F55">
-            <v>1210</v>
-          </cell>
-        </row>
-        <row r="56">
-          <cell r="A56" t="str">
-            <v>FS6112</v>
-          </cell>
-          <cell r="F56">
-            <v>828</v>
-          </cell>
-        </row>
-        <row r="57">
-          <cell r="A57" t="str">
-            <v>AR1979</v>
-          </cell>
-          <cell r="F57">
-            <v>159</v>
-          </cell>
-        </row>
-        <row r="58">
-          <cell r="A58" t="str">
-            <v>ES5329</v>
-          </cell>
-          <cell r="F58">
-            <v>503</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="A59" t="str">
-            <v>ES5361</v>
-          </cell>
-          <cell r="F59">
-            <v>1463</v>
-          </cell>
-        </row>
-        <row r="60">
-          <cell r="A60" t="str">
-            <v>ES5323</v>
-          </cell>
-          <cell r="F60">
-            <v>207</v>
-          </cell>
-        </row>
-        <row r="61">
-          <cell r="A61" t="str">
-            <v>ME3253</v>
-          </cell>
-          <cell r="F61">
-            <v>663</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="A62" t="str">
-            <v>ES5452</v>
-          </cell>
-          <cell r="F62">
-            <v>427</v>
-          </cell>
-        </row>
-        <row r="63">
-          <cell r="A63" t="str">
-            <v>MK9113</v>
-          </cell>
-          <cell r="F63">
-            <v>304</v>
-          </cell>
-        </row>
-        <row r="64">
-          <cell r="A64" t="str">
-            <v>FS6086</v>
-          </cell>
-          <cell r="F64">
-            <v>695</v>
-          </cell>
-        </row>
-        <row r="65">
-          <cell r="A65" t="str">
-            <v>ES5434</v>
-          </cell>
-          <cell r="F65">
-            <v>685</v>
-          </cell>
-        </row>
-        <row r="66">
-          <cell r="A66" t="str">
-            <v>AX1970</v>
-          </cell>
-          <cell r="F66">
-            <v>69</v>
-          </cell>
-        </row>
-        <row r="67">
-          <cell r="A67" t="str">
-            <v>FS6140</v>
-          </cell>
-          <cell r="F67">
-            <v>797</v>
-          </cell>
-        </row>
-        <row r="68">
-          <cell r="A68" t="str">
-            <v>ES5363</v>
-          </cell>
-          <cell r="F68">
-            <v>954</v>
-          </cell>
-        </row>
-        <row r="69">
-          <cell r="A69" t="str">
-            <v>FS6032</v>
-          </cell>
-          <cell r="F69">
-            <v>419</v>
-          </cell>
-        </row>
-        <row r="70">
-          <cell r="A70" t="str">
-            <v>ES5303</v>
-          </cell>
-          <cell r="F70">
-            <v>290</v>
-          </cell>
-        </row>
-        <row r="71">
-          <cell r="A71" t="str">
-            <v>AX4186</v>
-          </cell>
-          <cell r="F71">
-            <v>78</v>
-          </cell>
-        </row>
-        <row r="72">
-          <cell r="A72" t="str">
-            <v>ES5419</v>
-          </cell>
-          <cell r="F72">
-            <v>888</v>
-          </cell>
-        </row>
-        <row r="73">
-          <cell r="A73" t="str">
-            <v>MK7506</v>
-          </cell>
-          <cell r="F73">
-            <v>276</v>
-          </cell>
-        </row>
-        <row r="74">
-          <cell r="A74" t="str">
-            <v>ES5420</v>
-          </cell>
-          <cell r="F74">
-            <v>437</v>
-          </cell>
-        </row>
-        <row r="75">
-          <cell r="A75" t="str">
-            <v>AX2761</v>
-          </cell>
-          <cell r="F75">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="76">
-          <cell r="A76" t="str">
-            <v>FS6139</v>
-          </cell>
-          <cell r="F76">
-            <v>1019</v>
-          </cell>
-        </row>
-        <row r="77">
-          <cell r="A77" t="str">
-            <v>ES5319</v>
-          </cell>
-          <cell r="F77">
-            <v>286</v>
-          </cell>
-        </row>
-        <row r="78">
-          <cell r="A78" t="str">
-            <v>DZ1206</v>
-          </cell>
-          <cell r="F78">
-            <v>605</v>
-          </cell>
-        </row>
-        <row r="79">
-          <cell r="A79" t="str">
-            <v>FS5901</v>
-          </cell>
-          <cell r="F79">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="80">
-          <cell r="A80" t="str">
-            <v>ES5338</v>
-          </cell>
-          <cell r="F80">
-            <v>306</v>
-          </cell>
-        </row>
-        <row r="81">
-          <cell r="A81" t="str">
-            <v>FS6087</v>
-          </cell>
-          <cell r="F81">
-            <v>998</v>
-          </cell>
-        </row>
-        <row r="82">
-          <cell r="A82" t="str">
-            <v>MK9177</v>
-          </cell>
-          <cell r="F82">
-            <v>354</v>
-          </cell>
-        </row>
-        <row r="83">
-          <cell r="A83" t="str">
-            <v>MK3197</v>
-          </cell>
-          <cell r="F83">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="84">
-          <cell r="A84" t="str">
-            <v>AR11669</v>
-          </cell>
-          <cell r="F84">
-            <v>39</v>
-          </cell>
-        </row>
-        <row r="85">
-          <cell r="A85" t="str">
-            <v>AX2823</v>
-          </cell>
-          <cell r="F85">
-            <v>983</v>
-          </cell>
-        </row>
-        <row r="86">
-          <cell r="A86" t="str">
-            <v>FS6128</v>
-          </cell>
-          <cell r="F86">
-            <v>690</v>
-          </cell>
-        </row>
-        <row r="87">
-          <cell r="A87" t="str">
-            <v>FS6132</v>
-          </cell>
-          <cell r="F87">
-            <v>751</v>
-          </cell>
-        </row>
-        <row r="88">
-          <cell r="A88" t="str">
-            <v>AX5911</v>
-          </cell>
-          <cell r="F88">
-            <v>15</v>
-          </cell>
-        </row>
-        <row r="89">
-          <cell r="A89" t="str">
-            <v>AX7175SET</v>
-          </cell>
-          <cell r="F89">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="90">
-          <cell r="A90" t="str">
-            <v>AR11500</v>
-          </cell>
-          <cell r="F90">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="91">
-          <cell r="A91" t="str">
-            <v>AR11575</v>
-          </cell>
-          <cell r="F91">
-            <v>381</v>
-          </cell>
-        </row>
-        <row r="92">
-          <cell r="A92" t="str">
-            <v>AR11620</v>
-          </cell>
-          <cell r="F92">
-            <v>174</v>
-          </cell>
-        </row>
-        <row r="93">
-          <cell r="A93" t="str">
-            <v>AX2461</v>
-          </cell>
-          <cell r="F93">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="94">
-          <cell r="A94" t="str">
-            <v>MK9193</v>
-          </cell>
-          <cell r="F94">
-            <v>594</v>
-          </cell>
-        </row>
-        <row r="95">
-          <cell r="A95" t="str">
-            <v>ME3218</v>
-          </cell>
-          <cell r="F95">
-            <v>726</v>
-          </cell>
-        </row>
-        <row r="96">
-          <cell r="A96" t="str">
-            <v>AR11666</v>
-          </cell>
-          <cell r="F96">
-            <v>14</v>
-          </cell>
-        </row>
-        <row r="97">
-          <cell r="A97" t="str">
-            <v>ES5271</v>
-          </cell>
-          <cell r="F97">
-            <v>265</v>
-          </cell>
-        </row>
-        <row r="98">
-          <cell r="A98" t="str">
-            <v>FS6094</v>
-          </cell>
-          <cell r="F98">
-            <v>261</v>
-          </cell>
-        </row>
-        <row r="99">
-          <cell r="A99" t="str">
-            <v>FS6081SET</v>
-          </cell>
-          <cell r="F99">
-            <v>83</v>
-          </cell>
-        </row>
-        <row r="100">
-          <cell r="A100" t="str">
-            <v>ES5421</v>
-          </cell>
-          <cell r="F100">
-            <v>1319</v>
-          </cell>
-        </row>
-        <row r="101">
-          <cell r="A101" t="str">
-            <v>FS6129</v>
-          </cell>
-          <cell r="F101">
-            <v>303</v>
-          </cell>
-        </row>
-        <row r="102">
-          <cell r="A102" t="str">
-            <v>AX4621</v>
-          </cell>
-          <cell r="F102">
-            <v>140</v>
-          </cell>
-        </row>
-        <row r="103">
-          <cell r="A103" t="str">
-            <v>FS6144</v>
-          </cell>
-          <cell r="F103">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="104">
-          <cell r="A104" t="str">
-            <v>ES5387SET</v>
-          </cell>
-          <cell r="F104">
-            <v>138</v>
-          </cell>
-        </row>
-        <row r="105">
-          <cell r="A105" t="str">
-            <v>AX7151SET</v>
-          </cell>
-          <cell r="F105">
-            <v>130</v>
-          </cell>
-        </row>
-        <row r="106">
-          <cell r="A106" t="str">
-            <v>MK3190</v>
-          </cell>
-          <cell r="F106">
-            <v>140</v>
-          </cell>
-        </row>
-        <row r="107">
-          <cell r="A107" t="str">
-            <v>FS6056</v>
-          </cell>
-          <cell r="F107">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="108">
-          <cell r="A108" t="str">
-            <v>MK9185</v>
-          </cell>
-          <cell r="F108">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="109">
-          <cell r="A109" t="str">
-            <v>AR11665</v>
-          </cell>
-          <cell r="F109">
-            <v>10</v>
-          </cell>
-        </row>
-        <row r="110">
-          <cell r="A110" t="str">
-            <v>AR11637</v>
-          </cell>
-          <cell r="F110">
-            <v>352</v>
-          </cell>
-        </row>
-        <row r="111">
-          <cell r="A111" t="str">
-            <v>MK9179</v>
-          </cell>
-          <cell r="F111">
-            <v>645</v>
-          </cell>
-        </row>
-        <row r="112">
-          <cell r="A112" t="str">
-            <v>AR11338</v>
-          </cell>
-          <cell r="F112">
-            <v>625</v>
-          </cell>
-        </row>
-        <row r="113">
-          <cell r="A113" t="str">
-            <v>ES5306</v>
-          </cell>
-          <cell r="F113">
-            <v>419</v>
-          </cell>
-        </row>
-        <row r="114">
-          <cell r="A114" t="str">
-            <v>AR11622</v>
-          </cell>
-          <cell r="F114">
-            <v>12</v>
-          </cell>
-        </row>
-        <row r="115">
-          <cell r="A115" t="str">
-            <v>MK4845</v>
-          </cell>
-          <cell r="F115">
-            <v>17</v>
-          </cell>
-        </row>
-        <row r="116">
-          <cell r="A116" t="str">
-            <v>AR11639</v>
-          </cell>
-          <cell r="F116">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="117">
-          <cell r="A117" t="str">
-            <v>AX1767</v>
-          </cell>
-          <cell r="F117">
-            <v>273</v>
-          </cell>
-        </row>
-        <row r="118">
-          <cell r="A118" t="str">
-            <v>AX5730</v>
-          </cell>
-          <cell r="F118">
-            <v>69</v>
-          </cell>
-        </row>
-        <row r="119">
-          <cell r="A119" t="str">
-            <v>MK9165</v>
-          </cell>
-          <cell r="F119">
-            <v>555</v>
-          </cell>
-        </row>
-        <row r="120">
-          <cell r="A120" t="str">
-            <v>AX2460</v>
-          </cell>
-          <cell r="F120">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="121">
-          <cell r="A121" t="str">
-            <v>FS6131</v>
-          </cell>
-          <cell r="F121">
-            <v>288</v>
-          </cell>
-        </row>
-        <row r="122">
-          <cell r="A122" t="str">
-            <v>ME3270</v>
-          </cell>
-          <cell r="F122">
-            <v>1356</v>
-          </cell>
-        </row>
-        <row r="123">
-          <cell r="A123" t="str">
-            <v>AX4181</v>
-          </cell>
-          <cell r="F123">
-            <v>910</v>
-          </cell>
-        </row>
-        <row r="124">
-          <cell r="A124" t="str">
-            <v>AX2413</v>
-          </cell>
-          <cell r="F124">
-            <v>297</v>
-          </cell>
-        </row>
-        <row r="125">
-          <cell r="A125" t="str">
-            <v>FS5699</v>
-          </cell>
-          <cell r="F125">
-            <v>892</v>
-          </cell>
-        </row>
-        <row r="126">
-          <cell r="A126" t="str">
-            <v>FS6104</v>
-          </cell>
-          <cell r="F126">
-            <v>647</v>
-          </cell>
-        </row>
-        <row r="127">
-          <cell r="A127" t="str">
-            <v>AX7163SET</v>
-          </cell>
-          <cell r="F127">
-            <v>125</v>
-          </cell>
-        </row>
-        <row r="128">
-          <cell r="A128" t="str">
-            <v>MK9191</v>
-          </cell>
-          <cell r="F128">
-            <v>310</v>
-          </cell>
-        </row>
-        <row r="129">
-          <cell r="A129" t="str">
-            <v>MK4710</v>
-          </cell>
-          <cell r="F129">
-            <v>159</v>
-          </cell>
-        </row>
-        <row r="130">
-          <cell r="A130" t="str">
-            <v>AR11582</v>
-          </cell>
-          <cell r="F130">
-            <v>37</v>
-          </cell>
-        </row>
-        <row r="131">
-          <cell r="A131" t="str">
-            <v>AX2454</v>
-          </cell>
-          <cell r="F131">
-            <v>1068</v>
-          </cell>
-        </row>
-        <row r="132">
-          <cell r="A132" t="str">
-            <v>MK7474</v>
-          </cell>
-          <cell r="F132">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="133">
-          <cell r="A133" t="str">
-            <v>AX5725</v>
-          </cell>
-          <cell r="F133">
-            <v>349</v>
-          </cell>
-        </row>
-        <row r="134">
-          <cell r="A134" t="str">
-            <v>SKW2694</v>
-          </cell>
-          <cell r="F134">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="135">
-          <cell r="A135" t="str">
-            <v>DZ4548</v>
-          </cell>
-          <cell r="F135">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="136">
-          <cell r="A136" t="str">
-            <v>ES5381</v>
-          </cell>
-          <cell r="F136">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="137">
-          <cell r="A137" t="str">
-            <v>FS6071</v>
-          </cell>
-          <cell r="F137">
-            <v>845</v>
-          </cell>
-        </row>
-        <row r="138">
-          <cell r="A138" t="str">
-            <v>AR11677</v>
-          </cell>
-          <cell r="F138">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="139">
-          <cell r="A139" t="str">
-            <v>ES5357</v>
-          </cell>
-          <cell r="F139">
-            <v>470</v>
-          </cell>
-        </row>
-        <row r="140">
-          <cell r="A140" t="str">
-            <v>MK4882</v>
-          </cell>
-          <cell r="F140">
-            <v>549</v>
-          </cell>
-        </row>
-        <row r="141">
-          <cell r="A141" t="str">
-            <v>ES5331</v>
-          </cell>
-          <cell r="F141">
-            <v>875</v>
-          </cell>
-        </row>
-        <row r="142">
-          <cell r="A142" t="str">
-            <v>ME3206</v>
-          </cell>
-          <cell r="F142">
-            <v>1051</v>
-          </cell>
-        </row>
-        <row r="143">
-          <cell r="A143" t="str">
-            <v>AR11625</v>
-          </cell>
-          <cell r="F143">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="144">
-          <cell r="A144" t="str">
-            <v>AR11484</v>
-          </cell>
-          <cell r="F144">
-            <v>241</v>
-          </cell>
-        </row>
-        <row r="145">
-          <cell r="A145" t="str">
-            <v>MK9178</v>
-          </cell>
-          <cell r="F145">
-            <v>664</v>
-          </cell>
-        </row>
-        <row r="146">
-          <cell r="A146" t="str">
-            <v>ES5350</v>
-          </cell>
-          <cell r="F146">
-            <v>1176</v>
-          </cell>
-        </row>
-        <row r="147">
-          <cell r="A147" t="str">
-            <v>AR11621</v>
-          </cell>
-          <cell r="F147">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="148">
-          <cell r="A148" t="str">
-            <v>AR11596</v>
-          </cell>
-          <cell r="F148">
-            <v>470</v>
-          </cell>
-        </row>
-        <row r="149">
-          <cell r="A149" t="str">
-            <v>DZ4659</v>
-          </cell>
-          <cell r="F149">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="150">
-          <cell r="A150" t="str">
-            <v>AX1962</v>
-          </cell>
-          <cell r="F150">
-            <v>138</v>
-          </cell>
-        </row>
-        <row r="151">
-          <cell r="A151" t="str">
-            <v>MK9153</v>
-          </cell>
-          <cell r="F151">
-            <v>899</v>
-          </cell>
-        </row>
-        <row r="152">
-          <cell r="A152" t="str">
-            <v>DZ2189</v>
-          </cell>
-          <cell r="F152">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="153">
-          <cell r="A153" t="str">
-            <v>MK4864</v>
-          </cell>
-          <cell r="F153">
-            <v>26</v>
-          </cell>
-        </row>
-        <row r="154">
-          <cell r="A154" t="str">
-            <v>AR11671</v>
-          </cell>
-          <cell r="F154">
-            <v>377</v>
-          </cell>
-        </row>
-        <row r="155">
-          <cell r="A155" t="str">
-            <v>ES5399</v>
-          </cell>
-          <cell r="F155">
-            <v>412</v>
-          </cell>
-        </row>
-        <row r="156">
-          <cell r="A156" t="str">
-            <v>ES5400</v>
-          </cell>
-          <cell r="F156">
-            <v>616</v>
-          </cell>
-        </row>
-        <row r="157">
-          <cell r="A157" t="str">
-            <v>AR11661</v>
-          </cell>
-          <cell r="F157">
-            <v>233</v>
-          </cell>
-        </row>
-        <row r="158">
-          <cell r="A158" t="str">
-            <v>MK4823</v>
-          </cell>
-          <cell r="F158">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="159">
-          <cell r="A159" t="str">
-            <v>AR11690</v>
-          </cell>
-          <cell r="F159">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="160">
-          <cell r="A160" t="str">
-            <v>AX1739</v>
-          </cell>
-          <cell r="F160">
-            <v>571</v>
-          </cell>
-        </row>
-        <row r="161">
-          <cell r="A161" t="str">
-            <v>AR11691</v>
-          </cell>
-          <cell r="F161">
-            <v>489</v>
-          </cell>
-        </row>
-        <row r="162">
-          <cell r="A162" t="str">
-            <v>MK4824</v>
-          </cell>
-          <cell r="F162">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="163">
-          <cell r="A163" t="str">
-            <v>AR11693</v>
-          </cell>
-          <cell r="F163">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="164">
-          <cell r="A164" t="str">
-            <v>AR11568</v>
-          </cell>
-          <cell r="F164">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="165">
-          <cell r="A165" t="str">
-            <v>AR11694</v>
-          </cell>
-          <cell r="F165">
-            <v>15</v>
-          </cell>
-        </row>
-        <row r="166">
-          <cell r="A166" t="str">
-            <v>AR11706</v>
-          </cell>
-          <cell r="F166">
-            <v>543</v>
-          </cell>
-        </row>
-        <row r="167">
-          <cell r="A167" t="str">
-            <v>AX2822</v>
-          </cell>
-          <cell r="F167">
-            <v>541</v>
-          </cell>
-        </row>
-        <row r="168">
-          <cell r="A168" t="str">
-            <v>AX5732</v>
-          </cell>
-          <cell r="F168">
-            <v>351</v>
-          </cell>
-        </row>
-        <row r="169">
-          <cell r="A169" t="str">
-            <v>DZ2212</v>
-          </cell>
-          <cell r="F169">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="170">
-          <cell r="A170" t="str">
-            <v>DZ2213</v>
-          </cell>
-          <cell r="F170">
-            <v>93</v>
-          </cell>
-        </row>
-        <row r="171">
-          <cell r="A171" t="str">
-            <v>FS6133</v>
-          </cell>
-          <cell r="F171">
-            <v>1511</v>
-          </cell>
-        </row>
-        <row r="172">
-          <cell r="A172" t="str">
-            <v>MK9220</v>
-          </cell>
-          <cell r="F172">
-            <v>930</v>
-          </cell>
-        </row>
-        <row r="173">
-          <cell r="A173" t="str">
-            <v>MK4847</v>
-          </cell>
-          <cell r="F173">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="174">
-          <cell r="A174" t="str">
-            <v>MK9176</v>
-          </cell>
-          <cell r="F174">
-            <v>469</v>
-          </cell>
-        </row>
-        <row r="175">
-          <cell r="A175" t="str">
-            <v>DZ2210SET</v>
-          </cell>
-          <cell r="F175">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="176">
-          <cell r="A176" t="str">
-            <v>MK9221</v>
-          </cell>
-          <cell r="F176">
-            <v>736</v>
-          </cell>
-        </row>
-        <row r="177">
-          <cell r="A177" t="str">
-            <v>MK9163</v>
-          </cell>
-          <cell r="F177">
-            <v>52</v>
-          </cell>
-        </row>
-        <row r="178">
-          <cell r="A178" t="str">
-            <v>MK4923</v>
-          </cell>
-          <cell r="F178">
-            <v>746</v>
-          </cell>
-        </row>
-        <row r="179">
-          <cell r="A179" t="str">
-            <v>AX1764</v>
-          </cell>
-          <cell r="F179">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="180">
-          <cell r="A180" t="str">
-            <v>MK7488</v>
-          </cell>
-          <cell r="F180">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="181">
-          <cell r="A181" t="str">
-            <v>AR80083SET</v>
-          </cell>
-          <cell r="F181">
-            <v>13</v>
-          </cell>
-        </row>
-        <row r="182">
-          <cell r="A182" t="str">
-            <v>MK9156</v>
-          </cell>
-          <cell r="F182">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="183">
-          <cell r="A183" t="str">
-            <v>AR11360</v>
-          </cell>
-          <cell r="F183">
-            <v>211</v>
-          </cell>
-        </row>
-        <row r="184">
-          <cell r="A184" t="str">
-            <v>AX7165SET</v>
-          </cell>
-          <cell r="F184">
-            <v>309</v>
-          </cell>
-        </row>
-        <row r="185">
-          <cell r="A185" t="str">
-            <v>AR2502</v>
-          </cell>
-          <cell r="F185">
-            <v>200</v>
-          </cell>
-        </row>
-        <row r="186">
-          <cell r="A186" t="str">
-            <v>AR80065SET</v>
-          </cell>
-          <cell r="F186">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="187">
-          <cell r="A187" t="str">
-            <v>ME3261</v>
-          </cell>
-          <cell r="F187">
-            <v>598</v>
-          </cell>
-        </row>
-        <row r="188">
-          <cell r="A188" t="str">
-            <v>FS4656</v>
-          </cell>
-          <cell r="F188">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="189">
-          <cell r="A189" t="str">
-            <v>MK4829</v>
-          </cell>
-          <cell r="F189">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="190">
-          <cell r="A190" t="str">
-            <v>ES3466</v>
-          </cell>
-          <cell r="F190">
-            <v>2151</v>
-          </cell>
-        </row>
-        <row r="191">
-          <cell r="A191" t="str">
-            <v>SKW6355</v>
-          </cell>
-          <cell r="F191">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="192">
-          <cell r="A192" t="str">
-            <v>ME3061</v>
-          </cell>
-          <cell r="F192">
-            <v>1032</v>
-          </cell>
-        </row>
-        <row r="193">
-          <cell r="A193" t="str">
-            <v>MK4843</v>
-          </cell>
-          <cell r="F193">
-            <v>111</v>
-          </cell>
-        </row>
-        <row r="194">
-          <cell r="A194" t="str">
-            <v>AR11636</v>
-          </cell>
-          <cell r="F194">
-            <v>46</v>
-          </cell>
-        </row>
-        <row r="195">
-          <cell r="A195" t="str">
-            <v>FS5151</v>
-          </cell>
-          <cell r="F195">
-            <v>1484</v>
-          </cell>
-        </row>
-        <row r="196">
-          <cell r="A196" t="str">
-            <v>FS5452</v>
-          </cell>
-          <cell r="F196">
-            <v>112</v>
-          </cell>
-        </row>
-        <row r="197">
-          <cell r="A197" t="str">
-            <v>ME3265</v>
-          </cell>
-          <cell r="F197">
-            <v>1127</v>
-          </cell>
-        </row>
-        <row r="198">
-          <cell r="A198" t="str">
-            <v>FS5822</v>
-          </cell>
-          <cell r="F198">
-            <v>180</v>
-          </cell>
-        </row>
-        <row r="199">
-          <cell r="A199" t="str">
-            <v>FS5708SET</v>
-          </cell>
-          <cell r="F199">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="200">
-          <cell r="A200" t="str">
-            <v>AX2101</v>
-          </cell>
-          <cell r="F200">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="201">
-          <cell r="A201" t="str">
-            <v>MK9192</v>
-          </cell>
-          <cell r="F201">
-            <v>532</v>
-          </cell>
-        </row>
-        <row r="202">
-          <cell r="A202" t="str">
-            <v>AR11676</v>
-          </cell>
-          <cell r="F202">
-            <v>262</v>
-          </cell>
-        </row>
-        <row r="203">
-          <cell r="A203" t="str">
-            <v>FS6107</v>
-          </cell>
-          <cell r="F203">
-            <v>402</v>
-          </cell>
-        </row>
-        <row r="204">
-          <cell r="A204" t="str">
-            <v>FS6089</v>
-          </cell>
-          <cell r="F204">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="205">
-          <cell r="A205" t="str">
-            <v>MK4709</v>
-          </cell>
-          <cell r="F205">
-            <v>21</v>
-          </cell>
-        </row>
-        <row r="206">
-          <cell r="A206" t="str">
-            <v>MK4873</v>
-          </cell>
-          <cell r="F206">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="207">
-          <cell r="A207" t="str">
-            <v>ES5380</v>
-          </cell>
-          <cell r="F207">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="208">
-          <cell r="A208" t="str">
-            <v>DZ2215</v>
-          </cell>
-          <cell r="F208">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="209">
-          <cell r="A209" t="str">
-            <v>AR60080</v>
-          </cell>
-          <cell r="F209">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="210">
-          <cell r="A210" t="str">
-            <v>AX7161SET</v>
-          </cell>
-          <cell r="F210">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="211">
-          <cell r="A211" t="str">
-            <v>DZ2214</v>
-          </cell>
-          <cell r="F211">
-            <v>6</v>
-          </cell>
-        </row>
-        <row r="212">
-          <cell r="A212" t="str">
-            <v>AR11635</v>
-          </cell>
-          <cell r="F212">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="213">
-          <cell r="A213" t="str">
-            <v>MK8603</v>
-          </cell>
-          <cell r="F213">
-            <v>182</v>
-          </cell>
-        </row>
-        <row r="214">
-          <cell r="A214" t="str">
-            <v>MK4339</v>
-          </cell>
-          <cell r="F214">
-            <v>11</v>
-          </cell>
-        </row>
-        <row r="215">
-          <cell r="A215" t="str">
-            <v>FS6085</v>
-          </cell>
-          <cell r="F215">
-            <v>27</v>
-          </cell>
-        </row>
-        <row r="216">
-          <cell r="A216" t="str">
-            <v>AX5729</v>
-          </cell>
-          <cell r="F216">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="217">
-          <cell r="A217" t="str">
-            <v>ES5402</v>
-          </cell>
-          <cell r="F217">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="218">
-          <cell r="A218" t="str">
-            <v>ES5398</v>
-          </cell>
-          <cell r="F218">
-            <v>806</v>
-          </cell>
-        </row>
-        <row r="219">
-          <cell r="A219" t="str">
-            <v>MK7519LE</v>
-          </cell>
-          <cell r="F219">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="220">
-          <cell r="A220" t="str">
-            <v>MK9196</v>
-          </cell>
-          <cell r="F220">
-            <v>477</v>
-          </cell>
-        </row>
-        <row r="221">
-          <cell r="A221" t="str">
-            <v>MK9198</v>
-          </cell>
-          <cell r="F221">
-            <v>758</v>
-          </cell>
-        </row>
-        <row r="222">
-          <cell r="A222" t="str">
-            <v>MK9201</v>
-          </cell>
-          <cell r="F222">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="223">
-          <cell r="A223" t="str">
-            <v>AR11660</v>
-          </cell>
-          <cell r="F223">
-            <v>94</v>
-          </cell>
-        </row>
-        <row r="224">
-          <cell r="A224" t="str">
-            <v>AR11662</v>
-          </cell>
-          <cell r="F224">
-            <v>242</v>
-          </cell>
-        </row>
-        <row r="225">
-          <cell r="A225" t="str">
-            <v>AR11663</v>
-          </cell>
-          <cell r="F225">
-            <v>426</v>
-          </cell>
-        </row>
-        <row r="226">
-          <cell r="A226" t="str">
-            <v>DZ5612</v>
-          </cell>
-          <cell r="F226">
-            <v>30</v>
-          </cell>
-        </row>
-        <row r="227">
-          <cell r="A227" t="str">
-            <v>DZ5613</v>
-          </cell>
-          <cell r="F227">
-            <v>45</v>
-          </cell>
-        </row>
-        <row r="228">
-          <cell r="A228" t="str">
-            <v>DZ7487</v>
-          </cell>
-          <cell r="F228">
-            <v>156</v>
-          </cell>
-        </row>
-        <row r="229">
-          <cell r="A229" t="str">
-            <v>AR11707</v>
-          </cell>
-          <cell r="F229">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="230">
-          <cell r="A230" t="str">
-            <v>AX2820</v>
-          </cell>
-          <cell r="F230">
-            <v>199</v>
-          </cell>
-        </row>
-        <row r="231">
-          <cell r="A231" t="str">
-            <v>ES5422</v>
-          </cell>
-          <cell r="F231">
-            <v>782</v>
-          </cell>
-        </row>
-        <row r="232">
-          <cell r="A232" t="str">
-            <v>DZ4670</v>
-          </cell>
-          <cell r="F232">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="233">
-          <cell r="A233" t="str">
-            <v>AR11713</v>
-          </cell>
-          <cell r="F233">
-            <v>118</v>
-          </cell>
-        </row>
-        <row r="234">
-          <cell r="A234" t="str">
-            <v>AR11714</v>
-          </cell>
-          <cell r="F234">
-            <v>208</v>
-          </cell>
-        </row>
-        <row r="235">
-          <cell r="A235" t="str">
-            <v>AR11689</v>
-          </cell>
-          <cell r="F235">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="236">
-          <cell r="A236" t="str">
-            <v>AX4173</v>
-          </cell>
-          <cell r="F236">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="237">
-          <cell r="A237" t="str">
-            <v>ME3266</v>
-          </cell>
-          <cell r="F237">
-            <v>807</v>
-          </cell>
-        </row>
-        <row r="238">
-          <cell r="A238" t="str">
-            <v>AR1926</v>
-          </cell>
-          <cell r="F238">
-            <v>768</v>
-          </cell>
-        </row>
-        <row r="239">
-          <cell r="A239" t="str">
-            <v>AR11624</v>
-          </cell>
-          <cell r="F239">
-            <v>60</v>
-          </cell>
-        </row>
-        <row r="240">
-          <cell r="A240" t="str">
-            <v>MK4817SET</v>
-          </cell>
-          <cell r="F240">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="241">
-          <cell r="A241" t="str">
-            <v>MK4863</v>
-          </cell>
-          <cell r="F241">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="242">
-          <cell r="A242" t="str">
-            <v>FS6045</v>
-          </cell>
-          <cell r="F242">
-            <v>869</v>
-          </cell>
-        </row>
-        <row r="243">
-          <cell r="A243" t="str">
-            <v>MK9152</v>
-          </cell>
-          <cell r="F243">
-            <v>550</v>
-          </cell>
-        </row>
-        <row r="244">
-          <cell r="A244" t="str">
-            <v>AR11626</v>
-          </cell>
-          <cell r="F244">
-            <v>213</v>
-          </cell>
-        </row>
-        <row r="245">
-          <cell r="A245" t="str">
-            <v>AX5724</v>
-          </cell>
-          <cell r="F245">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="246">
-          <cell r="A246" t="str">
-            <v>MK4822</v>
-          </cell>
-          <cell r="F246">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="247">
-          <cell r="A247" t="str">
-            <v>FS5971</v>
-          </cell>
-          <cell r="F247">
-            <v>409</v>
-          </cell>
-        </row>
-        <row r="248">
-          <cell r="A248" t="str">
-            <v>AR11674</v>
-          </cell>
-          <cell r="F248">
-            <v>377</v>
-          </cell>
-        </row>
-        <row r="249">
-          <cell r="A249" t="str">
-            <v>AR11688</v>
-          </cell>
-          <cell r="F249">
-            <v>66</v>
-          </cell>
-        </row>
-        <row r="250">
-          <cell r="A250" t="str">
-            <v>AR11708</v>
-          </cell>
-          <cell r="F250">
-            <v>149</v>
-          </cell>
-        </row>
-        <row r="251">
-          <cell r="A251" t="str">
-            <v>AX2821</v>
-          </cell>
-          <cell r="F251">
-            <v>389</v>
-          </cell>
-        </row>
-        <row r="252">
-          <cell r="A252" t="str">
-            <v>ES5418</v>
-          </cell>
-          <cell r="F252">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="253">
-          <cell r="A253" t="str">
-            <v>AX5735</v>
-          </cell>
-          <cell r="F253">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="254">
-          <cell r="A254" t="str">
-            <v>ES5417</v>
-          </cell>
-          <cell r="F254">
-            <v>1519</v>
-          </cell>
-        </row>
-        <row r="255">
-          <cell r="A255" t="str">
-            <v>MK4931</v>
-          </cell>
-          <cell r="F255">
-            <v>1334</v>
-          </cell>
-        </row>
-        <row r="256">
-          <cell r="A256" t="str">
-            <v>MK4933</v>
-          </cell>
-          <cell r="F256">
-            <v>247</v>
-          </cell>
-        </row>
-        <row r="257">
-          <cell r="A257" t="str">
-            <v>MK4934</v>
-          </cell>
-          <cell r="F257">
-            <v>1272</v>
-          </cell>
-        </row>
-        <row r="258">
-          <cell r="A258" t="str">
-            <v>MK4935</v>
-          </cell>
-          <cell r="F258">
-            <v>583</v>
-          </cell>
-        </row>
-        <row r="259">
-          <cell r="A259" t="str">
-            <v>MK9222</v>
-          </cell>
-          <cell r="F259">
-            <v>420</v>
-          </cell>
-        </row>
-        <row r="260">
-          <cell r="A260" t="str">
-            <v>MK4932</v>
-          </cell>
-          <cell r="F260">
-            <v>1058</v>
-          </cell>
-        </row>
-        <row r="261">
-          <cell r="A261" t="str">
-            <v>MK7559</v>
-          </cell>
-          <cell r="F261">
-            <v>415</v>
-          </cell>
-        </row>
-        <row r="262">
-          <cell r="A262" t="str">
-            <v>DZ4671</v>
-          </cell>
-          <cell r="F262">
-            <v>73</v>
-          </cell>
-        </row>
-        <row r="263">
-          <cell r="A263" t="str">
-            <v>AR11718</v>
-          </cell>
-          <cell r="F263">
-            <v>52</v>
-          </cell>
-        </row>
-        <row r="264">
-          <cell r="A264" t="str">
-            <v>AX7176SET</v>
-          </cell>
-          <cell r="F264">
-            <v>151</v>
-          </cell>
-        </row>
-        <row r="265">
-          <cell r="A265" t="str">
-            <v>ES5443</v>
-          </cell>
-          <cell r="F265">
-            <v>1538</v>
-          </cell>
-        </row>
-        <row r="266">
-          <cell r="A266" t="str">
-            <v>ES5444</v>
-          </cell>
-          <cell r="F266">
-            <v>484</v>
-          </cell>
-        </row>
-        <row r="267">
-          <cell r="A267" t="str">
-            <v>ES5451</v>
-          </cell>
-          <cell r="F267">
-            <v>859</v>
-          </cell>
-        </row>
-        <row r="268">
-          <cell r="A268" t="str">
-            <v>MK4963</v>
-          </cell>
-          <cell r="F268">
-            <v>1028</v>
-          </cell>
-        </row>
-        <row r="269">
-          <cell r="A269" t="str">
-            <v>MK4964</v>
-          </cell>
-          <cell r="F269">
-            <v>17</v>
-          </cell>
-        </row>
-        <row r="270">
-          <cell r="A270" t="str">
-            <v>MK9240</v>
-          </cell>
-          <cell r="F270">
-            <v>1623</v>
-          </cell>
-        </row>
-        <row r="271">
-          <cell r="A271" t="str">
-            <v>MK9245SET</v>
-          </cell>
-          <cell r="F271">
-            <v>62</v>
-          </cell>
-        </row>
-        <row r="272">
-          <cell r="A272" t="str">
-            <v>AR2434</v>
-          </cell>
-          <cell r="F272">
-            <v>73</v>
-          </cell>
-        </row>
-        <row r="273">
-          <cell r="A273" t="str">
-            <v>AR11610</v>
-          </cell>
-          <cell r="F273">
-            <v>152</v>
-          </cell>
-        </row>
-        <row r="274">
-          <cell r="A274" t="str">
-            <v>DZ7395</v>
-          </cell>
-          <cell r="F274">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="275">
-          <cell r="A275" t="str">
-            <v>DZ4667</v>
-          </cell>
-          <cell r="F275">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="276">
-          <cell r="A276" t="str">
-            <v>DZ5618</v>
-          </cell>
-          <cell r="F276">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="277">
-          <cell r="A277" t="str">
-            <v>DZ4662</v>
-          </cell>
-          <cell r="F277">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="278">
-          <cell r="A278" t="str">
-            <v>DZ4665</v>
-          </cell>
-          <cell r="F278">
-            <v>123</v>
-          </cell>
-        </row>
-        <row r="279">
-          <cell r="A279" t="str">
-            <v>AR11623</v>
-          </cell>
-          <cell r="F279">
-            <v>27</v>
-          </cell>
-        </row>
-        <row r="280">
-          <cell r="A280" t="str">
-            <v>AR11672</v>
-          </cell>
-          <cell r="F280">
-            <v>355</v>
-          </cell>
-        </row>
-        <row r="281">
-          <cell r="A281" t="str">
-            <v>AX5916</v>
-          </cell>
-          <cell r="F281">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="282">
-          <cell r="A282" t="str">
-            <v>FS6108</v>
-          </cell>
-          <cell r="F282">
-            <v>210</v>
-          </cell>
-        </row>
-        <row r="283">
-          <cell r="A283" t="str">
-            <v>AR11664</v>
-          </cell>
-          <cell r="F283">
-            <v>27</v>
-          </cell>
-        </row>
-        <row r="284">
-          <cell r="A284" t="str">
-            <v>DZ5609</v>
-          </cell>
-          <cell r="F284">
-            <v>83</v>
-          </cell>
-        </row>
-        <row r="285">
-          <cell r="A285" t="str">
-            <v>DZ5611</v>
-          </cell>
-          <cell r="F285">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="286">
-          <cell r="A286" t="str">
-            <v>ES5438</v>
-          </cell>
-          <cell r="F286">
-            <v>318</v>
-          </cell>
-        </row>
-        <row r="287">
-          <cell r="A287" t="str">
-            <v>ES5439</v>
-          </cell>
-          <cell r="F287">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="288">
-          <cell r="A288" t="str">
-            <v>AX4199</v>
-          </cell>
-          <cell r="F288">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="289">
-          <cell r="A289" t="str">
-            <v>FS6149</v>
-          </cell>
-          <cell r="F289">
-            <v>1047</v>
-          </cell>
-        </row>
-        <row r="290">
-          <cell r="A290" t="str">
-            <v>FS6151</v>
-          </cell>
-          <cell r="F290">
-            <v>1169</v>
-          </cell>
-        </row>
-        <row r="291">
-          <cell r="A291" t="str">
-            <v>MK4962</v>
-          </cell>
-          <cell r="F291">
-            <v>1582</v>
-          </cell>
-        </row>
-        <row r="292">
-          <cell r="A292" t="str">
-            <v>MK4965</v>
-          </cell>
-          <cell r="F292">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="293">
-          <cell r="A293" t="str">
-            <v>MK4967</v>
-          </cell>
-          <cell r="F293">
-            <v>18</v>
-          </cell>
-        </row>
-        <row r="294">
-          <cell r="A294" t="str">
-            <v>MK9242</v>
-          </cell>
-          <cell r="F294">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="295">
-          <cell r="A295" t="str">
-            <v>ES5386</v>
-          </cell>
-          <cell r="F295">
-            <v>29</v>
-          </cell>
-        </row>
-        <row r="296">
-          <cell r="A296" t="str">
-            <v>DZ4627</v>
-          </cell>
-          <cell r="F296">
-            <v>221</v>
-          </cell>
-        </row>
-        <row r="297">
-          <cell r="A297" t="str">
-            <v>FS6150</v>
-          </cell>
-          <cell r="F297">
-            <v>1695</v>
-          </cell>
-        </row>
-        <row r="298">
-          <cell r="A298" t="str">
-            <v>ES5362</v>
-          </cell>
-          <cell r="F298">
-            <v>1221</v>
-          </cell>
-        </row>
-        <row r="299">
-          <cell r="A299" t="str">
-            <v>MK4805</v>
-          </cell>
-          <cell r="F299">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="300">
-          <cell r="A300" t="str">
-            <v>ME3154</v>
-          </cell>
-          <cell r="F300">
-            <v>238</v>
-          </cell>
-        </row>
-        <row r="301">
-          <cell r="A301" t="str">
-            <v>AR11692</v>
-          </cell>
-          <cell r="F301">
-            <v>162</v>
-          </cell>
-        </row>
-        <row r="302">
-          <cell r="A302" t="str">
-            <v>MKO1224</v>
-          </cell>
-          <cell r="F302">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="303">
-          <cell r="A303" t="str">
-            <v>AX1971</v>
-          </cell>
-          <cell r="F303">
-            <v>49</v>
-          </cell>
-        </row>
-        <row r="304">
-          <cell r="A304" t="str">
-            <v>AX1972</v>
-          </cell>
-          <cell r="F304">
-            <v>176</v>
-          </cell>
-        </row>
-        <row r="305">
-          <cell r="A305" t="str">
-            <v>AX1973</v>
-          </cell>
-          <cell r="F305">
-            <v>164</v>
-          </cell>
-        </row>
-        <row r="306">
-          <cell r="A306" t="str">
-            <v>AX2766</v>
-          </cell>
-          <cell r="F306">
-            <v>10</v>
-          </cell>
-        </row>
-        <row r="307">
-          <cell r="A307" t="str">
-            <v>AX2767</v>
-          </cell>
-          <cell r="F307">
-            <v>15</v>
-          </cell>
-        </row>
-        <row r="308">
-          <cell r="A308" t="str">
-            <v>AX4405</v>
-          </cell>
-          <cell r="F308">
-            <v>568</v>
-          </cell>
-        </row>
-        <row r="309">
-          <cell r="A309" t="str">
-            <v>AX4406</v>
-          </cell>
-          <cell r="F309">
-            <v>1274</v>
-          </cell>
-        </row>
-        <row r="310">
-          <cell r="A310" t="str">
-            <v>AX4407</v>
-          </cell>
-          <cell r="F310">
-            <v>1138</v>
-          </cell>
-        </row>
-        <row r="311">
-          <cell r="A311" t="str">
-            <v>AX4408</v>
-          </cell>
-          <cell r="F311">
-            <v>928</v>
-          </cell>
-        </row>
-        <row r="312">
-          <cell r="A312" t="str">
-            <v>AX4625</v>
-          </cell>
-          <cell r="F312">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="313">
-          <cell r="A313" t="str">
-            <v>DZ2234</v>
-          </cell>
-          <cell r="F313">
-            <v>95</v>
-          </cell>
-        </row>
-        <row r="314">
-          <cell r="A314" t="str">
-            <v>DZ4702</v>
-          </cell>
-          <cell r="F314">
-            <v>45</v>
-          </cell>
-        </row>
-        <row r="315">
-          <cell r="A315" t="str">
-            <v>DZ4709</v>
-          </cell>
-          <cell r="F315">
-            <v>186</v>
-          </cell>
-        </row>
-        <row r="316">
-          <cell r="A316" t="str">
-            <v>AR11755</v>
-          </cell>
-          <cell r="F316">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="317">
-          <cell r="A317" t="str">
-            <v>AR80087SET</v>
-          </cell>
-          <cell r="F317">
-            <v>70</v>
-          </cell>
-        </row>
-        <row r="318">
-          <cell r="A318" t="str">
-            <v>ES5455</v>
-          </cell>
-          <cell r="F318">
-            <v>10</v>
-          </cell>
-        </row>
-        <row r="319">
-          <cell r="A319" t="str">
-            <v>ES5456</v>
-          </cell>
-          <cell r="F319">
-            <v>526</v>
-          </cell>
-        </row>
-        <row r="320">
-          <cell r="A320" t="str">
-            <v>ES5472</v>
-          </cell>
-          <cell r="F320">
-            <v>317</v>
-          </cell>
-        </row>
-        <row r="321">
-          <cell r="A321" t="str">
-            <v>FS6154</v>
-          </cell>
-          <cell r="F321">
-            <v>497</v>
-          </cell>
-        </row>
-        <row r="322">
-          <cell r="A322" t="str">
-            <v>FS6161</v>
-          </cell>
-          <cell r="F322">
-            <v>463</v>
-          </cell>
-        </row>
-        <row r="323">
-          <cell r="A323" t="str">
-            <v>FS6163</v>
-          </cell>
-          <cell r="F323">
-            <v>919</v>
-          </cell>
-        </row>
-        <row r="324">
-          <cell r="A324" t="str">
-            <v>MK4997</v>
-          </cell>
-          <cell r="F324">
-            <v>431</v>
-          </cell>
-        </row>
-        <row r="325">
-          <cell r="A325" t="str">
-            <v>MK4998</v>
-          </cell>
-          <cell r="F325">
-            <v>678</v>
-          </cell>
-        </row>
-        <row r="326">
-          <cell r="A326" t="str">
-            <v>MK4999</v>
-          </cell>
-          <cell r="F326">
-            <v>628</v>
-          </cell>
-        </row>
-        <row r="327">
-          <cell r="A327" t="str">
-            <v>MK7568</v>
-          </cell>
-          <cell r="F327">
-            <v>473</v>
-          </cell>
-        </row>
-        <row r="328">
-          <cell r="A328" t="str">
-            <v>MK7570SET</v>
-          </cell>
-          <cell r="F328">
-            <v>39</v>
-          </cell>
-        </row>
-        <row r="329">
-          <cell r="A329" t="str">
-            <v>MK7581</v>
-          </cell>
-          <cell r="F329">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="330">
-          <cell r="A330" t="str">
-            <v>MK7582</v>
-          </cell>
-          <cell r="F330">
-            <v>51</v>
-          </cell>
-        </row>
-        <row r="331">
-          <cell r="A331" t="str">
-            <v>MK7589</v>
-          </cell>
-          <cell r="F331">
-            <v>225</v>
-          </cell>
-        </row>
-        <row r="332">
-          <cell r="A332" t="str">
-            <v>MK7590</v>
-          </cell>
-          <cell r="F332">
-            <v>729</v>
-          </cell>
-        </row>
-        <row r="333">
-          <cell r="A333" t="str">
-            <v>DZ4703</v>
-          </cell>
-          <cell r="F333">
-            <v>91</v>
-          </cell>
-        </row>
-        <row r="334">
-          <cell r="A334" t="str">
-            <v>AR11754</v>
-          </cell>
-          <cell r="F334">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="335">
-          <cell r="A335" t="str">
-            <v>AR11756</v>
-          </cell>
-          <cell r="F335">
-            <v>115</v>
-          </cell>
-        </row>
-        <row r="336">
-          <cell r="A336" t="str">
-            <v>AR11757</v>
-          </cell>
-          <cell r="F336">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="337">
-          <cell r="A337" t="str">
-            <v>AR11759</v>
-          </cell>
-          <cell r="F337">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="338">
-          <cell r="A338" t="str">
-            <v>AR11770</v>
-          </cell>
-          <cell r="F338">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="339">
-          <cell r="A339" t="str">
-            <v>AR11771</v>
-          </cell>
-          <cell r="F339">
-            <v>347</v>
-          </cell>
-        </row>
-        <row r="340">
-          <cell r="A340" t="str">
-            <v>AR11772</v>
-          </cell>
-          <cell r="F340">
-            <v>353</v>
-          </cell>
-        </row>
-        <row r="341">
-          <cell r="A341" t="str">
-            <v>AR11774</v>
-          </cell>
-          <cell r="F341">
-            <v>6</v>
-          </cell>
-        </row>
-        <row r="342">
-          <cell r="A342" t="str">
-            <v>AR11783</v>
-          </cell>
-          <cell r="F342">
-            <v>750</v>
-          </cell>
-        </row>
-        <row r="343">
-          <cell r="A343" t="str">
-            <v>FS6162</v>
-          </cell>
-          <cell r="F343">
-            <v>1085</v>
-          </cell>
-        </row>
-        <row r="344">
-          <cell r="A344" t="str">
-            <v>FS6164</v>
-          </cell>
-          <cell r="F344">
-            <v>1341</v>
-          </cell>
-        </row>
-        <row r="345">
-          <cell r="A345" t="str">
-            <v>MK7572</v>
-          </cell>
-          <cell r="F345">
-            <v>928</v>
-          </cell>
-        </row>
-        <row r="346">
-          <cell r="A346" t="str">
-            <v>MK7573</v>
-          </cell>
-          <cell r="F346">
-            <v>791</v>
-          </cell>
-        </row>
-        <row r="347">
-          <cell r="A347" t="str">
-            <v>MK7574</v>
-          </cell>
-          <cell r="F347">
-            <v>394</v>
-          </cell>
-        </row>
-        <row r="348">
-          <cell r="A348" t="str">
-            <v>MK7584</v>
-          </cell>
-          <cell r="F348">
-            <v>134</v>
-          </cell>
-        </row>
-        <row r="349">
-          <cell r="A349" t="str">
-            <v>MK7587</v>
-          </cell>
-          <cell r="F349">
-            <v>41</v>
-          </cell>
-        </row>
-        <row r="350">
-          <cell r="A350" t="str">
-            <v>ES5388</v>
-          </cell>
-          <cell r="F350">
-            <v>7</v>
-          </cell>
-        </row>
-        <row r="351">
-          <cell r="A351" t="str">
-            <v>AX1956</v>
-          </cell>
-          <cell r="F351">
-            <v>564</v>
-          </cell>
-        </row>
-        <row r="352">
-          <cell r="A352" t="str">
-            <v>AR11773</v>
-          </cell>
-          <cell r="F352">
-            <v>198</v>
-          </cell>
-        </row>
-        <row r="353">
-          <cell r="A353" t="str">
-            <v>AR70010</v>
-          </cell>
-          <cell r="F353">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="354">
-          <cell r="A354" t="str">
-            <v>AR11349</v>
-          </cell>
-          <cell r="F354">
-            <v>275</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7262,24 +4449,23 @@
         <v>12</v>
       </c>
       <c r="I2" s="8">
-        <v>479</v>
+        <v>449</v>
       </c>
       <c r="J2" s="8">
         <v>0</v>
       </c>
       <c r="K2" s="8">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="L2" s="8">
         <v>0</v>
       </c>
       <c r="M2" s="8">
         <f>I2+J2+K2+L2</f>
-        <v>527</v>
+        <v>593</v>
       </c>
       <c r="N2" s="8">
-        <f>_xlfn.XLOOKUP(C2,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>1911</v>
+        <v>1767</v>
       </c>
       <c r="O2" s="8"/>
       <c r="P2" s="8"/>
@@ -7330,7 +4516,6 @@
         <v>2</v>
       </c>
       <c r="N3" s="8">
-        <f>_xlfn.XLOOKUP(C3,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O3" s="8"/>
@@ -7366,7 +4551,7 @@
         <v>12</v>
       </c>
       <c r="I4" s="8">
-        <v>310</v>
+        <v>296</v>
       </c>
       <c r="J4" s="8">
         <v>0</v>
@@ -7379,10 +4564,9 @@
       </c>
       <c r="M4" s="8">
         <f t="shared" si="0"/>
-        <v>310</v>
+        <v>296</v>
       </c>
       <c r="N4" s="8">
-        <f>_xlfn.XLOOKUP(C4,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O4" s="8"/>
@@ -7418,7 +4602,7 @@
         <v>12</v>
       </c>
       <c r="I5" s="8">
-        <v>301</v>
+        <v>270</v>
       </c>
       <c r="J5" s="8">
         <v>0</v>
@@ -7431,11 +4615,10 @@
       </c>
       <c r="M5" s="8">
         <f t="shared" si="0"/>
-        <v>301</v>
+        <v>270</v>
       </c>
       <c r="N5" s="8">
-        <f>_xlfn.XLOOKUP(C5,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="O5" s="8"/>
       <c r="P5" s="8"/>
@@ -7470,24 +4653,23 @@
         <v>12</v>
       </c>
       <c r="I6" s="8">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="J6" s="8">
         <v>0</v>
       </c>
       <c r="K6" s="8">
-        <v>72</v>
+        <v>240</v>
       </c>
       <c r="L6" s="8">
         <v>0</v>
       </c>
       <c r="M6" s="8">
         <f t="shared" si="0"/>
-        <v>528</v>
+        <v>686</v>
       </c>
       <c r="N6" s="8">
-        <f>_xlfn.XLOOKUP(C6,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>2414</v>
+        <v>2175</v>
       </c>
       <c r="O6" s="8"/>
       <c r="P6" s="8"/>
@@ -7522,24 +4704,23 @@
         <v>12</v>
       </c>
       <c r="I7" s="8">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="J7" s="8">
         <v>0</v>
       </c>
       <c r="K7" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" s="8">
         <v>0</v>
       </c>
       <c r="M7" s="8">
         <f t="shared" si="0"/>
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="N7" s="8">
-        <f>_xlfn.XLOOKUP(C7,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>2</v>
+        <v>540</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
@@ -7574,24 +4755,23 @@
         <v>12</v>
       </c>
       <c r="I8" s="8">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="J8" s="8">
         <v>0</v>
       </c>
       <c r="K8" s="8">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="L8" s="8">
         <v>0</v>
       </c>
       <c r="M8" s="8">
         <f t="shared" si="0"/>
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="N8" s="8">
-        <f>_xlfn.XLOOKUP(C8,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>900</v>
+        <v>873</v>
       </c>
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
@@ -7626,7 +4806,7 @@
         <v>12</v>
       </c>
       <c r="I9" s="8">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="J9" s="8">
         <v>0</v>
@@ -7639,11 +4819,10 @@
       </c>
       <c r="M9" s="8">
         <f t="shared" si="0"/>
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="N9" s="8">
-        <f>_xlfn.XLOOKUP(C9,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>667</v>
+        <v>649</v>
       </c>
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
@@ -7678,24 +4857,23 @@
         <v>12</v>
       </c>
       <c r="I10" s="8">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J10" s="8">
         <v>0</v>
       </c>
       <c r="K10" s="8">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L10" s="8">
         <v>0</v>
       </c>
       <c r="M10" s="8">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="N10" s="8">
-        <f>_xlfn.XLOOKUP(C10,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>638</v>
+        <v>621</v>
       </c>
       <c r="O10" s="8"/>
       <c r="P10" s="8"/>
@@ -7730,24 +4908,23 @@
         <v>12</v>
       </c>
       <c r="I11" s="8">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="J11" s="8">
         <v>0</v>
       </c>
       <c r="K11" s="8">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="L11" s="8">
         <v>0</v>
       </c>
       <c r="M11" s="8">
         <f t="shared" si="0"/>
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="N11" s="8">
-        <f>_xlfn.XLOOKUP(C11,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>526</v>
+        <v>477</v>
       </c>
       <c r="O11" s="8"/>
       <c r="P11" s="8"/>
@@ -7788,18 +4965,17 @@
         <v>0</v>
       </c>
       <c r="K12" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L12" s="8">
         <v>0</v>
       </c>
       <c r="M12" s="8">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="N12" s="8">
-        <f>_xlfn.XLOOKUP(C12,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>774</v>
+        <v>1190</v>
       </c>
       <c r="O12" s="8"/>
       <c r="P12" s="8"/>
@@ -7834,7 +5010,7 @@
         <v>12</v>
       </c>
       <c r="I13" s="8">
-        <v>240</v>
+        <v>208</v>
       </c>
       <c r="J13" s="8">
         <v>0</v>
@@ -7847,11 +5023,10 @@
       </c>
       <c r="M13" s="8">
         <f t="shared" si="0"/>
-        <v>240</v>
+        <v>208</v>
       </c>
       <c r="N13" s="8">
-        <f>_xlfn.XLOOKUP(C13,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="O13" s="8"/>
       <c r="P13" s="8"/>
@@ -7886,24 +5061,23 @@
         <v>12</v>
       </c>
       <c r="I14" s="8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J14" s="8">
         <v>0</v>
       </c>
       <c r="K14" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L14" s="8">
         <v>0</v>
       </c>
       <c r="M14" s="8">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N14" s="8">
-        <f>_xlfn.XLOOKUP(C14,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>1416</v>
+        <v>1401</v>
       </c>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
@@ -7944,18 +5118,17 @@
         <v>0</v>
       </c>
       <c r="K15" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L15" s="8">
         <v>0</v>
       </c>
       <c r="M15" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N15" s="8">
-        <f>_xlfn.XLOOKUP(C15,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>7</v>
+        <v>318</v>
       </c>
       <c r="O15" s="8"/>
       <c r="P15" s="8"/>
@@ -7996,18 +5169,17 @@
         <v>0</v>
       </c>
       <c r="K16" s="8">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L16" s="8">
         <v>0</v>
       </c>
       <c r="M16" s="8">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="N16" s="8">
-        <f>_xlfn.XLOOKUP(C16,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>764</v>
+        <v>731</v>
       </c>
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
@@ -8042,7 +5214,7 @@
         <v>12</v>
       </c>
       <c r="I17" s="8">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J17" s="8">
         <v>0</v>
@@ -8055,11 +5227,10 @@
       </c>
       <c r="M17" s="8">
         <f t="shared" si="0"/>
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N17" s="8">
-        <f>_xlfn.XLOOKUP(C17,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="O17" s="8"/>
       <c r="P17" s="8"/>
@@ -8110,8 +5281,7 @@
         <v>39</v>
       </c>
       <c r="N18" s="8">
-        <f>_xlfn.XLOOKUP(C18,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>535</v>
+        <v>825</v>
       </c>
       <c r="O18" s="8"/>
       <c r="P18" s="8"/>
@@ -8146,7 +5316,7 @@
         <v>13</v>
       </c>
       <c r="I19" s="8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J19" s="8">
         <v>0</v>
@@ -8159,11 +5329,10 @@
       </c>
       <c r="M19" s="8">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N19" s="8">
-        <f>_xlfn.XLOOKUP(C19,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>892</v>
+        <v>843</v>
       </c>
       <c r="O19" s="8"/>
       <c r="P19" s="8"/>
@@ -8198,24 +5367,23 @@
         <v>14</v>
       </c>
       <c r="I20" s="8">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J20" s="8">
         <v>0</v>
       </c>
       <c r="K20" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L20" s="8">
         <v>0</v>
       </c>
       <c r="M20" s="8">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N20" s="8">
-        <f>_xlfn.XLOOKUP(C20,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O20" s="8"/>
       <c r="P20" s="8"/>
@@ -8250,24 +5418,23 @@
         <v>13</v>
       </c>
       <c r="I21" s="8">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J21" s="8">
         <v>0</v>
       </c>
       <c r="K21" s="8">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L21" s="8">
         <v>0</v>
       </c>
       <c r="M21" s="8">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="N21" s="8">
-        <f>_xlfn.XLOOKUP(C21,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>187</v>
+        <v>381</v>
       </c>
       <c r="O21" s="8"/>
       <c r="P21" s="8"/>
@@ -8318,7 +5485,6 @@
         <v>1</v>
       </c>
       <c r="N22" s="8">
-        <f>_xlfn.XLOOKUP(C22,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O22" s="8"/>
@@ -8354,7 +5520,7 @@
         <v>12</v>
       </c>
       <c r="I23" s="8">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="J23" s="8">
         <v>0</v>
@@ -8367,11 +5533,10 @@
       </c>
       <c r="M23" s="8">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="N23" s="8">
-        <f>_xlfn.XLOOKUP(C23,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>449</v>
+        <v>407</v>
       </c>
       <c r="O23" s="8"/>
       <c r="P23" s="8"/>
@@ -8406,7 +5571,7 @@
         <v>14</v>
       </c>
       <c r="I24" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J24" s="8">
         <v>0</v>
@@ -8419,11 +5584,10 @@
       </c>
       <c r="M24" s="8">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N24" s="8">
-        <f>_xlfn.XLOOKUP(C24,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="O24" s="8"/>
       <c r="P24" s="8"/>
@@ -8515,18 +5679,17 @@
         <v>0</v>
       </c>
       <c r="K26" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" s="8">
         <v>0</v>
       </c>
       <c r="M26" s="8">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N26" s="8">
-        <f>_xlfn.XLOOKUP(C26,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>1283</v>
+        <v>1263</v>
       </c>
       <c r="O26" s="8"/>
       <c r="P26" s="8"/>
@@ -8561,24 +5724,23 @@
         <v>12</v>
       </c>
       <c r="I27" s="8">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J27" s="8">
         <v>0</v>
       </c>
       <c r="K27" s="8">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="L27" s="8">
         <v>0</v>
       </c>
       <c r="M27" s="8">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="N27" s="8">
-        <f>_xlfn.XLOOKUP(C27,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>953</v>
+        <v>943</v>
       </c>
       <c r="O27" s="8"/>
       <c r="P27" s="8"/>
@@ -8613,7 +5775,7 @@
         <v>12</v>
       </c>
       <c r="I28" s="8">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="J28" s="8">
         <v>0</v>
@@ -8626,10 +5788,9 @@
       </c>
       <c r="M28" s="8">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="N28" s="8">
-        <f>_xlfn.XLOOKUP(C28,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O28" s="8"/>
@@ -8665,7 +5826,7 @@
         <v>13</v>
       </c>
       <c r="I29" s="8">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J29" s="8">
         <v>0</v>
@@ -8678,11 +5839,10 @@
       </c>
       <c r="M29" s="8">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="N29" s="8">
-        <f>_xlfn.XLOOKUP(C29,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="O29" s="8"/>
       <c r="P29" s="8"/>
@@ -8733,8 +5893,7 @@
         <v>14</v>
       </c>
       <c r="N30" s="8">
-        <f>_xlfn.XLOOKUP(C30,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>1223</v>
+        <v>1215</v>
       </c>
       <c r="O30" s="8"/>
       <c r="P30" s="8"/>
@@ -8785,7 +5944,6 @@
         <v>1</v>
       </c>
       <c r="N31" s="8">
-        <f>_xlfn.XLOOKUP(C31,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O31" s="8"/>
@@ -8827,18 +5985,17 @@
         <v>0</v>
       </c>
       <c r="K32" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L32" s="8">
         <v>0</v>
       </c>
       <c r="M32" s="8">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N32" s="8">
-        <f>_xlfn.XLOOKUP(C32,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>863</v>
+        <v>852</v>
       </c>
       <c r="O32" s="8"/>
       <c r="P32" s="8"/>
@@ -8873,7 +6030,7 @@
         <v>12</v>
       </c>
       <c r="I33" s="8">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J33" s="8">
         <v>0</v>
@@ -8886,11 +6043,10 @@
       </c>
       <c r="M33" s="8">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="N33" s="8">
-        <f>_xlfn.XLOOKUP(C33,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>474</v>
+        <v>455</v>
       </c>
       <c r="O33" s="8"/>
       <c r="P33" s="8"/>
@@ -8925,13 +6081,13 @@
         <v>12</v>
       </c>
       <c r="I34" s="8">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J34" s="8">
         <v>0</v>
       </c>
       <c r="K34" s="8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L34" s="8">
         <v>0</v>
@@ -8941,8 +6097,7 @@
         <v>23</v>
       </c>
       <c r="N34" s="8">
-        <f>_xlfn.XLOOKUP(C34,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>1110</v>
+        <v>1102</v>
       </c>
       <c r="O34" s="8"/>
       <c r="P34" s="8"/>
@@ -8993,8 +6148,7 @@
         <v>17</v>
       </c>
       <c r="N35" s="8">
-        <f>_xlfn.XLOOKUP(C35,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O35" s="8"/>
       <c r="P35" s="8"/>
@@ -9045,8 +6199,7 @@
         <v>15</v>
       </c>
       <c r="N36" s="8">
-        <f>_xlfn.XLOOKUP(C36,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="O36" s="8"/>
       <c r="P36" s="8"/>
@@ -9081,7 +6234,7 @@
         <v>13</v>
       </c>
       <c r="I37" s="8">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J37" s="8">
         <v>0</v>
@@ -9094,11 +6247,10 @@
       </c>
       <c r="M37" s="8">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N37" s="8">
-        <f>_xlfn.XLOOKUP(C37,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>269</v>
+        <v>484</v>
       </c>
       <c r="O37" s="8"/>
       <c r="P37" s="8"/>
@@ -9149,8 +6301,7 @@
         <v>18</v>
       </c>
       <c r="N38" s="8">
-        <f>_xlfn.XLOOKUP(C38,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="O38" s="8"/>
       <c r="P38" s="8"/>
@@ -9191,18 +6342,17 @@
         <v>0</v>
       </c>
       <c r="K39" s="8">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L39" s="8">
         <v>0</v>
       </c>
       <c r="M39" s="8">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="N39" s="8">
-        <f>_xlfn.XLOOKUP(C39,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>2080</v>
+        <v>2048</v>
       </c>
       <c r="O39" s="8"/>
       <c r="P39" s="8"/>
@@ -9237,7 +6387,7 @@
         <v>12</v>
       </c>
       <c r="I40" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J40" s="8">
         <v>0</v>
@@ -9250,11 +6400,10 @@
       </c>
       <c r="M40" s="8">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N40" s="8">
-        <f>_xlfn.XLOOKUP(C40,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="O40" s="8"/>
       <c r="P40" s="8"/>
@@ -9289,24 +6438,23 @@
         <v>12</v>
       </c>
       <c r="I41" s="8">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J41" s="8">
         <v>0</v>
       </c>
       <c r="K41" s="8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L41" s="8">
         <v>0</v>
       </c>
       <c r="M41" s="8">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N41" s="8">
-        <f>_xlfn.XLOOKUP(C41,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="O41" s="8"/>
       <c r="P41" s="8"/>
@@ -9341,24 +6489,23 @@
         <v>13</v>
       </c>
       <c r="I42" s="8">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J42" s="8">
         <v>0</v>
       </c>
       <c r="K42" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L42" s="8">
         <v>0</v>
       </c>
       <c r="M42" s="8">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N42" s="8">
-        <f>_xlfn.XLOOKUP(C42,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>921</v>
+        <v>903</v>
       </c>
       <c r="O42" s="8"/>
       <c r="P42" s="8"/>
@@ -9393,7 +6540,7 @@
         <v>12</v>
       </c>
       <c r="I43" s="8">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J43" s="8">
         <v>0</v>
@@ -9406,11 +6553,10 @@
       </c>
       <c r="M43" s="8">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N43" s="8">
-        <f>_xlfn.XLOOKUP(C43,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="O43" s="8"/>
       <c r="P43" s="8"/>
@@ -9445,13 +6591,13 @@
         <v>12</v>
       </c>
       <c r="I44" s="8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J44" s="8">
         <v>0</v>
       </c>
       <c r="K44" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L44" s="8">
         <v>0</v>
@@ -9461,8 +6607,7 @@
         <v>11</v>
       </c>
       <c r="N44" s="8">
-        <f>_xlfn.XLOOKUP(C44,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>577</v>
+        <v>555</v>
       </c>
       <c r="O44" s="8"/>
       <c r="P44" s="8"/>
@@ -9497,13 +6642,13 @@
         <v>12</v>
       </c>
       <c r="I45" s="8">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J45" s="8">
         <v>0</v>
       </c>
       <c r="K45" s="8">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L45" s="8">
         <v>0</v>
@@ -9513,8 +6658,7 @@
         <v>15</v>
       </c>
       <c r="N45" s="8">
-        <f>_xlfn.XLOOKUP(C45,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>934</v>
+        <v>925</v>
       </c>
       <c r="O45" s="8"/>
       <c r="P45" s="8"/>
@@ -9549,24 +6693,23 @@
         <v>12</v>
       </c>
       <c r="I46" s="8">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J46" s="8">
         <v>0</v>
       </c>
       <c r="K46" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L46" s="8">
         <v>0</v>
       </c>
       <c r="M46" s="8">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N46" s="8">
-        <f>_xlfn.XLOOKUP(C46,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="O46" s="8"/>
       <c r="P46" s="8"/>
@@ -9601,7 +6744,7 @@
         <v>13</v>
       </c>
       <c r="I47" s="8">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J47" s="8">
         <v>0</v>
@@ -9614,11 +6757,10 @@
       </c>
       <c r="M47" s="8">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N47" s="8">
-        <f>_xlfn.XLOOKUP(C47,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>149</v>
+        <v>437</v>
       </c>
       <c r="O47" s="8"/>
       <c r="P47" s="8"/>
@@ -9669,8 +6811,7 @@
         <v>20</v>
       </c>
       <c r="N48" s="8">
-        <f>_xlfn.XLOOKUP(C48,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>1210</v>
+        <v>1201</v>
       </c>
       <c r="O48" s="8"/>
       <c r="P48" s="8"/>
@@ -9721,8 +6862,7 @@
         <v>15</v>
       </c>
       <c r="N49" s="8">
-        <f>_xlfn.XLOOKUP(C49,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>828</v>
+        <v>1084</v>
       </c>
       <c r="O49" s="8"/>
       <c r="P49" s="8"/>
@@ -9773,7 +6913,6 @@
         <v>9</v>
       </c>
       <c r="N50" s="8">
-        <f>_xlfn.XLOOKUP(C50,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>159</v>
       </c>
       <c r="O50" s="8"/>
@@ -9809,13 +6948,13 @@
         <v>12</v>
       </c>
       <c r="I51" s="8">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J51" s="8">
         <v>0</v>
       </c>
       <c r="K51" s="8">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L51" s="8">
         <v>0</v>
@@ -9825,8 +6964,7 @@
         <v>24</v>
       </c>
       <c r="N51" s="8">
-        <f>_xlfn.XLOOKUP(C51,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>503</v>
+        <v>492</v>
       </c>
       <c r="O51" s="8"/>
       <c r="P51" s="8"/>
@@ -9861,24 +6999,23 @@
         <v>12</v>
       </c>
       <c r="I52" s="8">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J52" s="8">
         <v>0</v>
       </c>
       <c r="K52" s="8">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L52" s="8">
         <v>0</v>
       </c>
       <c r="M52" s="8">
         <f t="shared" si="0"/>
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="N52" s="8">
-        <f>_xlfn.XLOOKUP(C52,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>1463</v>
+        <v>1343</v>
       </c>
       <c r="O52" s="8"/>
       <c r="P52" s="8"/>
@@ -9913,7 +7050,7 @@
         <v>12</v>
       </c>
       <c r="I53" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J53" s="8">
         <v>0</v>
@@ -9926,11 +7063,10 @@
       </c>
       <c r="M53" s="8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N53" s="8">
-        <f>_xlfn.XLOOKUP(C53,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="O53" s="8"/>
       <c r="P53" s="8"/>
@@ -9981,8 +7117,7 @@
         <v>11</v>
       </c>
       <c r="N54" s="8">
-        <f>_xlfn.XLOOKUP(C54,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>663</v>
+        <v>652</v>
       </c>
       <c r="O54" s="8"/>
       <c r="P54" s="8"/>
@@ -10017,24 +7152,23 @@
         <v>12</v>
       </c>
       <c r="I55" s="8">
+        <v>30</v>
+      </c>
+      <c r="J55" s="8">
+        <v>0</v>
+      </c>
+      <c r="K55" s="8">
         <v>27</v>
-      </c>
-      <c r="J55" s="8">
-        <v>0</v>
-      </c>
-      <c r="K55" s="8">
-        <v>9</v>
       </c>
       <c r="L55" s="8">
         <v>0</v>
       </c>
       <c r="M55" s="8">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="N55" s="8">
-        <f>_xlfn.XLOOKUP(C55,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>427</v>
+        <v>326</v>
       </c>
       <c r="O55" s="8"/>
       <c r="P55" s="8"/>
@@ -10085,8 +7219,7 @@
         <v>7</v>
       </c>
       <c r="N56" s="8">
-        <f>_xlfn.XLOOKUP(C56,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O56" s="8"/>
       <c r="P56" s="8"/>
@@ -10121,7 +7254,7 @@
         <v>12</v>
       </c>
       <c r="I57" s="8">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J57" s="8">
         <v>0</v>
@@ -10134,11 +7267,10 @@
       </c>
       <c r="M57" s="8">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N57" s="8">
-        <f>_xlfn.XLOOKUP(C57,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="O57" s="8"/>
       <c r="P57" s="8"/>
@@ -10189,8 +7321,7 @@
         <v>6</v>
       </c>
       <c r="N58" s="8">
-        <f>_xlfn.XLOOKUP(C58,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="O58" s="8"/>
       <c r="P58" s="8"/>
@@ -10241,7 +7372,6 @@
         <v>9</v>
       </c>
       <c r="N59" s="8">
-        <f>_xlfn.XLOOKUP(C59,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>69</v>
       </c>
       <c r="O59" s="8"/>
@@ -10293,8 +7423,7 @@
         <v>5</v>
       </c>
       <c r="N60" s="8">
-        <f>_xlfn.XLOOKUP(C60,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>797</v>
+        <v>781</v>
       </c>
       <c r="O60" s="8"/>
       <c r="P60" s="8"/>
@@ -10329,24 +7458,23 @@
         <v>12</v>
       </c>
       <c r="I61" s="8">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="J61" s="8">
         <v>0</v>
       </c>
       <c r="K61" s="8">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L61" s="8">
         <v>0</v>
       </c>
       <c r="M61" s="8">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N61" s="8">
-        <f>_xlfn.XLOOKUP(C61,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>954</v>
+        <v>919</v>
       </c>
       <c r="O61" s="8"/>
       <c r="P61" s="8"/>
@@ -10381,7 +7509,7 @@
         <v>12</v>
       </c>
       <c r="I62" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J62" s="8">
         <v>0</v>
@@ -10394,11 +7522,10 @@
       </c>
       <c r="M62" s="8">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N62" s="8">
-        <f>_xlfn.XLOOKUP(C62,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="O62" s="8"/>
       <c r="P62" s="8"/>
@@ -10433,13 +7560,13 @@
         <v>12</v>
       </c>
       <c r="I63" s="8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J63" s="8">
         <v>0</v>
       </c>
       <c r="K63" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L63" s="8">
         <v>0</v>
@@ -10449,8 +7576,7 @@
         <v>7</v>
       </c>
       <c r="N63" s="8">
-        <f>_xlfn.XLOOKUP(C63,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="O63" s="8"/>
       <c r="P63" s="8"/>
@@ -10501,8 +7627,7 @@
         <v>12</v>
       </c>
       <c r="N64" s="8">
-        <f>_xlfn.XLOOKUP(C64,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="O64" s="8"/>
       <c r="P64" s="8"/>
@@ -10537,7 +7662,7 @@
         <v>12</v>
       </c>
       <c r="I65" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J65" s="8">
         <v>0</v>
@@ -10550,11 +7675,10 @@
       </c>
       <c r="M65" s="8">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N65" s="8">
-        <f>_xlfn.XLOOKUP(C65,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="O65" s="8"/>
       <c r="P65" s="8"/>
@@ -10605,7 +7729,6 @@
         <v>4</v>
       </c>
       <c r="N66" s="8">
-        <f>_xlfn.XLOOKUP(C66,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>276</v>
       </c>
       <c r="O66" s="8"/>
@@ -10641,7 +7764,7 @@
         <v>12</v>
       </c>
       <c r="I67" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J67" s="8">
         <v>0</v>
@@ -10654,11 +7777,10 @@
       </c>
       <c r="M67" s="8">
         <f t="shared" ref="M67:M130" si="1">I67+J67+K67+L67</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N67" s="8">
-        <f>_xlfn.XLOOKUP(C67,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>437</v>
+        <v>409</v>
       </c>
       <c r="O67" s="8"/>
       <c r="P67" s="8"/>
@@ -10693,7 +7815,7 @@
         <v>12</v>
       </c>
       <c r="I68" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J68" s="8">
         <v>0</v>
@@ -10706,11 +7828,10 @@
       </c>
       <c r="M68" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N68" s="8">
-        <f>_xlfn.XLOOKUP(C68,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>1019</v>
+        <v>1013</v>
       </c>
       <c r="O68" s="8"/>
       <c r="P68" s="8"/>
@@ -10751,18 +7872,17 @@
         <v>0</v>
       </c>
       <c r="K69" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" s="8">
         <v>0</v>
       </c>
       <c r="M69" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N69" s="8">
-        <f>_xlfn.XLOOKUP(C69,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="O69" s="8"/>
       <c r="P69" s="8"/>
@@ -10813,8 +7933,7 @@
         <v>4</v>
       </c>
       <c r="N70" s="8">
-        <f>_xlfn.XLOOKUP(C70,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="O70" s="8"/>
       <c r="P70" s="8"/>
@@ -10849,7 +7968,7 @@
         <v>12</v>
       </c>
       <c r="I71" s="8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J71" s="8">
         <v>0</v>
@@ -10862,11 +7981,10 @@
       </c>
       <c r="M71" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N71" s="8">
-        <f>_xlfn.XLOOKUP(C71,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>1</v>
+        <v>113</v>
       </c>
       <c r="O71" s="8"/>
       <c r="P71" s="8"/>
@@ -10901,7 +8019,7 @@
         <v>12</v>
       </c>
       <c r="I72" s="8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J72" s="8">
         <v>0</v>
@@ -10914,11 +8032,10 @@
       </c>
       <c r="M72" s="8">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N72" s="8">
-        <f>_xlfn.XLOOKUP(C72,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="O72" s="8"/>
       <c r="P72" s="8"/>
@@ -10953,24 +8070,23 @@
         <v>12</v>
       </c>
       <c r="I73" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J73" s="8">
         <v>0</v>
       </c>
       <c r="K73" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L73" s="8">
         <v>0</v>
       </c>
       <c r="M73" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N73" s="8">
-        <f>_xlfn.XLOOKUP(C73,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>998</v>
+        <v>985</v>
       </c>
       <c r="O73" s="8"/>
       <c r="P73" s="8"/>
@@ -11005,13 +8121,13 @@
         <v>14</v>
       </c>
       <c r="I74" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J74" s="8">
         <v>0</v>
       </c>
       <c r="K74" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L74" s="8">
         <v>0</v>
@@ -11021,8 +8137,7 @@
         <v>4</v>
       </c>
       <c r="N74" s="8">
-        <f>_xlfn.XLOOKUP(C74,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>354</v>
+        <v>326</v>
       </c>
       <c r="O74" s="8"/>
       <c r="P74" s="8"/>
@@ -11073,7 +8188,6 @@
         <v>8</v>
       </c>
       <c r="N75" s="8">
-        <f>_xlfn.XLOOKUP(C75,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>39</v>
       </c>
       <c r="O75" s="8"/>
@@ -11125,8 +8239,7 @@
         <v>7</v>
       </c>
       <c r="N76" s="8">
-        <f>_xlfn.XLOOKUP(C76,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="O76" s="8"/>
       <c r="P76" s="8"/>
@@ -11177,8 +8290,7 @@
         <v>5</v>
       </c>
       <c r="N77" s="8">
-        <f>_xlfn.XLOOKUP(C77,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>690</v>
+        <v>669</v>
       </c>
       <c r="O77" s="8"/>
       <c r="P77" s="8"/>
@@ -11213,24 +8325,23 @@
         <v>12</v>
       </c>
       <c r="I78" s="8">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J78" s="8">
         <v>0</v>
       </c>
       <c r="K78" s="8">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L78" s="8">
         <v>0</v>
       </c>
       <c r="M78" s="8">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N78" s="8">
-        <f>_xlfn.XLOOKUP(C78,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>751</v>
+        <v>742</v>
       </c>
       <c r="O78" s="8"/>
       <c r="P78" s="8"/>
@@ -11265,7 +8376,7 @@
         <v>13</v>
       </c>
       <c r="I79" s="8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J79" s="8">
         <v>0</v>
@@ -11278,11 +8389,10 @@
       </c>
       <c r="M79" s="8">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N79" s="8">
-        <f>_xlfn.XLOOKUP(C79,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="O79" s="8"/>
       <c r="P79" s="8"/>
@@ -11333,7 +8443,6 @@
         <v>6</v>
       </c>
       <c r="N80" s="8">
-        <f>_xlfn.XLOOKUP(C80,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O80" s="8"/>
@@ -11385,7 +8494,6 @@
         <v>1</v>
       </c>
       <c r="N81" s="8">
-        <f>_xlfn.XLOOKUP(C81,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O81" s="8"/>
@@ -11421,7 +8529,7 @@
         <v>15</v>
       </c>
       <c r="I82" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J82" s="8">
         <v>0</v>
@@ -11434,11 +8542,10 @@
       </c>
       <c r="M82" s="8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N82" s="8">
-        <f>_xlfn.XLOOKUP(C82,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="O82" s="8"/>
       <c r="P82" s="8"/>
@@ -11489,8 +8596,7 @@
         <v>6</v>
       </c>
       <c r="N83" s="8">
-        <f>_xlfn.XLOOKUP(C83,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="O83" s="8"/>
       <c r="P83" s="8"/>
@@ -11541,8 +8647,7 @@
         <v>1</v>
       </c>
       <c r="N84" s="8">
-        <f>_xlfn.XLOOKUP(C84,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O84" s="8"/>
       <c r="P84" s="8"/>
@@ -11577,7 +8682,7 @@
         <v>14</v>
       </c>
       <c r="I85" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J85" s="8">
         <v>0</v>
@@ -11590,11 +8695,10 @@
       </c>
       <c r="M85" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N85" s="8">
-        <f>_xlfn.XLOOKUP(C85,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>594</v>
+        <v>554</v>
       </c>
       <c r="O85" s="8"/>
       <c r="P85" s="8"/>
@@ -11629,7 +8733,7 @@
         <v>12</v>
       </c>
       <c r="I86" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J86" s="8">
         <v>0</v>
@@ -11642,11 +8746,10 @@
       </c>
       <c r="M86" s="8">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N86" s="8">
-        <f>_xlfn.XLOOKUP(C86,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="O86" s="8"/>
       <c r="P86" s="8"/>
@@ -11681,7 +8784,7 @@
         <v>13</v>
       </c>
       <c r="I87" s="8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J87" s="8">
         <v>0</v>
@@ -11694,10 +8797,9 @@
       </c>
       <c r="M87" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N87" s="8">
-        <f>_xlfn.XLOOKUP(C87,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>14</v>
       </c>
       <c r="O87" s="8"/>
@@ -11733,7 +8835,7 @@
         <v>12</v>
       </c>
       <c r="I88" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J88" s="8">
         <v>0</v>
@@ -11746,10 +8848,9 @@
       </c>
       <c r="M88" s="8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N88" s="8">
-        <f>_xlfn.XLOOKUP(C88,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>265</v>
       </c>
       <c r="O88" s="8"/>
@@ -11785,24 +8886,23 @@
         <v>12</v>
       </c>
       <c r="I89" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J89" s="8">
         <v>0</v>
       </c>
       <c r="K89" s="8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L89" s="8">
         <v>0</v>
       </c>
       <c r="M89" s="8">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N89" s="8">
-        <f>_xlfn.XLOOKUP(C89,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="O89" s="8"/>
       <c r="P89" s="8"/>
@@ -11853,7 +8953,6 @@
         <v>7</v>
       </c>
       <c r="N90" s="8">
-        <f>_xlfn.XLOOKUP(C90,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>83</v>
       </c>
       <c r="O90" s="8"/>
@@ -11905,8 +9004,7 @@
         <v>6</v>
       </c>
       <c r="N91" s="8">
-        <f>_xlfn.XLOOKUP(C91,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>1319</v>
+        <v>1307</v>
       </c>
       <c r="O91" s="8"/>
       <c r="P91" s="8"/>
@@ -11941,7 +9039,7 @@
         <v>12</v>
       </c>
       <c r="I92" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J92" s="8">
         <v>0</v>
@@ -11954,11 +9052,10 @@
       </c>
       <c r="M92" s="8">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N92" s="8">
-        <f>_xlfn.XLOOKUP(C92,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="O92" s="8"/>
       <c r="P92" s="8"/>
@@ -11993,24 +9090,23 @@
         <v>13</v>
       </c>
       <c r="I93" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J93" s="8">
         <v>0</v>
       </c>
       <c r="K93" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="8">
         <v>0</v>
       </c>
       <c r="M93" s="8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N93" s="8">
-        <f>_xlfn.XLOOKUP(C93,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O93" s="8"/>
       <c r="P93" s="8"/>
@@ -12045,7 +9141,7 @@
         <v>12</v>
       </c>
       <c r="I94" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J94" s="8">
         <v>0</v>
@@ -12058,10 +9154,9 @@
       </c>
       <c r="M94" s="8">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N94" s="8">
-        <f>_xlfn.XLOOKUP(C94,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O94" s="8"/>
@@ -12113,8 +9208,7 @@
         <v>9</v>
       </c>
       <c r="N95" s="8">
-        <f>_xlfn.XLOOKUP(C95,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="O95" s="8"/>
       <c r="P95" s="8"/>
@@ -12149,7 +9243,7 @@
         <v>13</v>
       </c>
       <c r="I96" s="8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J96" s="8">
         <v>0</v>
@@ -12162,10 +9256,9 @@
       </c>
       <c r="M96" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N96" s="8">
-        <f>_xlfn.XLOOKUP(C96,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>130</v>
       </c>
       <c r="O96" s="8"/>
@@ -12201,7 +9294,7 @@
         <v>14</v>
       </c>
       <c r="I97" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J97" s="8">
         <v>0</v>
@@ -12214,11 +9307,10 @@
       </c>
       <c r="M97" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N97" s="8">
-        <f>_xlfn.XLOOKUP(C97,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>140</v>
+        <v>349</v>
       </c>
       <c r="O97" s="8"/>
       <c r="P97" s="8"/>
@@ -12269,7 +9361,6 @@
         <v>5</v>
       </c>
       <c r="N98" s="8">
-        <f>_xlfn.XLOOKUP(C98,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O98" s="8"/>
@@ -12321,7 +9412,7 @@
         <v>0</v>
       </c>
       <c r="N99" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O99" s="8"/>
       <c r="P99" s="8"/>
@@ -12372,8 +9463,7 @@
         <v>10</v>
       </c>
       <c r="N100" s="8">
-        <f>_xlfn.XLOOKUP(C100,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O100" s="8"/>
       <c r="P100" s="8"/>
@@ -12424,7 +9514,6 @@
         <v>3</v>
       </c>
       <c r="N101" s="8">
-        <f>_xlfn.XLOOKUP(C101,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>352</v>
       </c>
       <c r="O101" s="8"/>
@@ -12460,24 +9549,23 @@
         <v>14</v>
       </c>
       <c r="I102" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J102" s="8">
         <v>0</v>
       </c>
       <c r="K102" s="8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L102" s="8">
         <v>0</v>
       </c>
       <c r="M102" s="8">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N102" s="8">
-        <f>_xlfn.XLOOKUP(C102,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>645</v>
+        <v>582</v>
       </c>
       <c r="O102" s="8"/>
       <c r="P102" s="8"/>
@@ -12528,8 +9616,7 @@
         <v>4</v>
       </c>
       <c r="N103" s="8">
-        <f>_xlfn.XLOOKUP(C103,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="O103" s="8"/>
       <c r="P103" s="8"/>
@@ -12615,13 +9702,13 @@
         <v>12</v>
       </c>
       <c r="I105" s="8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J105" s="8">
         <v>0</v>
       </c>
       <c r="K105" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L105" s="8">
         <v>0</v>
@@ -12631,8 +9718,7 @@
         <v>8</v>
       </c>
       <c r="N105" s="8">
-        <f>_xlfn.XLOOKUP(C105,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="O105" s="8"/>
       <c r="P105" s="8"/>
@@ -12683,8 +9769,7 @@
         <v>6</v>
       </c>
       <c r="N106" s="8">
-        <f>_xlfn.XLOOKUP(C106,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O106" s="8"/>
       <c r="P106" s="8"/>
@@ -12735,8 +9820,7 @@
         <v>4</v>
       </c>
       <c r="N107" s="8">
-        <f>_xlfn.XLOOKUP(C107,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="O107" s="8"/>
       <c r="P107" s="8"/>
@@ -12787,7 +9871,6 @@
         <v>1</v>
       </c>
       <c r="N108" s="8">
-        <f>_xlfn.XLOOKUP(C108,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O108" s="8"/>
@@ -12823,24 +9906,23 @@
         <v>13</v>
       </c>
       <c r="I109" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J109" s="8">
         <v>0</v>
       </c>
       <c r="K109" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L109" s="8">
         <v>0</v>
       </c>
       <c r="M109" s="8">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N109" s="8">
-        <f>_xlfn.XLOOKUP(C109,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="O109" s="8"/>
       <c r="P109" s="8"/>
@@ -12875,24 +9957,23 @@
         <v>13</v>
       </c>
       <c r="I110" s="8">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J110" s="8">
         <v>0</v>
       </c>
       <c r="K110" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L110" s="8">
         <v>0</v>
       </c>
       <c r="M110" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="N110" s="8">
-        <f>_xlfn.XLOOKUP(C110,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="O110" s="8"/>
       <c r="P110" s="8"/>
@@ -12927,7 +10008,7 @@
         <v>13</v>
       </c>
       <c r="I111" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J111" s="8">
         <v>0</v>
@@ -12940,10 +10021,9 @@
       </c>
       <c r="M111" s="8">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N111" s="8">
-        <f>_xlfn.XLOOKUP(C111,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O111" s="8"/>
@@ -12985,18 +10065,17 @@
         <v>0</v>
       </c>
       <c r="K112" s="8">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="L112" s="8">
         <v>0</v>
       </c>
       <c r="M112" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>145</v>
       </c>
       <c r="N112" s="8">
-        <f>_xlfn.XLOOKUP(C112,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>288</v>
+        <v>781</v>
       </c>
       <c r="O112" s="8"/>
       <c r="P112" s="8"/>
@@ -13031,24 +10110,23 @@
         <v>12</v>
       </c>
       <c r="I113" s="8">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J113" s="8">
         <v>0</v>
       </c>
       <c r="K113" s="8">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="L113" s="8">
         <v>0</v>
       </c>
       <c r="M113" s="8">
         <f t="shared" si="1"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N113" s="8">
-        <f>_xlfn.XLOOKUP(C113,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>1356</v>
+        <v>1351</v>
       </c>
       <c r="O113" s="8"/>
       <c r="P113" s="8"/>
@@ -13083,7 +10161,7 @@
         <v>13</v>
       </c>
       <c r="I114" s="8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J114" s="8">
         <v>0</v>
@@ -13096,11 +10174,10 @@
       </c>
       <c r="M114" s="8">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N114" s="8">
-        <f>_xlfn.XLOOKUP(C114,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>910</v>
+        <v>923</v>
       </c>
       <c r="O114" s="8"/>
       <c r="P114" s="8"/>
@@ -13151,8 +10228,7 @@
         <v>12</v>
       </c>
       <c r="N115" s="8">
-        <f>_xlfn.XLOOKUP(C115,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>297</v>
+        <v>370</v>
       </c>
       <c r="O115" s="8"/>
       <c r="P115" s="8"/>
@@ -13187,7 +10263,7 @@
         <v>12</v>
       </c>
       <c r="I116" s="8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J116" s="8">
         <v>0</v>
@@ -13200,11 +10276,10 @@
       </c>
       <c r="M116" s="8">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N116" s="8">
-        <f>_xlfn.XLOOKUP(C116,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>892</v>
+        <v>884</v>
       </c>
       <c r="O116" s="8"/>
       <c r="P116" s="8"/>
@@ -13239,24 +10314,23 @@
         <v>12</v>
       </c>
       <c r="I117" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J117" s="8">
         <v>0</v>
       </c>
       <c r="K117" s="8">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L117" s="8">
         <v>0</v>
       </c>
       <c r="M117" s="8">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="N117" s="8">
-        <f>_xlfn.XLOOKUP(C117,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>647</v>
+        <v>612</v>
       </c>
       <c r="O117" s="8"/>
       <c r="P117" s="8"/>
@@ -13307,7 +10381,6 @@
         <v>7</v>
       </c>
       <c r="N118" s="8">
-        <f>_xlfn.XLOOKUP(C118,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>125</v>
       </c>
       <c r="O118" s="8"/>
@@ -13359,8 +10432,7 @@
         <v>11</v>
       </c>
       <c r="N119" s="8">
-        <f>_xlfn.XLOOKUP(C119,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>310</v>
+        <v>594</v>
       </c>
       <c r="O119" s="8"/>
       <c r="P119" s="8"/>
@@ -13395,7 +10467,7 @@
         <v>14</v>
       </c>
       <c r="I120" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J120" s="8">
         <v>0</v>
@@ -13408,11 +10480,10 @@
       </c>
       <c r="M120" s="8">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N120" s="8">
-        <f>_xlfn.XLOOKUP(C120,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="O120" s="8"/>
       <c r="P120" s="8"/>
@@ -13463,8 +10534,7 @@
         <v>7</v>
       </c>
       <c r="N121" s="8">
-        <f>_xlfn.XLOOKUP(C121,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="O121" s="8"/>
       <c r="P121" s="8"/>
@@ -13499,7 +10569,7 @@
         <v>13</v>
       </c>
       <c r="I122" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J122" s="8">
         <v>0</v>
@@ -13512,11 +10582,10 @@
       </c>
       <c r="M122" s="8">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N122" s="8">
-        <f>_xlfn.XLOOKUP(C122,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="O122" s="8"/>
       <c r="P122" s="8"/>
@@ -13567,8 +10636,7 @@
         <v>5</v>
       </c>
       <c r="N123" s="8">
-        <f>_xlfn.XLOOKUP(C123,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O123" s="8"/>
       <c r="P123" s="8"/>
@@ -13654,7 +10722,7 @@
         <v>13</v>
       </c>
       <c r="I125" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J125" s="8">
         <v>0</v>
@@ -13667,11 +10735,10 @@
       </c>
       <c r="M125" s="8">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N125" s="8">
-        <f>_xlfn.XLOOKUP(C125,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>349</v>
+        <v>481</v>
       </c>
       <c r="O125" s="8"/>
       <c r="P125" s="8"/>
@@ -13722,7 +10789,6 @@
         <v>6</v>
       </c>
       <c r="N126" s="8">
-        <f>_xlfn.XLOOKUP(C126,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O126" s="8"/>
@@ -13774,7 +10840,6 @@
         <v>2</v>
       </c>
       <c r="N127" s="8">
-        <f>_xlfn.XLOOKUP(C127,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O127" s="8"/>
@@ -13826,8 +10891,7 @@
         <v>4</v>
       </c>
       <c r="N128" s="8">
-        <f>_xlfn.XLOOKUP(C128,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="O128" s="8"/>
       <c r="P128" s="8"/>
@@ -13878,7 +10942,6 @@
         <v>1</v>
       </c>
       <c r="N129" s="8">
-        <f>_xlfn.XLOOKUP(C129,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O129" s="8"/>
@@ -13914,7 +10977,7 @@
         <v>12</v>
       </c>
       <c r="I130" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J130" s="8">
         <v>0</v>
@@ -13927,11 +10990,10 @@
       </c>
       <c r="M130" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N130" s="8">
-        <f>_xlfn.XLOOKUP(C130,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="O130" s="8"/>
       <c r="P130" s="8"/>
@@ -13966,7 +11028,7 @@
         <v>14</v>
       </c>
       <c r="I131" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J131" s="8">
         <v>0</v>
@@ -13979,11 +11041,10 @@
       </c>
       <c r="M131" s="8">
         <f t="shared" ref="M131:M194" si="2">I131+J131+K131+L131</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N131" s="8">
-        <f>_xlfn.XLOOKUP(C131,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>549</v>
+        <v>519</v>
       </c>
       <c r="O131" s="8"/>
       <c r="P131" s="8"/>
@@ -14034,8 +11095,7 @@
         <v>6</v>
       </c>
       <c r="N132" s="8">
-        <f>_xlfn.XLOOKUP(C132,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="O132" s="8"/>
       <c r="P132" s="8"/>
@@ -14070,24 +11130,23 @@
         <v>12</v>
       </c>
       <c r="I133" s="8">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J133" s="8">
         <v>0</v>
       </c>
       <c r="K133" s="8">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="L133" s="8">
         <v>0</v>
       </c>
       <c r="M133" s="8">
         <f t="shared" si="2"/>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N133" s="8">
-        <f>_xlfn.XLOOKUP(C133,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>1051</v>
+        <v>1015</v>
       </c>
       <c r="O133" s="8"/>
       <c r="P133" s="8"/>
@@ -14138,8 +11197,7 @@
         <v>3</v>
       </c>
       <c r="N134" s="8">
-        <f>_xlfn.XLOOKUP(C134,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O134" s="8"/>
       <c r="P134" s="8"/>
@@ -14190,8 +11248,7 @@
         <v>4</v>
       </c>
       <c r="N135" s="8">
-        <f>_xlfn.XLOOKUP(C135,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="O135" s="8"/>
       <c r="P135" s="8"/>
@@ -14232,18 +11289,17 @@
         <v>0</v>
       </c>
       <c r="K136" s="8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L136" s="8">
         <v>0</v>
       </c>
       <c r="M136" s="8">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N136" s="8">
-        <f>_xlfn.XLOOKUP(C136,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>664</v>
+        <v>630</v>
       </c>
       <c r="O136" s="8"/>
       <c r="P136" s="8"/>
@@ -14284,18 +11340,17 @@
         <v>0</v>
       </c>
       <c r="K137" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L137" s="8">
         <v>0</v>
       </c>
       <c r="M137" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N137" s="8">
-        <f>_xlfn.XLOOKUP(C137,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O137" s="8"/>
       <c r="P137" s="8"/>
@@ -14346,7 +11401,6 @@
         <v>5</v>
       </c>
       <c r="N138" s="8">
-        <f>_xlfn.XLOOKUP(C138,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>1176</v>
       </c>
       <c r="O138" s="8"/>
@@ -14398,8 +11452,7 @@
         <v>1</v>
       </c>
       <c r="N139" s="8">
-        <f>_xlfn.XLOOKUP(C139,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O139" s="8"/>
       <c r="P139" s="8"/>
@@ -14450,7 +11503,6 @@
         <v>5</v>
       </c>
       <c r="N140" s="8">
-        <f>_xlfn.XLOOKUP(C140,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>470</v>
       </c>
       <c r="O140" s="8"/>
@@ -14502,7 +11554,6 @@
         <v>0</v>
       </c>
       <c r="N141" s="8">
-        <f>_xlfn.XLOOKUP(C141,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>564</v>
       </c>
       <c r="O141" s="8"/>
@@ -14554,7 +11605,6 @@
         <v>2</v>
       </c>
       <c r="N142" s="8">
-        <f>_xlfn.XLOOKUP(C142,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O142" s="8"/>
@@ -14606,8 +11656,7 @@
         <v>3</v>
       </c>
       <c r="N143" s="8">
-        <f>_xlfn.XLOOKUP(C143,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="O143" s="8"/>
       <c r="P143" s="8"/>
@@ -14699,17 +11748,16 @@
         <v>0</v>
       </c>
       <c r="K145" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L145" s="8">
         <v>0</v>
       </c>
       <c r="M145" s="8">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N145" s="8">
-        <f>_xlfn.XLOOKUP(C145,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>899</v>
       </c>
       <c r="O145" s="8"/>
@@ -14761,7 +11809,6 @@
         <v>3</v>
       </c>
       <c r="N146" s="8">
-        <f>_xlfn.XLOOKUP(C146,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O146" s="8"/>
@@ -14813,8 +11860,7 @@
         <v>3</v>
       </c>
       <c r="N147" s="8">
-        <f>_xlfn.XLOOKUP(C147,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O147" s="8"/>
       <c r="P147" s="8"/>
@@ -14855,18 +11901,17 @@
         <v>0</v>
       </c>
       <c r="K148" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L148" s="8">
         <v>0</v>
       </c>
       <c r="M148" s="8">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N148" s="8">
-        <f>_xlfn.XLOOKUP(C148,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>377</v>
+        <v>355</v>
       </c>
       <c r="O148" s="8"/>
       <c r="P148" s="8"/>
@@ -14901,24 +11946,23 @@
         <v>12</v>
       </c>
       <c r="I149" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J149" s="8">
         <v>0</v>
       </c>
       <c r="K149" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L149" s="8">
         <v>0</v>
       </c>
       <c r="M149" s="8">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N149" s="8">
-        <f>_xlfn.XLOOKUP(C149,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="O149" s="8"/>
       <c r="P149" s="8"/>
@@ -14953,13 +11997,13 @@
         <v>12</v>
       </c>
       <c r="I150" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J150" s="8">
         <v>0</v>
       </c>
       <c r="K150" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L150" s="8">
         <v>0</v>
@@ -14969,8 +12013,7 @@
         <v>2</v>
       </c>
       <c r="N150" s="8">
-        <f>_xlfn.XLOOKUP(C150,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="O150" s="8"/>
       <c r="P150" s="8"/>
@@ -15021,8 +12064,7 @@
         <v>6</v>
       </c>
       <c r="N151" s="8">
-        <f>_xlfn.XLOOKUP(C151,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>233</v>
+        <v>211</v>
       </c>
       <c r="O151" s="8"/>
       <c r="P151" s="8"/>
@@ -15073,8 +12115,7 @@
         <v>4</v>
       </c>
       <c r="N152" s="8">
-        <f>_xlfn.XLOOKUP(C152,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="O152" s="8"/>
       <c r="P152" s="8"/>
@@ -15109,7 +12150,7 @@
         <v>13</v>
       </c>
       <c r="I153" s="8">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J153" s="8">
         <v>0</v>
@@ -15122,10 +12163,9 @@
       </c>
       <c r="M153" s="8">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="N153" s="8">
-        <f>_xlfn.XLOOKUP(C153,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>571</v>
       </c>
       <c r="O153" s="8"/>
@@ -15177,8 +12217,7 @@
         <v>5</v>
       </c>
       <c r="N154" s="8">
-        <f>_xlfn.XLOOKUP(C154,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O154" s="8"/>
       <c r="P154" s="8"/>
@@ -15229,7 +12268,6 @@
         <v>5</v>
       </c>
       <c r="N155" s="8">
-        <f>_xlfn.XLOOKUP(C155,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O155" s="8"/>
@@ -15281,7 +12319,6 @@
         <v>5</v>
       </c>
       <c r="N156" s="8">
-        <f>_xlfn.XLOOKUP(C156,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O156" s="8"/>
@@ -15333,7 +12370,6 @@
         <v>4</v>
       </c>
       <c r="N157" s="8">
-        <f>_xlfn.XLOOKUP(C157,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O157" s="8"/>
@@ -15436,7 +12472,6 @@
         <v>5</v>
       </c>
       <c r="N159" s="8">
-        <f>_xlfn.XLOOKUP(C159,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>15</v>
       </c>
       <c r="O159" s="8"/>
@@ -15488,8 +12523,7 @@
         <v>5</v>
       </c>
       <c r="N160" s="8">
-        <f>_xlfn.XLOOKUP(C160,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="O160" s="8"/>
       <c r="P160" s="8"/>
@@ -15540,8 +12574,7 @@
         <v>6</v>
       </c>
       <c r="N161" s="8">
-        <f>_xlfn.XLOOKUP(C161,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="O161" s="8"/>
       <c r="P161" s="8"/>
@@ -15576,13 +12609,13 @@
         <v>13</v>
       </c>
       <c r="I162" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J162" s="8">
         <v>0</v>
       </c>
       <c r="K162" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L162" s="8">
         <v>0</v>
@@ -15592,8 +12625,7 @@
         <v>3</v>
       </c>
       <c r="N162" s="8">
-        <f>_xlfn.XLOOKUP(C162,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="O162" s="8"/>
       <c r="P162" s="8"/>
@@ -15644,7 +12676,6 @@
         <v>4</v>
       </c>
       <c r="N163" s="8">
-        <f>_xlfn.XLOOKUP(C163,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O163" s="8"/>
@@ -15696,8 +12727,7 @@
         <v>3</v>
       </c>
       <c r="N164" s="8">
-        <f>_xlfn.XLOOKUP(C164,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="O164" s="8"/>
       <c r="P164" s="8"/>
@@ -15732,24 +12762,23 @@
         <v>12</v>
       </c>
       <c r="I165" s="8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J165" s="8">
         <v>0</v>
       </c>
       <c r="K165" s="8">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L165" s="8">
         <v>0</v>
       </c>
       <c r="M165" s="8">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N165" s="8">
-        <f>_xlfn.XLOOKUP(C165,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>1511</v>
+        <v>1498</v>
       </c>
       <c r="O165" s="8"/>
       <c r="P165" s="8"/>
@@ -15800,8 +12829,7 @@
         <v>5</v>
       </c>
       <c r="N166" s="8">
-        <f>_xlfn.XLOOKUP(C166,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>930</v>
+        <v>908</v>
       </c>
       <c r="O166" s="8"/>
       <c r="P166" s="8"/>
@@ -15852,7 +12880,6 @@
         <v>1</v>
       </c>
       <c r="N167" s="8">
-        <f>_xlfn.XLOOKUP(C167,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O167" s="8"/>
@@ -15888,24 +12915,23 @@
         <v>14</v>
       </c>
       <c r="I168" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J168" s="8">
         <v>0</v>
       </c>
       <c r="K168" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L168" s="8">
         <v>0</v>
       </c>
       <c r="M168" s="8">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N168" s="8">
-        <f>_xlfn.XLOOKUP(C168,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>469</v>
+        <v>449</v>
       </c>
       <c r="O168" s="8"/>
       <c r="P168" s="8"/>
@@ -15956,7 +12982,6 @@
         <v>6</v>
       </c>
       <c r="N169" s="8">
-        <f>_xlfn.XLOOKUP(C169,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O169" s="8"/>
@@ -16008,8 +13033,7 @@
         <v>5</v>
       </c>
       <c r="N170" s="8">
-        <f>_xlfn.XLOOKUP(C170,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>736</v>
+        <v>710</v>
       </c>
       <c r="O170" s="8"/>
       <c r="P170" s="8"/>
@@ -16111,7 +13135,6 @@
         <v>3</v>
       </c>
       <c r="N172" s="8">
-        <f>_xlfn.XLOOKUP(C172,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>52</v>
       </c>
       <c r="O172" s="8"/>
@@ -16163,8 +13186,7 @@
         <v>2</v>
       </c>
       <c r="N173" s="8">
-        <f>_xlfn.XLOOKUP(C173,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="O173" s="8"/>
       <c r="P173" s="8"/>
@@ -16215,7 +13237,6 @@
         <v>2</v>
       </c>
       <c r="N174" s="8">
-        <f>_xlfn.XLOOKUP(C174,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O174" s="8"/>
@@ -16267,7 +13288,6 @@
         <v>3</v>
       </c>
       <c r="N175" s="8">
-        <f>_xlfn.XLOOKUP(C175,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O175" s="8"/>
@@ -16319,8 +13339,7 @@
         <v>2</v>
       </c>
       <c r="N176" s="8">
-        <f>_xlfn.XLOOKUP(C176,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="O176" s="8"/>
       <c r="P176" s="8"/>
@@ -16371,7 +13390,6 @@
         <v>2</v>
       </c>
       <c r="N177" s="8">
-        <f>_xlfn.XLOOKUP(C177,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O177" s="8"/>
@@ -16474,8 +13492,7 @@
         <v>3</v>
       </c>
       <c r="N179" s="8">
-        <f>_xlfn.XLOOKUP(C179,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="O179" s="8"/>
       <c r="P179" s="8"/>
@@ -16526,8 +13543,7 @@
         <v>8</v>
       </c>
       <c r="N180" s="8">
-        <f>_xlfn.XLOOKUP(C180,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>309</v>
+        <v>527</v>
       </c>
       <c r="O180" s="8"/>
       <c r="P180" s="8"/>
@@ -16578,8 +13594,7 @@
         <v>4</v>
       </c>
       <c r="N181" s="8">
-        <f>_xlfn.XLOOKUP(C181,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="O181" s="8"/>
       <c r="P181" s="8"/>
@@ -16630,7 +13645,6 @@
         <v>1</v>
       </c>
       <c r="N182" s="8">
-        <f>_xlfn.XLOOKUP(C182,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O182" s="8"/>
@@ -16666,24 +13680,23 @@
         <v>12</v>
       </c>
       <c r="I183" s="8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J183" s="8">
         <v>0</v>
       </c>
       <c r="K183" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L183" s="8">
         <v>0</v>
       </c>
       <c r="M183" s="8">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N183" s="8">
-        <f>_xlfn.XLOOKUP(C183,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>598</v>
+        <v>640</v>
       </c>
       <c r="O183" s="8"/>
       <c r="P183" s="8"/>
@@ -16718,7 +13731,7 @@
         <v>14</v>
       </c>
       <c r="I184" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J184" s="8">
         <v>0</v>
@@ -16731,11 +13744,10 @@
       </c>
       <c r="M184" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N184" s="8">
-        <f>_xlfn.XLOOKUP(C184,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O184" s="8"/>
       <c r="P184" s="8"/>
@@ -16770,24 +13782,23 @@
         <v>12</v>
       </c>
       <c r="I185" s="8">
-        <v>288</v>
+        <v>259</v>
       </c>
       <c r="J185" s="8">
         <v>0</v>
       </c>
       <c r="K185" s="8">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="L185" s="8">
         <v>0</v>
       </c>
       <c r="M185" s="8">
         <f t="shared" si="2"/>
-        <v>288</v>
+        <v>307</v>
       </c>
       <c r="N185" s="8">
-        <f>_xlfn.XLOOKUP(C185,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>2151</v>
+        <v>2103</v>
       </c>
       <c r="O185" s="8"/>
       <c r="P185" s="8"/>
@@ -16838,8 +13849,7 @@
         <v>9</v>
       </c>
       <c r="N186" s="8">
-        <f>_xlfn.XLOOKUP(C186,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>1032</v>
+        <v>1025</v>
       </c>
       <c r="O186" s="8"/>
       <c r="P186" s="8"/>
@@ -16890,8 +13900,7 @@
         <v>2</v>
       </c>
       <c r="N187" s="8">
-        <f>_xlfn.XLOOKUP(C187,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="O187" s="8"/>
       <c r="P187" s="8"/>
@@ -16926,7 +13935,7 @@
         <v>15</v>
       </c>
       <c r="I188" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J188" s="8">
         <v>0</v>
@@ -16939,11 +13948,10 @@
       </c>
       <c r="M188" s="8">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N188" s="8">
-        <f>_xlfn.XLOOKUP(C188,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O188" s="8"/>
       <c r="P188" s="8"/>
@@ -17029,24 +14037,23 @@
         <v>12</v>
       </c>
       <c r="I190" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J190" s="8">
         <v>0</v>
       </c>
       <c r="K190" s="8">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L190" s="8">
         <v>0</v>
       </c>
       <c r="M190" s="8">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="N190" s="8">
-        <f>_xlfn.XLOOKUP(C190,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="O190" s="8"/>
       <c r="P190" s="8"/>
@@ -17081,7 +14088,7 @@
         <v>12</v>
       </c>
       <c r="I191" s="8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J191" s="8">
         <v>0</v>
@@ -17094,11 +14101,10 @@
       </c>
       <c r="M191" s="8">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N191" s="8">
-        <f>_xlfn.XLOOKUP(C191,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>1127</v>
+        <v>1108</v>
       </c>
       <c r="O191" s="8"/>
       <c r="P191" s="8"/>
@@ -17149,7 +14155,6 @@
         <v>3</v>
       </c>
       <c r="N192" s="8">
-        <f>_xlfn.XLOOKUP(C192,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O192" s="8"/>
@@ -17201,8 +14206,7 @@
         <v>3</v>
       </c>
       <c r="N193" s="8">
-        <f>_xlfn.XLOOKUP(C193,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O193" s="8"/>
       <c r="P193" s="8"/>
@@ -17253,8 +14257,7 @@
         <v>5</v>
       </c>
       <c r="N194" s="8">
-        <f>_xlfn.XLOOKUP(C194,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="O194" s="8"/>
       <c r="P194" s="8"/>
@@ -17407,8 +14410,7 @@
         <v>5</v>
       </c>
       <c r="N197" s="8">
-        <f>_xlfn.XLOOKUP(C197,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>402</v>
+        <v>659</v>
       </c>
       <c r="O197" s="8"/>
       <c r="P197" s="8"/>
@@ -17443,7 +14445,7 @@
         <v>12</v>
       </c>
       <c r="I198" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J198" s="8">
         <v>0</v>
@@ -17456,10 +14458,9 @@
       </c>
       <c r="M198" s="8">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N198" s="8">
-        <f>_xlfn.XLOOKUP(C198,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O198" s="8"/>
@@ -17501,18 +14502,17 @@
         <v>0</v>
       </c>
       <c r="K199" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L199" s="8">
         <v>0</v>
       </c>
       <c r="M199" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N199" s="8">
-        <f>_xlfn.XLOOKUP(C199,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="O199" s="8"/>
       <c r="P199" s="8"/>
@@ -17563,7 +14563,6 @@
         <v>3</v>
       </c>
       <c r="N200" s="8">
-        <f>_xlfn.XLOOKUP(C200,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O200" s="8"/>
@@ -17605,18 +14604,17 @@
         <v>0</v>
       </c>
       <c r="K201" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L201" s="8">
         <v>0</v>
       </c>
       <c r="M201" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N201" s="8">
-        <f>_xlfn.XLOOKUP(C201,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O201" s="8"/>
       <c r="P201" s="8"/>
@@ -17667,7 +14665,6 @@
         <v>3</v>
       </c>
       <c r="N202" s="8">
-        <f>_xlfn.XLOOKUP(C202,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O202" s="8"/>
@@ -17719,8 +14716,7 @@
         <v>3</v>
       </c>
       <c r="N203" s="8">
-        <f>_xlfn.XLOOKUP(C203,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O203" s="8"/>
       <c r="P203" s="8"/>
@@ -17771,7 +14767,6 @@
         <v>1</v>
       </c>
       <c r="N204" s="8">
-        <f>_xlfn.XLOOKUP(C204,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O204" s="8"/>
@@ -17823,8 +14818,7 @@
         <v>6</v>
       </c>
       <c r="N205" s="8">
-        <f>_xlfn.XLOOKUP(C205,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O205" s="8"/>
       <c r="P205" s="8"/>
@@ -17875,7 +14869,6 @@
         <v>1</v>
       </c>
       <c r="N206" s="8">
-        <f>_xlfn.XLOOKUP(C206,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O206" s="8"/>
@@ -17911,7 +14904,7 @@
         <v>14</v>
       </c>
       <c r="I207" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J207" s="8">
         <v>0</v>
@@ -17924,11 +14917,10 @@
       </c>
       <c r="M207" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N207" s="8">
-        <f>_xlfn.XLOOKUP(C207,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="O207" s="8"/>
       <c r="P207" s="8"/>
@@ -17963,13 +14955,13 @@
         <v>14</v>
       </c>
       <c r="I208" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J208" s="8">
         <v>0</v>
       </c>
       <c r="K208" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L208" s="8">
         <v>0</v>
@@ -17979,7 +14971,6 @@
         <v>3</v>
       </c>
       <c r="N208" s="8">
-        <f>_xlfn.XLOOKUP(C208,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>11</v>
       </c>
       <c r="O208" s="8"/>
@@ -18031,8 +15022,7 @@
         <v>4</v>
       </c>
       <c r="N209" s="8">
-        <f>_xlfn.XLOOKUP(C209,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="O209" s="8"/>
       <c r="P209" s="8"/>
@@ -18118,7 +15108,7 @@
         <v>12</v>
       </c>
       <c r="I211" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J211" s="8">
         <v>0</v>
@@ -18131,11 +15121,10 @@
       </c>
       <c r="M211" s="8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N211" s="8">
-        <f>_xlfn.XLOOKUP(C211,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="O211" s="8"/>
       <c r="P211" s="8"/>
@@ -18186,7 +15175,6 @@
         <v>2</v>
       </c>
       <c r="N212" s="8">
-        <f>_xlfn.XLOOKUP(C212,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O212" s="8"/>
@@ -18238,7 +15226,7 @@
         <v>0</v>
       </c>
       <c r="N213" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O213" s="8"/>
       <c r="P213" s="8"/>
@@ -18289,8 +15277,7 @@
         <v>4</v>
       </c>
       <c r="N214" s="8">
-        <f>_xlfn.XLOOKUP(C214,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="O214" s="8"/>
       <c r="P214" s="8"/>
@@ -18341,8 +15328,7 @@
         <v>6</v>
       </c>
       <c r="N215" s="8">
-        <f>_xlfn.XLOOKUP(C215,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="O215" s="8"/>
       <c r="P215" s="8"/>
@@ -18393,7 +15379,6 @@
         <v>4</v>
       </c>
       <c r="N216" s="8">
-        <f>_xlfn.XLOOKUP(C216,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O216" s="8"/>
@@ -18445,7 +15430,6 @@
         <v>4</v>
       </c>
       <c r="N217" s="8">
-        <f>_xlfn.XLOOKUP(C217,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>94</v>
       </c>
       <c r="O217" s="8"/>
@@ -18497,7 +15481,6 @@
         <v>6</v>
       </c>
       <c r="N218" s="8">
-        <f>_xlfn.XLOOKUP(C218,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>242</v>
       </c>
       <c r="O218" s="8"/>
@@ -18549,8 +15532,7 @@
         <v>6</v>
       </c>
       <c r="N219" s="8">
-        <f>_xlfn.XLOOKUP(C219,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="O219" s="8"/>
       <c r="P219" s="8"/>
@@ -18601,8 +15583,7 @@
         <v>4</v>
       </c>
       <c r="N220" s="8">
-        <f>_xlfn.XLOOKUP(C220,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O220" s="8"/>
       <c r="P220" s="8"/>
@@ -18653,7 +15634,6 @@
         <v>4</v>
       </c>
       <c r="N221" s="8">
-        <f>_xlfn.XLOOKUP(C221,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>45</v>
       </c>
       <c r="O221" s="8"/>
@@ -18689,13 +15669,13 @@
         <v>16</v>
       </c>
       <c r="I222" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J222" s="8">
         <v>0</v>
       </c>
       <c r="K222" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L222" s="8">
         <v>0</v>
@@ -18705,7 +15685,6 @@
         <v>2</v>
       </c>
       <c r="N222" s="8">
-        <f>_xlfn.XLOOKUP(C222,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>156</v>
       </c>
       <c r="O222" s="8"/>
@@ -18757,8 +15736,7 @@
         <v>2</v>
       </c>
       <c r="N223" s="8">
-        <f>_xlfn.XLOOKUP(C223,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O223" s="8"/>
       <c r="P223" s="8"/>
@@ -18809,7 +15787,6 @@
         <v>3</v>
       </c>
       <c r="N224" s="8">
-        <f>_xlfn.XLOOKUP(C224,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>199</v>
       </c>
       <c r="O224" s="8"/>
@@ -18861,8 +15838,7 @@
         <v>4</v>
       </c>
       <c r="N225" s="8">
-        <f>_xlfn.XLOOKUP(C225,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>782</v>
+        <v>763</v>
       </c>
       <c r="O225" s="8"/>
       <c r="P225" s="8"/>
@@ -18964,7 +15940,6 @@
         <v>1</v>
       </c>
       <c r="N227" s="8">
-        <f>_xlfn.XLOOKUP(C227,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O227" s="8"/>
@@ -19000,7 +15975,7 @@
         <v>15</v>
       </c>
       <c r="I228" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J228" s="8">
         <v>0</v>
@@ -19013,11 +15988,10 @@
       </c>
       <c r="M228" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N228" s="8">
-        <f>_xlfn.XLOOKUP(C228,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>118</v>
+        <v>160</v>
       </c>
       <c r="O228" s="8"/>
       <c r="P228" s="8"/>
@@ -19068,7 +16042,6 @@
         <v>3</v>
       </c>
       <c r="N229" s="8">
-        <f>_xlfn.XLOOKUP(C229,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>208</v>
       </c>
       <c r="O229" s="8"/>
@@ -19120,7 +16093,6 @@
         <v>3</v>
       </c>
       <c r="N230" s="8">
-        <f>_xlfn.XLOOKUP(C230,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O230" s="8"/>
@@ -19172,7 +16144,6 @@
         <v>3</v>
       </c>
       <c r="N231" s="8">
-        <f>_xlfn.XLOOKUP(C231,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O231" s="8"/>
@@ -19224,8 +16195,7 @@
         <v>14</v>
       </c>
       <c r="N232" s="8">
-        <f>_xlfn.XLOOKUP(C232,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>807</v>
+        <v>797</v>
       </c>
       <c r="O232" s="8"/>
       <c r="P232" s="8"/>
@@ -19276,8 +16246,7 @@
         <v>7</v>
       </c>
       <c r="N233" s="8">
-        <f>_xlfn.XLOOKUP(C233,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="O233" s="8"/>
       <c r="P233" s="8"/>
@@ -19328,8 +16297,7 @@
         <v>2</v>
       </c>
       <c r="N234" s="8">
-        <f>_xlfn.XLOOKUP(C234,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O234" s="8"/>
       <c r="P234" s="8"/>
@@ -19380,8 +16348,7 @@
         <v>3</v>
       </c>
       <c r="N235" s="8">
-        <f>_xlfn.XLOOKUP(C235,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>100</v>
+        <v>177</v>
       </c>
       <c r="O235" s="8"/>
       <c r="P235" s="8"/>
@@ -19432,7 +16399,6 @@
         <v>1</v>
       </c>
       <c r="N236" s="8">
-        <f>_xlfn.XLOOKUP(C236,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O236" s="8"/>
@@ -19468,7 +16434,7 @@
         <v>12</v>
       </c>
       <c r="I237" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J237" s="8">
         <v>0</v>
@@ -19481,11 +16447,10 @@
       </c>
       <c r="M237" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N237" s="8">
-        <f>_xlfn.XLOOKUP(C237,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="O237" s="8"/>
       <c r="P237" s="8"/>
@@ -19536,8 +16501,7 @@
         <v>6</v>
       </c>
       <c r="N238" s="8">
-        <f>_xlfn.XLOOKUP(C238,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="O238" s="8"/>
       <c r="P238" s="8"/>
@@ -19572,7 +16536,7 @@
         <v>15</v>
       </c>
       <c r="I239" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J239" s="8">
         <v>0</v>
@@ -19585,11 +16549,10 @@
       </c>
       <c r="M239" s="8">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N239" s="8">
-        <f>_xlfn.XLOOKUP(C239,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="O239" s="8"/>
       <c r="P239" s="8"/>
@@ -19640,7 +16603,6 @@
         <v>1</v>
       </c>
       <c r="N240" s="8">
-        <f>_xlfn.XLOOKUP(C240,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O240" s="8"/>
@@ -19692,8 +16654,7 @@
         <v>3</v>
       </c>
       <c r="N241" s="8">
-        <f>_xlfn.XLOOKUP(C241,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O241" s="8"/>
       <c r="P241" s="8"/>
@@ -19744,8 +16705,7 @@
         <v>3</v>
       </c>
       <c r="N242" s="8">
-        <f>_xlfn.XLOOKUP(C242,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>409</v>
+        <v>691</v>
       </c>
       <c r="O242" s="8"/>
       <c r="P242" s="8"/>
@@ -19796,8 +16756,7 @@
         <v>4</v>
       </c>
       <c r="N243" s="8">
-        <f>_xlfn.XLOOKUP(C243,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="O243" s="8"/>
       <c r="P243" s="8"/>
@@ -19848,7 +16807,7 @@
         <v>0</v>
       </c>
       <c r="N244" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O244" s="8"/>
       <c r="P244" s="8"/>
@@ -19883,13 +16842,13 @@
         <v>15</v>
       </c>
       <c r="I245" s="8">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J245" s="8">
         <v>0</v>
       </c>
       <c r="K245" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L245" s="8">
         <v>0</v>
@@ -19899,8 +16858,7 @@
         <v>6</v>
       </c>
       <c r="N245" s="8">
-        <f>_xlfn.XLOOKUP(C245,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="O245" s="8"/>
       <c r="P245" s="8"/>
@@ -19951,8 +16909,7 @@
         <v>2</v>
       </c>
       <c r="N246" s="8">
-        <f>_xlfn.XLOOKUP(C246,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="O246" s="8"/>
       <c r="P246" s="8"/>
@@ -20003,8 +16960,7 @@
         <v>3</v>
       </c>
       <c r="N247" s="8">
-        <f>_xlfn.XLOOKUP(C247,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="O247" s="8"/>
       <c r="P247" s="8"/>
@@ -20039,7 +16995,7 @@
         <v>12</v>
       </c>
       <c r="I248" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J248" s="8">
         <v>0</v>
@@ -20052,10 +17008,9 @@
       </c>
       <c r="M248" s="8">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N248" s="8">
-        <f>_xlfn.XLOOKUP(C248,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O248" s="8"/>
@@ -20107,7 +17062,6 @@
         <v>1</v>
       </c>
       <c r="N249" s="8">
-        <f>_xlfn.XLOOKUP(C249,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O249" s="8"/>
@@ -20143,7 +17097,7 @@
         <v>12</v>
       </c>
       <c r="I250" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J250" s="8">
         <v>0</v>
@@ -20156,11 +17110,10 @@
       </c>
       <c r="M250" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N250" s="8">
-        <f>_xlfn.XLOOKUP(C250,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="O250" s="8"/>
       <c r="P250" s="8"/>
@@ -20211,8 +17164,7 @@
         <v>3</v>
       </c>
       <c r="N251" s="8">
-        <f>_xlfn.XLOOKUP(C251,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>1334</v>
+        <v>1292</v>
       </c>
       <c r="O251" s="8"/>
       <c r="P251" s="8"/>
@@ -20263,8 +17215,7 @@
         <v>3</v>
       </c>
       <c r="N252" s="8">
-        <f>_xlfn.XLOOKUP(C252,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>247</v>
+        <v>217</v>
       </c>
       <c r="O252" s="8"/>
       <c r="P252" s="8"/>
@@ -20315,8 +17266,7 @@
         <v>3</v>
       </c>
       <c r="N253" s="8">
-        <f>_xlfn.XLOOKUP(C253,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>1272</v>
+        <v>1240</v>
       </c>
       <c r="O253" s="8"/>
       <c r="P253" s="8"/>
@@ -20351,13 +17301,13 @@
         <v>14</v>
       </c>
       <c r="I254" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J254" s="8">
         <v>0</v>
       </c>
       <c r="K254" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L254" s="8">
         <v>0</v>
@@ -20367,8 +17317,7 @@
         <v>3</v>
       </c>
       <c r="N254" s="8">
-        <f>_xlfn.XLOOKUP(C254,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>583</v>
+        <v>552</v>
       </c>
       <c r="O254" s="8"/>
       <c r="P254" s="8"/>
@@ -20419,8 +17368,7 @@
         <v>3</v>
       </c>
       <c r="N255" s="8">
-        <f>_xlfn.XLOOKUP(C255,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="O255" s="8"/>
       <c r="P255" s="8"/>
@@ -20471,8 +17419,7 @@
         <v>3</v>
       </c>
       <c r="N256" s="8">
-        <f>_xlfn.XLOOKUP(C256,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="O256" s="8"/>
       <c r="P256" s="8"/>
@@ -20523,8 +17470,7 @@
         <v>4</v>
       </c>
       <c r="N257" s="8">
-        <f>_xlfn.XLOOKUP(C257,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="O257" s="8"/>
       <c r="P257" s="8"/>
@@ -20575,8 +17521,7 @@
         <v>3</v>
       </c>
       <c r="N258" s="8">
-        <f>_xlfn.XLOOKUP(C258,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O258" s="8"/>
       <c r="P258" s="8"/>
@@ -20627,7 +17572,6 @@
         <v>2</v>
       </c>
       <c r="N259" s="8">
-        <f>_xlfn.XLOOKUP(C259,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>52</v>
       </c>
       <c r="O259" s="8"/>
@@ -20679,8 +17623,7 @@
         <v>5</v>
       </c>
       <c r="N260" s="8">
-        <f>_xlfn.XLOOKUP(C260,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>151</v>
+        <v>193</v>
       </c>
       <c r="O260" s="8"/>
       <c r="P260" s="8"/>
@@ -20715,13 +17658,13 @@
         <v>12</v>
       </c>
       <c r="I261" s="8">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J261" s="8">
         <v>0</v>
       </c>
       <c r="K261" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L261" s="8">
         <v>0</v>
@@ -20731,8 +17674,7 @@
         <v>29</v>
       </c>
       <c r="N261" s="8">
-        <f>_xlfn.XLOOKUP(C261,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>1538</v>
+        <v>1513</v>
       </c>
       <c r="O261" s="8"/>
       <c r="P261" s="8"/>
@@ -20773,18 +17715,17 @@
         <v>0</v>
       </c>
       <c r="K262" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L262" s="8">
         <v>0</v>
       </c>
       <c r="M262" s="8">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N262" s="8">
-        <f>_xlfn.XLOOKUP(C262,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="O262" s="8"/>
       <c r="P262" s="8"/>
@@ -20819,24 +17760,23 @@
         <v>12</v>
       </c>
       <c r="I263" s="8">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J263" s="8">
         <v>0</v>
       </c>
       <c r="K263" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L263" s="8">
         <v>0</v>
       </c>
       <c r="M263" s="8">
         <f t="shared" si="4"/>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N263" s="8">
-        <f>_xlfn.XLOOKUP(C263,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>859</v>
+        <v>813</v>
       </c>
       <c r="O263" s="8"/>
       <c r="P263" s="8"/>
@@ -20887,7 +17827,6 @@
         <v>3</v>
       </c>
       <c r="N264" s="8">
-        <f>_xlfn.XLOOKUP(C264,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>1028</v>
       </c>
       <c r="O264" s="8"/>
@@ -20939,8 +17878,7 @@
         <v>2</v>
       </c>
       <c r="N265" s="8">
-        <f>_xlfn.XLOOKUP(C265,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="O265" s="8"/>
       <c r="P265" s="8"/>
@@ -20991,8 +17929,7 @@
         <v>3</v>
       </c>
       <c r="N266" s="8">
-        <f>_xlfn.XLOOKUP(C266,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>1623</v>
+        <v>1584</v>
       </c>
       <c r="O266" s="8"/>
       <c r="P266" s="8"/>
@@ -21043,7 +17980,6 @@
         <v>3</v>
       </c>
       <c r="N267" s="8">
-        <f>_xlfn.XLOOKUP(C267,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>62</v>
       </c>
       <c r="O267" s="8"/>
@@ -21079,7 +18015,7 @@
         <v>15</v>
       </c>
       <c r="I268" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J268" s="8">
         <v>0</v>
@@ -21092,11 +18028,10 @@
       </c>
       <c r="M268" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N268" s="8">
-        <f>_xlfn.XLOOKUP(C268,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="O268" s="8"/>
       <c r="P268" s="8"/>
@@ -21131,7 +18066,7 @@
         <v>15</v>
       </c>
       <c r="I269" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J269" s="8">
         <v>0</v>
@@ -21144,11 +18079,10 @@
       </c>
       <c r="M269" s="8">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N269" s="8">
-        <f>_xlfn.XLOOKUP(C269,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="O269" s="8"/>
       <c r="P269" s="8"/>
@@ -21199,7 +18133,6 @@
         <v>2</v>
       </c>
       <c r="N270" s="8">
-        <f>_xlfn.XLOOKUP(C270,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O270" s="8"/>
@@ -21235,7 +18168,7 @@
         <v>16</v>
       </c>
       <c r="I271" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J271" s="8">
         <v>0</v>
@@ -21248,10 +18181,9 @@
       </c>
       <c r="M271" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N271" s="8">
-        <f>_xlfn.XLOOKUP(C271,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O271" s="8"/>
@@ -21303,7 +18235,6 @@
         <v>2</v>
       </c>
       <c r="N272" s="8">
-        <f>_xlfn.XLOOKUP(C272,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O272" s="8"/>
@@ -21355,7 +18286,6 @@
         <v>2</v>
       </c>
       <c r="N273" s="8">
-        <f>_xlfn.XLOOKUP(C273,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O273" s="8"/>
@@ -21397,18 +18327,17 @@
         <v>0</v>
       </c>
       <c r="K274" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L274" s="8">
         <v>0</v>
       </c>
       <c r="M274" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N274" s="8">
-        <f>_xlfn.XLOOKUP(C274,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O274" s="8"/>
       <c r="P274" s="8"/>
@@ -21459,7 +18388,6 @@
         <v>4</v>
       </c>
       <c r="N275" s="8">
-        <f>_xlfn.XLOOKUP(C275,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>27</v>
       </c>
       <c r="O275" s="8"/>
@@ -21495,7 +18423,7 @@
         <v>15</v>
       </c>
       <c r="I276" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J276" s="8">
         <v>0</v>
@@ -21508,11 +18436,10 @@
       </c>
       <c r="M276" s="8">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N276" s="8">
-        <f>_xlfn.XLOOKUP(C276,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="O276" s="8"/>
       <c r="P276" s="8"/>
@@ -21563,7 +18490,6 @@
         <v>1</v>
       </c>
       <c r="N277" s="8">
-        <f>_xlfn.XLOOKUP(C277,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O277" s="8"/>
@@ -21599,7 +18525,7 @@
         <v>12</v>
       </c>
       <c r="I278" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J278" s="8">
         <v>0</v>
@@ -21612,11 +18538,10 @@
       </c>
       <c r="M278" s="8">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N278" s="8">
-        <f>_xlfn.XLOOKUP(C278,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>210</v>
+        <v>984</v>
       </c>
       <c r="O278" s="8"/>
       <c r="P278" s="8"/>
@@ -21667,7 +18592,6 @@
         <v>3</v>
       </c>
       <c r="N279" s="8">
-        <f>_xlfn.XLOOKUP(C279,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>27</v>
       </c>
       <c r="O279" s="8"/>
@@ -21719,7 +18643,6 @@
         <v>3</v>
       </c>
       <c r="N280" s="8">
-        <f>_xlfn.XLOOKUP(C280,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>83</v>
       </c>
       <c r="O280" s="8"/>
@@ -21771,8 +18694,7 @@
         <v>2</v>
       </c>
       <c r="N281" s="8">
-        <f>_xlfn.XLOOKUP(C281,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O281" s="8"/>
       <c r="P281" s="8"/>
@@ -21864,18 +18786,17 @@
         <v>0</v>
       </c>
       <c r="K283" s="8">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L283" s="8">
         <v>0</v>
       </c>
       <c r="M283" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="N283" s="8">
-        <f>_xlfn.XLOOKUP(C283,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>318</v>
+        <v>587</v>
       </c>
       <c r="O283" s="8"/>
       <c r="P283" s="8"/>
@@ -21910,13 +18831,13 @@
         <v>12</v>
       </c>
       <c r="I284" s="8">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="J284" s="8">
         <v>0</v>
       </c>
       <c r="K284" s="8">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="L284" s="8">
         <v>0</v>
@@ -21926,8 +18847,7 @@
         <v>36</v>
       </c>
       <c r="N284" s="8">
-        <f>_xlfn.XLOOKUP(C284,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>1</v>
+        <v>275</v>
       </c>
       <c r="O284" s="8"/>
       <c r="P284" s="8"/>
@@ -21978,7 +18898,6 @@
         <v>3</v>
       </c>
       <c r="N285" s="8">
-        <f>_xlfn.XLOOKUP(C285,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O285" s="8"/>
@@ -22030,8 +18949,7 @@
         <v>4</v>
       </c>
       <c r="N286" s="8">
-        <f>_xlfn.XLOOKUP(C286,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="O286" s="8"/>
       <c r="P286" s="8"/>
@@ -22066,13 +18984,13 @@
         <v>12</v>
       </c>
       <c r="I287" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J287" s="8">
         <v>0</v>
       </c>
       <c r="K287" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L287" s="8">
         <v>0</v>
@@ -22082,8 +19000,7 @@
         <v>7</v>
       </c>
       <c r="N287" s="8">
-        <f>_xlfn.XLOOKUP(C287,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="O287" s="8"/>
       <c r="P287" s="8"/>
@@ -22134,8 +19051,7 @@
         <v>5</v>
       </c>
       <c r="N288" s="8">
-        <f>_xlfn.XLOOKUP(C288,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>1582</v>
+        <v>1577</v>
       </c>
       <c r="O288" s="8"/>
       <c r="P288" s="8"/>
@@ -22186,8 +19102,7 @@
         <v>2</v>
       </c>
       <c r="N289" s="8">
-        <f>_xlfn.XLOOKUP(C289,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="O289" s="8"/>
       <c r="P289" s="8"/>
@@ -22238,7 +19153,6 @@
         <v>3</v>
       </c>
       <c r="N290" s="8">
-        <f>_xlfn.XLOOKUP(C290,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O290" s="8"/>
@@ -22274,13 +19188,13 @@
         <v>12</v>
       </c>
       <c r="I291" s="8">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J291" s="8">
         <v>0</v>
       </c>
       <c r="K291" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L291" s="8">
         <v>0</v>
@@ -22290,8 +19204,7 @@
         <v>16</v>
       </c>
       <c r="N291" s="8">
-        <f>_xlfn.XLOOKUP(C291,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="O291" s="8"/>
       <c r="P291" s="8"/>
@@ -22326,7 +19239,7 @@
         <v>16</v>
       </c>
       <c r="I292" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J292" s="8">
         <v>0</v>
@@ -22339,10 +19252,9 @@
       </c>
       <c r="M292" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N292" s="8">
-        <f>_xlfn.XLOOKUP(C292,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>221</v>
       </c>
       <c r="O292" s="8"/>
@@ -22429,7 +19341,7 @@
         <v>12</v>
       </c>
       <c r="I294" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J294" s="8">
         <v>0</v>
@@ -22442,11 +19354,10 @@
       </c>
       <c r="M294" s="8">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N294" s="8">
-        <f>_xlfn.XLOOKUP(C294,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>1695</v>
+        <v>1687</v>
       </c>
       <c r="O294" s="8"/>
       <c r="P294" s="8"/>
@@ -22548,7 +19459,6 @@
         <v>1</v>
       </c>
       <c r="N296" s="8">
-        <f>_xlfn.XLOOKUP(C296,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O296" s="8"/>
@@ -22702,7 +19612,6 @@
         <v>2</v>
       </c>
       <c r="N299" s="8">
-        <f>_xlfn.XLOOKUP(C299,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O299" s="8"/>
@@ -22738,13 +19647,13 @@
         <v>13</v>
       </c>
       <c r="I300" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J300" s="8">
         <v>0</v>
       </c>
       <c r="K300" s="8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L300" s="8">
         <v>0</v>
@@ -22754,8 +19663,7 @@
         <v>8</v>
       </c>
       <c r="N300" s="8">
-        <f>_xlfn.XLOOKUP(C300,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="O300" s="8"/>
       <c r="P300" s="8"/>
@@ -22806,7 +19714,6 @@
         <v>6</v>
       </c>
       <c r="N301" s="8">
-        <f>_xlfn.XLOOKUP(C301,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>176</v>
       </c>
       <c r="O301" s="8"/>
@@ -22842,7 +19749,7 @@
         <v>13</v>
       </c>
       <c r="I302" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J302" s="8">
         <v>0</v>
@@ -22855,11 +19762,10 @@
       </c>
       <c r="M302" s="8">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N302" s="8">
-        <f>_xlfn.XLOOKUP(C302,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O302" s="8"/>
       <c r="P302" s="8"/>
@@ -22910,8 +19816,7 @@
         <v>3</v>
       </c>
       <c r="N303" s="8">
-        <f>_xlfn.XLOOKUP(C303,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O303" s="8"/>
       <c r="P303" s="8"/>
@@ -22962,7 +19867,6 @@
         <v>4</v>
       </c>
       <c r="N304" s="8">
-        <f>_xlfn.XLOOKUP(C304,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>15</v>
       </c>
       <c r="O304" s="8"/>
@@ -22998,7 +19902,7 @@
         <v>13</v>
       </c>
       <c r="I305" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J305" s="8">
         <v>0</v>
@@ -23011,11 +19915,10 @@
       </c>
       <c r="M305" s="8">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N305" s="8">
-        <f>_xlfn.XLOOKUP(C305,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>568</v>
+        <v>593</v>
       </c>
       <c r="O305" s="8"/>
       <c r="P305" s="8"/>
@@ -23066,8 +19969,7 @@
         <v>10</v>
       </c>
       <c r="N306" s="8">
-        <f>_xlfn.XLOOKUP(C306,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="O306" s="8"/>
       <c r="P306" s="8"/>
@@ -23118,8 +20020,7 @@
         <v>11</v>
       </c>
       <c r="N307" s="8">
-        <f>_xlfn.XLOOKUP(C307,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>1138</v>
+        <v>1132</v>
       </c>
       <c r="O307" s="8"/>
       <c r="P307" s="8"/>
@@ -23170,8 +20071,7 @@
         <v>11</v>
       </c>
       <c r="N308" s="8">
-        <f>_xlfn.XLOOKUP(C308,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>928</v>
+        <v>934</v>
       </c>
       <c r="O308" s="8"/>
       <c r="P308" s="8"/>
@@ -23222,8 +20122,7 @@
         <v>4</v>
       </c>
       <c r="N309" s="8">
-        <f>_xlfn.XLOOKUP(C309,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O309" s="8"/>
       <c r="P309" s="8"/>
@@ -23274,7 +20173,6 @@
         <v>4</v>
       </c>
       <c r="N310" s="8">
-        <f>_xlfn.XLOOKUP(C310,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>45</v>
       </c>
       <c r="O310" s="8"/>
@@ -23326,7 +20224,6 @@
         <v>3</v>
       </c>
       <c r="N311" s="8">
-        <f>_xlfn.XLOOKUP(C311,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>186</v>
       </c>
       <c r="O311" s="8"/>
@@ -23368,18 +20265,17 @@
         <v>0</v>
       </c>
       <c r="K312" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L312" s="8">
         <v>0</v>
       </c>
       <c r="M312" s="8">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N312" s="8">
-        <f>_xlfn.XLOOKUP(C312,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="O312" s="8"/>
       <c r="P312" s="8"/>
@@ -23430,8 +20326,7 @@
         <v>3</v>
       </c>
       <c r="N313" s="8">
-        <f>_xlfn.XLOOKUP(C313,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="O313" s="8"/>
       <c r="P313" s="8"/>
@@ -23482,8 +20377,7 @@
         <v>3</v>
       </c>
       <c r="N314" s="8">
-        <f>_xlfn.XLOOKUP(C314,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="O314" s="8"/>
       <c r="P314" s="8"/>
@@ -23534,8 +20428,7 @@
         <v>8</v>
       </c>
       <c r="N315" s="8">
-        <f>_xlfn.XLOOKUP(C315,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>317</v>
+        <v>480</v>
       </c>
       <c r="O315" s="8"/>
       <c r="P315" s="8"/>
@@ -23576,18 +20469,17 @@
         <v>0</v>
       </c>
       <c r="K316" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L316" s="8">
         <v>0</v>
       </c>
       <c r="M316" s="8">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N316" s="8">
-        <f>_xlfn.XLOOKUP(C316,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="O316" s="8"/>
       <c r="P316" s="8"/>
@@ -23638,8 +20530,7 @@
         <v>6</v>
       </c>
       <c r="N317" s="8">
-        <f>_xlfn.XLOOKUP(C317,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="O317" s="8"/>
       <c r="P317" s="8"/>
@@ -23674,13 +20565,13 @@
         <v>12</v>
       </c>
       <c r="I318" s="8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J318" s="8">
         <v>0</v>
       </c>
       <c r="K318" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L318" s="8">
         <v>0</v>
@@ -23690,8 +20581,7 @@
         <v>8</v>
       </c>
       <c r="N318" s="8">
-        <f>_xlfn.XLOOKUP(C318,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>919</v>
+        <v>894</v>
       </c>
       <c r="O318" s="8"/>
       <c r="P318" s="8"/>
@@ -23742,8 +20632,7 @@
         <v>4</v>
       </c>
       <c r="N319" s="8">
-        <f>_xlfn.XLOOKUP(C319,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="O319" s="8"/>
       <c r="P319" s="8"/>
@@ -23794,8 +20683,7 @@
         <v>4</v>
       </c>
       <c r="N320" s="8">
-        <f>_xlfn.XLOOKUP(C320,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="O320" s="8"/>
       <c r="P320" s="8"/>
@@ -23830,7 +20718,7 @@
         <v>14</v>
       </c>
       <c r="I321" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J321" s="8">
         <v>0</v>
@@ -23843,11 +20731,10 @@
       </c>
       <c r="M321" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N321" s="8">
-        <f>_xlfn.XLOOKUP(C321,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="O321" s="8"/>
       <c r="P321" s="8"/>
@@ -23898,7 +20785,6 @@
         <v>3</v>
       </c>
       <c r="N322" s="8">
-        <f>_xlfn.XLOOKUP(C322,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>473</v>
       </c>
       <c r="O322" s="8"/>
@@ -23950,7 +20836,6 @@
         <v>4</v>
       </c>
       <c r="N323" s="8">
-        <f>_xlfn.XLOOKUP(C323,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>100</v>
       </c>
       <c r="O323" s="8"/>
@@ -24053,8 +20938,7 @@
         <v>4</v>
       </c>
       <c r="N325" s="8">
-        <f>_xlfn.XLOOKUP(C325,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>225</v>
+        <v>416</v>
       </c>
       <c r="O325" s="8"/>
       <c r="P325" s="8"/>
@@ -24105,8 +20989,7 @@
         <v>3</v>
       </c>
       <c r="N326" s="8">
-        <f>_xlfn.XLOOKUP(C326,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>729</v>
+        <v>826</v>
       </c>
       <c r="O326" s="8"/>
       <c r="P326" s="8"/>
@@ -24157,7 +21040,6 @@
         <v>3</v>
       </c>
       <c r="N327" s="8">
-        <f>_xlfn.XLOOKUP(C327,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>91</v>
       </c>
       <c r="O327" s="8"/>
@@ -24209,8 +21091,7 @@
         <v>1</v>
       </c>
       <c r="N328" s="8">
-        <f>_xlfn.XLOOKUP(C328,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="O328" s="8"/>
       <c r="P328" s="8"/>
@@ -24245,13 +21126,13 @@
         <v>13</v>
       </c>
       <c r="I329" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J329" s="8">
         <v>0</v>
       </c>
       <c r="K329" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L329" s="8">
         <v>0</v>
@@ -24261,8 +21142,7 @@
         <v>4</v>
       </c>
       <c r="N329" s="8">
-        <f>_xlfn.XLOOKUP(C329,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="O329" s="8"/>
       <c r="P329" s="8"/>
@@ -24313,8 +21193,7 @@
         <v>2</v>
       </c>
       <c r="N330" s="8">
-        <f>_xlfn.XLOOKUP(C330,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="O330" s="8"/>
       <c r="P330" s="8"/>
@@ -24365,7 +21244,6 @@
         <v>3</v>
       </c>
       <c r="N331" s="8">
-        <f>_xlfn.XLOOKUP(C331,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O331" s="8"/>
@@ -24417,7 +21295,6 @@
         <v>1</v>
       </c>
       <c r="N332" s="8">
-        <f>_xlfn.XLOOKUP(C332,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O332" s="8"/>
@@ -24469,7 +21346,6 @@
         <v>3</v>
       </c>
       <c r="N333" s="8">
-        <f>_xlfn.XLOOKUP(C333,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>347</v>
       </c>
       <c r="O333" s="8"/>
@@ -24521,7 +21397,6 @@
         <v>4</v>
       </c>
       <c r="N334" s="8">
-        <f>_xlfn.XLOOKUP(C334,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>353</v>
       </c>
       <c r="O334" s="8"/>
@@ -24573,8 +21448,7 @@
         <v>1</v>
       </c>
       <c r="N335" s="8">
-        <f>_xlfn.XLOOKUP(C335,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O335" s="8"/>
       <c r="P335" s="8"/>
@@ -24625,8 +21499,7 @@
         <v>5</v>
       </c>
       <c r="N336" s="8">
-        <f>_xlfn.XLOOKUP(C336,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="O336" s="8"/>
       <c r="P336" s="8"/>
@@ -24661,24 +21534,23 @@
         <v>12</v>
       </c>
       <c r="I337" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J337" s="8">
         <v>0</v>
       </c>
       <c r="K337" s="8">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L337" s="8">
         <v>0</v>
       </c>
       <c r="M337" s="8">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="N337" s="8">
-        <f>_xlfn.XLOOKUP(C337,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>1085</v>
+        <v>1073</v>
       </c>
       <c r="O337" s="8"/>
       <c r="P337" s="8"/>
@@ -24713,7 +21585,7 @@
         <v>12</v>
       </c>
       <c r="I338" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J338" s="8">
         <v>0</v>
@@ -24726,11 +21598,10 @@
       </c>
       <c r="M338" s="8">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N338" s="8">
-        <f>_xlfn.XLOOKUP(C338,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>1341</v>
+        <v>1321</v>
       </c>
       <c r="O338" s="8"/>
       <c r="P338" s="8"/>
@@ -24781,8 +21652,7 @@
         <v>3</v>
       </c>
       <c r="N339" s="8">
-        <f>_xlfn.XLOOKUP(C339,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="O339" s="8"/>
       <c r="P339" s="8"/>
@@ -24817,24 +21687,23 @@
         <v>14</v>
       </c>
       <c r="I340" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J340" s="8">
         <v>0</v>
       </c>
       <c r="K340" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L340" s="8">
         <v>0</v>
       </c>
       <c r="M340" s="8">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N340" s="8">
-        <f>_xlfn.XLOOKUP(C340,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>791</v>
+        <v>773</v>
       </c>
       <c r="O340" s="8"/>
       <c r="P340" s="8"/>
@@ -24869,7 +21738,7 @@
         <v>14</v>
       </c>
       <c r="I341" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J341" s="8">
         <v>0</v>
@@ -24882,10 +21751,9 @@
       </c>
       <c r="M341" s="8">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N341" s="8">
-        <f>_xlfn.XLOOKUP(C341,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>394</v>
       </c>
       <c r="O341" s="8"/>
@@ -24937,8 +21805,7 @@
         <v>4</v>
       </c>
       <c r="N342" s="8">
-        <f>_xlfn.XLOOKUP(C342,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>134</v>
+        <v>326</v>
       </c>
       <c r="O342" s="8"/>
       <c r="P342" s="8"/>
@@ -24989,7 +21856,6 @@
         <v>4</v>
       </c>
       <c r="N343" s="8">
-        <f>_xlfn.XLOOKUP(C343,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>41</v>
       </c>
       <c r="O343" s="8"/>
@@ -25025,7 +21891,7 @@
         <v>12</v>
       </c>
       <c r="I344" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J344" s="8">
         <v>0</v>
@@ -25038,10 +21904,9 @@
       </c>
       <c r="M344" s="8">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N344" s="8">
-        <f>_xlfn.XLOOKUP(C344,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O344" s="8"/>
@@ -25077,7 +21942,7 @@
         <v>12</v>
       </c>
       <c r="I345" s="8">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J345" s="8">
         <v>0</v>
@@ -25090,10 +21955,9 @@
       </c>
       <c r="M345" s="8">
         <f t="shared" si="5"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N345" s="8">
-        <f>_xlfn.XLOOKUP(C345,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O345" s="8"/>
@@ -25145,7 +22009,6 @@
         <v>295</v>
       </c>
       <c r="N346" s="8">
-        <f>_xlfn.XLOOKUP(C346,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O346" s="8"/>
@@ -25181,24 +22044,23 @@
         <v>13</v>
       </c>
       <c r="I347" s="8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J347" s="8">
         <v>0</v>
       </c>
       <c r="K347" s="8">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L347" s="8">
         <v>0</v>
       </c>
       <c r="M347" s="8">
         <f t="shared" si="5"/>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="N347" s="8">
-        <f>_xlfn.XLOOKUP(C347,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="O347" s="8"/>
       <c r="P347" s="9"/>
@@ -25233,7 +22095,7 @@
         <v>12</v>
       </c>
       <c r="I348" s="8">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="J348" s="8">
         <v>0</v>
@@ -25246,10 +22108,9 @@
       </c>
       <c r="M348" s="8">
         <f t="shared" si="5"/>
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="N348" s="8">
-        <f>_xlfn.XLOOKUP(C348,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>92</v>
       </c>
       <c r="O348" s="8"/>
@@ -25352,7 +22213,6 @@
         <v>1</v>
       </c>
       <c r="N350" s="8">
-        <f>_xlfn.XLOOKUP(C350,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O350" s="8"/>
@@ -25439,7 +22299,7 @@
         <v>14</v>
       </c>
       <c r="I352" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J352" s="8">
         <v>0</v>
@@ -25452,11 +22312,10 @@
       </c>
       <c r="M352" s="8">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N352" s="8">
-        <f>_xlfn.XLOOKUP(C352,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="O352" s="8"/>
       <c r="P352" s="9"/>
@@ -25609,8 +22468,7 @@
         <v>4</v>
       </c>
       <c r="N355" s="8">
-        <f>_xlfn.XLOOKUP(C355,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O355" s="8"/>
       <c r="P355" s="9"/>
@@ -25661,7 +22519,7 @@
         <v>0</v>
       </c>
       <c r="N356" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O356" s="8"/>
       <c r="P356" s="9"/>
@@ -25814,7 +22672,6 @@
         <v>3</v>
       </c>
       <c r="N359" s="8">
-        <f>_xlfn.XLOOKUP(C359,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O359" s="8"/>
@@ -26003,24 +22860,23 @@
         <v>12</v>
       </c>
       <c r="I363" s="8">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J363" s="8">
         <v>0</v>
       </c>
       <c r="K363" s="8">
-        <v>24</v>
+        <v>240</v>
       </c>
       <c r="L363" s="8">
         <v>0</v>
       </c>
       <c r="M363" s="8">
         <f t="shared" si="5"/>
-        <v>84</v>
+        <v>285</v>
       </c>
       <c r="N363" s="8">
-        <f>_xlfn.XLOOKUP(C363,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>1484</v>
+        <v>1244</v>
       </c>
       <c r="O363" s="8"/>
       <c r="P363" s="9"/>
@@ -26122,7 +22978,6 @@
         <v>1</v>
       </c>
       <c r="N365" s="8">
-        <f>_xlfn.XLOOKUP(C365,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O365" s="8"/>
@@ -26164,18 +23019,17 @@
         <v>0</v>
       </c>
       <c r="K366" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L366" s="8">
         <v>0</v>
       </c>
       <c r="M366" s="8">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N366" s="8">
-        <f>_xlfn.XLOOKUP(C366,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="O366" s="8"/>
       <c r="P366" s="9"/>
@@ -26210,24 +23064,23 @@
         <v>12</v>
       </c>
       <c r="I367" s="8">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J367" s="8">
         <v>0</v>
       </c>
       <c r="K367" s="8">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="L367" s="8">
         <v>0</v>
       </c>
       <c r="M367" s="8">
         <f t="shared" si="5"/>
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="N367" s="8">
-        <f>_xlfn.XLOOKUP(C367,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>1221</v>
+        <v>1020</v>
       </c>
       <c r="O367" s="8"/>
       <c r="P367" s="9"/>
@@ -26262,7 +23115,7 @@
         <v>12</v>
       </c>
       <c r="I368" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J368" s="8">
         <v>0</v>
@@ -26275,11 +23128,10 @@
       </c>
       <c r="M368" s="8">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N368" s="8">
-        <f>_xlfn.XLOOKUP(C368,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="O368" s="8"/>
       <c r="P368" s="9"/>
@@ -26314,13 +23166,13 @@
         <v>15</v>
       </c>
       <c r="I369" s="8">
+        <v>0</v>
+      </c>
+      <c r="J369" s="8">
+        <v>0</v>
+      </c>
+      <c r="K369" s="8">
         <v>1</v>
-      </c>
-      <c r="J369" s="8">
-        <v>0</v>
-      </c>
-      <c r="K369" s="8">
-        <v>0</v>
       </c>
       <c r="L369" s="8">
         <v>0</v>
@@ -26330,8 +23182,7 @@
         <v>1</v>
       </c>
       <c r="N369" s="8">
-        <f>_xlfn.XLOOKUP(C369,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="O369" s="8"/>
       <c r="P369" s="9"/>
@@ -26382,8 +23233,7 @@
         <v>2</v>
       </c>
       <c r="N370" s="8">
-        <f>_xlfn.XLOOKUP(C370,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="O370" s="8"/>
       <c r="P370" s="9"/>
@@ -26434,8 +23284,7 @@
         <v>3</v>
       </c>
       <c r="N371" s="8">
-        <f>_xlfn.XLOOKUP(C371,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O371" s="8"/>
       <c r="P371" s="9"/>
@@ -26486,7 +23335,6 @@
         <v>3</v>
       </c>
       <c r="N372" s="8">
-        <f>_xlfn.XLOOKUP(C372,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>39</v>
       </c>
       <c r="O372" s="8"/>
@@ -26538,7 +23386,6 @@
         <v>5</v>
       </c>
       <c r="N373" s="8">
-        <f>_xlfn.XLOOKUP(C373,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>51</v>
       </c>
       <c r="O373" s="8"/>
@@ -26641,7 +23488,6 @@
         <v>1</v>
       </c>
       <c r="N375" s="8">
-        <f>_xlfn.XLOOKUP(C375,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O375" s="8"/>
@@ -26693,7 +23539,6 @@
         <v>1</v>
       </c>
       <c r="N376" s="8">
-        <f>_xlfn.XLOOKUP(C376,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O376" s="8"/>
@@ -26745,7 +23590,6 @@
         <v>1</v>
       </c>
       <c r="N377" s="8">
-        <f>_xlfn.XLOOKUP(C377,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O377" s="8"/>
@@ -26797,7 +23641,6 @@
         <v>1</v>
       </c>
       <c r="N378" s="8">
-        <f>_xlfn.XLOOKUP(C378,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O378" s="8"/>
@@ -26849,7 +23692,6 @@
         <v>1</v>
       </c>
       <c r="N379" s="8">
-        <f>_xlfn.XLOOKUP(C379,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O379" s="8"/>
@@ -26901,7 +23743,6 @@
         <v>1</v>
       </c>
       <c r="N380" s="8">
-        <f>_xlfn.XLOOKUP(C380,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O380" s="8"/>
@@ -26953,7 +23794,6 @@
         <v>1</v>
       </c>
       <c r="N381" s="8">
-        <f>_xlfn.XLOOKUP(C381,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O381" s="8"/>
@@ -27005,7 +23845,6 @@
         <v>1</v>
       </c>
       <c r="N382" s="8">
-        <f>_xlfn.XLOOKUP(C382,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O382" s="8"/>
@@ -27057,7 +23896,6 @@
         <v>1</v>
       </c>
       <c r="N383" s="8">
-        <f>_xlfn.XLOOKUP(C383,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>0</v>
       </c>
       <c r="O383" s="8"/>
@@ -27109,8 +23947,7 @@
         <v>5</v>
       </c>
       <c r="N384" s="8">
-        <f>_xlfn.XLOOKUP(C384,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="O384" s="8"/>
       <c r="P384" s="9"/>
@@ -27145,7 +23982,7 @@
         <v>12</v>
       </c>
       <c r="I385" s="8">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="J385" s="8">
         <v>0</v>
@@ -27158,10 +23995,9 @@
       </c>
       <c r="M385" s="8">
         <f t="shared" si="5"/>
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="N385" s="8">
-        <f>_xlfn.XLOOKUP(C385,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
         <v>353</v>
       </c>
       <c r="O385" s="8"/>
@@ -27260,7 +24096,7 @@
         <v>0</v>
       </c>
       <c r="M387" s="8">
-        <f t="shared" ref="M387:M401" si="6">I387+J387+K387+L387</f>
+        <f t="shared" ref="M387:M402" si="6">I387+J387+K387+L387</f>
         <v>0</v>
       </c>
       <c r="N387" s="8">
@@ -27315,7 +24151,7 @@
         <v>0</v>
       </c>
       <c r="N388" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O388" s="8"/>
       <c r="P388" s="7"/>
@@ -27417,8 +24253,7 @@
         <v>5</v>
       </c>
       <c r="N390" s="8">
-        <f>_xlfn.XLOOKUP(C390,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="O390" s="8"/>
       <c r="P390" s="7"/>
@@ -27826,8 +24661,7 @@
         <v>0</v>
       </c>
       <c r="N398" s="8">
-        <f>_xlfn.XLOOKUP(C398,[1]SOH!$A:$A,[1]SOH!$F:$F)</f>
-        <v>275</v>
+        <v>255</v>
       </c>
       <c r="O398" s="7"/>
       <c r="P398" s="7"/>
@@ -27990,20 +24824,49 @@
       <c r="T401" s="7"/>
     </row>
     <row r="402" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A402" s="7"/>
-      <c r="B402" s="7"/>
-      <c r="C402" s="7"/>
-      <c r="D402" s="7"/>
-      <c r="E402" s="7"/>
-      <c r="F402" s="7"/>
-      <c r="G402" s="7"/>
-      <c r="H402" s="7"/>
-      <c r="I402" s="7"/>
-      <c r="J402" s="7"/>
-      <c r="K402" s="7"/>
-      <c r="L402" s="7"/>
-      <c r="M402" s="7"/>
-      <c r="N402" s="7"/>
+      <c r="A402" s="7" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B402" s="7" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C402" s="10" t="s">
+        <v>1246</v>
+      </c>
+      <c r="D402" s="10" t="s">
+        <v>701</v>
+      </c>
+      <c r="E402" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F402" s="7" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G402" s="7" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H402" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I402" s="8">
+        <v>0</v>
+      </c>
+      <c r="J402" s="8">
+        <v>0</v>
+      </c>
+      <c r="K402" s="8">
+        <v>0</v>
+      </c>
+      <c r="L402" s="8">
+        <v>0</v>
+      </c>
+      <c r="M402" s="8">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="N402" s="8">
+        <v>2</v>
+      </c>
       <c r="O402" s="7"/>
       <c r="P402" s="7"/>
       <c r="Q402" s="7"/>
@@ -36020,15 +32883,21 @@
       <c r="T766" s="7"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:T402" xr:uid="{AF55B7BF-85DC-4082-9A73-200B4D79A598}"/>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="5" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="3" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C402">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
+++ b/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\Fossil Replenishment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3302EB5-14A2-4A41-A106-F49943D5FEA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41DD4EE8-2D85-43AC-823E-B99764E8B6DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6662473D-6E1F-42FD-999B-28162E22D4B5}"/>
   </bookViews>
@@ -4800,7 +4800,7 @@
         <v>1068</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>12</v>
@@ -4851,7 +4851,7 @@
         <v>1068</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H10" s="8" t="s">
         <v>12</v>
@@ -6279,7 +6279,7 @@
         <v>1068</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H38" s="8" t="s">
         <v>12</v>
@@ -7350,7 +7350,7 @@
         <v>1068</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H59" s="8" t="s">
         <v>13</v>
@@ -7656,7 +7656,7 @@
         <v>1069</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H65" s="8" t="s">
         <v>12</v>
@@ -8166,7 +8166,7 @@
         <v>1068</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H75" s="8" t="s">
         <v>13</v>
@@ -8217,7 +8217,7 @@
         <v>1069</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H76" s="8" t="s">
         <v>13</v>
@@ -8727,7 +8727,7 @@
         <v>1068</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H86" s="8" t="s">
         <v>12</v>
@@ -8982,7 +8982,7 @@
         <v>1069</v>
       </c>
       <c r="G91" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H91" s="8" t="s">
         <v>12</v>
@@ -9084,7 +9084,7 @@
         <v>1068</v>
       </c>
       <c r="G93" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H93" s="8" t="s">
         <v>13</v>
@@ -9135,7 +9135,7 @@
         <v>1068</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H94" s="8" t="s">
         <v>12</v>
@@ -9594,7 +9594,7 @@
         <v>1068</v>
       </c>
       <c r="G103" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H103" s="8" t="s">
         <v>15</v>
@@ -10614,7 +10614,7 @@
         <v>1068</v>
       </c>
       <c r="G123" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H123" s="8" t="s">
         <v>14</v>
@@ -10767,7 +10767,7 @@
         <v>1068</v>
       </c>
       <c r="G126" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H126" s="8" t="s">
         <v>17</v>
@@ -11022,7 +11022,7 @@
         <v>1068</v>
       </c>
       <c r="G131" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H131" s="8" t="s">
         <v>14</v>
@@ -11226,7 +11226,7 @@
         <v>1069</v>
       </c>
       <c r="G135" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H135" s="8" t="s">
         <v>15</v>
@@ -11481,7 +11481,7 @@
         <v>1069</v>
       </c>
       <c r="G140" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H140" s="8" t="s">
         <v>15</v>
@@ -11940,7 +11940,7 @@
         <v>1068</v>
       </c>
       <c r="G149" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H149" s="8" t="s">
         <v>12</v>
@@ -11991,7 +11991,7 @@
         <v>1068</v>
       </c>
       <c r="G150" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H150" s="8" t="s">
         <v>12</v>
@@ -12144,7 +12144,7 @@
         <v>1068</v>
       </c>
       <c r="G153" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H153" s="8" t="s">
         <v>13</v>
@@ -12297,7 +12297,7 @@
         <v>1068</v>
       </c>
       <c r="G156" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H156" s="8" t="s">
         <v>15</v>
@@ -12450,7 +12450,7 @@
         <v>1068</v>
       </c>
       <c r="G159" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H159" s="8" t="s">
         <v>15</v>
@@ -12603,7 +12603,7 @@
         <v>1069</v>
       </c>
       <c r="G162" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H162" s="8" t="s">
         <v>13</v>
@@ -12807,7 +12807,7 @@
         <v>1068</v>
       </c>
       <c r="G166" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H166" s="8" t="s">
         <v>14</v>
@@ -13011,7 +13011,7 @@
         <v>1068</v>
       </c>
       <c r="G170" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H170" s="8" t="s">
         <v>14</v>
@@ -14490,7 +14490,7 @@
         <v>1068</v>
       </c>
       <c r="G199" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H199" s="8" t="s">
         <v>14</v>
@@ -14592,7 +14592,7 @@
         <v>1068</v>
       </c>
       <c r="G201" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H201" s="8" t="s">
         <v>12</v>
@@ -14745,7 +14745,7 @@
         <v>1068</v>
       </c>
       <c r="G204" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H204" s="8" t="s">
         <v>13</v>
@@ -14796,7 +14796,7 @@
         <v>1068</v>
       </c>
       <c r="G205" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H205" s="8" t="s">
         <v>16</v>
@@ -15000,7 +15000,7 @@
         <v>1068</v>
       </c>
       <c r="G209" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H209" s="8" t="s">
         <v>12</v>
@@ -15051,7 +15051,7 @@
         <v>1068</v>
       </c>
       <c r="G210" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H210" s="8" t="s">
         <v>13</v>
@@ -15102,7 +15102,7 @@
         <v>1068</v>
       </c>
       <c r="G211" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H211" s="8" t="s">
         <v>12</v>
@@ -15561,7 +15561,7 @@
         <v>1068</v>
       </c>
       <c r="G220" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H220" s="8" t="s">
         <v>16</v>
@@ -15765,7 +15765,7 @@
         <v>1069</v>
       </c>
       <c r="G224" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H224" s="8" t="s">
         <v>13</v>
@@ -16020,7 +16020,7 @@
         <v>1068</v>
       </c>
       <c r="G229" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H229" s="8" t="s">
         <v>15</v>
@@ -16275,7 +16275,7 @@
         <v>1068</v>
       </c>
       <c r="G234" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H234" s="8" t="s">
         <v>15</v>
@@ -16428,7 +16428,7 @@
         <v>1069</v>
       </c>
       <c r="G237" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H237" s="8" t="s">
         <v>12</v>
@@ -16530,7 +16530,7 @@
         <v>1068</v>
       </c>
       <c r="G239" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H239" s="8" t="s">
         <v>15</v>
@@ -16683,7 +16683,7 @@
         <v>1068</v>
       </c>
       <c r="G242" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H242" s="8" t="s">
         <v>12</v>
@@ -16734,7 +16734,7 @@
         <v>1069</v>
       </c>
       <c r="G243" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H243" s="8" t="s">
         <v>15</v>
@@ -16938,7 +16938,7 @@
         <v>1069</v>
       </c>
       <c r="G247" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H247" s="8" t="s">
         <v>13</v>
@@ -17091,7 +17091,7 @@
         <v>1068</v>
       </c>
       <c r="G250" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H250" s="8" t="s">
         <v>12</v>
@@ -17142,7 +17142,7 @@
         <v>1068</v>
       </c>
       <c r="G251" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H251" s="8" t="s">
         <v>14</v>
@@ -17193,7 +17193,7 @@
         <v>1068</v>
       </c>
       <c r="G252" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H252" s="8" t="s">
         <v>14</v>
@@ -17244,7 +17244,7 @@
         <v>1068</v>
       </c>
       <c r="G253" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H253" s="8" t="s">
         <v>14</v>
@@ -17295,7 +17295,7 @@
         <v>1068</v>
       </c>
       <c r="G254" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H254" s="8" t="s">
         <v>14</v>
@@ -17907,7 +17907,7 @@
         <v>1068</v>
       </c>
       <c r="G266" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H266" s="8" t="s">
         <v>14</v>
@@ -18468,7 +18468,7 @@
         <v>1068</v>
       </c>
       <c r="G277" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H277" s="8" t="s">
         <v>13</v>
@@ -18570,7 +18570,7 @@
         <v>1068</v>
       </c>
       <c r="G279" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H279" s="8" t="s">
         <v>13</v>
@@ -19131,7 +19131,7 @@
         <v>1068</v>
       </c>
       <c r="G290" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H290" s="8" t="s">
         <v>14</v>
@@ -19284,7 +19284,7 @@
         <v>1068</v>
       </c>
       <c r="G293" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H293" s="8" t="s">
         <v>12</v>
@@ -19335,7 +19335,7 @@
         <v>1068</v>
       </c>
       <c r="G294" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H294" s="8" t="s">
         <v>12</v>
@@ -19488,7 +19488,7 @@
         <v>1068</v>
       </c>
       <c r="G297" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H297" s="8" t="s">
         <v>17</v>
@@ -19539,7 +19539,7 @@
         <v>1068</v>
       </c>
       <c r="G298" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H298" s="8" t="s">
         <v>14</v>
@@ -20508,7 +20508,7 @@
         <v>1068</v>
       </c>
       <c r="G317" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H317" s="8" t="s">
         <v>12</v>
@@ -22191,7 +22191,7 @@
         <v>1068</v>
       </c>
       <c r="G350" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H350" s="8" t="s">
         <v>13</v>
@@ -22242,7 +22242,7 @@
         <v>1068</v>
       </c>
       <c r="G351" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H351" s="8" t="s">
         <v>15</v>
@@ -22599,7 +22599,7 @@
         <v>1068</v>
       </c>
       <c r="G358" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H358" s="8" t="s">
         <v>13</v>
@@ -23721,7 +23721,7 @@
         <v>1068</v>
       </c>
       <c r="G380" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H380" s="8" t="s">
         <v>12</v>
@@ -23772,7 +23772,7 @@
         <v>1068</v>
       </c>
       <c r="G381" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H381" s="8" t="s">
         <v>17</v>
@@ -24180,7 +24180,7 @@
         <v>1068</v>
       </c>
       <c r="G389" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H389" s="8" t="s">
         <v>12</v>
@@ -24639,7 +24639,7 @@
         <v>418</v>
       </c>
       <c r="G398" s="7" t="s">
-        <v>418</v>
+        <v>1062</v>
       </c>
       <c r="H398" s="7" t="s">
         <v>15</v>
@@ -24791,8 +24791,8 @@
       <c r="F401" s="7" t="s">
         <v>1068</v>
       </c>
-      <c r="G401" s="7" t="s">
-        <v>1061</v>
+      <c r="G401" s="8" t="s">
+        <v>1062</v>
       </c>
       <c r="H401" s="7" t="s">
         <v>15</v>

--- a/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
+++ b/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\Fossil Replenishment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41DD4EE8-2D85-43AC-823E-B99764E8B6DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED659486-E664-421E-9999-0EBD0A5D8EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6662473D-6E1F-42FD-999B-28162E22D4B5}"/>
   </bookViews>
@@ -18,19 +18,10 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$T$402</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -4449,23 +4440,23 @@
         <v>12</v>
       </c>
       <c r="I2" s="8">
-        <v>449</v>
+        <v>572</v>
       </c>
       <c r="J2" s="8">
         <v>0</v>
       </c>
       <c r="K2" s="8">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="L2" s="8">
         <v>0</v>
       </c>
       <c r="M2" s="8">
         <f>I2+J2+K2+L2</f>
-        <v>593</v>
+        <v>693</v>
       </c>
       <c r="N2" s="8">
-        <v>1767</v>
+        <v>1671</v>
       </c>
       <c r="O2" s="8"/>
       <c r="P2" s="8"/>
@@ -4500,7 +4491,7 @@
         <v>12</v>
       </c>
       <c r="I3" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3" s="8">
         <v>0</v>
@@ -4513,7 +4504,7 @@
       </c>
       <c r="M3" s="8">
         <f t="shared" ref="M3:M66" si="0">I3+J3+K3+L3</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N3" s="8">
         <v>0</v>
@@ -4551,7 +4542,7 @@
         <v>12</v>
       </c>
       <c r="I4" s="8">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="J4" s="8">
         <v>0</v>
@@ -4564,7 +4555,7 @@
       </c>
       <c r="M4" s="8">
         <f t="shared" si="0"/>
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="N4" s="8">
         <v>0</v>
@@ -4602,7 +4593,7 @@
         <v>12</v>
       </c>
       <c r="I5" s="8">
-        <v>270</v>
+        <v>236</v>
       </c>
       <c r="J5" s="8">
         <v>0</v>
@@ -4615,10 +4606,10 @@
       </c>
       <c r="M5" s="8">
         <f t="shared" si="0"/>
-        <v>270</v>
+        <v>236</v>
       </c>
       <c r="N5" s="8">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="O5" s="8"/>
       <c r="P5" s="8"/>
@@ -4653,23 +4644,23 @@
         <v>12</v>
       </c>
       <c r="I6" s="8">
-        <v>446</v>
+        <v>632</v>
       </c>
       <c r="J6" s="8">
         <v>0</v>
       </c>
       <c r="K6" s="8">
-        <v>240</v>
+        <v>146</v>
       </c>
       <c r="L6" s="8">
         <v>0</v>
       </c>
       <c r="M6" s="8">
         <f t="shared" si="0"/>
-        <v>686</v>
+        <v>778</v>
       </c>
       <c r="N6" s="8">
-        <v>2175</v>
+        <v>2030</v>
       </c>
       <c r="O6" s="8"/>
       <c r="P6" s="8"/>
@@ -4704,23 +4695,23 @@
         <v>12</v>
       </c>
       <c r="I7" s="8">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J7" s="8">
         <v>0</v>
       </c>
       <c r="K7" s="8">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="L7" s="8">
         <v>0</v>
       </c>
       <c r="M7" s="8">
         <f t="shared" si="0"/>
-        <v>58</v>
+        <v>178</v>
       </c>
       <c r="N7" s="8">
-        <v>540</v>
+        <v>303</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
@@ -4755,23 +4746,23 @@
         <v>12</v>
       </c>
       <c r="I8" s="8">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="J8" s="8">
         <v>0</v>
       </c>
       <c r="K8" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L8" s="8">
         <v>0</v>
       </c>
       <c r="M8" s="8">
         <f t="shared" si="0"/>
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N8" s="8">
-        <v>873</v>
+        <v>681</v>
       </c>
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
@@ -4806,7 +4797,7 @@
         <v>12</v>
       </c>
       <c r="I9" s="8">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="J9" s="8">
         <v>0</v>
@@ -4819,10 +4810,10 @@
       </c>
       <c r="M9" s="8">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N9" s="8">
-        <v>649</v>
+        <v>562</v>
       </c>
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
@@ -4857,23 +4848,23 @@
         <v>12</v>
       </c>
       <c r="I10" s="8">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="J10" s="8">
         <v>0</v>
       </c>
       <c r="K10" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L10" s="8">
         <v>0</v>
       </c>
       <c r="M10" s="8">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N10" s="8">
-        <v>621</v>
+        <v>503</v>
       </c>
       <c r="O10" s="8"/>
       <c r="P10" s="8"/>
@@ -4908,23 +4899,23 @@
         <v>12</v>
       </c>
       <c r="I11" s="8">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="J11" s="8">
         <v>0</v>
       </c>
       <c r="K11" s="8">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="L11" s="8">
         <v>0</v>
       </c>
       <c r="M11" s="8">
         <f t="shared" si="0"/>
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="N11" s="8">
-        <v>477</v>
+        <v>300</v>
       </c>
       <c r="O11" s="8"/>
       <c r="P11" s="8"/>
@@ -4959,23 +4950,23 @@
         <v>12</v>
       </c>
       <c r="I12" s="8">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J12" s="8">
         <v>0</v>
       </c>
       <c r="K12" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L12" s="8">
         <v>0</v>
       </c>
       <c r="M12" s="8">
         <f t="shared" si="0"/>
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="N12" s="8">
-        <v>1190</v>
+        <v>858</v>
       </c>
       <c r="O12" s="8"/>
       <c r="P12" s="8"/>
@@ -5010,23 +5001,23 @@
         <v>12</v>
       </c>
       <c r="I13" s="8">
-        <v>208</v>
+        <v>179</v>
       </c>
       <c r="J13" s="8">
         <v>0</v>
       </c>
       <c r="K13" s="8">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="L13" s="8">
         <v>0</v>
       </c>
       <c r="M13" s="8">
         <f t="shared" si="0"/>
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="N13" s="8">
-        <v>1046</v>
+        <v>998</v>
       </c>
       <c r="O13" s="8"/>
       <c r="P13" s="8"/>
@@ -5061,13 +5052,13 @@
         <v>12</v>
       </c>
       <c r="I14" s="8">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J14" s="8">
         <v>0</v>
       </c>
       <c r="K14" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L14" s="8">
         <v>0</v>
@@ -5077,7 +5068,7 @@
         <v>23</v>
       </c>
       <c r="N14" s="8">
-        <v>1401</v>
+        <v>1268</v>
       </c>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
@@ -5118,17 +5109,17 @@
         <v>0</v>
       </c>
       <c r="K15" s="8">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L15" s="8">
         <v>0</v>
       </c>
       <c r="M15" s="8">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N15" s="8">
-        <v>318</v>
+        <v>276</v>
       </c>
       <c r="O15" s="8"/>
       <c r="P15" s="8"/>
@@ -5163,23 +5154,23 @@
         <v>12</v>
       </c>
       <c r="I16" s="8">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="J16" s="8">
         <v>0</v>
       </c>
       <c r="K16" s="8">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L16" s="8">
         <v>0</v>
       </c>
       <c r="M16" s="8">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="N16" s="8">
-        <v>731</v>
+        <v>661</v>
       </c>
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
@@ -5214,7 +5205,7 @@
         <v>12</v>
       </c>
       <c r="I17" s="8">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="J17" s="8">
         <v>0</v>
@@ -5227,10 +5218,10 @@
       </c>
       <c r="M17" s="8">
         <f t="shared" si="0"/>
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="N17" s="8">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="O17" s="8"/>
       <c r="P17" s="8"/>
@@ -5265,7 +5256,7 @@
         <v>12</v>
       </c>
       <c r="I18" s="8">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="J18" s="8">
         <v>0</v>
@@ -5278,10 +5269,10 @@
       </c>
       <c r="M18" s="8">
         <f t="shared" si="0"/>
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="N18" s="8">
-        <v>825</v>
+        <v>636</v>
       </c>
       <c r="O18" s="8"/>
       <c r="P18" s="8"/>
@@ -5316,7 +5307,7 @@
         <v>13</v>
       </c>
       <c r="I19" s="8">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J19" s="8">
         <v>0</v>
@@ -5329,10 +5320,10 @@
       </c>
       <c r="M19" s="8">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N19" s="8">
-        <v>843</v>
+        <v>618</v>
       </c>
       <c r="O19" s="8"/>
       <c r="P19" s="8"/>
@@ -5373,17 +5364,17 @@
         <v>0</v>
       </c>
       <c r="K20" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L20" s="8">
         <v>0</v>
       </c>
       <c r="M20" s="8">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N20" s="8">
-        <v>243</v>
+        <v>142</v>
       </c>
       <c r="O20" s="8"/>
       <c r="P20" s="8"/>
@@ -5418,23 +5409,23 @@
         <v>13</v>
       </c>
       <c r="I21" s="8">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="J21" s="8">
         <v>0</v>
       </c>
       <c r="K21" s="8">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L21" s="8">
         <v>0</v>
       </c>
       <c r="M21" s="8">
         <f t="shared" si="0"/>
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N21" s="8">
-        <v>381</v>
+        <v>104</v>
       </c>
       <c r="O21" s="8"/>
       <c r="P21" s="8"/>
@@ -5469,7 +5460,7 @@
         <v>12</v>
       </c>
       <c r="I22" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" s="8">
         <v>0</v>
@@ -5482,7 +5473,7 @@
       </c>
       <c r="M22" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" s="8">
         <v>0</v>
@@ -5520,7 +5511,7 @@
         <v>12</v>
       </c>
       <c r="I23" s="8">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J23" s="8">
         <v>0</v>
@@ -5533,10 +5524,10 @@
       </c>
       <c r="M23" s="8">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="N23" s="8">
-        <v>407</v>
+        <v>166</v>
       </c>
       <c r="O23" s="8"/>
       <c r="P23" s="8"/>
@@ -5587,7 +5578,7 @@
         <v>12</v>
       </c>
       <c r="N24" s="8">
-        <v>256</v>
+        <v>762</v>
       </c>
       <c r="O24" s="8"/>
       <c r="P24" s="8"/>
@@ -5673,7 +5664,7 @@
         <v>12</v>
       </c>
       <c r="I26" s="8">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J26" s="8">
         <v>0</v>
@@ -5686,10 +5677,10 @@
       </c>
       <c r="M26" s="8">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="N26" s="8">
-        <v>1263</v>
+        <v>1003</v>
       </c>
       <c r="O26" s="8"/>
       <c r="P26" s="8"/>
@@ -5724,23 +5715,23 @@
         <v>12</v>
       </c>
       <c r="I27" s="8">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J27" s="8">
         <v>0</v>
       </c>
       <c r="K27" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L27" s="8">
         <v>0</v>
       </c>
       <c r="M27" s="8">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N27" s="8">
-        <v>943</v>
+        <v>904</v>
       </c>
       <c r="O27" s="8"/>
       <c r="P27" s="8"/>
@@ -5775,7 +5766,7 @@
         <v>12</v>
       </c>
       <c r="I28" s="8">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="J28" s="8">
         <v>0</v>
@@ -5788,7 +5779,7 @@
       </c>
       <c r="M28" s="8">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="N28" s="8">
         <v>0</v>
@@ -5826,7 +5817,7 @@
         <v>13</v>
       </c>
       <c r="I29" s="8">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J29" s="8">
         <v>0</v>
@@ -5839,10 +5830,10 @@
       </c>
       <c r="M29" s="8">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N29" s="8">
-        <v>723</v>
+        <v>598</v>
       </c>
       <c r="O29" s="8"/>
       <c r="P29" s="8"/>
@@ -5877,7 +5868,7 @@
         <v>14</v>
       </c>
       <c r="I30" s="8">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J30" s="8">
         <v>0</v>
@@ -5890,10 +5881,10 @@
       </c>
       <c r="M30" s="8">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N30" s="8">
-        <v>1215</v>
+        <v>1155</v>
       </c>
       <c r="O30" s="8"/>
       <c r="P30" s="8"/>
@@ -5928,7 +5919,7 @@
         <v>13</v>
       </c>
       <c r="I31" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="8">
         <v>0</v>
@@ -5941,7 +5932,7 @@
       </c>
       <c r="M31" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N31" s="8">
         <v>0</v>
@@ -5979,7 +5970,7 @@
         <v>12</v>
       </c>
       <c r="I32" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J32" s="8">
         <v>0</v>
@@ -5992,10 +5983,10 @@
       </c>
       <c r="M32" s="8">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N32" s="8">
-        <v>852</v>
+        <v>820</v>
       </c>
       <c r="O32" s="8"/>
       <c r="P32" s="8"/>
@@ -6030,23 +6021,23 @@
         <v>12</v>
       </c>
       <c r="I33" s="8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J33" s="8">
         <v>0</v>
       </c>
       <c r="K33" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="8">
         <v>0</v>
       </c>
       <c r="M33" s="8">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="N33" s="8">
-        <v>455</v>
+        <v>389</v>
       </c>
       <c r="O33" s="8"/>
       <c r="P33" s="8"/>
@@ -6081,23 +6072,23 @@
         <v>12</v>
       </c>
       <c r="I34" s="8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J34" s="8">
         <v>0</v>
       </c>
       <c r="K34" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L34" s="8">
         <v>0</v>
       </c>
       <c r="M34" s="8">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N34" s="8">
-        <v>1102</v>
+        <v>1082</v>
       </c>
       <c r="O34" s="8"/>
       <c r="P34" s="8"/>
@@ -6148,7 +6139,7 @@
         <v>17</v>
       </c>
       <c r="N35" s="8">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="O35" s="8"/>
       <c r="P35" s="8"/>
@@ -6199,7 +6190,7 @@
         <v>15</v>
       </c>
       <c r="N36" s="8">
-        <v>309</v>
+        <v>792</v>
       </c>
       <c r="O36" s="8"/>
       <c r="P36" s="8"/>
@@ -6234,7 +6225,7 @@
         <v>13</v>
       </c>
       <c r="I37" s="8">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="J37" s="8">
         <v>0</v>
@@ -6247,10 +6238,10 @@
       </c>
       <c r="M37" s="8">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="N37" s="8">
-        <v>484</v>
+        <v>769</v>
       </c>
       <c r="O37" s="8"/>
       <c r="P37" s="8"/>
@@ -6285,7 +6276,7 @@
         <v>12</v>
       </c>
       <c r="I38" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J38" s="8">
         <v>0</v>
@@ -6298,10 +6289,10 @@
       </c>
       <c r="M38" s="8">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N38" s="8">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="O38" s="8"/>
       <c r="P38" s="8"/>
@@ -6336,23 +6327,23 @@
         <v>12</v>
       </c>
       <c r="I39" s="8">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J39" s="8">
         <v>0</v>
       </c>
       <c r="K39" s="8">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L39" s="8">
         <v>0</v>
       </c>
       <c r="M39" s="8">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="N39" s="8">
-        <v>2048</v>
+        <v>1762</v>
       </c>
       <c r="O39" s="8"/>
       <c r="P39" s="8"/>
@@ -6387,23 +6378,23 @@
         <v>12</v>
       </c>
       <c r="I40" s="8">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J40" s="8">
         <v>0</v>
       </c>
       <c r="K40" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L40" s="8">
         <v>0</v>
       </c>
       <c r="M40" s="8">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N40" s="8">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="O40" s="8"/>
       <c r="P40" s="8"/>
@@ -6438,13 +6429,13 @@
         <v>12</v>
       </c>
       <c r="I41" s="8">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J41" s="8">
         <v>0</v>
       </c>
       <c r="K41" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L41" s="8">
         <v>0</v>
@@ -6454,7 +6445,7 @@
         <v>22</v>
       </c>
       <c r="N41" s="8">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="O41" s="8"/>
       <c r="P41" s="8"/>
@@ -6489,13 +6480,13 @@
         <v>13</v>
       </c>
       <c r="I42" s="8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J42" s="8">
         <v>0</v>
       </c>
       <c r="K42" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" s="8">
         <v>0</v>
@@ -6505,7 +6496,7 @@
         <v>15</v>
       </c>
       <c r="N42" s="8">
-        <v>903</v>
+        <v>687</v>
       </c>
       <c r="O42" s="8"/>
       <c r="P42" s="8"/>
@@ -6540,7 +6531,7 @@
         <v>12</v>
       </c>
       <c r="I43" s="8">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J43" s="8">
         <v>0</v>
@@ -6553,10 +6544,10 @@
       </c>
       <c r="M43" s="8">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="N43" s="8">
-        <v>172</v>
+        <v>62</v>
       </c>
       <c r="O43" s="8"/>
       <c r="P43" s="8"/>
@@ -6591,13 +6582,13 @@
         <v>12</v>
       </c>
       <c r="I44" s="8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J44" s="8">
         <v>0</v>
       </c>
       <c r="K44" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="8">
         <v>0</v>
@@ -6607,7 +6598,7 @@
         <v>11</v>
       </c>
       <c r="N44" s="8">
-        <v>555</v>
+        <v>513</v>
       </c>
       <c r="O44" s="8"/>
       <c r="P44" s="8"/>
@@ -6642,13 +6633,13 @@
         <v>12</v>
       </c>
       <c r="I45" s="8">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J45" s="8">
         <v>0</v>
       </c>
       <c r="K45" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L45" s="8">
         <v>0</v>
@@ -6658,7 +6649,7 @@
         <v>15</v>
       </c>
       <c r="N45" s="8">
-        <v>925</v>
+        <v>897</v>
       </c>
       <c r="O45" s="8"/>
       <c r="P45" s="8"/>
@@ -6693,13 +6684,13 @@
         <v>12</v>
       </c>
       <c r="I46" s="8">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J46" s="8">
         <v>0</v>
       </c>
       <c r="K46" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L46" s="8">
         <v>0</v>
@@ -6709,7 +6700,7 @@
         <v>15</v>
       </c>
       <c r="N46" s="8">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="O46" s="8"/>
       <c r="P46" s="8"/>
@@ -6744,7 +6735,7 @@
         <v>13</v>
       </c>
       <c r="I47" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J47" s="8">
         <v>0</v>
@@ -6757,10 +6748,10 @@
       </c>
       <c r="M47" s="8">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N47" s="8">
-        <v>437</v>
+        <v>282</v>
       </c>
       <c r="O47" s="8"/>
       <c r="P47" s="8"/>
@@ -6795,7 +6786,7 @@
         <v>12</v>
       </c>
       <c r="I48" s="8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J48" s="8">
         <v>0</v>
@@ -6808,10 +6799,10 @@
       </c>
       <c r="M48" s="8">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N48" s="8">
-        <v>1201</v>
+        <v>1188</v>
       </c>
       <c r="O48" s="8"/>
       <c r="P48" s="8"/>
@@ -6846,7 +6837,7 @@
         <v>12</v>
       </c>
       <c r="I49" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J49" s="8">
         <v>0</v>
@@ -6859,10 +6850,10 @@
       </c>
       <c r="M49" s="8">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N49" s="8">
-        <v>1084</v>
+        <v>1033</v>
       </c>
       <c r="O49" s="8"/>
       <c r="P49" s="8"/>
@@ -6897,7 +6888,7 @@
         <v>15</v>
       </c>
       <c r="I50" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J50" s="8">
         <v>0</v>
@@ -6910,10 +6901,10 @@
       </c>
       <c r="M50" s="8">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N50" s="8">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="O50" s="8"/>
       <c r="P50" s="8"/>
@@ -6948,13 +6939,13 @@
         <v>12</v>
       </c>
       <c r="I51" s="8">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J51" s="8">
         <v>0</v>
       </c>
       <c r="K51" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L51" s="8">
         <v>0</v>
@@ -6964,7 +6955,7 @@
         <v>24</v>
       </c>
       <c r="N51" s="8">
-        <v>492</v>
+        <v>459</v>
       </c>
       <c r="O51" s="8"/>
       <c r="P51" s="8"/>
@@ -6999,23 +6990,23 @@
         <v>12</v>
       </c>
       <c r="I52" s="8">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="J52" s="8">
         <v>0</v>
       </c>
       <c r="K52" s="8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L52" s="8">
         <v>0</v>
       </c>
       <c r="M52" s="8">
         <f t="shared" si="0"/>
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="N52" s="8">
-        <v>1343</v>
+        <v>1239</v>
       </c>
       <c r="O52" s="8"/>
       <c r="P52" s="8"/>
@@ -7050,13 +7041,13 @@
         <v>12</v>
       </c>
       <c r="I53" s="8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J53" s="8">
         <v>0</v>
       </c>
       <c r="K53" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L53" s="8">
         <v>0</v>
@@ -7066,7 +7057,7 @@
         <v>9</v>
       </c>
       <c r="N53" s="8">
-        <v>195</v>
+        <v>167</v>
       </c>
       <c r="O53" s="8"/>
       <c r="P53" s="8"/>
@@ -7101,7 +7092,7 @@
         <v>12</v>
       </c>
       <c r="I54" s="8">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J54" s="8">
         <v>0</v>
@@ -7114,10 +7105,10 @@
       </c>
       <c r="M54" s="8">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N54" s="8">
-        <v>652</v>
+        <v>489</v>
       </c>
       <c r="O54" s="8"/>
       <c r="P54" s="8"/>
@@ -7152,23 +7143,23 @@
         <v>12</v>
       </c>
       <c r="I55" s="8">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="J55" s="8">
         <v>0</v>
       </c>
       <c r="K55" s="8">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="L55" s="8">
         <v>0</v>
       </c>
       <c r="M55" s="8">
         <f t="shared" si="0"/>
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="N55" s="8">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="O55" s="8"/>
       <c r="P55" s="8"/>
@@ -7203,7 +7194,7 @@
         <v>14</v>
       </c>
       <c r="I56" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J56" s="8">
         <v>0</v>
@@ -7216,10 +7207,10 @@
       </c>
       <c r="M56" s="8">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N56" s="8">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="O56" s="8"/>
       <c r="P56" s="8"/>
@@ -7254,23 +7245,23 @@
         <v>12</v>
       </c>
       <c r="I57" s="8">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J57" s="8">
         <v>0</v>
       </c>
       <c r="K57" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L57" s="8">
         <v>0</v>
       </c>
       <c r="M57" s="8">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N57" s="8">
-        <v>690</v>
+        <v>525</v>
       </c>
       <c r="O57" s="8"/>
       <c r="P57" s="8"/>
@@ -7321,7 +7312,7 @@
         <v>6</v>
       </c>
       <c r="N58" s="8">
-        <v>683</v>
+        <v>669</v>
       </c>
       <c r="O58" s="8"/>
       <c r="P58" s="8"/>
@@ -7372,7 +7363,7 @@
         <v>9</v>
       </c>
       <c r="N59" s="8">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="O59" s="8"/>
       <c r="P59" s="8"/>
@@ -7423,7 +7414,7 @@
         <v>5</v>
       </c>
       <c r="N60" s="8">
-        <v>781</v>
+        <v>728</v>
       </c>
       <c r="O60" s="8"/>
       <c r="P60" s="8"/>
@@ -7458,23 +7449,23 @@
         <v>12</v>
       </c>
       <c r="I61" s="8">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J61" s="8">
         <v>0</v>
       </c>
       <c r="K61" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L61" s="8">
         <v>0</v>
       </c>
       <c r="M61" s="8">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N61" s="8">
-        <v>919</v>
+        <v>639</v>
       </c>
       <c r="O61" s="8"/>
       <c r="P61" s="8"/>
@@ -7509,7 +7500,7 @@
         <v>12</v>
       </c>
       <c r="I62" s="8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J62" s="8">
         <v>0</v>
@@ -7522,10 +7513,10 @@
       </c>
       <c r="M62" s="8">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N62" s="8">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="O62" s="8"/>
       <c r="P62" s="8"/>
@@ -7576,7 +7567,7 @@
         <v>7</v>
       </c>
       <c r="N63" s="8">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="O63" s="8"/>
       <c r="P63" s="8"/>
@@ -7611,7 +7602,7 @@
         <v>13</v>
       </c>
       <c r="I64" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J64" s="8">
         <v>0</v>
@@ -7624,10 +7615,10 @@
       </c>
       <c r="M64" s="8">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N64" s="8">
-        <v>52</v>
+        <v>183</v>
       </c>
       <c r="O64" s="8"/>
       <c r="P64" s="8"/>
@@ -7662,7 +7653,7 @@
         <v>12</v>
       </c>
       <c r="I65" s="8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J65" s="8">
         <v>0</v>
@@ -7675,10 +7666,10 @@
       </c>
       <c r="M65" s="8">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N65" s="8">
-        <v>883</v>
+        <v>994</v>
       </c>
       <c r="O65" s="8"/>
       <c r="P65" s="8"/>
@@ -7729,7 +7720,7 @@
         <v>4</v>
       </c>
       <c r="N66" s="8">
-        <v>276</v>
+        <v>241</v>
       </c>
       <c r="O66" s="8"/>
       <c r="P66" s="8"/>
@@ -7780,7 +7771,7 @@
         <v>5</v>
       </c>
       <c r="N67" s="8">
-        <v>409</v>
+        <v>227</v>
       </c>
       <c r="O67" s="8"/>
       <c r="P67" s="8"/>
@@ -7831,7 +7822,7 @@
         <v>6</v>
       </c>
       <c r="N68" s="8">
-        <v>1013</v>
+        <v>990</v>
       </c>
       <c r="O68" s="8"/>
       <c r="P68" s="8"/>
@@ -7872,17 +7863,17 @@
         <v>0</v>
       </c>
       <c r="K69" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L69" s="8">
         <v>0</v>
       </c>
       <c r="M69" s="8">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N69" s="8">
-        <v>304</v>
+        <v>278</v>
       </c>
       <c r="O69" s="8"/>
       <c r="P69" s="8"/>
@@ -7917,7 +7908,7 @@
         <v>16</v>
       </c>
       <c r="I70" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J70" s="8">
         <v>0</v>
@@ -7930,10 +7921,10 @@
       </c>
       <c r="M70" s="8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N70" s="8">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="O70" s="8"/>
       <c r="P70" s="8"/>
@@ -7984,7 +7975,7 @@
         <v>8</v>
       </c>
       <c r="N71" s="8">
-        <v>113</v>
+        <v>12</v>
       </c>
       <c r="O71" s="8"/>
       <c r="P71" s="8"/>
@@ -8035,7 +8026,7 @@
         <v>10</v>
       </c>
       <c r="N72" s="8">
-        <v>301</v>
+        <v>404</v>
       </c>
       <c r="O72" s="8"/>
       <c r="P72" s="8"/>
@@ -8070,23 +8061,23 @@
         <v>12</v>
       </c>
       <c r="I73" s="8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J73" s="8">
         <v>0</v>
       </c>
       <c r="K73" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L73" s="8">
         <v>0</v>
       </c>
       <c r="M73" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N73" s="8">
-        <v>985</v>
+        <v>792</v>
       </c>
       <c r="O73" s="8"/>
       <c r="P73" s="8"/>
@@ -8121,7 +8112,7 @@
         <v>14</v>
       </c>
       <c r="I74" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J74" s="8">
         <v>0</v>
@@ -8134,10 +8125,10 @@
       </c>
       <c r="M74" s="8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N74" s="8">
-        <v>326</v>
+        <v>251</v>
       </c>
       <c r="O74" s="8"/>
       <c r="P74" s="8"/>
@@ -8188,7 +8179,7 @@
         <v>8</v>
       </c>
       <c r="N75" s="8">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O75" s="8"/>
       <c r="P75" s="8"/>
@@ -8239,7 +8230,7 @@
         <v>7</v>
       </c>
       <c r="N76" s="8">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="O76" s="8"/>
       <c r="P76" s="8"/>
@@ -8274,7 +8265,7 @@
         <v>12</v>
       </c>
       <c r="I77" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J77" s="8">
         <v>0</v>
@@ -8287,10 +8278,10 @@
       </c>
       <c r="M77" s="8">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N77" s="8">
-        <v>669</v>
+        <v>445</v>
       </c>
       <c r="O77" s="8"/>
       <c r="P77" s="8"/>
@@ -8325,13 +8316,13 @@
         <v>12</v>
       </c>
       <c r="I78" s="8">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J78" s="8">
         <v>0</v>
       </c>
       <c r="K78" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L78" s="8">
         <v>0</v>
@@ -8341,7 +8332,7 @@
         <v>21</v>
       </c>
       <c r="N78" s="8">
-        <v>742</v>
+        <v>675</v>
       </c>
       <c r="O78" s="8"/>
       <c r="P78" s="8"/>
@@ -8392,7 +8383,7 @@
         <v>9</v>
       </c>
       <c r="N79" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O79" s="8"/>
       <c r="P79" s="8"/>
@@ -8478,7 +8469,7 @@
         <v>15</v>
       </c>
       <c r="I81" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J81" s="8">
         <v>0</v>
@@ -8491,7 +8482,7 @@
       </c>
       <c r="M81" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N81" s="8">
         <v>0</v>
@@ -8545,7 +8536,7 @@
         <v>3</v>
       </c>
       <c r="N82" s="8">
-        <v>384</v>
+        <v>350</v>
       </c>
       <c r="O82" s="8"/>
       <c r="P82" s="8"/>
@@ -8596,7 +8587,7 @@
         <v>6</v>
       </c>
       <c r="N83" s="8">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="O83" s="8"/>
       <c r="P83" s="8"/>
@@ -8631,7 +8622,7 @@
         <v>13</v>
       </c>
       <c r="I84" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J84" s="8">
         <v>0</v>
@@ -8644,10 +8635,10 @@
       </c>
       <c r="M84" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N84" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O84" s="8"/>
       <c r="P84" s="8"/>
@@ -8698,7 +8689,7 @@
         <v>6</v>
       </c>
       <c r="N85" s="8">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="O85" s="8"/>
       <c r="P85" s="8"/>
@@ -8733,7 +8724,7 @@
         <v>12</v>
       </c>
       <c r="I86" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J86" s="8">
         <v>0</v>
@@ -8746,10 +8737,10 @@
       </c>
       <c r="M86" s="8">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N86" s="8">
-        <v>720</v>
+        <v>671</v>
       </c>
       <c r="O86" s="8"/>
       <c r="P86" s="8"/>
@@ -8784,7 +8775,7 @@
         <v>13</v>
       </c>
       <c r="I87" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J87" s="8">
         <v>0</v>
@@ -8797,10 +8788,10 @@
       </c>
       <c r="M87" s="8">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N87" s="8">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="O87" s="8"/>
       <c r="P87" s="8"/>
@@ -8835,23 +8826,23 @@
         <v>12</v>
       </c>
       <c r="I88" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J88" s="8">
         <v>0</v>
       </c>
       <c r="K88" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="8">
         <v>0</v>
       </c>
       <c r="M88" s="8">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N88" s="8">
-        <v>265</v>
+        <v>155</v>
       </c>
       <c r="O88" s="8"/>
       <c r="P88" s="8"/>
@@ -8886,23 +8877,23 @@
         <v>12</v>
       </c>
       <c r="I89" s="8">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J89" s="8">
         <v>0</v>
       </c>
       <c r="K89" s="8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L89" s="8">
         <v>0</v>
       </c>
       <c r="M89" s="8">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="N89" s="8">
-        <v>253</v>
+        <v>191</v>
       </c>
       <c r="O89" s="8"/>
       <c r="P89" s="8"/>
@@ -8988,7 +8979,7 @@
         <v>12</v>
       </c>
       <c r="I91" s="8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J91" s="8">
         <v>0</v>
@@ -9001,10 +8992,10 @@
       </c>
       <c r="M91" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N91" s="8">
-        <v>1307</v>
+        <v>1273</v>
       </c>
       <c r="O91" s="8"/>
       <c r="P91" s="8"/>
@@ -9055,7 +9046,7 @@
         <v>7</v>
       </c>
       <c r="N92" s="8">
-        <v>296</v>
+        <v>155</v>
       </c>
       <c r="O92" s="8"/>
       <c r="P92" s="8"/>
@@ -9096,17 +9087,17 @@
         <v>0</v>
       </c>
       <c r="K93" s="8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L93" s="8">
         <v>0</v>
       </c>
       <c r="M93" s="8">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N93" s="8">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="O93" s="8"/>
       <c r="P93" s="8"/>
@@ -9208,7 +9199,7 @@
         <v>9</v>
       </c>
       <c r="N95" s="8">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="O95" s="8"/>
       <c r="P95" s="8"/>
@@ -9249,17 +9240,17 @@
         <v>0</v>
       </c>
       <c r="K96" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L96" s="8">
         <v>0</v>
       </c>
       <c r="M96" s="8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N96" s="8">
-        <v>130</v>
+        <v>188</v>
       </c>
       <c r="O96" s="8"/>
       <c r="P96" s="8"/>
@@ -9294,23 +9285,23 @@
         <v>14</v>
       </c>
       <c r="I97" s="8">
+        <v>9</v>
+      </c>
+      <c r="J97" s="8">
+        <v>0</v>
+      </c>
+      <c r="K97" s="8">
         <v>3</v>
-      </c>
-      <c r="J97" s="8">
-        <v>0</v>
-      </c>
-      <c r="K97" s="8">
-        <v>6</v>
       </c>
       <c r="L97" s="8">
         <v>0</v>
       </c>
       <c r="M97" s="8">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="N97" s="8">
-        <v>349</v>
+        <v>293</v>
       </c>
       <c r="O97" s="8"/>
       <c r="P97" s="8"/>
@@ -9412,7 +9403,7 @@
         <v>0</v>
       </c>
       <c r="N99" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O99" s="8"/>
       <c r="P99" s="8"/>
@@ -9447,7 +9438,7 @@
         <v>15</v>
       </c>
       <c r="I100" s="8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J100" s="8">
         <v>0</v>
@@ -9460,10 +9451,10 @@
       </c>
       <c r="M100" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N100" s="8">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O100" s="8"/>
       <c r="P100" s="8"/>
@@ -9555,17 +9546,17 @@
         <v>0</v>
       </c>
       <c r="K102" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L102" s="8">
         <v>0</v>
       </c>
       <c r="M102" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N102" s="8">
-        <v>582</v>
+        <v>517</v>
       </c>
       <c r="O102" s="8"/>
       <c r="P102" s="8"/>
@@ -9616,7 +9607,7 @@
         <v>4</v>
       </c>
       <c r="N103" s="8">
-        <v>623</v>
+        <v>588</v>
       </c>
       <c r="O103" s="8"/>
       <c r="P103" s="8"/>
@@ -9702,13 +9693,13 @@
         <v>12</v>
       </c>
       <c r="I105" s="8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J105" s="8">
         <v>0</v>
       </c>
       <c r="K105" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L105" s="8">
         <v>0</v>
@@ -9718,7 +9709,7 @@
         <v>8</v>
       </c>
       <c r="N105" s="8">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="O105" s="8"/>
       <c r="P105" s="8"/>
@@ -9769,7 +9760,7 @@
         <v>6</v>
       </c>
       <c r="N106" s="8">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="O106" s="8"/>
       <c r="P106" s="8"/>
@@ -9820,7 +9811,7 @@
         <v>4</v>
       </c>
       <c r="N107" s="8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O107" s="8"/>
       <c r="P107" s="8"/>
@@ -9855,7 +9846,7 @@
         <v>15</v>
       </c>
       <c r="I108" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J108" s="8">
         <v>0</v>
@@ -9868,7 +9859,7 @@
       </c>
       <c r="M108" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N108" s="8">
         <v>0</v>
@@ -9906,13 +9897,13 @@
         <v>13</v>
       </c>
       <c r="I109" s="8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J109" s="8">
         <v>0</v>
       </c>
       <c r="K109" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L109" s="8">
         <v>0</v>
@@ -9922,7 +9913,7 @@
         <v>6</v>
       </c>
       <c r="N109" s="8">
-        <v>260</v>
+        <v>16</v>
       </c>
       <c r="O109" s="8"/>
       <c r="P109" s="8"/>
@@ -9957,13 +9948,13 @@
         <v>13</v>
       </c>
       <c r="I110" s="8">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J110" s="8">
         <v>0</v>
       </c>
       <c r="K110" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L110" s="8">
         <v>0</v>
@@ -9973,7 +9964,7 @@
         <v>12</v>
       </c>
       <c r="N110" s="8">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="O110" s="8"/>
       <c r="P110" s="8"/>
@@ -10008,7 +9999,7 @@
         <v>13</v>
       </c>
       <c r="I111" s="8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J111" s="8">
         <v>0</v>
@@ -10021,7 +10012,7 @@
       </c>
       <c r="M111" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N111" s="8">
         <v>0</v>
@@ -10059,23 +10050,23 @@
         <v>12</v>
       </c>
       <c r="I112" s="8">
-        <v>1</v>
+        <v>116</v>
       </c>
       <c r="J112" s="8">
         <v>0</v>
       </c>
       <c r="K112" s="8">
-        <v>144</v>
+        <v>28</v>
       </c>
       <c r="L112" s="8">
         <v>0</v>
       </c>
       <c r="M112" s="8">
         <f t="shared" si="1"/>
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N112" s="8">
-        <v>781</v>
+        <v>333</v>
       </c>
       <c r="O112" s="8"/>
       <c r="P112" s="8"/>
@@ -10110,23 +10101,23 @@
         <v>12</v>
       </c>
       <c r="I113" s="8">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J113" s="8">
         <v>0</v>
       </c>
       <c r="K113" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L113" s="8">
         <v>0</v>
       </c>
       <c r="M113" s="8">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N113" s="8">
-        <v>1351</v>
+        <v>1226</v>
       </c>
       <c r="O113" s="8"/>
       <c r="P113" s="8"/>
@@ -10161,23 +10152,23 @@
         <v>13</v>
       </c>
       <c r="I114" s="8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J114" s="8">
         <v>0</v>
       </c>
       <c r="K114" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L114" s="8">
         <v>0</v>
       </c>
       <c r="M114" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N114" s="8">
-        <v>923</v>
+        <v>727</v>
       </c>
       <c r="O114" s="8"/>
       <c r="P114" s="8"/>
@@ -10212,7 +10203,7 @@
         <v>13</v>
       </c>
       <c r="I115" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J115" s="8">
         <v>0</v>
@@ -10225,10 +10216,10 @@
       </c>
       <c r="M115" s="8">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N115" s="8">
-        <v>370</v>
+        <v>351</v>
       </c>
       <c r="O115" s="8"/>
       <c r="P115" s="8"/>
@@ -10263,7 +10254,7 @@
         <v>12</v>
       </c>
       <c r="I116" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J116" s="8">
         <v>0</v>
@@ -10276,10 +10267,10 @@
       </c>
       <c r="M116" s="8">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N116" s="8">
-        <v>884</v>
+        <v>859</v>
       </c>
       <c r="O116" s="8"/>
       <c r="P116" s="8"/>
@@ -10314,23 +10305,23 @@
         <v>12</v>
       </c>
       <c r="I117" s="8">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="J117" s="8">
         <v>0</v>
       </c>
       <c r="K117" s="8">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="L117" s="8">
         <v>0</v>
       </c>
       <c r="M117" s="8">
         <f t="shared" si="1"/>
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="N117" s="8">
-        <v>612</v>
+        <v>515</v>
       </c>
       <c r="O117" s="8"/>
       <c r="P117" s="8"/>
@@ -10365,7 +10356,7 @@
         <v>13</v>
       </c>
       <c r="I118" s="8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J118" s="8">
         <v>0</v>
@@ -10378,10 +10369,10 @@
       </c>
       <c r="M118" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N118" s="8">
-        <v>125</v>
+        <v>167</v>
       </c>
       <c r="O118" s="8"/>
       <c r="P118" s="8"/>
@@ -10416,7 +10407,7 @@
         <v>14</v>
       </c>
       <c r="I119" s="8">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J119" s="8">
         <v>0</v>
@@ -10429,10 +10420,10 @@
       </c>
       <c r="M119" s="8">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N119" s="8">
-        <v>594</v>
+        <v>567</v>
       </c>
       <c r="O119" s="8"/>
       <c r="P119" s="8"/>
@@ -10467,7 +10458,7 @@
         <v>14</v>
       </c>
       <c r="I120" s="8">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J120" s="8">
         <v>0</v>
@@ -10480,10 +10471,10 @@
       </c>
       <c r="M120" s="8">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N120" s="8">
-        <v>156</v>
+        <v>81</v>
       </c>
       <c r="O120" s="8"/>
       <c r="P120" s="8"/>
@@ -10534,7 +10525,7 @@
         <v>7</v>
       </c>
       <c r="N121" s="8">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="O121" s="8"/>
       <c r="P121" s="8"/>
@@ -10585,7 +10576,7 @@
         <v>2</v>
       </c>
       <c r="N122" s="8">
-        <v>1065</v>
+        <v>1049</v>
       </c>
       <c r="O122" s="8"/>
       <c r="P122" s="8"/>
@@ -10738,7 +10729,7 @@
         <v>8</v>
       </c>
       <c r="N125" s="8">
-        <v>481</v>
+        <v>357</v>
       </c>
       <c r="O125" s="8"/>
       <c r="P125" s="8"/>
@@ -10891,7 +10882,7 @@
         <v>4</v>
       </c>
       <c r="N128" s="8">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="O128" s="8"/>
       <c r="P128" s="8"/>
@@ -10977,23 +10968,23 @@
         <v>12</v>
       </c>
       <c r="I130" s="8">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J130" s="8">
         <v>0</v>
       </c>
       <c r="K130" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L130" s="8">
         <v>0</v>
       </c>
       <c r="M130" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N130" s="8">
-        <v>463</v>
+        <v>299</v>
       </c>
       <c r="O130" s="8"/>
       <c r="P130" s="8"/>
@@ -11044,7 +11035,7 @@
         <v>4</v>
       </c>
       <c r="N131" s="8">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="O131" s="8"/>
       <c r="P131" s="8"/>
@@ -11095,7 +11086,7 @@
         <v>6</v>
       </c>
       <c r="N132" s="8">
-        <v>873</v>
+        <v>864</v>
       </c>
       <c r="O132" s="8"/>
       <c r="P132" s="8"/>
@@ -11130,23 +11121,23 @@
         <v>12</v>
       </c>
       <c r="I133" s="8">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J133" s="8">
         <v>0</v>
       </c>
       <c r="K133" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L133" s="8">
         <v>0</v>
       </c>
       <c r="M133" s="8">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N133" s="8">
-        <v>1015</v>
+        <v>698</v>
       </c>
       <c r="O133" s="8"/>
       <c r="P133" s="8"/>
@@ -11181,7 +11172,7 @@
         <v>15</v>
       </c>
       <c r="I134" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J134" s="8">
         <v>0</v>
@@ -11194,10 +11185,10 @@
       </c>
       <c r="M134" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N134" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O134" s="8"/>
       <c r="P134" s="8"/>
@@ -11232,7 +11223,7 @@
         <v>15</v>
       </c>
       <c r="I135" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J135" s="8">
         <v>0</v>
@@ -11245,10 +11236,10 @@
       </c>
       <c r="M135" s="8">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N135" s="8">
-        <v>238</v>
+        <v>203</v>
       </c>
       <c r="O135" s="8"/>
       <c r="P135" s="8"/>
@@ -11283,13 +11274,13 @@
         <v>14</v>
       </c>
       <c r="I136" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J136" s="8">
         <v>0</v>
       </c>
       <c r="K136" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L136" s="8">
         <v>0</v>
@@ -11299,7 +11290,7 @@
         <v>5</v>
       </c>
       <c r="N136" s="8">
-        <v>630</v>
+        <v>584</v>
       </c>
       <c r="O136" s="8"/>
       <c r="P136" s="8"/>
@@ -11334,20 +11325,20 @@
         <v>15</v>
       </c>
       <c r="I137" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J137" s="8">
         <v>0</v>
       </c>
       <c r="K137" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L137" s="8">
         <v>0</v>
       </c>
       <c r="M137" s="8">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N137" s="8">
         <v>0</v>
@@ -11401,7 +11392,7 @@
         <v>5</v>
       </c>
       <c r="N138" s="8">
-        <v>1176</v>
+        <v>1054</v>
       </c>
       <c r="O138" s="8"/>
       <c r="P138" s="8"/>
@@ -11452,7 +11443,7 @@
         <v>1</v>
       </c>
       <c r="N139" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O139" s="8"/>
       <c r="P139" s="8"/>
@@ -11487,7 +11478,7 @@
         <v>15</v>
       </c>
       <c r="I140" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J140" s="8">
         <v>0</v>
@@ -11500,10 +11491,10 @@
       </c>
       <c r="M140" s="8">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N140" s="8">
-        <v>470</v>
+        <v>452</v>
       </c>
       <c r="O140" s="8"/>
       <c r="P140" s="8"/>
@@ -11544,17 +11535,17 @@
         <v>0</v>
       </c>
       <c r="K141" s="8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L141" s="8">
         <v>0</v>
       </c>
       <c r="M141" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N141" s="8">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="O141" s="8"/>
       <c r="P141" s="8"/>
@@ -11640,7 +11631,7 @@
         <v>13</v>
       </c>
       <c r="I143" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J143" s="8">
         <v>0</v>
@@ -11653,10 +11644,10 @@
       </c>
       <c r="M143" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N143" s="8">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O143" s="8"/>
       <c r="P143" s="8"/>
@@ -11742,13 +11733,13 @@
         <v>14</v>
       </c>
       <c r="I145" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J145" s="8">
         <v>0</v>
       </c>
       <c r="K145" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L145" s="8">
         <v>0</v>
@@ -11758,7 +11749,7 @@
         <v>4</v>
       </c>
       <c r="N145" s="8">
-        <v>899</v>
+        <v>870</v>
       </c>
       <c r="O145" s="8"/>
       <c r="P145" s="8"/>
@@ -11860,7 +11851,7 @@
         <v>3</v>
       </c>
       <c r="N147" s="8">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O147" s="8"/>
       <c r="P147" s="8"/>
@@ -11895,23 +11886,23 @@
         <v>15</v>
       </c>
       <c r="I148" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J148" s="8">
         <v>0</v>
       </c>
       <c r="K148" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L148" s="8">
         <v>0</v>
       </c>
       <c r="M148" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N148" s="8">
-        <v>355</v>
+        <v>332</v>
       </c>
       <c r="O148" s="8"/>
       <c r="P148" s="8"/>
@@ -11946,23 +11937,23 @@
         <v>12</v>
       </c>
       <c r="I149" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J149" s="8">
         <v>0</v>
       </c>
       <c r="K149" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L149" s="8">
         <v>0</v>
       </c>
       <c r="M149" s="8">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N149" s="8">
-        <v>408</v>
+        <v>385</v>
       </c>
       <c r="O149" s="8"/>
       <c r="P149" s="8"/>
@@ -11997,23 +11988,23 @@
         <v>12</v>
       </c>
       <c r="I150" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J150" s="8">
         <v>0</v>
       </c>
       <c r="K150" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L150" s="8">
         <v>0</v>
       </c>
       <c r="M150" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N150" s="8">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="O150" s="8"/>
       <c r="P150" s="8"/>
@@ -12048,7 +12039,7 @@
         <v>13</v>
       </c>
       <c r="I151" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J151" s="8">
         <v>0</v>
@@ -12061,10 +12052,10 @@
       </c>
       <c r="M151" s="8">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N151" s="8">
-        <v>211</v>
+        <v>188</v>
       </c>
       <c r="O151" s="8"/>
       <c r="P151" s="8"/>
@@ -12115,7 +12106,7 @@
         <v>4</v>
       </c>
       <c r="N152" s="8">
-        <v>74</v>
+        <v>9</v>
       </c>
       <c r="O152" s="8"/>
       <c r="P152" s="8"/>
@@ -12150,23 +12141,23 @@
         <v>13</v>
       </c>
       <c r="I153" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J153" s="8">
         <v>0</v>
       </c>
       <c r="K153" s="8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L153" s="8">
         <v>0</v>
       </c>
       <c r="M153" s="8">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N153" s="8">
-        <v>571</v>
+        <v>538</v>
       </c>
       <c r="O153" s="8"/>
       <c r="P153" s="8"/>
@@ -12472,7 +12463,7 @@
         <v>5</v>
       </c>
       <c r="N159" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O159" s="8"/>
       <c r="P159" s="8"/>
@@ -12523,7 +12514,7 @@
         <v>5</v>
       </c>
       <c r="N160" s="8">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="O160" s="8"/>
       <c r="P160" s="8"/>
@@ -12574,7 +12565,7 @@
         <v>6</v>
       </c>
       <c r="N161" s="8">
-        <v>535</v>
+        <v>503</v>
       </c>
       <c r="O161" s="8"/>
       <c r="P161" s="8"/>
@@ -12625,7 +12616,7 @@
         <v>3</v>
       </c>
       <c r="N162" s="8">
-        <v>344</v>
+        <v>293</v>
       </c>
       <c r="O162" s="8"/>
       <c r="P162" s="8"/>
@@ -12727,7 +12718,7 @@
         <v>3</v>
       </c>
       <c r="N164" s="8">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="O164" s="8"/>
       <c r="P164" s="8"/>
@@ -12762,23 +12753,23 @@
         <v>12</v>
       </c>
       <c r="I165" s="8">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J165" s="8">
         <v>0</v>
       </c>
       <c r="K165" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L165" s="8">
         <v>0</v>
       </c>
       <c r="M165" s="8">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N165" s="8">
-        <v>1498</v>
+        <v>1443</v>
       </c>
       <c r="O165" s="8"/>
       <c r="P165" s="8"/>
@@ -12931,7 +12922,7 @@
         <v>4</v>
       </c>
       <c r="N168" s="8">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="O168" s="8"/>
       <c r="P168" s="8"/>
@@ -13033,7 +13024,7 @@
         <v>5</v>
       </c>
       <c r="N170" s="8">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="O170" s="8"/>
       <c r="P170" s="8"/>
@@ -13135,7 +13126,7 @@
         <v>3</v>
       </c>
       <c r="N172" s="8">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O172" s="8"/>
       <c r="P172" s="8"/>
@@ -13186,7 +13177,7 @@
         <v>2</v>
       </c>
       <c r="N173" s="8">
-        <v>743</v>
+        <v>717</v>
       </c>
       <c r="O173" s="8"/>
       <c r="P173" s="8"/>
@@ -13221,7 +13212,7 @@
         <v>13</v>
       </c>
       <c r="I174" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J174" s="8">
         <v>0</v>
@@ -13234,7 +13225,7 @@
       </c>
       <c r="M174" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N174" s="8">
         <v>0</v>
@@ -13339,7 +13330,7 @@
         <v>2</v>
       </c>
       <c r="N176" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O176" s="8"/>
       <c r="P176" s="8"/>
@@ -13492,7 +13483,7 @@
         <v>3</v>
       </c>
       <c r="N179" s="8">
-        <v>204</v>
+        <v>176</v>
       </c>
       <c r="O179" s="8"/>
       <c r="P179" s="8"/>
@@ -13543,7 +13534,7 @@
         <v>8</v>
       </c>
       <c r="N180" s="8">
-        <v>527</v>
+        <v>458</v>
       </c>
       <c r="O180" s="8"/>
       <c r="P180" s="8"/>
@@ -13594,7 +13585,7 @@
         <v>4</v>
       </c>
       <c r="N181" s="8">
-        <v>194</v>
+        <v>167</v>
       </c>
       <c r="O181" s="8"/>
       <c r="P181" s="8"/>
@@ -13696,7 +13687,7 @@
         <v>6</v>
       </c>
       <c r="N183" s="8">
-        <v>640</v>
+        <v>623</v>
       </c>
       <c r="O183" s="8"/>
       <c r="P183" s="8"/>
@@ -13747,7 +13738,7 @@
         <v>2</v>
       </c>
       <c r="N184" s="8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O184" s="8"/>
       <c r="P184" s="8"/>
@@ -13782,23 +13773,23 @@
         <v>12</v>
       </c>
       <c r="I185" s="8">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="J185" s="8">
         <v>0</v>
       </c>
       <c r="K185" s="8">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="L185" s="8">
         <v>0</v>
       </c>
       <c r="M185" s="8">
         <f t="shared" si="2"/>
-        <v>307</v>
+        <v>348</v>
       </c>
       <c r="N185" s="8">
-        <v>2103</v>
+        <v>2031</v>
       </c>
       <c r="O185" s="8"/>
       <c r="P185" s="8"/>
@@ -13849,7 +13840,7 @@
         <v>9</v>
       </c>
       <c r="N186" s="8">
-        <v>1025</v>
+        <v>997</v>
       </c>
       <c r="O186" s="8"/>
       <c r="P186" s="8"/>
@@ -13900,7 +13891,7 @@
         <v>2</v>
       </c>
       <c r="N187" s="8">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="O187" s="8"/>
       <c r="P187" s="8"/>
@@ -13935,7 +13926,7 @@
         <v>15</v>
       </c>
       <c r="I188" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J188" s="8">
         <v>0</v>
@@ -13948,10 +13939,10 @@
       </c>
       <c r="M188" s="8">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N188" s="8">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="O188" s="8"/>
       <c r="P188" s="8"/>
@@ -14037,23 +14028,23 @@
         <v>12</v>
       </c>
       <c r="I190" s="8">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J190" s="8">
         <v>0</v>
       </c>
       <c r="K190" s="8">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L190" s="8">
         <v>0</v>
       </c>
       <c r="M190" s="8">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N190" s="8">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="O190" s="8"/>
       <c r="P190" s="8"/>
@@ -14088,13 +14079,13 @@
         <v>12</v>
       </c>
       <c r="I191" s="8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J191" s="8">
         <v>0</v>
       </c>
       <c r="K191" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L191" s="8">
         <v>0</v>
@@ -14104,7 +14095,7 @@
         <v>9</v>
       </c>
       <c r="N191" s="8">
-        <v>1108</v>
+        <v>1016</v>
       </c>
       <c r="O191" s="8"/>
       <c r="P191" s="8"/>
@@ -14206,7 +14197,7 @@
         <v>3</v>
       </c>
       <c r="N193" s="8">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="O193" s="8"/>
       <c r="P193" s="8"/>
@@ -14257,7 +14248,7 @@
         <v>5</v>
       </c>
       <c r="N194" s="8">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="O194" s="8"/>
       <c r="P194" s="8"/>
@@ -14410,7 +14401,7 @@
         <v>5</v>
       </c>
       <c r="N197" s="8">
-        <v>659</v>
+        <v>563</v>
       </c>
       <c r="O197" s="8"/>
       <c r="P197" s="8"/>
@@ -14445,7 +14436,7 @@
         <v>12</v>
       </c>
       <c r="I198" s="8">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J198" s="8">
         <v>0</v>
@@ -14458,7 +14449,7 @@
       </c>
       <c r="M198" s="8">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N198" s="8">
         <v>0</v>
@@ -14598,13 +14589,13 @@
         <v>12</v>
       </c>
       <c r="I201" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J201" s="8">
         <v>0</v>
       </c>
       <c r="K201" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L201" s="8">
         <v>0</v>
@@ -14716,7 +14707,7 @@
         <v>3</v>
       </c>
       <c r="N203" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O203" s="8"/>
       <c r="P203" s="8"/>
@@ -14920,7 +14911,7 @@
         <v>2</v>
       </c>
       <c r="N207" s="8">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="O207" s="8"/>
       <c r="P207" s="8"/>
@@ -14971,7 +14962,7 @@
         <v>3</v>
       </c>
       <c r="N208" s="8">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="O208" s="8"/>
       <c r="P208" s="8"/>
@@ -15022,7 +15013,7 @@
         <v>4</v>
       </c>
       <c r="N209" s="8">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="O209" s="8"/>
       <c r="P209" s="8"/>
@@ -15124,7 +15115,7 @@
         <v>3</v>
       </c>
       <c r="N211" s="8">
-        <v>804</v>
+        <v>776</v>
       </c>
       <c r="O211" s="8"/>
       <c r="P211" s="8"/>
@@ -15226,7 +15217,7 @@
         <v>0</v>
       </c>
       <c r="N213" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O213" s="8"/>
       <c r="P213" s="8"/>
@@ -15261,7 +15252,7 @@
         <v>14</v>
       </c>
       <c r="I214" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J214" s="8">
         <v>0</v>
@@ -15274,10 +15265,10 @@
       </c>
       <c r="M214" s="8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N214" s="8">
-        <v>476</v>
+        <v>460</v>
       </c>
       <c r="O214" s="8"/>
       <c r="P214" s="8"/>
@@ -15328,7 +15319,7 @@
         <v>6</v>
       </c>
       <c r="N215" s="8">
-        <v>760</v>
+        <v>749</v>
       </c>
       <c r="O215" s="8"/>
       <c r="P215" s="8"/>
@@ -15363,7 +15354,7 @@
         <v>14</v>
       </c>
       <c r="I216" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J216" s="8">
         <v>0</v>
@@ -15376,7 +15367,7 @@
       </c>
       <c r="M216" s="8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N216" s="8">
         <v>0</v>
@@ -15430,7 +15421,7 @@
         <v>4</v>
       </c>
       <c r="N217" s="8">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="O217" s="8"/>
       <c r="P217" s="8"/>
@@ -15532,7 +15523,7 @@
         <v>6</v>
       </c>
       <c r="N219" s="8">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="O219" s="8"/>
       <c r="P219" s="8"/>
@@ -15634,7 +15625,7 @@
         <v>4</v>
       </c>
       <c r="N221" s="8">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="O221" s="8"/>
       <c r="P221" s="8"/>
@@ -15685,7 +15676,7 @@
         <v>2</v>
       </c>
       <c r="N222" s="8">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="O222" s="8"/>
       <c r="P222" s="8"/>
@@ -15787,7 +15778,7 @@
         <v>3</v>
       </c>
       <c r="N224" s="8">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="O224" s="8"/>
       <c r="P224" s="8"/>
@@ -15822,7 +15813,7 @@
         <v>12</v>
       </c>
       <c r="I225" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J225" s="8">
         <v>0</v>
@@ -15835,10 +15826,10 @@
       </c>
       <c r="M225" s="8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N225" s="8">
-        <v>763</v>
+        <v>722</v>
       </c>
       <c r="O225" s="8"/>
       <c r="P225" s="8"/>
@@ -15981,17 +15972,17 @@
         <v>0</v>
       </c>
       <c r="K228" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L228" s="8">
         <v>0</v>
       </c>
       <c r="M228" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N228" s="8">
-        <v>160</v>
+        <v>52</v>
       </c>
       <c r="O228" s="8"/>
       <c r="P228" s="8"/>
@@ -16042,7 +16033,7 @@
         <v>3</v>
       </c>
       <c r="N229" s="8">
-        <v>208</v>
+        <v>179</v>
       </c>
       <c r="O229" s="8"/>
       <c r="P229" s="8"/>
@@ -16179,7 +16170,7 @@
         <v>12</v>
       </c>
       <c r="I232" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J232" s="8">
         <v>0</v>
@@ -16192,10 +16183,10 @@
       </c>
       <c r="M232" s="8">
         <f t="shared" si="3"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N232" s="8">
-        <v>797</v>
+        <v>746</v>
       </c>
       <c r="O232" s="8"/>
       <c r="P232" s="8"/>
@@ -16246,7 +16237,7 @@
         <v>7</v>
       </c>
       <c r="N233" s="8">
-        <v>766</v>
+        <v>731</v>
       </c>
       <c r="O233" s="8"/>
       <c r="P233" s="8"/>
@@ -16297,7 +16288,7 @@
         <v>2</v>
       </c>
       <c r="N234" s="8">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O234" s="8"/>
       <c r="P234" s="8"/>
@@ -16348,7 +16339,7 @@
         <v>3</v>
       </c>
       <c r="N235" s="8">
-        <v>177</v>
+        <v>132</v>
       </c>
       <c r="O235" s="8"/>
       <c r="P235" s="8"/>
@@ -16440,17 +16431,17 @@
         <v>0</v>
       </c>
       <c r="K237" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L237" s="8">
         <v>0</v>
       </c>
       <c r="M237" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N237" s="8">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O237" s="8"/>
       <c r="P237" s="8"/>
@@ -16501,7 +16492,7 @@
         <v>6</v>
       </c>
       <c r="N238" s="8">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="O238" s="8"/>
       <c r="P238" s="8"/>
@@ -16552,7 +16543,7 @@
         <v>4</v>
       </c>
       <c r="N239" s="8">
-        <v>215</v>
+        <v>180</v>
       </c>
       <c r="O239" s="8"/>
       <c r="P239" s="8"/>
@@ -16587,23 +16578,23 @@
         <v>13</v>
       </c>
       <c r="I240" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J240" s="8">
         <v>0</v>
       </c>
       <c r="K240" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L240" s="8">
         <v>0</v>
       </c>
       <c r="M240" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N240" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O240" s="8"/>
       <c r="P240" s="8"/>
@@ -16654,7 +16645,7 @@
         <v>3</v>
       </c>
       <c r="N241" s="8">
-        <v>1</v>
+        <v>153</v>
       </c>
       <c r="O241" s="8"/>
       <c r="P241" s="8"/>
@@ -16705,7 +16696,7 @@
         <v>3</v>
       </c>
       <c r="N242" s="8">
-        <v>691</v>
+        <v>701</v>
       </c>
       <c r="O242" s="8"/>
       <c r="P242" s="8"/>
@@ -16740,7 +16731,7 @@
         <v>15</v>
       </c>
       <c r="I243" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J243" s="8">
         <v>0</v>
@@ -16753,10 +16744,10 @@
       </c>
       <c r="M243" s="8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N243" s="8">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="O243" s="8"/>
       <c r="P243" s="8"/>
@@ -16807,7 +16798,7 @@
         <v>0</v>
       </c>
       <c r="N244" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O244" s="8"/>
       <c r="P244" s="8"/>
@@ -16858,7 +16849,7 @@
         <v>6</v>
       </c>
       <c r="N245" s="8">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="O245" s="8"/>
       <c r="P245" s="8"/>
@@ -16893,7 +16884,7 @@
         <v>15</v>
       </c>
       <c r="I246" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J246" s="8">
         <v>0</v>
@@ -16906,10 +16897,10 @@
       </c>
       <c r="M246" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N246" s="8">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="O246" s="8"/>
       <c r="P246" s="8"/>
@@ -16960,7 +16951,7 @@
         <v>3</v>
       </c>
       <c r="N247" s="8">
-        <v>387</v>
+        <v>361</v>
       </c>
       <c r="O247" s="8"/>
       <c r="P247" s="8"/>
@@ -16995,7 +16986,7 @@
         <v>12</v>
       </c>
       <c r="I248" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J248" s="8">
         <v>0</v>
@@ -17008,7 +16999,7 @@
       </c>
       <c r="M248" s="8">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N248" s="8">
         <v>0</v>
@@ -17103,17 +17094,17 @@
         <v>0</v>
       </c>
       <c r="K250" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L250" s="8">
         <v>0</v>
       </c>
       <c r="M250" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N250" s="8">
-        <v>1517</v>
+        <v>1483</v>
       </c>
       <c r="O250" s="8"/>
       <c r="P250" s="8"/>
@@ -17164,7 +17155,7 @@
         <v>3</v>
       </c>
       <c r="N251" s="8">
-        <v>1292</v>
+        <v>1286</v>
       </c>
       <c r="O251" s="8"/>
       <c r="P251" s="8"/>
@@ -17215,7 +17206,7 @@
         <v>3</v>
       </c>
       <c r="N252" s="8">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="O252" s="8"/>
       <c r="P252" s="8"/>
@@ -17266,7 +17257,7 @@
         <v>3</v>
       </c>
       <c r="N253" s="8">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="O253" s="8"/>
       <c r="P253" s="8"/>
@@ -17317,7 +17308,7 @@
         <v>3</v>
       </c>
       <c r="N254" s="8">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="O254" s="8"/>
       <c r="P254" s="8"/>
@@ -17368,7 +17359,7 @@
         <v>3</v>
       </c>
       <c r="N255" s="8">
-        <v>428</v>
+        <v>408</v>
       </c>
       <c r="O255" s="8"/>
       <c r="P255" s="8"/>
@@ -17419,7 +17410,7 @@
         <v>3</v>
       </c>
       <c r="N256" s="8">
-        <v>1056</v>
+        <v>1050</v>
       </c>
       <c r="O256" s="8"/>
       <c r="P256" s="8"/>
@@ -17470,7 +17461,7 @@
         <v>4</v>
       </c>
       <c r="N257" s="8">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="O257" s="8"/>
       <c r="P257" s="8"/>
@@ -17572,7 +17563,7 @@
         <v>2</v>
       </c>
       <c r="N259" s="8">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="O259" s="8"/>
       <c r="P259" s="8"/>
@@ -17607,7 +17598,7 @@
         <v>13</v>
       </c>
       <c r="I260" s="8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J260" s="8">
         <v>0</v>
@@ -17620,10 +17611,10 @@
       </c>
       <c r="M260" s="8">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N260" s="8">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="O260" s="8"/>
       <c r="P260" s="8"/>
@@ -17658,13 +17649,13 @@
         <v>12</v>
       </c>
       <c r="I261" s="8">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J261" s="8">
         <v>0</v>
       </c>
       <c r="K261" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L261" s="8">
         <v>0</v>
@@ -17674,7 +17665,7 @@
         <v>29</v>
       </c>
       <c r="N261" s="8">
-        <v>1513</v>
+        <v>1264</v>
       </c>
       <c r="O261" s="8"/>
       <c r="P261" s="8"/>
@@ -17715,17 +17706,17 @@
         <v>0</v>
       </c>
       <c r="K262" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L262" s="8">
         <v>0</v>
       </c>
       <c r="M262" s="8">
         <f t="shared" si="4"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N262" s="8">
-        <v>472</v>
+        <v>443</v>
       </c>
       <c r="O262" s="8"/>
       <c r="P262" s="8"/>
@@ -17760,23 +17751,23 @@
         <v>12</v>
       </c>
       <c r="I263" s="8">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J263" s="8">
         <v>0</v>
       </c>
       <c r="K263" s="8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L263" s="8">
         <v>0</v>
       </c>
       <c r="M263" s="8">
         <f t="shared" si="4"/>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="N263" s="8">
-        <v>813</v>
+        <v>541</v>
       </c>
       <c r="O263" s="8"/>
       <c r="P263" s="8"/>
@@ -17811,7 +17802,7 @@
         <v>14</v>
       </c>
       <c r="I264" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J264" s="8">
         <v>0</v>
@@ -17824,10 +17815,10 @@
       </c>
       <c r="M264" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N264" s="8">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="O264" s="8"/>
       <c r="P264" s="8"/>
@@ -17878,7 +17869,7 @@
         <v>2</v>
       </c>
       <c r="N265" s="8">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O265" s="8"/>
       <c r="P265" s="8"/>
@@ -17929,7 +17920,7 @@
         <v>3</v>
       </c>
       <c r="N266" s="8">
-        <v>1584</v>
+        <v>1578</v>
       </c>
       <c r="O266" s="8"/>
       <c r="P266" s="8"/>
@@ -18015,23 +18006,23 @@
         <v>15</v>
       </c>
       <c r="I268" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J268" s="8">
         <v>0</v>
       </c>
       <c r="K268" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L268" s="8">
         <v>0</v>
       </c>
       <c r="M268" s="8">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N268" s="8">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="O268" s="8"/>
       <c r="P268" s="8"/>
@@ -18082,7 +18073,7 @@
         <v>5</v>
       </c>
       <c r="N269" s="8">
-        <v>147</v>
+        <v>110</v>
       </c>
       <c r="O269" s="8"/>
       <c r="P269" s="8"/>
@@ -18321,13 +18312,13 @@
         <v>16</v>
       </c>
       <c r="I274" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J274" s="8">
         <v>0</v>
       </c>
       <c r="K274" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L274" s="8">
         <v>0</v>
@@ -18337,7 +18328,7 @@
         <v>4</v>
       </c>
       <c r="N274" s="8">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="O274" s="8"/>
       <c r="P274" s="8"/>
@@ -18388,7 +18379,7 @@
         <v>4</v>
       </c>
       <c r="N275" s="8">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="O275" s="8"/>
       <c r="P275" s="8"/>
@@ -18439,7 +18430,7 @@
         <v>3</v>
       </c>
       <c r="N276" s="8">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="O276" s="8"/>
       <c r="P276" s="8"/>
@@ -18541,7 +18532,7 @@
         <v>8</v>
       </c>
       <c r="N278" s="8">
-        <v>984</v>
+        <v>1131</v>
       </c>
       <c r="O278" s="8"/>
       <c r="P278" s="8"/>
@@ -18592,7 +18583,7 @@
         <v>3</v>
       </c>
       <c r="N279" s="8">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="O279" s="8"/>
       <c r="P279" s="8"/>
@@ -18643,7 +18634,7 @@
         <v>3</v>
       </c>
       <c r="N280" s="8">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="O280" s="8"/>
       <c r="P280" s="8"/>
@@ -18694,7 +18685,7 @@
         <v>2</v>
       </c>
       <c r="N281" s="8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O281" s="8"/>
       <c r="P281" s="8"/>
@@ -18780,23 +18771,23 @@
         <v>12</v>
       </c>
       <c r="I283" s="8">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J283" s="8">
         <v>0</v>
       </c>
       <c r="K283" s="8">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L283" s="8">
         <v>0</v>
       </c>
       <c r="M283" s="8">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N283" s="8">
-        <v>587</v>
+        <v>362</v>
       </c>
       <c r="O283" s="8"/>
       <c r="P283" s="8"/>
@@ -18831,23 +18822,23 @@
         <v>12</v>
       </c>
       <c r="I284" s="8">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J284" s="8">
         <v>0</v>
       </c>
       <c r="K284" s="8">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="L284" s="8">
         <v>0</v>
       </c>
       <c r="M284" s="8">
         <f t="shared" si="4"/>
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="N284" s="8">
-        <v>275</v>
+        <v>0</v>
       </c>
       <c r="O284" s="8"/>
       <c r="P284" s="8"/>
@@ -18949,7 +18940,7 @@
         <v>4</v>
       </c>
       <c r="N286" s="8">
-        <v>1045</v>
+        <v>1016</v>
       </c>
       <c r="O286" s="8"/>
       <c r="P286" s="8"/>
@@ -18984,23 +18975,23 @@
         <v>12</v>
       </c>
       <c r="I287" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J287" s="8">
         <v>0</v>
       </c>
       <c r="K287" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L287" s="8">
         <v>0</v>
       </c>
       <c r="M287" s="8">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N287" s="8">
-        <v>1168</v>
+        <v>1163</v>
       </c>
       <c r="O287" s="8"/>
       <c r="P287" s="8"/>
@@ -19035,7 +19026,7 @@
         <v>14</v>
       </c>
       <c r="I288" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J288" s="8">
         <v>0</v>
@@ -19048,10 +19039,10 @@
       </c>
       <c r="M288" s="8">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N288" s="8">
-        <v>1577</v>
+        <v>1547</v>
       </c>
       <c r="O288" s="8"/>
       <c r="P288" s="8"/>
@@ -19086,7 +19077,7 @@
         <v>14</v>
       </c>
       <c r="I289" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J289" s="8">
         <v>0</v>
@@ -19099,10 +19090,10 @@
       </c>
       <c r="M289" s="8">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N289" s="8">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="O289" s="8"/>
       <c r="P289" s="8"/>
@@ -19188,13 +19179,13 @@
         <v>12</v>
       </c>
       <c r="I291" s="8">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J291" s="8">
         <v>0</v>
       </c>
       <c r="K291" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L291" s="8">
         <v>0</v>
@@ -19255,7 +19246,7 @@
         <v>2</v>
       </c>
       <c r="N292" s="8">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="O292" s="8"/>
       <c r="P292" s="8"/>
@@ -19341,7 +19332,7 @@
         <v>12</v>
       </c>
       <c r="I294" s="8">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J294" s="8">
         <v>0</v>
@@ -19354,10 +19345,10 @@
       </c>
       <c r="M294" s="8">
         <f t="shared" si="4"/>
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="N294" s="8">
-        <v>1687</v>
+        <v>1656</v>
       </c>
       <c r="O294" s="8"/>
       <c r="P294" s="8"/>
@@ -19647,23 +19638,23 @@
         <v>13</v>
       </c>
       <c r="I300" s="8">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J300" s="8">
         <v>0</v>
       </c>
       <c r="K300" s="8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L300" s="8">
         <v>0</v>
       </c>
       <c r="M300" s="8">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N300" s="8">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="O300" s="8"/>
       <c r="P300" s="8"/>
@@ -19714,7 +19705,7 @@
         <v>6</v>
       </c>
       <c r="N301" s="8">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="O301" s="8"/>
       <c r="P301" s="8"/>
@@ -19765,7 +19756,7 @@
         <v>6</v>
       </c>
       <c r="N302" s="8">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="O302" s="8"/>
       <c r="P302" s="8"/>
@@ -19816,7 +19807,7 @@
         <v>3</v>
       </c>
       <c r="N303" s="8">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O303" s="8"/>
       <c r="P303" s="8"/>
@@ -19867,7 +19858,7 @@
         <v>4</v>
       </c>
       <c r="N304" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O304" s="8"/>
       <c r="P304" s="8"/>
@@ -19918,7 +19909,7 @@
         <v>8</v>
       </c>
       <c r="N305" s="8">
-        <v>593</v>
+        <v>568</v>
       </c>
       <c r="O305" s="8"/>
       <c r="P305" s="8"/>
@@ -19969,7 +19960,7 @@
         <v>10</v>
       </c>
       <c r="N306" s="8">
-        <v>1273</v>
+        <v>1231</v>
       </c>
       <c r="O306" s="8"/>
       <c r="P306" s="8"/>
@@ -20020,7 +20011,7 @@
         <v>11</v>
       </c>
       <c r="N307" s="8">
-        <v>1132</v>
+        <v>1101</v>
       </c>
       <c r="O307" s="8"/>
       <c r="P307" s="8"/>
@@ -20071,7 +20062,7 @@
         <v>11</v>
       </c>
       <c r="N308" s="8">
-        <v>934</v>
+        <v>874</v>
       </c>
       <c r="O308" s="8"/>
       <c r="P308" s="8"/>
@@ -20122,7 +20113,7 @@
         <v>4</v>
       </c>
       <c r="N309" s="8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O309" s="8"/>
       <c r="P309" s="8"/>
@@ -20173,7 +20164,7 @@
         <v>4</v>
       </c>
       <c r="N310" s="8">
-        <v>45</v>
+        <v>153</v>
       </c>
       <c r="O310" s="8"/>
       <c r="P310" s="8"/>
@@ -20259,13 +20250,13 @@
         <v>13</v>
       </c>
       <c r="I312" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J312" s="8">
         <v>0</v>
       </c>
       <c r="K312" s="8">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L312" s="8">
         <v>0</v>
@@ -20275,7 +20266,7 @@
         <v>6</v>
       </c>
       <c r="N312" s="8">
-        <v>185</v>
+        <v>93</v>
       </c>
       <c r="O312" s="8"/>
       <c r="P312" s="8"/>
@@ -20326,7 +20317,7 @@
         <v>3</v>
       </c>
       <c r="N313" s="8">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O313" s="8"/>
       <c r="P313" s="8"/>
@@ -20377,7 +20368,7 @@
         <v>3</v>
       </c>
       <c r="N314" s="8">
-        <v>517</v>
+        <v>487</v>
       </c>
       <c r="O314" s="8"/>
       <c r="P314" s="8"/>
@@ -20428,7 +20419,7 @@
         <v>8</v>
       </c>
       <c r="N315" s="8">
-        <v>480</v>
+        <v>384</v>
       </c>
       <c r="O315" s="8"/>
       <c r="P315" s="8"/>
@@ -20463,7 +20454,7 @@
         <v>12</v>
       </c>
       <c r="I316" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J316" s="8">
         <v>0</v>
@@ -20476,10 +20467,10 @@
       </c>
       <c r="M316" s="8">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N316" s="8">
-        <v>494</v>
+        <v>773</v>
       </c>
       <c r="O316" s="8"/>
       <c r="P316" s="8"/>
@@ -20514,13 +20505,13 @@
         <v>12</v>
       </c>
       <c r="I317" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J317" s="8">
         <v>0</v>
       </c>
       <c r="K317" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L317" s="8">
         <v>0</v>
@@ -20530,7 +20521,7 @@
         <v>6</v>
       </c>
       <c r="N317" s="8">
-        <v>456</v>
+        <v>431</v>
       </c>
       <c r="O317" s="8"/>
       <c r="P317" s="8"/>
@@ -20565,23 +20556,23 @@
         <v>12</v>
       </c>
       <c r="I318" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J318" s="8">
         <v>0</v>
       </c>
       <c r="K318" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L318" s="8">
         <v>0</v>
       </c>
       <c r="M318" s="8">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N318" s="8">
-        <v>894</v>
+        <v>647</v>
       </c>
       <c r="O318" s="8"/>
       <c r="P318" s="8"/>
@@ -20632,7 +20623,7 @@
         <v>4</v>
       </c>
       <c r="N319" s="8">
-        <v>436</v>
+        <v>415</v>
       </c>
       <c r="O319" s="8"/>
       <c r="P319" s="8"/>
@@ -20683,7 +20674,7 @@
         <v>4</v>
       </c>
       <c r="N320" s="8">
-        <v>682</v>
+        <v>664</v>
       </c>
       <c r="O320" s="8"/>
       <c r="P320" s="8"/>
@@ -20734,7 +20725,7 @@
         <v>2</v>
       </c>
       <c r="N321" s="8">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="O321" s="8"/>
       <c r="P321" s="8"/>
@@ -20922,7 +20913,7 @@
         <v>14</v>
       </c>
       <c r="I325" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J325" s="8">
         <v>0</v>
@@ -20935,10 +20926,10 @@
       </c>
       <c r="M325" s="8">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N325" s="8">
-        <v>416</v>
+        <v>379</v>
       </c>
       <c r="O325" s="8"/>
       <c r="P325" s="8"/>
@@ -20989,7 +20980,7 @@
         <v>3</v>
       </c>
       <c r="N326" s="8">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="O326" s="8"/>
       <c r="P326" s="8"/>
@@ -21040,7 +21031,7 @@
         <v>3</v>
       </c>
       <c r="N327" s="8">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="O327" s="8"/>
       <c r="P327" s="8"/>
@@ -21091,7 +21082,7 @@
         <v>1</v>
       </c>
       <c r="N328" s="8">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="O328" s="8"/>
       <c r="P328" s="8"/>
@@ -21142,7 +21133,7 @@
         <v>4</v>
       </c>
       <c r="N329" s="8">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="O329" s="8"/>
       <c r="P329" s="8"/>
@@ -21193,7 +21184,7 @@
         <v>2</v>
       </c>
       <c r="N330" s="8">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="O330" s="8"/>
       <c r="P330" s="8"/>
@@ -21228,7 +21219,7 @@
         <v>13</v>
       </c>
       <c r="I331" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J331" s="8">
         <v>0</v>
@@ -21241,7 +21232,7 @@
       </c>
       <c r="M331" s="8">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N331" s="8">
         <v>0</v>
@@ -21346,7 +21337,7 @@
         <v>3</v>
       </c>
       <c r="N333" s="8">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="O333" s="8"/>
       <c r="P333" s="8"/>
@@ -21397,7 +21388,7 @@
         <v>4</v>
       </c>
       <c r="N334" s="8">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="O334" s="8"/>
       <c r="P334" s="8"/>
@@ -21448,7 +21439,7 @@
         <v>1</v>
       </c>
       <c r="N335" s="8">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O335" s="8"/>
       <c r="P335" s="8"/>
@@ -21499,7 +21490,7 @@
         <v>5</v>
       </c>
       <c r="N336" s="8">
-        <v>748</v>
+        <v>707</v>
       </c>
       <c r="O336" s="8"/>
       <c r="P336" s="8"/>
@@ -21534,13 +21525,13 @@
         <v>12</v>
       </c>
       <c r="I337" s="8">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J337" s="8">
         <v>0</v>
       </c>
       <c r="K337" s="8">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L337" s="8">
         <v>0</v>
@@ -21550,7 +21541,7 @@
         <v>12</v>
       </c>
       <c r="N337" s="8">
-        <v>1073</v>
+        <v>1063</v>
       </c>
       <c r="O337" s="8"/>
       <c r="P337" s="8"/>
@@ -21601,7 +21592,7 @@
         <v>6</v>
       </c>
       <c r="N338" s="8">
-        <v>1321</v>
+        <v>1221</v>
       </c>
       <c r="O338" s="8"/>
       <c r="P338" s="8"/>
@@ -21652,7 +21643,7 @@
         <v>3</v>
       </c>
       <c r="N339" s="8">
-        <v>924</v>
+        <v>908</v>
       </c>
       <c r="O339" s="8"/>
       <c r="P339" s="8"/>
@@ -21693,17 +21684,17 @@
         <v>0</v>
       </c>
       <c r="K340" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L340" s="8">
         <v>0</v>
       </c>
       <c r="M340" s="8">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N340" s="8">
-        <v>773</v>
+        <v>675</v>
       </c>
       <c r="O340" s="8"/>
       <c r="P340" s="8"/>
@@ -21754,7 +21745,7 @@
         <v>4</v>
       </c>
       <c r="N341" s="8">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="O341" s="8"/>
       <c r="P341" s="8"/>
@@ -21805,7 +21796,7 @@
         <v>4</v>
       </c>
       <c r="N342" s="8">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="O342" s="8"/>
       <c r="P342" s="8"/>
@@ -21891,7 +21882,7 @@
         <v>12</v>
       </c>
       <c r="I344" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J344" s="8">
         <v>0</v>
@@ -21904,7 +21895,7 @@
       </c>
       <c r="M344" s="8">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N344" s="8">
         <v>0</v>
@@ -21942,7 +21933,7 @@
         <v>12</v>
       </c>
       <c r="I345" s="8">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J345" s="8">
         <v>0</v>
@@ -21955,7 +21946,7 @@
       </c>
       <c r="M345" s="8">
         <f t="shared" si="5"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="N345" s="8">
         <v>0</v>
@@ -21993,7 +21984,7 @@
         <v>13</v>
       </c>
       <c r="I346" s="8">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="J346" s="8">
         <v>0</v>
@@ -22006,7 +21997,7 @@
       </c>
       <c r="M346" s="8">
         <f t="shared" si="5"/>
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="N346" s="8">
         <v>0</v>
@@ -22044,23 +22035,23 @@
         <v>13</v>
       </c>
       <c r="I347" s="8">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J347" s="8">
         <v>0</v>
       </c>
       <c r="K347" s="8">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L347" s="8">
         <v>0</v>
       </c>
       <c r="M347" s="8">
         <f t="shared" si="5"/>
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="N347" s="8">
-        <v>201</v>
+        <v>561</v>
       </c>
       <c r="O347" s="8"/>
       <c r="P347" s="9"/>
@@ -22095,7 +22086,7 @@
         <v>12</v>
       </c>
       <c r="I348" s="8">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J348" s="8">
         <v>0</v>
@@ -22108,10 +22099,10 @@
       </c>
       <c r="M348" s="8">
         <f t="shared" si="5"/>
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="N348" s="8">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="O348" s="8"/>
       <c r="P348" s="9"/>
@@ -22197,7 +22188,7 @@
         <v>13</v>
       </c>
       <c r="I350" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J350" s="8">
         <v>0</v>
@@ -22210,7 +22201,7 @@
       </c>
       <c r="M350" s="8">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N350" s="8">
         <v>0</v>
@@ -22315,7 +22306,7 @@
         <v>2</v>
       </c>
       <c r="N352" s="8">
-        <v>552</v>
+        <v>523</v>
       </c>
       <c r="O352" s="8"/>
       <c r="P352" s="9"/>
@@ -22452,7 +22443,7 @@
         <v>16</v>
       </c>
       <c r="I355" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J355" s="8">
         <v>0</v>
@@ -22465,7 +22456,7 @@
       </c>
       <c r="M355" s="8">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N355" s="8">
         <v>0</v>
@@ -22519,7 +22510,7 @@
         <v>0</v>
       </c>
       <c r="N356" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O356" s="8"/>
       <c r="P356" s="9"/>
@@ -22860,23 +22851,23 @@
         <v>12</v>
       </c>
       <c r="I363" s="8">
-        <v>45</v>
+        <v>236</v>
       </c>
       <c r="J363" s="8">
         <v>0</v>
       </c>
       <c r="K363" s="8">
-        <v>240</v>
+        <v>112</v>
       </c>
       <c r="L363" s="8">
         <v>0</v>
       </c>
       <c r="M363" s="8">
         <f t="shared" si="5"/>
-        <v>285</v>
+        <v>348</v>
       </c>
       <c r="N363" s="8">
-        <v>1244</v>
+        <v>1172</v>
       </c>
       <c r="O363" s="8"/>
       <c r="P363" s="9"/>
@@ -23013,13 +23004,13 @@
         <v>14</v>
       </c>
       <c r="I366" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J366" s="8">
         <v>0</v>
       </c>
       <c r="K366" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L366" s="8">
         <v>0</v>
@@ -23029,7 +23020,7 @@
         <v>3</v>
       </c>
       <c r="N366" s="8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O366" s="8"/>
       <c r="P366" s="9"/>
@@ -23064,23 +23055,23 @@
         <v>12</v>
       </c>
       <c r="I367" s="8">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="J367" s="8">
         <v>0</v>
       </c>
       <c r="K367" s="8">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="L367" s="8">
         <v>0</v>
       </c>
       <c r="M367" s="8">
         <f t="shared" si="5"/>
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N367" s="8">
-        <v>1020</v>
+        <v>477</v>
       </c>
       <c r="O367" s="8"/>
       <c r="P367" s="9"/>
@@ -23115,13 +23106,13 @@
         <v>12</v>
       </c>
       <c r="I368" s="8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J368" s="8">
         <v>0</v>
       </c>
       <c r="K368" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L368" s="8">
         <v>0</v>
@@ -23131,7 +23122,7 @@
         <v>6</v>
       </c>
       <c r="N368" s="8">
-        <v>228</v>
+        <v>181</v>
       </c>
       <c r="O368" s="8"/>
       <c r="P368" s="9"/>
@@ -23166,23 +23157,23 @@
         <v>15</v>
       </c>
       <c r="I369" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J369" s="8">
         <v>0</v>
       </c>
       <c r="K369" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L369" s="8">
         <v>0</v>
       </c>
       <c r="M369" s="8">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N369" s="8">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="O369" s="8"/>
       <c r="P369" s="9"/>
@@ -23233,7 +23224,7 @@
         <v>2</v>
       </c>
       <c r="N370" s="8">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O370" s="8"/>
       <c r="P370" s="9"/>
@@ -23386,7 +23377,7 @@
         <v>5</v>
       </c>
       <c r="N373" s="8">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="O373" s="8"/>
       <c r="P373" s="9"/>
@@ -23523,7 +23514,7 @@
         <v>12</v>
       </c>
       <c r="I376" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J376" s="8">
         <v>0</v>
@@ -23536,7 +23527,7 @@
       </c>
       <c r="M376" s="8">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N376" s="8">
         <v>0</v>
@@ -23625,7 +23616,7 @@
         <v>14</v>
       </c>
       <c r="I378" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J378" s="8">
         <v>0</v>
@@ -23638,7 +23629,7 @@
       </c>
       <c r="M378" s="8">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N378" s="8">
         <v>0</v>
@@ -23676,7 +23667,7 @@
         <v>14</v>
       </c>
       <c r="I379" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J379" s="8">
         <v>0</v>
@@ -23689,7 +23680,7 @@
       </c>
       <c r="M379" s="8">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N379" s="8">
         <v>0</v>
@@ -23727,7 +23718,7 @@
         <v>12</v>
       </c>
       <c r="I380" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J380" s="8">
         <v>0</v>
@@ -23740,7 +23731,7 @@
       </c>
       <c r="M380" s="8">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N380" s="8">
         <v>0</v>
@@ -23778,7 +23769,7 @@
         <v>17</v>
       </c>
       <c r="I381" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J381" s="8">
         <v>0</v>
@@ -23791,7 +23782,7 @@
       </c>
       <c r="M381" s="8">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N381" s="8">
         <v>0</v>
@@ -23880,7 +23871,7 @@
         <v>12</v>
       </c>
       <c r="I383" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J383" s="8">
         <v>0</v>
@@ -23893,7 +23884,7 @@
       </c>
       <c r="M383" s="8">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N383" s="8">
         <v>0</v>
@@ -23947,7 +23938,7 @@
         <v>5</v>
       </c>
       <c r="N384" s="8">
-        <v>175</v>
+        <v>128</v>
       </c>
       <c r="O384" s="8"/>
       <c r="P384" s="9"/>
@@ -23982,23 +23973,23 @@
         <v>12</v>
       </c>
       <c r="I385" s="8">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J385" s="8">
         <v>0</v>
       </c>
       <c r="K385" s="8">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="L385" s="8">
         <v>0</v>
       </c>
       <c r="M385" s="8">
         <f t="shared" si="5"/>
-        <v>129</v>
+        <v>173</v>
       </c>
       <c r="N385" s="8">
-        <v>353</v>
+        <v>305</v>
       </c>
       <c r="O385" s="8"/>
       <c r="P385" s="7"/>
@@ -24151,7 +24142,7 @@
         <v>0</v>
       </c>
       <c r="N388" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O388" s="8"/>
       <c r="P388" s="7"/>
@@ -24253,7 +24244,7 @@
         <v>5</v>
       </c>
       <c r="N390" s="8">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="O390" s="8"/>
       <c r="P390" s="7"/>
@@ -24288,7 +24279,7 @@
         <v>12</v>
       </c>
       <c r="I391" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J391" s="8">
         <v>0</v>
@@ -24301,7 +24292,7 @@
       </c>
       <c r="M391" s="8">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N391" s="8">
         <v>0</v>
@@ -24441,7 +24432,7 @@
         <v>12</v>
       </c>
       <c r="I394" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J394" s="8">
         <v>0</v>
@@ -24454,7 +24445,7 @@
       </c>
       <c r="M394" s="8">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N394" s="8">
         <v>0</v>
@@ -24543,7 +24534,7 @@
         <v>12</v>
       </c>
       <c r="I396" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J396" s="8">
         <v>0</v>
@@ -24556,7 +24547,7 @@
       </c>
       <c r="M396" s="8">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N396" s="8">
         <v>0</v>
@@ -24651,17 +24642,17 @@
         <v>0</v>
       </c>
       <c r="K398" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L398" s="8">
         <v>0</v>
       </c>
       <c r="M398" s="8">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N398" s="8">
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="O398" s="7"/>
       <c r="P398" s="7"/>
@@ -24865,7 +24856,7 @@
         <v>0</v>
       </c>
       <c r="N402" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O402" s="7"/>
       <c r="P402" s="7"/>

--- a/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
+++ b/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\Fossil Replenishment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED659486-E664-421E-9999-0EBD0A5D8EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F13E24F-C4AD-4270-8B2A-63BAC3DFD745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6662473D-6E1F-42FD-999B-28162E22D4B5}"/>
   </bookViews>
@@ -16,19 +16,28 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$T$402</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$T$403</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3228" uniqueCount="1249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3236" uniqueCount="1252">
   <si>
     <t>In Transit PO</t>
   </si>
@@ -3775,6 +3784,15 @@
   </si>
   <si>
     <t>FBA79902</t>
+  </si>
+  <si>
+    <t>AX2765</t>
+  </si>
+  <si>
+    <t>B0FRVT4SJ1</t>
+  </si>
+  <si>
+    <t>FBA79922</t>
   </si>
 </sst>
 </file>
@@ -3870,7 +3888,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3902,11 +3920,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -4440,23 +4491,23 @@
         <v>12</v>
       </c>
       <c r="I2" s="8">
-        <v>572</v>
+        <v>650</v>
       </c>
       <c r="J2" s="8">
         <v>0</v>
       </c>
       <c r="K2" s="8">
-        <v>121</v>
+        <v>207</v>
       </c>
       <c r="L2" s="8">
         <v>0</v>
       </c>
       <c r="M2" s="8">
         <f>I2+J2+K2+L2</f>
-        <v>693</v>
+        <v>857</v>
       </c>
       <c r="N2" s="8">
-        <v>1671</v>
+        <v>1479</v>
       </c>
       <c r="O2" s="8"/>
       <c r="P2" s="8"/>
@@ -4491,7 +4542,7 @@
         <v>12</v>
       </c>
       <c r="I3" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3" s="8">
         <v>0</v>
@@ -4504,7 +4555,7 @@
       </c>
       <c r="M3" s="8">
         <f t="shared" ref="M3:M66" si="0">I3+J3+K3+L3</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N3" s="8">
         <v>0</v>
@@ -4542,7 +4593,7 @@
         <v>12</v>
       </c>
       <c r="I4" s="8">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="J4" s="8">
         <v>0</v>
@@ -4555,7 +4606,7 @@
       </c>
       <c r="M4" s="8">
         <f t="shared" si="0"/>
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="N4" s="8">
         <v>0</v>
@@ -4593,7 +4644,7 @@
         <v>12</v>
       </c>
       <c r="I5" s="8">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="J5" s="8">
         <v>0</v>
@@ -4606,7 +4657,7 @@
       </c>
       <c r="M5" s="8">
         <f t="shared" si="0"/>
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="N5" s="8">
         <v>0</v>
@@ -4644,23 +4695,23 @@
         <v>12</v>
       </c>
       <c r="I6" s="8">
-        <v>632</v>
+        <v>675</v>
       </c>
       <c r="J6" s="8">
         <v>0</v>
       </c>
       <c r="K6" s="8">
-        <v>146</v>
+        <v>178</v>
       </c>
       <c r="L6" s="8">
         <v>0</v>
       </c>
       <c r="M6" s="8">
         <f t="shared" si="0"/>
-        <v>778</v>
+        <v>853</v>
       </c>
       <c r="N6" s="8">
-        <v>2030</v>
+        <v>1862</v>
       </c>
       <c r="O6" s="8"/>
       <c r="P6" s="8"/>
@@ -4695,23 +4746,23 @@
         <v>12</v>
       </c>
       <c r="I7" s="8">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="J7" s="8">
         <v>0</v>
       </c>
       <c r="K7" s="8">
-        <v>128</v>
+        <v>176</v>
       </c>
       <c r="L7" s="8">
         <v>0</v>
       </c>
       <c r="M7" s="8">
         <f t="shared" si="0"/>
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="N7" s="8">
-        <v>303</v>
+        <v>211</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
@@ -4746,7 +4797,7 @@
         <v>12</v>
       </c>
       <c r="I8" s="8">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="J8" s="8">
         <v>0</v>
@@ -4759,10 +4810,10 @@
       </c>
       <c r="M8" s="8">
         <f t="shared" si="0"/>
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="N8" s="8">
-        <v>681</v>
+        <v>1111</v>
       </c>
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
@@ -4797,7 +4848,7 @@
         <v>12</v>
       </c>
       <c r="I9" s="8">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J9" s="8">
         <v>0</v>
@@ -4810,10 +4861,10 @@
       </c>
       <c r="M9" s="8">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N9" s="8">
-        <v>562</v>
+        <v>531</v>
       </c>
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
@@ -4848,7 +4899,7 @@
         <v>12</v>
       </c>
       <c r="I10" s="8">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="J10" s="8">
         <v>0</v>
@@ -4861,10 +4912,10 @@
       </c>
       <c r="M10" s="8">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="N10" s="8">
-        <v>503</v>
+        <v>477</v>
       </c>
       <c r="O10" s="8"/>
       <c r="P10" s="8"/>
@@ -4899,23 +4950,23 @@
         <v>12</v>
       </c>
       <c r="I11" s="8">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="J11" s="8">
         <v>0</v>
       </c>
       <c r="K11" s="8">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="L11" s="8">
         <v>0</v>
       </c>
       <c r="M11" s="8">
         <f t="shared" si="0"/>
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="N11" s="8">
-        <v>300</v>
+        <v>321</v>
       </c>
       <c r="O11" s="8"/>
       <c r="P11" s="8"/>
@@ -4950,23 +5001,23 @@
         <v>12</v>
       </c>
       <c r="I12" s="8">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J12" s="8">
         <v>0</v>
       </c>
       <c r="K12" s="8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L12" s="8">
         <v>0</v>
       </c>
       <c r="M12" s="8">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="N12" s="8">
-        <v>858</v>
+        <v>2436</v>
       </c>
       <c r="O12" s="8"/>
       <c r="P12" s="8"/>
@@ -5001,23 +5052,23 @@
         <v>12</v>
       </c>
       <c r="I13" s="8">
-        <v>179</v>
+        <v>226</v>
       </c>
       <c r="J13" s="8">
         <v>0</v>
       </c>
       <c r="K13" s="8">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="L13" s="8">
         <v>0</v>
       </c>
       <c r="M13" s="8">
         <f t="shared" si="0"/>
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="N13" s="8">
-        <v>998</v>
+        <v>962</v>
       </c>
       <c r="O13" s="8"/>
       <c r="P13" s="8"/>
@@ -5052,23 +5103,23 @@
         <v>12</v>
       </c>
       <c r="I14" s="8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J14" s="8">
         <v>0</v>
       </c>
       <c r="K14" s="8">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="L14" s="8">
         <v>0</v>
       </c>
       <c r="M14" s="8">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="N14" s="8">
-        <v>1268</v>
+        <v>1208</v>
       </c>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
@@ -5103,23 +5154,23 @@
         <v>12</v>
       </c>
       <c r="I15" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" s="8">
         <v>0</v>
       </c>
       <c r="K15" s="8">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="L15" s="8">
         <v>0</v>
       </c>
       <c r="M15" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="N15" s="8">
-        <v>276</v>
+        <v>346</v>
       </c>
       <c r="O15" s="8"/>
       <c r="P15" s="8"/>
@@ -5154,23 +5205,23 @@
         <v>12</v>
       </c>
       <c r="I16" s="8">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="J16" s="8">
         <v>0</v>
       </c>
       <c r="K16" s="8">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L16" s="8">
         <v>0</v>
       </c>
       <c r="M16" s="8">
         <f t="shared" si="0"/>
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N16" s="8">
-        <v>661</v>
+        <v>638</v>
       </c>
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
@@ -5205,7 +5256,7 @@
         <v>12</v>
       </c>
       <c r="I17" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J17" s="8">
         <v>0</v>
@@ -5218,10 +5269,10 @@
       </c>
       <c r="M17" s="8">
         <f t="shared" si="0"/>
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N17" s="8">
-        <v>470</v>
+        <v>494</v>
       </c>
       <c r="O17" s="8"/>
       <c r="P17" s="8"/>
@@ -5256,13 +5307,13 @@
         <v>12</v>
       </c>
       <c r="I18" s="8">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J18" s="8">
         <v>0</v>
       </c>
       <c r="K18" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="8">
         <v>0</v>
@@ -5272,7 +5323,7 @@
         <v>34</v>
       </c>
       <c r="N18" s="8">
-        <v>636</v>
+        <v>610</v>
       </c>
       <c r="O18" s="8"/>
       <c r="P18" s="8"/>
@@ -5307,7 +5358,7 @@
         <v>13</v>
       </c>
       <c r="I19" s="8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J19" s="8">
         <v>0</v>
@@ -5320,10 +5371,10 @@
       </c>
       <c r="M19" s="8">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N19" s="8">
-        <v>618</v>
+        <v>554</v>
       </c>
       <c r="O19" s="8"/>
       <c r="P19" s="8"/>
@@ -5364,17 +5415,17 @@
         <v>0</v>
       </c>
       <c r="K20" s="8">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L20" s="8">
         <v>0</v>
       </c>
       <c r="M20" s="8">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="N20" s="8">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="O20" s="8"/>
       <c r="P20" s="8"/>
@@ -5409,23 +5460,23 @@
         <v>13</v>
       </c>
       <c r="I21" s="8">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="J21" s="8">
         <v>0</v>
       </c>
       <c r="K21" s="8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L21" s="8">
         <v>0</v>
       </c>
       <c r="M21" s="8">
         <f t="shared" si="0"/>
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N21" s="8">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="O21" s="8"/>
       <c r="P21" s="8"/>
@@ -5511,23 +5562,23 @@
         <v>12</v>
       </c>
       <c r="I23" s="8">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J23" s="8">
         <v>0</v>
       </c>
       <c r="K23" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L23" s="8">
         <v>0</v>
       </c>
       <c r="M23" s="8">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N23" s="8">
-        <v>166</v>
+        <v>93</v>
       </c>
       <c r="O23" s="8"/>
       <c r="P23" s="8"/>
@@ -5562,7 +5613,7 @@
         <v>14</v>
       </c>
       <c r="I24" s="8">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J24" s="8">
         <v>0</v>
@@ -5575,10 +5626,10 @@
       </c>
       <c r="M24" s="8">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N24" s="8">
-        <v>762</v>
+        <v>817</v>
       </c>
       <c r="O24" s="8"/>
       <c r="P24" s="8"/>
@@ -5664,23 +5715,23 @@
         <v>12</v>
       </c>
       <c r="I26" s="8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J26" s="8">
         <v>0</v>
       </c>
       <c r="K26" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L26" s="8">
         <v>0</v>
       </c>
       <c r="M26" s="8">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="N26" s="8">
-        <v>1003</v>
+        <v>913</v>
       </c>
       <c r="O26" s="8"/>
       <c r="P26" s="8"/>
@@ -5731,7 +5782,7 @@
         <v>27</v>
       </c>
       <c r="N27" s="8">
-        <v>904</v>
+        <v>877</v>
       </c>
       <c r="O27" s="8"/>
       <c r="P27" s="8"/>
@@ -5766,7 +5817,7 @@
         <v>12</v>
       </c>
       <c r="I28" s="8">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J28" s="8">
         <v>0</v>
@@ -5779,7 +5830,7 @@
       </c>
       <c r="M28" s="8">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="N28" s="8">
         <v>0</v>
@@ -5817,7 +5868,7 @@
         <v>13</v>
       </c>
       <c r="I29" s="8">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J29" s="8">
         <v>0</v>
@@ -5830,10 +5881,10 @@
       </c>
       <c r="M29" s="8">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N29" s="8">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="O29" s="8"/>
       <c r="P29" s="8"/>
@@ -5868,7 +5919,7 @@
         <v>14</v>
       </c>
       <c r="I30" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J30" s="8">
         <v>0</v>
@@ -5881,10 +5932,10 @@
       </c>
       <c r="M30" s="8">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N30" s="8">
-        <v>1155</v>
+        <v>1127</v>
       </c>
       <c r="O30" s="8"/>
       <c r="P30" s="8"/>
@@ -5919,7 +5970,7 @@
         <v>13</v>
       </c>
       <c r="I31" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J31" s="8">
         <v>0</v>
@@ -5932,7 +5983,7 @@
       </c>
       <c r="M31" s="8">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N31" s="8">
         <v>0</v>
@@ -5970,23 +6021,23 @@
         <v>12</v>
       </c>
       <c r="I32" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J32" s="8">
         <v>0</v>
       </c>
       <c r="K32" s="8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L32" s="8">
         <v>0</v>
       </c>
       <c r="M32" s="8">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="N32" s="8">
-        <v>820</v>
+        <v>808</v>
       </c>
       <c r="O32" s="8"/>
       <c r="P32" s="8"/>
@@ -6021,7 +6072,7 @@
         <v>12</v>
       </c>
       <c r="I33" s="8">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J33" s="8">
         <v>0</v>
@@ -6034,10 +6085,10 @@
       </c>
       <c r="M33" s="8">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N33" s="8">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="O33" s="8"/>
       <c r="P33" s="8"/>
@@ -6088,7 +6139,7 @@
         <v>22</v>
       </c>
       <c r="N34" s="8">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="O34" s="8"/>
       <c r="P34" s="8"/>
@@ -6123,7 +6174,7 @@
         <v>12</v>
       </c>
       <c r="I35" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J35" s="8">
         <v>0</v>
@@ -6136,10 +6187,10 @@
       </c>
       <c r="M35" s="8">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N35" s="8">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="O35" s="8"/>
       <c r="P35" s="8"/>
@@ -6174,7 +6225,7 @@
         <v>13</v>
       </c>
       <c r="I36" s="8">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J36" s="8">
         <v>0</v>
@@ -6187,10 +6238,10 @@
       </c>
       <c r="M36" s="8">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="N36" s="8">
-        <v>792</v>
+        <v>780</v>
       </c>
       <c r="O36" s="8"/>
       <c r="P36" s="8"/>
@@ -6225,7 +6276,7 @@
         <v>13</v>
       </c>
       <c r="I37" s="8">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J37" s="8">
         <v>0</v>
@@ -6238,10 +6289,10 @@
       </c>
       <c r="M37" s="8">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="N37" s="8">
-        <v>769</v>
+        <v>733</v>
       </c>
       <c r="O37" s="8"/>
       <c r="P37" s="8"/>
@@ -6276,7 +6327,7 @@
         <v>12</v>
       </c>
       <c r="I38" s="8">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J38" s="8">
         <v>0</v>
@@ -6289,10 +6340,10 @@
       </c>
       <c r="M38" s="8">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N38" s="8">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="O38" s="8"/>
       <c r="P38" s="8"/>
@@ -6333,17 +6384,17 @@
         <v>0</v>
       </c>
       <c r="K39" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L39" s="8">
         <v>0</v>
       </c>
       <c r="M39" s="8">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="N39" s="8">
-        <v>1762</v>
+        <v>1679</v>
       </c>
       <c r="O39" s="8"/>
       <c r="P39" s="8"/>
@@ -6378,23 +6429,23 @@
         <v>12</v>
       </c>
       <c r="I40" s="8">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J40" s="8">
         <v>0</v>
       </c>
       <c r="K40" s="8">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L40" s="8">
         <v>0</v>
       </c>
       <c r="M40" s="8">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N40" s="8">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O40" s="8"/>
       <c r="P40" s="8"/>
@@ -6429,7 +6480,7 @@
         <v>12</v>
       </c>
       <c r="I41" s="8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J41" s="8">
         <v>0</v>
@@ -6442,10 +6493,10 @@
       </c>
       <c r="M41" s="8">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N41" s="8">
-        <v>275</v>
+        <v>301</v>
       </c>
       <c r="O41" s="8"/>
       <c r="P41" s="8"/>
@@ -6531,23 +6582,23 @@
         <v>12</v>
       </c>
       <c r="I43" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J43" s="8">
         <v>0</v>
       </c>
       <c r="K43" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L43" s="8">
         <v>0</v>
       </c>
       <c r="M43" s="8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="N43" s="8">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="O43" s="8"/>
       <c r="P43" s="8"/>
@@ -6598,7 +6649,7 @@
         <v>11</v>
       </c>
       <c r="N44" s="8">
-        <v>513</v>
+        <v>494</v>
       </c>
       <c r="O44" s="8"/>
       <c r="P44" s="8"/>
@@ -6633,7 +6684,7 @@
         <v>12</v>
       </c>
       <c r="I45" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J45" s="8">
         <v>0</v>
@@ -6646,10 +6697,10 @@
       </c>
       <c r="M45" s="8">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N45" s="8">
-        <v>897</v>
+        <v>904</v>
       </c>
       <c r="O45" s="8"/>
       <c r="P45" s="8"/>
@@ -6700,7 +6751,7 @@
         <v>15</v>
       </c>
       <c r="N46" s="8">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="O46" s="8"/>
       <c r="P46" s="8"/>
@@ -6735,7 +6786,7 @@
         <v>13</v>
       </c>
       <c r="I47" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J47" s="8">
         <v>0</v>
@@ -6748,10 +6799,10 @@
       </c>
       <c r="M47" s="8">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N47" s="8">
-        <v>282</v>
+        <v>1060</v>
       </c>
       <c r="O47" s="8"/>
       <c r="P47" s="8"/>
@@ -6802,7 +6853,7 @@
         <v>19</v>
       </c>
       <c r="N48" s="8">
-        <v>1188</v>
+        <v>1113</v>
       </c>
       <c r="O48" s="8"/>
       <c r="P48" s="8"/>
@@ -6853,7 +6904,7 @@
         <v>16</v>
       </c>
       <c r="N49" s="8">
-        <v>1033</v>
+        <v>1023</v>
       </c>
       <c r="O49" s="8"/>
       <c r="P49" s="8"/>
@@ -6904,7 +6955,7 @@
         <v>8</v>
       </c>
       <c r="N50" s="8">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="O50" s="8"/>
       <c r="P50" s="8"/>
@@ -6955,7 +7006,7 @@
         <v>24</v>
       </c>
       <c r="N51" s="8">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="O51" s="8"/>
       <c r="P51" s="8"/>
@@ -6990,23 +7041,23 @@
         <v>12</v>
       </c>
       <c r="I52" s="8">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="J52" s="8">
         <v>0</v>
       </c>
       <c r="K52" s="8">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="L52" s="8">
         <v>0</v>
       </c>
       <c r="M52" s="8">
         <f t="shared" si="0"/>
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="N52" s="8">
-        <v>1239</v>
+        <v>1218</v>
       </c>
       <c r="O52" s="8"/>
       <c r="P52" s="8"/>
@@ -7057,7 +7108,7 @@
         <v>9</v>
       </c>
       <c r="N53" s="8">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="O53" s="8"/>
       <c r="P53" s="8"/>
@@ -7092,7 +7143,7 @@
         <v>12</v>
       </c>
       <c r="I54" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J54" s="8">
         <v>0</v>
@@ -7105,10 +7156,10 @@
       </c>
       <c r="M54" s="8">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N54" s="8">
-        <v>489</v>
+        <v>439</v>
       </c>
       <c r="O54" s="8"/>
       <c r="P54" s="8"/>
@@ -7143,23 +7194,23 @@
         <v>12</v>
       </c>
       <c r="I55" s="8">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J55" s="8">
         <v>0</v>
       </c>
       <c r="K55" s="8">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="L55" s="8">
         <v>0</v>
       </c>
       <c r="M55" s="8">
         <f t="shared" si="0"/>
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="N55" s="8">
-        <v>317</v>
+        <v>295</v>
       </c>
       <c r="O55" s="8"/>
       <c r="P55" s="8"/>
@@ -7210,7 +7261,7 @@
         <v>6</v>
       </c>
       <c r="N56" s="8">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O56" s="8"/>
       <c r="P56" s="8"/>
@@ -7251,17 +7302,17 @@
         <v>0</v>
       </c>
       <c r="K57" s="8">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L57" s="8">
         <v>0</v>
       </c>
       <c r="M57" s="8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="N57" s="8">
-        <v>525</v>
+        <v>604</v>
       </c>
       <c r="O57" s="8"/>
       <c r="P57" s="8"/>
@@ -7296,7 +7347,7 @@
         <v>12</v>
       </c>
       <c r="I58" s="8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J58" s="8">
         <v>0</v>
@@ -7309,10 +7360,10 @@
       </c>
       <c r="M58" s="8">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N58" s="8">
-        <v>669</v>
+        <v>660</v>
       </c>
       <c r="O58" s="8"/>
       <c r="P58" s="8"/>
@@ -7347,7 +7398,7 @@
         <v>13</v>
       </c>
       <c r="I59" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J59" s="8">
         <v>0</v>
@@ -7360,10 +7411,10 @@
       </c>
       <c r="M59" s="8">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N59" s="8">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="O59" s="8"/>
       <c r="P59" s="8"/>
@@ -7414,7 +7465,7 @@
         <v>5</v>
       </c>
       <c r="N60" s="8">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="O60" s="8"/>
       <c r="P60" s="8"/>
@@ -7449,23 +7500,23 @@
         <v>12</v>
       </c>
       <c r="I61" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J61" s="8">
         <v>0</v>
       </c>
       <c r="K61" s="8">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="L61" s="8">
         <v>0</v>
       </c>
       <c r="M61" s="8">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="N61" s="8">
-        <v>639</v>
+        <v>593</v>
       </c>
       <c r="O61" s="8"/>
       <c r="P61" s="8"/>
@@ -7516,7 +7567,7 @@
         <v>8</v>
       </c>
       <c r="N62" s="8">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="O62" s="8"/>
       <c r="P62" s="8"/>
@@ -7551,7 +7602,7 @@
         <v>12</v>
       </c>
       <c r="I63" s="8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J63" s="8">
         <v>0</v>
@@ -7564,10 +7615,10 @@
       </c>
       <c r="M63" s="8">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N63" s="8">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O63" s="8"/>
       <c r="P63" s="8"/>
@@ -7618,7 +7669,7 @@
         <v>11</v>
       </c>
       <c r="N64" s="8">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="O64" s="8"/>
       <c r="P64" s="8"/>
@@ -7669,7 +7720,7 @@
         <v>7</v>
       </c>
       <c r="N65" s="8">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="O65" s="8"/>
       <c r="P65" s="8"/>
@@ -7720,7 +7771,7 @@
         <v>4</v>
       </c>
       <c r="N66" s="8">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="O66" s="8"/>
       <c r="P66" s="8"/>
@@ -7771,7 +7822,7 @@
         <v>5</v>
       </c>
       <c r="N67" s="8">
-        <v>227</v>
+        <v>195</v>
       </c>
       <c r="O67" s="8"/>
       <c r="P67" s="8"/>
@@ -7806,7 +7857,7 @@
         <v>12</v>
       </c>
       <c r="I68" s="8">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J68" s="8">
         <v>0</v>
@@ -7819,10 +7870,10 @@
       </c>
       <c r="M68" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N68" s="8">
-        <v>990</v>
+        <v>983</v>
       </c>
       <c r="O68" s="8"/>
       <c r="P68" s="8"/>
@@ -7873,7 +7924,7 @@
         <v>11</v>
       </c>
       <c r="N69" s="8">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="O69" s="8"/>
       <c r="P69" s="8"/>
@@ -7908,7 +7959,7 @@
         <v>16</v>
       </c>
       <c r="I70" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J70" s="8">
         <v>0</v>
@@ -7921,10 +7972,10 @@
       </c>
       <c r="M70" s="8">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N70" s="8">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="O70" s="8"/>
       <c r="P70" s="8"/>
@@ -7975,7 +8026,7 @@
         <v>8</v>
       </c>
       <c r="N71" s="8">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="O71" s="8"/>
       <c r="P71" s="8"/>
@@ -8026,7 +8077,7 @@
         <v>10</v>
       </c>
       <c r="N72" s="8">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="O72" s="8"/>
       <c r="P72" s="8"/>
@@ -8061,23 +8112,23 @@
         <v>12</v>
       </c>
       <c r="I73" s="8">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J73" s="8">
         <v>0</v>
       </c>
       <c r="K73" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L73" s="8">
         <v>0</v>
       </c>
       <c r="M73" s="8">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="N73" s="8">
-        <v>792</v>
+        <v>901</v>
       </c>
       <c r="O73" s="8"/>
       <c r="P73" s="8"/>
@@ -8112,23 +8163,23 @@
         <v>14</v>
       </c>
       <c r="I74" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J74" s="8">
         <v>0</v>
       </c>
       <c r="K74" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L74" s="8">
         <v>0</v>
       </c>
       <c r="M74" s="8">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N74" s="8">
-        <v>251</v>
+        <v>278</v>
       </c>
       <c r="O74" s="8"/>
       <c r="P74" s="8"/>
@@ -8163,7 +8214,7 @@
         <v>13</v>
       </c>
       <c r="I75" s="8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J75" s="8">
         <v>0</v>
@@ -8176,7 +8227,7 @@
       </c>
       <c r="M75" s="8">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N75" s="8">
         <v>38</v>
@@ -8214,7 +8265,7 @@
         <v>13</v>
       </c>
       <c r="I76" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J76" s="8">
         <v>0</v>
@@ -8227,10 +8278,10 @@
       </c>
       <c r="M76" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N76" s="8">
-        <v>980</v>
+        <v>967</v>
       </c>
       <c r="O76" s="8"/>
       <c r="P76" s="8"/>
@@ -8265,7 +8316,7 @@
         <v>12</v>
       </c>
       <c r="I77" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J77" s="8">
         <v>0</v>
@@ -8278,10 +8329,10 @@
       </c>
       <c r="M77" s="8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N77" s="8">
-        <v>445</v>
+        <v>413</v>
       </c>
       <c r="O77" s="8"/>
       <c r="P77" s="8"/>
@@ -8316,23 +8367,23 @@
         <v>12</v>
       </c>
       <c r="I78" s="8">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J78" s="8">
         <v>0</v>
       </c>
       <c r="K78" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="8">
         <v>0</v>
       </c>
       <c r="M78" s="8">
         <f t="shared" si="1"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N78" s="8">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="O78" s="8"/>
       <c r="P78" s="8"/>
@@ -8367,7 +8418,7 @@
         <v>13</v>
       </c>
       <c r="I79" s="8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J79" s="8">
         <v>0</v>
@@ -8380,10 +8431,10 @@
       </c>
       <c r="M79" s="8">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N79" s="8">
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="O79" s="8"/>
       <c r="P79" s="8"/>
@@ -8418,7 +8469,7 @@
         <v>13</v>
       </c>
       <c r="I80" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J80" s="8">
         <v>0</v>
@@ -8431,7 +8482,7 @@
       </c>
       <c r="M80" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N80" s="8">
         <v>0</v>
@@ -8526,17 +8577,17 @@
         <v>0</v>
       </c>
       <c r="K82" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L82" s="8">
         <v>0</v>
       </c>
       <c r="M82" s="8">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N82" s="8">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="O82" s="8"/>
       <c r="P82" s="8"/>
@@ -8587,7 +8638,7 @@
         <v>6</v>
       </c>
       <c r="N83" s="8">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="O83" s="8"/>
       <c r="P83" s="8"/>
@@ -8673,7 +8724,7 @@
         <v>14</v>
       </c>
       <c r="I85" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J85" s="8">
         <v>0</v>
@@ -8686,10 +8737,10 @@
       </c>
       <c r="M85" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N85" s="8">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="O85" s="8"/>
       <c r="P85" s="8"/>
@@ -8724,7 +8775,7 @@
         <v>12</v>
       </c>
       <c r="I86" s="8">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J86" s="8">
         <v>0</v>
@@ -8737,10 +8788,10 @@
       </c>
       <c r="M86" s="8">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="N86" s="8">
-        <v>671</v>
+        <v>703</v>
       </c>
       <c r="O86" s="8"/>
       <c r="P86" s="8"/>
@@ -8791,7 +8842,7 @@
         <v>7</v>
       </c>
       <c r="N87" s="8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O87" s="8"/>
       <c r="P87" s="8"/>
@@ -8832,17 +8883,17 @@
         <v>0</v>
       </c>
       <c r="K88" s="8">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="L88" s="8">
         <v>0</v>
       </c>
       <c r="M88" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="N88" s="8">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="O88" s="8"/>
       <c r="P88" s="8"/>
@@ -8893,7 +8944,7 @@
         <v>27</v>
       </c>
       <c r="N89" s="8">
-        <v>191</v>
+        <v>155</v>
       </c>
       <c r="O89" s="8"/>
       <c r="P89" s="8"/>
@@ -8928,7 +8979,7 @@
         <v>12</v>
       </c>
       <c r="I90" s="8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J90" s="8">
         <v>0</v>
@@ -8941,10 +8992,10 @@
       </c>
       <c r="M90" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N90" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O90" s="8"/>
       <c r="P90" s="8"/>
@@ -8995,7 +9046,7 @@
         <v>4</v>
       </c>
       <c r="N91" s="8">
-        <v>1273</v>
+        <v>1256</v>
       </c>
       <c r="O91" s="8"/>
       <c r="P91" s="8"/>
@@ -9046,7 +9097,7 @@
         <v>7</v>
       </c>
       <c r="N92" s="8">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="O92" s="8"/>
       <c r="P92" s="8"/>
@@ -9081,13 +9132,13 @@
         <v>13</v>
       </c>
       <c r="I93" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J93" s="8">
         <v>0</v>
       </c>
       <c r="K93" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L93" s="8">
         <v>0</v>
@@ -9097,7 +9148,7 @@
         <v>6</v>
       </c>
       <c r="N93" s="8">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="O93" s="8"/>
       <c r="P93" s="8"/>
@@ -9132,7 +9183,7 @@
         <v>12</v>
       </c>
       <c r="I94" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J94" s="8">
         <v>0</v>
@@ -9145,7 +9196,7 @@
       </c>
       <c r="M94" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N94" s="8">
         <v>0</v>
@@ -9183,7 +9234,7 @@
         <v>12</v>
       </c>
       <c r="I95" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J95" s="8">
         <v>0</v>
@@ -9196,10 +9247,10 @@
       </c>
       <c r="M95" s="8">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N95" s="8">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O95" s="8"/>
       <c r="P95" s="8"/>
@@ -9250,7 +9301,7 @@
         <v>8</v>
       </c>
       <c r="N96" s="8">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="O96" s="8"/>
       <c r="P96" s="8"/>
@@ -9301,7 +9352,7 @@
         <v>12</v>
       </c>
       <c r="N97" s="8">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="O97" s="8"/>
       <c r="P97" s="8"/>
@@ -9438,7 +9489,7 @@
         <v>15</v>
       </c>
       <c r="I100" s="8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J100" s="8">
         <v>0</v>
@@ -9451,7 +9502,7 @@
       </c>
       <c r="M100" s="8">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N100" s="8">
         <v>0</v>
@@ -9505,7 +9556,7 @@
         <v>3</v>
       </c>
       <c r="N101" s="8">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O101" s="8"/>
       <c r="P101" s="8"/>
@@ -9540,23 +9591,23 @@
         <v>14</v>
       </c>
       <c r="I102" s="8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J102" s="8">
         <v>0</v>
       </c>
       <c r="K102" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L102" s="8">
         <v>0</v>
       </c>
       <c r="M102" s="8">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N102" s="8">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="O102" s="8"/>
       <c r="P102" s="8"/>
@@ -9591,7 +9642,7 @@
         <v>15</v>
       </c>
       <c r="I103" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J103" s="8">
         <v>0</v>
@@ -9604,10 +9655,10 @@
       </c>
       <c r="M103" s="8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N103" s="8">
-        <v>588</v>
+        <v>554</v>
       </c>
       <c r="O103" s="8"/>
       <c r="P103" s="8"/>
@@ -9709,7 +9760,7 @@
         <v>8</v>
       </c>
       <c r="N105" s="8">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="O105" s="8"/>
       <c r="P105" s="8"/>
@@ -9744,7 +9795,7 @@
         <v>15</v>
       </c>
       <c r="I106" s="8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J106" s="8">
         <v>0</v>
@@ -9757,7 +9808,7 @@
       </c>
       <c r="M106" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N106" s="8">
         <v>3</v>
@@ -9913,7 +9964,7 @@
         <v>6</v>
       </c>
       <c r="N109" s="8">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="O109" s="8"/>
       <c r="P109" s="8"/>
@@ -9948,7 +9999,7 @@
         <v>13</v>
       </c>
       <c r="I110" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J110" s="8">
         <v>0</v>
@@ -9961,10 +10012,10 @@
       </c>
       <c r="M110" s="8">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N110" s="8">
-        <v>68</v>
+        <v>559</v>
       </c>
       <c r="O110" s="8"/>
       <c r="P110" s="8"/>
@@ -9999,7 +10050,7 @@
         <v>13</v>
       </c>
       <c r="I111" s="8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J111" s="8">
         <v>0</v>
@@ -10012,7 +10063,7 @@
       </c>
       <c r="M111" s="8">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N111" s="8">
         <v>0</v>
@@ -10050,23 +10101,23 @@
         <v>12</v>
       </c>
       <c r="I112" s="8">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="J112" s="8">
         <v>0</v>
       </c>
       <c r="K112" s="8">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="L112" s="8">
         <v>0</v>
       </c>
       <c r="M112" s="8">
         <f t="shared" si="1"/>
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="N112" s="8">
-        <v>333</v>
+        <v>247</v>
       </c>
       <c r="O112" s="8"/>
       <c r="P112" s="8"/>
@@ -10101,7 +10152,7 @@
         <v>12</v>
       </c>
       <c r="I113" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J113" s="8">
         <v>0</v>
@@ -10114,10 +10165,10 @@
       </c>
       <c r="M113" s="8">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N113" s="8">
-        <v>1226</v>
+        <v>1198</v>
       </c>
       <c r="O113" s="8"/>
       <c r="P113" s="8"/>
@@ -10152,7 +10203,7 @@
         <v>13</v>
       </c>
       <c r="I114" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J114" s="8">
         <v>0</v>
@@ -10165,10 +10216,10 @@
       </c>
       <c r="M114" s="8">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N114" s="8">
-        <v>727</v>
+        <v>664</v>
       </c>
       <c r="O114" s="8"/>
       <c r="P114" s="8"/>
@@ -10219,7 +10270,7 @@
         <v>11</v>
       </c>
       <c r="N115" s="8">
-        <v>351</v>
+        <v>332</v>
       </c>
       <c r="O115" s="8"/>
       <c r="P115" s="8"/>
@@ -10254,7 +10305,7 @@
         <v>12</v>
       </c>
       <c r="I116" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J116" s="8">
         <v>0</v>
@@ -10267,10 +10318,10 @@
       </c>
       <c r="M116" s="8">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N116" s="8">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="O116" s="8"/>
       <c r="P116" s="8"/>
@@ -10305,13 +10356,13 @@
         <v>12</v>
       </c>
       <c r="I117" s="8">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J117" s="8">
         <v>0</v>
       </c>
       <c r="K117" s="8">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L117" s="8">
         <v>0</v>
@@ -10321,7 +10372,7 @@
         <v>31</v>
       </c>
       <c r="N117" s="8">
-        <v>515</v>
+        <v>498</v>
       </c>
       <c r="O117" s="8"/>
       <c r="P117" s="8"/>
@@ -10356,7 +10407,7 @@
         <v>13</v>
       </c>
       <c r="I118" s="8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J118" s="8">
         <v>0</v>
@@ -10369,7 +10420,7 @@
       </c>
       <c r="M118" s="8">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N118" s="8">
         <v>167</v>
@@ -10407,7 +10458,7 @@
         <v>14</v>
       </c>
       <c r="I119" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J119" s="8">
         <v>0</v>
@@ -10420,10 +10471,10 @@
       </c>
       <c r="M119" s="8">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N119" s="8">
-        <v>567</v>
+        <v>553</v>
       </c>
       <c r="O119" s="8"/>
       <c r="P119" s="8"/>
@@ -10474,7 +10525,7 @@
         <v>13</v>
       </c>
       <c r="N120" s="8">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="O120" s="8"/>
       <c r="P120" s="8"/>
@@ -10525,7 +10576,7 @@
         <v>7</v>
       </c>
       <c r="N121" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O121" s="8"/>
       <c r="P121" s="8"/>
@@ -10560,7 +10611,7 @@
         <v>13</v>
       </c>
       <c r="I122" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J122" s="8">
         <v>0</v>
@@ -10573,10 +10624,10 @@
       </c>
       <c r="M122" s="8">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N122" s="8">
-        <v>1049</v>
+        <v>1041</v>
       </c>
       <c r="O122" s="8"/>
       <c r="P122" s="8"/>
@@ -10729,7 +10780,7 @@
         <v>8</v>
       </c>
       <c r="N125" s="8">
-        <v>357</v>
+        <v>329</v>
       </c>
       <c r="O125" s="8"/>
       <c r="P125" s="8"/>
@@ -10764,7 +10815,7 @@
         <v>17</v>
       </c>
       <c r="I126" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J126" s="8">
         <v>0</v>
@@ -10777,7 +10828,7 @@
       </c>
       <c r="M126" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N126" s="8">
         <v>0</v>
@@ -10882,7 +10933,7 @@
         <v>4</v>
       </c>
       <c r="N128" s="8">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="O128" s="8"/>
       <c r="P128" s="8"/>
@@ -10968,23 +11019,23 @@
         <v>12</v>
       </c>
       <c r="I130" s="8">
+        <v>4</v>
+      </c>
+      <c r="J130" s="8">
+        <v>0</v>
+      </c>
+      <c r="K130" s="8">
         <v>3</v>
-      </c>
-      <c r="J130" s="8">
-        <v>0</v>
-      </c>
-      <c r="K130" s="8">
-        <v>2</v>
       </c>
       <c r="L130" s="8">
         <v>0</v>
       </c>
       <c r="M130" s="8">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N130" s="8">
-        <v>299</v>
+        <v>338</v>
       </c>
       <c r="O130" s="8"/>
       <c r="P130" s="8"/>
@@ -11035,7 +11086,7 @@
         <v>4</v>
       </c>
       <c r="N131" s="8">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="O131" s="8"/>
       <c r="P131" s="8"/>
@@ -11121,23 +11172,23 @@
         <v>12</v>
       </c>
       <c r="I133" s="8">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J133" s="8">
         <v>0</v>
       </c>
       <c r="K133" s="8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L133" s="8">
         <v>0</v>
       </c>
       <c r="M133" s="8">
         <f t="shared" si="2"/>
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="N133" s="8">
-        <v>698</v>
+        <v>590</v>
       </c>
       <c r="O133" s="8"/>
       <c r="P133" s="8"/>
@@ -11172,7 +11223,7 @@
         <v>15</v>
       </c>
       <c r="I134" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J134" s="8">
         <v>0</v>
@@ -11185,7 +11236,7 @@
       </c>
       <c r="M134" s="8">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N134" s="8">
         <v>0</v>
@@ -11223,7 +11274,7 @@
         <v>15</v>
       </c>
       <c r="I135" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J135" s="8">
         <v>0</v>
@@ -11236,10 +11287,10 @@
       </c>
       <c r="M135" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N135" s="8">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="O135" s="8"/>
       <c r="P135" s="8"/>
@@ -11274,7 +11325,7 @@
         <v>14</v>
       </c>
       <c r="I136" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J136" s="8">
         <v>0</v>
@@ -11287,10 +11338,10 @@
       </c>
       <c r="M136" s="8">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N136" s="8">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="O136" s="8"/>
       <c r="P136" s="8"/>
@@ -11325,7 +11376,7 @@
         <v>15</v>
       </c>
       <c r="I137" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J137" s="8">
         <v>0</v>
@@ -11338,10 +11389,10 @@
       </c>
       <c r="M137" s="8">
         <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="N137" s="8">
         <v>2</v>
-      </c>
-      <c r="N137" s="8">
-        <v>0</v>
       </c>
       <c r="O137" s="8"/>
       <c r="P137" s="8"/>
@@ -11392,7 +11443,7 @@
         <v>5</v>
       </c>
       <c r="N138" s="8">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="O138" s="8"/>
       <c r="P138" s="8"/>
@@ -11427,7 +11478,7 @@
         <v>15</v>
       </c>
       <c r="I139" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J139" s="8">
         <v>0</v>
@@ -11440,7 +11491,7 @@
       </c>
       <c r="M139" s="8">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N139" s="8">
         <v>0</v>
@@ -11631,7 +11682,7 @@
         <v>13</v>
       </c>
       <c r="I143" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J143" s="8">
         <v>0</v>
@@ -11644,7 +11695,7 @@
       </c>
       <c r="M143" s="8">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N143" s="8">
         <v>134</v>
@@ -11749,7 +11800,7 @@
         <v>4</v>
       </c>
       <c r="N145" s="8">
-        <v>870</v>
+        <v>856</v>
       </c>
       <c r="O145" s="8"/>
       <c r="P145" s="8"/>
@@ -11851,7 +11902,7 @@
         <v>3</v>
       </c>
       <c r="N147" s="8">
-        <v>19</v>
+        <v>193</v>
       </c>
       <c r="O147" s="8"/>
       <c r="P147" s="8"/>
@@ -11902,7 +11953,7 @@
         <v>3</v>
       </c>
       <c r="N148" s="8">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O148" s="8"/>
       <c r="P148" s="8"/>
@@ -11937,13 +11988,13 @@
         <v>12</v>
       </c>
       <c r="I149" s="8">
+        <v>0</v>
+      </c>
+      <c r="J149" s="8">
+        <v>0</v>
+      </c>
+      <c r="K149" s="8">
         <v>3</v>
-      </c>
-      <c r="J149" s="8">
-        <v>0</v>
-      </c>
-      <c r="K149" s="8">
-        <v>0</v>
       </c>
       <c r="L149" s="8">
         <v>0</v>
@@ -11953,7 +12004,7 @@
         <v>3</v>
       </c>
       <c r="N149" s="8">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="O149" s="8"/>
       <c r="P149" s="8"/>
@@ -12039,7 +12090,7 @@
         <v>13</v>
       </c>
       <c r="I151" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J151" s="8">
         <v>0</v>
@@ -12052,7 +12103,7 @@
       </c>
       <c r="M151" s="8">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N151" s="8">
         <v>188</v>
@@ -12106,7 +12157,7 @@
         <v>4</v>
       </c>
       <c r="N152" s="8">
-        <v>9</v>
+        <v>279</v>
       </c>
       <c r="O152" s="8"/>
       <c r="P152" s="8"/>
@@ -12294,7 +12345,7 @@
         <v>15</v>
       </c>
       <c r="I156" s="8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J156" s="8">
         <v>0</v>
@@ -12307,7 +12358,7 @@
       </c>
       <c r="M156" s="8">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N156" s="8">
         <v>0</v>
@@ -12447,7 +12498,7 @@
         <v>15</v>
       </c>
       <c r="I159" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J159" s="8">
         <v>0</v>
@@ -12460,7 +12511,7 @@
       </c>
       <c r="M159" s="8">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N159" s="8">
         <v>14</v>
@@ -12498,7 +12549,7 @@
         <v>15</v>
       </c>
       <c r="I160" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J160" s="8">
         <v>0</v>
@@ -12511,10 +12562,10 @@
       </c>
       <c r="M160" s="8">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N160" s="8">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="O160" s="8"/>
       <c r="P160" s="8"/>
@@ -12565,7 +12616,7 @@
         <v>6</v>
       </c>
       <c r="N161" s="8">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="O161" s="8"/>
       <c r="P161" s="8"/>
@@ -12616,7 +12667,7 @@
         <v>3</v>
       </c>
       <c r="N162" s="8">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="O162" s="8"/>
       <c r="P162" s="8"/>
@@ -12718,7 +12769,7 @@
         <v>3</v>
       </c>
       <c r="N164" s="8">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="O164" s="8"/>
       <c r="P164" s="8"/>
@@ -12753,7 +12804,7 @@
         <v>12</v>
       </c>
       <c r="I165" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J165" s="8">
         <v>0</v>
@@ -12766,10 +12817,10 @@
       </c>
       <c r="M165" s="8">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N165" s="8">
-        <v>1443</v>
+        <v>1428</v>
       </c>
       <c r="O165" s="8"/>
       <c r="P165" s="8"/>
@@ -12820,7 +12871,7 @@
         <v>5</v>
       </c>
       <c r="N166" s="8">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="O166" s="8"/>
       <c r="P166" s="8"/>
@@ -12855,7 +12906,7 @@
         <v>14</v>
       </c>
       <c r="I167" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J167" s="8">
         <v>0</v>
@@ -12868,7 +12919,7 @@
       </c>
       <c r="M167" s="8">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N167" s="8">
         <v>0</v>
@@ -13024,7 +13075,7 @@
         <v>5</v>
       </c>
       <c r="N170" s="8">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="O170" s="8"/>
       <c r="P170" s="8"/>
@@ -13110,7 +13161,7 @@
         <v>14</v>
       </c>
       <c r="I172" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J172" s="8">
         <v>0</v>
@@ -13123,7 +13174,7 @@
       </c>
       <c r="M172" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N172" s="8">
         <v>51</v>
@@ -13177,7 +13228,7 @@
         <v>2</v>
       </c>
       <c r="N173" s="8">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="O173" s="8"/>
       <c r="P173" s="8"/>
@@ -13330,7 +13381,7 @@
         <v>2</v>
       </c>
       <c r="N176" s="8">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O176" s="8"/>
       <c r="P176" s="8"/>
@@ -13483,7 +13534,7 @@
         <v>3</v>
       </c>
       <c r="N179" s="8">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="O179" s="8"/>
       <c r="P179" s="8"/>
@@ -13534,7 +13585,7 @@
         <v>8</v>
       </c>
       <c r="N180" s="8">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="O180" s="8"/>
       <c r="P180" s="8"/>
@@ -13585,7 +13636,7 @@
         <v>4</v>
       </c>
       <c r="N181" s="8">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="O181" s="8"/>
       <c r="P181" s="8"/>
@@ -13773,23 +13824,23 @@
         <v>12</v>
       </c>
       <c r="I185" s="8">
-        <v>261</v>
+        <v>302</v>
       </c>
       <c r="J185" s="8">
         <v>0</v>
       </c>
       <c r="K185" s="8">
-        <v>87</v>
+        <v>156</v>
       </c>
       <c r="L185" s="8">
         <v>0</v>
       </c>
       <c r="M185" s="8">
         <f t="shared" si="2"/>
-        <v>348</v>
+        <v>458</v>
       </c>
       <c r="N185" s="8">
-        <v>2031</v>
+        <v>1887</v>
       </c>
       <c r="O185" s="8"/>
       <c r="P185" s="8"/>
@@ -13824,7 +13875,7 @@
         <v>12</v>
       </c>
       <c r="I186" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J186" s="8">
         <v>0</v>
@@ -13837,10 +13888,10 @@
       </c>
       <c r="M186" s="8">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N186" s="8">
-        <v>997</v>
+        <v>986</v>
       </c>
       <c r="O186" s="8"/>
       <c r="P186" s="8"/>
@@ -13891,7 +13942,7 @@
         <v>2</v>
       </c>
       <c r="N187" s="8">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="O187" s="8"/>
       <c r="P187" s="8"/>
@@ -13942,7 +13993,7 @@
         <v>5</v>
       </c>
       <c r="N188" s="8">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="O188" s="8"/>
       <c r="P188" s="8"/>
@@ -14028,23 +14079,23 @@
         <v>12</v>
       </c>
       <c r="I190" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J190" s="8">
         <v>0</v>
       </c>
       <c r="K190" s="8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L190" s="8">
         <v>0</v>
       </c>
       <c r="M190" s="8">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N190" s="8">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="O190" s="8"/>
       <c r="P190" s="8"/>
@@ -14095,7 +14146,7 @@
         <v>9</v>
       </c>
       <c r="N191" s="8">
-        <v>1016</v>
+        <v>1002</v>
       </c>
       <c r="O191" s="8"/>
       <c r="P191" s="8"/>
@@ -14197,7 +14248,7 @@
         <v>3</v>
       </c>
       <c r="N193" s="8">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="O193" s="8"/>
       <c r="P193" s="8"/>
@@ -14248,7 +14299,7 @@
         <v>5</v>
       </c>
       <c r="N194" s="8">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="O194" s="8"/>
       <c r="P194" s="8"/>
@@ -14385,7 +14436,7 @@
         <v>12</v>
       </c>
       <c r="I197" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J197" s="8">
         <v>0</v>
@@ -14398,10 +14449,10 @@
       </c>
       <c r="M197" s="8">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N197" s="8">
-        <v>563</v>
+        <v>811</v>
       </c>
       <c r="O197" s="8"/>
       <c r="P197" s="8"/>
@@ -14691,7 +14742,7 @@
         <v>15</v>
       </c>
       <c r="I203" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J203" s="8">
         <v>0</v>
@@ -14704,7 +14755,7 @@
       </c>
       <c r="M203" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N203" s="8">
         <v>0</v>
@@ -14844,7 +14895,7 @@
         <v>15</v>
       </c>
       <c r="I206" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J206" s="8">
         <v>0</v>
@@ -14857,7 +14908,7 @@
       </c>
       <c r="M206" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N206" s="8">
         <v>0</v>
@@ -14911,7 +14962,7 @@
         <v>2</v>
       </c>
       <c r="N207" s="8">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="O207" s="8"/>
       <c r="P207" s="8"/>
@@ -14946,7 +14997,7 @@
         <v>14</v>
       </c>
       <c r="I208" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J208" s="8">
         <v>0</v>
@@ -14959,10 +15010,10 @@
       </c>
       <c r="M208" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N208" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O208" s="8"/>
       <c r="P208" s="8"/>
@@ -15013,7 +15064,7 @@
         <v>4</v>
       </c>
       <c r="N209" s="8">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="O209" s="8"/>
       <c r="P209" s="8"/>
@@ -15099,7 +15150,7 @@
         <v>12</v>
       </c>
       <c r="I211" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J211" s="8">
         <v>0</v>
@@ -15112,10 +15163,10 @@
       </c>
       <c r="M211" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N211" s="8">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="O211" s="8"/>
       <c r="P211" s="8"/>
@@ -15252,7 +15303,7 @@
         <v>14</v>
       </c>
       <c r="I214" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J214" s="8">
         <v>0</v>
@@ -15265,10 +15316,10 @@
       </c>
       <c r="M214" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N214" s="8">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="O214" s="8"/>
       <c r="P214" s="8"/>
@@ -15303,7 +15354,7 @@
         <v>14</v>
       </c>
       <c r="I215" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J215" s="8">
         <v>0</v>
@@ -15316,10 +15367,10 @@
       </c>
       <c r="M215" s="8">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N215" s="8">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="O215" s="8"/>
       <c r="P215" s="8"/>
@@ -15523,7 +15574,7 @@
         <v>6</v>
       </c>
       <c r="N219" s="8">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="O219" s="8"/>
       <c r="P219" s="8"/>
@@ -15558,7 +15609,7 @@
         <v>16</v>
       </c>
       <c r="I220" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J220" s="8">
         <v>0</v>
@@ -15571,7 +15622,7 @@
       </c>
       <c r="M220" s="8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N220" s="8">
         <v>0</v>
@@ -15625,7 +15676,7 @@
         <v>4</v>
       </c>
       <c r="N221" s="8">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O221" s="8"/>
       <c r="P221" s="8"/>
@@ -15778,7 +15829,7 @@
         <v>3</v>
       </c>
       <c r="N224" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="O224" s="8"/>
       <c r="P224" s="8"/>
@@ -15813,7 +15864,7 @@
         <v>12</v>
       </c>
       <c r="I225" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J225" s="8">
         <v>0</v>
@@ -15826,10 +15877,10 @@
       </c>
       <c r="M225" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N225" s="8">
-        <v>722</v>
+        <v>701</v>
       </c>
       <c r="O225" s="8"/>
       <c r="P225" s="8"/>
@@ -15982,7 +16033,7 @@
         <v>3</v>
       </c>
       <c r="N228" s="8">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="O228" s="8"/>
       <c r="P228" s="8"/>
@@ -16017,7 +16068,7 @@
         <v>15</v>
       </c>
       <c r="I229" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J229" s="8">
         <v>0</v>
@@ -16030,10 +16081,10 @@
       </c>
       <c r="M229" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N229" s="8">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="O229" s="8"/>
       <c r="P229" s="8"/>
@@ -16068,7 +16119,7 @@
         <v>15</v>
       </c>
       <c r="I230" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J230" s="8">
         <v>0</v>
@@ -16081,7 +16132,7 @@
       </c>
       <c r="M230" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N230" s="8">
         <v>0</v>
@@ -16186,7 +16237,7 @@
         <v>13</v>
       </c>
       <c r="N232" s="8">
-        <v>746</v>
+        <v>716</v>
       </c>
       <c r="O232" s="8"/>
       <c r="P232" s="8"/>
@@ -16221,7 +16272,7 @@
         <v>15</v>
       </c>
       <c r="I233" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J233" s="8">
         <v>0</v>
@@ -16234,10 +16285,10 @@
       </c>
       <c r="M233" s="8">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N233" s="8">
-        <v>731</v>
+        <v>713</v>
       </c>
       <c r="O233" s="8"/>
       <c r="P233" s="8"/>
@@ -16272,7 +16323,7 @@
         <v>15</v>
       </c>
       <c r="I234" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J234" s="8">
         <v>0</v>
@@ -16285,7 +16336,7 @@
       </c>
       <c r="M234" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N234" s="8">
         <v>58</v>
@@ -16339,7 +16390,7 @@
         <v>3</v>
       </c>
       <c r="N235" s="8">
-        <v>132</v>
+        <v>101</v>
       </c>
       <c r="O235" s="8"/>
       <c r="P235" s="8"/>
@@ -16425,7 +16476,7 @@
         <v>12</v>
       </c>
       <c r="I237" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J237" s="8">
         <v>0</v>
@@ -16438,7 +16489,7 @@
       </c>
       <c r="M237" s="8">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N237" s="8">
         <v>862</v>
@@ -16492,7 +16543,7 @@
         <v>6</v>
       </c>
       <c r="N238" s="8">
-        <v>537</v>
+        <v>524</v>
       </c>
       <c r="O238" s="8"/>
       <c r="P238" s="8"/>
@@ -16543,7 +16594,7 @@
         <v>4</v>
       </c>
       <c r="N239" s="8">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="O239" s="8"/>
       <c r="P239" s="8"/>
@@ -16584,17 +16635,17 @@
         <v>0</v>
       </c>
       <c r="K240" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L240" s="8">
         <v>0</v>
       </c>
       <c r="M240" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N240" s="8">
-        <v>6</v>
+        <v>477</v>
       </c>
       <c r="O240" s="8"/>
       <c r="P240" s="8"/>
@@ -16645,7 +16696,7 @@
         <v>3</v>
       </c>
       <c r="N241" s="8">
-        <v>153</v>
+        <v>287</v>
       </c>
       <c r="O241" s="8"/>
       <c r="P241" s="8"/>
@@ -16696,7 +16747,7 @@
         <v>3</v>
       </c>
       <c r="N242" s="8">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="O242" s="8"/>
       <c r="P242" s="8"/>
@@ -16731,7 +16782,7 @@
         <v>15</v>
       </c>
       <c r="I243" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J243" s="8">
         <v>0</v>
@@ -16744,10 +16795,10 @@
       </c>
       <c r="M243" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N243" s="8">
-        <v>363</v>
+        <v>341</v>
       </c>
       <c r="O243" s="8"/>
       <c r="P243" s="8"/>
@@ -16833,7 +16884,7 @@
         <v>15</v>
       </c>
       <c r="I245" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J245" s="8">
         <v>0</v>
@@ -16846,7 +16897,7 @@
       </c>
       <c r="M245" s="8">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N245" s="8">
         <v>0</v>
@@ -16890,17 +16941,17 @@
         <v>0</v>
       </c>
       <c r="K246" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L246" s="8">
         <v>0</v>
       </c>
       <c r="M246" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N246" s="8">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="O246" s="8"/>
       <c r="P246" s="8"/>
@@ -16935,7 +16986,7 @@
         <v>13</v>
       </c>
       <c r="I247" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J247" s="8">
         <v>0</v>
@@ -16948,10 +16999,10 @@
       </c>
       <c r="M247" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N247" s="8">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O247" s="8"/>
       <c r="P247" s="8"/>
@@ -16986,7 +17037,7 @@
         <v>12</v>
       </c>
       <c r="I248" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J248" s="8">
         <v>0</v>
@@ -16999,7 +17050,7 @@
       </c>
       <c r="M248" s="8">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N248" s="8">
         <v>0</v>
@@ -17088,7 +17139,7 @@
         <v>12</v>
       </c>
       <c r="I250" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J250" s="8">
         <v>0</v>
@@ -17101,10 +17152,10 @@
       </c>
       <c r="M250" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N250" s="8">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="O250" s="8"/>
       <c r="P250" s="8"/>
@@ -17139,7 +17190,7 @@
         <v>14</v>
       </c>
       <c r="I251" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J251" s="8">
         <v>0</v>
@@ -17152,10 +17203,10 @@
       </c>
       <c r="M251" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N251" s="8">
-        <v>1286</v>
+        <v>1279</v>
       </c>
       <c r="O251" s="8"/>
       <c r="P251" s="8"/>
@@ -17190,7 +17241,7 @@
         <v>14</v>
       </c>
       <c r="I252" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J252" s="8">
         <v>0</v>
@@ -17203,7 +17254,7 @@
       </c>
       <c r="M252" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N252" s="8">
         <v>216</v>
@@ -17257,7 +17308,7 @@
         <v>3</v>
       </c>
       <c r="N253" s="8">
-        <v>1237</v>
+        <v>1232</v>
       </c>
       <c r="O253" s="8"/>
       <c r="P253" s="8"/>
@@ -17292,7 +17343,7 @@
         <v>14</v>
       </c>
       <c r="I254" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J254" s="8">
         <v>0</v>
@@ -17305,10 +17356,10 @@
       </c>
       <c r="M254" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N254" s="8">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="O254" s="8"/>
       <c r="P254" s="8"/>
@@ -17343,7 +17394,7 @@
         <v>14</v>
       </c>
       <c r="I255" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J255" s="8">
         <v>0</v>
@@ -17356,10 +17407,10 @@
       </c>
       <c r="M255" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N255" s="8">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="O255" s="8"/>
       <c r="P255" s="8"/>
@@ -17394,7 +17445,7 @@
         <v>14</v>
       </c>
       <c r="I256" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J256" s="8">
         <v>0</v>
@@ -17407,10 +17458,10 @@
       </c>
       <c r="M256" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N256" s="8">
-        <v>1050</v>
+        <v>1043</v>
       </c>
       <c r="O256" s="8"/>
       <c r="P256" s="8"/>
@@ -17461,7 +17512,7 @@
         <v>4</v>
       </c>
       <c r="N257" s="8">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="O257" s="8"/>
       <c r="P257" s="8"/>
@@ -17563,7 +17614,7 @@
         <v>2</v>
       </c>
       <c r="N259" s="8">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="O259" s="8"/>
       <c r="P259" s="8"/>
@@ -17598,23 +17649,23 @@
         <v>13</v>
       </c>
       <c r="I260" s="8">
+        <v>2</v>
+      </c>
+      <c r="J260" s="8">
+        <v>0</v>
+      </c>
+      <c r="K260" s="8">
         <v>3</v>
-      </c>
-      <c r="J260" s="8">
-        <v>0</v>
-      </c>
-      <c r="K260" s="8">
-        <v>0</v>
       </c>
       <c r="L260" s="8">
         <v>0</v>
       </c>
       <c r="M260" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N260" s="8">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="O260" s="8"/>
       <c r="P260" s="8"/>
@@ -17649,7 +17700,7 @@
         <v>12</v>
       </c>
       <c r="I261" s="8">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J261" s="8">
         <v>0</v>
@@ -17662,10 +17713,10 @@
       </c>
       <c r="M261" s="8">
         <f t="shared" si="4"/>
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N261" s="8">
-        <v>1264</v>
+        <v>1232</v>
       </c>
       <c r="O261" s="8"/>
       <c r="P261" s="8"/>
@@ -17700,7 +17751,7 @@
         <v>12</v>
       </c>
       <c r="I262" s="8">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J262" s="8">
         <v>0</v>
@@ -17713,10 +17764,10 @@
       </c>
       <c r="M262" s="8">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N262" s="8">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="O262" s="8"/>
       <c r="P262" s="8"/>
@@ -17757,17 +17808,17 @@
         <v>0</v>
       </c>
       <c r="K263" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L263" s="8">
         <v>0</v>
       </c>
       <c r="M263" s="8">
         <f t="shared" si="4"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N263" s="8">
-        <v>541</v>
+        <v>579</v>
       </c>
       <c r="O263" s="8"/>
       <c r="P263" s="8"/>
@@ -17818,7 +17869,7 @@
         <v>2</v>
       </c>
       <c r="N264" s="8">
-        <v>1025</v>
+        <v>1019</v>
       </c>
       <c r="O264" s="8"/>
       <c r="P264" s="8"/>
@@ -17869,7 +17920,7 @@
         <v>2</v>
       </c>
       <c r="N265" s="8">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O265" s="8"/>
       <c r="P265" s="8"/>
@@ -17920,7 +17971,7 @@
         <v>3</v>
       </c>
       <c r="N266" s="8">
-        <v>1578</v>
+        <v>1574</v>
       </c>
       <c r="O266" s="8"/>
       <c r="P266" s="8"/>
@@ -18006,7 +18057,7 @@
         <v>15</v>
       </c>
       <c r="I268" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J268" s="8">
         <v>0</v>
@@ -18019,10 +18070,10 @@
       </c>
       <c r="M268" s="8">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N268" s="8">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="O268" s="8"/>
       <c r="P268" s="8"/>
@@ -18057,7 +18108,7 @@
         <v>15</v>
       </c>
       <c r="I269" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J269" s="8">
         <v>0</v>
@@ -18070,10 +18121,10 @@
       </c>
       <c r="M269" s="8">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N269" s="8">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="O269" s="8"/>
       <c r="P269" s="8"/>
@@ -18261,7 +18312,7 @@
         <v>16</v>
       </c>
       <c r="I273" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J273" s="8">
         <v>0</v>
@@ -18274,7 +18325,7 @@
       </c>
       <c r="M273" s="8">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N273" s="8">
         <v>0</v>
@@ -18312,7 +18363,7 @@
         <v>16</v>
       </c>
       <c r="I274" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J274" s="8">
         <v>0</v>
@@ -18325,10 +18376,10 @@
       </c>
       <c r="M274" s="8">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N274" s="8">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="O274" s="8"/>
       <c r="P274" s="8"/>
@@ -18379,7 +18430,7 @@
         <v>4</v>
       </c>
       <c r="N275" s="8">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O275" s="8"/>
       <c r="P275" s="8"/>
@@ -18430,7 +18481,7 @@
         <v>3</v>
       </c>
       <c r="N276" s="8">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="O276" s="8"/>
       <c r="P276" s="8"/>
@@ -18465,7 +18516,7 @@
         <v>13</v>
       </c>
       <c r="I277" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J277" s="8">
         <v>0</v>
@@ -18478,7 +18529,7 @@
       </c>
       <c r="M277" s="8">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N277" s="8">
         <v>0</v>
@@ -18516,7 +18567,7 @@
         <v>12</v>
       </c>
       <c r="I278" s="8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J278" s="8">
         <v>0</v>
@@ -18529,10 +18580,10 @@
       </c>
       <c r="M278" s="8">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N278" s="8">
-        <v>1131</v>
+        <v>1873</v>
       </c>
       <c r="O278" s="8"/>
       <c r="P278" s="8"/>
@@ -18567,7 +18618,7 @@
         <v>13</v>
       </c>
       <c r="I279" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J279" s="8">
         <v>0</v>
@@ -18580,10 +18631,10 @@
       </c>
       <c r="M279" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N279" s="8">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="O279" s="8"/>
       <c r="P279" s="8"/>
@@ -18777,17 +18828,17 @@
         <v>0</v>
       </c>
       <c r="K283" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L283" s="8">
         <v>0</v>
       </c>
       <c r="M283" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N283" s="8">
-        <v>362</v>
+        <v>340</v>
       </c>
       <c r="O283" s="8"/>
       <c r="P283" s="8"/>
@@ -18822,20 +18873,20 @@
         <v>12</v>
       </c>
       <c r="I284" s="8">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="J284" s="8">
         <v>0</v>
       </c>
       <c r="K284" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L284" s="8">
         <v>0</v>
       </c>
       <c r="M284" s="8">
         <f t="shared" si="4"/>
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="N284" s="8">
         <v>0</v>
@@ -18981,17 +19032,17 @@
         <v>0</v>
       </c>
       <c r="K287" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L287" s="8">
         <v>0</v>
       </c>
       <c r="M287" s="8">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N287" s="8">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="O287" s="8"/>
       <c r="P287" s="8"/>
@@ -19026,13 +19077,13 @@
         <v>14</v>
       </c>
       <c r="I288" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J288" s="8">
         <v>0</v>
       </c>
       <c r="K288" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L288" s="8">
         <v>0</v>
@@ -19042,7 +19093,7 @@
         <v>4</v>
       </c>
       <c r="N288" s="8">
-        <v>1547</v>
+        <v>1535</v>
       </c>
       <c r="O288" s="8"/>
       <c r="P288" s="8"/>
@@ -19083,17 +19134,17 @@
         <v>0</v>
       </c>
       <c r="K289" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L289" s="8">
         <v>0</v>
       </c>
       <c r="M289" s="8">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N289" s="8">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="O289" s="8"/>
       <c r="P289" s="8"/>
@@ -19128,7 +19179,7 @@
         <v>14</v>
       </c>
       <c r="I290" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J290" s="8">
         <v>0</v>
@@ -19141,7 +19192,7 @@
       </c>
       <c r="M290" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N290" s="8">
         <v>0</v>
@@ -19179,7 +19230,7 @@
         <v>12</v>
       </c>
       <c r="I291" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J291" s="8">
         <v>0</v>
@@ -19192,10 +19243,10 @@
       </c>
       <c r="M291" s="8">
         <f t="shared" si="4"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N291" s="8">
-        <v>0</v>
+        <v>714</v>
       </c>
       <c r="O291" s="8"/>
       <c r="P291" s="8"/>
@@ -19236,17 +19287,17 @@
         <v>0</v>
       </c>
       <c r="K292" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L292" s="8">
         <v>0</v>
       </c>
       <c r="M292" s="8">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N292" s="8">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="O292" s="8"/>
       <c r="P292" s="8"/>
@@ -19332,7 +19383,7 @@
         <v>12</v>
       </c>
       <c r="I294" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J294" s="8">
         <v>0</v>
@@ -19345,10 +19396,10 @@
       </c>
       <c r="M294" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N294" s="8">
-        <v>1656</v>
+        <v>1652</v>
       </c>
       <c r="O294" s="8"/>
       <c r="P294" s="8"/>
@@ -19807,7 +19858,7 @@
         <v>3</v>
       </c>
       <c r="N303" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O303" s="8"/>
       <c r="P303" s="8"/>
@@ -19858,7 +19909,7 @@
         <v>4</v>
       </c>
       <c r="N304" s="8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O304" s="8"/>
       <c r="P304" s="8"/>
@@ -19909,7 +19960,7 @@
         <v>8</v>
       </c>
       <c r="N305" s="8">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="O305" s="8"/>
       <c r="P305" s="8"/>
@@ -19960,7 +20011,7 @@
         <v>10</v>
       </c>
       <c r="N306" s="8">
-        <v>1231</v>
+        <v>1210</v>
       </c>
       <c r="O306" s="8"/>
       <c r="P306" s="8"/>
@@ -20011,7 +20062,7 @@
         <v>11</v>
       </c>
       <c r="N307" s="8">
-        <v>1101</v>
+        <v>1087</v>
       </c>
       <c r="O307" s="8"/>
       <c r="P307" s="8"/>
@@ -20062,7 +20113,7 @@
         <v>11</v>
       </c>
       <c r="N308" s="8">
-        <v>874</v>
+        <v>832</v>
       </c>
       <c r="O308" s="8"/>
       <c r="P308" s="8"/>
@@ -20164,7 +20215,7 @@
         <v>4</v>
       </c>
       <c r="N310" s="8">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="O310" s="8"/>
       <c r="P310" s="8"/>
@@ -20199,7 +20250,7 @@
         <v>16</v>
       </c>
       <c r="I311" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J311" s="8">
         <v>0</v>
@@ -20212,7 +20263,7 @@
       </c>
       <c r="M311" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N311" s="8">
         <v>186</v>
@@ -20250,13 +20301,13 @@
         <v>13</v>
       </c>
       <c r="I312" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J312" s="8">
         <v>0</v>
       </c>
       <c r="K312" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L312" s="8">
         <v>0</v>
@@ -20266,7 +20317,7 @@
         <v>6</v>
       </c>
       <c r="N312" s="8">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="O312" s="8"/>
       <c r="P312" s="8"/>
@@ -20317,7 +20368,7 @@
         <v>3</v>
       </c>
       <c r="N313" s="8">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="O313" s="8"/>
       <c r="P313" s="8"/>
@@ -20352,7 +20403,7 @@
         <v>12</v>
       </c>
       <c r="I314" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J314" s="8">
         <v>0</v>
@@ -20365,10 +20416,10 @@
       </c>
       <c r="M314" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N314" s="8">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="O314" s="8"/>
       <c r="P314" s="8"/>
@@ -20419,7 +20470,7 @@
         <v>8</v>
       </c>
       <c r="N315" s="8">
-        <v>384</v>
+        <v>365</v>
       </c>
       <c r="O315" s="8"/>
       <c r="P315" s="8"/>
@@ -20470,7 +20521,7 @@
         <v>5</v>
       </c>
       <c r="N316" s="8">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="O316" s="8"/>
       <c r="P316" s="8"/>
@@ -20505,7 +20556,7 @@
         <v>12</v>
       </c>
       <c r="I317" s="8">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J317" s="8">
         <v>0</v>
@@ -20518,10 +20569,10 @@
       </c>
       <c r="M317" s="8">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N317" s="8">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O317" s="8"/>
       <c r="P317" s="8"/>
@@ -20556,13 +20607,13 @@
         <v>12</v>
       </c>
       <c r="I318" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J318" s="8">
         <v>0</v>
       </c>
       <c r="K318" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L318" s="8">
         <v>0</v>
@@ -20572,7 +20623,7 @@
         <v>6</v>
       </c>
       <c r="N318" s="8">
-        <v>647</v>
+        <v>951</v>
       </c>
       <c r="O318" s="8"/>
       <c r="P318" s="8"/>
@@ -20623,7 +20674,7 @@
         <v>4</v>
       </c>
       <c r="N319" s="8">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="O319" s="8"/>
       <c r="P319" s="8"/>
@@ -20674,7 +20725,7 @@
         <v>4</v>
       </c>
       <c r="N320" s="8">
-        <v>664</v>
+        <v>655</v>
       </c>
       <c r="O320" s="8"/>
       <c r="P320" s="8"/>
@@ -20725,7 +20776,7 @@
         <v>2</v>
       </c>
       <c r="N321" s="8">
-        <v>617</v>
+        <v>596</v>
       </c>
       <c r="O321" s="8"/>
       <c r="P321" s="8"/>
@@ -20776,7 +20827,7 @@
         <v>3</v>
       </c>
       <c r="N322" s="8">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="O322" s="8"/>
       <c r="P322" s="8"/>
@@ -20827,7 +20878,7 @@
         <v>4</v>
       </c>
       <c r="N323" s="8">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O323" s="8"/>
       <c r="P323" s="8"/>
@@ -20913,7 +20964,7 @@
         <v>14</v>
       </c>
       <c r="I325" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J325" s="8">
         <v>0</v>
@@ -20926,10 +20977,10 @@
       </c>
       <c r="M325" s="8">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N325" s="8">
-        <v>379</v>
+        <v>355</v>
       </c>
       <c r="O325" s="8"/>
       <c r="P325" s="8"/>
@@ -20980,7 +21031,7 @@
         <v>3</v>
       </c>
       <c r="N326" s="8">
-        <v>822</v>
+        <v>815</v>
       </c>
       <c r="O326" s="8"/>
       <c r="P326" s="8"/>
@@ -21082,7 +21133,7 @@
         <v>1</v>
       </c>
       <c r="N328" s="8">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O328" s="8"/>
       <c r="P328" s="8"/>
@@ -21133,7 +21184,7 @@
         <v>4</v>
       </c>
       <c r="N329" s="8">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O329" s="8"/>
       <c r="P329" s="8"/>
@@ -21184,7 +21235,7 @@
         <v>2</v>
       </c>
       <c r="N330" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O330" s="8"/>
       <c r="P330" s="8"/>
@@ -21388,7 +21439,7 @@
         <v>4</v>
       </c>
       <c r="N334" s="8">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O334" s="8"/>
       <c r="P334" s="8"/>
@@ -21490,7 +21541,7 @@
         <v>5</v>
       </c>
       <c r="N336" s="8">
-        <v>707</v>
+        <v>691</v>
       </c>
       <c r="O336" s="8"/>
       <c r="P336" s="8"/>
@@ -21531,17 +21582,17 @@
         <v>0</v>
       </c>
       <c r="K337" s="8">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L337" s="8">
         <v>0</v>
       </c>
       <c r="M337" s="8">
         <f t="shared" si="5"/>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N337" s="8">
-        <v>1063</v>
+        <v>1052</v>
       </c>
       <c r="O337" s="8"/>
       <c r="P337" s="8"/>
@@ -21576,7 +21627,7 @@
         <v>12</v>
       </c>
       <c r="I338" s="8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J338" s="8">
         <v>0</v>
@@ -21589,10 +21640,10 @@
       </c>
       <c r="M338" s="8">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N338" s="8">
-        <v>1221</v>
+        <v>1209</v>
       </c>
       <c r="O338" s="8"/>
       <c r="P338" s="8"/>
@@ -21643,7 +21694,7 @@
         <v>3</v>
       </c>
       <c r="N339" s="8">
-        <v>908</v>
+        <v>899</v>
       </c>
       <c r="O339" s="8"/>
       <c r="P339" s="8"/>
@@ -21684,17 +21735,17 @@
         <v>0</v>
       </c>
       <c r="K340" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L340" s="8">
         <v>0</v>
       </c>
       <c r="M340" s="8">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N340" s="8">
-        <v>675</v>
+        <v>558</v>
       </c>
       <c r="O340" s="8"/>
       <c r="P340" s="8"/>
@@ -21745,7 +21796,7 @@
         <v>4</v>
       </c>
       <c r="N341" s="8">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="O341" s="8"/>
       <c r="P341" s="8"/>
@@ -21796,7 +21847,7 @@
         <v>4</v>
       </c>
       <c r="N342" s="8">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O342" s="8"/>
       <c r="P342" s="8"/>
@@ -21847,7 +21898,7 @@
         <v>4</v>
       </c>
       <c r="N343" s="8">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O343" s="8"/>
       <c r="P343" s="8"/>
@@ -21882,7 +21933,7 @@
         <v>12</v>
       </c>
       <c r="I344" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J344" s="8">
         <v>0</v>
@@ -21895,7 +21946,7 @@
       </c>
       <c r="M344" s="8">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N344" s="8">
         <v>0</v>
@@ -21933,7 +21984,7 @@
         <v>12</v>
       </c>
       <c r="I345" s="8">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J345" s="8">
         <v>0</v>
@@ -21946,7 +21997,7 @@
       </c>
       <c r="M345" s="8">
         <f t="shared" si="5"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N345" s="8">
         <v>0</v>
@@ -21984,7 +22035,7 @@
         <v>13</v>
       </c>
       <c r="I346" s="8">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="J346" s="8">
         <v>0</v>
@@ -21997,7 +22048,7 @@
       </c>
       <c r="M346" s="8">
         <f t="shared" si="5"/>
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="N346" s="8">
         <v>0</v>
@@ -22035,23 +22086,23 @@
         <v>13</v>
       </c>
       <c r="I347" s="8">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J347" s="8">
         <v>0</v>
       </c>
       <c r="K347" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L347" s="8">
         <v>0</v>
       </c>
       <c r="M347" s="8">
         <f t="shared" si="5"/>
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N347" s="8">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="O347" s="8"/>
       <c r="P347" s="9"/>
@@ -22086,7 +22137,7 @@
         <v>12</v>
       </c>
       <c r="I348" s="8">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J348" s="8">
         <v>0</v>
@@ -22099,7 +22150,7 @@
       </c>
       <c r="M348" s="8">
         <f t="shared" si="5"/>
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N348" s="8">
         <v>84</v>
@@ -22306,7 +22357,7 @@
         <v>2</v>
       </c>
       <c r="N352" s="8">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="O352" s="8"/>
       <c r="P352" s="9"/>
@@ -22851,23 +22902,23 @@
         <v>12</v>
       </c>
       <c r="I363" s="8">
-        <v>236</v>
+        <v>316</v>
       </c>
       <c r="J363" s="8">
         <v>0</v>
       </c>
       <c r="K363" s="8">
-        <v>112</v>
+        <v>219</v>
       </c>
       <c r="L363" s="8">
         <v>0</v>
       </c>
       <c r="M363" s="8">
         <f t="shared" si="5"/>
-        <v>348</v>
+        <v>535</v>
       </c>
       <c r="N363" s="8">
-        <v>1172</v>
+        <v>956</v>
       </c>
       <c r="O363" s="8"/>
       <c r="P363" s="9"/>
@@ -23020,7 +23071,7 @@
         <v>3</v>
       </c>
       <c r="N366" s="8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O366" s="8"/>
       <c r="P366" s="9"/>
@@ -23055,23 +23106,23 @@
         <v>12</v>
       </c>
       <c r="I367" s="8">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="J367" s="8">
         <v>0</v>
       </c>
       <c r="K367" s="8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L367" s="8">
         <v>0</v>
       </c>
       <c r="M367" s="8">
         <f t="shared" si="5"/>
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="N367" s="8">
-        <v>477</v>
+        <v>259</v>
       </c>
       <c r="O367" s="8"/>
       <c r="P367" s="9"/>
@@ -23106,7 +23157,7 @@
         <v>12</v>
       </c>
       <c r="I368" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J368" s="8">
         <v>0</v>
@@ -23119,10 +23170,10 @@
       </c>
       <c r="M368" s="8">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N368" s="8">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="O368" s="8"/>
       <c r="P368" s="9"/>
@@ -23173,7 +23224,7 @@
         <v>3</v>
       </c>
       <c r="N369" s="8">
-        <v>83</v>
+        <v>30</v>
       </c>
       <c r="O369" s="8"/>
       <c r="P369" s="9"/>
@@ -23275,7 +23326,7 @@
         <v>3</v>
       </c>
       <c r="N371" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O371" s="8"/>
       <c r="P371" s="9"/>
@@ -23326,7 +23377,7 @@
         <v>3</v>
       </c>
       <c r="N372" s="8">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O372" s="8"/>
       <c r="P372" s="9"/>
@@ -23377,7 +23428,7 @@
         <v>5</v>
       </c>
       <c r="N373" s="8">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="O373" s="8"/>
       <c r="P373" s="9"/>
@@ -23463,7 +23514,7 @@
         <v>12</v>
       </c>
       <c r="I375" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J375" s="8">
         <v>0</v>
@@ -23476,7 +23527,7 @@
       </c>
       <c r="M375" s="8">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N375" s="8">
         <v>0</v>
@@ -23514,7 +23565,7 @@
         <v>12</v>
       </c>
       <c r="I376" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J376" s="8">
         <v>0</v>
@@ -23527,7 +23578,7 @@
       </c>
       <c r="M376" s="8">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N376" s="8">
         <v>0</v>
@@ -23565,7 +23616,7 @@
         <v>13</v>
       </c>
       <c r="I377" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J377" s="8">
         <v>0</v>
@@ -23578,7 +23629,7 @@
       </c>
       <c r="M377" s="8">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N377" s="8">
         <v>0</v>
@@ -23871,7 +23922,7 @@
         <v>12</v>
       </c>
       <c r="I383" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J383" s="8">
         <v>0</v>
@@ -23884,7 +23935,7 @@
       </c>
       <c r="M383" s="8">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N383" s="8">
         <v>0</v>
@@ -23938,7 +23989,7 @@
         <v>5</v>
       </c>
       <c r="N384" s="8">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="O384" s="8"/>
       <c r="P384" s="9"/>
@@ -23973,23 +24024,23 @@
         <v>12</v>
       </c>
       <c r="I385" s="8">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="J385" s="8">
         <v>0</v>
       </c>
       <c r="K385" s="8">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="L385" s="8">
         <v>0</v>
       </c>
       <c r="M385" s="8">
         <f t="shared" si="5"/>
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="N385" s="8">
-        <v>305</v>
+        <v>257</v>
       </c>
       <c r="O385" s="8"/>
       <c r="P385" s="7"/>
@@ -24279,7 +24330,7 @@
         <v>12</v>
       </c>
       <c r="I391" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J391" s="8">
         <v>0</v>
@@ -24292,7 +24343,7 @@
       </c>
       <c r="M391" s="8">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N391" s="8">
         <v>0</v>
@@ -24381,7 +24432,7 @@
         <v>12</v>
       </c>
       <c r="I393" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J393" s="8">
         <v>0</v>
@@ -24394,7 +24445,7 @@
       </c>
       <c r="M393" s="8">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N393" s="8">
         <v>0</v>
@@ -24432,7 +24483,7 @@
         <v>12</v>
       </c>
       <c r="I394" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J394" s="8">
         <v>0</v>
@@ -24445,7 +24496,7 @@
       </c>
       <c r="M394" s="8">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N394" s="8">
         <v>0</v>
@@ -24483,7 +24534,7 @@
         <v>13</v>
       </c>
       <c r="I395" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J395" s="8">
         <v>0</v>
@@ -24496,7 +24547,7 @@
       </c>
       <c r="M395" s="8">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N395" s="8">
         <v>0</v>
@@ -24534,7 +24585,7 @@
         <v>12</v>
       </c>
       <c r="I396" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J396" s="8">
         <v>0</v>
@@ -24547,7 +24598,7 @@
       </c>
       <c r="M396" s="8">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N396" s="8">
         <v>0</v>
@@ -24585,7 +24636,7 @@
         <v>14</v>
       </c>
       <c r="I397" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J397" s="8">
         <v>0</v>
@@ -24598,7 +24649,7 @@
       </c>
       <c r="M397" s="8">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N397" s="8">
         <v>0</v>
@@ -24652,7 +24703,7 @@
         <v>3</v>
       </c>
       <c r="N398" s="8">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="O398" s="7"/>
       <c r="P398" s="7"/>
@@ -24866,20 +24917,49 @@
       <c r="T402" s="7"/>
     </row>
     <row r="403" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A403" s="7"/>
-      <c r="B403" s="7"/>
-      <c r="C403" s="7"/>
-      <c r="D403" s="7"/>
-      <c r="E403" s="7"/>
-      <c r="F403" s="7"/>
-      <c r="G403" s="7"/>
-      <c r="H403" s="7"/>
-      <c r="I403" s="7"/>
-      <c r="J403" s="7"/>
-      <c r="K403" s="7"/>
-      <c r="L403" s="7"/>
-      <c r="M403" s="7"/>
-      <c r="N403" s="7"/>
+      <c r="A403" s="11" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B403" s="7" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C403" s="10" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D403" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="E403" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F403" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G403" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H403" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="I403" s="8">
+        <v>0</v>
+      </c>
+      <c r="J403" s="8">
+        <v>0</v>
+      </c>
+      <c r="K403" s="8">
+        <v>0</v>
+      </c>
+      <c r="L403" s="8">
+        <v>0</v>
+      </c>
+      <c r="M403" s="8">
+        <f t="shared" ref="M403" si="7">I403+J403+K403+L403</f>
+        <v>0</v>
+      </c>
+      <c r="N403" s="8">
+        <v>1</v>
+      </c>
       <c r="O403" s="7"/>
       <c r="P403" s="7"/>
       <c r="Q403" s="7"/>
@@ -32874,18 +32954,23 @@
       <c r="T766" s="7"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T402" xr:uid="{AF55B7BF-85DC-4082-9A73-200B4D79A598}"/>
+  <autoFilter ref="A1:T403" xr:uid="{AF55B7BF-85DC-4082-9A73-200B4D79A598}"/>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="8" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="6" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C402">
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C403">
     <cfRule type="duplicateValues" dxfId="2" priority="1"/>
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>

--- a/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
+++ b/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\Fossil Replenishment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F13E24F-C4AD-4270-8B2A-63BAC3DFD745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5996548-35F5-4253-9CD3-B99C8E981674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6662473D-6E1F-42FD-999B-28162E22D4B5}"/>
   </bookViews>
@@ -4491,20 +4491,20 @@
         <v>12</v>
       </c>
       <c r="I2" s="8">
-        <v>650</v>
+        <v>783</v>
       </c>
       <c r="J2" s="8">
         <v>0</v>
       </c>
       <c r="K2" s="8">
-        <v>207</v>
+        <v>50</v>
       </c>
       <c r="L2" s="8">
         <v>0</v>
       </c>
       <c r="M2" s="8">
         <f>I2+J2+K2+L2</f>
-        <v>857</v>
+        <v>833</v>
       </c>
       <c r="N2" s="8">
         <v>1479</v>
@@ -4542,7 +4542,7 @@
         <v>12</v>
       </c>
       <c r="I3" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3" s="8">
         <v>0</v>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="M3" s="8">
         <f t="shared" ref="M3:M66" si="0">I3+J3+K3+L3</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N3" s="8">
         <v>0</v>
@@ -4593,7 +4593,7 @@
         <v>12</v>
       </c>
       <c r="I4" s="8">
-        <v>270</v>
+        <v>204</v>
       </c>
       <c r="J4" s="8">
         <v>0</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="M4" s="8">
         <f t="shared" si="0"/>
-        <v>270</v>
+        <v>204</v>
       </c>
       <c r="N4" s="8">
         <v>0</v>
@@ -4644,7 +4644,7 @@
         <v>12</v>
       </c>
       <c r="I5" s="8">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="J5" s="8">
         <v>0</v>
@@ -4657,7 +4657,7 @@
       </c>
       <c r="M5" s="8">
         <f t="shared" si="0"/>
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="N5" s="8">
         <v>0</v>
@@ -4695,20 +4695,20 @@
         <v>12</v>
       </c>
       <c r="I6" s="8">
-        <v>675</v>
+        <v>830</v>
       </c>
       <c r="J6" s="8">
         <v>0</v>
       </c>
       <c r="K6" s="8">
-        <v>178</v>
+        <v>47</v>
       </c>
       <c r="L6" s="8">
         <v>0</v>
       </c>
       <c r="M6" s="8">
         <f t="shared" si="0"/>
-        <v>853</v>
+        <v>877</v>
       </c>
       <c r="N6" s="8">
         <v>1862</v>
@@ -4746,23 +4746,23 @@
         <v>12</v>
       </c>
       <c r="I7" s="8">
-        <v>43</v>
+        <v>212</v>
       </c>
       <c r="J7" s="8">
         <v>0</v>
       </c>
       <c r="K7" s="8">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="L7" s="8">
         <v>0</v>
       </c>
       <c r="M7" s="8">
         <f t="shared" si="0"/>
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="N7" s="8">
-        <v>211</v>
+        <v>160</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
@@ -4797,7 +4797,7 @@
         <v>12</v>
       </c>
       <c r="I8" s="8">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="J8" s="8">
         <v>0</v>
@@ -4810,10 +4810,10 @@
       </c>
       <c r="M8" s="8">
         <f t="shared" si="0"/>
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="N8" s="8">
-        <v>1111</v>
+        <v>1083</v>
       </c>
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
@@ -4848,7 +4848,7 @@
         <v>12</v>
       </c>
       <c r="I9" s="8">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="J9" s="8">
         <v>0</v>
@@ -4861,10 +4861,10 @@
       </c>
       <c r="M9" s="8">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N9" s="8">
-        <v>531</v>
+        <v>477</v>
       </c>
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
@@ -4899,23 +4899,23 @@
         <v>12</v>
       </c>
       <c r="I10" s="8">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J10" s="8">
         <v>0</v>
       </c>
       <c r="K10" s="8">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="L10" s="8">
         <v>0</v>
       </c>
       <c r="M10" s="8">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="N10" s="8">
-        <v>477</v>
+        <v>408</v>
       </c>
       <c r="O10" s="8"/>
       <c r="P10" s="8"/>
@@ -4950,7 +4950,7 @@
         <v>12</v>
       </c>
       <c r="I11" s="8">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J11" s="8">
         <v>0</v>
@@ -4963,10 +4963,10 @@
       </c>
       <c r="M11" s="8">
         <f t="shared" si="0"/>
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="N11" s="8">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="O11" s="8"/>
       <c r="P11" s="8"/>
@@ -5001,23 +5001,23 @@
         <v>12</v>
       </c>
       <c r="I12" s="8">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J12" s="8">
         <v>0</v>
       </c>
       <c r="K12" s="8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L12" s="8">
         <v>0</v>
       </c>
       <c r="M12" s="8">
         <f t="shared" si="0"/>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="N12" s="8">
-        <v>2436</v>
+        <v>2284</v>
       </c>
       <c r="O12" s="8"/>
       <c r="P12" s="8"/>
@@ -5052,20 +5052,20 @@
         <v>12</v>
       </c>
       <c r="I13" s="8">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="J13" s="8">
         <v>0</v>
       </c>
       <c r="K13" s="8">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="L13" s="8">
         <v>0</v>
       </c>
       <c r="M13" s="8">
         <f t="shared" si="0"/>
-        <v>262</v>
+        <v>224</v>
       </c>
       <c r="N13" s="8">
         <v>962</v>
@@ -5103,13 +5103,13 @@
         <v>12</v>
       </c>
       <c r="I14" s="8">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J14" s="8">
         <v>0</v>
       </c>
       <c r="K14" s="8">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L14" s="8">
         <v>0</v>
@@ -5119,7 +5119,7 @@
         <v>32</v>
       </c>
       <c r="N14" s="8">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
@@ -5154,23 +5154,23 @@
         <v>12</v>
       </c>
       <c r="I15" s="8">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="J15" s="8">
         <v>0</v>
       </c>
       <c r="K15" s="8">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="L15" s="8">
         <v>0</v>
       </c>
       <c r="M15" s="8">
         <f t="shared" si="0"/>
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="N15" s="8">
-        <v>346</v>
+        <v>66</v>
       </c>
       <c r="O15" s="8"/>
       <c r="P15" s="8"/>
@@ -5205,23 +5205,23 @@
         <v>12</v>
       </c>
       <c r="I16" s="8">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="J16" s="8">
         <v>0</v>
       </c>
       <c r="K16" s="8">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L16" s="8">
         <v>0</v>
       </c>
       <c r="M16" s="8">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="N16" s="8">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
@@ -5256,7 +5256,7 @@
         <v>12</v>
       </c>
       <c r="I17" s="8">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="J17" s="8">
         <v>0</v>
@@ -5269,10 +5269,10 @@
       </c>
       <c r="M17" s="8">
         <f t="shared" si="0"/>
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="N17" s="8">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="O17" s="8"/>
       <c r="P17" s="8"/>
@@ -5307,23 +5307,23 @@
         <v>12</v>
       </c>
       <c r="I18" s="8">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="J18" s="8">
         <v>0</v>
       </c>
       <c r="K18" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" s="8">
         <v>0</v>
       </c>
       <c r="M18" s="8">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="N18" s="8">
-        <v>610</v>
+        <v>432</v>
       </c>
       <c r="O18" s="8"/>
       <c r="P18" s="8"/>
@@ -5358,7 +5358,7 @@
         <v>13</v>
       </c>
       <c r="I19" s="8">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J19" s="8">
         <v>0</v>
@@ -5371,10 +5371,10 @@
       </c>
       <c r="M19" s="8">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="N19" s="8">
-        <v>554</v>
+        <v>920</v>
       </c>
       <c r="O19" s="8"/>
       <c r="P19" s="8"/>
@@ -5409,23 +5409,23 @@
         <v>14</v>
       </c>
       <c r="I20" s="8">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="J20" s="8">
         <v>0</v>
       </c>
       <c r="K20" s="8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L20" s="8">
         <v>0</v>
       </c>
       <c r="M20" s="8">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N20" s="8">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="O20" s="8"/>
       <c r="P20" s="8"/>
@@ -5460,20 +5460,20 @@
         <v>13</v>
       </c>
       <c r="I21" s="8">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="J21" s="8">
         <v>0</v>
       </c>
       <c r="K21" s="8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L21" s="8">
         <v>0</v>
       </c>
       <c r="M21" s="8">
         <f t="shared" si="0"/>
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="N21" s="8">
         <v>0</v>
@@ -5562,13 +5562,13 @@
         <v>12</v>
       </c>
       <c r="I23" s="8">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J23" s="8">
         <v>0</v>
       </c>
       <c r="K23" s="8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L23" s="8">
         <v>0</v>
@@ -5578,7 +5578,7 @@
         <v>31</v>
       </c>
       <c r="N23" s="8">
-        <v>93</v>
+        <v>40</v>
       </c>
       <c r="O23" s="8"/>
       <c r="P23" s="8"/>
@@ -5613,7 +5613,7 @@
         <v>14</v>
       </c>
       <c r="I24" s="8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J24" s="8">
         <v>0</v>
@@ -5626,10 +5626,10 @@
       </c>
       <c r="M24" s="8">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N24" s="8">
-        <v>817</v>
+        <v>786</v>
       </c>
       <c r="O24" s="8"/>
       <c r="P24" s="8"/>
@@ -5721,17 +5721,17 @@
         <v>0</v>
       </c>
       <c r="K26" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L26" s="8">
         <v>0</v>
       </c>
       <c r="M26" s="8">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="N26" s="8">
-        <v>913</v>
+        <v>746</v>
       </c>
       <c r="O26" s="8"/>
       <c r="P26" s="8"/>
@@ -5766,7 +5766,7 @@
         <v>12</v>
       </c>
       <c r="I27" s="8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J27" s="8">
         <v>0</v>
@@ -5779,10 +5779,10 @@
       </c>
       <c r="M27" s="8">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N27" s="8">
-        <v>877</v>
+        <v>863</v>
       </c>
       <c r="O27" s="8"/>
       <c r="P27" s="8"/>
@@ -5817,7 +5817,7 @@
         <v>12</v>
       </c>
       <c r="I28" s="8">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J28" s="8">
         <v>0</v>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="M28" s="8">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N28" s="8">
         <v>0</v>
@@ -5868,23 +5868,23 @@
         <v>13</v>
       </c>
       <c r="I29" s="8">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J29" s="8">
         <v>0</v>
       </c>
       <c r="K29" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L29" s="8">
         <v>0</v>
       </c>
       <c r="M29" s="8">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N29" s="8">
-        <v>605</v>
+        <v>503</v>
       </c>
       <c r="O29" s="8"/>
       <c r="P29" s="8"/>
@@ -5919,23 +5919,23 @@
         <v>14</v>
       </c>
       <c r="I30" s="8">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J30" s="8">
         <v>0</v>
       </c>
       <c r="K30" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L30" s="8">
         <v>0</v>
       </c>
       <c r="M30" s="8">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N30" s="8">
-        <v>1127</v>
+        <v>1079</v>
       </c>
       <c r="O30" s="8"/>
       <c r="P30" s="8"/>
@@ -6021,7 +6021,7 @@
         <v>12</v>
       </c>
       <c r="I32" s="8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J32" s="8">
         <v>0</v>
@@ -6034,10 +6034,10 @@
       </c>
       <c r="M32" s="8">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N32" s="8">
-        <v>808</v>
+        <v>793</v>
       </c>
       <c r="O32" s="8"/>
       <c r="P32" s="8"/>
@@ -6072,13 +6072,13 @@
         <v>12</v>
       </c>
       <c r="I33" s="8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J33" s="8">
         <v>0</v>
       </c>
       <c r="K33" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" s="8">
         <v>0</v>
@@ -6088,7 +6088,7 @@
         <v>24</v>
       </c>
       <c r="N33" s="8">
-        <v>400</v>
+        <v>1159</v>
       </c>
       <c r="O33" s="8"/>
       <c r="P33" s="8"/>
@@ -6139,7 +6139,7 @@
         <v>22</v>
       </c>
       <c r="N34" s="8">
-        <v>1079</v>
+        <v>1067</v>
       </c>
       <c r="O34" s="8"/>
       <c r="P34" s="8"/>
@@ -6190,7 +6190,7 @@
         <v>16</v>
       </c>
       <c r="N35" s="8">
-        <v>212</v>
+        <v>347</v>
       </c>
       <c r="O35" s="8"/>
       <c r="P35" s="8"/>
@@ -6241,7 +6241,7 @@
         <v>12</v>
       </c>
       <c r="N36" s="8">
-        <v>780</v>
+        <v>766</v>
       </c>
       <c r="O36" s="8"/>
       <c r="P36" s="8"/>
@@ -6276,7 +6276,7 @@
         <v>13</v>
       </c>
       <c r="I37" s="8">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J37" s="8">
         <v>0</v>
@@ -6289,10 +6289,10 @@
       </c>
       <c r="M37" s="8">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N37" s="8">
-        <v>733</v>
+        <v>893</v>
       </c>
       <c r="O37" s="8"/>
       <c r="P37" s="8"/>
@@ -6327,7 +6327,7 @@
         <v>12</v>
       </c>
       <c r="I38" s="8">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J38" s="8">
         <v>0</v>
@@ -6340,10 +6340,10 @@
       </c>
       <c r="M38" s="8">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N38" s="8">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="O38" s="8"/>
       <c r="P38" s="8"/>
@@ -6378,23 +6378,23 @@
         <v>12</v>
       </c>
       <c r="I39" s="8">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J39" s="8">
         <v>0</v>
       </c>
       <c r="K39" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L39" s="8">
         <v>0</v>
       </c>
       <c r="M39" s="8">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N39" s="8">
-        <v>1679</v>
+        <v>1540</v>
       </c>
       <c r="O39" s="8"/>
       <c r="P39" s="8"/>
@@ -6429,23 +6429,23 @@
         <v>12</v>
       </c>
       <c r="I40" s="8">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J40" s="8">
         <v>0</v>
       </c>
       <c r="K40" s="8">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L40" s="8">
         <v>0</v>
       </c>
       <c r="M40" s="8">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N40" s="8">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="O40" s="8"/>
       <c r="P40" s="8"/>
@@ -6480,7 +6480,7 @@
         <v>12</v>
       </c>
       <c r="I41" s="8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J41" s="8">
         <v>0</v>
@@ -6493,10 +6493,10 @@
       </c>
       <c r="M41" s="8">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N41" s="8">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="O41" s="8"/>
       <c r="P41" s="8"/>
@@ -6547,7 +6547,7 @@
         <v>15</v>
       </c>
       <c r="N42" s="8">
-        <v>687</v>
+        <v>1026</v>
       </c>
       <c r="O42" s="8"/>
       <c r="P42" s="8"/>
@@ -6582,23 +6582,23 @@
         <v>12</v>
       </c>
       <c r="I43" s="8">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J43" s="8">
         <v>0</v>
       </c>
       <c r="K43" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L43" s="8">
         <v>0</v>
       </c>
       <c r="M43" s="8">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N43" s="8">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="O43" s="8"/>
       <c r="P43" s="8"/>
@@ -6633,7 +6633,7 @@
         <v>12</v>
       </c>
       <c r="I44" s="8">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J44" s="8">
         <v>0</v>
@@ -6646,10 +6646,10 @@
       </c>
       <c r="M44" s="8">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N44" s="8">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="O44" s="8"/>
       <c r="P44" s="8"/>
@@ -6684,7 +6684,7 @@
         <v>12</v>
       </c>
       <c r="I45" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J45" s="8">
         <v>0</v>
@@ -6697,10 +6697,10 @@
       </c>
       <c r="M45" s="8">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N45" s="8">
-        <v>904</v>
+        <v>870</v>
       </c>
       <c r="O45" s="8"/>
       <c r="P45" s="8"/>
@@ -6735,7 +6735,7 @@
         <v>12</v>
       </c>
       <c r="I46" s="8">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J46" s="8">
         <v>0</v>
@@ -6748,10 +6748,10 @@
       </c>
       <c r="M46" s="8">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N46" s="8">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="O46" s="8"/>
       <c r="P46" s="8"/>
@@ -6786,7 +6786,7 @@
         <v>13</v>
       </c>
       <c r="I47" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J47" s="8">
         <v>0</v>
@@ -6799,10 +6799,10 @@
       </c>
       <c r="M47" s="8">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N47" s="8">
-        <v>1060</v>
+        <v>1068</v>
       </c>
       <c r="O47" s="8"/>
       <c r="P47" s="8"/>
@@ -6837,7 +6837,7 @@
         <v>12</v>
       </c>
       <c r="I48" s="8">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J48" s="8">
         <v>0</v>
@@ -6850,10 +6850,10 @@
       </c>
       <c r="M48" s="8">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="N48" s="8">
-        <v>1113</v>
+        <v>1066</v>
       </c>
       <c r="O48" s="8"/>
       <c r="P48" s="8"/>
@@ -6888,7 +6888,7 @@
         <v>12</v>
       </c>
       <c r="I49" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J49" s="8">
         <v>0</v>
@@ -6901,10 +6901,10 @@
       </c>
       <c r="M49" s="8">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N49" s="8">
-        <v>1023</v>
+        <v>983</v>
       </c>
       <c r="O49" s="8"/>
       <c r="P49" s="8"/>
@@ -7006,7 +7006,7 @@
         <v>24</v>
       </c>
       <c r="N51" s="8">
-        <v>454</v>
+        <v>440</v>
       </c>
       <c r="O51" s="8"/>
       <c r="P51" s="8"/>
@@ -7041,23 +7041,23 @@
         <v>12</v>
       </c>
       <c r="I52" s="8">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="J52" s="8">
         <v>0</v>
       </c>
       <c r="K52" s="8">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="L52" s="8">
         <v>0</v>
       </c>
       <c r="M52" s="8">
         <f t="shared" si="0"/>
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="N52" s="8">
-        <v>1218</v>
+        <v>1789</v>
       </c>
       <c r="O52" s="8"/>
       <c r="P52" s="8"/>
@@ -7108,7 +7108,7 @@
         <v>9</v>
       </c>
       <c r="N53" s="8">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="O53" s="8"/>
       <c r="P53" s="8"/>
@@ -7143,7 +7143,7 @@
         <v>12</v>
       </c>
       <c r="I54" s="8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J54" s="8">
         <v>0</v>
@@ -7156,10 +7156,10 @@
       </c>
       <c r="M54" s="8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N54" s="8">
-        <v>439</v>
+        <v>396</v>
       </c>
       <c r="O54" s="8"/>
       <c r="P54" s="8"/>
@@ -7194,23 +7194,23 @@
         <v>12</v>
       </c>
       <c r="I55" s="8">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="J55" s="8">
         <v>0</v>
       </c>
       <c r="K55" s="8">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L55" s="8">
         <v>0</v>
       </c>
       <c r="M55" s="8">
         <f t="shared" si="0"/>
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="N55" s="8">
-        <v>295</v>
+        <v>238</v>
       </c>
       <c r="O55" s="8"/>
       <c r="P55" s="8"/>
@@ -7296,23 +7296,23 @@
         <v>12</v>
       </c>
       <c r="I57" s="8">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="J57" s="8">
         <v>0</v>
       </c>
       <c r="K57" s="8">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L57" s="8">
         <v>0</v>
       </c>
       <c r="M57" s="8">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N57" s="8">
-        <v>604</v>
+        <v>586</v>
       </c>
       <c r="O57" s="8"/>
       <c r="P57" s="8"/>
@@ -7363,7 +7363,7 @@
         <v>4</v>
       </c>
       <c r="N58" s="8">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="O58" s="8"/>
       <c r="P58" s="8"/>
@@ -7398,7 +7398,7 @@
         <v>13</v>
       </c>
       <c r="I59" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J59" s="8">
         <v>0</v>
@@ -7411,10 +7411,10 @@
       </c>
       <c r="M59" s="8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N59" s="8">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="O59" s="8"/>
       <c r="P59" s="8"/>
@@ -7465,7 +7465,7 @@
         <v>5</v>
       </c>
       <c r="N60" s="8">
-        <v>714</v>
+        <v>699</v>
       </c>
       <c r="O60" s="8"/>
       <c r="P60" s="8"/>
@@ -7500,13 +7500,13 @@
         <v>12</v>
       </c>
       <c r="I61" s="8">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J61" s="8">
         <v>0</v>
       </c>
       <c r="K61" s="8">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L61" s="8">
         <v>0</v>
@@ -7516,7 +7516,7 @@
         <v>29</v>
       </c>
       <c r="N61" s="8">
-        <v>593</v>
+        <v>542</v>
       </c>
       <c r="O61" s="8"/>
       <c r="P61" s="8"/>
@@ -7567,7 +7567,7 @@
         <v>8</v>
       </c>
       <c r="N62" s="8">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="O62" s="8"/>
       <c r="P62" s="8"/>
@@ -7602,7 +7602,7 @@
         <v>12</v>
       </c>
       <c r="I63" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J63" s="8">
         <v>0</v>
@@ -7615,10 +7615,10 @@
       </c>
       <c r="M63" s="8">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N63" s="8">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="O63" s="8"/>
       <c r="P63" s="8"/>
@@ -7653,7 +7653,7 @@
         <v>13</v>
       </c>
       <c r="I64" s="8">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J64" s="8">
         <v>0</v>
@@ -7666,10 +7666,10 @@
       </c>
       <c r="M64" s="8">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N64" s="8">
-        <v>158</v>
+        <v>106</v>
       </c>
       <c r="O64" s="8"/>
       <c r="P64" s="8"/>
@@ -7704,7 +7704,7 @@
         <v>12</v>
       </c>
       <c r="I65" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J65" s="8">
         <v>0</v>
@@ -7717,10 +7717,10 @@
       </c>
       <c r="M65" s="8">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N65" s="8">
-        <v>997</v>
+        <v>980</v>
       </c>
       <c r="O65" s="8"/>
       <c r="P65" s="8"/>
@@ -7822,7 +7822,7 @@
         <v>5</v>
       </c>
       <c r="N67" s="8">
-        <v>195</v>
+        <v>166</v>
       </c>
       <c r="O67" s="8"/>
       <c r="P67" s="8"/>
@@ -7863,17 +7863,17 @@
         <v>0</v>
       </c>
       <c r="K68" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L68" s="8">
         <v>0</v>
       </c>
       <c r="M68" s="8">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N68" s="8">
-        <v>983</v>
+        <v>971</v>
       </c>
       <c r="O68" s="8"/>
       <c r="P68" s="8"/>
@@ -7908,23 +7908,23 @@
         <v>12</v>
       </c>
       <c r="I69" s="8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J69" s="8">
         <v>0</v>
       </c>
       <c r="K69" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L69" s="8">
         <v>0</v>
       </c>
       <c r="M69" s="8">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N69" s="8">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="O69" s="8"/>
       <c r="P69" s="8"/>
@@ -7959,7 +7959,7 @@
         <v>16</v>
       </c>
       <c r="I70" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J70" s="8">
         <v>0</v>
@@ -7972,7 +7972,7 @@
       </c>
       <c r="M70" s="8">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N70" s="8">
         <v>597</v>
@@ -8010,7 +8010,7 @@
         <v>12</v>
       </c>
       <c r="I71" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J71" s="8">
         <v>0</v>
@@ -8023,10 +8023,10 @@
       </c>
       <c r="M71" s="8">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N71" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O71" s="8"/>
       <c r="P71" s="8"/>
@@ -8077,7 +8077,7 @@
         <v>10</v>
       </c>
       <c r="N72" s="8">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="O72" s="8"/>
       <c r="P72" s="8"/>
@@ -8112,23 +8112,23 @@
         <v>12</v>
       </c>
       <c r="I73" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J73" s="8">
         <v>0</v>
       </c>
       <c r="K73" s="8">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L73" s="8">
         <v>0</v>
       </c>
       <c r="M73" s="8">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="N73" s="8">
-        <v>901</v>
+        <v>841</v>
       </c>
       <c r="O73" s="8"/>
       <c r="P73" s="8"/>
@@ -8163,13 +8163,13 @@
         <v>14</v>
       </c>
       <c r="I74" s="8">
+        <v>4</v>
+      </c>
+      <c r="J74" s="8">
+        <v>0</v>
+      </c>
+      <c r="K74" s="8">
         <v>1</v>
-      </c>
-      <c r="J74" s="8">
-        <v>0</v>
-      </c>
-      <c r="K74" s="8">
-        <v>4</v>
       </c>
       <c r="L74" s="8">
         <v>0</v>
@@ -8179,7 +8179,7 @@
         <v>5</v>
       </c>
       <c r="N74" s="8">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="O74" s="8"/>
       <c r="P74" s="8"/>
@@ -8214,7 +8214,7 @@
         <v>13</v>
       </c>
       <c r="I75" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J75" s="8">
         <v>0</v>
@@ -8227,10 +8227,10 @@
       </c>
       <c r="M75" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N75" s="8">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O75" s="8"/>
       <c r="P75" s="8"/>
@@ -8265,7 +8265,7 @@
         <v>13</v>
       </c>
       <c r="I76" s="8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J76" s="8">
         <v>0</v>
@@ -8278,10 +8278,10 @@
       </c>
       <c r="M76" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N76" s="8">
-        <v>967</v>
+        <v>949</v>
       </c>
       <c r="O76" s="8"/>
       <c r="P76" s="8"/>
@@ -8332,7 +8332,7 @@
         <v>5</v>
       </c>
       <c r="N77" s="8">
-        <v>413</v>
+        <v>390</v>
       </c>
       <c r="O77" s="8"/>
       <c r="P77" s="8"/>
@@ -8383,7 +8383,7 @@
         <v>20</v>
       </c>
       <c r="N78" s="8">
-        <v>674</v>
+        <v>639</v>
       </c>
       <c r="O78" s="8"/>
       <c r="P78" s="8"/>
@@ -8418,7 +8418,7 @@
         <v>13</v>
       </c>
       <c r="I79" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J79" s="8">
         <v>0</v>
@@ -8431,10 +8431,10 @@
       </c>
       <c r="M79" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N79" s="8">
-        <v>254</v>
+        <v>209</v>
       </c>
       <c r="O79" s="8"/>
       <c r="P79" s="8"/>
@@ -8571,13 +8571,13 @@
         <v>15</v>
       </c>
       <c r="I82" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J82" s="8">
         <v>0</v>
       </c>
       <c r="K82" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L82" s="8">
         <v>0</v>
@@ -8587,7 +8587,7 @@
         <v>5</v>
       </c>
       <c r="N82" s="8">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="O82" s="8"/>
       <c r="P82" s="8"/>
@@ -8622,7 +8622,7 @@
         <v>15</v>
       </c>
       <c r="I83" s="8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J83" s="8">
         <v>0</v>
@@ -8635,10 +8635,10 @@
       </c>
       <c r="M83" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N83" s="8">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O83" s="8"/>
       <c r="P83" s="8"/>
@@ -8740,7 +8740,7 @@
         <v>5</v>
       </c>
       <c r="N85" s="8">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="O85" s="8"/>
       <c r="P85" s="8"/>
@@ -8775,7 +8775,7 @@
         <v>12</v>
       </c>
       <c r="I86" s="8">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J86" s="8">
         <v>0</v>
@@ -8788,10 +8788,10 @@
       </c>
       <c r="M86" s="8">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N86" s="8">
-        <v>703</v>
+        <v>634</v>
       </c>
       <c r="O86" s="8"/>
       <c r="P86" s="8"/>
@@ -8842,7 +8842,7 @@
         <v>7</v>
       </c>
       <c r="N87" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O87" s="8"/>
       <c r="P87" s="8"/>
@@ -8877,13 +8877,13 @@
         <v>12</v>
       </c>
       <c r="I88" s="8">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J88" s="8">
         <v>0</v>
       </c>
       <c r="K88" s="8">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L88" s="8">
         <v>0</v>
@@ -8893,7 +8893,7 @@
         <v>13</v>
       </c>
       <c r="N88" s="8">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="O88" s="8"/>
       <c r="P88" s="8"/>
@@ -8928,23 +8928,23 @@
         <v>12</v>
       </c>
       <c r="I89" s="8">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J89" s="8">
         <v>0</v>
       </c>
       <c r="K89" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L89" s="8">
         <v>0</v>
       </c>
       <c r="M89" s="8">
         <f t="shared" si="1"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N89" s="8">
-        <v>155</v>
+        <v>108</v>
       </c>
       <c r="O89" s="8"/>
       <c r="P89" s="8"/>
@@ -9030,7 +9030,7 @@
         <v>12</v>
       </c>
       <c r="I91" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J91" s="8">
         <v>0</v>
@@ -9043,10 +9043,10 @@
       </c>
       <c r="M91" s="8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N91" s="8">
-        <v>1256</v>
+        <v>1237</v>
       </c>
       <c r="O91" s="8"/>
       <c r="P91" s="8"/>
@@ -9081,7 +9081,7 @@
         <v>12</v>
       </c>
       <c r="I92" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J92" s="8">
         <v>0</v>
@@ -9094,10 +9094,10 @@
       </c>
       <c r="M92" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N92" s="8">
-        <v>134</v>
+        <v>406</v>
       </c>
       <c r="O92" s="8"/>
       <c r="P92" s="8"/>
@@ -9132,23 +9132,23 @@
         <v>13</v>
       </c>
       <c r="I93" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J93" s="8">
         <v>0</v>
       </c>
       <c r="K93" s="8">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L93" s="8">
         <v>0</v>
       </c>
       <c r="M93" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N93" s="8">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="O93" s="8"/>
       <c r="P93" s="8"/>
@@ -9183,7 +9183,7 @@
         <v>12</v>
       </c>
       <c r="I94" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J94" s="8">
         <v>0</v>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="M94" s="8">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N94" s="8">
         <v>0</v>
@@ -9250,7 +9250,7 @@
         <v>8</v>
       </c>
       <c r="N95" s="8">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O95" s="8"/>
       <c r="P95" s="8"/>
@@ -9285,23 +9285,23 @@
         <v>13</v>
       </c>
       <c r="I96" s="8">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J96" s="8">
         <v>0</v>
       </c>
       <c r="K96" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L96" s="8">
         <v>0</v>
       </c>
       <c r="M96" s="8">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N96" s="8">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="O96" s="8"/>
       <c r="P96" s="8"/>
@@ -9336,23 +9336,23 @@
         <v>14</v>
       </c>
       <c r="I97" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J97" s="8">
         <v>0</v>
       </c>
       <c r="K97" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L97" s="8">
         <v>0</v>
       </c>
       <c r="M97" s="8">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="N97" s="8">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="O97" s="8"/>
       <c r="P97" s="8"/>
@@ -9489,7 +9489,7 @@
         <v>15</v>
       </c>
       <c r="I100" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J100" s="8">
         <v>0</v>
@@ -9502,7 +9502,7 @@
       </c>
       <c r="M100" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N100" s="8">
         <v>0</v>
@@ -9591,23 +9591,23 @@
         <v>14</v>
       </c>
       <c r="I102" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J102" s="8">
         <v>0</v>
       </c>
       <c r="K102" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L102" s="8">
         <v>0</v>
       </c>
       <c r="M102" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N102" s="8">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="O102" s="8"/>
       <c r="P102" s="8"/>
@@ -9642,7 +9642,7 @@
         <v>15</v>
       </c>
       <c r="I103" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J103" s="8">
         <v>0</v>
@@ -9655,7 +9655,7 @@
       </c>
       <c r="M103" s="8">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N103" s="8">
         <v>554</v>
@@ -9760,7 +9760,7 @@
         <v>8</v>
       </c>
       <c r="N105" s="8">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="O105" s="8"/>
       <c r="P105" s="8"/>
@@ -9811,7 +9811,7 @@
         <v>4</v>
       </c>
       <c r="N106" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O106" s="8"/>
       <c r="P106" s="8"/>
@@ -10050,7 +10050,7 @@
         <v>13</v>
       </c>
       <c r="I111" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J111" s="8">
         <v>0</v>
@@ -10063,7 +10063,7 @@
       </c>
       <c r="M111" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N111" s="8">
         <v>0</v>
@@ -10101,23 +10101,23 @@
         <v>12</v>
       </c>
       <c r="I112" s="8">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="J112" s="8">
         <v>0</v>
       </c>
       <c r="K112" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L112" s="8">
         <v>0</v>
       </c>
       <c r="M112" s="8">
         <f t="shared" si="1"/>
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="N112" s="8">
-        <v>247</v>
+        <v>38</v>
       </c>
       <c r="O112" s="8"/>
       <c r="P112" s="8"/>
@@ -10152,7 +10152,7 @@
         <v>12</v>
       </c>
       <c r="I113" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J113" s="8">
         <v>0</v>
@@ -10165,10 +10165,10 @@
       </c>
       <c r="M113" s="8">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N113" s="8">
-        <v>1198</v>
+        <v>1171</v>
       </c>
       <c r="O113" s="8"/>
       <c r="P113" s="8"/>
@@ -10209,17 +10209,17 @@
         <v>0</v>
       </c>
       <c r="K114" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="8">
         <v>0</v>
       </c>
       <c r="M114" s="8">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N114" s="8">
-        <v>664</v>
+        <v>547</v>
       </c>
       <c r="O114" s="8"/>
       <c r="P114" s="8"/>
@@ -10254,7 +10254,7 @@
         <v>13</v>
       </c>
       <c r="I115" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J115" s="8">
         <v>0</v>
@@ -10267,10 +10267,10 @@
       </c>
       <c r="M115" s="8">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N115" s="8">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="O115" s="8"/>
       <c r="P115" s="8"/>
@@ -10305,7 +10305,7 @@
         <v>12</v>
       </c>
       <c r="I116" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J116" s="8">
         <v>0</v>
@@ -10318,10 +10318,10 @@
       </c>
       <c r="M116" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N116" s="8">
-        <v>854</v>
+        <v>830</v>
       </c>
       <c r="O116" s="8"/>
       <c r="P116" s="8"/>
@@ -10362,17 +10362,17 @@
         <v>0</v>
       </c>
       <c r="K117" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L117" s="8">
         <v>0</v>
       </c>
       <c r="M117" s="8">
         <f t="shared" si="1"/>
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="N117" s="8">
-        <v>498</v>
+        <v>483</v>
       </c>
       <c r="O117" s="8"/>
       <c r="P117" s="8"/>
@@ -10407,23 +10407,23 @@
         <v>13</v>
       </c>
       <c r="I118" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J118" s="8">
         <v>0</v>
       </c>
       <c r="K118" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L118" s="8">
         <v>0</v>
       </c>
       <c r="M118" s="8">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N118" s="8">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="O118" s="8"/>
       <c r="P118" s="8"/>
@@ -10474,7 +10474,7 @@
         <v>8</v>
       </c>
       <c r="N119" s="8">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="O119" s="8"/>
       <c r="P119" s="8"/>
@@ -10509,7 +10509,7 @@
         <v>14</v>
       </c>
       <c r="I120" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J120" s="8">
         <v>0</v>
@@ -10522,10 +10522,10 @@
       </c>
       <c r="M120" s="8">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N120" s="8">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="O120" s="8"/>
       <c r="P120" s="8"/>
@@ -10576,7 +10576,7 @@
         <v>7</v>
       </c>
       <c r="N121" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O121" s="8"/>
       <c r="P121" s="8"/>
@@ -10617,17 +10617,17 @@
         <v>0</v>
       </c>
       <c r="K122" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L122" s="8">
         <v>0</v>
       </c>
       <c r="M122" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N122" s="8">
-        <v>1041</v>
+        <v>1034</v>
       </c>
       <c r="O122" s="8"/>
       <c r="P122" s="8"/>
@@ -10662,7 +10662,7 @@
         <v>14</v>
       </c>
       <c r="I123" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J123" s="8">
         <v>0</v>
@@ -10675,7 +10675,7 @@
       </c>
       <c r="M123" s="8">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N123" s="8">
         <v>0</v>
@@ -10764,7 +10764,7 @@
         <v>13</v>
       </c>
       <c r="I125" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J125" s="8">
         <v>0</v>
@@ -10777,10 +10777,10 @@
       </c>
       <c r="M125" s="8">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N125" s="8">
-        <v>329</v>
+        <v>308</v>
       </c>
       <c r="O125" s="8"/>
       <c r="P125" s="8"/>
@@ -10815,7 +10815,7 @@
         <v>17</v>
       </c>
       <c r="I126" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J126" s="8">
         <v>0</v>
@@ -10828,7 +10828,7 @@
       </c>
       <c r="M126" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N126" s="8">
         <v>0</v>
@@ -10866,7 +10866,7 @@
         <v>12</v>
       </c>
       <c r="I127" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J127" s="8">
         <v>0</v>
@@ -10879,7 +10879,7 @@
       </c>
       <c r="M127" s="8">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N127" s="8">
         <v>0</v>
@@ -10968,7 +10968,7 @@
         <v>15</v>
       </c>
       <c r="I129" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J129" s="8">
         <v>0</v>
@@ -10981,7 +10981,7 @@
       </c>
       <c r="M129" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N129" s="8">
         <v>0</v>
@@ -11019,23 +11019,23 @@
         <v>12</v>
       </c>
       <c r="I130" s="8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J130" s="8">
         <v>0</v>
       </c>
       <c r="K130" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L130" s="8">
         <v>0</v>
       </c>
       <c r="M130" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N130" s="8">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="O130" s="8"/>
       <c r="P130" s="8"/>
@@ -11086,7 +11086,7 @@
         <v>4</v>
       </c>
       <c r="N131" s="8">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="O131" s="8"/>
       <c r="P131" s="8"/>
@@ -11121,7 +11121,7 @@
         <v>12</v>
       </c>
       <c r="I132" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J132" s="8">
         <v>0</v>
@@ -11134,10 +11134,10 @@
       </c>
       <c r="M132" s="8">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N132" s="8">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="O132" s="8"/>
       <c r="P132" s="8"/>
@@ -11172,23 +11172,23 @@
         <v>12</v>
       </c>
       <c r="I133" s="8">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J133" s="8">
         <v>0</v>
       </c>
       <c r="K133" s="8">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L133" s="8">
         <v>0</v>
       </c>
       <c r="M133" s="8">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="N133" s="8">
-        <v>590</v>
+        <v>401</v>
       </c>
       <c r="O133" s="8"/>
       <c r="P133" s="8"/>
@@ -11223,7 +11223,7 @@
         <v>15</v>
       </c>
       <c r="I134" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J134" s="8">
         <v>0</v>
@@ -11236,7 +11236,7 @@
       </c>
       <c r="M134" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N134" s="8">
         <v>0</v>
@@ -11274,23 +11274,23 @@
         <v>15</v>
       </c>
       <c r="I135" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J135" s="8">
         <v>0</v>
       </c>
       <c r="K135" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L135" s="8">
         <v>0</v>
       </c>
       <c r="M135" s="8">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N135" s="8">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="O135" s="8"/>
       <c r="P135" s="8"/>
@@ -11325,13 +11325,13 @@
         <v>14</v>
       </c>
       <c r="I136" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J136" s="8">
         <v>0</v>
       </c>
       <c r="K136" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L136" s="8">
         <v>0</v>
@@ -11341,7 +11341,7 @@
         <v>4</v>
       </c>
       <c r="N136" s="8">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="O136" s="8"/>
       <c r="P136" s="8"/>
@@ -11427,7 +11427,7 @@
         <v>12</v>
       </c>
       <c r="I138" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J138" s="8">
         <v>0</v>
@@ -11440,7 +11440,7 @@
       </c>
       <c r="M138" s="8">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N138" s="8">
         <v>1055</v>
@@ -11529,7 +11529,7 @@
         <v>15</v>
       </c>
       <c r="I140" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J140" s="8">
         <v>0</v>
@@ -11542,7 +11542,7 @@
       </c>
       <c r="M140" s="8">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N140" s="8">
         <v>452</v>
@@ -11580,13 +11580,13 @@
         <v>13</v>
       </c>
       <c r="I141" s="8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J141" s="8">
         <v>0</v>
       </c>
       <c r="K141" s="8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L141" s="8">
         <v>0</v>
@@ -11800,7 +11800,7 @@
         <v>4</v>
       </c>
       <c r="N145" s="8">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="O145" s="8"/>
       <c r="P145" s="8"/>
@@ -11835,7 +11835,7 @@
         <v>16</v>
       </c>
       <c r="I146" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J146" s="8">
         <v>0</v>
@@ -11848,7 +11848,7 @@
       </c>
       <c r="M146" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N146" s="8">
         <v>0</v>
@@ -11902,7 +11902,7 @@
         <v>3</v>
       </c>
       <c r="N147" s="8">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="O147" s="8"/>
       <c r="P147" s="8"/>
@@ -11953,7 +11953,7 @@
         <v>3</v>
       </c>
       <c r="N148" s="8">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="O148" s="8"/>
       <c r="P148" s="8"/>
@@ -11988,23 +11988,23 @@
         <v>12</v>
       </c>
       <c r="I149" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J149" s="8">
         <v>0</v>
       </c>
       <c r="K149" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L149" s="8">
         <v>0</v>
       </c>
       <c r="M149" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N149" s="8">
-        <v>379</v>
+        <v>335</v>
       </c>
       <c r="O149" s="8"/>
       <c r="P149" s="8"/>
@@ -12039,23 +12039,23 @@
         <v>12</v>
       </c>
       <c r="I150" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J150" s="8">
         <v>0</v>
       </c>
       <c r="K150" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L150" s="8">
         <v>0</v>
       </c>
       <c r="M150" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N150" s="8">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="O150" s="8"/>
       <c r="P150" s="8"/>
@@ -12090,7 +12090,7 @@
         <v>13</v>
       </c>
       <c r="I151" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J151" s="8">
         <v>0</v>
@@ -12103,10 +12103,10 @@
       </c>
       <c r="M151" s="8">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N151" s="8">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="O151" s="8"/>
       <c r="P151" s="8"/>
@@ -12157,7 +12157,7 @@
         <v>4</v>
       </c>
       <c r="N152" s="8">
-        <v>279</v>
+        <v>246</v>
       </c>
       <c r="O152" s="8"/>
       <c r="P152" s="8"/>
@@ -12192,20 +12192,20 @@
         <v>13</v>
       </c>
       <c r="I153" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J153" s="8">
         <v>0</v>
       </c>
       <c r="K153" s="8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L153" s="8">
         <v>0</v>
       </c>
       <c r="M153" s="8">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="N153" s="8">
         <v>538</v>
@@ -12243,7 +12243,7 @@
         <v>15</v>
       </c>
       <c r="I154" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J154" s="8">
         <v>0</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="M154" s="8">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N154" s="8">
         <v>488</v>
@@ -12345,7 +12345,7 @@
         <v>15</v>
       </c>
       <c r="I156" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J156" s="8">
         <v>0</v>
@@ -12358,7 +12358,7 @@
       </c>
       <c r="M156" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N156" s="8">
         <v>0</v>
@@ -12498,7 +12498,7 @@
         <v>15</v>
       </c>
       <c r="I159" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J159" s="8">
         <v>0</v>
@@ -12511,10 +12511,10 @@
       </c>
       <c r="M159" s="8">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N159" s="8">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O159" s="8"/>
       <c r="P159" s="8"/>
@@ -12549,7 +12549,7 @@
         <v>15</v>
       </c>
       <c r="I160" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J160" s="8">
         <v>0</v>
@@ -12562,10 +12562,10 @@
       </c>
       <c r="M160" s="8">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N160" s="8">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="O160" s="8"/>
       <c r="P160" s="8"/>
@@ -12616,7 +12616,7 @@
         <v>6</v>
       </c>
       <c r="N161" s="8">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="O161" s="8"/>
       <c r="P161" s="8"/>
@@ -12651,7 +12651,7 @@
         <v>13</v>
       </c>
       <c r="I162" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J162" s="8">
         <v>0</v>
@@ -12664,10 +12664,10 @@
       </c>
       <c r="M162" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N162" s="8">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="O162" s="8"/>
       <c r="P162" s="8"/>
@@ -12769,7 +12769,7 @@
         <v>3</v>
       </c>
       <c r="N164" s="8">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O164" s="8"/>
       <c r="P164" s="8"/>
@@ -12820,7 +12820,7 @@
         <v>10</v>
       </c>
       <c r="N165" s="8">
-        <v>1428</v>
+        <v>1403</v>
       </c>
       <c r="O165" s="8"/>
       <c r="P165" s="8"/>
@@ -12855,7 +12855,7 @@
         <v>14</v>
       </c>
       <c r="I166" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J166" s="8">
         <v>0</v>
@@ -12868,10 +12868,10 @@
       </c>
       <c r="M166" s="8">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N166" s="8">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="O166" s="8"/>
       <c r="P166" s="8"/>
@@ -12973,7 +12973,7 @@
         <v>4</v>
       </c>
       <c r="N168" s="8">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="O168" s="8"/>
       <c r="P168" s="8"/>
@@ -13059,7 +13059,7 @@
         <v>14</v>
       </c>
       <c r="I170" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J170" s="8">
         <v>0</v>
@@ -13072,10 +13072,10 @@
       </c>
       <c r="M170" s="8">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N170" s="8">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="O170" s="8"/>
       <c r="P170" s="8"/>
@@ -13161,13 +13161,13 @@
         <v>14</v>
       </c>
       <c r="I172" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J172" s="8">
         <v>0</v>
       </c>
       <c r="K172" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L172" s="8">
         <v>0</v>
@@ -13177,7 +13177,7 @@
         <v>2</v>
       </c>
       <c r="N172" s="8">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O172" s="8"/>
       <c r="P172" s="8"/>
@@ -13228,7 +13228,7 @@
         <v>2</v>
       </c>
       <c r="N173" s="8">
-        <v>703</v>
+        <v>690</v>
       </c>
       <c r="O173" s="8"/>
       <c r="P173" s="8"/>
@@ -13314,7 +13314,7 @@
         <v>14</v>
       </c>
       <c r="I175" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J175" s="8">
         <v>0</v>
@@ -13327,7 +13327,7 @@
       </c>
       <c r="M175" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N175" s="8">
         <v>0</v>
@@ -13381,7 +13381,7 @@
         <v>2</v>
       </c>
       <c r="N176" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O176" s="8"/>
       <c r="P176" s="8"/>
@@ -13416,7 +13416,7 @@
         <v>14</v>
       </c>
       <c r="I177" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J177" s="8">
         <v>0</v>
@@ -13429,7 +13429,7 @@
       </c>
       <c r="M177" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N177" s="8">
         <v>0</v>
@@ -13534,7 +13534,7 @@
         <v>3</v>
       </c>
       <c r="N179" s="8">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="O179" s="8"/>
       <c r="P179" s="8"/>
@@ -13585,7 +13585,7 @@
         <v>8</v>
       </c>
       <c r="N180" s="8">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="O180" s="8"/>
       <c r="P180" s="8"/>
@@ -13620,7 +13620,7 @@
         <v>15</v>
       </c>
       <c r="I181" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J181" s="8">
         <v>0</v>
@@ -13633,10 +13633,10 @@
       </c>
       <c r="M181" s="8">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N181" s="8">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="O181" s="8"/>
       <c r="P181" s="8"/>
@@ -13738,7 +13738,7 @@
         <v>6</v>
       </c>
       <c r="N183" s="8">
-        <v>623</v>
+        <v>515</v>
       </c>
       <c r="O183" s="8"/>
       <c r="P183" s="8"/>
@@ -13824,20 +13824,20 @@
         <v>12</v>
       </c>
       <c r="I185" s="8">
-        <v>302</v>
+        <v>383</v>
       </c>
       <c r="J185" s="8">
         <v>0</v>
       </c>
       <c r="K185" s="8">
-        <v>156</v>
+        <v>36</v>
       </c>
       <c r="L185" s="8">
         <v>0</v>
       </c>
       <c r="M185" s="8">
         <f t="shared" si="2"/>
-        <v>458</v>
+        <v>419</v>
       </c>
       <c r="N185" s="8">
         <v>1887</v>
@@ -13875,7 +13875,7 @@
         <v>12</v>
       </c>
       <c r="I186" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J186" s="8">
         <v>0</v>
@@ -13888,10 +13888,10 @@
       </c>
       <c r="M186" s="8">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N186" s="8">
-        <v>986</v>
+        <v>977</v>
       </c>
       <c r="O186" s="8"/>
       <c r="P186" s="8"/>
@@ -13942,7 +13942,7 @@
         <v>2</v>
       </c>
       <c r="N187" s="8">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="O187" s="8"/>
       <c r="P187" s="8"/>
@@ -13977,7 +13977,7 @@
         <v>15</v>
       </c>
       <c r="I188" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J188" s="8">
         <v>0</v>
@@ -13990,10 +13990,10 @@
       </c>
       <c r="M188" s="8">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N188" s="8">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="O188" s="8"/>
       <c r="P188" s="8"/>
@@ -14079,23 +14079,23 @@
         <v>12</v>
       </c>
       <c r="I190" s="8">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J190" s="8">
         <v>0</v>
       </c>
       <c r="K190" s="8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L190" s="8">
         <v>0</v>
       </c>
       <c r="M190" s="8">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N190" s="8">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="O190" s="8"/>
       <c r="P190" s="8"/>
@@ -14130,7 +14130,7 @@
         <v>12</v>
       </c>
       <c r="I191" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J191" s="8">
         <v>0</v>
@@ -14143,10 +14143,10 @@
       </c>
       <c r="M191" s="8">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N191" s="8">
-        <v>1002</v>
+        <v>983</v>
       </c>
       <c r="O191" s="8"/>
       <c r="P191" s="8"/>
@@ -14283,7 +14283,7 @@
         <v>15</v>
       </c>
       <c r="I194" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J194" s="8">
         <v>0</v>
@@ -14296,10 +14296,10 @@
       </c>
       <c r="M194" s="8">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N194" s="8">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O194" s="8"/>
       <c r="P194" s="8"/>
@@ -14452,7 +14452,7 @@
         <v>4</v>
       </c>
       <c r="N197" s="8">
-        <v>811</v>
+        <v>798</v>
       </c>
       <c r="O197" s="8"/>
       <c r="P197" s="8"/>
@@ -14487,7 +14487,7 @@
         <v>12</v>
       </c>
       <c r="I198" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J198" s="8">
         <v>0</v>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="M198" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N198" s="8">
         <v>0</v>
@@ -14538,7 +14538,7 @@
         <v>14</v>
       </c>
       <c r="I199" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J199" s="8">
         <v>0</v>
@@ -14551,7 +14551,7 @@
       </c>
       <c r="M199" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N199" s="8">
         <v>0</v>
@@ -14589,7 +14589,7 @@
         <v>14</v>
       </c>
       <c r="I200" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J200" s="8">
         <v>0</v>
@@ -14602,7 +14602,7 @@
       </c>
       <c r="M200" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N200" s="8">
         <v>0</v>
@@ -14640,7 +14640,7 @@
         <v>12</v>
       </c>
       <c r="I201" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J201" s="8">
         <v>0</v>
@@ -14653,7 +14653,7 @@
       </c>
       <c r="M201" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N201" s="8">
         <v>0</v>
@@ -14844,7 +14844,7 @@
         <v>16</v>
       </c>
       <c r="I205" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J205" s="8">
         <v>0</v>
@@ -14857,7 +14857,7 @@
       </c>
       <c r="M205" s="8">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N205" s="8">
         <v>0</v>
@@ -14946,13 +14946,13 @@
         <v>14</v>
       </c>
       <c r="I207" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J207" s="8">
         <v>0</v>
       </c>
       <c r="K207" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L207" s="8">
         <v>0</v>
@@ -14962,7 +14962,7 @@
         <v>2</v>
       </c>
       <c r="N207" s="8">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="O207" s="8"/>
       <c r="P207" s="8"/>
@@ -15003,17 +15003,17 @@
         <v>0</v>
       </c>
       <c r="K208" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L208" s="8">
         <v>0</v>
       </c>
       <c r="M208" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N208" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O208" s="8"/>
       <c r="P208" s="8"/>
@@ -15048,7 +15048,7 @@
         <v>12</v>
       </c>
       <c r="I209" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J209" s="8">
         <v>0</v>
@@ -15061,10 +15061,10 @@
       </c>
       <c r="M209" s="8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N209" s="8">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="O209" s="8"/>
       <c r="P209" s="8"/>
@@ -15150,13 +15150,13 @@
         <v>12</v>
       </c>
       <c r="I211" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J211" s="8">
         <v>0</v>
       </c>
       <c r="K211" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L211" s="8">
         <v>0</v>
@@ -15166,7 +15166,7 @@
         <v>2</v>
       </c>
       <c r="N211" s="8">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="O211" s="8"/>
       <c r="P211" s="8"/>
@@ -15201,7 +15201,7 @@
         <v>14</v>
       </c>
       <c r="I212" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J212" s="8">
         <v>0</v>
@@ -15214,7 +15214,7 @@
       </c>
       <c r="M212" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N212" s="8">
         <v>0</v>
@@ -15309,17 +15309,17 @@
         <v>0</v>
       </c>
       <c r="K214" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L214" s="8">
         <v>0</v>
       </c>
       <c r="M214" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N214" s="8">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="O214" s="8"/>
       <c r="P214" s="8"/>
@@ -15354,7 +15354,7 @@
         <v>14</v>
       </c>
       <c r="I215" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J215" s="8">
         <v>0</v>
@@ -15367,7 +15367,7 @@
       </c>
       <c r="M215" s="8">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N215" s="8">
         <v>753</v>
@@ -15456,7 +15456,7 @@
         <v>13</v>
       </c>
       <c r="I217" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J217" s="8">
         <v>0</v>
@@ -15469,7 +15469,7 @@
       </c>
       <c r="M217" s="8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N217" s="8">
         <v>92</v>
@@ -15523,7 +15523,7 @@
         <v>6</v>
       </c>
       <c r="N218" s="8">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="O218" s="8"/>
       <c r="P218" s="8"/>
@@ -15574,7 +15574,7 @@
         <v>6</v>
       </c>
       <c r="N219" s="8">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="O219" s="8"/>
       <c r="P219" s="8"/>
@@ -15660,7 +15660,7 @@
         <v>16</v>
       </c>
       <c r="I221" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J221" s="8">
         <v>0</v>
@@ -15673,10 +15673,10 @@
       </c>
       <c r="M221" s="8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N221" s="8">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O221" s="8"/>
       <c r="P221" s="8"/>
@@ -15762,7 +15762,7 @@
         <v>15</v>
       </c>
       <c r="I223" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J223" s="8">
         <v>0</v>
@@ -15775,7 +15775,7 @@
       </c>
       <c r="M223" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N223" s="8">
         <v>0</v>
@@ -15870,17 +15870,17 @@
         <v>0</v>
       </c>
       <c r="K225" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L225" s="8">
         <v>0</v>
       </c>
       <c r="M225" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N225" s="8">
-        <v>701</v>
+        <v>688</v>
       </c>
       <c r="O225" s="8"/>
       <c r="P225" s="8"/>
@@ -16017,23 +16017,23 @@
         <v>15</v>
       </c>
       <c r="I228" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J228" s="8">
         <v>0</v>
       </c>
       <c r="K228" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L228" s="8">
         <v>0</v>
       </c>
       <c r="M228" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N228" s="8">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="O228" s="8"/>
       <c r="P228" s="8"/>
@@ -16084,7 +16084,7 @@
         <v>2</v>
       </c>
       <c r="N229" s="8">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="O229" s="8"/>
       <c r="P229" s="8"/>
@@ -16221,7 +16221,7 @@
         <v>12</v>
       </c>
       <c r="I232" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J232" s="8">
         <v>0</v>
@@ -16234,10 +16234,10 @@
       </c>
       <c r="M232" s="8">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N232" s="8">
-        <v>716</v>
+        <v>686</v>
       </c>
       <c r="O232" s="8"/>
       <c r="P232" s="8"/>
@@ -16272,7 +16272,7 @@
         <v>15</v>
       </c>
       <c r="I233" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J233" s="8">
         <v>0</v>
@@ -16285,10 +16285,10 @@
       </c>
       <c r="M233" s="8">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N233" s="8">
-        <v>713</v>
+        <v>695</v>
       </c>
       <c r="O233" s="8"/>
       <c r="P233" s="8"/>
@@ -16329,17 +16329,17 @@
         <v>0</v>
       </c>
       <c r="K234" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L234" s="8">
         <v>0</v>
       </c>
       <c r="M234" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N234" s="8">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="O234" s="8"/>
       <c r="P234" s="8"/>
@@ -16390,7 +16390,7 @@
         <v>3</v>
       </c>
       <c r="N235" s="8">
-        <v>101</v>
+        <v>31</v>
       </c>
       <c r="O235" s="8"/>
       <c r="P235" s="8"/>
@@ -16425,7 +16425,7 @@
         <v>14</v>
       </c>
       <c r="I236" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J236" s="8">
         <v>0</v>
@@ -16438,7 +16438,7 @@
       </c>
       <c r="M236" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N236" s="8">
         <v>0</v>
@@ -16476,23 +16476,23 @@
         <v>12</v>
       </c>
       <c r="I237" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J237" s="8">
         <v>0</v>
       </c>
       <c r="K237" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L237" s="8">
         <v>0</v>
       </c>
       <c r="M237" s="8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N237" s="8">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="O237" s="8"/>
       <c r="P237" s="8"/>
@@ -16543,7 +16543,7 @@
         <v>6</v>
       </c>
       <c r="N238" s="8">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="O238" s="8"/>
       <c r="P238" s="8"/>
@@ -16594,7 +16594,7 @@
         <v>4</v>
       </c>
       <c r="N239" s="8">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="O239" s="8"/>
       <c r="P239" s="8"/>
@@ -16629,23 +16629,23 @@
         <v>13</v>
       </c>
       <c r="I240" s="8">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J240" s="8">
         <v>0</v>
       </c>
       <c r="K240" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L240" s="8">
         <v>0</v>
       </c>
       <c r="M240" s="8">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N240" s="8">
-        <v>477</v>
+        <v>460</v>
       </c>
       <c r="O240" s="8"/>
       <c r="P240" s="8"/>
@@ -16747,7 +16747,7 @@
         <v>3</v>
       </c>
       <c r="N242" s="8">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="O242" s="8"/>
       <c r="P242" s="8"/>
@@ -16782,23 +16782,23 @@
         <v>15</v>
       </c>
       <c r="I243" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J243" s="8">
         <v>0</v>
       </c>
       <c r="K243" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L243" s="8">
         <v>0</v>
       </c>
       <c r="M243" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N243" s="8">
-        <v>341</v>
+        <v>315</v>
       </c>
       <c r="O243" s="8"/>
       <c r="P243" s="8"/>
@@ -16935,13 +16935,13 @@
         <v>15</v>
       </c>
       <c r="I246" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J246" s="8">
         <v>0</v>
       </c>
       <c r="K246" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L246" s="8">
         <v>0</v>
@@ -16951,7 +16951,7 @@
         <v>3</v>
       </c>
       <c r="N246" s="8">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="O246" s="8"/>
       <c r="P246" s="8"/>
@@ -17002,7 +17002,7 @@
         <v>2</v>
       </c>
       <c r="N247" s="8">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="O247" s="8"/>
       <c r="P247" s="8"/>
@@ -17139,23 +17139,23 @@
         <v>12</v>
       </c>
       <c r="I250" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J250" s="8">
         <v>0</v>
       </c>
       <c r="K250" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L250" s="8">
         <v>0</v>
       </c>
       <c r="M250" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N250" s="8">
-        <v>1480</v>
+        <v>1473</v>
       </c>
       <c r="O250" s="8"/>
       <c r="P250" s="8"/>
@@ -17206,7 +17206,7 @@
         <v>2</v>
       </c>
       <c r="N251" s="8">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="O251" s="8"/>
       <c r="P251" s="8"/>
@@ -17257,7 +17257,7 @@
         <v>2</v>
       </c>
       <c r="N252" s="8">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="O252" s="8"/>
       <c r="P252" s="8"/>
@@ -17292,7 +17292,7 @@
         <v>14</v>
       </c>
       <c r="I253" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J253" s="8">
         <v>0</v>
@@ -17305,10 +17305,10 @@
       </c>
       <c r="M253" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N253" s="8">
-        <v>1232</v>
+        <v>1228</v>
       </c>
       <c r="O253" s="8"/>
       <c r="P253" s="8"/>
@@ -17359,7 +17359,7 @@
         <v>2</v>
       </c>
       <c r="N254" s="8">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="O254" s="8"/>
       <c r="P254" s="8"/>
@@ -17400,17 +17400,17 @@
         <v>0</v>
       </c>
       <c r="K255" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L255" s="8">
         <v>0</v>
       </c>
       <c r="M255" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N255" s="8">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="O255" s="8"/>
       <c r="P255" s="8"/>
@@ -17461,7 +17461,7 @@
         <v>2</v>
       </c>
       <c r="N256" s="8">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="O256" s="8"/>
       <c r="P256" s="8"/>
@@ -17512,7 +17512,7 @@
         <v>4</v>
       </c>
       <c r="N257" s="8">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="O257" s="8"/>
       <c r="P257" s="8"/>
@@ -17547,7 +17547,7 @@
         <v>16</v>
       </c>
       <c r="I258" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J258" s="8">
         <v>0</v>
@@ -17560,7 +17560,7 @@
       </c>
       <c r="M258" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N258" s="8">
         <v>74</v>
@@ -17604,17 +17604,17 @@
         <v>0</v>
       </c>
       <c r="K259" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L259" s="8">
         <v>0</v>
       </c>
       <c r="M259" s="8">
         <f t="shared" ref="M259:M322" si="4">I259+J259+K259+L259</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N259" s="8">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O259" s="8"/>
       <c r="P259" s="8"/>
@@ -17649,23 +17649,23 @@
         <v>13</v>
       </c>
       <c r="I260" s="8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J260" s="8">
         <v>0</v>
       </c>
       <c r="K260" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L260" s="8">
         <v>0</v>
       </c>
       <c r="M260" s="8">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N260" s="8">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="O260" s="8"/>
       <c r="P260" s="8"/>
@@ -17716,7 +17716,7 @@
         <v>27</v>
       </c>
       <c r="N261" s="8">
-        <v>1232</v>
+        <v>1190</v>
       </c>
       <c r="O261" s="8"/>
       <c r="P261" s="8"/>
@@ -17751,23 +17751,23 @@
         <v>12</v>
       </c>
       <c r="I262" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J262" s="8">
         <v>0</v>
       </c>
       <c r="K262" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L262" s="8">
         <v>0</v>
       </c>
       <c r="M262" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="N262" s="8">
-        <v>433</v>
+        <v>413</v>
       </c>
       <c r="O262" s="8"/>
       <c r="P262" s="8"/>
@@ -17802,23 +17802,23 @@
         <v>12</v>
       </c>
       <c r="I263" s="8">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J263" s="8">
         <v>0</v>
       </c>
       <c r="K263" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L263" s="8">
         <v>0</v>
       </c>
       <c r="M263" s="8">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N263" s="8">
-        <v>579</v>
+        <v>534</v>
       </c>
       <c r="O263" s="8"/>
       <c r="P263" s="8"/>
@@ -17869,7 +17869,7 @@
         <v>2</v>
       </c>
       <c r="N264" s="8">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="O264" s="8"/>
       <c r="P264" s="8"/>
@@ -17971,7 +17971,7 @@
         <v>3</v>
       </c>
       <c r="N266" s="8">
-        <v>1574</v>
+        <v>1570</v>
       </c>
       <c r="O266" s="8"/>
       <c r="P266" s="8"/>
@@ -18057,13 +18057,13 @@
         <v>15</v>
       </c>
       <c r="I268" s="8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J268" s="8">
         <v>0</v>
       </c>
       <c r="K268" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L268" s="8">
         <v>0</v>
@@ -18073,7 +18073,7 @@
         <v>6</v>
       </c>
       <c r="N268" s="8">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="O268" s="8"/>
       <c r="P268" s="8"/>
@@ -18108,7 +18108,7 @@
         <v>15</v>
       </c>
       <c r="I269" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J269" s="8">
         <v>0</v>
@@ -18121,10 +18121,10 @@
       </c>
       <c r="M269" s="8">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N269" s="8">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="O269" s="8"/>
       <c r="P269" s="8"/>
@@ -18379,7 +18379,7 @@
         <v>3</v>
       </c>
       <c r="N274" s="8">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="O274" s="8"/>
       <c r="P274" s="8"/>
@@ -18430,7 +18430,7 @@
         <v>4</v>
       </c>
       <c r="N275" s="8">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="O275" s="8"/>
       <c r="P275" s="8"/>
@@ -18481,7 +18481,7 @@
         <v>3</v>
       </c>
       <c r="N276" s="8">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="O276" s="8"/>
       <c r="P276" s="8"/>
@@ -18573,17 +18573,17 @@
         <v>0</v>
       </c>
       <c r="K278" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L278" s="8">
         <v>0</v>
       </c>
       <c r="M278" s="8">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N278" s="8">
-        <v>1873</v>
+        <v>1813</v>
       </c>
       <c r="O278" s="8"/>
       <c r="P278" s="8"/>
@@ -18618,13 +18618,13 @@
         <v>13</v>
       </c>
       <c r="I279" s="8">
+        <v>0</v>
+      </c>
+      <c r="J279" s="8">
+        <v>0</v>
+      </c>
+      <c r="K279" s="8">
         <v>2</v>
-      </c>
-      <c r="J279" s="8">
-        <v>0</v>
-      </c>
-      <c r="K279" s="8">
-        <v>0</v>
       </c>
       <c r="L279" s="8">
         <v>0</v>
@@ -18634,7 +18634,7 @@
         <v>2</v>
       </c>
       <c r="N279" s="8">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="O279" s="8"/>
       <c r="P279" s="8"/>
@@ -18685,7 +18685,7 @@
         <v>3</v>
       </c>
       <c r="N280" s="8">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O280" s="8"/>
       <c r="P280" s="8"/>
@@ -18828,17 +18828,17 @@
         <v>0</v>
       </c>
       <c r="K283" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L283" s="8">
         <v>0</v>
       </c>
       <c r="M283" s="8">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N283" s="8">
-        <v>340</v>
+        <v>314</v>
       </c>
       <c r="O283" s="8"/>
       <c r="P283" s="8"/>
@@ -18873,23 +18873,23 @@
         <v>12</v>
       </c>
       <c r="I284" s="8">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J284" s="8">
         <v>0</v>
       </c>
       <c r="K284" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L284" s="8">
         <v>0</v>
       </c>
       <c r="M284" s="8">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="N284" s="8">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="O284" s="8"/>
       <c r="P284" s="8"/>
@@ -18991,7 +18991,7 @@
         <v>4</v>
       </c>
       <c r="N286" s="8">
-        <v>1016</v>
+        <v>1009</v>
       </c>
       <c r="O286" s="8"/>
       <c r="P286" s="8"/>
@@ -19026,23 +19026,23 @@
         <v>12</v>
       </c>
       <c r="I287" s="8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J287" s="8">
         <v>0</v>
       </c>
       <c r="K287" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L287" s="8">
         <v>0</v>
       </c>
       <c r="M287" s="8">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N287" s="8">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="O287" s="8"/>
       <c r="P287" s="8"/>
@@ -19077,13 +19077,13 @@
         <v>14</v>
       </c>
       <c r="I288" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J288" s="8">
         <v>0</v>
       </c>
       <c r="K288" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L288" s="8">
         <v>0</v>
@@ -19093,7 +19093,7 @@
         <v>4</v>
       </c>
       <c r="N288" s="8">
-        <v>1535</v>
+        <v>1510</v>
       </c>
       <c r="O288" s="8"/>
       <c r="P288" s="8"/>
@@ -19128,13 +19128,13 @@
         <v>14</v>
       </c>
       <c r="I289" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J289" s="8">
         <v>0</v>
       </c>
       <c r="K289" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L289" s="8">
         <v>0</v>
@@ -19144,7 +19144,7 @@
         <v>3</v>
       </c>
       <c r="N289" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O289" s="8"/>
       <c r="P289" s="8"/>
@@ -19236,17 +19236,17 @@
         <v>0</v>
       </c>
       <c r="K291" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L291" s="8">
         <v>0</v>
       </c>
       <c r="M291" s="8">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N291" s="8">
-        <v>714</v>
+        <v>862</v>
       </c>
       <c r="O291" s="8"/>
       <c r="P291" s="8"/>
@@ -19281,13 +19281,13 @@
         <v>16</v>
       </c>
       <c r="I292" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J292" s="8">
         <v>0</v>
       </c>
       <c r="K292" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L292" s="8">
         <v>0</v>
@@ -19383,7 +19383,7 @@
         <v>12</v>
       </c>
       <c r="I294" s="8">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J294" s="8">
         <v>0</v>
@@ -19396,10 +19396,10 @@
       </c>
       <c r="M294" s="8">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N294" s="8">
-        <v>1652</v>
+        <v>1629</v>
       </c>
       <c r="O294" s="8"/>
       <c r="P294" s="8"/>
@@ -19638,7 +19638,7 @@
         <v>14</v>
       </c>
       <c r="I299" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J299" s="8">
         <v>0</v>
@@ -19651,7 +19651,7 @@
       </c>
       <c r="M299" s="8">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N299" s="8">
         <v>0</v>
@@ -19689,13 +19689,13 @@
         <v>13</v>
       </c>
       <c r="I300" s="8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J300" s="8">
         <v>0</v>
       </c>
       <c r="K300" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L300" s="8">
         <v>0</v>
@@ -19756,7 +19756,7 @@
         <v>6</v>
       </c>
       <c r="N301" s="8">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="O301" s="8"/>
       <c r="P301" s="8"/>
@@ -19807,7 +19807,7 @@
         <v>6</v>
       </c>
       <c r="N302" s="8">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="O302" s="8"/>
       <c r="P302" s="8"/>
@@ -19858,7 +19858,7 @@
         <v>3</v>
       </c>
       <c r="N303" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O303" s="8"/>
       <c r="P303" s="8"/>
@@ -19909,7 +19909,7 @@
         <v>4</v>
       </c>
       <c r="N304" s="8">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="O304" s="8"/>
       <c r="P304" s="8"/>
@@ -19960,7 +19960,7 @@
         <v>8</v>
       </c>
       <c r="N305" s="8">
-        <v>561</v>
+        <v>551</v>
       </c>
       <c r="O305" s="8"/>
       <c r="P305" s="8"/>
@@ -20011,7 +20011,7 @@
         <v>10</v>
       </c>
       <c r="N306" s="8">
-        <v>1210</v>
+        <v>1180</v>
       </c>
       <c r="O306" s="8"/>
       <c r="P306" s="8"/>
@@ -20062,7 +20062,7 @@
         <v>11</v>
       </c>
       <c r="N307" s="8">
-        <v>1087</v>
+        <v>1077</v>
       </c>
       <c r="O307" s="8"/>
       <c r="P307" s="8"/>
@@ -20113,7 +20113,7 @@
         <v>11</v>
       </c>
       <c r="N308" s="8">
-        <v>832</v>
+        <v>795</v>
       </c>
       <c r="O308" s="8"/>
       <c r="P308" s="8"/>
@@ -20215,7 +20215,7 @@
         <v>4</v>
       </c>
       <c r="N310" s="8">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="O310" s="8"/>
       <c r="P310" s="8"/>
@@ -20317,7 +20317,7 @@
         <v>6</v>
       </c>
       <c r="N312" s="8">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="O312" s="8"/>
       <c r="P312" s="8"/>
@@ -20403,23 +20403,23 @@
         <v>12</v>
       </c>
       <c r="I314" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J314" s="8">
         <v>0</v>
       </c>
       <c r="K314" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L314" s="8">
         <v>0</v>
       </c>
       <c r="M314" s="8">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N314" s="8">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="O314" s="8"/>
       <c r="P314" s="8"/>
@@ -20470,7 +20470,7 @@
         <v>8</v>
       </c>
       <c r="N315" s="8">
-        <v>365</v>
+        <v>345</v>
       </c>
       <c r="O315" s="8"/>
       <c r="P315" s="8"/>
@@ -20505,23 +20505,23 @@
         <v>12</v>
       </c>
       <c r="I316" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J316" s="8">
         <v>0</v>
       </c>
       <c r="K316" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L316" s="8">
         <v>0</v>
       </c>
       <c r="M316" s="8">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N316" s="8">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="O316" s="8"/>
       <c r="P316" s="8"/>
@@ -20556,23 +20556,23 @@
         <v>12</v>
       </c>
       <c r="I317" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J317" s="8">
         <v>0</v>
       </c>
       <c r="K317" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L317" s="8">
         <v>0</v>
       </c>
       <c r="M317" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N317" s="8">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="O317" s="8"/>
       <c r="P317" s="8"/>
@@ -20613,17 +20613,17 @@
         <v>0</v>
       </c>
       <c r="K318" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L318" s="8">
         <v>0</v>
       </c>
       <c r="M318" s="8">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N318" s="8">
-        <v>951</v>
+        <v>1219</v>
       </c>
       <c r="O318" s="8"/>
       <c r="P318" s="8"/>
@@ -20674,7 +20674,7 @@
         <v>4</v>
       </c>
       <c r="N319" s="8">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="O319" s="8"/>
       <c r="P319" s="8"/>
@@ -20725,7 +20725,7 @@
         <v>4</v>
       </c>
       <c r="N320" s="8">
-        <v>655</v>
+        <v>696</v>
       </c>
       <c r="O320" s="8"/>
       <c r="P320" s="8"/>
@@ -20776,7 +20776,7 @@
         <v>2</v>
       </c>
       <c r="N321" s="8">
-        <v>596</v>
+        <v>575</v>
       </c>
       <c r="O321" s="8"/>
       <c r="P321" s="8"/>
@@ -20827,7 +20827,7 @@
         <v>3</v>
       </c>
       <c r="N322" s="8">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="O322" s="8"/>
       <c r="P322" s="8"/>
@@ -20862,7 +20862,7 @@
         <v>14</v>
       </c>
       <c r="I323" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J323" s="8">
         <v>0</v>
@@ -20875,10 +20875,10 @@
       </c>
       <c r="M323" s="8">
         <f t="shared" ref="M323:M386" si="5">I323+J323+K323+L323</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N323" s="8">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="O323" s="8"/>
       <c r="P323" s="8"/>
@@ -20970,17 +20970,17 @@
         <v>0</v>
       </c>
       <c r="K325" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L325" s="8">
         <v>0</v>
       </c>
       <c r="M325" s="8">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N325" s="8">
-        <v>355</v>
+        <v>339</v>
       </c>
       <c r="O325" s="8"/>
       <c r="P325" s="8"/>
@@ -21031,7 +21031,7 @@
         <v>3</v>
       </c>
       <c r="N326" s="8">
-        <v>815</v>
+        <v>1006</v>
       </c>
       <c r="O326" s="8"/>
       <c r="P326" s="8"/>
@@ -21123,17 +21123,17 @@
         <v>0</v>
       </c>
       <c r="K328" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L328" s="8">
         <v>0</v>
       </c>
       <c r="M328" s="8">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N328" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O328" s="8"/>
       <c r="P328" s="8"/>
@@ -21184,7 +21184,7 @@
         <v>4</v>
       </c>
       <c r="N329" s="8">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="O329" s="8"/>
       <c r="P329" s="8"/>
@@ -21270,7 +21270,7 @@
         <v>13</v>
       </c>
       <c r="I331" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J331" s="8">
         <v>0</v>
@@ -21283,7 +21283,7 @@
       </c>
       <c r="M331" s="8">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N331" s="8">
         <v>0</v>
@@ -21525,7 +21525,7 @@
         <v>13</v>
       </c>
       <c r="I336" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J336" s="8">
         <v>0</v>
@@ -21538,10 +21538,10 @@
       </c>
       <c r="M336" s="8">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N336" s="8">
-        <v>691</v>
+        <v>680</v>
       </c>
       <c r="O336" s="8"/>
       <c r="P336" s="8"/>
@@ -21576,23 +21576,23 @@
         <v>12</v>
       </c>
       <c r="I337" s="8">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J337" s="8">
         <v>0</v>
       </c>
       <c r="K337" s="8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L337" s="8">
         <v>0</v>
       </c>
       <c r="M337" s="8">
         <f t="shared" si="5"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N337" s="8">
-        <v>1052</v>
+        <v>1227</v>
       </c>
       <c r="O337" s="8"/>
       <c r="P337" s="8"/>
@@ -21627,7 +21627,7 @@
         <v>12</v>
       </c>
       <c r="I338" s="8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J338" s="8">
         <v>0</v>
@@ -21640,10 +21640,10 @@
       </c>
       <c r="M338" s="8">
         <f t="shared" si="5"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N338" s="8">
-        <v>1209</v>
+        <v>1479</v>
       </c>
       <c r="O338" s="8"/>
       <c r="P338" s="8"/>
@@ -21694,7 +21694,7 @@
         <v>3</v>
       </c>
       <c r="N339" s="8">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="O339" s="8"/>
       <c r="P339" s="8"/>
@@ -21729,23 +21729,23 @@
         <v>14</v>
       </c>
       <c r="I340" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J340" s="8">
         <v>0</v>
       </c>
       <c r="K340" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L340" s="8">
         <v>0</v>
       </c>
       <c r="M340" s="8">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N340" s="8">
-        <v>558</v>
+        <v>942</v>
       </c>
       <c r="O340" s="8"/>
       <c r="P340" s="8"/>
@@ -21796,7 +21796,7 @@
         <v>4</v>
       </c>
       <c r="N341" s="8">
-        <v>379</v>
+        <v>422</v>
       </c>
       <c r="O341" s="8"/>
       <c r="P341" s="8"/>
@@ -21847,7 +21847,7 @@
         <v>4</v>
       </c>
       <c r="N342" s="8">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="O342" s="8"/>
       <c r="P342" s="8"/>
@@ -21933,7 +21933,7 @@
         <v>12</v>
       </c>
       <c r="I344" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J344" s="8">
         <v>0</v>
@@ -21946,7 +21946,7 @@
       </c>
       <c r="M344" s="8">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N344" s="8">
         <v>0</v>
@@ -21984,7 +21984,7 @@
         <v>12</v>
       </c>
       <c r="I345" s="8">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J345" s="8">
         <v>0</v>
@@ -21997,7 +21997,7 @@
       </c>
       <c r="M345" s="8">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="N345" s="8">
         <v>0</v>
@@ -22035,7 +22035,7 @@
         <v>13</v>
       </c>
       <c r="I346" s="8">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="J346" s="8">
         <v>0</v>
@@ -22048,7 +22048,7 @@
       </c>
       <c r="M346" s="8">
         <f t="shared" si="5"/>
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="N346" s="8">
         <v>0</v>
@@ -22086,23 +22086,23 @@
         <v>13</v>
       </c>
       <c r="I347" s="8">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="J347" s="8">
         <v>0</v>
       </c>
       <c r="K347" s="8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L347" s="8">
         <v>0</v>
       </c>
       <c r="M347" s="8">
         <f t="shared" si="5"/>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N347" s="8">
-        <v>552</v>
+        <v>536</v>
       </c>
       <c r="O347" s="8"/>
       <c r="P347" s="9"/>
@@ -22357,7 +22357,7 @@
         <v>2</v>
       </c>
       <c r="N352" s="8">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="O352" s="8"/>
       <c r="P352" s="9"/>
@@ -22902,23 +22902,23 @@
         <v>12</v>
       </c>
       <c r="I363" s="8">
-        <v>316</v>
+        <v>475</v>
       </c>
       <c r="J363" s="8">
         <v>0</v>
       </c>
       <c r="K363" s="8">
-        <v>219</v>
+        <v>35</v>
       </c>
       <c r="L363" s="8">
         <v>0</v>
       </c>
       <c r="M363" s="8">
         <f t="shared" si="5"/>
-        <v>535</v>
+        <v>510</v>
       </c>
       <c r="N363" s="8">
-        <v>956</v>
+        <v>1417</v>
       </c>
       <c r="O363" s="8"/>
       <c r="P363" s="9"/>
@@ -23055,7 +23055,7 @@
         <v>14</v>
       </c>
       <c r="I366" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J366" s="8">
         <v>0</v>
@@ -23068,10 +23068,10 @@
       </c>
       <c r="M366" s="8">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N366" s="8">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="O366" s="8"/>
       <c r="P366" s="9"/>
@@ -23106,23 +23106,23 @@
         <v>12</v>
       </c>
       <c r="I367" s="8">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J367" s="8">
         <v>0</v>
       </c>
       <c r="K367" s="8">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="L367" s="8">
         <v>0</v>
       </c>
       <c r="M367" s="8">
         <f t="shared" si="5"/>
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="N367" s="8">
-        <v>259</v>
+        <v>426</v>
       </c>
       <c r="O367" s="8"/>
       <c r="P367" s="9"/>
@@ -23163,17 +23163,17 @@
         <v>0</v>
       </c>
       <c r="K368" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L368" s="8">
         <v>0</v>
       </c>
       <c r="M368" s="8">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N368" s="8">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="O368" s="8"/>
       <c r="P368" s="9"/>
@@ -23214,17 +23214,17 @@
         <v>0</v>
       </c>
       <c r="K369" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L369" s="8">
         <v>0</v>
       </c>
       <c r="M369" s="8">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N369" s="8">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="O369" s="8"/>
       <c r="P369" s="9"/>
@@ -23428,7 +23428,7 @@
         <v>5</v>
       </c>
       <c r="N373" s="8">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O373" s="8"/>
       <c r="P373" s="9"/>
@@ -23565,7 +23565,7 @@
         <v>12</v>
       </c>
       <c r="I376" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J376" s="8">
         <v>0</v>
@@ -23578,7 +23578,7 @@
       </c>
       <c r="M376" s="8">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N376" s="8">
         <v>0</v>
@@ -23922,7 +23922,7 @@
         <v>12</v>
       </c>
       <c r="I383" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J383" s="8">
         <v>0</v>
@@ -23935,7 +23935,7 @@
       </c>
       <c r="M383" s="8">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N383" s="8">
         <v>0</v>
@@ -23989,7 +23989,7 @@
         <v>5</v>
       </c>
       <c r="N384" s="8">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="O384" s="8"/>
       <c r="P384" s="9"/>
@@ -24024,20 +24024,20 @@
         <v>12</v>
       </c>
       <c r="I385" s="8">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="J385" s="8">
         <v>0</v>
       </c>
       <c r="K385" s="8">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="L385" s="8">
         <v>0</v>
       </c>
       <c r="M385" s="8">
         <f t="shared" si="5"/>
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="N385" s="8">
         <v>257</v>
@@ -24295,7 +24295,7 @@
         <v>5</v>
       </c>
       <c r="N390" s="8">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="O390" s="8"/>
       <c r="P390" s="7"/>
@@ -24432,7 +24432,7 @@
         <v>12</v>
       </c>
       <c r="I393" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J393" s="8">
         <v>0</v>
@@ -24445,7 +24445,7 @@
       </c>
       <c r="M393" s="8">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N393" s="8">
         <v>0</v>
@@ -24636,7 +24636,7 @@
         <v>14</v>
       </c>
       <c r="I397" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J397" s="8">
         <v>0</v>
@@ -24649,7 +24649,7 @@
       </c>
       <c r="M397" s="8">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N397" s="8">
         <v>0</v>
@@ -24687,13 +24687,13 @@
         <v>15</v>
       </c>
       <c r="I398" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J398" s="8">
         <v>0</v>
       </c>
       <c r="K398" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L398" s="8">
         <v>0</v>
@@ -24958,7 +24958,7 @@
         <v>0</v>
       </c>
       <c r="N403" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O403" s="7"/>
       <c r="P403" s="7"/>

--- a/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
+++ b/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\Fossil Replenishment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5996548-35F5-4253-9CD3-B99C8E981674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A47E66-92E8-4C61-9702-2E1A65FD8C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6662473D-6E1F-42FD-999B-28162E22D4B5}"/>
   </bookViews>
@@ -4491,23 +4491,23 @@
         <v>12</v>
       </c>
       <c r="I2" s="8">
-        <v>783</v>
+        <v>818</v>
       </c>
       <c r="J2" s="8">
         <v>0</v>
       </c>
       <c r="K2" s="8">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L2" s="8">
         <v>0</v>
       </c>
       <c r="M2" s="8">
         <f>I2+J2+K2+L2</f>
-        <v>833</v>
+        <v>866</v>
       </c>
       <c r="N2" s="8">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="O2" s="8"/>
       <c r="P2" s="8"/>
@@ -4593,7 +4593,7 @@
         <v>12</v>
       </c>
       <c r="I4" s="8">
-        <v>204</v>
+        <v>146</v>
       </c>
       <c r="J4" s="8">
         <v>0</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="M4" s="8">
         <f t="shared" si="0"/>
-        <v>204</v>
+        <v>146</v>
       </c>
       <c r="N4" s="8">
         <v>0</v>
@@ -4644,7 +4644,7 @@
         <v>12</v>
       </c>
       <c r="I5" s="8">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="J5" s="8">
         <v>0</v>
@@ -4657,7 +4657,7 @@
       </c>
       <c r="M5" s="8">
         <f t="shared" si="0"/>
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="N5" s="8">
         <v>0</v>
@@ -4695,23 +4695,23 @@
         <v>12</v>
       </c>
       <c r="I6" s="8">
-        <v>830</v>
+        <v>856</v>
       </c>
       <c r="J6" s="8">
         <v>0</v>
       </c>
       <c r="K6" s="8">
-        <v>47</v>
+        <v>120</v>
       </c>
       <c r="L6" s="8">
         <v>0</v>
       </c>
       <c r="M6" s="8">
         <f t="shared" si="0"/>
-        <v>877</v>
+        <v>976</v>
       </c>
       <c r="N6" s="8">
-        <v>1862</v>
+        <v>1742</v>
       </c>
       <c r="O6" s="8"/>
       <c r="P6" s="8"/>
@@ -4746,7 +4746,7 @@
         <v>12</v>
       </c>
       <c r="I7" s="8">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="J7" s="8">
         <v>0</v>
@@ -4759,10 +4759,10 @@
       </c>
       <c r="M7" s="8">
         <f t="shared" si="0"/>
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="N7" s="8">
-        <v>160</v>
+        <v>127</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
@@ -4797,7 +4797,7 @@
         <v>12</v>
       </c>
       <c r="I8" s="8">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J8" s="8">
         <v>0</v>
@@ -4810,10 +4810,10 @@
       </c>
       <c r="M8" s="8">
         <f t="shared" si="0"/>
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="N8" s="8">
-        <v>1083</v>
+        <v>1049</v>
       </c>
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
@@ -4848,7 +4848,7 @@
         <v>12</v>
       </c>
       <c r="I9" s="8">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J9" s="8">
         <v>0</v>
@@ -4861,10 +4861,10 @@
       </c>
       <c r="M9" s="8">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N9" s="8">
-        <v>477</v>
+        <v>438</v>
       </c>
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
@@ -4899,23 +4899,23 @@
         <v>12</v>
       </c>
       <c r="I10" s="8">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J10" s="8">
         <v>0</v>
       </c>
       <c r="K10" s="8">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L10" s="8">
         <v>0</v>
       </c>
       <c r="M10" s="8">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="N10" s="8">
-        <v>408</v>
+        <v>324</v>
       </c>
       <c r="O10" s="8"/>
       <c r="P10" s="8"/>
@@ -4950,23 +4950,23 @@
         <v>12</v>
       </c>
       <c r="I11" s="8">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="J11" s="8">
         <v>0</v>
       </c>
       <c r="K11" s="8">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="L11" s="8">
         <v>0</v>
       </c>
       <c r="M11" s="8">
         <f t="shared" si="0"/>
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="N11" s="8">
-        <v>308</v>
+        <v>255</v>
       </c>
       <c r="O11" s="8"/>
       <c r="P11" s="8"/>
@@ -5001,23 +5001,23 @@
         <v>12</v>
       </c>
       <c r="I12" s="8">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J12" s="8">
         <v>0</v>
       </c>
       <c r="K12" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L12" s="8">
         <v>0</v>
       </c>
       <c r="M12" s="8">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="N12" s="8">
-        <v>2284</v>
+        <v>0</v>
       </c>
       <c r="O12" s="8"/>
       <c r="P12" s="8"/>
@@ -5052,23 +5052,23 @@
         <v>12</v>
       </c>
       <c r="I13" s="8">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="J13" s="8">
         <v>0</v>
       </c>
       <c r="K13" s="8">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="L13" s="8">
         <v>0</v>
       </c>
       <c r="M13" s="8">
         <f t="shared" si="0"/>
-        <v>224</v>
+        <v>273</v>
       </c>
       <c r="N13" s="8">
-        <v>962</v>
+        <v>914</v>
       </c>
       <c r="O13" s="8"/>
       <c r="P13" s="8"/>
@@ -5103,7 +5103,7 @@
         <v>12</v>
       </c>
       <c r="I14" s="8">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="J14" s="8">
         <v>0</v>
@@ -5116,10 +5116,10 @@
       </c>
       <c r="M14" s="8">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="N14" s="8">
-        <v>1206</v>
+        <v>1201</v>
       </c>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
@@ -5154,7 +5154,7 @@
         <v>12</v>
       </c>
       <c r="I15" s="8">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="J15" s="8">
         <v>0</v>
@@ -5167,10 +5167,10 @@
       </c>
       <c r="M15" s="8">
         <f t="shared" si="0"/>
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="N15" s="8">
-        <v>66</v>
+        <v>432</v>
       </c>
       <c r="O15" s="8"/>
       <c r="P15" s="8"/>
@@ -5205,7 +5205,7 @@
         <v>12</v>
       </c>
       <c r="I16" s="8">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="J16" s="8">
         <v>0</v>
@@ -5218,10 +5218,10 @@
       </c>
       <c r="M16" s="8">
         <f t="shared" si="0"/>
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="N16" s="8">
-        <v>634</v>
+        <v>871</v>
       </c>
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
@@ -5256,7 +5256,7 @@
         <v>12</v>
       </c>
       <c r="I17" s="8">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J17" s="8">
         <v>0</v>
@@ -5269,10 +5269,10 @@
       </c>
       <c r="M17" s="8">
         <f t="shared" si="0"/>
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="N17" s="8">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="O17" s="8"/>
       <c r="P17" s="8"/>
@@ -5323,7 +5323,7 @@
         <v>30</v>
       </c>
       <c r="N18" s="8">
-        <v>432</v>
+        <v>407</v>
       </c>
       <c r="O18" s="8"/>
       <c r="P18" s="8"/>
@@ -5374,7 +5374,7 @@
         <v>17</v>
       </c>
       <c r="N19" s="8">
-        <v>920</v>
+        <v>1042</v>
       </c>
       <c r="O19" s="8"/>
       <c r="P19" s="8"/>
@@ -5425,7 +5425,7 @@
         <v>23</v>
       </c>
       <c r="N20" s="8">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="O20" s="8"/>
       <c r="P20" s="8"/>
@@ -5460,7 +5460,7 @@
         <v>13</v>
       </c>
       <c r="I21" s="8">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J21" s="8">
         <v>0</v>
@@ -5473,10 +5473,10 @@
       </c>
       <c r="M21" s="8">
         <f t="shared" si="0"/>
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="N21" s="8">
-        <v>0</v>
+        <v>489</v>
       </c>
       <c r="O21" s="8"/>
       <c r="P21" s="8"/>
@@ -5562,7 +5562,7 @@
         <v>12</v>
       </c>
       <c r="I23" s="8">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J23" s="8">
         <v>0</v>
@@ -5575,10 +5575,10 @@
       </c>
       <c r="M23" s="8">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N23" s="8">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="O23" s="8"/>
       <c r="P23" s="8"/>
@@ -5613,7 +5613,7 @@
         <v>14</v>
       </c>
       <c r="I24" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J24" s="8">
         <v>0</v>
@@ -5626,10 +5626,10 @@
       </c>
       <c r="M24" s="8">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N24" s="8">
-        <v>786</v>
+        <v>775</v>
       </c>
       <c r="O24" s="8"/>
       <c r="P24" s="8"/>
@@ -5715,23 +5715,23 @@
         <v>12</v>
       </c>
       <c r="I26" s="8">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J26" s="8">
         <v>0</v>
       </c>
       <c r="K26" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L26" s="8">
         <v>0</v>
       </c>
       <c r="M26" s="8">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N26" s="8">
-        <v>746</v>
+        <v>686</v>
       </c>
       <c r="O26" s="8"/>
       <c r="P26" s="8"/>
@@ -5766,7 +5766,7 @@
         <v>12</v>
       </c>
       <c r="I27" s="8">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J27" s="8">
         <v>0</v>
@@ -5779,10 +5779,10 @@
       </c>
       <c r="M27" s="8">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N27" s="8">
-        <v>863</v>
+        <v>853</v>
       </c>
       <c r="O27" s="8"/>
       <c r="P27" s="8"/>
@@ -5817,7 +5817,7 @@
         <v>12</v>
       </c>
       <c r="I28" s="8">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J28" s="8">
         <v>0</v>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="M28" s="8">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="N28" s="8">
         <v>0</v>
@@ -5868,23 +5868,23 @@
         <v>13</v>
       </c>
       <c r="I29" s="8">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J29" s="8">
         <v>0</v>
       </c>
       <c r="K29" s="8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L29" s="8">
         <v>0</v>
       </c>
       <c r="M29" s="8">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="N29" s="8">
-        <v>503</v>
+        <v>0</v>
       </c>
       <c r="O29" s="8"/>
       <c r="P29" s="8"/>
@@ -5919,13 +5919,13 @@
         <v>14</v>
       </c>
       <c r="I30" s="8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J30" s="8">
         <v>0</v>
       </c>
       <c r="K30" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L30" s="8">
         <v>0</v>
@@ -5935,7 +5935,7 @@
         <v>10</v>
       </c>
       <c r="N30" s="8">
-        <v>1079</v>
+        <v>1073</v>
       </c>
       <c r="O30" s="8"/>
       <c r="P30" s="8"/>
@@ -5970,7 +5970,7 @@
         <v>13</v>
       </c>
       <c r="I31" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" s="8">
         <v>0</v>
@@ -5983,7 +5983,7 @@
       </c>
       <c r="M31" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N31" s="8">
         <v>0</v>
@@ -6021,23 +6021,23 @@
         <v>12</v>
       </c>
       <c r="I32" s="8">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J32" s="8">
         <v>0</v>
       </c>
       <c r="K32" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L32" s="8">
         <v>0</v>
       </c>
       <c r="M32" s="8">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="N32" s="8">
-        <v>793</v>
+        <v>762</v>
       </c>
       <c r="O32" s="8"/>
       <c r="P32" s="8"/>
@@ -6072,7 +6072,7 @@
         <v>12</v>
       </c>
       <c r="I33" s="8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J33" s="8">
         <v>0</v>
@@ -6085,10 +6085,10 @@
       </c>
       <c r="M33" s="8">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N33" s="8">
-        <v>1159</v>
+        <v>1153</v>
       </c>
       <c r="O33" s="8"/>
       <c r="P33" s="8"/>
@@ -6139,7 +6139,7 @@
         <v>22</v>
       </c>
       <c r="N34" s="8">
-        <v>1067</v>
+        <v>1054</v>
       </c>
       <c r="O34" s="8"/>
       <c r="P34" s="8"/>
@@ -6174,7 +6174,7 @@
         <v>12</v>
       </c>
       <c r="I35" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J35" s="8">
         <v>0</v>
@@ -6187,10 +6187,10 @@
       </c>
       <c r="M35" s="8">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N35" s="8">
-        <v>347</v>
+        <v>497</v>
       </c>
       <c r="O35" s="8"/>
       <c r="P35" s="8"/>
@@ -6241,7 +6241,7 @@
         <v>12</v>
       </c>
       <c r="N36" s="8">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="O36" s="8"/>
       <c r="P36" s="8"/>
@@ -6276,7 +6276,7 @@
         <v>13</v>
       </c>
       <c r="I37" s="8">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J37" s="8">
         <v>0</v>
@@ -6289,10 +6289,10 @@
       </c>
       <c r="M37" s="8">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N37" s="8">
-        <v>893</v>
+        <v>938</v>
       </c>
       <c r="O37" s="8"/>
       <c r="P37" s="8"/>
@@ -6327,7 +6327,7 @@
         <v>12</v>
       </c>
       <c r="I38" s="8">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J38" s="8">
         <v>0</v>
@@ -6340,10 +6340,10 @@
       </c>
       <c r="M38" s="8">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N38" s="8">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="O38" s="8"/>
       <c r="P38" s="8"/>
@@ -6394,7 +6394,7 @@
         <v>30</v>
       </c>
       <c r="N39" s="8">
-        <v>1540</v>
+        <v>1489</v>
       </c>
       <c r="O39" s="8"/>
       <c r="P39" s="8"/>
@@ -6429,23 +6429,23 @@
         <v>12</v>
       </c>
       <c r="I40" s="8">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J40" s="8">
         <v>0</v>
       </c>
       <c r="K40" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L40" s="8">
         <v>0</v>
       </c>
       <c r="M40" s="8">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N40" s="8">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="O40" s="8"/>
       <c r="P40" s="8"/>
@@ -6480,7 +6480,7 @@
         <v>12</v>
       </c>
       <c r="I41" s="8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J41" s="8">
         <v>0</v>
@@ -6493,10 +6493,10 @@
       </c>
       <c r="M41" s="8">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N41" s="8">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="O41" s="8"/>
       <c r="P41" s="8"/>
@@ -6531,7 +6531,7 @@
         <v>13</v>
       </c>
       <c r="I42" s="8">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J42" s="8">
         <v>0</v>
@@ -6544,10 +6544,10 @@
       </c>
       <c r="M42" s="8">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="N42" s="8">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="O42" s="8"/>
       <c r="P42" s="8"/>
@@ -6582,23 +6582,23 @@
         <v>12</v>
       </c>
       <c r="I43" s="8">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J43" s="8">
         <v>0</v>
       </c>
       <c r="K43" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L43" s="8">
         <v>0</v>
       </c>
       <c r="M43" s="8">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N43" s="8">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="O43" s="8"/>
       <c r="P43" s="8"/>
@@ -6633,23 +6633,23 @@
         <v>12</v>
       </c>
       <c r="I44" s="8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J44" s="8">
         <v>0</v>
       </c>
       <c r="K44" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L44" s="8">
         <v>0</v>
       </c>
       <c r="M44" s="8">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N44" s="8">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="O44" s="8"/>
       <c r="P44" s="8"/>
@@ -6700,7 +6700,7 @@
         <v>13</v>
       </c>
       <c r="N45" s="8">
-        <v>870</v>
+        <v>862</v>
       </c>
       <c r="O45" s="8"/>
       <c r="P45" s="8"/>
@@ -6735,7 +6735,7 @@
         <v>12</v>
       </c>
       <c r="I46" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J46" s="8">
         <v>0</v>
@@ -6748,10 +6748,10 @@
       </c>
       <c r="M46" s="8">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N46" s="8">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="O46" s="8"/>
       <c r="P46" s="8"/>
@@ -6786,7 +6786,7 @@
         <v>13</v>
       </c>
       <c r="I47" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J47" s="8">
         <v>0</v>
@@ -6799,10 +6799,10 @@
       </c>
       <c r="M47" s="8">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N47" s="8">
-        <v>1068</v>
+        <v>1060</v>
       </c>
       <c r="O47" s="8"/>
       <c r="P47" s="8"/>
@@ -6837,7 +6837,7 @@
         <v>12</v>
       </c>
       <c r="I48" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J48" s="8">
         <v>0</v>
@@ -6850,10 +6850,10 @@
       </c>
       <c r="M48" s="8">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N48" s="8">
-        <v>1066</v>
+        <v>1309</v>
       </c>
       <c r="O48" s="8"/>
       <c r="P48" s="8"/>
@@ -6888,7 +6888,7 @@
         <v>12</v>
       </c>
       <c r="I49" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J49" s="8">
         <v>0</v>
@@ -6901,10 +6901,10 @@
       </c>
       <c r="M49" s="8">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N49" s="8">
-        <v>983</v>
+        <v>978</v>
       </c>
       <c r="O49" s="8"/>
       <c r="P49" s="8"/>
@@ -6939,7 +6939,7 @@
         <v>15</v>
       </c>
       <c r="I50" s="8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J50" s="8">
         <v>0</v>
@@ -6952,10 +6952,10 @@
       </c>
       <c r="M50" s="8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N50" s="8">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="O50" s="8"/>
       <c r="P50" s="8"/>
@@ -7006,7 +7006,7 @@
         <v>24</v>
       </c>
       <c r="N51" s="8">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="O51" s="8"/>
       <c r="P51" s="8"/>
@@ -7041,13 +7041,13 @@
         <v>12</v>
       </c>
       <c r="I52" s="8">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="J52" s="8">
         <v>0</v>
       </c>
       <c r="K52" s="8">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L52" s="8">
         <v>0</v>
@@ -7057,7 +7057,7 @@
         <v>86</v>
       </c>
       <c r="N52" s="8">
-        <v>1789</v>
+        <v>0</v>
       </c>
       <c r="O52" s="8"/>
       <c r="P52" s="8"/>
@@ -7108,7 +7108,7 @@
         <v>9</v>
       </c>
       <c r="N53" s="8">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="O53" s="8"/>
       <c r="P53" s="8"/>
@@ -7143,7 +7143,7 @@
         <v>12</v>
       </c>
       <c r="I54" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J54" s="8">
         <v>0</v>
@@ -7156,10 +7156,10 @@
       </c>
       <c r="M54" s="8">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N54" s="8">
-        <v>396</v>
+        <v>361</v>
       </c>
       <c r="O54" s="8"/>
       <c r="P54" s="8"/>
@@ -7194,7 +7194,7 @@
         <v>12</v>
       </c>
       <c r="I55" s="8">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="J55" s="8">
         <v>0</v>
@@ -7207,10 +7207,10 @@
       </c>
       <c r="M55" s="8">
         <f t="shared" si="0"/>
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="N55" s="8">
-        <v>238</v>
+        <v>205</v>
       </c>
       <c r="O55" s="8"/>
       <c r="P55" s="8"/>
@@ -7261,7 +7261,7 @@
         <v>6</v>
       </c>
       <c r="N56" s="8">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="O56" s="8"/>
       <c r="P56" s="8"/>
@@ -7296,7 +7296,7 @@
         <v>12</v>
       </c>
       <c r="I57" s="8">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J57" s="8">
         <v>0</v>
@@ -7309,10 +7309,10 @@
       </c>
       <c r="M57" s="8">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="N57" s="8">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="O57" s="8"/>
       <c r="P57" s="8"/>
@@ -7363,7 +7363,7 @@
         <v>4</v>
       </c>
       <c r="N58" s="8">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="O58" s="8"/>
       <c r="P58" s="8"/>
@@ -7414,7 +7414,7 @@
         <v>7</v>
       </c>
       <c r="N59" s="8">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="O59" s="8"/>
       <c r="P59" s="8"/>
@@ -7465,7 +7465,7 @@
         <v>5</v>
       </c>
       <c r="N60" s="8">
-        <v>699</v>
+        <v>684</v>
       </c>
       <c r="O60" s="8"/>
       <c r="P60" s="8"/>
@@ -7500,7 +7500,7 @@
         <v>12</v>
       </c>
       <c r="I61" s="8">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J61" s="8">
         <v>0</v>
@@ -7513,10 +7513,10 @@
       </c>
       <c r="M61" s="8">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N61" s="8">
-        <v>542</v>
+        <v>505</v>
       </c>
       <c r="O61" s="8"/>
       <c r="P61" s="8"/>
@@ -7567,7 +7567,7 @@
         <v>8</v>
       </c>
       <c r="N62" s="8">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="O62" s="8"/>
       <c r="P62" s="8"/>
@@ -7618,7 +7618,7 @@
         <v>4</v>
       </c>
       <c r="N63" s="8">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="O63" s="8"/>
       <c r="P63" s="8"/>
@@ -7653,7 +7653,7 @@
         <v>13</v>
       </c>
       <c r="I64" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J64" s="8">
         <v>0</v>
@@ -7666,10 +7666,10 @@
       </c>
       <c r="M64" s="8">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N64" s="8">
-        <v>106</v>
+        <v>585</v>
       </c>
       <c r="O64" s="8"/>
       <c r="P64" s="8"/>
@@ -7720,7 +7720,7 @@
         <v>6</v>
       </c>
       <c r="N65" s="8">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="O65" s="8"/>
       <c r="P65" s="8"/>
@@ -7806,7 +7806,7 @@
         <v>12</v>
       </c>
       <c r="I67" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J67" s="8">
         <v>0</v>
@@ -7819,10 +7819,10 @@
       </c>
       <c r="M67" s="8">
         <f t="shared" ref="M67:M130" si="1">I67+J67+K67+L67</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N67" s="8">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="O67" s="8"/>
       <c r="P67" s="8"/>
@@ -7857,13 +7857,13 @@
         <v>12</v>
       </c>
       <c r="I68" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J68" s="8">
         <v>0</v>
       </c>
       <c r="K68" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L68" s="8">
         <v>0</v>
@@ -7873,7 +7873,7 @@
         <v>5</v>
       </c>
       <c r="N68" s="8">
-        <v>971</v>
+        <v>959</v>
       </c>
       <c r="O68" s="8"/>
       <c r="P68" s="8"/>
@@ -7908,7 +7908,7 @@
         <v>12</v>
       </c>
       <c r="I69" s="8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J69" s="8">
         <v>0</v>
@@ -7921,10 +7921,10 @@
       </c>
       <c r="M69" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N69" s="8">
-        <v>261</v>
+        <v>291</v>
       </c>
       <c r="O69" s="8"/>
       <c r="P69" s="8"/>
@@ -7959,7 +7959,7 @@
         <v>16</v>
       </c>
       <c r="I70" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J70" s="8">
         <v>0</v>
@@ -7972,10 +7972,10 @@
       </c>
       <c r="M70" s="8">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N70" s="8">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="O70" s="8"/>
       <c r="P70" s="8"/>
@@ -8061,7 +8061,7 @@
         <v>12</v>
       </c>
       <c r="I72" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J72" s="8">
         <v>0</v>
@@ -8074,10 +8074,10 @@
       </c>
       <c r="M72" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N72" s="8">
-        <v>396</v>
+        <v>633</v>
       </c>
       <c r="O72" s="8"/>
       <c r="P72" s="8"/>
@@ -8112,23 +8112,23 @@
         <v>12</v>
       </c>
       <c r="I73" s="8">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="J73" s="8">
         <v>0</v>
       </c>
       <c r="K73" s="8">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="L73" s="8">
         <v>0</v>
       </c>
       <c r="M73" s="8">
         <f t="shared" si="1"/>
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N73" s="8">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="O73" s="8"/>
       <c r="P73" s="8"/>
@@ -8163,23 +8163,23 @@
         <v>14</v>
       </c>
       <c r="I74" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J74" s="8">
         <v>0</v>
       </c>
       <c r="K74" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L74" s="8">
         <v>0</v>
       </c>
       <c r="M74" s="8">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N74" s="8">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="O74" s="8"/>
       <c r="P74" s="8"/>
@@ -8214,7 +8214,7 @@
         <v>13</v>
       </c>
       <c r="I75" s="8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J75" s="8">
         <v>0</v>
@@ -8227,7 +8227,7 @@
       </c>
       <c r="M75" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N75" s="8">
         <v>34</v>
@@ -8265,7 +8265,7 @@
         <v>13</v>
       </c>
       <c r="I76" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J76" s="8">
         <v>0</v>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="M76" s="8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N76" s="8">
         <v>949</v>
@@ -8332,7 +8332,7 @@
         <v>5</v>
       </c>
       <c r="N77" s="8">
-        <v>390</v>
+        <v>886</v>
       </c>
       <c r="O77" s="8"/>
       <c r="P77" s="8"/>
@@ -8373,17 +8373,17 @@
         <v>0</v>
       </c>
       <c r="K78" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L78" s="8">
         <v>0</v>
       </c>
       <c r="M78" s="8">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N78" s="8">
-        <v>639</v>
+        <v>621</v>
       </c>
       <c r="O78" s="8"/>
       <c r="P78" s="8"/>
@@ -8434,7 +8434,7 @@
         <v>6</v>
       </c>
       <c r="N79" s="8">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="O79" s="8"/>
       <c r="P79" s="8"/>
@@ -8587,7 +8587,7 @@
         <v>5</v>
       </c>
       <c r="N82" s="8">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="O82" s="8"/>
       <c r="P82" s="8"/>
@@ -8638,7 +8638,7 @@
         <v>4</v>
       </c>
       <c r="N83" s="8">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="O83" s="8"/>
       <c r="P83" s="8"/>
@@ -8740,7 +8740,7 @@
         <v>5</v>
       </c>
       <c r="N85" s="8">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="O85" s="8"/>
       <c r="P85" s="8"/>
@@ -8775,7 +8775,7 @@
         <v>12</v>
       </c>
       <c r="I86" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J86" s="8">
         <v>0</v>
@@ -8788,10 +8788,10 @@
       </c>
       <c r="M86" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N86" s="8">
-        <v>634</v>
+        <v>604</v>
       </c>
       <c r="O86" s="8"/>
       <c r="P86" s="8"/>
@@ -8826,7 +8826,7 @@
         <v>13</v>
       </c>
       <c r="I87" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J87" s="8">
         <v>0</v>
@@ -8839,10 +8839,10 @@
       </c>
       <c r="M87" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N87" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O87" s="8"/>
       <c r="P87" s="8"/>
@@ -8877,7 +8877,7 @@
         <v>12</v>
       </c>
       <c r="I88" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J88" s="8">
         <v>0</v>
@@ -8890,10 +8890,10 @@
       </c>
       <c r="M88" s="8">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N88" s="8">
-        <v>109</v>
+        <v>592</v>
       </c>
       <c r="O88" s="8"/>
       <c r="P88" s="8"/>
@@ -8928,7 +8928,7 @@
         <v>12</v>
       </c>
       <c r="I89" s="8">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J89" s="8">
         <v>0</v>
@@ -8941,10 +8941,10 @@
       </c>
       <c r="M89" s="8">
         <f t="shared" si="1"/>
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N89" s="8">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="O89" s="8"/>
       <c r="P89" s="8"/>
@@ -9036,17 +9036,17 @@
         <v>0</v>
       </c>
       <c r="K91" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="8">
         <v>0</v>
       </c>
       <c r="M91" s="8">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N91" s="8">
-        <v>1237</v>
+        <v>1222</v>
       </c>
       <c r="O91" s="8"/>
       <c r="P91" s="8"/>
@@ -9081,7 +9081,7 @@
         <v>12</v>
       </c>
       <c r="I92" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J92" s="8">
         <v>0</v>
@@ -9094,10 +9094,10 @@
       </c>
       <c r="M92" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N92" s="8">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="O92" s="8"/>
       <c r="P92" s="8"/>
@@ -9132,23 +9132,23 @@
         <v>13</v>
       </c>
       <c r="I93" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J93" s="8">
         <v>0</v>
       </c>
       <c r="K93" s="8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L93" s="8">
         <v>0</v>
       </c>
       <c r="M93" s="8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="N93" s="8">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="O93" s="8"/>
       <c r="P93" s="8"/>
@@ -9234,7 +9234,7 @@
         <v>12</v>
       </c>
       <c r="I95" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J95" s="8">
         <v>0</v>
@@ -9247,10 +9247,10 @@
       </c>
       <c r="M95" s="8">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N95" s="8">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="O95" s="8"/>
       <c r="P95" s="8"/>
@@ -9301,7 +9301,7 @@
         <v>7</v>
       </c>
       <c r="N96" s="8">
-        <v>191</v>
+        <v>270</v>
       </c>
       <c r="O96" s="8"/>
       <c r="P96" s="8"/>
@@ -9336,7 +9336,7 @@
         <v>14</v>
       </c>
       <c r="I97" s="8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J97" s="8">
         <v>0</v>
@@ -9349,10 +9349,10 @@
       </c>
       <c r="M97" s="8">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N97" s="8">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="O97" s="8"/>
       <c r="P97" s="8"/>
@@ -9489,7 +9489,7 @@
         <v>15</v>
       </c>
       <c r="I100" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J100" s="8">
         <v>0</v>
@@ -9502,7 +9502,7 @@
       </c>
       <c r="M100" s="8">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N100" s="8">
         <v>0</v>
@@ -9540,7 +9540,7 @@
         <v>15</v>
       </c>
       <c r="I101" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J101" s="8">
         <v>0</v>
@@ -9553,10 +9553,10 @@
       </c>
       <c r="M101" s="8">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N101" s="8">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="O101" s="8"/>
       <c r="P101" s="8"/>
@@ -9591,23 +9591,23 @@
         <v>14</v>
       </c>
       <c r="I102" s="8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J102" s="8">
         <v>0</v>
       </c>
       <c r="K102" s="8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L102" s="8">
         <v>0</v>
       </c>
       <c r="M102" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N102" s="8">
-        <v>502</v>
+        <v>517</v>
       </c>
       <c r="O102" s="8"/>
       <c r="P102" s="8"/>
@@ -9642,13 +9642,13 @@
         <v>15</v>
       </c>
       <c r="I103" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J103" s="8">
         <v>0</v>
       </c>
       <c r="K103" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" s="8">
         <v>0</v>
@@ -9658,7 +9658,7 @@
         <v>2</v>
       </c>
       <c r="N103" s="8">
-        <v>554</v>
+        <v>539</v>
       </c>
       <c r="O103" s="8"/>
       <c r="P103" s="8"/>
@@ -9760,7 +9760,7 @@
         <v>8</v>
       </c>
       <c r="N105" s="8">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="O105" s="8"/>
       <c r="P105" s="8"/>
@@ -9811,7 +9811,7 @@
         <v>4</v>
       </c>
       <c r="N106" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O106" s="8"/>
       <c r="P106" s="8"/>
@@ -9897,7 +9897,7 @@
         <v>15</v>
       </c>
       <c r="I108" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J108" s="8">
         <v>0</v>
@@ -9910,7 +9910,7 @@
       </c>
       <c r="M108" s="8">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N108" s="8">
         <v>0</v>
@@ -9948,7 +9948,7 @@
         <v>13</v>
       </c>
       <c r="I109" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J109" s="8">
         <v>0</v>
@@ -9961,7 +9961,7 @@
       </c>
       <c r="M109" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N109" s="8">
         <v>32</v>
@@ -10101,23 +10101,23 @@
         <v>12</v>
       </c>
       <c r="I112" s="8">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="J112" s="8">
         <v>0</v>
       </c>
       <c r="K112" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L112" s="8">
         <v>0</v>
       </c>
       <c r="M112" s="8">
         <f t="shared" si="1"/>
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="N112" s="8">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="O112" s="8"/>
       <c r="P112" s="8"/>
@@ -10152,7 +10152,7 @@
         <v>12</v>
       </c>
       <c r="I113" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J113" s="8">
         <v>0</v>
@@ -10165,10 +10165,10 @@
       </c>
       <c r="M113" s="8">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N113" s="8">
-        <v>1171</v>
+        <v>1151</v>
       </c>
       <c r="O113" s="8"/>
       <c r="P113" s="8"/>
@@ -10203,13 +10203,13 @@
         <v>13</v>
       </c>
       <c r="I114" s="8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J114" s="8">
         <v>0</v>
       </c>
       <c r="K114" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L114" s="8">
         <v>0</v>
@@ -10219,7 +10219,7 @@
         <v>9</v>
       </c>
       <c r="N114" s="8">
-        <v>547</v>
+        <v>605</v>
       </c>
       <c r="O114" s="8"/>
       <c r="P114" s="8"/>
@@ -10270,7 +10270,7 @@
         <v>10</v>
       </c>
       <c r="N115" s="8">
-        <v>325</v>
+        <v>616</v>
       </c>
       <c r="O115" s="8"/>
       <c r="P115" s="8"/>
@@ -10321,7 +10321,7 @@
         <v>6</v>
       </c>
       <c r="N116" s="8">
-        <v>830</v>
+        <v>825</v>
       </c>
       <c r="O116" s="8"/>
       <c r="P116" s="8"/>
@@ -10356,7 +10356,7 @@
         <v>12</v>
       </c>
       <c r="I117" s="8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J117" s="8">
         <v>0</v>
@@ -10369,10 +10369,10 @@
       </c>
       <c r="M117" s="8">
         <f t="shared" si="1"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N117" s="8">
-        <v>483</v>
+        <v>458</v>
       </c>
       <c r="O117" s="8"/>
       <c r="P117" s="8"/>
@@ -10407,13 +10407,13 @@
         <v>13</v>
       </c>
       <c r="I118" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J118" s="8">
         <v>0</v>
       </c>
       <c r="K118" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L118" s="8">
         <v>0</v>
@@ -10423,7 +10423,7 @@
         <v>7</v>
       </c>
       <c r="N118" s="8">
-        <v>164</v>
+        <v>203</v>
       </c>
       <c r="O118" s="8"/>
       <c r="P118" s="8"/>
@@ -10474,7 +10474,7 @@
         <v>8</v>
       </c>
       <c r="N119" s="8">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="O119" s="8"/>
       <c r="P119" s="8"/>
@@ -10525,7 +10525,7 @@
         <v>12</v>
       </c>
       <c r="N120" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O120" s="8"/>
       <c r="P120" s="8"/>
@@ -10611,13 +10611,13 @@
         <v>13</v>
       </c>
       <c r="I122" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J122" s="8">
         <v>0</v>
       </c>
       <c r="K122" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L122" s="8">
         <v>0</v>
@@ -10627,7 +10627,7 @@
         <v>2</v>
       </c>
       <c r="N122" s="8">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="O122" s="8"/>
       <c r="P122" s="8"/>
@@ -10780,7 +10780,7 @@
         <v>7</v>
       </c>
       <c r="N125" s="8">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="O125" s="8"/>
       <c r="P125" s="8"/>
@@ -10933,7 +10933,7 @@
         <v>4</v>
       </c>
       <c r="N128" s="8">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="O128" s="8"/>
       <c r="P128" s="8"/>
@@ -11019,13 +11019,13 @@
         <v>12</v>
       </c>
       <c r="I130" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J130" s="8">
         <v>0</v>
       </c>
       <c r="K130" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L130" s="8">
         <v>0</v>
@@ -11035,7 +11035,7 @@
         <v>8</v>
       </c>
       <c r="N130" s="8">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="O130" s="8"/>
       <c r="P130" s="8"/>
@@ -11070,7 +11070,7 @@
         <v>14</v>
       </c>
       <c r="I131" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J131" s="8">
         <v>0</v>
@@ -11083,10 +11083,10 @@
       </c>
       <c r="M131" s="8">
         <f t="shared" ref="M131:M194" si="2">I131+J131+K131+L131</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N131" s="8">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="O131" s="8"/>
       <c r="P131" s="8"/>
@@ -11137,7 +11137,7 @@
         <v>5</v>
       </c>
       <c r="N132" s="8">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="O132" s="8"/>
       <c r="P132" s="8"/>
@@ -11172,23 +11172,23 @@
         <v>12</v>
       </c>
       <c r="I133" s="8">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J133" s="8">
         <v>0</v>
       </c>
       <c r="K133" s="8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L133" s="8">
         <v>0</v>
       </c>
       <c r="M133" s="8">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N133" s="8">
-        <v>401</v>
+        <v>359</v>
       </c>
       <c r="O133" s="8"/>
       <c r="P133" s="8"/>
@@ -11274,13 +11274,13 @@
         <v>15</v>
       </c>
       <c r="I135" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J135" s="8">
         <v>0</v>
       </c>
       <c r="K135" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L135" s="8">
         <v>0</v>
@@ -11290,7 +11290,7 @@
         <v>3</v>
       </c>
       <c r="N135" s="8">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="O135" s="8"/>
       <c r="P135" s="8"/>
@@ -11325,23 +11325,23 @@
         <v>14</v>
       </c>
       <c r="I136" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J136" s="8">
         <v>0</v>
       </c>
       <c r="K136" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L136" s="8">
         <v>0</v>
       </c>
       <c r="M136" s="8">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N136" s="8">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="O136" s="8"/>
       <c r="P136" s="8"/>
@@ -11427,7 +11427,7 @@
         <v>12</v>
       </c>
       <c r="I138" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J138" s="8">
         <v>0</v>
@@ -11440,7 +11440,7 @@
       </c>
       <c r="M138" s="8">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N138" s="8">
         <v>1055</v>
@@ -11580,7 +11580,7 @@
         <v>13</v>
       </c>
       <c r="I141" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J141" s="8">
         <v>0</v>
@@ -11593,7 +11593,7 @@
       </c>
       <c r="M141" s="8">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N141" s="8">
         <v>556</v>
@@ -11800,7 +11800,7 @@
         <v>4</v>
       </c>
       <c r="N145" s="8">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="O145" s="8"/>
       <c r="P145" s="8"/>
@@ -11902,7 +11902,7 @@
         <v>3</v>
       </c>
       <c r="N147" s="8">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="O147" s="8"/>
       <c r="P147" s="8"/>
@@ -11953,7 +11953,7 @@
         <v>3</v>
       </c>
       <c r="N148" s="8">
-        <v>329</v>
+        <v>348</v>
       </c>
       <c r="O148" s="8"/>
       <c r="P148" s="8"/>
@@ -11988,13 +11988,13 @@
         <v>12</v>
       </c>
       <c r="I149" s="8">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J149" s="8">
         <v>0</v>
       </c>
       <c r="K149" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L149" s="8">
         <v>0</v>
@@ -12004,7 +12004,7 @@
         <v>8</v>
       </c>
       <c r="N149" s="8">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="O149" s="8"/>
       <c r="P149" s="8"/>
@@ -12039,13 +12039,13 @@
         <v>12</v>
       </c>
       <c r="I150" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J150" s="8">
         <v>0</v>
       </c>
       <c r="K150" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L150" s="8">
         <v>0</v>
@@ -12055,7 +12055,7 @@
         <v>4</v>
       </c>
       <c r="N150" s="8">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="O150" s="8"/>
       <c r="P150" s="8"/>
@@ -12106,7 +12106,7 @@
         <v>3</v>
       </c>
       <c r="N151" s="8">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="O151" s="8"/>
       <c r="P151" s="8"/>
@@ -12141,7 +12141,7 @@
         <v>15</v>
       </c>
       <c r="I152" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J152" s="8">
         <v>0</v>
@@ -12154,10 +12154,10 @@
       </c>
       <c r="M152" s="8">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N152" s="8">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="O152" s="8"/>
       <c r="P152" s="8"/>
@@ -12192,7 +12192,7 @@
         <v>13</v>
       </c>
       <c r="I153" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J153" s="8">
         <v>0</v>
@@ -12205,7 +12205,7 @@
       </c>
       <c r="M153" s="8">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N153" s="8">
         <v>538</v>
@@ -12498,7 +12498,7 @@
         <v>15</v>
       </c>
       <c r="I159" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J159" s="8">
         <v>0</v>
@@ -12511,10 +12511,10 @@
       </c>
       <c r="M159" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N159" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O159" s="8"/>
       <c r="P159" s="8"/>
@@ -12565,7 +12565,7 @@
         <v>3</v>
       </c>
       <c r="N160" s="8">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="O160" s="8"/>
       <c r="P160" s="8"/>
@@ -12667,7 +12667,7 @@
         <v>2</v>
       </c>
       <c r="N162" s="8">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="O162" s="8"/>
       <c r="P162" s="8"/>
@@ -12769,7 +12769,7 @@
         <v>3</v>
       </c>
       <c r="N164" s="8">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="O164" s="8"/>
       <c r="P164" s="8"/>
@@ -12820,7 +12820,7 @@
         <v>10</v>
       </c>
       <c r="N165" s="8">
-        <v>1403</v>
+        <v>1363</v>
       </c>
       <c r="O165" s="8"/>
       <c r="P165" s="8"/>
@@ -12871,7 +12871,7 @@
         <v>4</v>
       </c>
       <c r="N166" s="8">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="O166" s="8"/>
       <c r="P166" s="8"/>
@@ -12957,7 +12957,7 @@
         <v>14</v>
       </c>
       <c r="I168" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J168" s="8">
         <v>0</v>
@@ -12970,10 +12970,10 @@
       </c>
       <c r="M168" s="8">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N168" s="8">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="O168" s="8"/>
       <c r="P168" s="8"/>
@@ -13075,7 +13075,7 @@
         <v>4</v>
       </c>
       <c r="N170" s="8">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="O170" s="8"/>
       <c r="P170" s="8"/>
@@ -13161,13 +13161,13 @@
         <v>14</v>
       </c>
       <c r="I172" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J172" s="8">
         <v>0</v>
       </c>
       <c r="K172" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L172" s="8">
         <v>0</v>
@@ -13228,7 +13228,7 @@
         <v>2</v>
       </c>
       <c r="N173" s="8">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="O173" s="8"/>
       <c r="P173" s="8"/>
@@ -13381,7 +13381,7 @@
         <v>2</v>
       </c>
       <c r="N176" s="8">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="O176" s="8"/>
       <c r="P176" s="8"/>
@@ -13518,7 +13518,7 @@
         <v>15</v>
       </c>
       <c r="I179" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J179" s="8">
         <v>0</v>
@@ -13531,10 +13531,10 @@
       </c>
       <c r="M179" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N179" s="8">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="O179" s="8"/>
       <c r="P179" s="8"/>
@@ -13585,7 +13585,7 @@
         <v>8</v>
       </c>
       <c r="N180" s="8">
-        <v>438</v>
+        <v>620</v>
       </c>
       <c r="O180" s="8"/>
       <c r="P180" s="8"/>
@@ -13620,7 +13620,7 @@
         <v>15</v>
       </c>
       <c r="I181" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J181" s="8">
         <v>0</v>
@@ -13633,10 +13633,10 @@
       </c>
       <c r="M181" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N181" s="8">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="O181" s="8"/>
       <c r="P181" s="8"/>
@@ -13738,7 +13738,7 @@
         <v>6</v>
       </c>
       <c r="N183" s="8">
-        <v>515</v>
+        <v>502</v>
       </c>
       <c r="O183" s="8"/>
       <c r="P183" s="8"/>
@@ -13824,23 +13824,23 @@
         <v>12</v>
       </c>
       <c r="I185" s="8">
-        <v>383</v>
+        <v>427</v>
       </c>
       <c r="J185" s="8">
         <v>0</v>
       </c>
       <c r="K185" s="8">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="L185" s="8">
         <v>0</v>
       </c>
       <c r="M185" s="8">
         <f t="shared" si="2"/>
-        <v>419</v>
+        <v>499</v>
       </c>
       <c r="N185" s="8">
-        <v>1887</v>
+        <v>1815</v>
       </c>
       <c r="O185" s="8"/>
       <c r="P185" s="8"/>
@@ -13875,7 +13875,7 @@
         <v>12</v>
       </c>
       <c r="I186" s="8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J186" s="8">
         <v>0</v>
@@ -13888,10 +13888,10 @@
       </c>
       <c r="M186" s="8">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N186" s="8">
-        <v>977</v>
+        <v>970</v>
       </c>
       <c r="O186" s="8"/>
       <c r="P186" s="8"/>
@@ -13942,7 +13942,7 @@
         <v>2</v>
       </c>
       <c r="N187" s="8">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O187" s="8"/>
       <c r="P187" s="8"/>
@@ -14079,7 +14079,7 @@
         <v>12</v>
       </c>
       <c r="I190" s="8">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J190" s="8">
         <v>0</v>
@@ -14092,10 +14092,10 @@
       </c>
       <c r="M190" s="8">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="N190" s="8">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="O190" s="8"/>
       <c r="P190" s="8"/>
@@ -14146,7 +14146,7 @@
         <v>8</v>
       </c>
       <c r="N191" s="8">
-        <v>983</v>
+        <v>973</v>
       </c>
       <c r="O191" s="8"/>
       <c r="P191" s="8"/>
@@ -14452,7 +14452,7 @@
         <v>4</v>
       </c>
       <c r="N197" s="8">
-        <v>798</v>
+        <v>784</v>
       </c>
       <c r="O197" s="8"/>
       <c r="P197" s="8"/>
@@ -14946,23 +14946,23 @@
         <v>14</v>
       </c>
       <c r="I207" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J207" s="8">
         <v>0</v>
       </c>
       <c r="K207" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L207" s="8">
         <v>0</v>
       </c>
       <c r="M207" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N207" s="8">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="O207" s="8"/>
       <c r="P207" s="8"/>
@@ -14997,13 +14997,13 @@
         <v>14</v>
       </c>
       <c r="I208" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J208" s="8">
         <v>0</v>
       </c>
       <c r="K208" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L208" s="8">
         <v>0</v>
@@ -15013,7 +15013,7 @@
         <v>3</v>
       </c>
       <c r="N208" s="8">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="O208" s="8"/>
       <c r="P208" s="8"/>
@@ -15064,7 +15064,7 @@
         <v>2</v>
       </c>
       <c r="N209" s="8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O209" s="8"/>
       <c r="P209" s="8"/>
@@ -15150,7 +15150,7 @@
         <v>12</v>
       </c>
       <c r="I211" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J211" s="8">
         <v>0</v>
@@ -15163,10 +15163,10 @@
       </c>
       <c r="M211" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N211" s="8">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="O211" s="8"/>
       <c r="P211" s="8"/>
@@ -15303,13 +15303,13 @@
         <v>14</v>
       </c>
       <c r="I214" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J214" s="8">
         <v>0</v>
       </c>
       <c r="K214" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L214" s="8">
         <v>0</v>
@@ -15523,7 +15523,7 @@
         <v>6</v>
       </c>
       <c r="N218" s="8">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O218" s="8"/>
       <c r="P218" s="8"/>
@@ -15574,7 +15574,7 @@
         <v>6</v>
       </c>
       <c r="N219" s="8">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="O219" s="8"/>
       <c r="P219" s="8"/>
@@ -15711,7 +15711,7 @@
         <v>16</v>
       </c>
       <c r="I222" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J222" s="8">
         <v>0</v>
@@ -15724,7 +15724,7 @@
       </c>
       <c r="M222" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N222" s="8">
         <v>136</v>
@@ -15864,13 +15864,13 @@
         <v>12</v>
       </c>
       <c r="I225" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J225" s="8">
         <v>0</v>
       </c>
       <c r="K225" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L225" s="8">
         <v>0</v>
@@ -15880,7 +15880,7 @@
         <v>3</v>
       </c>
       <c r="N225" s="8">
-        <v>688</v>
+        <v>677</v>
       </c>
       <c r="O225" s="8"/>
       <c r="P225" s="8"/>
@@ -15966,7 +15966,7 @@
         <v>16</v>
       </c>
       <c r="I227" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J227" s="8">
         <v>0</v>
@@ -15979,7 +15979,7 @@
       </c>
       <c r="M227" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N227" s="8">
         <v>0</v>
@@ -16023,17 +16023,17 @@
         <v>0</v>
       </c>
       <c r="K228" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L228" s="8">
         <v>0</v>
       </c>
       <c r="M228" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N228" s="8">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O228" s="8"/>
       <c r="P228" s="8"/>
@@ -16084,7 +16084,7 @@
         <v>2</v>
       </c>
       <c r="N229" s="8">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="O229" s="8"/>
       <c r="P229" s="8"/>
@@ -16237,7 +16237,7 @@
         <v>12</v>
       </c>
       <c r="N232" s="8">
-        <v>686</v>
+        <v>661</v>
       </c>
       <c r="O232" s="8"/>
       <c r="P232" s="8"/>
@@ -16288,7 +16288,7 @@
         <v>5</v>
       </c>
       <c r="N233" s="8">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="O233" s="8"/>
       <c r="P233" s="8"/>
@@ -16323,13 +16323,13 @@
         <v>15</v>
       </c>
       <c r="I234" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J234" s="8">
         <v>0</v>
       </c>
       <c r="K234" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L234" s="8">
         <v>0</v>
@@ -16339,7 +16339,7 @@
         <v>3</v>
       </c>
       <c r="N234" s="8">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="O234" s="8"/>
       <c r="P234" s="8"/>
@@ -16390,7 +16390,7 @@
         <v>3</v>
       </c>
       <c r="N235" s="8">
-        <v>31</v>
+        <v>94</v>
       </c>
       <c r="O235" s="8"/>
       <c r="P235" s="8"/>
@@ -16482,17 +16482,17 @@
         <v>0</v>
       </c>
       <c r="K237" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L237" s="8">
         <v>0</v>
       </c>
       <c r="M237" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N237" s="8">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="O237" s="8"/>
       <c r="P237" s="8"/>
@@ -16543,7 +16543,7 @@
         <v>6</v>
       </c>
       <c r="N238" s="8">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="O238" s="8"/>
       <c r="P238" s="8"/>
@@ -16594,7 +16594,7 @@
         <v>4</v>
       </c>
       <c r="N239" s="8">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O239" s="8"/>
       <c r="P239" s="8"/>
@@ -16629,7 +16629,7 @@
         <v>13</v>
       </c>
       <c r="I240" s="8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J240" s="8">
         <v>0</v>
@@ -16642,10 +16642,10 @@
       </c>
       <c r="M240" s="8">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N240" s="8">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="O240" s="8"/>
       <c r="P240" s="8"/>
@@ -16696,7 +16696,7 @@
         <v>3</v>
       </c>
       <c r="N241" s="8">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O241" s="8"/>
       <c r="P241" s="8"/>
@@ -16747,7 +16747,7 @@
         <v>3</v>
       </c>
       <c r="N242" s="8">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="O242" s="8"/>
       <c r="P242" s="8"/>
@@ -16782,23 +16782,23 @@
         <v>15</v>
       </c>
       <c r="I243" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J243" s="8">
         <v>0</v>
       </c>
       <c r="K243" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L243" s="8">
         <v>0</v>
       </c>
       <c r="M243" s="8">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N243" s="8">
-        <v>315</v>
+        <v>287</v>
       </c>
       <c r="O243" s="8"/>
       <c r="P243" s="8"/>
@@ -16884,7 +16884,7 @@
         <v>15</v>
       </c>
       <c r="I245" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J245" s="8">
         <v>0</v>
@@ -16897,7 +16897,7 @@
       </c>
       <c r="M245" s="8">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N245" s="8">
         <v>0</v>
@@ -16951,7 +16951,7 @@
         <v>3</v>
       </c>
       <c r="N246" s="8">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="O246" s="8"/>
       <c r="P246" s="8"/>
@@ -17002,7 +17002,7 @@
         <v>2</v>
       </c>
       <c r="N247" s="8">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="O247" s="8"/>
       <c r="P247" s="8"/>
@@ -17139,13 +17139,13 @@
         <v>12</v>
       </c>
       <c r="I250" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J250" s="8">
         <v>0</v>
       </c>
       <c r="K250" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L250" s="8">
         <v>0</v>
@@ -17155,7 +17155,7 @@
         <v>3</v>
       </c>
       <c r="N250" s="8">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="O250" s="8"/>
       <c r="P250" s="8"/>
@@ -17206,7 +17206,7 @@
         <v>2</v>
       </c>
       <c r="N251" s="8">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="O251" s="8"/>
       <c r="P251" s="8"/>
@@ -17257,7 +17257,7 @@
         <v>2</v>
       </c>
       <c r="N252" s="8">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="O252" s="8"/>
       <c r="P252" s="8"/>
@@ -17298,17 +17298,17 @@
         <v>0</v>
       </c>
       <c r="K253" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L253" s="8">
         <v>0</v>
       </c>
       <c r="M253" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N253" s="8">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="O253" s="8"/>
       <c r="P253" s="8"/>
@@ -17394,13 +17394,13 @@
         <v>14</v>
       </c>
       <c r="I255" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J255" s="8">
         <v>0</v>
       </c>
       <c r="K255" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L255" s="8">
         <v>0</v>
@@ -17461,7 +17461,7 @@
         <v>2</v>
       </c>
       <c r="N256" s="8">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="O256" s="8"/>
       <c r="P256" s="8"/>
@@ -17512,7 +17512,7 @@
         <v>4</v>
       </c>
       <c r="N257" s="8">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="O257" s="8"/>
       <c r="P257" s="8"/>
@@ -17598,13 +17598,13 @@
         <v>15</v>
       </c>
       <c r="I259" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J259" s="8">
         <v>0</v>
       </c>
       <c r="K259" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L259" s="8">
         <v>0</v>
@@ -17614,7 +17614,7 @@
         <v>3</v>
       </c>
       <c r="N259" s="8">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O259" s="8"/>
       <c r="P259" s="8"/>
@@ -17649,13 +17649,13 @@
         <v>13</v>
       </c>
       <c r="I260" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J260" s="8">
         <v>0</v>
       </c>
       <c r="K260" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L260" s="8">
         <v>0</v>
@@ -17665,7 +17665,7 @@
         <v>7</v>
       </c>
       <c r="N260" s="8">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="O260" s="8"/>
       <c r="P260" s="8"/>
@@ -17700,7 +17700,7 @@
         <v>12</v>
       </c>
       <c r="I261" s="8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J261" s="8">
         <v>0</v>
@@ -17713,10 +17713,10 @@
       </c>
       <c r="M261" s="8">
         <f t="shared" si="4"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N261" s="8">
-        <v>1190</v>
+        <v>1170</v>
       </c>
       <c r="O261" s="8"/>
       <c r="P261" s="8"/>
@@ -17751,23 +17751,23 @@
         <v>12</v>
       </c>
       <c r="I262" s="8">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J262" s="8">
         <v>0</v>
       </c>
       <c r="K262" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L262" s="8">
         <v>0</v>
       </c>
       <c r="M262" s="8">
         <f t="shared" si="4"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N262" s="8">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="O262" s="8"/>
       <c r="P262" s="8"/>
@@ -17802,23 +17802,23 @@
         <v>12</v>
       </c>
       <c r="I263" s="8">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J263" s="8">
         <v>0</v>
       </c>
       <c r="K263" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L263" s="8">
         <v>0</v>
       </c>
       <c r="M263" s="8">
         <f t="shared" si="4"/>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="N263" s="8">
-        <v>534</v>
+        <v>498</v>
       </c>
       <c r="O263" s="8"/>
       <c r="P263" s="8"/>
@@ -17971,7 +17971,7 @@
         <v>3</v>
       </c>
       <c r="N266" s="8">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="O266" s="8"/>
       <c r="P266" s="8"/>
@@ -18073,7 +18073,7 @@
         <v>6</v>
       </c>
       <c r="N268" s="8">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O268" s="8"/>
       <c r="P268" s="8"/>
@@ -18114,17 +18114,17 @@
         <v>0</v>
       </c>
       <c r="K269" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L269" s="8">
         <v>0</v>
       </c>
       <c r="M269" s="8">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N269" s="8">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="O269" s="8"/>
       <c r="P269" s="8"/>
@@ -18159,7 +18159,7 @@
         <v>16</v>
       </c>
       <c r="I270" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J270" s="8">
         <v>0</v>
@@ -18172,7 +18172,7 @@
       </c>
       <c r="M270" s="8">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N270" s="8">
         <v>0</v>
@@ -18312,7 +18312,7 @@
         <v>16</v>
       </c>
       <c r="I273" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J273" s="8">
         <v>0</v>
@@ -18325,7 +18325,7 @@
       </c>
       <c r="M273" s="8">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N273" s="8">
         <v>0</v>
@@ -18363,7 +18363,7 @@
         <v>16</v>
       </c>
       <c r="I274" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J274" s="8">
         <v>0</v>
@@ -18376,7 +18376,7 @@
       </c>
       <c r="M274" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N274" s="8">
         <v>106</v>
@@ -18481,7 +18481,7 @@
         <v>3</v>
       </c>
       <c r="N276" s="8">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="O276" s="8"/>
       <c r="P276" s="8"/>
@@ -18567,13 +18567,13 @@
         <v>12</v>
       </c>
       <c r="I278" s="8">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J278" s="8">
         <v>0</v>
       </c>
       <c r="K278" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L278" s="8">
         <v>0</v>
@@ -18583,7 +18583,7 @@
         <v>9</v>
       </c>
       <c r="N278" s="8">
-        <v>1813</v>
+        <v>1773</v>
       </c>
       <c r="O278" s="8"/>
       <c r="P278" s="8"/>
@@ -18618,13 +18618,13 @@
         <v>13</v>
       </c>
       <c r="I279" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J279" s="8">
         <v>0</v>
       </c>
       <c r="K279" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L279" s="8">
         <v>0</v>
@@ -18736,7 +18736,7 @@
         <v>2</v>
       </c>
       <c r="N281" s="8">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O281" s="8"/>
       <c r="P281" s="8"/>
@@ -18822,23 +18822,23 @@
         <v>12</v>
       </c>
       <c r="I283" s="8">
+        <v>5</v>
+      </c>
+      <c r="J283" s="8">
+        <v>0</v>
+      </c>
+      <c r="K283" s="8">
         <v>7</v>
-      </c>
-      <c r="J283" s="8">
-        <v>0</v>
-      </c>
-      <c r="K283" s="8">
-        <v>0</v>
       </c>
       <c r="L283" s="8">
         <v>0</v>
       </c>
       <c r="M283" s="8">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="N283" s="8">
-        <v>314</v>
+        <v>283</v>
       </c>
       <c r="O283" s="8"/>
       <c r="P283" s="8"/>
@@ -18873,23 +18873,23 @@
         <v>12</v>
       </c>
       <c r="I284" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J284" s="8">
         <v>0</v>
       </c>
       <c r="K284" s="8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L284" s="8">
         <v>0</v>
       </c>
       <c r="M284" s="8">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>101</v>
       </c>
       <c r="N284" s="8">
-        <v>202</v>
+        <v>29</v>
       </c>
       <c r="O284" s="8"/>
       <c r="P284" s="8"/>
@@ -18940,7 +18940,7 @@
         <v>3</v>
       </c>
       <c r="N285" s="8">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="O285" s="8"/>
       <c r="P285" s="8"/>
@@ -18991,7 +18991,7 @@
         <v>4</v>
       </c>
       <c r="N286" s="8">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="O286" s="8"/>
       <c r="P286" s="8"/>
@@ -19026,13 +19026,13 @@
         <v>12</v>
       </c>
       <c r="I287" s="8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J287" s="8">
         <v>0</v>
       </c>
       <c r="K287" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L287" s="8">
         <v>0</v>
@@ -19093,7 +19093,7 @@
         <v>4</v>
       </c>
       <c r="N288" s="8">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="O288" s="8"/>
       <c r="P288" s="8"/>
@@ -19128,7 +19128,7 @@
         <v>14</v>
       </c>
       <c r="I289" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J289" s="8">
         <v>0</v>
@@ -19141,10 +19141,10 @@
       </c>
       <c r="M289" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N289" s="8">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="O289" s="8"/>
       <c r="P289" s="8"/>
@@ -19230,13 +19230,13 @@
         <v>12</v>
       </c>
       <c r="I291" s="8">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J291" s="8">
         <v>0</v>
       </c>
       <c r="K291" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L291" s="8">
         <v>0</v>
@@ -19246,7 +19246,7 @@
         <v>17</v>
       </c>
       <c r="N291" s="8">
-        <v>862</v>
+        <v>1334</v>
       </c>
       <c r="O291" s="8"/>
       <c r="P291" s="8"/>
@@ -19297,7 +19297,7 @@
         <v>3</v>
       </c>
       <c r="N292" s="8">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="O292" s="8"/>
       <c r="P292" s="8"/>
@@ -19383,23 +19383,23 @@
         <v>12</v>
       </c>
       <c r="I294" s="8">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J294" s="8">
         <v>0</v>
       </c>
       <c r="K294" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L294" s="8">
         <v>0</v>
       </c>
       <c r="M294" s="8">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N294" s="8">
-        <v>1629</v>
+        <v>1601</v>
       </c>
       <c r="O294" s="8"/>
       <c r="P294" s="8"/>
@@ -19689,7 +19689,7 @@
         <v>13</v>
       </c>
       <c r="I300" s="8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J300" s="8">
         <v>0</v>
@@ -19702,7 +19702,7 @@
       </c>
       <c r="M300" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N300" s="8">
         <v>0</v>
@@ -19858,7 +19858,7 @@
         <v>3</v>
       </c>
       <c r="N303" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O303" s="8"/>
       <c r="P303" s="8"/>
@@ -19909,7 +19909,7 @@
         <v>4</v>
       </c>
       <c r="N304" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O304" s="8"/>
       <c r="P304" s="8"/>
@@ -19960,7 +19960,7 @@
         <v>8</v>
       </c>
       <c r="N305" s="8">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="O305" s="8"/>
       <c r="P305" s="8"/>
@@ -20011,7 +20011,7 @@
         <v>10</v>
       </c>
       <c r="N306" s="8">
-        <v>1180</v>
+        <v>1149</v>
       </c>
       <c r="O306" s="8"/>
       <c r="P306" s="8"/>
@@ -20062,7 +20062,7 @@
         <v>11</v>
       </c>
       <c r="N307" s="8">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O307" s="8"/>
       <c r="P307" s="8"/>
@@ -20113,7 +20113,7 @@
         <v>11</v>
       </c>
       <c r="N308" s="8">
-        <v>795</v>
+        <v>1048</v>
       </c>
       <c r="O308" s="8"/>
       <c r="P308" s="8"/>
@@ -20148,7 +20148,7 @@
         <v>13</v>
       </c>
       <c r="I309" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J309" s="8">
         <v>0</v>
@@ -20161,7 +20161,7 @@
       </c>
       <c r="M309" s="8">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N309" s="8">
         <v>0</v>
@@ -20215,7 +20215,7 @@
         <v>4</v>
       </c>
       <c r="N310" s="8">
-        <v>165</v>
+        <v>215</v>
       </c>
       <c r="O310" s="8"/>
       <c r="P310" s="8"/>
@@ -20317,7 +20317,7 @@
         <v>6</v>
       </c>
       <c r="N312" s="8">
-        <v>20</v>
+        <v>180</v>
       </c>
       <c r="O312" s="8"/>
       <c r="P312" s="8"/>
@@ -20368,7 +20368,7 @@
         <v>3</v>
       </c>
       <c r="N313" s="8">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="O313" s="8"/>
       <c r="P313" s="8"/>
@@ -20403,23 +20403,23 @@
         <v>12</v>
       </c>
       <c r="I314" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J314" s="8">
         <v>0</v>
       </c>
       <c r="K314" s="8">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L314" s="8">
         <v>0</v>
       </c>
       <c r="M314" s="8">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N314" s="8">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="O314" s="8"/>
       <c r="P314" s="8"/>
@@ -20470,7 +20470,7 @@
         <v>8</v>
       </c>
       <c r="N315" s="8">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="O315" s="8"/>
       <c r="P315" s="8"/>
@@ -20505,13 +20505,13 @@
         <v>12</v>
       </c>
       <c r="I316" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J316" s="8">
         <v>0</v>
       </c>
       <c r="K316" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L316" s="8">
         <v>0</v>
@@ -20521,7 +20521,7 @@
         <v>7</v>
       </c>
       <c r="N316" s="8">
-        <v>772</v>
+        <v>763</v>
       </c>
       <c r="O316" s="8"/>
       <c r="P316" s="8"/>
@@ -20556,23 +20556,23 @@
         <v>12</v>
       </c>
       <c r="I317" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J317" s="8">
         <v>0</v>
       </c>
       <c r="K317" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L317" s="8">
         <v>0</v>
       </c>
       <c r="M317" s="8">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N317" s="8">
-        <v>485</v>
+        <v>455</v>
       </c>
       <c r="O317" s="8"/>
       <c r="P317" s="8"/>
@@ -20613,17 +20613,17 @@
         <v>0</v>
       </c>
       <c r="K318" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L318" s="8">
         <v>0</v>
       </c>
       <c r="M318" s="8">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N318" s="8">
-        <v>1219</v>
+        <v>1178</v>
       </c>
       <c r="O318" s="8"/>
       <c r="P318" s="8"/>
@@ -20725,7 +20725,7 @@
         <v>4</v>
       </c>
       <c r="N320" s="8">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="O320" s="8"/>
       <c r="P320" s="8"/>
@@ -20776,7 +20776,7 @@
         <v>2</v>
       </c>
       <c r="N321" s="8">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="O321" s="8"/>
       <c r="P321" s="8"/>
@@ -20827,7 +20827,7 @@
         <v>3</v>
       </c>
       <c r="N322" s="8">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="O322" s="8"/>
       <c r="P322" s="8"/>
@@ -20878,7 +20878,7 @@
         <v>3</v>
       </c>
       <c r="N323" s="8">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O323" s="8"/>
       <c r="P323" s="8"/>
@@ -20929,7 +20929,7 @@
         <v>0</v>
       </c>
       <c r="N324" s="8">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O324" s="8"/>
       <c r="P324" s="8"/>
@@ -20964,13 +20964,13 @@
         <v>14</v>
       </c>
       <c r="I325" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J325" s="8">
         <v>0</v>
       </c>
       <c r="K325" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L325" s="8">
         <v>0</v>
@@ -20980,7 +20980,7 @@
         <v>3</v>
       </c>
       <c r="N325" s="8">
-        <v>339</v>
+        <v>538</v>
       </c>
       <c r="O325" s="8"/>
       <c r="P325" s="8"/>
@@ -21031,7 +21031,7 @@
         <v>3</v>
       </c>
       <c r="N326" s="8">
-        <v>1006</v>
+        <v>1018</v>
       </c>
       <c r="O326" s="8"/>
       <c r="P326" s="8"/>
@@ -21117,13 +21117,13 @@
         <v>13</v>
       </c>
       <c r="I328" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J328" s="8">
         <v>0</v>
       </c>
       <c r="K328" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L328" s="8">
         <v>0</v>
@@ -21133,7 +21133,7 @@
         <v>2</v>
       </c>
       <c r="N328" s="8">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="O328" s="8"/>
       <c r="P328" s="8"/>
@@ -21184,7 +21184,7 @@
         <v>4</v>
       </c>
       <c r="N329" s="8">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="O329" s="8"/>
       <c r="P329" s="8"/>
@@ -21235,7 +21235,7 @@
         <v>2</v>
       </c>
       <c r="N330" s="8">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="O330" s="8"/>
       <c r="P330" s="8"/>
@@ -21270,7 +21270,7 @@
         <v>13</v>
       </c>
       <c r="I331" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J331" s="8">
         <v>0</v>
@@ -21283,7 +21283,7 @@
       </c>
       <c r="M331" s="8">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N331" s="8">
         <v>0</v>
@@ -21439,7 +21439,7 @@
         <v>4</v>
       </c>
       <c r="N334" s="8">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O334" s="8"/>
       <c r="P334" s="8"/>
@@ -21490,7 +21490,7 @@
         <v>1</v>
       </c>
       <c r="N335" s="8">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O335" s="8"/>
       <c r="P335" s="8"/>
@@ -21541,7 +21541,7 @@
         <v>4</v>
       </c>
       <c r="N336" s="8">
-        <v>680</v>
+        <v>668</v>
       </c>
       <c r="O336" s="8"/>
       <c r="P336" s="8"/>
@@ -21576,7 +21576,7 @@
         <v>12</v>
       </c>
       <c r="I337" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J337" s="8">
         <v>0</v>
@@ -21589,10 +21589,10 @@
       </c>
       <c r="M337" s="8">
         <f t="shared" si="5"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N337" s="8">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="O337" s="8"/>
       <c r="P337" s="8"/>
@@ -21627,7 +21627,7 @@
         <v>12</v>
       </c>
       <c r="I338" s="8">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J338" s="8">
         <v>0</v>
@@ -21640,10 +21640,10 @@
       </c>
       <c r="M338" s="8">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N338" s="8">
-        <v>1479</v>
+        <v>1475</v>
       </c>
       <c r="O338" s="8"/>
       <c r="P338" s="8"/>
@@ -21694,7 +21694,7 @@
         <v>3</v>
       </c>
       <c r="N339" s="8">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="O339" s="8"/>
       <c r="P339" s="8"/>
@@ -21729,23 +21729,23 @@
         <v>14</v>
       </c>
       <c r="I340" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J340" s="8">
         <v>0</v>
       </c>
       <c r="K340" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L340" s="8">
         <v>0</v>
       </c>
       <c r="M340" s="8">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N340" s="8">
-        <v>942</v>
+        <v>917</v>
       </c>
       <c r="O340" s="8"/>
       <c r="P340" s="8"/>
@@ -21780,7 +21780,7 @@
         <v>14</v>
       </c>
       <c r="I341" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J341" s="8">
         <v>0</v>
@@ -21793,10 +21793,10 @@
       </c>
       <c r="M341" s="8">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N341" s="8">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="O341" s="8"/>
       <c r="P341" s="8"/>
@@ -21984,7 +21984,7 @@
         <v>12</v>
       </c>
       <c r="I345" s="8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J345" s="8">
         <v>0</v>
@@ -21997,7 +21997,7 @@
       </c>
       <c r="M345" s="8">
         <f t="shared" si="5"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N345" s="8">
         <v>0</v>
@@ -22035,13 +22035,13 @@
         <v>13</v>
       </c>
       <c r="I346" s="8">
+        <v>0</v>
+      </c>
+      <c r="J346" s="8">
+        <v>0</v>
+      </c>
+      <c r="K346" s="8">
         <v>304</v>
-      </c>
-      <c r="J346" s="8">
-        <v>0</v>
-      </c>
-      <c r="K346" s="8">
-        <v>0</v>
       </c>
       <c r="L346" s="8">
         <v>0</v>
@@ -22086,7 +22086,7 @@
         <v>13</v>
       </c>
       <c r="I347" s="8">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J347" s="8">
         <v>0</v>
@@ -22099,10 +22099,10 @@
       </c>
       <c r="M347" s="8">
         <f t="shared" si="5"/>
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="N347" s="8">
-        <v>536</v>
+        <v>769</v>
       </c>
       <c r="O347" s="8"/>
       <c r="P347" s="9"/>
@@ -22137,7 +22137,7 @@
         <v>12</v>
       </c>
       <c r="I348" s="8">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J348" s="8">
         <v>0</v>
@@ -22150,7 +22150,7 @@
       </c>
       <c r="M348" s="8">
         <f t="shared" si="5"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N348" s="8">
         <v>84</v>
@@ -22357,7 +22357,7 @@
         <v>2</v>
       </c>
       <c r="N352" s="8">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="O352" s="8"/>
       <c r="P352" s="9"/>
@@ -22494,7 +22494,7 @@
         <v>16</v>
       </c>
       <c r="I355" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J355" s="8">
         <v>0</v>
@@ -22507,10 +22507,10 @@
       </c>
       <c r="M355" s="8">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N355" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O355" s="8"/>
       <c r="P355" s="9"/>
@@ -22902,23 +22902,23 @@
         <v>12</v>
       </c>
       <c r="I363" s="8">
-        <v>475</v>
+        <v>536</v>
       </c>
       <c r="J363" s="8">
         <v>0</v>
       </c>
       <c r="K363" s="8">
-        <v>35</v>
+        <v>134</v>
       </c>
       <c r="L363" s="8">
         <v>0</v>
       </c>
       <c r="M363" s="8">
         <f t="shared" si="5"/>
-        <v>510</v>
+        <v>670</v>
       </c>
       <c r="N363" s="8">
-        <v>1417</v>
+        <v>1318</v>
       </c>
       <c r="O363" s="8"/>
       <c r="P363" s="9"/>
@@ -23071,7 +23071,7 @@
         <v>2</v>
       </c>
       <c r="N366" s="8">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="O366" s="8"/>
       <c r="P366" s="9"/>
@@ -23106,23 +23106,23 @@
         <v>12</v>
       </c>
       <c r="I367" s="8">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="J367" s="8">
         <v>0</v>
       </c>
       <c r="K367" s="8">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="L367" s="8">
         <v>0</v>
       </c>
       <c r="M367" s="8">
         <f t="shared" si="5"/>
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="N367" s="8">
-        <v>426</v>
+        <v>0</v>
       </c>
       <c r="O367" s="8"/>
       <c r="P367" s="9"/>
@@ -23157,23 +23157,23 @@
         <v>12</v>
       </c>
       <c r="I368" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J368" s="8">
         <v>0</v>
       </c>
       <c r="K368" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L368" s="8">
         <v>0</v>
       </c>
       <c r="M368" s="8">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N368" s="8">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="O368" s="8"/>
       <c r="P368" s="9"/>
@@ -23214,17 +23214,17 @@
         <v>0</v>
       </c>
       <c r="K369" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L369" s="8">
         <v>0</v>
       </c>
       <c r="M369" s="8">
         <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="N369" s="8">
         <v>1</v>
-      </c>
-      <c r="N369" s="8">
-        <v>11</v>
       </c>
       <c r="O369" s="8"/>
       <c r="P369" s="9"/>
@@ -23326,7 +23326,7 @@
         <v>3</v>
       </c>
       <c r="N371" s="8">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="O371" s="8"/>
       <c r="P371" s="9"/>
@@ -23377,7 +23377,7 @@
         <v>3</v>
       </c>
       <c r="N372" s="8">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O372" s="8"/>
       <c r="P372" s="9"/>
@@ -23428,7 +23428,7 @@
         <v>5</v>
       </c>
       <c r="N373" s="8">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="O373" s="8"/>
       <c r="P373" s="9"/>
@@ -23514,7 +23514,7 @@
         <v>12</v>
       </c>
       <c r="I375" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J375" s="8">
         <v>0</v>
@@ -23527,7 +23527,7 @@
       </c>
       <c r="M375" s="8">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N375" s="8">
         <v>0</v>
@@ -23989,7 +23989,7 @@
         <v>5</v>
       </c>
       <c r="N384" s="8">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="O384" s="8"/>
       <c r="P384" s="9"/>
@@ -24024,20 +24024,20 @@
         <v>12</v>
       </c>
       <c r="I385" s="8">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="J385" s="8">
         <v>0</v>
       </c>
       <c r="K385" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L385" s="8">
         <v>0</v>
       </c>
       <c r="M385" s="8">
         <f t="shared" si="5"/>
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="N385" s="8">
         <v>257</v>
@@ -24295,7 +24295,7 @@
         <v>5</v>
       </c>
       <c r="N390" s="8">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="O390" s="8"/>
       <c r="P390" s="7"/>
@@ -24585,7 +24585,7 @@
         <v>12</v>
       </c>
       <c r="I396" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J396" s="8">
         <v>0</v>
@@ -24598,7 +24598,7 @@
       </c>
       <c r="M396" s="8">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N396" s="8">
         <v>0</v>
@@ -24687,7 +24687,7 @@
         <v>15</v>
       </c>
       <c r="I398" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J398" s="8">
         <v>0</v>
@@ -24700,7 +24700,7 @@
       </c>
       <c r="M398" s="8">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N398" s="8">
         <v>248</v>

--- a/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
+++ b/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\Fossil Replenishment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A47E66-92E8-4C61-9702-2E1A65FD8C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E26E24FE-D6B3-4B79-91C6-8B36413DA822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6662473D-6E1F-42FD-999B-28162E22D4B5}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$T$403</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$T$433</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3236" uniqueCount="1252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3476" uniqueCount="1343">
   <si>
     <t>In Transit PO</t>
   </si>
@@ -3793,6 +3793,279 @@
   </si>
   <si>
     <t>FBA79922</t>
+  </si>
+  <si>
+    <t>AR11742</t>
+  </si>
+  <si>
+    <t>B0GDKG6QRV</t>
+  </si>
+  <si>
+    <t>AR11743</t>
+  </si>
+  <si>
+    <t>B0GDX6M95H</t>
+  </si>
+  <si>
+    <t>AR11763</t>
+  </si>
+  <si>
+    <t>B0GHJMFM23</t>
+  </si>
+  <si>
+    <t>AR11769</t>
+  </si>
+  <si>
+    <t>B0GHD9GN9C</t>
+  </si>
+  <si>
+    <t>AX4300</t>
+  </si>
+  <si>
+    <t>B0GTC9238R</t>
+  </si>
+  <si>
+    <t>AX7178SET</t>
+  </si>
+  <si>
+    <t>B0GTC9PS5Z</t>
+  </si>
+  <si>
+    <t>DZ2237</t>
+  </si>
+  <si>
+    <t>B07SV6HR8T</t>
+  </si>
+  <si>
+    <t>DZ2239</t>
+  </si>
+  <si>
+    <t>B07SW9C6ZH</t>
+  </si>
+  <si>
+    <t>DZ4711</t>
+  </si>
+  <si>
+    <t>B07SYFYGR6</t>
+  </si>
+  <si>
+    <t>DZ4712</t>
+  </si>
+  <si>
+    <t>B07SYSQJDN</t>
+  </si>
+  <si>
+    <t>ES5473</t>
+  </si>
+  <si>
+    <t>B0GTC2MW2C</t>
+  </si>
+  <si>
+    <t>ES5477</t>
+  </si>
+  <si>
+    <t>B0GTC3BMTN</t>
+  </si>
+  <si>
+    <t>ES5478</t>
+  </si>
+  <si>
+    <t>B0GTC7QS9P</t>
+  </si>
+  <si>
+    <t>FS6166</t>
+  </si>
+  <si>
+    <t>B0GTBY76NG</t>
+  </si>
+  <si>
+    <t>FS6169</t>
+  </si>
+  <si>
+    <t>B0GTCF15F4</t>
+  </si>
+  <si>
+    <t>MK4992SET</t>
+  </si>
+  <si>
+    <t>B0GF71S5WW</t>
+  </si>
+  <si>
+    <t>MK4994SET</t>
+  </si>
+  <si>
+    <t>B0GF7N3S44</t>
+  </si>
+  <si>
+    <t>MK7615</t>
+  </si>
+  <si>
+    <t>B0GTC998R6</t>
+  </si>
+  <si>
+    <t>MK7616</t>
+  </si>
+  <si>
+    <t>B0GTC4D5NP</t>
+  </si>
+  <si>
+    <t>MK9107</t>
+  </si>
+  <si>
+    <t>B0CLH9H16G</t>
+  </si>
+  <si>
+    <t>MK9108</t>
+  </si>
+  <si>
+    <t>B0CJJXL9TJ</t>
+  </si>
+  <si>
+    <t>MK9263</t>
+  </si>
+  <si>
+    <t>B0GTC5JGY7</t>
+  </si>
+  <si>
+    <t>MK9270SET</t>
+  </si>
+  <si>
+    <t>B0GTC9239V</t>
+  </si>
+  <si>
+    <t>MK9272SET</t>
+  </si>
+  <si>
+    <t>B0GTBY2FK6</t>
+  </si>
+  <si>
+    <t>MK7569</t>
+  </si>
+  <si>
+    <t>B0GF7CZNZC</t>
+  </si>
+  <si>
+    <t>MK7586</t>
+  </si>
+  <si>
+    <t>B0GF7BHFS4</t>
+  </si>
+  <si>
+    <t>MK7606</t>
+  </si>
+  <si>
+    <t>B0GTC5GQY4</t>
+  </si>
+  <si>
+    <t>MK7607</t>
+  </si>
+  <si>
+    <t>B0GTC2G6FF</t>
+  </si>
+  <si>
+    <t>MK7613</t>
+  </si>
+  <si>
+    <t>B0GTC6M3QM</t>
+  </si>
+  <si>
+    <t>MK7614</t>
+  </si>
+  <si>
+    <t>B0GTCB716R</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>FBA80220</t>
+  </si>
+  <si>
+    <t>FBA80221</t>
+  </si>
+  <si>
+    <t>FBA80222</t>
+  </si>
+  <si>
+    <t>FBA80223</t>
+  </si>
+  <si>
+    <t>FBA80224</t>
+  </si>
+  <si>
+    <t>FBA80225</t>
+  </si>
+  <si>
+    <t>FBA80226</t>
+  </si>
+  <si>
+    <t>FBA80227</t>
+  </si>
+  <si>
+    <t>FBA80228</t>
+  </si>
+  <si>
+    <t>FBA80229</t>
+  </si>
+  <si>
+    <t>FBA80230</t>
+  </si>
+  <si>
+    <t>FBA80231</t>
+  </si>
+  <si>
+    <t>FBA80232</t>
+  </si>
+  <si>
+    <t>FBA80233</t>
+  </si>
+  <si>
+    <t>FBA80234</t>
+  </si>
+  <si>
+    <t>FBA80235</t>
+  </si>
+  <si>
+    <t>FBA80236</t>
+  </si>
+  <si>
+    <t>FBA80243</t>
+  </si>
+  <si>
+    <t>FBA80244</t>
+  </si>
+  <si>
+    <t>FBA80245</t>
+  </si>
+  <si>
+    <t>FBA80246</t>
+  </si>
+  <si>
+    <t>FBA80247</t>
+  </si>
+  <si>
+    <t>FBA80248</t>
+  </si>
+  <si>
+    <t>FBA80249</t>
+  </si>
+  <si>
+    <t>FBA80237</t>
+  </si>
+  <si>
+    <t>FBA80238</t>
+  </si>
+  <si>
+    <t>FBA80239</t>
+  </si>
+  <si>
+    <t>FBA80240</t>
+  </si>
+  <si>
+    <t>FBA80241</t>
+  </si>
+  <si>
+    <t>FBA80242</t>
   </si>
 </sst>
 </file>
@@ -4378,7 +4651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF55B7BF-85DC-4082-9A73-200B4D79A598}">
-  <dimension ref="A1:T766"/>
+  <dimension ref="A1:T763"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.109375" style="6" bestFit="1" customWidth="1"/>
@@ -4491,23 +4764,23 @@
         <v>12</v>
       </c>
       <c r="I2" s="8">
-        <v>818</v>
+        <v>705</v>
       </c>
       <c r="J2" s="8">
         <v>0</v>
       </c>
       <c r="K2" s="8">
-        <v>48</v>
+        <v>106</v>
       </c>
       <c r="L2" s="8">
         <v>0</v>
       </c>
       <c r="M2" s="8">
         <f>I2+J2+K2+L2</f>
-        <v>866</v>
+        <v>811</v>
       </c>
       <c r="N2" s="8">
-        <v>1481</v>
+        <v>1385</v>
       </c>
       <c r="O2" s="8"/>
       <c r="P2" s="8"/>
@@ -4593,7 +4866,7 @@
         <v>12</v>
       </c>
       <c r="I4" s="8">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J4" s="8">
         <v>0</v>
@@ -4606,7 +4879,7 @@
       </c>
       <c r="M4" s="8">
         <f t="shared" si="0"/>
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N4" s="8">
         <v>0</v>
@@ -4644,7 +4917,7 @@
         <v>12</v>
       </c>
       <c r="I5" s="8">
-        <v>158</v>
+        <v>120</v>
       </c>
       <c r="J5" s="8">
         <v>0</v>
@@ -4657,7 +4930,7 @@
       </c>
       <c r="M5" s="8">
         <f t="shared" si="0"/>
-        <v>158</v>
+        <v>120</v>
       </c>
       <c r="N5" s="8">
         <v>0</v>
@@ -4695,23 +4968,23 @@
         <v>12</v>
       </c>
       <c r="I6" s="8">
-        <v>856</v>
+        <v>797</v>
       </c>
       <c r="J6" s="8">
         <v>0</v>
       </c>
       <c r="K6" s="8">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="L6" s="8">
         <v>0</v>
       </c>
       <c r="M6" s="8">
         <f t="shared" si="0"/>
-        <v>976</v>
+        <v>894</v>
       </c>
       <c r="N6" s="8">
-        <v>1742</v>
+        <v>1658</v>
       </c>
       <c r="O6" s="8"/>
       <c r="P6" s="8"/>
@@ -4746,7 +5019,7 @@
         <v>12</v>
       </c>
       <c r="I7" s="8">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="J7" s="8">
         <v>0</v>
@@ -4759,10 +5032,10 @@
       </c>
       <c r="M7" s="8">
         <f t="shared" si="0"/>
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="N7" s="8">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
@@ -4797,7 +5070,7 @@
         <v>12</v>
       </c>
       <c r="I8" s="8">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="J8" s="8">
         <v>0</v>
@@ -4810,10 +5083,10 @@
       </c>
       <c r="M8" s="8">
         <f t="shared" si="0"/>
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="N8" s="8">
-        <v>1049</v>
+        <v>825</v>
       </c>
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
@@ -4848,7 +5121,7 @@
         <v>12</v>
       </c>
       <c r="I9" s="8">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="J9" s="8">
         <v>0</v>
@@ -4857,14 +5130,14 @@
         <v>0</v>
       </c>
       <c r="L9" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M9" s="8">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="N9" s="8">
-        <v>438</v>
+        <v>222</v>
       </c>
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
@@ -4899,23 +5172,23 @@
         <v>12</v>
       </c>
       <c r="I10" s="8">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J10" s="8">
         <v>0</v>
       </c>
       <c r="K10" s="8">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L10" s="8">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M10" s="8">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N10" s="8">
-        <v>324</v>
+        <v>128</v>
       </c>
       <c r="O10" s="8"/>
       <c r="P10" s="8"/>
@@ -4950,23 +5223,23 @@
         <v>12</v>
       </c>
       <c r="I11" s="8">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="J11" s="8">
         <v>0</v>
       </c>
       <c r="K11" s="8">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L11" s="8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M11" s="8">
         <f t="shared" si="0"/>
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="N11" s="8">
-        <v>255</v>
+        <v>217</v>
       </c>
       <c r="O11" s="8"/>
       <c r="P11" s="8"/>
@@ -5001,7 +5274,7 @@
         <v>12</v>
       </c>
       <c r="I12" s="8">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="J12" s="8">
         <v>0</v>
@@ -5014,7 +5287,7 @@
       </c>
       <c r="M12" s="8">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="N12" s="8">
         <v>0</v>
@@ -5052,23 +5325,23 @@
         <v>12</v>
       </c>
       <c r="I13" s="8">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="J13" s="8">
         <v>0</v>
       </c>
       <c r="K13" s="8">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="L13" s="8">
         <v>0</v>
       </c>
       <c r="M13" s="8">
         <f t="shared" si="0"/>
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="N13" s="8">
-        <v>914</v>
+        <v>858</v>
       </c>
       <c r="O13" s="8"/>
       <c r="P13" s="8"/>
@@ -5119,7 +5392,7 @@
         <v>28</v>
       </c>
       <c r="N14" s="8">
-        <v>1201</v>
+        <v>1117</v>
       </c>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
@@ -5154,7 +5427,7 @@
         <v>12</v>
       </c>
       <c r="I15" s="8">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="J15" s="8">
         <v>0</v>
@@ -5163,14 +5436,14 @@
         <v>0</v>
       </c>
       <c r="L15" s="8">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M15" s="8">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
       <c r="N15" s="8">
-        <v>432</v>
+        <v>252</v>
       </c>
       <c r="O15" s="8"/>
       <c r="P15" s="8"/>
@@ -5205,7 +5478,7 @@
         <v>12</v>
       </c>
       <c r="I16" s="8">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="J16" s="8">
         <v>0</v>
@@ -5214,14 +5487,14 @@
         <v>0</v>
       </c>
       <c r="L16" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M16" s="8">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="N16" s="8">
-        <v>871</v>
+        <v>841</v>
       </c>
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
@@ -5272,7 +5545,7 @@
         <v>74</v>
       </c>
       <c r="N17" s="8">
-        <v>478</v>
+        <v>457</v>
       </c>
       <c r="O17" s="8"/>
       <c r="P17" s="8"/>
@@ -5307,7 +5580,7 @@
         <v>12</v>
       </c>
       <c r="I18" s="8">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J18" s="8">
         <v>0</v>
@@ -5316,14 +5589,14 @@
         <v>0</v>
       </c>
       <c r="L18" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="8">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N18" s="8">
-        <v>407</v>
+        <v>50</v>
       </c>
       <c r="O18" s="8"/>
       <c r="P18" s="8"/>
@@ -5358,7 +5631,7 @@
         <v>13</v>
       </c>
       <c r="I19" s="8">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J19" s="8">
         <v>0</v>
@@ -5371,10 +5644,10 @@
       </c>
       <c r="M19" s="8">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="N19" s="8">
-        <v>1042</v>
+        <v>1104</v>
       </c>
       <c r="O19" s="8"/>
       <c r="P19" s="8"/>
@@ -5409,7 +5682,7 @@
         <v>14</v>
       </c>
       <c r="I20" s="8">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J20" s="8">
         <v>0</v>
@@ -5422,10 +5695,10 @@
       </c>
       <c r="M20" s="8">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N20" s="8">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="O20" s="8"/>
       <c r="P20" s="8"/>
@@ -5460,7 +5733,7 @@
         <v>13</v>
       </c>
       <c r="I21" s="8">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J21" s="8">
         <v>0</v>
@@ -5469,14 +5742,14 @@
         <v>0</v>
       </c>
       <c r="L21" s="8">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M21" s="8">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="N21" s="8">
-        <v>489</v>
+        <v>115</v>
       </c>
       <c r="O21" s="8"/>
       <c r="P21" s="8"/>
@@ -5562,7 +5835,7 @@
         <v>12</v>
       </c>
       <c r="I23" s="8">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J23" s="8">
         <v>0</v>
@@ -5575,10 +5848,10 @@
       </c>
       <c r="M23" s="8">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="N23" s="8">
-        <v>16</v>
+        <v>163</v>
       </c>
       <c r="O23" s="8"/>
       <c r="P23" s="8"/>
@@ -5613,7 +5886,7 @@
         <v>14</v>
       </c>
       <c r="I24" s="8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J24" s="8">
         <v>0</v>
@@ -5626,10 +5899,10 @@
       </c>
       <c r="M24" s="8">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N24" s="8">
-        <v>775</v>
+        <v>703</v>
       </c>
       <c r="O24" s="8"/>
       <c r="P24" s="8"/>
@@ -5715,23 +5988,23 @@
         <v>12</v>
       </c>
       <c r="I26" s="8">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J26" s="8">
         <v>0</v>
       </c>
       <c r="K26" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L26" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M26" s="8">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="N26" s="8">
-        <v>686</v>
+        <v>738</v>
       </c>
       <c r="O26" s="8"/>
       <c r="P26" s="8"/>
@@ -5782,7 +6055,7 @@
         <v>24</v>
       </c>
       <c r="N27" s="8">
-        <v>853</v>
+        <v>1077</v>
       </c>
       <c r="O27" s="8"/>
       <c r="P27" s="8"/>
@@ -5817,7 +6090,7 @@
         <v>12</v>
       </c>
       <c r="I28" s="8">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J28" s="8">
         <v>0</v>
@@ -5830,7 +6103,7 @@
       </c>
       <c r="M28" s="8">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="N28" s="8">
         <v>0</v>
@@ -5874,14 +6147,14 @@
         <v>0</v>
       </c>
       <c r="K29" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L29" s="8">
         <v>0</v>
       </c>
       <c r="M29" s="8">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N29" s="8">
         <v>0</v>
@@ -5925,17 +6198,17 @@
         <v>0</v>
       </c>
       <c r="K30" s="8">
+        <v>0</v>
+      </c>
+      <c r="L30" s="8">
         <v>1</v>
-      </c>
-      <c r="L30" s="8">
-        <v>0</v>
       </c>
       <c r="M30" s="8">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N30" s="8">
-        <v>1073</v>
+        <v>1420</v>
       </c>
       <c r="O30" s="8"/>
       <c r="P30" s="8"/>
@@ -6021,23 +6294,23 @@
         <v>12</v>
       </c>
       <c r="I32" s="8">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J32" s="8">
         <v>0</v>
       </c>
       <c r="K32" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L32" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M32" s="8">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N32" s="8">
-        <v>762</v>
+        <v>720</v>
       </c>
       <c r="O32" s="8"/>
       <c r="P32" s="8"/>
@@ -6072,7 +6345,7 @@
         <v>12</v>
       </c>
       <c r="I33" s="8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J33" s="8">
         <v>0</v>
@@ -6085,10 +6358,10 @@
       </c>
       <c r="M33" s="8">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N33" s="8">
-        <v>1153</v>
+        <v>1109</v>
       </c>
       <c r="O33" s="8"/>
       <c r="P33" s="8"/>
@@ -6123,7 +6396,7 @@
         <v>12</v>
       </c>
       <c r="I34" s="8">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J34" s="8">
         <v>0</v>
@@ -6136,10 +6409,10 @@
       </c>
       <c r="M34" s="8">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="N34" s="8">
-        <v>1054</v>
+        <v>1021</v>
       </c>
       <c r="O34" s="8"/>
       <c r="P34" s="8"/>
@@ -6190,7 +6463,7 @@
         <v>15</v>
       </c>
       <c r="N35" s="8">
-        <v>497</v>
+        <v>643</v>
       </c>
       <c r="O35" s="8"/>
       <c r="P35" s="8"/>
@@ -6241,7 +6514,7 @@
         <v>12</v>
       </c>
       <c r="N36" s="8">
-        <v>764</v>
+        <v>737</v>
       </c>
       <c r="O36" s="8"/>
       <c r="P36" s="8"/>
@@ -6292,7 +6565,7 @@
         <v>33</v>
       </c>
       <c r="N37" s="8">
-        <v>938</v>
+        <v>1521</v>
       </c>
       <c r="O37" s="8"/>
       <c r="P37" s="8"/>
@@ -6327,7 +6600,7 @@
         <v>12</v>
       </c>
       <c r="I38" s="8">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J38" s="8">
         <v>0</v>
@@ -6340,10 +6613,10 @@
       </c>
       <c r="M38" s="8">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N38" s="8">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="O38" s="8"/>
       <c r="P38" s="8"/>
@@ -6378,7 +6651,7 @@
         <v>12</v>
       </c>
       <c r="I39" s="8">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J39" s="8">
         <v>0</v>
@@ -6391,10 +6664,10 @@
       </c>
       <c r="M39" s="8">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="N39" s="8">
-        <v>1489</v>
+        <v>1303</v>
       </c>
       <c r="O39" s="8"/>
       <c r="P39" s="8"/>
@@ -6445,7 +6718,7 @@
         <v>18</v>
       </c>
       <c r="N40" s="8">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="O40" s="8"/>
       <c r="P40" s="8"/>
@@ -6480,7 +6753,7 @@
         <v>12</v>
       </c>
       <c r="I41" s="8">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J41" s="8">
         <v>0</v>
@@ -6493,10 +6766,10 @@
       </c>
       <c r="M41" s="8">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="N41" s="8">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="O41" s="8"/>
       <c r="P41" s="8"/>
@@ -6531,7 +6804,7 @@
         <v>13</v>
       </c>
       <c r="I42" s="8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J42" s="8">
         <v>0</v>
@@ -6544,10 +6817,10 @@
       </c>
       <c r="M42" s="8">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N42" s="8">
-        <v>1027</v>
+        <v>1209</v>
       </c>
       <c r="O42" s="8"/>
       <c r="P42" s="8"/>
@@ -6582,7 +6855,7 @@
         <v>12</v>
       </c>
       <c r="I43" s="8">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J43" s="8">
         <v>0</v>
@@ -6595,10 +6868,10 @@
       </c>
       <c r="M43" s="8">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="N43" s="8">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O43" s="8"/>
       <c r="P43" s="8"/>
@@ -6633,23 +6906,23 @@
         <v>12</v>
       </c>
       <c r="I44" s="8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J44" s="8">
         <v>0</v>
       </c>
       <c r="K44" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L44" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M44" s="8">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N44" s="8">
-        <v>478</v>
+        <v>433</v>
       </c>
       <c r="O44" s="8"/>
       <c r="P44" s="8"/>
@@ -6700,7 +6973,7 @@
         <v>13</v>
       </c>
       <c r="N45" s="8">
-        <v>862</v>
+        <v>834</v>
       </c>
       <c r="O45" s="8"/>
       <c r="P45" s="8"/>
@@ -6735,7 +7008,7 @@
         <v>12</v>
       </c>
       <c r="I46" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J46" s="8">
         <v>0</v>
@@ -6748,10 +7021,10 @@
       </c>
       <c r="M46" s="8">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N46" s="8">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="O46" s="8"/>
       <c r="P46" s="8"/>
@@ -6786,7 +7059,7 @@
         <v>13</v>
       </c>
       <c r="I47" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J47" s="8">
         <v>0</v>
@@ -6799,10 +7072,10 @@
       </c>
       <c r="M47" s="8">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N47" s="8">
-        <v>1060</v>
+        <v>963</v>
       </c>
       <c r="O47" s="8"/>
       <c r="P47" s="8"/>
@@ -6853,7 +7126,7 @@
         <v>15</v>
       </c>
       <c r="N48" s="8">
-        <v>1309</v>
+        <v>1943</v>
       </c>
       <c r="O48" s="8"/>
       <c r="P48" s="8"/>
@@ -6888,7 +7161,7 @@
         <v>12</v>
       </c>
       <c r="I49" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J49" s="8">
         <v>0</v>
@@ -6901,10 +7174,10 @@
       </c>
       <c r="M49" s="8">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N49" s="8">
-        <v>978</v>
+        <v>923</v>
       </c>
       <c r="O49" s="8"/>
       <c r="P49" s="8"/>
@@ -6939,7 +7212,7 @@
         <v>15</v>
       </c>
       <c r="I50" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J50" s="8">
         <v>0</v>
@@ -6952,7 +7225,7 @@
       </c>
       <c r="M50" s="8">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N50" s="8">
         <v>143</v>
@@ -7006,7 +7279,7 @@
         <v>24</v>
       </c>
       <c r="N51" s="8">
-        <v>439</v>
+        <v>371</v>
       </c>
       <c r="O51" s="8"/>
       <c r="P51" s="8"/>
@@ -7041,7 +7314,7 @@
         <v>12</v>
       </c>
       <c r="I52" s="8">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="J52" s="8">
         <v>0</v>
@@ -7054,7 +7327,7 @@
       </c>
       <c r="M52" s="8">
         <f t="shared" si="0"/>
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="N52" s="8">
         <v>0</v>
@@ -7092,7 +7365,7 @@
         <v>12</v>
       </c>
       <c r="I53" s="8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J53" s="8">
         <v>0</v>
@@ -7105,10 +7378,10 @@
       </c>
       <c r="M53" s="8">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N53" s="8">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="O53" s="8"/>
       <c r="P53" s="8"/>
@@ -7152,14 +7425,14 @@
         <v>0</v>
       </c>
       <c r="L54" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N54" s="8">
-        <v>361</v>
+        <v>228</v>
       </c>
       <c r="O54" s="8"/>
       <c r="P54" s="8"/>
@@ -7194,7 +7467,7 @@
         <v>12</v>
       </c>
       <c r="I55" s="8">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="J55" s="8">
         <v>0</v>
@@ -7203,14 +7476,14 @@
         <v>0</v>
       </c>
       <c r="L55" s="8">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M55" s="8">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="N55" s="8">
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="O55" s="8"/>
       <c r="P55" s="8"/>
@@ -7296,7 +7569,7 @@
         <v>12</v>
       </c>
       <c r="I57" s="8">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J57" s="8">
         <v>0</v>
@@ -7305,14 +7578,14 @@
         <v>0</v>
       </c>
       <c r="L57" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M57" s="8">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N57" s="8">
-        <v>583</v>
+        <v>553</v>
       </c>
       <c r="O57" s="8"/>
       <c r="P57" s="8"/>
@@ -7347,7 +7620,7 @@
         <v>12</v>
       </c>
       <c r="I58" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J58" s="8">
         <v>0</v>
@@ -7360,10 +7633,10 @@
       </c>
       <c r="M58" s="8">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N58" s="8">
-        <v>663</v>
+        <v>641</v>
       </c>
       <c r="O58" s="8"/>
       <c r="P58" s="8"/>
@@ -7398,7 +7671,7 @@
         <v>13</v>
       </c>
       <c r="I59" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J59" s="8">
         <v>0</v>
@@ -7411,10 +7684,10 @@
       </c>
       <c r="M59" s="8">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N59" s="8">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="O59" s="8"/>
       <c r="P59" s="8"/>
@@ -7465,7 +7738,7 @@
         <v>5</v>
       </c>
       <c r="N60" s="8">
-        <v>684</v>
+        <v>645</v>
       </c>
       <c r="O60" s="8"/>
       <c r="P60" s="8"/>
@@ -7500,7 +7773,7 @@
         <v>12</v>
       </c>
       <c r="I61" s="8">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J61" s="8">
         <v>0</v>
@@ -7513,10 +7786,10 @@
       </c>
       <c r="M61" s="8">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="N61" s="8">
-        <v>505</v>
+        <v>265</v>
       </c>
       <c r="O61" s="8"/>
       <c r="P61" s="8"/>
@@ -7567,7 +7840,7 @@
         <v>8</v>
       </c>
       <c r="N62" s="8">
-        <v>402</v>
+        <v>372</v>
       </c>
       <c r="O62" s="8"/>
       <c r="P62" s="8"/>
@@ -7618,7 +7891,7 @@
         <v>4</v>
       </c>
       <c r="N63" s="8">
-        <v>266</v>
+        <v>205</v>
       </c>
       <c r="O63" s="8"/>
       <c r="P63" s="8"/>
@@ -7653,7 +7926,7 @@
         <v>13</v>
       </c>
       <c r="I64" s="8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J64" s="8">
         <v>0</v>
@@ -7666,10 +7939,10 @@
       </c>
       <c r="M64" s="8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N64" s="8">
-        <v>585</v>
+        <v>523</v>
       </c>
       <c r="O64" s="8"/>
       <c r="P64" s="8"/>
@@ -7704,7 +7977,7 @@
         <v>12</v>
       </c>
       <c r="I65" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J65" s="8">
         <v>0</v>
@@ -7717,10 +7990,10 @@
       </c>
       <c r="M65" s="8">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N65" s="8">
-        <v>976</v>
+        <v>926</v>
       </c>
       <c r="O65" s="8"/>
       <c r="P65" s="8"/>
@@ -7771,7 +8044,7 @@
         <v>4</v>
       </c>
       <c r="N66" s="8">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="O66" s="8"/>
       <c r="P66" s="8"/>
@@ -7822,7 +8095,7 @@
         <v>4</v>
       </c>
       <c r="N67" s="8">
-        <v>139</v>
+        <v>1</v>
       </c>
       <c r="O67" s="8"/>
       <c r="P67" s="8"/>
@@ -7873,7 +8146,7 @@
         <v>5</v>
       </c>
       <c r="N68" s="8">
-        <v>959</v>
+        <v>934</v>
       </c>
       <c r="O68" s="8"/>
       <c r="P68" s="8"/>
@@ -7908,7 +8181,7 @@
         <v>12</v>
       </c>
       <c r="I69" s="8">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J69" s="8">
         <v>0</v>
@@ -7921,10 +8194,10 @@
       </c>
       <c r="M69" s="8">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N69" s="8">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="O69" s="8"/>
       <c r="P69" s="8"/>
@@ -7975,7 +8248,7 @@
         <v>2</v>
       </c>
       <c r="N70" s="8">
-        <v>599</v>
+        <v>579</v>
       </c>
       <c r="O70" s="8"/>
       <c r="P70" s="8"/>
@@ -8010,7 +8283,7 @@
         <v>12</v>
       </c>
       <c r="I71" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J71" s="8">
         <v>0</v>
@@ -8023,7 +8296,7 @@
       </c>
       <c r="M71" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N71" s="8">
         <v>0</v>
@@ -8061,7 +8334,7 @@
         <v>12</v>
       </c>
       <c r="I72" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J72" s="8">
         <v>0</v>
@@ -8074,10 +8347,10 @@
       </c>
       <c r="M72" s="8">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N72" s="8">
-        <v>633</v>
+        <v>671</v>
       </c>
       <c r="O72" s="8"/>
       <c r="P72" s="8"/>
@@ -8112,7 +8385,7 @@
         <v>12</v>
       </c>
       <c r="I73" s="8">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="J73" s="8">
         <v>0</v>
@@ -8125,10 +8398,10 @@
       </c>
       <c r="M73" s="8">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="N73" s="8">
-        <v>837</v>
+        <v>812</v>
       </c>
       <c r="O73" s="8"/>
       <c r="P73" s="8"/>
@@ -8163,23 +8436,23 @@
         <v>14</v>
       </c>
       <c r="I74" s="8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J74" s="8">
         <v>0</v>
       </c>
       <c r="K74" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L74" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M74" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N74" s="8">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="O74" s="8"/>
       <c r="P74" s="8"/>
@@ -8265,7 +8538,7 @@
         <v>13</v>
       </c>
       <c r="I76" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J76" s="8">
         <v>0</v>
@@ -8278,10 +8551,10 @@
       </c>
       <c r="M76" s="8">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N76" s="8">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="O76" s="8"/>
       <c r="P76" s="8"/>
@@ -8332,7 +8605,7 @@
         <v>5</v>
       </c>
       <c r="N77" s="8">
-        <v>886</v>
+        <v>764</v>
       </c>
       <c r="O77" s="8"/>
       <c r="P77" s="8"/>
@@ -8373,17 +8646,17 @@
         <v>0</v>
       </c>
       <c r="K78" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L78" s="8">
         <v>0</v>
       </c>
       <c r="M78" s="8">
         <f t="shared" si="1"/>
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N78" s="8">
-        <v>621</v>
+        <v>559</v>
       </c>
       <c r="O78" s="8"/>
       <c r="P78" s="8"/>
@@ -8434,7 +8707,7 @@
         <v>6</v>
       </c>
       <c r="N79" s="8">
-        <v>202</v>
+        <v>114</v>
       </c>
       <c r="O79" s="8"/>
       <c r="P79" s="8"/>
@@ -8587,7 +8860,7 @@
         <v>5</v>
       </c>
       <c r="N82" s="8">
-        <v>325</v>
+        <v>297</v>
       </c>
       <c r="O82" s="8"/>
       <c r="P82" s="8"/>
@@ -8638,7 +8911,7 @@
         <v>4</v>
       </c>
       <c r="N83" s="8">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="O83" s="8"/>
       <c r="P83" s="8"/>
@@ -8740,7 +9013,7 @@
         <v>5</v>
       </c>
       <c r="N85" s="8">
-        <v>538</v>
+        <v>527</v>
       </c>
       <c r="O85" s="8"/>
       <c r="P85" s="8"/>
@@ -8775,7 +9048,7 @@
         <v>12</v>
       </c>
       <c r="I86" s="8">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J86" s="8">
         <v>0</v>
@@ -8784,14 +9057,14 @@
         <v>0</v>
       </c>
       <c r="L86" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M86" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N86" s="8">
-        <v>604</v>
+        <v>468</v>
       </c>
       <c r="O86" s="8"/>
       <c r="P86" s="8"/>
@@ -8826,7 +9099,7 @@
         <v>13</v>
       </c>
       <c r="I87" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J87" s="8">
         <v>0</v>
@@ -8839,10 +9112,10 @@
       </c>
       <c r="M87" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N87" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O87" s="8"/>
       <c r="P87" s="8"/>
@@ -8893,7 +9166,7 @@
         <v>12</v>
       </c>
       <c r="N88" s="8">
-        <v>592</v>
+        <v>458</v>
       </c>
       <c r="O88" s="8"/>
       <c r="P88" s="8"/>
@@ -8928,7 +9201,7 @@
         <v>12</v>
       </c>
       <c r="I89" s="8">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J89" s="8">
         <v>0</v>
@@ -8941,10 +9214,10 @@
       </c>
       <c r="M89" s="8">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N89" s="8">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="O89" s="8"/>
       <c r="P89" s="8"/>
@@ -9030,23 +9303,23 @@
         <v>12</v>
       </c>
       <c r="I91" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J91" s="8">
         <v>0</v>
       </c>
       <c r="K91" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L91" s="8">
         <v>0</v>
       </c>
       <c r="M91" s="8">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N91" s="8">
-        <v>1222</v>
+        <v>1137</v>
       </c>
       <c r="O91" s="8"/>
       <c r="P91" s="8"/>
@@ -9090,14 +9363,14 @@
         <v>0</v>
       </c>
       <c r="L92" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" s="8">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N92" s="8">
-        <v>389</v>
+        <v>237</v>
       </c>
       <c r="O92" s="8"/>
       <c r="P92" s="8"/>
@@ -9132,23 +9405,23 @@
         <v>13</v>
       </c>
       <c r="I93" s="8">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J93" s="8">
         <v>0</v>
       </c>
       <c r="K93" s="8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L93" s="8">
         <v>0</v>
       </c>
       <c r="M93" s="8">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N93" s="8">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="O93" s="8"/>
       <c r="P93" s="8"/>
@@ -9234,7 +9507,7 @@
         <v>12</v>
       </c>
       <c r="I95" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J95" s="8">
         <v>0</v>
@@ -9247,10 +9520,10 @@
       </c>
       <c r="M95" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N95" s="8">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="O95" s="8"/>
       <c r="P95" s="8"/>
@@ -9301,7 +9574,7 @@
         <v>7</v>
       </c>
       <c r="N96" s="8">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="O96" s="8"/>
       <c r="P96" s="8"/>
@@ -9336,7 +9609,7 @@
         <v>14</v>
       </c>
       <c r="I97" s="8">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J97" s="8">
         <v>0</v>
@@ -9345,14 +9618,14 @@
         <v>0</v>
       </c>
       <c r="L97" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M97" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N97" s="8">
-        <v>277</v>
+        <v>247</v>
       </c>
       <c r="O97" s="8"/>
       <c r="P97" s="8"/>
@@ -9556,7 +9829,7 @@
         <v>2</v>
       </c>
       <c r="N101" s="8">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="O101" s="8"/>
       <c r="P101" s="8"/>
@@ -9591,23 +9864,23 @@
         <v>14</v>
       </c>
       <c r="I102" s="8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J102" s="8">
         <v>0</v>
       </c>
       <c r="K102" s="8">
+        <v>0</v>
+      </c>
+      <c r="L102" s="8">
         <v>2</v>
-      </c>
-      <c r="L102" s="8">
-        <v>0</v>
       </c>
       <c r="M102" s="8">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N102" s="8">
-        <v>517</v>
+        <v>496</v>
       </c>
       <c r="O102" s="8"/>
       <c r="P102" s="8"/>
@@ -9648,17 +9921,17 @@
         <v>0</v>
       </c>
       <c r="K103" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L103" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M103" s="8">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N103" s="8">
-        <v>539</v>
+        <v>494</v>
       </c>
       <c r="O103" s="8"/>
       <c r="P103" s="8"/>
@@ -9760,7 +10033,7 @@
         <v>8</v>
       </c>
       <c r="N105" s="8">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="O105" s="8"/>
       <c r="P105" s="8"/>
@@ -9897,7 +10170,7 @@
         <v>15</v>
       </c>
       <c r="I108" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J108" s="8">
         <v>0</v>
@@ -9910,7 +10183,7 @@
       </c>
       <c r="M108" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N108" s="8">
         <v>0</v>
@@ -9964,7 +10237,7 @@
         <v>5</v>
       </c>
       <c r="N109" s="8">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O109" s="8"/>
       <c r="P109" s="8"/>
@@ -10101,23 +10374,23 @@
         <v>12</v>
       </c>
       <c r="I112" s="8">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="J112" s="8">
         <v>0</v>
       </c>
       <c r="K112" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L112" s="8">
         <v>0</v>
       </c>
       <c r="M112" s="8">
         <f t="shared" si="1"/>
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="N112" s="8">
-        <v>0</v>
+        <v>953</v>
       </c>
       <c r="O112" s="8"/>
       <c r="P112" s="8"/>
@@ -10152,7 +10425,7 @@
         <v>12</v>
       </c>
       <c r="I113" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J113" s="8">
         <v>0</v>
@@ -10165,10 +10438,10 @@
       </c>
       <c r="M113" s="8">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N113" s="8">
-        <v>1151</v>
+        <v>1042</v>
       </c>
       <c r="O113" s="8"/>
       <c r="P113" s="8"/>
@@ -10219,7 +10492,7 @@
         <v>9</v>
       </c>
       <c r="N114" s="8">
-        <v>605</v>
+        <v>956</v>
       </c>
       <c r="O114" s="8"/>
       <c r="P114" s="8"/>
@@ -10254,7 +10527,7 @@
         <v>13</v>
       </c>
       <c r="I115" s="8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J115" s="8">
         <v>0</v>
@@ -10267,10 +10540,10 @@
       </c>
       <c r="M115" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N115" s="8">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="O115" s="8"/>
       <c r="P115" s="8"/>
@@ -10314,14 +10587,14 @@
         <v>0</v>
       </c>
       <c r="L116" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M116" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N116" s="8">
-        <v>825</v>
+        <v>802</v>
       </c>
       <c r="O116" s="8"/>
       <c r="P116" s="8"/>
@@ -10356,7 +10629,7 @@
         <v>12</v>
       </c>
       <c r="I117" s="8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J117" s="8">
         <v>0</v>
@@ -10369,10 +10642,10 @@
       </c>
       <c r="M117" s="8">
         <f t="shared" si="1"/>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N117" s="8">
-        <v>458</v>
+        <v>385</v>
       </c>
       <c r="O117" s="8"/>
       <c r="P117" s="8"/>
@@ -10423,7 +10696,7 @@
         <v>7</v>
       </c>
       <c r="N118" s="8">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="O118" s="8"/>
       <c r="P118" s="8"/>
@@ -10474,7 +10747,7 @@
         <v>8</v>
       </c>
       <c r="N119" s="8">
-        <v>545</v>
+        <v>521</v>
       </c>
       <c r="O119" s="8"/>
       <c r="P119" s="8"/>
@@ -10509,7 +10782,7 @@
         <v>14</v>
       </c>
       <c r="I120" s="8">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J120" s="8">
         <v>0</v>
@@ -10522,10 +10795,10 @@
       </c>
       <c r="M120" s="8">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N120" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O120" s="8"/>
       <c r="P120" s="8"/>
@@ -10627,7 +10900,7 @@
         <v>2</v>
       </c>
       <c r="N122" s="8">
-        <v>1033</v>
+        <v>1024</v>
       </c>
       <c r="O122" s="8"/>
       <c r="P122" s="8"/>
@@ -10780,7 +11053,7 @@
         <v>7</v>
       </c>
       <c r="N125" s="8">
-        <v>296</v>
+        <v>245</v>
       </c>
       <c r="O125" s="8"/>
       <c r="P125" s="8"/>
@@ -10933,7 +11206,7 @@
         <v>4</v>
       </c>
       <c r="N128" s="8">
-        <v>836</v>
+        <v>826</v>
       </c>
       <c r="O128" s="8"/>
       <c r="P128" s="8"/>
@@ -11025,17 +11298,17 @@
         <v>0</v>
       </c>
       <c r="K130" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L130" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M130" s="8">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N130" s="8">
-        <v>335</v>
+        <v>315</v>
       </c>
       <c r="O130" s="8"/>
       <c r="P130" s="8"/>
@@ -11086,7 +11359,7 @@
         <v>3</v>
       </c>
       <c r="N131" s="8">
-        <v>496</v>
+        <v>472</v>
       </c>
       <c r="O131" s="8"/>
       <c r="P131" s="8"/>
@@ -11121,7 +11394,7 @@
         <v>12</v>
       </c>
       <c r="I132" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J132" s="8">
         <v>0</v>
@@ -11134,10 +11407,10 @@
       </c>
       <c r="M132" s="8">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N132" s="8">
-        <v>859</v>
+        <v>848</v>
       </c>
       <c r="O132" s="8"/>
       <c r="P132" s="8"/>
@@ -11172,7 +11445,7 @@
         <v>12</v>
       </c>
       <c r="I133" s="8">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J133" s="8">
         <v>0</v>
@@ -11185,10 +11458,10 @@
       </c>
       <c r="M133" s="8">
         <f t="shared" si="2"/>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N133" s="8">
-        <v>359</v>
+        <v>254</v>
       </c>
       <c r="O133" s="8"/>
       <c r="P133" s="8"/>
@@ -11274,7 +11547,7 @@
         <v>15</v>
       </c>
       <c r="I135" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J135" s="8">
         <v>0</v>
@@ -11287,10 +11560,10 @@
       </c>
       <c r="M135" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N135" s="8">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="O135" s="8"/>
       <c r="P135" s="8"/>
@@ -11325,23 +11598,23 @@
         <v>14</v>
       </c>
       <c r="I136" s="8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J136" s="8">
         <v>0</v>
       </c>
       <c r="K136" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L136" s="8">
         <v>0</v>
       </c>
       <c r="M136" s="8">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N136" s="8">
-        <v>565</v>
+        <v>506</v>
       </c>
       <c r="O136" s="8"/>
       <c r="P136" s="8"/>
@@ -11392,7 +11665,7 @@
         <v>3</v>
       </c>
       <c r="N137" s="8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O137" s="8"/>
       <c r="P137" s="8"/>
@@ -11443,7 +11716,7 @@
         <v>3</v>
       </c>
       <c r="N138" s="8">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="O138" s="8"/>
       <c r="P138" s="8"/>
@@ -11478,7 +11751,7 @@
         <v>15</v>
       </c>
       <c r="I139" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J139" s="8">
         <v>0</v>
@@ -11491,7 +11764,7 @@
       </c>
       <c r="M139" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N139" s="8">
         <v>0</v>
@@ -11545,7 +11818,7 @@
         <v>2</v>
       </c>
       <c r="N140" s="8">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="O140" s="8"/>
       <c r="P140" s="8"/>
@@ -11580,7 +11853,7 @@
         <v>13</v>
       </c>
       <c r="I141" s="8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J141" s="8">
         <v>0</v>
@@ -11593,10 +11866,10 @@
       </c>
       <c r="M141" s="8">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N141" s="8">
-        <v>556</v>
+        <v>575</v>
       </c>
       <c r="O141" s="8"/>
       <c r="P141" s="8"/>
@@ -11682,7 +11955,7 @@
         <v>13</v>
       </c>
       <c r="I143" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J143" s="8">
         <v>0</v>
@@ -11695,10 +11968,10 @@
       </c>
       <c r="M143" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N143" s="8">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="O143" s="8"/>
       <c r="P143" s="8"/>
@@ -11800,7 +12073,7 @@
         <v>4</v>
       </c>
       <c r="N145" s="8">
-        <v>856</v>
+        <v>844</v>
       </c>
       <c r="O145" s="8"/>
       <c r="P145" s="8"/>
@@ -11886,7 +12159,7 @@
         <v>14</v>
       </c>
       <c r="I147" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J147" s="8">
         <v>0</v>
@@ -11899,10 +12172,10 @@
       </c>
       <c r="M147" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N147" s="8">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="O147" s="8"/>
       <c r="P147" s="8"/>
@@ -11953,7 +12226,7 @@
         <v>3</v>
       </c>
       <c r="N148" s="8">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O148" s="8"/>
       <c r="P148" s="8"/>
@@ -11988,7 +12261,7 @@
         <v>12</v>
       </c>
       <c r="I149" s="8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J149" s="8">
         <v>0</v>
@@ -12001,10 +12274,10 @@
       </c>
       <c r="M149" s="8">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N149" s="8">
-        <v>325</v>
+        <v>279</v>
       </c>
       <c r="O149" s="8"/>
       <c r="P149" s="8"/>
@@ -12039,7 +12312,7 @@
         <v>12</v>
       </c>
       <c r="I150" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J150" s="8">
         <v>0</v>
@@ -12052,10 +12325,10 @@
       </c>
       <c r="M150" s="8">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N150" s="8">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="O150" s="8"/>
       <c r="P150" s="8"/>
@@ -12106,7 +12379,7 @@
         <v>3</v>
       </c>
       <c r="N151" s="8">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="O151" s="8"/>
       <c r="P151" s="8"/>
@@ -12157,7 +12430,7 @@
         <v>3</v>
       </c>
       <c r="N152" s="8">
-        <v>238</v>
+        <v>123</v>
       </c>
       <c r="O152" s="8"/>
       <c r="P152" s="8"/>
@@ -12192,7 +12465,7 @@
         <v>13</v>
       </c>
       <c r="I153" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J153" s="8">
         <v>0</v>
@@ -12201,14 +12474,14 @@
         <v>0</v>
       </c>
       <c r="L153" s="8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M153" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N153" s="8">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="O153" s="8"/>
       <c r="P153" s="8"/>
@@ -12565,7 +12838,7 @@
         <v>3</v>
       </c>
       <c r="N160" s="8">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="O160" s="8"/>
       <c r="P160" s="8"/>
@@ -12616,7 +12889,7 @@
         <v>6</v>
       </c>
       <c r="N161" s="8">
-        <v>487</v>
+        <v>455</v>
       </c>
       <c r="O161" s="8"/>
       <c r="P161" s="8"/>
@@ -12651,7 +12924,7 @@
         <v>13</v>
       </c>
       <c r="I162" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J162" s="8">
         <v>0</v>
@@ -12664,10 +12937,10 @@
       </c>
       <c r="M162" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N162" s="8">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="O162" s="8"/>
       <c r="P162" s="8"/>
@@ -12769,7 +13042,7 @@
         <v>3</v>
       </c>
       <c r="N164" s="8">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="O164" s="8"/>
       <c r="P164" s="8"/>
@@ -12820,7 +13093,7 @@
         <v>10</v>
       </c>
       <c r="N165" s="8">
-        <v>1363</v>
+        <v>1310</v>
       </c>
       <c r="O165" s="8"/>
       <c r="P165" s="8"/>
@@ -12871,7 +13144,7 @@
         <v>4</v>
       </c>
       <c r="N166" s="8">
-        <v>906</v>
+        <v>884</v>
       </c>
       <c r="O166" s="8"/>
       <c r="P166" s="8"/>
@@ -12957,7 +13230,7 @@
         <v>14</v>
       </c>
       <c r="I168" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J168" s="8">
         <v>0</v>
@@ -12970,10 +13243,10 @@
       </c>
       <c r="M168" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N168" s="8">
-        <v>419</v>
+        <v>383</v>
       </c>
       <c r="O168" s="8"/>
       <c r="P168" s="8"/>
@@ -13075,7 +13348,7 @@
         <v>4</v>
       </c>
       <c r="N170" s="8">
-        <v>695</v>
+        <v>666</v>
       </c>
       <c r="O170" s="8"/>
       <c r="P170" s="8"/>
@@ -13228,7 +13501,7 @@
         <v>2</v>
       </c>
       <c r="N173" s="8">
-        <v>687</v>
+        <v>635</v>
       </c>
       <c r="O173" s="8"/>
       <c r="P173" s="8"/>
@@ -13381,7 +13654,7 @@
         <v>2</v>
       </c>
       <c r="N176" s="8">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="O176" s="8"/>
       <c r="P176" s="8"/>
@@ -13585,7 +13858,7 @@
         <v>8</v>
       </c>
       <c r="N180" s="8">
-        <v>620</v>
+        <v>591</v>
       </c>
       <c r="O180" s="8"/>
       <c r="P180" s="8"/>
@@ -13629,14 +13902,14 @@
         <v>0</v>
       </c>
       <c r="L181" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M181" s="8">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N181" s="8">
-        <v>144</v>
+        <v>117</v>
       </c>
       <c r="O181" s="8"/>
       <c r="P181" s="8"/>
@@ -13738,7 +14011,7 @@
         <v>6</v>
       </c>
       <c r="N183" s="8">
-        <v>502</v>
+        <v>478</v>
       </c>
       <c r="O183" s="8"/>
       <c r="P183" s="8"/>
@@ -13824,23 +14097,23 @@
         <v>12</v>
       </c>
       <c r="I185" s="8">
-        <v>427</v>
+        <v>387</v>
       </c>
       <c r="J185" s="8">
         <v>0</v>
       </c>
       <c r="K185" s="8">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="L185" s="8">
         <v>0</v>
       </c>
       <c r="M185" s="8">
         <f t="shared" si="2"/>
-        <v>499</v>
+        <v>469</v>
       </c>
       <c r="N185" s="8">
-        <v>1815</v>
+        <v>1743</v>
       </c>
       <c r="O185" s="8"/>
       <c r="P185" s="8"/>
@@ -13875,7 +14148,7 @@
         <v>12</v>
       </c>
       <c r="I186" s="8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J186" s="8">
         <v>0</v>
@@ -13888,10 +14161,10 @@
       </c>
       <c r="M186" s="8">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N186" s="8">
-        <v>970</v>
+        <v>945</v>
       </c>
       <c r="O186" s="8"/>
       <c r="P186" s="8"/>
@@ -13942,7 +14215,7 @@
         <v>2</v>
       </c>
       <c r="N187" s="8">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="O187" s="8"/>
       <c r="P187" s="8"/>
@@ -13977,7 +14250,7 @@
         <v>15</v>
       </c>
       <c r="I188" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J188" s="8">
         <v>0</v>
@@ -13990,10 +14263,10 @@
       </c>
       <c r="M188" s="8">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N188" s="8">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="O188" s="8"/>
       <c r="P188" s="8"/>
@@ -14079,7 +14352,7 @@
         <v>12</v>
       </c>
       <c r="I190" s="8">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J190" s="8">
         <v>0</v>
@@ -14088,14 +14361,14 @@
         <v>0</v>
       </c>
       <c r="L190" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M190" s="8">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N190" s="8">
-        <v>70</v>
+        <v>312</v>
       </c>
       <c r="O190" s="8"/>
       <c r="P190" s="8"/>
@@ -14146,7 +14419,7 @@
         <v>8</v>
       </c>
       <c r="N191" s="8">
-        <v>973</v>
+        <v>898</v>
       </c>
       <c r="O191" s="8"/>
       <c r="P191" s="8"/>
@@ -14283,7 +14556,7 @@
         <v>15</v>
       </c>
       <c r="I194" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J194" s="8">
         <v>0</v>
@@ -14296,10 +14569,10 @@
       </c>
       <c r="M194" s="8">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N194" s="8">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="O194" s="8"/>
       <c r="P194" s="8"/>
@@ -14436,7 +14709,7 @@
         <v>12</v>
       </c>
       <c r="I197" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J197" s="8">
         <v>0</v>
@@ -14449,10 +14722,10 @@
       </c>
       <c r="M197" s="8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N197" s="8">
-        <v>784</v>
+        <v>675</v>
       </c>
       <c r="O197" s="8"/>
       <c r="P197" s="8"/>
@@ -14538,7 +14811,7 @@
         <v>14</v>
       </c>
       <c r="I199" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J199" s="8">
         <v>0</v>
@@ -14551,7 +14824,7 @@
       </c>
       <c r="M199" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N199" s="8">
         <v>0</v>
@@ -14656,7 +14929,7 @@
         <v>2</v>
       </c>
       <c r="N201" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O201" s="8"/>
       <c r="P201" s="8"/>
@@ -14844,7 +15117,7 @@
         <v>16</v>
       </c>
       <c r="I205" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J205" s="8">
         <v>0</v>
@@ -14857,7 +15130,7 @@
       </c>
       <c r="M205" s="8">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N205" s="8">
         <v>0</v>
@@ -14946,13 +15219,13 @@
         <v>14</v>
       </c>
       <c r="I207" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J207" s="8">
         <v>0</v>
       </c>
       <c r="K207" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L207" s="8">
         <v>0</v>
@@ -14962,7 +15235,7 @@
         <v>5</v>
       </c>
       <c r="N207" s="8">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="O207" s="8"/>
       <c r="P207" s="8"/>
@@ -15013,7 +15286,7 @@
         <v>3</v>
       </c>
       <c r="N208" s="8">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="O208" s="8"/>
       <c r="P208" s="8"/>
@@ -15048,7 +15321,7 @@
         <v>12</v>
       </c>
       <c r="I209" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J209" s="8">
         <v>0</v>
@@ -15061,10 +15334,10 @@
       </c>
       <c r="M209" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N209" s="8">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="O209" s="8"/>
       <c r="P209" s="8"/>
@@ -15156,17 +15429,17 @@
         <v>0</v>
       </c>
       <c r="K211" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L211" s="8">
         <v>0</v>
       </c>
       <c r="M211" s="8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N211" s="8">
-        <v>768</v>
+        <v>738</v>
       </c>
       <c r="O211" s="8"/>
       <c r="P211" s="8"/>
@@ -15303,7 +15576,7 @@
         <v>14</v>
       </c>
       <c r="I214" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J214" s="8">
         <v>0</v>
@@ -15316,7 +15589,7 @@
       </c>
       <c r="M214" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N214" s="8">
         <v>469</v>
@@ -15370,7 +15643,7 @@
         <v>4</v>
       </c>
       <c r="N215" s="8">
-        <v>753</v>
+        <v>703</v>
       </c>
       <c r="O215" s="8"/>
       <c r="P215" s="8"/>
@@ -15472,7 +15745,7 @@
         <v>3</v>
       </c>
       <c r="N217" s="8">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O217" s="8"/>
       <c r="P217" s="8"/>
@@ -15574,7 +15847,7 @@
         <v>6</v>
       </c>
       <c r="N219" s="8">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="O219" s="8"/>
       <c r="P219" s="8"/>
@@ -15720,14 +15993,14 @@
         <v>0</v>
       </c>
       <c r="L222" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M222" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N222" s="8">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O222" s="8"/>
       <c r="P222" s="8"/>
@@ -15762,7 +16035,7 @@
         <v>15</v>
       </c>
       <c r="I223" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J223" s="8">
         <v>0</v>
@@ -15775,7 +16048,7 @@
       </c>
       <c r="M223" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N223" s="8">
         <v>0</v>
@@ -15813,7 +16086,7 @@
         <v>13</v>
       </c>
       <c r="I224" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J224" s="8">
         <v>0</v>
@@ -15826,10 +16099,10 @@
       </c>
       <c r="M224" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N224" s="8">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="O224" s="8"/>
       <c r="P224" s="8"/>
@@ -15880,7 +16153,7 @@
         <v>3</v>
       </c>
       <c r="N225" s="8">
-        <v>677</v>
+        <v>597</v>
       </c>
       <c r="O225" s="8"/>
       <c r="P225" s="8"/>
@@ -15966,7 +16239,7 @@
         <v>16</v>
       </c>
       <c r="I227" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J227" s="8">
         <v>0</v>
@@ -15979,7 +16252,7 @@
       </c>
       <c r="M227" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N227" s="8">
         <v>0</v>
@@ -16017,23 +16290,23 @@
         <v>15</v>
       </c>
       <c r="I228" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J228" s="8">
         <v>0</v>
       </c>
       <c r="K228" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L228" s="8">
         <v>0</v>
       </c>
       <c r="M228" s="8">
         <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="N228" s="8">
         <v>4</v>
-      </c>
-      <c r="N228" s="8">
-        <v>0</v>
       </c>
       <c r="O228" s="8"/>
       <c r="P228" s="8"/>
@@ -16084,7 +16357,7 @@
         <v>2</v>
       </c>
       <c r="N229" s="8">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="O229" s="8"/>
       <c r="P229" s="8"/>
@@ -16119,7 +16392,7 @@
         <v>15</v>
       </c>
       <c r="I230" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J230" s="8">
         <v>0</v>
@@ -16132,10 +16405,10 @@
       </c>
       <c r="M230" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N230" s="8">
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="O230" s="8"/>
       <c r="P230" s="8"/>
@@ -16237,7 +16510,7 @@
         <v>12</v>
       </c>
       <c r="N232" s="8">
-        <v>661</v>
+        <v>588</v>
       </c>
       <c r="O232" s="8"/>
       <c r="P232" s="8"/>
@@ -16272,7 +16545,7 @@
         <v>15</v>
       </c>
       <c r="I233" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J233" s="8">
         <v>0</v>
@@ -16285,10 +16558,10 @@
       </c>
       <c r="M233" s="8">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N233" s="8">
-        <v>689</v>
+        <v>663</v>
       </c>
       <c r="O233" s="8"/>
       <c r="P233" s="8"/>
@@ -16323,7 +16596,7 @@
         <v>15</v>
       </c>
       <c r="I234" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J234" s="8">
         <v>0</v>
@@ -16336,10 +16609,10 @@
       </c>
       <c r="M234" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N234" s="8">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="O234" s="8"/>
       <c r="P234" s="8"/>
@@ -16390,7 +16663,7 @@
         <v>3</v>
       </c>
       <c r="N235" s="8">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="O235" s="8"/>
       <c r="P235" s="8"/>
@@ -16482,17 +16755,17 @@
         <v>0</v>
       </c>
       <c r="K237" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L237" s="8">
         <v>0</v>
       </c>
       <c r="M237" s="8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N237" s="8">
-        <v>855</v>
+        <v>844</v>
       </c>
       <c r="O237" s="8"/>
       <c r="P237" s="8"/>
@@ -16543,7 +16816,7 @@
         <v>6</v>
       </c>
       <c r="N238" s="8">
-        <v>516</v>
+        <v>502</v>
       </c>
       <c r="O238" s="8"/>
       <c r="P238" s="8"/>
@@ -16578,7 +16851,7 @@
         <v>15</v>
       </c>
       <c r="I239" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J239" s="8">
         <v>0</v>
@@ -16591,10 +16864,10 @@
       </c>
       <c r="M239" s="8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N239" s="8">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="O239" s="8"/>
       <c r="P239" s="8"/>
@@ -16629,7 +16902,7 @@
         <v>13</v>
       </c>
       <c r="I240" s="8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J240" s="8">
         <v>0</v>
@@ -16642,10 +16915,10 @@
       </c>
       <c r="M240" s="8">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N240" s="8">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="O240" s="8"/>
       <c r="P240" s="8"/>
@@ -16696,7 +16969,7 @@
         <v>3</v>
       </c>
       <c r="N241" s="8">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="O241" s="8"/>
       <c r="P241" s="8"/>
@@ -16747,7 +17020,7 @@
         <v>3</v>
       </c>
       <c r="N242" s="8">
-        <v>699</v>
+        <v>687</v>
       </c>
       <c r="O242" s="8"/>
       <c r="P242" s="8"/>
@@ -16782,7 +17055,7 @@
         <v>15</v>
       </c>
       <c r="I243" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J243" s="8">
         <v>0</v>
@@ -16791,14 +17064,14 @@
         <v>0</v>
       </c>
       <c r="L243" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M243" s="8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N243" s="8">
-        <v>287</v>
+        <v>237</v>
       </c>
       <c r="O243" s="8"/>
       <c r="P243" s="8"/>
@@ -16951,7 +17224,7 @@
         <v>3</v>
       </c>
       <c r="N246" s="8">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="O246" s="8"/>
       <c r="P246" s="8"/>
@@ -16986,7 +17259,7 @@
         <v>13</v>
       </c>
       <c r="I247" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J247" s="8">
         <v>0</v>
@@ -16999,10 +17272,10 @@
       </c>
       <c r="M247" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N247" s="8">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="O247" s="8"/>
       <c r="P247" s="8"/>
@@ -17037,7 +17310,7 @@
         <v>12</v>
       </c>
       <c r="I248" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J248" s="8">
         <v>0</v>
@@ -17050,7 +17323,7 @@
       </c>
       <c r="M248" s="8">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N248" s="8">
         <v>0</v>
@@ -17155,7 +17428,7 @@
         <v>3</v>
       </c>
       <c r="N250" s="8">
-        <v>1472</v>
+        <v>1442</v>
       </c>
       <c r="O250" s="8"/>
       <c r="P250" s="8"/>
@@ -17206,7 +17479,7 @@
         <v>2</v>
       </c>
       <c r="N251" s="8">
-        <v>1273</v>
+        <v>1240</v>
       </c>
       <c r="O251" s="8"/>
       <c r="P251" s="8"/>
@@ -17257,7 +17530,7 @@
         <v>2</v>
       </c>
       <c r="N252" s="8">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="O252" s="8"/>
       <c r="P252" s="8"/>
@@ -17292,13 +17565,13 @@
         <v>14</v>
       </c>
       <c r="I253" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J253" s="8">
         <v>0</v>
       </c>
       <c r="K253" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L253" s="8">
         <v>0</v>
@@ -17308,7 +17581,7 @@
         <v>2</v>
       </c>
       <c r="N253" s="8">
-        <v>1226</v>
+        <v>1203</v>
       </c>
       <c r="O253" s="8"/>
       <c r="P253" s="8"/>
@@ -17359,7 +17632,7 @@
         <v>2</v>
       </c>
       <c r="N254" s="8">
-        <v>539</v>
+        <v>518</v>
       </c>
       <c r="O254" s="8"/>
       <c r="P254" s="8"/>
@@ -17410,7 +17683,7 @@
         <v>3</v>
       </c>
       <c r="N255" s="8">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="O255" s="8"/>
       <c r="P255" s="8"/>
@@ -17445,7 +17718,7 @@
         <v>14</v>
       </c>
       <c r="I256" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J256" s="8">
         <v>0</v>
@@ -17458,10 +17731,10 @@
       </c>
       <c r="M256" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N256" s="8">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="O256" s="8"/>
       <c r="P256" s="8"/>
@@ -17512,7 +17785,7 @@
         <v>4</v>
       </c>
       <c r="N257" s="8">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="O257" s="8"/>
       <c r="P257" s="8"/>
@@ -17649,7 +17922,7 @@
         <v>13</v>
       </c>
       <c r="I260" s="8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J260" s="8">
         <v>0</v>
@@ -17662,10 +17935,10 @@
       </c>
       <c r="M260" s="8">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N260" s="8">
-        <v>177</v>
+        <v>219</v>
       </c>
       <c r="O260" s="8"/>
       <c r="P260" s="8"/>
@@ -17700,7 +17973,7 @@
         <v>12</v>
       </c>
       <c r="I261" s="8">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J261" s="8">
         <v>0</v>
@@ -17713,10 +17986,10 @@
       </c>
       <c r="M261" s="8">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N261" s="8">
-        <v>1170</v>
+        <v>875</v>
       </c>
       <c r="O261" s="8"/>
       <c r="P261" s="8"/>
@@ -17751,23 +18024,23 @@
         <v>12</v>
       </c>
       <c r="I262" s="8">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J262" s="8">
         <v>0</v>
       </c>
       <c r="K262" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L262" s="8">
         <v>0</v>
       </c>
       <c r="M262" s="8">
         <f t="shared" si="4"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N262" s="8">
-        <v>401</v>
+        <v>366</v>
       </c>
       <c r="O262" s="8"/>
       <c r="P262" s="8"/>
@@ -17802,23 +18075,23 @@
         <v>12</v>
       </c>
       <c r="I263" s="8">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J263" s="8">
         <v>0</v>
       </c>
       <c r="K263" s="8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L263" s="8">
         <v>0</v>
       </c>
       <c r="M263" s="8">
         <f t="shared" si="4"/>
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N263" s="8">
-        <v>498</v>
+        <v>248</v>
       </c>
       <c r="O263" s="8"/>
       <c r="P263" s="8"/>
@@ -17869,7 +18142,7 @@
         <v>2</v>
       </c>
       <c r="N264" s="8">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="O264" s="8"/>
       <c r="P264" s="8"/>
@@ -17920,7 +18193,7 @@
         <v>2</v>
       </c>
       <c r="N265" s="8">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="O265" s="8"/>
       <c r="P265" s="8"/>
@@ -17971,7 +18244,7 @@
         <v>3</v>
       </c>
       <c r="N266" s="8">
-        <v>1569</v>
+        <v>1545</v>
       </c>
       <c r="O266" s="8"/>
       <c r="P266" s="8"/>
@@ -18022,7 +18295,7 @@
         <v>3</v>
       </c>
       <c r="N267" s="8">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="O267" s="8"/>
       <c r="P267" s="8"/>
@@ -18057,7 +18330,7 @@
         <v>15</v>
       </c>
       <c r="I268" s="8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J268" s="8">
         <v>0</v>
@@ -18070,10 +18343,10 @@
       </c>
       <c r="M268" s="8">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N268" s="8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O268" s="8"/>
       <c r="P268" s="8"/>
@@ -18108,23 +18381,23 @@
         <v>15</v>
       </c>
       <c r="I269" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J269" s="8">
         <v>0</v>
       </c>
       <c r="K269" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L269" s="8">
         <v>0</v>
       </c>
       <c r="M269" s="8">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N269" s="8">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="O269" s="8"/>
       <c r="P269" s="8"/>
@@ -18372,14 +18645,14 @@
         <v>0</v>
       </c>
       <c r="L274" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M274" s="8">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N274" s="8">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="O274" s="8"/>
       <c r="P274" s="8"/>
@@ -18430,7 +18703,7 @@
         <v>4</v>
       </c>
       <c r="N275" s="8">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="O275" s="8"/>
       <c r="P275" s="8"/>
@@ -18481,7 +18754,7 @@
         <v>3</v>
       </c>
       <c r="N276" s="8">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="O276" s="8"/>
       <c r="P276" s="8"/>
@@ -18583,7 +18856,7 @@
         <v>9</v>
       </c>
       <c r="N278" s="8">
-        <v>1773</v>
+        <v>1553</v>
       </c>
       <c r="O278" s="8"/>
       <c r="P278" s="8"/>
@@ -18627,14 +18900,14 @@
         <v>0</v>
       </c>
       <c r="L279" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M279" s="8">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N279" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O279" s="8"/>
       <c r="P279" s="8"/>
@@ -18822,13 +19095,13 @@
         <v>12</v>
       </c>
       <c r="I283" s="8">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J283" s="8">
         <v>0</v>
       </c>
       <c r="K283" s="8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L283" s="8">
         <v>0</v>
@@ -18838,7 +19111,7 @@
         <v>12</v>
       </c>
       <c r="N283" s="8">
-        <v>283</v>
+        <v>49</v>
       </c>
       <c r="O283" s="8"/>
       <c r="P283" s="8"/>
@@ -18873,23 +19146,23 @@
         <v>12</v>
       </c>
       <c r="I284" s="8">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="J284" s="8">
         <v>0</v>
       </c>
       <c r="K284" s="8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L284" s="8">
         <v>0</v>
       </c>
       <c r="M284" s="8">
         <f t="shared" si="4"/>
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="N284" s="8">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="O284" s="8"/>
       <c r="P284" s="8"/>
@@ -18940,7 +19213,7 @@
         <v>3</v>
       </c>
       <c r="N285" s="8">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="O285" s="8"/>
       <c r="P285" s="8"/>
@@ -18991,7 +19264,7 @@
         <v>4</v>
       </c>
       <c r="N286" s="8">
-        <v>1008</v>
+        <v>994</v>
       </c>
       <c r="O286" s="8"/>
       <c r="P286" s="8"/>
@@ -19042,7 +19315,7 @@
         <v>9</v>
       </c>
       <c r="N287" s="8">
-        <v>1156</v>
+        <v>1142</v>
       </c>
       <c r="O287" s="8"/>
       <c r="P287" s="8"/>
@@ -19093,7 +19366,7 @@
         <v>4</v>
       </c>
       <c r="N288" s="8">
-        <v>1508</v>
+        <v>1476</v>
       </c>
       <c r="O288" s="8"/>
       <c r="P288" s="8"/>
@@ -19137,14 +19410,14 @@
         <v>0</v>
       </c>
       <c r="L289" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M289" s="8">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N289" s="8">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="O289" s="8"/>
       <c r="P289" s="8"/>
@@ -19179,7 +19452,7 @@
         <v>14</v>
       </c>
       <c r="I290" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J290" s="8">
         <v>0</v>
@@ -19192,7 +19465,7 @@
       </c>
       <c r="M290" s="8">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N290" s="8">
         <v>0</v>
@@ -19230,7 +19503,7 @@
         <v>12</v>
       </c>
       <c r="I291" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J291" s="8">
         <v>0</v>
@@ -19243,10 +19516,10 @@
       </c>
       <c r="M291" s="8">
         <f t="shared" si="4"/>
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="N291" s="8">
-        <v>1334</v>
+        <v>2020</v>
       </c>
       <c r="O291" s="8"/>
       <c r="P291" s="8"/>
@@ -19297,7 +19570,7 @@
         <v>3</v>
       </c>
       <c r="N292" s="8">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O292" s="8"/>
       <c r="P292" s="8"/>
@@ -19383,23 +19656,23 @@
         <v>12</v>
       </c>
       <c r="I294" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J294" s="8">
         <v>0</v>
       </c>
       <c r="K294" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L294" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M294" s="8">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N294" s="8">
-        <v>1601</v>
+        <v>1518</v>
       </c>
       <c r="O294" s="8"/>
       <c r="P294" s="8"/>
@@ -19638,7 +19911,7 @@
         <v>14</v>
       </c>
       <c r="I299" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J299" s="8">
         <v>0</v>
@@ -19651,7 +19924,7 @@
       </c>
       <c r="M299" s="8">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N299" s="8">
         <v>0</v>
@@ -19689,7 +19962,7 @@
         <v>13</v>
       </c>
       <c r="I300" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J300" s="8">
         <v>0</v>
@@ -19702,7 +19975,7 @@
       </c>
       <c r="M300" s="8">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N300" s="8">
         <v>0</v>
@@ -19756,7 +20029,7 @@
         <v>6</v>
       </c>
       <c r="N301" s="8">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O301" s="8"/>
       <c r="P301" s="8"/>
@@ -19791,7 +20064,7 @@
         <v>13</v>
       </c>
       <c r="I302" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J302" s="8">
         <v>0</v>
@@ -19804,10 +20077,10 @@
       </c>
       <c r="M302" s="8">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N302" s="8">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="O302" s="8"/>
       <c r="P302" s="8"/>
@@ -19960,7 +20233,7 @@
         <v>8</v>
       </c>
       <c r="N305" s="8">
-        <v>546</v>
+        <v>521</v>
       </c>
       <c r="O305" s="8"/>
       <c r="P305" s="8"/>
@@ -19995,7 +20268,7 @@
         <v>13</v>
       </c>
       <c r="I306" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J306" s="8">
         <v>0</v>
@@ -20008,10 +20281,10 @@
       </c>
       <c r="M306" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N306" s="8">
-        <v>1149</v>
+        <v>1098</v>
       </c>
       <c r="O306" s="8"/>
       <c r="P306" s="8"/>
@@ -20062,7 +20335,7 @@
         <v>11</v>
       </c>
       <c r="N307" s="8">
-        <v>1076</v>
+        <v>1048</v>
       </c>
       <c r="O307" s="8"/>
       <c r="P307" s="8"/>
@@ -20113,7 +20386,7 @@
         <v>11</v>
       </c>
       <c r="N308" s="8">
-        <v>1048</v>
+        <v>1036</v>
       </c>
       <c r="O308" s="8"/>
       <c r="P308" s="8"/>
@@ -20215,7 +20488,7 @@
         <v>4</v>
       </c>
       <c r="N310" s="8">
-        <v>215</v>
+        <v>261</v>
       </c>
       <c r="O310" s="8"/>
       <c r="P310" s="8"/>
@@ -20317,7 +20590,7 @@
         <v>6</v>
       </c>
       <c r="N312" s="8">
-        <v>180</v>
+        <v>126</v>
       </c>
       <c r="O312" s="8"/>
       <c r="P312" s="8"/>
@@ -20352,7 +20625,7 @@
         <v>13</v>
       </c>
       <c r="I313" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J313" s="8">
         <v>0</v>
@@ -20365,7 +20638,7 @@
       </c>
       <c r="M313" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N313" s="8">
         <v>123</v>
@@ -20403,23 +20676,23 @@
         <v>12</v>
       </c>
       <c r="I314" s="8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J314" s="8">
         <v>0</v>
       </c>
       <c r="K314" s="8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L314" s="8">
         <v>0</v>
       </c>
       <c r="M314" s="8">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N314" s="8">
-        <v>472</v>
+        <v>445</v>
       </c>
       <c r="O314" s="8"/>
       <c r="P314" s="8"/>
@@ -20470,7 +20743,7 @@
         <v>8</v>
       </c>
       <c r="N315" s="8">
-        <v>359</v>
+        <v>237</v>
       </c>
       <c r="O315" s="8"/>
       <c r="P315" s="8"/>
@@ -20521,7 +20794,7 @@
         <v>7</v>
       </c>
       <c r="N316" s="8">
-        <v>763</v>
+        <v>746</v>
       </c>
       <c r="O316" s="8"/>
       <c r="P316" s="8"/>
@@ -20556,23 +20829,23 @@
         <v>12</v>
       </c>
       <c r="I317" s="8">
+        <v>3</v>
+      </c>
+      <c r="J317" s="8">
+        <v>0</v>
+      </c>
+      <c r="K317" s="8">
+        <v>0</v>
+      </c>
+      <c r="L317" s="8">
         <v>2</v>
-      </c>
-      <c r="J317" s="8">
-        <v>0</v>
-      </c>
-      <c r="K317" s="8">
-        <v>4</v>
-      </c>
-      <c r="L317" s="8">
-        <v>0</v>
       </c>
       <c r="M317" s="8">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N317" s="8">
-        <v>455</v>
+        <v>389</v>
       </c>
       <c r="O317" s="8"/>
       <c r="P317" s="8"/>
@@ -20607,7 +20880,7 @@
         <v>12</v>
       </c>
       <c r="I318" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J318" s="8">
         <v>0</v>
@@ -20616,14 +20889,14 @@
         <v>0</v>
       </c>
       <c r="L318" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M318" s="8">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N318" s="8">
-        <v>1178</v>
+        <v>951</v>
       </c>
       <c r="O318" s="8"/>
       <c r="P318" s="8"/>
@@ -20674,7 +20947,7 @@
         <v>4</v>
       </c>
       <c r="N319" s="8">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="O319" s="8"/>
       <c r="P319" s="8"/>
@@ -20725,7 +20998,7 @@
         <v>4</v>
       </c>
       <c r="N320" s="8">
-        <v>694</v>
+        <v>685</v>
       </c>
       <c r="O320" s="8"/>
       <c r="P320" s="8"/>
@@ -20760,7 +21033,7 @@
         <v>14</v>
       </c>
       <c r="I321" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J321" s="8">
         <v>0</v>
@@ -20773,10 +21046,10 @@
       </c>
       <c r="M321" s="8">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N321" s="8">
-        <v>572</v>
+        <v>561</v>
       </c>
       <c r="O321" s="8"/>
       <c r="P321" s="8"/>
@@ -20862,7 +21135,7 @@
         <v>14</v>
       </c>
       <c r="I323" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J323" s="8">
         <v>0</v>
@@ -20875,7 +21148,7 @@
       </c>
       <c r="M323" s="8">
         <f t="shared" ref="M323:M386" si="5">I323+J323+K323+L323</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N323" s="8">
         <v>93</v>
@@ -20922,14 +21195,14 @@
         <v>0</v>
       </c>
       <c r="L324" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M324" s="8">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N324" s="8">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O324" s="8"/>
       <c r="P324" s="8"/>
@@ -20980,7 +21253,7 @@
         <v>3</v>
       </c>
       <c r="N325" s="8">
-        <v>538</v>
+        <v>501</v>
       </c>
       <c r="O325" s="8"/>
       <c r="P325" s="8"/>
@@ -21031,7 +21304,7 @@
         <v>3</v>
       </c>
       <c r="N326" s="8">
-        <v>1018</v>
+        <v>1013</v>
       </c>
       <c r="O326" s="8"/>
       <c r="P326" s="8"/>
@@ -21184,7 +21457,7 @@
         <v>4</v>
       </c>
       <c r="N329" s="8">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="O329" s="8"/>
       <c r="P329" s="8"/>
@@ -21235,7 +21508,7 @@
         <v>2</v>
       </c>
       <c r="N330" s="8">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O330" s="8"/>
       <c r="P330" s="8"/>
@@ -21270,7 +21543,7 @@
         <v>13</v>
       </c>
       <c r="I331" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J331" s="8">
         <v>0</v>
@@ -21283,7 +21556,7 @@
       </c>
       <c r="M331" s="8">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N331" s="8">
         <v>0</v>
@@ -21483,14 +21756,14 @@
         <v>0</v>
       </c>
       <c r="L335" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M335" s="8">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N335" s="8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O335" s="8"/>
       <c r="P335" s="8"/>
@@ -21541,7 +21814,7 @@
         <v>4</v>
       </c>
       <c r="N336" s="8">
-        <v>668</v>
+        <v>649</v>
       </c>
       <c r="O336" s="8"/>
       <c r="P336" s="8"/>
@@ -21576,7 +21849,7 @@
         <v>12</v>
       </c>
       <c r="I337" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J337" s="8">
         <v>0</v>
@@ -21589,10 +21862,10 @@
       </c>
       <c r="M337" s="8">
         <f t="shared" si="5"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N337" s="8">
-        <v>1228</v>
+        <v>1211</v>
       </c>
       <c r="O337" s="8"/>
       <c r="P337" s="8"/>
@@ -21627,7 +21900,7 @@
         <v>12</v>
       </c>
       <c r="I338" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J338" s="8">
         <v>0</v>
@@ -21636,14 +21909,14 @@
         <v>0</v>
       </c>
       <c r="L338" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M338" s="8">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N338" s="8">
-        <v>1475</v>
+        <v>1323</v>
       </c>
       <c r="O338" s="8"/>
       <c r="P338" s="8"/>
@@ -21694,7 +21967,7 @@
         <v>3</v>
       </c>
       <c r="N339" s="8">
-        <v>892</v>
+        <v>874</v>
       </c>
       <c r="O339" s="8"/>
       <c r="P339" s="8"/>
@@ -21729,23 +22002,23 @@
         <v>14</v>
       </c>
       <c r="I340" s="8">
+        <v>1</v>
+      </c>
+      <c r="J340" s="8">
+        <v>0</v>
+      </c>
+      <c r="K340" s="8">
+        <v>0</v>
+      </c>
+      <c r="L340" s="8">
         <v>5</v>
-      </c>
-      <c r="J340" s="8">
-        <v>0</v>
-      </c>
-      <c r="K340" s="8">
-        <v>1</v>
-      </c>
-      <c r="L340" s="8">
-        <v>0</v>
       </c>
       <c r="M340" s="8">
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="N340" s="8">
-        <v>917</v>
+        <v>842</v>
       </c>
       <c r="O340" s="8"/>
       <c r="P340" s="8"/>
@@ -21789,14 +22062,14 @@
         <v>0</v>
       </c>
       <c r="L341" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M341" s="8">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N341" s="8">
-        <v>416</v>
+        <v>400</v>
       </c>
       <c r="O341" s="8"/>
       <c r="P341" s="8"/>
@@ -21847,7 +22120,7 @@
         <v>4</v>
       </c>
       <c r="N342" s="8">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="O342" s="8"/>
       <c r="P342" s="8"/>
@@ -21898,7 +22171,7 @@
         <v>4</v>
       </c>
       <c r="N343" s="8">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="O343" s="8"/>
       <c r="P343" s="8"/>
@@ -21933,7 +22206,7 @@
         <v>12</v>
       </c>
       <c r="I344" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J344" s="8">
         <v>0</v>
@@ -21946,7 +22219,7 @@
       </c>
       <c r="M344" s="8">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N344" s="8">
         <v>0</v>
@@ -21984,7 +22257,7 @@
         <v>12</v>
       </c>
       <c r="I345" s="8">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J345" s="8">
         <v>0</v>
@@ -21997,7 +22270,7 @@
       </c>
       <c r="M345" s="8">
         <f t="shared" si="5"/>
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N345" s="8">
         <v>0</v>
@@ -22041,14 +22314,14 @@
         <v>0</v>
       </c>
       <c r="K346" s="8">
-        <v>304</v>
+        <v>0</v>
       </c>
       <c r="L346" s="8">
         <v>0</v>
       </c>
       <c r="M346" s="8">
         <f t="shared" si="5"/>
-        <v>304</v>
+        <v>0</v>
       </c>
       <c r="N346" s="8">
         <v>0</v>
@@ -22086,7 +22359,7 @@
         <v>13</v>
       </c>
       <c r="I347" s="8">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J347" s="8">
         <v>0</v>
@@ -22095,14 +22368,14 @@
         <v>0</v>
       </c>
       <c r="L347" s="8">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M347" s="8">
         <f t="shared" si="5"/>
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="N347" s="8">
-        <v>769</v>
+        <v>675</v>
       </c>
       <c r="O347" s="8"/>
       <c r="P347" s="9"/>
@@ -22137,7 +22410,7 @@
         <v>12</v>
       </c>
       <c r="I348" s="8">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="J348" s="8">
         <v>0</v>
@@ -22150,10 +22423,10 @@
       </c>
       <c r="M348" s="8">
         <f t="shared" si="5"/>
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="N348" s="8">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="O348" s="8"/>
       <c r="P348" s="9"/>
@@ -22357,7 +22630,7 @@
         <v>2</v>
       </c>
       <c r="N352" s="8">
-        <v>505</v>
+        <v>494</v>
       </c>
       <c r="O352" s="8"/>
       <c r="P352" s="9"/>
@@ -22494,7 +22767,7 @@
         <v>16</v>
       </c>
       <c r="I355" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J355" s="8">
         <v>0</v>
@@ -22507,10 +22780,10 @@
       </c>
       <c r="M355" s="8">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N355" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O355" s="8"/>
       <c r="P355" s="9"/>
@@ -22612,7 +22885,7 @@
         <v>0</v>
       </c>
       <c r="N357" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O357" s="8"/>
       <c r="P357" s="9"/>
@@ -22902,20 +23175,20 @@
         <v>12</v>
       </c>
       <c r="I363" s="8">
-        <v>536</v>
+        <v>609</v>
       </c>
       <c r="J363" s="8">
         <v>0</v>
       </c>
       <c r="K363" s="8">
-        <v>134</v>
+        <v>24</v>
       </c>
       <c r="L363" s="8">
         <v>0</v>
       </c>
       <c r="M363" s="8">
         <f t="shared" si="5"/>
-        <v>670</v>
+        <v>633</v>
       </c>
       <c r="N363" s="8">
         <v>1318</v>
@@ -23071,7 +23344,7 @@
         <v>2</v>
       </c>
       <c r="N366" s="8">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="O366" s="8"/>
       <c r="P366" s="9"/>
@@ -23106,20 +23379,20 @@
         <v>12</v>
       </c>
       <c r="I367" s="8">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="J367" s="8">
         <v>0</v>
       </c>
       <c r="K367" s="8">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L367" s="8">
         <v>0</v>
       </c>
       <c r="M367" s="8">
         <f t="shared" si="5"/>
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="N367" s="8">
         <v>0</v>
@@ -23157,7 +23430,7 @@
         <v>12</v>
       </c>
       <c r="I368" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J368" s="8">
         <v>0</v>
@@ -23166,14 +23439,14 @@
         <v>0</v>
       </c>
       <c r="L368" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M368" s="8">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N368" s="8">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="O368" s="8"/>
       <c r="P368" s="9"/>
@@ -23208,13 +23481,13 @@
         <v>15</v>
       </c>
       <c r="I369" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J369" s="8">
         <v>0</v>
       </c>
       <c r="K369" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L369" s="8">
         <v>0</v>
@@ -23224,7 +23497,7 @@
         <v>4</v>
       </c>
       <c r="N369" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O369" s="8"/>
       <c r="P369" s="9"/>
@@ -23326,7 +23599,7 @@
         <v>3</v>
       </c>
       <c r="N371" s="8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O371" s="8"/>
       <c r="P371" s="9"/>
@@ -23428,7 +23701,7 @@
         <v>5</v>
       </c>
       <c r="N373" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O373" s="8"/>
       <c r="P373" s="9"/>
@@ -23514,7 +23787,7 @@
         <v>12</v>
       </c>
       <c r="I375" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J375" s="8">
         <v>0</v>
@@ -23527,7 +23800,7 @@
       </c>
       <c r="M375" s="8">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N375" s="8">
         <v>0</v>
@@ -23973,7 +24246,7 @@
         <v>12</v>
       </c>
       <c r="I384" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J384" s="8">
         <v>0</v>
@@ -23986,10 +24259,10 @@
       </c>
       <c r="M384" s="8">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N384" s="8">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="O384" s="8"/>
       <c r="P384" s="9"/>
@@ -24024,7 +24297,7 @@
         <v>12</v>
       </c>
       <c r="I385" s="8">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="J385" s="8">
         <v>0</v>
@@ -24037,7 +24310,7 @@
       </c>
       <c r="M385" s="8">
         <f t="shared" si="5"/>
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="N385" s="8">
         <v>257</v>
@@ -24279,7 +24552,7 @@
         <v>12</v>
       </c>
       <c r="I390" s="8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J390" s="8">
         <v>0</v>
@@ -24292,10 +24565,10 @@
       </c>
       <c r="M390" s="8">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N390" s="8">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="O390" s="8"/>
       <c r="P390" s="7"/>
@@ -24585,7 +24858,7 @@
         <v>12</v>
       </c>
       <c r="I396" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J396" s="8">
         <v>0</v>
@@ -24598,7 +24871,7 @@
       </c>
       <c r="M396" s="8">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N396" s="8">
         <v>0</v>
@@ -24687,7 +24960,7 @@
         <v>15</v>
       </c>
       <c r="I398" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J398" s="8">
         <v>0</v>
@@ -24696,14 +24969,14 @@
         <v>0</v>
       </c>
       <c r="L398" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M398" s="8">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N398" s="8">
-        <v>248</v>
+        <v>272</v>
       </c>
       <c r="O398" s="7"/>
       <c r="P398" s="7"/>
@@ -24954,7 +25227,7 @@
         <v>0</v>
       </c>
       <c r="M403" s="8">
-        <f t="shared" ref="M403" si="7">I403+J403+K403+L403</f>
+        <f t="shared" ref="M403:M433" si="7">I403+J403+K403+L403</f>
         <v>0</v>
       </c>
       <c r="N403" s="8">
@@ -24968,20 +25241,49 @@
       <c r="T403" s="7"/>
     </row>
     <row r="404" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A404" s="7"/>
-      <c r="B404" s="7"/>
-      <c r="C404" s="7"/>
-      <c r="D404" s="7"/>
-      <c r="E404" s="7"/>
-      <c r="F404" s="7"/>
-      <c r="G404" s="7"/>
-      <c r="H404" s="7"/>
-      <c r="I404" s="7"/>
-      <c r="J404" s="7"/>
-      <c r="K404" s="7"/>
-      <c r="L404" s="7"/>
-      <c r="M404" s="7"/>
-      <c r="N404" s="7"/>
+      <c r="A404" s="6" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B404" s="7" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C404" s="7" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D404" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E404" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F404" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G404" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H404" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I404" s="8">
+        <v>0</v>
+      </c>
+      <c r="J404" s="8">
+        <v>0</v>
+      </c>
+      <c r="K404" s="8">
+        <v>0</v>
+      </c>
+      <c r="L404" s="8">
+        <v>2</v>
+      </c>
+      <c r="M404" s="8">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="N404" s="8">
+        <v>46</v>
+      </c>
       <c r="O404" s="7"/>
       <c r="P404" s="7"/>
       <c r="Q404" s="7"/>
@@ -24990,20 +25292,49 @@
       <c r="T404" s="7"/>
     </row>
     <row r="405" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A405" s="7"/>
-      <c r="B405" s="7"/>
-      <c r="C405" s="7"/>
-      <c r="D405" s="7"/>
-      <c r="E405" s="7"/>
-      <c r="F405" s="7"/>
-      <c r="G405" s="7"/>
-      <c r="H405" s="7"/>
-      <c r="I405" s="7"/>
-      <c r="J405" s="7"/>
-      <c r="K405" s="7"/>
-      <c r="L405" s="7"/>
-      <c r="M405" s="7"/>
-      <c r="N405" s="7"/>
+      <c r="A405" s="6" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B405" s="7" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C405" s="7" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D405" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E405" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F405" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G405" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H405" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I405" s="8">
+        <v>0</v>
+      </c>
+      <c r="J405" s="8">
+        <v>0</v>
+      </c>
+      <c r="K405" s="8">
+        <v>0</v>
+      </c>
+      <c r="L405" s="8">
+        <v>2</v>
+      </c>
+      <c r="M405" s="8">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="N405" s="8">
+        <v>435</v>
+      </c>
       <c r="O405" s="7"/>
       <c r="P405" s="7"/>
       <c r="Q405" s="7"/>
@@ -25012,20 +25343,49 @@
       <c r="T405" s="7"/>
     </row>
     <row r="406" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A406" s="7"/>
-      <c r="B406" s="7"/>
-      <c r="C406" s="7"/>
-      <c r="D406" s="7"/>
-      <c r="E406" s="7"/>
-      <c r="F406" s="7"/>
-      <c r="G406" s="7"/>
-      <c r="H406" s="7"/>
-      <c r="I406" s="7"/>
-      <c r="J406" s="7"/>
-      <c r="K406" s="7"/>
-      <c r="L406" s="7"/>
-      <c r="M406" s="7"/>
-      <c r="N406" s="7"/>
+      <c r="A406" s="6" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B406" s="7" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C406" s="7" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D406" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E406" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F406" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G406" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H406" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I406" s="8">
+        <v>0</v>
+      </c>
+      <c r="J406" s="8">
+        <v>0</v>
+      </c>
+      <c r="K406" s="8">
+        <v>0</v>
+      </c>
+      <c r="L406" s="8">
+        <v>1</v>
+      </c>
+      <c r="M406" s="8">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="N406" s="8">
+        <v>0</v>
+      </c>
       <c r="O406" s="7"/>
       <c r="P406" s="7"/>
       <c r="Q406" s="7"/>
@@ -25034,20 +25394,49 @@
       <c r="T406" s="7"/>
     </row>
     <row r="407" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A407" s="7"/>
-      <c r="B407" s="7"/>
-      <c r="C407" s="7"/>
-      <c r="D407" s="7"/>
-      <c r="E407" s="7"/>
-      <c r="F407" s="7"/>
-      <c r="G407" s="7"/>
-      <c r="H407" s="7"/>
-      <c r="I407" s="7"/>
-      <c r="J407" s="7"/>
-      <c r="K407" s="7"/>
-      <c r="L407" s="7"/>
-      <c r="M407" s="7"/>
-      <c r="N407" s="7"/>
+      <c r="A407" s="6" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B407" s="7" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C407" s="7" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D407" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E407" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F407" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G407" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H407" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I407" s="8">
+        <v>0</v>
+      </c>
+      <c r="J407" s="8">
+        <v>0</v>
+      </c>
+      <c r="K407" s="8">
+        <v>0</v>
+      </c>
+      <c r="L407" s="8">
+        <v>2</v>
+      </c>
+      <c r="M407" s="8">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="N407" s="8">
+        <v>0</v>
+      </c>
       <c r="O407" s="7"/>
       <c r="P407" s="7"/>
       <c r="Q407" s="7"/>
@@ -25056,20 +25445,49 @@
       <c r="T407" s="7"/>
     </row>
     <row r="408" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A408" s="7"/>
-      <c r="B408" s="7"/>
-      <c r="C408" s="7"/>
-      <c r="D408" s="7"/>
-      <c r="E408" s="7"/>
-      <c r="F408" s="7"/>
-      <c r="G408" s="7"/>
-      <c r="H408" s="7"/>
-      <c r="I408" s="7"/>
-      <c r="J408" s="7"/>
-      <c r="K408" s="7"/>
-      <c r="L408" s="7"/>
-      <c r="M408" s="7"/>
-      <c r="N408" s="7"/>
+      <c r="A408" s="6" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B408" s="7" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C408" s="7" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D408" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E408" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F408" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G408" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H408" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="I408" s="8">
+        <v>0</v>
+      </c>
+      <c r="J408" s="8">
+        <v>0</v>
+      </c>
+      <c r="K408" s="8">
+        <v>0</v>
+      </c>
+      <c r="L408" s="8">
+        <v>2</v>
+      </c>
+      <c r="M408" s="8">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="N408" s="8">
+        <v>19</v>
+      </c>
       <c r="O408" s="7"/>
       <c r="P408" s="7"/>
       <c r="Q408" s="7"/>
@@ -25078,20 +25496,49 @@
       <c r="T408" s="7"/>
     </row>
     <row r="409" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A409" s="7"/>
-      <c r="B409" s="7"/>
-      <c r="C409" s="7"/>
-      <c r="D409" s="7"/>
-      <c r="E409" s="7"/>
-      <c r="F409" s="7"/>
-      <c r="G409" s="7"/>
-      <c r="H409" s="7"/>
-      <c r="I409" s="7"/>
-      <c r="J409" s="7"/>
-      <c r="K409" s="7"/>
-      <c r="L409" s="7"/>
-      <c r="M409" s="7"/>
-      <c r="N409" s="7"/>
+      <c r="A409" s="6" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B409" s="7" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C409" s="7" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D409" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E409" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F409" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G409" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H409" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="I409" s="8">
+        <v>0</v>
+      </c>
+      <c r="J409" s="8">
+        <v>0</v>
+      </c>
+      <c r="K409" s="8">
+        <v>0</v>
+      </c>
+      <c r="L409" s="8">
+        <v>2</v>
+      </c>
+      <c r="M409" s="8">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="N409" s="8">
+        <v>10</v>
+      </c>
       <c r="O409" s="7"/>
       <c r="P409" s="7"/>
       <c r="Q409" s="7"/>
@@ -25100,20 +25547,49 @@
       <c r="T409" s="7"/>
     </row>
     <row r="410" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A410" s="7"/>
-      <c r="B410" s="7"/>
-      <c r="C410" s="7"/>
-      <c r="D410" s="7"/>
-      <c r="E410" s="7"/>
-      <c r="F410" s="7"/>
-      <c r="G410" s="7"/>
-      <c r="H410" s="7"/>
-      <c r="I410" s="7"/>
-      <c r="J410" s="7"/>
-      <c r="K410" s="7"/>
-      <c r="L410" s="7"/>
-      <c r="M410" s="7"/>
-      <c r="N410" s="7"/>
+      <c r="A410" s="6" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B410" s="7" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C410" s="7" t="s">
+        <v>1264</v>
+      </c>
+      <c r="D410" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E410" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F410" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G410" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H410" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I410" s="8">
+        <v>0</v>
+      </c>
+      <c r="J410" s="8">
+        <v>0</v>
+      </c>
+      <c r="K410" s="8">
+        <v>0</v>
+      </c>
+      <c r="L410" s="8">
+        <v>2</v>
+      </c>
+      <c r="M410" s="8">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="N410" s="8">
+        <v>112</v>
+      </c>
       <c r="O410" s="7"/>
       <c r="P410" s="7"/>
       <c r="Q410" s="7"/>
@@ -25122,20 +25598,49 @@
       <c r="T410" s="7"/>
     </row>
     <row r="411" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A411" s="7"/>
-      <c r="B411" s="7"/>
-      <c r="C411" s="7"/>
-      <c r="D411" s="7"/>
-      <c r="E411" s="7"/>
-      <c r="F411" s="7"/>
-      <c r="G411" s="7"/>
-      <c r="H411" s="7"/>
-      <c r="I411" s="7"/>
-      <c r="J411" s="7"/>
-      <c r="K411" s="7"/>
-      <c r="L411" s="7"/>
-      <c r="M411" s="7"/>
-      <c r="N411" s="7"/>
+      <c r="A411" s="6" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B411" s="7" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C411" s="7" t="s">
+        <v>1266</v>
+      </c>
+      <c r="D411" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E411" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F411" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G411" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H411" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I411" s="8">
+        <v>0</v>
+      </c>
+      <c r="J411" s="8">
+        <v>0</v>
+      </c>
+      <c r="K411" s="8">
+        <v>0</v>
+      </c>
+      <c r="L411" s="8">
+        <v>2</v>
+      </c>
+      <c r="M411" s="8">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="N411" s="8">
+        <v>96</v>
+      </c>
       <c r="O411" s="7"/>
       <c r="P411" s="7"/>
       <c r="Q411" s="7"/>
@@ -25144,20 +25649,49 @@
       <c r="T411" s="7"/>
     </row>
     <row r="412" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A412" s="7"/>
-      <c r="B412" s="7"/>
-      <c r="C412" s="7"/>
-      <c r="D412" s="7"/>
-      <c r="E412" s="7"/>
-      <c r="F412" s="7"/>
-      <c r="G412" s="7"/>
-      <c r="H412" s="7"/>
-      <c r="I412" s="7"/>
-      <c r="J412" s="7"/>
-      <c r="K412" s="7"/>
-      <c r="L412" s="7"/>
-      <c r="M412" s="7"/>
-      <c r="N412" s="7"/>
+      <c r="A412" s="6" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B412" s="7" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C412" s="7" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D412" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E412" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F412" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G412" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H412" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I412" s="8">
+        <v>0</v>
+      </c>
+      <c r="J412" s="8">
+        <v>0</v>
+      </c>
+      <c r="K412" s="8">
+        <v>0</v>
+      </c>
+      <c r="L412" s="8">
+        <v>2</v>
+      </c>
+      <c r="M412" s="8">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="N412" s="8">
+        <v>100</v>
+      </c>
       <c r="O412" s="7"/>
       <c r="P412" s="7"/>
       <c r="Q412" s="7"/>
@@ -25166,20 +25700,49 @@
       <c r="T412" s="7"/>
     </row>
     <row r="413" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A413" s="7"/>
-      <c r="B413" s="7"/>
-      <c r="C413" s="7"/>
-      <c r="D413" s="7"/>
-      <c r="E413" s="7"/>
-      <c r="F413" s="7"/>
-      <c r="G413" s="7"/>
-      <c r="H413" s="7"/>
-      <c r="I413" s="7"/>
-      <c r="J413" s="7"/>
-      <c r="K413" s="7"/>
-      <c r="L413" s="7"/>
-      <c r="M413" s="7"/>
-      <c r="N413" s="7"/>
+      <c r="A413" s="6" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B413" s="7" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C413" s="7" t="s">
+        <v>1270</v>
+      </c>
+      <c r="D413" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E413" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F413" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G413" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H413" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I413" s="8">
+        <v>0</v>
+      </c>
+      <c r="J413" s="8">
+        <v>0</v>
+      </c>
+      <c r="K413" s="8">
+        <v>0</v>
+      </c>
+      <c r="L413" s="8">
+        <v>2</v>
+      </c>
+      <c r="M413" s="8">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="N413" s="8">
+        <v>166</v>
+      </c>
       <c r="O413" s="7"/>
       <c r="P413" s="7"/>
       <c r="Q413" s="7"/>
@@ -25188,20 +25751,49 @@
       <c r="T413" s="7"/>
     </row>
     <row r="414" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A414" s="7"/>
-      <c r="B414" s="7"/>
-      <c r="C414" s="7"/>
-      <c r="D414" s="7"/>
-      <c r="E414" s="7"/>
-      <c r="F414" s="7"/>
-      <c r="G414" s="7"/>
-      <c r="H414" s="7"/>
-      <c r="I414" s="7"/>
-      <c r="J414" s="7"/>
-      <c r="K414" s="7"/>
-      <c r="L414" s="7"/>
-      <c r="M414" s="7"/>
-      <c r="N414" s="7"/>
+      <c r="A414" s="6" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B414" s="7" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C414" s="7" t="s">
+        <v>1272</v>
+      </c>
+      <c r="D414" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E414" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F414" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G414" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H414" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I414" s="8">
+        <v>0</v>
+      </c>
+      <c r="J414" s="8">
+        <v>0</v>
+      </c>
+      <c r="K414" s="8">
+        <v>0</v>
+      </c>
+      <c r="L414" s="8">
+        <v>3</v>
+      </c>
+      <c r="M414" s="8">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="N414" s="8">
+        <v>0</v>
+      </c>
       <c r="O414" s="7"/>
       <c r="P414" s="7"/>
       <c r="Q414" s="7"/>
@@ -25210,20 +25802,49 @@
       <c r="T414" s="7"/>
     </row>
     <row r="415" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A415" s="7"/>
-      <c r="B415" s="7"/>
-      <c r="C415" s="7"/>
-      <c r="D415" s="7"/>
-      <c r="E415" s="7"/>
-      <c r="F415" s="7"/>
-      <c r="G415" s="7"/>
-      <c r="H415" s="7"/>
-      <c r="I415" s="7"/>
-      <c r="J415" s="7"/>
-      <c r="K415" s="7"/>
-      <c r="L415" s="7"/>
-      <c r="M415" s="7"/>
-      <c r="N415" s="7"/>
+      <c r="A415" s="6" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B415" s="7" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C415" s="7" t="s">
+        <v>1274</v>
+      </c>
+      <c r="D415" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E415" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F415" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G415" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H415" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I415" s="8">
+        <v>0</v>
+      </c>
+      <c r="J415" s="8">
+        <v>0</v>
+      </c>
+      <c r="K415" s="8">
+        <v>0</v>
+      </c>
+      <c r="L415" s="8">
+        <v>3</v>
+      </c>
+      <c r="M415" s="8">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="N415" s="8">
+        <v>0</v>
+      </c>
       <c r="O415" s="7"/>
       <c r="P415" s="7"/>
       <c r="Q415" s="7"/>
@@ -25232,20 +25853,49 @@
       <c r="T415" s="7"/>
     </row>
     <row r="416" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A416" s="7"/>
-      <c r="B416" s="7"/>
-      <c r="C416" s="7"/>
-      <c r="D416" s="7"/>
-      <c r="E416" s="7"/>
-      <c r="F416" s="7"/>
-      <c r="G416" s="7"/>
-      <c r="H416" s="7"/>
-      <c r="I416" s="7"/>
-      <c r="J416" s="7"/>
-      <c r="K416" s="7"/>
-      <c r="L416" s="7"/>
-      <c r="M416" s="7"/>
-      <c r="N416" s="7"/>
+      <c r="A416" s="6" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B416" s="7" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C416" s="7" t="s">
+        <v>1276</v>
+      </c>
+      <c r="D416" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E416" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F416" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G416" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H416" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I416" s="8">
+        <v>0</v>
+      </c>
+      <c r="J416" s="8">
+        <v>0</v>
+      </c>
+      <c r="K416" s="8">
+        <v>0</v>
+      </c>
+      <c r="L416" s="8">
+        <v>3</v>
+      </c>
+      <c r="M416" s="8">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="N416" s="8">
+        <v>19</v>
+      </c>
       <c r="O416" s="7"/>
       <c r="P416" s="7"/>
       <c r="Q416" s="7"/>
@@ -25254,20 +25904,49 @@
       <c r="T416" s="7"/>
     </row>
     <row r="417" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A417" s="7"/>
-      <c r="B417" s="7"/>
-      <c r="C417" s="7"/>
-      <c r="D417" s="7"/>
-      <c r="E417" s="7"/>
-      <c r="F417" s="7"/>
-      <c r="G417" s="7"/>
-      <c r="H417" s="7"/>
-      <c r="I417" s="7"/>
-      <c r="J417" s="7"/>
-      <c r="K417" s="7"/>
-      <c r="L417" s="7"/>
-      <c r="M417" s="7"/>
-      <c r="N417" s="7"/>
+      <c r="A417" s="6" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B417" s="7" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C417" s="7" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D417" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E417" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F417" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G417" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H417" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I417" s="8">
+        <v>0</v>
+      </c>
+      <c r="J417" s="8">
+        <v>0</v>
+      </c>
+      <c r="K417" s="8">
+        <v>0</v>
+      </c>
+      <c r="L417" s="8">
+        <v>3</v>
+      </c>
+      <c r="M417" s="8">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="N417" s="8">
+        <v>25</v>
+      </c>
       <c r="O417" s="7"/>
       <c r="P417" s="7"/>
       <c r="Q417" s="7"/>
@@ -25276,20 +25955,49 @@
       <c r="T417" s="7"/>
     </row>
     <row r="418" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A418" s="7"/>
-      <c r="B418" s="7"/>
-      <c r="C418" s="7"/>
-      <c r="D418" s="7"/>
-      <c r="E418" s="7"/>
-      <c r="F418" s="7"/>
-      <c r="G418" s="7"/>
-      <c r="H418" s="7"/>
-      <c r="I418" s="7"/>
-      <c r="J418" s="7"/>
-      <c r="K418" s="7"/>
-      <c r="L418" s="7"/>
-      <c r="M418" s="7"/>
-      <c r="N418" s="7"/>
+      <c r="A418" s="6" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B418" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C418" s="7" t="s">
+        <v>1280</v>
+      </c>
+      <c r="D418" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E418" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F418" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G418" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H418" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I418" s="8">
+        <v>0</v>
+      </c>
+      <c r="J418" s="8">
+        <v>0</v>
+      </c>
+      <c r="K418" s="8">
+        <v>0</v>
+      </c>
+      <c r="L418" s="8">
+        <v>3</v>
+      </c>
+      <c r="M418" s="8">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="N418" s="8">
+        <v>25</v>
+      </c>
       <c r="O418" s="7"/>
       <c r="P418" s="7"/>
       <c r="Q418" s="7"/>
@@ -25298,20 +26006,49 @@
       <c r="T418" s="7"/>
     </row>
     <row r="419" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A419" s="7"/>
-      <c r="B419" s="7"/>
-      <c r="C419" s="7"/>
-      <c r="D419" s="7"/>
-      <c r="E419" s="7"/>
-      <c r="F419" s="7"/>
-      <c r="G419" s="7"/>
-      <c r="H419" s="7"/>
-      <c r="I419" s="7"/>
-      <c r="J419" s="7"/>
-      <c r="K419" s="7"/>
-      <c r="L419" s="7"/>
-      <c r="M419" s="7"/>
-      <c r="N419" s="7"/>
+      <c r="A419" s="6" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B419" s="7" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C419" s="7" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D419" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E419" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F419" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G419" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H419" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I419" s="8">
+        <v>0</v>
+      </c>
+      <c r="J419" s="8">
+        <v>0</v>
+      </c>
+      <c r="K419" s="8">
+        <v>0</v>
+      </c>
+      <c r="L419" s="8">
+        <v>3</v>
+      </c>
+      <c r="M419" s="8">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="N419" s="8">
+        <v>197</v>
+      </c>
       <c r="O419" s="7"/>
       <c r="P419" s="7"/>
       <c r="Q419" s="7"/>
@@ -25320,20 +26057,49 @@
       <c r="T419" s="7"/>
     </row>
     <row r="420" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A420" s="7"/>
-      <c r="B420" s="7"/>
-      <c r="C420" s="7"/>
-      <c r="D420" s="7"/>
-      <c r="E420" s="7"/>
-      <c r="F420" s="7"/>
-      <c r="G420" s="7"/>
-      <c r="H420" s="7"/>
-      <c r="I420" s="7"/>
-      <c r="J420" s="7"/>
-      <c r="K420" s="7"/>
-      <c r="L420" s="7"/>
-      <c r="M420" s="7"/>
-      <c r="N420" s="7"/>
+      <c r="A420" s="6" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B420" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C420" s="7" t="s">
+        <v>1284</v>
+      </c>
+      <c r="D420" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E420" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F420" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G420" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H420" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I420" s="8">
+        <v>0</v>
+      </c>
+      <c r="J420" s="8">
+        <v>0</v>
+      </c>
+      <c r="K420" s="8">
+        <v>0</v>
+      </c>
+      <c r="L420" s="8">
+        <v>3</v>
+      </c>
+      <c r="M420" s="8">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="N420" s="8">
+        <v>460</v>
+      </c>
       <c r="O420" s="7"/>
       <c r="P420" s="7"/>
       <c r="Q420" s="7"/>
@@ -25342,20 +26108,49 @@
       <c r="T420" s="7"/>
     </row>
     <row r="421" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A421" s="7"/>
-      <c r="B421" s="7"/>
-      <c r="C421" s="7"/>
-      <c r="D421" s="7"/>
-      <c r="E421" s="7"/>
-      <c r="F421" s="7"/>
-      <c r="G421" s="7"/>
-      <c r="H421" s="7"/>
-      <c r="I421" s="7"/>
-      <c r="J421" s="7"/>
-      <c r="K421" s="7"/>
-      <c r="L421" s="7"/>
-      <c r="M421" s="7"/>
-      <c r="N421" s="7"/>
+      <c r="A421" s="6" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B421" s="7" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C421" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="D421" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E421" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F421" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G421" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H421" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I421" s="8">
+        <v>0</v>
+      </c>
+      <c r="J421" s="8">
+        <v>0</v>
+      </c>
+      <c r="K421" s="8">
+        <v>0</v>
+      </c>
+      <c r="L421" s="8">
+        <v>2</v>
+      </c>
+      <c r="M421" s="8">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="N421" s="8">
+        <v>458</v>
+      </c>
       <c r="O421" s="7"/>
       <c r="P421" s="7"/>
       <c r="Q421" s="7"/>
@@ -25364,20 +26159,49 @@
       <c r="T421" s="7"/>
     </row>
     <row r="422" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A422" s="7"/>
-      <c r="B422" s="7"/>
-      <c r="C422" s="7"/>
-      <c r="D422" s="7"/>
-      <c r="E422" s="7"/>
-      <c r="F422" s="7"/>
-      <c r="G422" s="7"/>
-      <c r="H422" s="7"/>
-      <c r="I422" s="7"/>
-      <c r="J422" s="7"/>
-      <c r="K422" s="7"/>
-      <c r="L422" s="7"/>
-      <c r="M422" s="7"/>
-      <c r="N422" s="7"/>
+      <c r="A422" s="6" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B422" s="7" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C422" s="7" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D422" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E422" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F422" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G422" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H422" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I422" s="8">
+        <v>0</v>
+      </c>
+      <c r="J422" s="8">
+        <v>0</v>
+      </c>
+      <c r="K422" s="8">
+        <v>0</v>
+      </c>
+      <c r="L422" s="8">
+        <v>2</v>
+      </c>
+      <c r="M422" s="8">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="N422" s="8">
+        <v>284</v>
+      </c>
       <c r="O422" s="7"/>
       <c r="P422" s="7"/>
       <c r="Q422" s="7"/>
@@ -25386,20 +26210,49 @@
       <c r="T422" s="7"/>
     </row>
     <row r="423" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A423" s="7"/>
-      <c r="B423" s="7"/>
-      <c r="C423" s="7"/>
-      <c r="D423" s="7"/>
-      <c r="E423" s="7"/>
-      <c r="F423" s="7"/>
-      <c r="G423" s="7"/>
-      <c r="H423" s="7"/>
-      <c r="I423" s="7"/>
-      <c r="J423" s="7"/>
-      <c r="K423" s="7"/>
-      <c r="L423" s="7"/>
-      <c r="M423" s="7"/>
-      <c r="N423" s="7"/>
+      <c r="A423" s="6" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B423" s="7" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C423" s="7" t="s">
+        <v>1290</v>
+      </c>
+      <c r="D423" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E423" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F423" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G423" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H423" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I423" s="8">
+        <v>0</v>
+      </c>
+      <c r="J423" s="8">
+        <v>0</v>
+      </c>
+      <c r="K423" s="8">
+        <v>0</v>
+      </c>
+      <c r="L423" s="8">
+        <v>2</v>
+      </c>
+      <c r="M423" s="8">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="N423" s="8">
+        <v>55</v>
+      </c>
       <c r="O423" s="7"/>
       <c r="P423" s="7"/>
       <c r="Q423" s="7"/>
@@ -25408,20 +26261,49 @@
       <c r="T423" s="7"/>
     </row>
     <row r="424" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A424" s="7"/>
-      <c r="B424" s="7"/>
-      <c r="C424" s="7"/>
-      <c r="D424" s="7"/>
-      <c r="E424" s="7"/>
-      <c r="F424" s="7"/>
-      <c r="G424" s="7"/>
-      <c r="H424" s="7"/>
-      <c r="I424" s="7"/>
-      <c r="J424" s="7"/>
-      <c r="K424" s="7"/>
-      <c r="L424" s="7"/>
-      <c r="M424" s="7"/>
-      <c r="N424" s="7"/>
+      <c r="A424" s="6" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B424" s="7" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C424" s="7" t="s">
+        <v>1292</v>
+      </c>
+      <c r="D424" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E424" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F424" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G424" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H424" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I424" s="8">
+        <v>0</v>
+      </c>
+      <c r="J424" s="8">
+        <v>0</v>
+      </c>
+      <c r="K424" s="8">
+        <v>0</v>
+      </c>
+      <c r="L424" s="8">
+        <v>2</v>
+      </c>
+      <c r="M424" s="8">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="N424" s="8">
+        <v>48</v>
+      </c>
       <c r="O424" s="7"/>
       <c r="P424" s="7"/>
       <c r="Q424" s="7"/>
@@ -25430,20 +26312,49 @@
       <c r="T424" s="7"/>
     </row>
     <row r="425" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A425" s="7"/>
-      <c r="B425" s="7"/>
-      <c r="C425" s="7"/>
-      <c r="D425" s="7"/>
-      <c r="E425" s="7"/>
-      <c r="F425" s="7"/>
-      <c r="G425" s="7"/>
-      <c r="H425" s="7"/>
-      <c r="I425" s="7"/>
-      <c r="J425" s="7"/>
-      <c r="K425" s="7"/>
-      <c r="L425" s="7"/>
-      <c r="M425" s="7"/>
-      <c r="N425" s="7"/>
+      <c r="A425" s="6" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B425" s="7" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C425" s="7" t="s">
+        <v>1294</v>
+      </c>
+      <c r="D425" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E425" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F425" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G425" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H425" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I425" s="8">
+        <v>0</v>
+      </c>
+      <c r="J425" s="8">
+        <v>0</v>
+      </c>
+      <c r="K425" s="8">
+        <v>0</v>
+      </c>
+      <c r="L425" s="8">
+        <v>2</v>
+      </c>
+      <c r="M425" s="8">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="N425" s="8">
+        <v>14</v>
+      </c>
       <c r="O425" s="7"/>
       <c r="P425" s="7"/>
       <c r="Q425" s="7"/>
@@ -25452,20 +26363,49 @@
       <c r="T425" s="7"/>
     </row>
     <row r="426" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A426" s="7"/>
-      <c r="B426" s="7"/>
-      <c r="C426" s="7"/>
-      <c r="D426" s="7"/>
-      <c r="E426" s="7"/>
-      <c r="F426" s="7"/>
-      <c r="G426" s="7"/>
-      <c r="H426" s="7"/>
-      <c r="I426" s="7"/>
-      <c r="J426" s="7"/>
-      <c r="K426" s="7"/>
-      <c r="L426" s="7"/>
-      <c r="M426" s="7"/>
-      <c r="N426" s="7"/>
+      <c r="A426" s="6" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B426" s="7" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C426" s="7" t="s">
+        <v>1296</v>
+      </c>
+      <c r="D426" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E426" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F426" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G426" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H426" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I426" s="8">
+        <v>0</v>
+      </c>
+      <c r="J426" s="8">
+        <v>0</v>
+      </c>
+      <c r="K426" s="8">
+        <v>0</v>
+      </c>
+      <c r="L426" s="8">
+        <v>2</v>
+      </c>
+      <c r="M426" s="8">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="N426" s="8">
+        <v>5</v>
+      </c>
       <c r="O426" s="7"/>
       <c r="P426" s="7"/>
       <c r="Q426" s="7"/>
@@ -25474,20 +26414,49 @@
       <c r="T426" s="7"/>
     </row>
     <row r="427" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A427" s="7"/>
-      <c r="B427" s="7"/>
-      <c r="C427" s="7"/>
-      <c r="D427" s="7"/>
-      <c r="E427" s="7"/>
-      <c r="F427" s="7"/>
-      <c r="G427" s="7"/>
-      <c r="H427" s="7"/>
-      <c r="I427" s="7"/>
-      <c r="J427" s="7"/>
-      <c r="K427" s="7"/>
-      <c r="L427" s="7"/>
-      <c r="M427" s="7"/>
-      <c r="N427" s="7"/>
+      <c r="A427" s="6" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B427" s="7" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C427" s="7" t="s">
+        <v>1298</v>
+      </c>
+      <c r="D427" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E427" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F427" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G427" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H427" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I427" s="8">
+        <v>0</v>
+      </c>
+      <c r="J427" s="8">
+        <v>0</v>
+      </c>
+      <c r="K427" s="8">
+        <v>0</v>
+      </c>
+      <c r="L427" s="8">
+        <v>2</v>
+      </c>
+      <c r="M427" s="8">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="N427" s="8">
+        <v>63</v>
+      </c>
       <c r="O427" s="7"/>
       <c r="P427" s="7"/>
       <c r="Q427" s="7"/>
@@ -25496,20 +26465,49 @@
       <c r="T427" s="7"/>
     </row>
     <row r="428" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A428" s="7"/>
-      <c r="B428" s="7"/>
-      <c r="C428" s="7"/>
-      <c r="D428" s="7"/>
-      <c r="E428" s="7"/>
-      <c r="F428" s="7"/>
-      <c r="G428" s="7"/>
-      <c r="H428" s="7"/>
-      <c r="I428" s="7"/>
-      <c r="J428" s="7"/>
-      <c r="K428" s="7"/>
-      <c r="L428" s="7"/>
-      <c r="M428" s="7"/>
-      <c r="N428" s="7"/>
+      <c r="A428" s="6" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B428" s="7" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C428" s="7" t="s">
+        <v>1300</v>
+      </c>
+      <c r="D428" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E428" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F428" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G428" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H428" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I428" s="8">
+        <v>0</v>
+      </c>
+      <c r="J428" s="8">
+        <v>0</v>
+      </c>
+      <c r="K428" s="8">
+        <v>0</v>
+      </c>
+      <c r="L428" s="8">
+        <v>0</v>
+      </c>
+      <c r="M428" s="8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="N428" s="8">
+        <v>18</v>
+      </c>
       <c r="O428" s="7"/>
       <c r="P428" s="7"/>
       <c r="Q428" s="7"/>
@@ -25518,20 +26516,49 @@
       <c r="T428" s="7"/>
     </row>
     <row r="429" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A429" s="7"/>
-      <c r="B429" s="7"/>
-      <c r="C429" s="7"/>
-      <c r="D429" s="7"/>
-      <c r="E429" s="7"/>
-      <c r="F429" s="7"/>
-      <c r="G429" s="7"/>
-      <c r="H429" s="7"/>
-      <c r="I429" s="7"/>
-      <c r="J429" s="7"/>
-      <c r="K429" s="7"/>
-      <c r="L429" s="7"/>
-      <c r="M429" s="7"/>
-      <c r="N429" s="7"/>
+      <c r="A429" s="6" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B429" s="7" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C429" s="7" t="s">
+        <v>1302</v>
+      </c>
+      <c r="D429" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E429" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F429" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G429" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H429" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I429" s="8">
+        <v>0</v>
+      </c>
+      <c r="J429" s="8">
+        <v>0</v>
+      </c>
+      <c r="K429" s="8">
+        <v>0</v>
+      </c>
+      <c r="L429" s="8">
+        <v>0</v>
+      </c>
+      <c r="M429" s="8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="N429" s="8">
+        <v>4</v>
+      </c>
       <c r="O429" s="7"/>
       <c r="P429" s="7"/>
       <c r="Q429" s="7"/>
@@ -25540,20 +26567,49 @@
       <c r="T429" s="7"/>
     </row>
     <row r="430" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A430" s="7"/>
-      <c r="B430" s="7"/>
-      <c r="C430" s="7"/>
-      <c r="D430" s="7"/>
-      <c r="E430" s="7"/>
-      <c r="F430" s="7"/>
-      <c r="G430" s="7"/>
-      <c r="H430" s="7"/>
-      <c r="I430" s="7"/>
-      <c r="J430" s="7"/>
-      <c r="K430" s="7"/>
-      <c r="L430" s="7"/>
-      <c r="M430" s="7"/>
-      <c r="N430" s="7"/>
+      <c r="A430" s="6" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B430" s="7" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C430" s="7" t="s">
+        <v>1304</v>
+      </c>
+      <c r="D430" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E430" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F430" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G430" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H430" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I430" s="8">
+        <v>0</v>
+      </c>
+      <c r="J430" s="8">
+        <v>0</v>
+      </c>
+      <c r="K430" s="8">
+        <v>0</v>
+      </c>
+      <c r="L430" s="8">
+        <v>0</v>
+      </c>
+      <c r="M430" s="8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="N430" s="8">
+        <v>44</v>
+      </c>
       <c r="O430" s="7"/>
       <c r="P430" s="7"/>
       <c r="Q430" s="7"/>
@@ -25562,20 +26618,49 @@
       <c r="T430" s="7"/>
     </row>
     <row r="431" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A431" s="7"/>
-      <c r="B431" s="7"/>
-      <c r="C431" s="7"/>
-      <c r="D431" s="7"/>
-      <c r="E431" s="7"/>
-      <c r="F431" s="7"/>
-      <c r="G431" s="7"/>
-      <c r="H431" s="7"/>
-      <c r="I431" s="7"/>
-      <c r="J431" s="7"/>
-      <c r="K431" s="7"/>
-      <c r="L431" s="7"/>
-      <c r="M431" s="7"/>
-      <c r="N431" s="7"/>
+      <c r="A431" s="6" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B431" s="7" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C431" s="7" t="s">
+        <v>1306</v>
+      </c>
+      <c r="D431" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E431" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F431" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G431" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H431" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I431" s="8">
+        <v>0</v>
+      </c>
+      <c r="J431" s="8">
+        <v>0</v>
+      </c>
+      <c r="K431" s="8">
+        <v>0</v>
+      </c>
+      <c r="L431" s="8">
+        <v>0</v>
+      </c>
+      <c r="M431" s="8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="N431" s="8">
+        <v>29</v>
+      </c>
       <c r="O431" s="7"/>
       <c r="P431" s="7"/>
       <c r="Q431" s="7"/>
@@ -25584,20 +26669,49 @@
       <c r="T431" s="7"/>
     </row>
     <row r="432" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A432" s="7"/>
-      <c r="B432" s="7"/>
-      <c r="C432" s="7"/>
-      <c r="D432" s="7"/>
-      <c r="E432" s="7"/>
-      <c r="F432" s="7"/>
-      <c r="G432" s="7"/>
-      <c r="H432" s="7"/>
-      <c r="I432" s="7"/>
-      <c r="J432" s="7"/>
-      <c r="K432" s="7"/>
-      <c r="L432" s="7"/>
-      <c r="M432" s="7"/>
-      <c r="N432" s="7"/>
+      <c r="A432" s="6" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B432" s="7" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C432" s="7" t="s">
+        <v>1308</v>
+      </c>
+      <c r="D432" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E432" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F432" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G432" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H432" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I432" s="8">
+        <v>0</v>
+      </c>
+      <c r="J432" s="8">
+        <v>0</v>
+      </c>
+      <c r="K432" s="8">
+        <v>0</v>
+      </c>
+      <c r="L432" s="8">
+        <v>0</v>
+      </c>
+      <c r="M432" s="8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="N432" s="8">
+        <v>12</v>
+      </c>
       <c r="O432" s="7"/>
       <c r="P432" s="7"/>
       <c r="Q432" s="7"/>
@@ -25606,20 +26720,49 @@
       <c r="T432" s="7"/>
     </row>
     <row r="433" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A433" s="7"/>
-      <c r="B433" s="7"/>
-      <c r="C433" s="7"/>
-      <c r="D433" s="7"/>
-      <c r="E433" s="7"/>
-      <c r="F433" s="7"/>
-      <c r="G433" s="7"/>
-      <c r="H433" s="7"/>
-      <c r="I433" s="7"/>
-      <c r="J433" s="7"/>
-      <c r="K433" s="7"/>
-      <c r="L433" s="7"/>
-      <c r="M433" s="7"/>
-      <c r="N433" s="7"/>
+      <c r="A433" s="6" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B433" s="7" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C433" s="7" t="s">
+        <v>1310</v>
+      </c>
+      <c r="D433" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E433" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F433" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G433" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H433" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I433" s="8">
+        <v>0</v>
+      </c>
+      <c r="J433" s="8">
+        <v>0</v>
+      </c>
+      <c r="K433" s="8">
+        <v>0</v>
+      </c>
+      <c r="L433" s="8">
+        <v>0</v>
+      </c>
+      <c r="M433" s="8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="N433" s="8">
+        <v>40</v>
+      </c>
       <c r="O433" s="7"/>
       <c r="P433" s="7"/>
       <c r="Q433" s="7"/>
@@ -32887,74 +34030,8 @@
       <c r="S763" s="7"/>
       <c r="T763" s="7"/>
     </row>
-    <row r="764" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A764" s="7"/>
-      <c r="B764" s="7"/>
-      <c r="C764" s="7"/>
-      <c r="D764" s="7"/>
-      <c r="E764" s="7"/>
-      <c r="F764" s="7"/>
-      <c r="G764" s="7"/>
-      <c r="H764" s="7"/>
-      <c r="I764" s="7"/>
-      <c r="J764" s="7"/>
-      <c r="K764" s="7"/>
-      <c r="L764" s="7"/>
-      <c r="M764" s="7"/>
-      <c r="N764" s="7"/>
-      <c r="O764" s="7"/>
-      <c r="P764" s="7"/>
-      <c r="Q764" s="7"/>
-      <c r="R764" s="7"/>
-      <c r="S764" s="7"/>
-      <c r="T764" s="7"/>
-    </row>
-    <row r="765" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A765" s="7"/>
-      <c r="B765" s="7"/>
-      <c r="C765" s="7"/>
-      <c r="D765" s="7"/>
-      <c r="E765" s="7"/>
-      <c r="F765" s="7"/>
-      <c r="G765" s="7"/>
-      <c r="H765" s="7"/>
-      <c r="I765" s="7"/>
-      <c r="J765" s="7"/>
-      <c r="K765" s="7"/>
-      <c r="L765" s="7"/>
-      <c r="M765" s="7"/>
-      <c r="N765" s="7"/>
-      <c r="O765" s="7"/>
-      <c r="P765" s="7"/>
-      <c r="Q765" s="7"/>
-      <c r="R765" s="7"/>
-      <c r="S765" s="7"/>
-      <c r="T765" s="7"/>
-    </row>
-    <row r="766" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A766" s="7"/>
-      <c r="B766" s="7"/>
-      <c r="C766" s="7"/>
-      <c r="D766" s="7"/>
-      <c r="E766" s="7"/>
-      <c r="F766" s="7"/>
-      <c r="G766" s="7"/>
-      <c r="H766" s="7"/>
-      <c r="I766" s="7"/>
-      <c r="J766" s="7"/>
-      <c r="K766" s="7"/>
-      <c r="L766" s="7"/>
-      <c r="M766" s="7"/>
-      <c r="N766" s="7"/>
-      <c r="O766" s="7"/>
-      <c r="P766" s="7"/>
-      <c r="Q766" s="7"/>
-      <c r="R766" s="7"/>
-      <c r="S766" s="7"/>
-      <c r="T766" s="7"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:T403" xr:uid="{AF55B7BF-85DC-4082-9A73-200B4D79A598}"/>
+  <autoFilter ref="A1:T433" xr:uid="{AF55B7BF-85DC-4082-9A73-200B4D79A598}"/>
   <conditionalFormatting sqref="A1:B1">
     <cfRule type="duplicateValues" dxfId="11" priority="19"/>
     <cfRule type="duplicateValues" dxfId="10" priority="20"/>

--- a/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
+++ b/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\Fossil Replenishment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E26E24FE-D6B3-4B79-91C6-8B36413DA822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C5A942F-14CB-4363-A063-10D05F099FA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6662473D-6E1F-42FD-999B-28162E22D4B5}"/>
   </bookViews>
@@ -4764,20 +4764,20 @@
         <v>12</v>
       </c>
       <c r="I2" s="8">
-        <v>705</v>
+        <v>741</v>
       </c>
       <c r="J2" s="8">
         <v>0</v>
       </c>
       <c r="K2" s="8">
-        <v>106</v>
+        <v>18</v>
       </c>
       <c r="L2" s="8">
         <v>0</v>
       </c>
       <c r="M2" s="8">
         <f>I2+J2+K2+L2</f>
-        <v>811</v>
+        <v>759</v>
       </c>
       <c r="N2" s="8">
         <v>1385</v>
@@ -4815,7 +4815,7 @@
         <v>12</v>
       </c>
       <c r="I3" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3" s="8">
         <v>0</v>
@@ -4828,7 +4828,7 @@
       </c>
       <c r="M3" s="8">
         <f t="shared" ref="M3:M66" si="0">I3+J3+K3+L3</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N3" s="8">
         <v>0</v>
@@ -4866,7 +4866,7 @@
         <v>12</v>
       </c>
       <c r="I4" s="8">
-        <v>147</v>
+        <v>183</v>
       </c>
       <c r="J4" s="8">
         <v>0</v>
@@ -4879,7 +4879,7 @@
       </c>
       <c r="M4" s="8">
         <f t="shared" si="0"/>
-        <v>147</v>
+        <v>183</v>
       </c>
       <c r="N4" s="8">
         <v>0</v>
@@ -4917,7 +4917,7 @@
         <v>12</v>
       </c>
       <c r="I5" s="8">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J5" s="8">
         <v>0</v>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="M5" s="8">
         <f t="shared" si="0"/>
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N5" s="8">
         <v>0</v>
@@ -4968,20 +4968,20 @@
         <v>12</v>
       </c>
       <c r="I6" s="8">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="J6" s="8">
         <v>0</v>
       </c>
       <c r="K6" s="8">
-        <v>97</v>
+        <v>16</v>
       </c>
       <c r="L6" s="8">
         <v>0</v>
       </c>
       <c r="M6" s="8">
         <f t="shared" si="0"/>
-        <v>894</v>
+        <v>808</v>
       </c>
       <c r="N6" s="8">
         <v>1658</v>
@@ -5019,7 +5019,7 @@
         <v>12</v>
       </c>
       <c r="I7" s="8">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J7" s="8">
         <v>0</v>
@@ -5032,10 +5032,10 @@
       </c>
       <c r="M7" s="8">
         <f t="shared" si="0"/>
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N7" s="8">
-        <v>0</v>
+        <v>515</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
@@ -5070,7 +5070,7 @@
         <v>12</v>
       </c>
       <c r="I8" s="8">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="J8" s="8">
         <v>0</v>
@@ -5083,10 +5083,10 @@
       </c>
       <c r="M8" s="8">
         <f t="shared" si="0"/>
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="N8" s="8">
-        <v>825</v>
+        <v>575</v>
       </c>
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
@@ -5121,23 +5121,23 @@
         <v>12</v>
       </c>
       <c r="I9" s="8">
+        <v>3</v>
+      </c>
+      <c r="J9" s="8">
+        <v>0</v>
+      </c>
+      <c r="K9" s="8">
+        <v>3</v>
+      </c>
+      <c r="L9" s="8">
         <v>10</v>
-      </c>
-      <c r="J9" s="8">
-        <v>0</v>
-      </c>
-      <c r="K9" s="8">
-        <v>0</v>
-      </c>
-      <c r="L9" s="8">
-        <v>3</v>
       </c>
       <c r="M9" s="8">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N9" s="8">
-        <v>222</v>
+        <v>125</v>
       </c>
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
@@ -5172,23 +5172,23 @@
         <v>12</v>
       </c>
       <c r="I10" s="8">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="J10" s="8">
         <v>0</v>
       </c>
       <c r="K10" s="8">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L10" s="8">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M10" s="8">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="N10" s="8">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="O10" s="8"/>
       <c r="P10" s="8"/>
@@ -5223,23 +5223,23 @@
         <v>12</v>
       </c>
       <c r="I11" s="8">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J11" s="8">
         <v>0</v>
       </c>
       <c r="K11" s="8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L11" s="8">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="M11" s="8">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="N11" s="8">
-        <v>217</v>
+        <v>172</v>
       </c>
       <c r="O11" s="8"/>
       <c r="P11" s="8"/>
@@ -5274,7 +5274,7 @@
         <v>12</v>
       </c>
       <c r="I12" s="8">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J12" s="8">
         <v>0</v>
@@ -5287,7 +5287,7 @@
       </c>
       <c r="M12" s="8">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="N12" s="8">
         <v>0</v>
@@ -5325,20 +5325,20 @@
         <v>12</v>
       </c>
       <c r="I13" s="8">
-        <v>207</v>
+        <v>234</v>
       </c>
       <c r="J13" s="8">
         <v>0</v>
       </c>
       <c r="K13" s="8">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="L13" s="8">
         <v>0</v>
       </c>
       <c r="M13" s="8">
         <f t="shared" si="0"/>
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="N13" s="8">
         <v>858</v>
@@ -5376,7 +5376,7 @@
         <v>12</v>
       </c>
       <c r="I14" s="8">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J14" s="8">
         <v>0</v>
@@ -5389,10 +5389,10 @@
       </c>
       <c r="M14" s="8">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="N14" s="8">
-        <v>1117</v>
+        <v>739</v>
       </c>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
@@ -5427,23 +5427,23 @@
         <v>12</v>
       </c>
       <c r="I15" s="8">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="J15" s="8">
         <v>0</v>
       </c>
       <c r="K15" s="8">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L15" s="8">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="M15" s="8">
         <f t="shared" si="0"/>
-        <v>51</v>
+        <v>129</v>
       </c>
       <c r="N15" s="8">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="O15" s="8"/>
       <c r="P15" s="8"/>
@@ -5478,23 +5478,23 @@
         <v>12</v>
       </c>
       <c r="I16" s="8">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="J16" s="8">
         <v>0</v>
       </c>
       <c r="K16" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L16" s="8">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M16" s="8">
         <f t="shared" si="0"/>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N16" s="8">
-        <v>841</v>
+        <v>664</v>
       </c>
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
@@ -5529,7 +5529,7 @@
         <v>12</v>
       </c>
       <c r="I17" s="8">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J17" s="8">
         <v>0</v>
@@ -5542,10 +5542,10 @@
       </c>
       <c r="M17" s="8">
         <f t="shared" si="0"/>
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="N17" s="8">
-        <v>457</v>
+        <v>367</v>
       </c>
       <c r="O17" s="8"/>
       <c r="P17" s="8"/>
@@ -5580,23 +5580,23 @@
         <v>12</v>
       </c>
       <c r="I18" s="8">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J18" s="8">
         <v>0</v>
       </c>
       <c r="K18" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" s="8">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N18" s="8">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O18" s="8"/>
       <c r="P18" s="8"/>
@@ -5647,7 +5647,7 @@
         <v>11</v>
       </c>
       <c r="N19" s="8">
-        <v>1104</v>
+        <v>809</v>
       </c>
       <c r="O19" s="8"/>
       <c r="P19" s="8"/>
@@ -5682,7 +5682,7 @@
         <v>14</v>
       </c>
       <c r="I20" s="8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J20" s="8">
         <v>0</v>
@@ -5695,10 +5695,10 @@
       </c>
       <c r="M20" s="8">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N20" s="8">
-        <v>4</v>
+        <v>491</v>
       </c>
       <c r="O20" s="8"/>
       <c r="P20" s="8"/>
@@ -5733,23 +5733,23 @@
         <v>13</v>
       </c>
       <c r="I21" s="8">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J21" s="8">
         <v>0</v>
       </c>
       <c r="K21" s="8">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="L21" s="8">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M21" s="8">
         <f t="shared" si="0"/>
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="N21" s="8">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="O21" s="8"/>
       <c r="P21" s="8"/>
@@ -5835,7 +5835,7 @@
         <v>12</v>
       </c>
       <c r="I23" s="8">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J23" s="8">
         <v>0</v>
@@ -5844,14 +5844,14 @@
         <v>0</v>
       </c>
       <c r="L23" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M23" s="8">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N23" s="8">
-        <v>163</v>
+        <v>116</v>
       </c>
       <c r="O23" s="8"/>
       <c r="P23" s="8"/>
@@ -5886,7 +5886,7 @@
         <v>14</v>
       </c>
       <c r="I24" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J24" s="8">
         <v>0</v>
@@ -5899,10 +5899,10 @@
       </c>
       <c r="M24" s="8">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N24" s="8">
-        <v>703</v>
+        <v>571</v>
       </c>
       <c r="O24" s="8"/>
       <c r="P24" s="8"/>
@@ -5988,23 +5988,23 @@
         <v>12</v>
       </c>
       <c r="I26" s="8">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J26" s="8">
         <v>0</v>
       </c>
       <c r="K26" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L26" s="8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M26" s="8">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="N26" s="8">
-        <v>738</v>
+        <v>477</v>
       </c>
       <c r="O26" s="8"/>
       <c r="P26" s="8"/>
@@ -6039,7 +6039,7 @@
         <v>12</v>
       </c>
       <c r="I27" s="8">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J27" s="8">
         <v>0</v>
@@ -6052,10 +6052,10 @@
       </c>
       <c r="M27" s="8">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="N27" s="8">
-        <v>1077</v>
+        <v>957</v>
       </c>
       <c r="O27" s="8"/>
       <c r="P27" s="8"/>
@@ -6090,7 +6090,7 @@
         <v>12</v>
       </c>
       <c r="I28" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J28" s="8">
         <v>0</v>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="M28" s="8">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N28" s="8">
         <v>0</v>
@@ -6141,7 +6141,7 @@
         <v>13</v>
       </c>
       <c r="I29" s="8">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J29" s="8">
         <v>0</v>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="M29" s="8">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="N29" s="8">
         <v>0</v>
@@ -6192,23 +6192,23 @@
         <v>14</v>
       </c>
       <c r="I30" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J30" s="8">
         <v>0</v>
       </c>
       <c r="K30" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="8">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N30" s="8">
-        <v>1420</v>
+        <v>1277</v>
       </c>
       <c r="O30" s="8"/>
       <c r="P30" s="8"/>
@@ -6294,23 +6294,23 @@
         <v>12</v>
       </c>
       <c r="I32" s="8">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J32" s="8">
         <v>0</v>
       </c>
       <c r="K32" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L32" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M32" s="8">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N32" s="8">
-        <v>720</v>
+        <v>649</v>
       </c>
       <c r="O32" s="8"/>
       <c r="P32" s="8"/>
@@ -6345,7 +6345,7 @@
         <v>12</v>
       </c>
       <c r="I33" s="8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J33" s="8">
         <v>0</v>
@@ -6358,10 +6358,10 @@
       </c>
       <c r="M33" s="8">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N33" s="8">
-        <v>1109</v>
+        <v>959</v>
       </c>
       <c r="O33" s="8"/>
       <c r="P33" s="8"/>
@@ -6412,7 +6412,7 @@
         <v>18</v>
       </c>
       <c r="N34" s="8">
-        <v>1021</v>
+        <v>952</v>
       </c>
       <c r="O34" s="8"/>
       <c r="P34" s="8"/>
@@ -6447,7 +6447,7 @@
         <v>12</v>
       </c>
       <c r="I35" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J35" s="8">
         <v>0</v>
@@ -6460,10 +6460,10 @@
       </c>
       <c r="M35" s="8">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N35" s="8">
-        <v>643</v>
+        <v>733</v>
       </c>
       <c r="O35" s="8"/>
       <c r="P35" s="8"/>
@@ -6514,7 +6514,7 @@
         <v>12</v>
       </c>
       <c r="N36" s="8">
-        <v>737</v>
+        <v>673</v>
       </c>
       <c r="O36" s="8"/>
       <c r="P36" s="8"/>
@@ -6549,7 +6549,7 @@
         <v>13</v>
       </c>
       <c r="I37" s="8">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J37" s="8">
         <v>0</v>
@@ -6562,10 +6562,10 @@
       </c>
       <c r="M37" s="8">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N37" s="8">
-        <v>1521</v>
+        <v>1211</v>
       </c>
       <c r="O37" s="8"/>
       <c r="P37" s="8"/>
@@ -6600,7 +6600,7 @@
         <v>12</v>
       </c>
       <c r="I38" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J38" s="8">
         <v>0</v>
@@ -6613,7 +6613,7 @@
       </c>
       <c r="M38" s="8">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N38" s="8">
         <v>0</v>
@@ -6651,7 +6651,7 @@
         <v>12</v>
       </c>
       <c r="I39" s="8">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J39" s="8">
         <v>0</v>
@@ -6664,10 +6664,10 @@
       </c>
       <c r="M39" s="8">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N39" s="8">
-        <v>1303</v>
+        <v>1837</v>
       </c>
       <c r="O39" s="8"/>
       <c r="P39" s="8"/>
@@ -6702,7 +6702,7 @@
         <v>12</v>
       </c>
       <c r="I40" s="8">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J40" s="8">
         <v>0</v>
@@ -6715,10 +6715,10 @@
       </c>
       <c r="M40" s="8">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="N40" s="8">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O40" s="8"/>
       <c r="P40" s="8"/>
@@ -6753,7 +6753,7 @@
         <v>12</v>
       </c>
       <c r="I41" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J41" s="8">
         <v>0</v>
@@ -6762,14 +6762,14 @@
         <v>0</v>
       </c>
       <c r="L41" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M41" s="8">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N41" s="8">
-        <v>284</v>
+        <v>204</v>
       </c>
       <c r="O41" s="8"/>
       <c r="P41" s="8"/>
@@ -6820,7 +6820,7 @@
         <v>12</v>
       </c>
       <c r="N42" s="8">
-        <v>1209</v>
+        <v>1358</v>
       </c>
       <c r="O42" s="8"/>
       <c r="P42" s="8"/>
@@ -6855,7 +6855,7 @@
         <v>12</v>
       </c>
       <c r="I43" s="8">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J43" s="8">
         <v>0</v>
@@ -6868,10 +6868,10 @@
       </c>
       <c r="M43" s="8">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="N43" s="8">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="O43" s="8"/>
       <c r="P43" s="8"/>
@@ -6906,23 +6906,23 @@
         <v>12</v>
       </c>
       <c r="I44" s="8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J44" s="8">
         <v>0</v>
       </c>
       <c r="K44" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L44" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M44" s="8">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N44" s="8">
-        <v>433</v>
+        <v>290</v>
       </c>
       <c r="O44" s="8"/>
       <c r="P44" s="8"/>
@@ -6973,7 +6973,7 @@
         <v>13</v>
       </c>
       <c r="N45" s="8">
-        <v>834</v>
+        <v>659</v>
       </c>
       <c r="O45" s="8"/>
       <c r="P45" s="8"/>
@@ -7024,7 +7024,7 @@
         <v>11</v>
       </c>
       <c r="N46" s="8">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="O46" s="8"/>
       <c r="P46" s="8"/>
@@ -7075,7 +7075,7 @@
         <v>9</v>
       </c>
       <c r="N47" s="8">
-        <v>963</v>
+        <v>898</v>
       </c>
       <c r="O47" s="8"/>
       <c r="P47" s="8"/>
@@ -7110,7 +7110,7 @@
         <v>12</v>
       </c>
       <c r="I48" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J48" s="8">
         <v>0</v>
@@ -7123,10 +7123,10 @@
       </c>
       <c r="M48" s="8">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N48" s="8">
-        <v>1943</v>
+        <v>1805</v>
       </c>
       <c r="O48" s="8"/>
       <c r="P48" s="8"/>
@@ -7177,7 +7177,7 @@
         <v>13</v>
       </c>
       <c r="N49" s="8">
-        <v>923</v>
+        <v>854</v>
       </c>
       <c r="O49" s="8"/>
       <c r="P49" s="8"/>
@@ -7228,7 +7228,7 @@
         <v>5</v>
       </c>
       <c r="N50" s="8">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="O50" s="8"/>
       <c r="P50" s="8"/>
@@ -7279,7 +7279,7 @@
         <v>24</v>
       </c>
       <c r="N51" s="8">
-        <v>371</v>
+        <v>346</v>
       </c>
       <c r="O51" s="8"/>
       <c r="P51" s="8"/>
@@ -7314,7 +7314,7 @@
         <v>12</v>
       </c>
       <c r="I52" s="8">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J52" s="8">
         <v>0</v>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="M52" s="8">
         <f t="shared" si="0"/>
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="N52" s="8">
         <v>0</v>
@@ -7365,7 +7365,7 @@
         <v>12</v>
       </c>
       <c r="I53" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J53" s="8">
         <v>0</v>
@@ -7378,10 +7378,10 @@
       </c>
       <c r="M53" s="8">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N53" s="8">
-        <v>122</v>
+        <v>81</v>
       </c>
       <c r="O53" s="8"/>
       <c r="P53" s="8"/>
@@ -7422,17 +7422,17 @@
         <v>0</v>
       </c>
       <c r="K54" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M54" s="8">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="N54" s="8">
-        <v>228</v>
+        <v>120</v>
       </c>
       <c r="O54" s="8"/>
       <c r="P54" s="8"/>
@@ -7467,20 +7467,20 @@
         <v>12</v>
       </c>
       <c r="I55" s="8">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J55" s="8">
         <v>0</v>
       </c>
       <c r="K55" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L55" s="8">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M55" s="8">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="N55" s="8">
         <v>0</v>
@@ -7534,7 +7534,7 @@
         <v>6</v>
       </c>
       <c r="N56" s="8">
-        <v>298</v>
+        <v>266</v>
       </c>
       <c r="O56" s="8"/>
       <c r="P56" s="8"/>
@@ -7569,23 +7569,23 @@
         <v>12</v>
       </c>
       <c r="I57" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57" s="8">
         <v>0</v>
       </c>
       <c r="K57" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L57" s="8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M57" s="8">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="N57" s="8">
-        <v>553</v>
+        <v>504</v>
       </c>
       <c r="O57" s="8"/>
       <c r="P57" s="8"/>
@@ -7636,7 +7636,7 @@
         <v>3</v>
       </c>
       <c r="N58" s="8">
-        <v>641</v>
+        <v>619</v>
       </c>
       <c r="O58" s="8"/>
       <c r="P58" s="8"/>
@@ -7687,7 +7687,7 @@
         <v>6</v>
       </c>
       <c r="N59" s="8">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="O59" s="8"/>
       <c r="P59" s="8"/>
@@ -7738,7 +7738,7 @@
         <v>5</v>
       </c>
       <c r="N60" s="8">
-        <v>645</v>
+        <v>574</v>
       </c>
       <c r="O60" s="8"/>
       <c r="P60" s="8"/>
@@ -7773,7 +7773,7 @@
         <v>12</v>
       </c>
       <c r="I61" s="8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J61" s="8">
         <v>0</v>
@@ -7786,10 +7786,10 @@
       </c>
       <c r="M61" s="8">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N61" s="8">
-        <v>265</v>
+        <v>97</v>
       </c>
       <c r="O61" s="8"/>
       <c r="P61" s="8"/>
@@ -7840,7 +7840,7 @@
         <v>8</v>
       </c>
       <c r="N62" s="8">
-        <v>372</v>
+        <v>295</v>
       </c>
       <c r="O62" s="8"/>
       <c r="P62" s="8"/>
@@ -7891,7 +7891,7 @@
         <v>4</v>
       </c>
       <c r="N63" s="8">
-        <v>205</v>
+        <v>179</v>
       </c>
       <c r="O63" s="8"/>
       <c r="P63" s="8"/>
@@ -7926,7 +7926,7 @@
         <v>13</v>
       </c>
       <c r="I64" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J64" s="8">
         <v>0</v>
@@ -7935,14 +7935,14 @@
         <v>0</v>
       </c>
       <c r="L64" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M64" s="8">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N64" s="8">
-        <v>523</v>
+        <v>333</v>
       </c>
       <c r="O64" s="8"/>
       <c r="P64" s="8"/>
@@ -7977,7 +7977,7 @@
         <v>12</v>
       </c>
       <c r="I65" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J65" s="8">
         <v>0</v>
@@ -7990,10 +7990,10 @@
       </c>
       <c r="M65" s="8">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N65" s="8">
-        <v>926</v>
+        <v>897</v>
       </c>
       <c r="O65" s="8"/>
       <c r="P65" s="8"/>
@@ -8044,7 +8044,7 @@
         <v>4</v>
       </c>
       <c r="N66" s="8">
-        <v>237</v>
+        <v>55</v>
       </c>
       <c r="O66" s="8"/>
       <c r="P66" s="8"/>
@@ -8095,7 +8095,7 @@
         <v>4</v>
       </c>
       <c r="N67" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O67" s="8"/>
       <c r="P67" s="8"/>
@@ -8146,7 +8146,7 @@
         <v>5</v>
       </c>
       <c r="N68" s="8">
-        <v>934</v>
+        <v>912</v>
       </c>
       <c r="O68" s="8"/>
       <c r="P68" s="8"/>
@@ -8190,14 +8190,14 @@
         <v>0</v>
       </c>
       <c r="L69" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" s="8">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N69" s="8">
-        <v>300</v>
+        <v>274</v>
       </c>
       <c r="O69" s="8"/>
       <c r="P69" s="8"/>
@@ -8232,7 +8232,7 @@
         <v>16</v>
       </c>
       <c r="I70" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J70" s="8">
         <v>0</v>
@@ -8245,10 +8245,10 @@
       </c>
       <c r="M70" s="8">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N70" s="8">
-        <v>579</v>
+        <v>555</v>
       </c>
       <c r="O70" s="8"/>
       <c r="P70" s="8"/>
@@ -8283,7 +8283,7 @@
         <v>12</v>
       </c>
       <c r="I71" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J71" s="8">
         <v>0</v>
@@ -8296,7 +8296,7 @@
       </c>
       <c r="M71" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N71" s="8">
         <v>0</v>
@@ -8350,7 +8350,7 @@
         <v>8</v>
       </c>
       <c r="N72" s="8">
-        <v>671</v>
+        <v>584</v>
       </c>
       <c r="O72" s="8"/>
       <c r="P72" s="8"/>
@@ -8385,7 +8385,7 @@
         <v>12</v>
       </c>
       <c r="I73" s="8">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J73" s="8">
         <v>0</v>
@@ -8394,14 +8394,14 @@
         <v>0</v>
       </c>
       <c r="L73" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M73" s="8">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N73" s="8">
-        <v>812</v>
+        <v>746</v>
       </c>
       <c r="O73" s="8"/>
       <c r="P73" s="8"/>
@@ -8436,23 +8436,23 @@
         <v>14</v>
       </c>
       <c r="I74" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J74" s="8">
         <v>0</v>
       </c>
       <c r="K74" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L74" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M74" s="8">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N74" s="8">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="O74" s="8"/>
       <c r="P74" s="8"/>
@@ -8503,7 +8503,7 @@
         <v>8</v>
       </c>
       <c r="N75" s="8">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="O75" s="8"/>
       <c r="P75" s="8"/>
@@ -8538,7 +8538,7 @@
         <v>13</v>
       </c>
       <c r="I76" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J76" s="8">
         <v>0</v>
@@ -8551,10 +8551,10 @@
       </c>
       <c r="M76" s="8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N76" s="8">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="O76" s="8"/>
       <c r="P76" s="8"/>
@@ -8605,7 +8605,7 @@
         <v>5</v>
       </c>
       <c r="N77" s="8">
-        <v>764</v>
+        <v>661</v>
       </c>
       <c r="O77" s="8"/>
       <c r="P77" s="8"/>
@@ -8640,7 +8640,7 @@
         <v>12</v>
       </c>
       <c r="I78" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J78" s="8">
         <v>0</v>
@@ -8649,14 +8649,14 @@
         <v>0</v>
       </c>
       <c r="L78" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M78" s="8">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N78" s="8">
-        <v>559</v>
+        <v>405</v>
       </c>
       <c r="O78" s="8"/>
       <c r="P78" s="8"/>
@@ -8707,7 +8707,7 @@
         <v>6</v>
       </c>
       <c r="N79" s="8">
-        <v>114</v>
+        <v>33</v>
       </c>
       <c r="O79" s="8"/>
       <c r="P79" s="8"/>
@@ -8860,7 +8860,7 @@
         <v>5</v>
       </c>
       <c r="N82" s="8">
-        <v>297</v>
+        <v>269</v>
       </c>
       <c r="O82" s="8"/>
       <c r="P82" s="8"/>
@@ -8911,7 +8911,7 @@
         <v>4</v>
       </c>
       <c r="N83" s="8">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="O83" s="8"/>
       <c r="P83" s="8"/>
@@ -8997,7 +8997,7 @@
         <v>14</v>
       </c>
       <c r="I85" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J85" s="8">
         <v>0</v>
@@ -9010,10 +9010,10 @@
       </c>
       <c r="M85" s="8">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N85" s="8">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="O85" s="8"/>
       <c r="P85" s="8"/>
@@ -9048,23 +9048,23 @@
         <v>12</v>
       </c>
       <c r="I86" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J86" s="8">
         <v>0</v>
       </c>
       <c r="K86" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L86" s="8">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M86" s="8">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="N86" s="8">
-        <v>468</v>
+        <v>117</v>
       </c>
       <c r="O86" s="8"/>
       <c r="P86" s="8"/>
@@ -9166,7 +9166,7 @@
         <v>12</v>
       </c>
       <c r="N88" s="8">
-        <v>458</v>
+        <v>386</v>
       </c>
       <c r="O88" s="8"/>
       <c r="P88" s="8"/>
@@ -9201,7 +9201,7 @@
         <v>12</v>
       </c>
       <c r="I89" s="8">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J89" s="8">
         <v>0</v>
@@ -9214,10 +9214,10 @@
       </c>
       <c r="M89" s="8">
         <f t="shared" si="1"/>
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N89" s="8">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="O89" s="8"/>
       <c r="P89" s="8"/>
@@ -9303,7 +9303,7 @@
         <v>12</v>
       </c>
       <c r="I91" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J91" s="8">
         <v>0</v>
@@ -9312,14 +9312,14 @@
         <v>0</v>
       </c>
       <c r="L91" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M91" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N91" s="8">
-        <v>1137</v>
+        <v>1033</v>
       </c>
       <c r="O91" s="8"/>
       <c r="P91" s="8"/>
@@ -9360,17 +9360,17 @@
         <v>0</v>
       </c>
       <c r="K92" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M92" s="8">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="N92" s="8">
-        <v>237</v>
+        <v>171</v>
       </c>
       <c r="O92" s="8"/>
       <c r="P92" s="8"/>
@@ -9405,7 +9405,7 @@
         <v>13</v>
       </c>
       <c r="I93" s="8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J93" s="8">
         <v>0</v>
@@ -9414,14 +9414,14 @@
         <v>0</v>
       </c>
       <c r="L93" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M93" s="8">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N93" s="8">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="O93" s="8"/>
       <c r="P93" s="8"/>
@@ -9456,7 +9456,7 @@
         <v>12</v>
       </c>
       <c r="I94" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J94" s="8">
         <v>0</v>
@@ -9469,7 +9469,7 @@
       </c>
       <c r="M94" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N94" s="8">
         <v>0</v>
@@ -9523,7 +9523,7 @@
         <v>6</v>
       </c>
       <c r="N95" s="8">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="O95" s="8"/>
       <c r="P95" s="8"/>
@@ -9574,7 +9574,7 @@
         <v>7</v>
       </c>
       <c r="N96" s="8">
-        <v>264</v>
+        <v>218</v>
       </c>
       <c r="O96" s="8"/>
       <c r="P96" s="8"/>
@@ -9609,23 +9609,23 @@
         <v>14</v>
       </c>
       <c r="I97" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J97" s="8">
         <v>0</v>
       </c>
       <c r="K97" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L97" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M97" s="8">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N97" s="8">
-        <v>247</v>
+        <v>219</v>
       </c>
       <c r="O97" s="8"/>
       <c r="P97" s="8"/>
@@ -9829,7 +9829,7 @@
         <v>2</v>
       </c>
       <c r="N101" s="8">
-        <v>344</v>
+        <v>328</v>
       </c>
       <c r="O101" s="8"/>
       <c r="P101" s="8"/>
@@ -9864,23 +9864,23 @@
         <v>14</v>
       </c>
       <c r="I102" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J102" s="8">
         <v>0</v>
       </c>
       <c r="K102" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L102" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M102" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N102" s="8">
-        <v>496</v>
+        <v>477</v>
       </c>
       <c r="O102" s="8"/>
       <c r="P102" s="8"/>
@@ -9921,17 +9921,17 @@
         <v>0</v>
       </c>
       <c r="K103" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L103" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M103" s="8">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="N103" s="8">
-        <v>494</v>
+        <v>437</v>
       </c>
       <c r="O103" s="8"/>
       <c r="P103" s="8"/>
@@ -10033,7 +10033,7 @@
         <v>8</v>
       </c>
       <c r="N105" s="8">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="O105" s="8"/>
       <c r="P105" s="8"/>
@@ -10237,7 +10237,7 @@
         <v>5</v>
       </c>
       <c r="N109" s="8">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O109" s="8"/>
       <c r="P109" s="8"/>
@@ -10288,7 +10288,7 @@
         <v>11</v>
       </c>
       <c r="N110" s="8">
-        <v>559</v>
+        <v>541</v>
       </c>
       <c r="O110" s="8"/>
       <c r="P110" s="8"/>
@@ -10374,7 +10374,7 @@
         <v>12</v>
       </c>
       <c r="I112" s="8">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J112" s="8">
         <v>0</v>
@@ -10383,14 +10383,14 @@
         <v>0</v>
       </c>
       <c r="L112" s="8">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M112" s="8">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>198</v>
       </c>
       <c r="N112" s="8">
-        <v>953</v>
+        <v>284</v>
       </c>
       <c r="O112" s="8"/>
       <c r="P112" s="8"/>
@@ -10425,7 +10425,7 @@
         <v>12</v>
       </c>
       <c r="I113" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J113" s="8">
         <v>0</v>
@@ -10438,10 +10438,10 @@
       </c>
       <c r="M113" s="8">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N113" s="8">
-        <v>1042</v>
+        <v>822</v>
       </c>
       <c r="O113" s="8"/>
       <c r="P113" s="8"/>
@@ -10492,7 +10492,7 @@
         <v>9</v>
       </c>
       <c r="N114" s="8">
-        <v>956</v>
+        <v>666</v>
       </c>
       <c r="O114" s="8"/>
       <c r="P114" s="8"/>
@@ -10527,7 +10527,7 @@
         <v>13</v>
       </c>
       <c r="I115" s="8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J115" s="8">
         <v>0</v>
@@ -10540,10 +10540,10 @@
       </c>
       <c r="M115" s="8">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N115" s="8">
-        <v>615</v>
+        <v>536</v>
       </c>
       <c r="O115" s="8"/>
       <c r="P115" s="8"/>
@@ -10584,17 +10584,17 @@
         <v>0</v>
       </c>
       <c r="K116" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L116" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M116" s="8">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="N116" s="8">
-        <v>802</v>
+        <v>730</v>
       </c>
       <c r="O116" s="8"/>
       <c r="P116" s="8"/>
@@ -10629,7 +10629,7 @@
         <v>12</v>
       </c>
       <c r="I117" s="8">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J117" s="8">
         <v>0</v>
@@ -10642,10 +10642,10 @@
       </c>
       <c r="M117" s="8">
         <f t="shared" si="1"/>
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N117" s="8">
-        <v>385</v>
+        <v>266</v>
       </c>
       <c r="O117" s="8"/>
       <c r="P117" s="8"/>
@@ -10696,7 +10696,7 @@
         <v>7</v>
       </c>
       <c r="N118" s="8">
-        <v>194</v>
+        <v>171</v>
       </c>
       <c r="O118" s="8"/>
       <c r="P118" s="8"/>
@@ -10747,7 +10747,7 @@
         <v>8</v>
       </c>
       <c r="N119" s="8">
-        <v>521</v>
+        <v>505</v>
       </c>
       <c r="O119" s="8"/>
       <c r="P119" s="8"/>
@@ -10798,7 +10798,7 @@
         <v>10</v>
       </c>
       <c r="N120" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O120" s="8"/>
       <c r="P120" s="8"/>
@@ -10900,7 +10900,7 @@
         <v>2</v>
       </c>
       <c r="N122" s="8">
-        <v>1024</v>
+        <v>989</v>
       </c>
       <c r="O122" s="8"/>
       <c r="P122" s="8"/>
@@ -10935,7 +10935,7 @@
         <v>14</v>
       </c>
       <c r="I123" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J123" s="8">
         <v>0</v>
@@ -10948,7 +10948,7 @@
       </c>
       <c r="M123" s="8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N123" s="8">
         <v>0</v>
@@ -11053,7 +11053,7 @@
         <v>7</v>
       </c>
       <c r="N125" s="8">
-        <v>245</v>
+        <v>186</v>
       </c>
       <c r="O125" s="8"/>
       <c r="P125" s="8"/>
@@ -11206,7 +11206,7 @@
         <v>4</v>
       </c>
       <c r="N128" s="8">
-        <v>826</v>
+        <v>814</v>
       </c>
       <c r="O128" s="8"/>
       <c r="P128" s="8"/>
@@ -11241,7 +11241,7 @@
         <v>15</v>
       </c>
       <c r="I129" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J129" s="8">
         <v>0</v>
@@ -11254,7 +11254,7 @@
       </c>
       <c r="M129" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N129" s="8">
         <v>0</v>
@@ -11298,17 +11298,17 @@
         <v>0</v>
       </c>
       <c r="K130" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L130" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M130" s="8">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="N130" s="8">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O130" s="8"/>
       <c r="P130" s="8"/>
@@ -11359,7 +11359,7 @@
         <v>3</v>
       </c>
       <c r="N131" s="8">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="O131" s="8"/>
       <c r="P131" s="8"/>
@@ -11394,7 +11394,7 @@
         <v>12</v>
       </c>
       <c r="I132" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J132" s="8">
         <v>0</v>
@@ -11403,14 +11403,14 @@
         <v>0</v>
       </c>
       <c r="L132" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M132" s="8">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N132" s="8">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="O132" s="8"/>
       <c r="P132" s="8"/>
@@ -11461,7 +11461,7 @@
         <v>29</v>
       </c>
       <c r="N133" s="8">
-        <v>254</v>
+        <v>14</v>
       </c>
       <c r="O133" s="8"/>
       <c r="P133" s="8"/>
@@ -11547,7 +11547,7 @@
         <v>15</v>
       </c>
       <c r="I135" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J135" s="8">
         <v>0</v>
@@ -11556,14 +11556,14 @@
         <v>0</v>
       </c>
       <c r="L135" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M135" s="8">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N135" s="8">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="O135" s="8"/>
       <c r="P135" s="8"/>
@@ -11598,7 +11598,7 @@
         <v>14</v>
       </c>
       <c r="I136" s="8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J136" s="8">
         <v>0</v>
@@ -11611,10 +11611,10 @@
       </c>
       <c r="M136" s="8">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N136" s="8">
-        <v>506</v>
+        <v>462</v>
       </c>
       <c r="O136" s="8"/>
       <c r="P136" s="8"/>
@@ -11716,7 +11716,7 @@
         <v>3</v>
       </c>
       <c r="N138" s="8">
-        <v>1051</v>
+        <v>1044</v>
       </c>
       <c r="O138" s="8"/>
       <c r="P138" s="8"/>
@@ -11802,7 +11802,7 @@
         <v>15</v>
       </c>
       <c r="I140" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J140" s="8">
         <v>0</v>
@@ -11815,10 +11815,10 @@
       </c>
       <c r="M140" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N140" s="8">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="O140" s="8"/>
       <c r="P140" s="8"/>
@@ -11869,7 +11869,7 @@
         <v>5</v>
       </c>
       <c r="N141" s="8">
-        <v>575</v>
+        <v>19</v>
       </c>
       <c r="O141" s="8"/>
       <c r="P141" s="8"/>
@@ -11955,23 +11955,23 @@
         <v>13</v>
       </c>
       <c r="I143" s="8">
+        <v>0</v>
+      </c>
+      <c r="J143" s="8">
+        <v>0</v>
+      </c>
+      <c r="K143" s="8">
+        <v>0</v>
+      </c>
+      <c r="L143" s="8">
         <v>1</v>
-      </c>
-      <c r="J143" s="8">
-        <v>0</v>
-      </c>
-      <c r="K143" s="8">
-        <v>0</v>
-      </c>
-      <c r="L143" s="8">
-        <v>0</v>
       </c>
       <c r="M143" s="8">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N143" s="8">
-        <v>145</v>
+        <v>9</v>
       </c>
       <c r="O143" s="8"/>
       <c r="P143" s="8"/>
@@ -12073,7 +12073,7 @@
         <v>4</v>
       </c>
       <c r="N145" s="8">
-        <v>844</v>
+        <v>835</v>
       </c>
       <c r="O145" s="8"/>
       <c r="P145" s="8"/>
@@ -12175,7 +12175,7 @@
         <v>2</v>
       </c>
       <c r="N147" s="8">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="O147" s="8"/>
       <c r="P147" s="8"/>
@@ -12226,7 +12226,7 @@
         <v>3</v>
       </c>
       <c r="N148" s="8">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="O148" s="8"/>
       <c r="P148" s="8"/>
@@ -12261,7 +12261,7 @@
         <v>12</v>
       </c>
       <c r="I149" s="8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J149" s="8">
         <v>0</v>
@@ -12270,14 +12270,14 @@
         <v>0</v>
       </c>
       <c r="L149" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M149" s="8">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="N149" s="8">
-        <v>279</v>
+        <v>218</v>
       </c>
       <c r="O149" s="8"/>
       <c r="P149" s="8"/>
@@ -12328,7 +12328,7 @@
         <v>3</v>
       </c>
       <c r="N150" s="8">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="O150" s="8"/>
       <c r="P150" s="8"/>
@@ -12379,7 +12379,7 @@
         <v>3</v>
       </c>
       <c r="N151" s="8">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="O151" s="8"/>
       <c r="P151" s="8"/>
@@ -12414,7 +12414,7 @@
         <v>15</v>
       </c>
       <c r="I152" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J152" s="8">
         <v>0</v>
@@ -12427,10 +12427,10 @@
       </c>
       <c r="M152" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N152" s="8">
-        <v>123</v>
+        <v>47</v>
       </c>
       <c r="O152" s="8"/>
       <c r="P152" s="8"/>
@@ -12471,17 +12471,17 @@
         <v>0</v>
       </c>
       <c r="K153" s="8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L153" s="8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M153" s="8">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="N153" s="8">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="O153" s="8"/>
       <c r="P153" s="8"/>
@@ -12532,7 +12532,7 @@
         <v>4</v>
       </c>
       <c r="N154" s="8">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="O154" s="8"/>
       <c r="P154" s="8"/>
@@ -12567,7 +12567,7 @@
         <v>14</v>
       </c>
       <c r="I155" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J155" s="8">
         <v>0</v>
@@ -12580,7 +12580,7 @@
       </c>
       <c r="M155" s="8">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N155" s="8">
         <v>0</v>
@@ -12771,7 +12771,7 @@
         <v>15</v>
       </c>
       <c r="I159" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J159" s="8">
         <v>0</v>
@@ -12784,10 +12784,10 @@
       </c>
       <c r="M159" s="8">
         <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="N159" s="8">
         <v>2</v>
-      </c>
-      <c r="N159" s="8">
-        <v>7</v>
       </c>
       <c r="O159" s="8"/>
       <c r="P159" s="8"/>
@@ -12838,7 +12838,7 @@
         <v>3</v>
       </c>
       <c r="N160" s="8">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="O160" s="8"/>
       <c r="P160" s="8"/>
@@ -12889,7 +12889,7 @@
         <v>6</v>
       </c>
       <c r="N161" s="8">
-        <v>455</v>
+        <v>427</v>
       </c>
       <c r="O161" s="8"/>
       <c r="P161" s="8"/>
@@ -12924,7 +12924,7 @@
         <v>13</v>
       </c>
       <c r="I162" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J162" s="8">
         <v>0</v>
@@ -12933,14 +12933,14 @@
         <v>0</v>
       </c>
       <c r="L162" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M162" s="8">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N162" s="8">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="O162" s="8"/>
       <c r="P162" s="8"/>
@@ -13042,7 +13042,7 @@
         <v>3</v>
       </c>
       <c r="N164" s="8">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="O164" s="8"/>
       <c r="P164" s="8"/>
@@ -13093,7 +13093,7 @@
         <v>10</v>
       </c>
       <c r="N165" s="8">
-        <v>1310</v>
+        <v>1237</v>
       </c>
       <c r="O165" s="8"/>
       <c r="P165" s="8"/>
@@ -13144,7 +13144,7 @@
         <v>4</v>
       </c>
       <c r="N166" s="8">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="O166" s="8"/>
       <c r="P166" s="8"/>
@@ -13230,7 +13230,7 @@
         <v>14</v>
       </c>
       <c r="I168" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J168" s="8">
         <v>0</v>
@@ -13239,14 +13239,14 @@
         <v>0</v>
       </c>
       <c r="L168" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M168" s="8">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="N168" s="8">
-        <v>383</v>
+        <v>361</v>
       </c>
       <c r="O168" s="8"/>
       <c r="P168" s="8"/>
@@ -13348,7 +13348,7 @@
         <v>4</v>
       </c>
       <c r="N170" s="8">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="O170" s="8"/>
       <c r="P170" s="8"/>
@@ -13450,7 +13450,7 @@
         <v>2</v>
       </c>
       <c r="N172" s="8">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O172" s="8"/>
       <c r="P172" s="8"/>
@@ -13501,7 +13501,7 @@
         <v>2</v>
       </c>
       <c r="N173" s="8">
-        <v>635</v>
+        <v>618</v>
       </c>
       <c r="O173" s="8"/>
       <c r="P173" s="8"/>
@@ -13654,7 +13654,7 @@
         <v>2</v>
       </c>
       <c r="N176" s="8">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="O176" s="8"/>
       <c r="P176" s="8"/>
@@ -13807,7 +13807,7 @@
         <v>2</v>
       </c>
       <c r="N179" s="8">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="O179" s="8"/>
       <c r="P179" s="8"/>
@@ -13842,7 +13842,7 @@
         <v>13</v>
       </c>
       <c r="I180" s="8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J180" s="8">
         <v>0</v>
@@ -13855,10 +13855,10 @@
       </c>
       <c r="M180" s="8">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N180" s="8">
-        <v>591</v>
+        <v>496</v>
       </c>
       <c r="O180" s="8"/>
       <c r="P180" s="8"/>
@@ -13899,17 +13899,17 @@
         <v>0</v>
       </c>
       <c r="K181" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L181" s="8">
         <v>1</v>
       </c>
       <c r="M181" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N181" s="8">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="O181" s="8"/>
       <c r="P181" s="8"/>
@@ -14011,7 +14011,7 @@
         <v>6</v>
       </c>
       <c r="N183" s="8">
-        <v>478</v>
+        <v>336</v>
       </c>
       <c r="O183" s="8"/>
       <c r="P183" s="8"/>
@@ -14097,20 +14097,20 @@
         <v>12</v>
       </c>
       <c r="I185" s="8">
-        <v>387</v>
+        <v>414</v>
       </c>
       <c r="J185" s="8">
         <v>0</v>
       </c>
       <c r="K185" s="8">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="L185" s="8">
         <v>0</v>
       </c>
       <c r="M185" s="8">
         <f t="shared" si="2"/>
-        <v>469</v>
+        <v>429</v>
       </c>
       <c r="N185" s="8">
         <v>1743</v>
@@ -14157,14 +14157,14 @@
         <v>0</v>
       </c>
       <c r="L186" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M186" s="8">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N186" s="8">
-        <v>945</v>
+        <v>876</v>
       </c>
       <c r="O186" s="8"/>
       <c r="P186" s="8"/>
@@ -14215,7 +14215,7 @@
         <v>2</v>
       </c>
       <c r="N187" s="8">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="O187" s="8"/>
       <c r="P187" s="8"/>
@@ -14266,7 +14266,7 @@
         <v>5</v>
       </c>
       <c r="N188" s="8">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O188" s="8"/>
       <c r="P188" s="8"/>
@@ -14358,17 +14358,17 @@
         <v>0</v>
       </c>
       <c r="K190" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L190" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M190" s="8">
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
       <c r="N190" s="8">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="O190" s="8"/>
       <c r="P190" s="8"/>
@@ -14419,7 +14419,7 @@
         <v>8</v>
       </c>
       <c r="N191" s="8">
-        <v>898</v>
+        <v>797</v>
       </c>
       <c r="O191" s="8"/>
       <c r="P191" s="8"/>
@@ -14521,7 +14521,7 @@
         <v>3</v>
       </c>
       <c r="N193" s="8">
-        <v>531</v>
+        <v>514</v>
       </c>
       <c r="O193" s="8"/>
       <c r="P193" s="8"/>
@@ -14725,7 +14725,7 @@
         <v>3</v>
       </c>
       <c r="N197" s="8">
-        <v>675</v>
+        <v>549</v>
       </c>
       <c r="O197" s="8"/>
       <c r="P197" s="8"/>
@@ -14929,7 +14929,7 @@
         <v>2</v>
       </c>
       <c r="N201" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O201" s="8"/>
       <c r="P201" s="8"/>
@@ -15235,7 +15235,7 @@
         <v>5</v>
       </c>
       <c r="N207" s="8">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="O207" s="8"/>
       <c r="P207" s="8"/>
@@ -15286,7 +15286,7 @@
         <v>3</v>
       </c>
       <c r="N208" s="8">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="O208" s="8"/>
       <c r="P208" s="8"/>
@@ -15321,23 +15321,23 @@
         <v>12</v>
       </c>
       <c r="I209" s="8">
+        <v>0</v>
+      </c>
+      <c r="J209" s="8">
+        <v>0</v>
+      </c>
+      <c r="K209" s="8">
+        <v>0</v>
+      </c>
+      <c r="L209" s="8">
         <v>1</v>
-      </c>
-      <c r="J209" s="8">
-        <v>0</v>
-      </c>
-      <c r="K209" s="8">
-        <v>0</v>
-      </c>
-      <c r="L209" s="8">
-        <v>0</v>
       </c>
       <c r="M209" s="8">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N209" s="8">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="O209" s="8"/>
       <c r="P209" s="8"/>
@@ -15423,7 +15423,7 @@
         <v>12</v>
       </c>
       <c r="I211" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J211" s="8">
         <v>0</v>
@@ -15436,10 +15436,10 @@
       </c>
       <c r="M211" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N211" s="8">
-        <v>738</v>
+        <v>728</v>
       </c>
       <c r="O211" s="8"/>
       <c r="P211" s="8"/>
@@ -15592,7 +15592,7 @@
         <v>2</v>
       </c>
       <c r="N214" s="8">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="O214" s="8"/>
       <c r="P214" s="8"/>
@@ -15627,7 +15627,7 @@
         <v>14</v>
       </c>
       <c r="I215" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J215" s="8">
         <v>0</v>
@@ -15640,7 +15640,7 @@
       </c>
       <c r="M215" s="8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N215" s="8">
         <v>703</v>
@@ -15745,7 +15745,7 @@
         <v>3</v>
       </c>
       <c r="N217" s="8">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="O217" s="8"/>
       <c r="P217" s="8"/>
@@ -15796,7 +15796,7 @@
         <v>6</v>
       </c>
       <c r="N218" s="8">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O218" s="8"/>
       <c r="P218" s="8"/>
@@ -15847,7 +15847,7 @@
         <v>6</v>
       </c>
       <c r="N219" s="8">
-        <v>407</v>
+        <v>393</v>
       </c>
       <c r="O219" s="8"/>
       <c r="P219" s="8"/>
@@ -15882,7 +15882,7 @@
         <v>16</v>
       </c>
       <c r="I220" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J220" s="8">
         <v>0</v>
@@ -15895,7 +15895,7 @@
       </c>
       <c r="M220" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N220" s="8">
         <v>0</v>
@@ -15949,7 +15949,7 @@
         <v>2</v>
       </c>
       <c r="N221" s="8">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="O221" s="8"/>
       <c r="P221" s="8"/>
@@ -15984,20 +15984,20 @@
         <v>16</v>
       </c>
       <c r="I222" s="8">
+        <v>0</v>
+      </c>
+      <c r="J222" s="8">
+        <v>0</v>
+      </c>
+      <c r="K222" s="8">
         <v>1</v>
       </c>
-      <c r="J222" s="8">
-        <v>0</v>
-      </c>
-      <c r="K222" s="8">
-        <v>0</v>
-      </c>
       <c r="L222" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M222" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N222" s="8">
         <v>135</v>
@@ -16051,7 +16051,7 @@
         <v>0</v>
       </c>
       <c r="N223" s="8">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="O223" s="8"/>
       <c r="P223" s="8"/>
@@ -16153,7 +16153,7 @@
         <v>3</v>
       </c>
       <c r="N225" s="8">
-        <v>597</v>
+        <v>552</v>
       </c>
       <c r="O225" s="8"/>
       <c r="P225" s="8"/>
@@ -16239,7 +16239,7 @@
         <v>16</v>
       </c>
       <c r="I227" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J227" s="8">
         <v>0</v>
@@ -16252,7 +16252,7 @@
       </c>
       <c r="M227" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N227" s="8">
         <v>0</v>
@@ -16299,14 +16299,14 @@
         <v>0</v>
       </c>
       <c r="L228" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M228" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N228" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O228" s="8"/>
       <c r="P228" s="8"/>
@@ -16357,7 +16357,7 @@
         <v>2</v>
       </c>
       <c r="N229" s="8">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="O229" s="8"/>
       <c r="P229" s="8"/>
@@ -16401,14 +16401,14 @@
         <v>0</v>
       </c>
       <c r="L230" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M230" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N230" s="8">
-        <v>213</v>
+        <v>93</v>
       </c>
       <c r="O230" s="8"/>
       <c r="P230" s="8"/>
@@ -16510,7 +16510,7 @@
         <v>12</v>
       </c>
       <c r="N232" s="8">
-        <v>588</v>
+        <v>518</v>
       </c>
       <c r="O232" s="8"/>
       <c r="P232" s="8"/>
@@ -16561,7 +16561,7 @@
         <v>4</v>
       </c>
       <c r="N233" s="8">
-        <v>663</v>
+        <v>588</v>
       </c>
       <c r="O233" s="8"/>
       <c r="P233" s="8"/>
@@ -16612,7 +16612,7 @@
         <v>2</v>
       </c>
       <c r="N234" s="8">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="O234" s="8"/>
       <c r="P234" s="8"/>
@@ -16663,7 +16663,7 @@
         <v>3</v>
       </c>
       <c r="N235" s="8">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="O235" s="8"/>
       <c r="P235" s="8"/>
@@ -16765,7 +16765,7 @@
         <v>3</v>
       </c>
       <c r="N237" s="8">
-        <v>844</v>
+        <v>785</v>
       </c>
       <c r="O237" s="8"/>
       <c r="P237" s="8"/>
@@ -16816,7 +16816,7 @@
         <v>6</v>
       </c>
       <c r="N238" s="8">
-        <v>502</v>
+        <v>456</v>
       </c>
       <c r="O238" s="8"/>
       <c r="P238" s="8"/>
@@ -16867,7 +16867,7 @@
         <v>3</v>
       </c>
       <c r="N239" s="8">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="O239" s="8"/>
       <c r="P239" s="8"/>
@@ -16902,7 +16902,7 @@
         <v>13</v>
       </c>
       <c r="I240" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J240" s="8">
         <v>0</v>
@@ -16911,14 +16911,14 @@
         <v>0</v>
       </c>
       <c r="L240" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M240" s="8">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="N240" s="8">
-        <v>444</v>
+        <v>367</v>
       </c>
       <c r="O240" s="8"/>
       <c r="P240" s="8"/>
@@ -16969,7 +16969,7 @@
         <v>3</v>
       </c>
       <c r="N241" s="8">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O241" s="8"/>
       <c r="P241" s="8"/>
@@ -17020,7 +17020,7 @@
         <v>3</v>
       </c>
       <c r="N242" s="8">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="O242" s="8"/>
       <c r="P242" s="8"/>
@@ -17055,23 +17055,23 @@
         <v>15</v>
       </c>
       <c r="I243" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J243" s="8">
         <v>0</v>
       </c>
       <c r="K243" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L243" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M243" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N243" s="8">
-        <v>237</v>
+        <v>156</v>
       </c>
       <c r="O243" s="8"/>
       <c r="P243" s="8"/>
@@ -17224,7 +17224,7 @@
         <v>3</v>
       </c>
       <c r="N246" s="8">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="O246" s="8"/>
       <c r="P246" s="8"/>
@@ -17259,23 +17259,23 @@
         <v>13</v>
       </c>
       <c r="I247" s="8">
+        <v>2</v>
+      </c>
+      <c r="J247" s="8">
+        <v>0</v>
+      </c>
+      <c r="K247" s="8">
+        <v>0</v>
+      </c>
+      <c r="L247" s="8">
         <v>1</v>
-      </c>
-      <c r="J247" s="8">
-        <v>0</v>
-      </c>
-      <c r="K247" s="8">
-        <v>0</v>
-      </c>
-      <c r="L247" s="8">
-        <v>0</v>
       </c>
       <c r="M247" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N247" s="8">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="O247" s="8"/>
       <c r="P247" s="8"/>
@@ -17310,7 +17310,7 @@
         <v>12</v>
       </c>
       <c r="I248" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J248" s="8">
         <v>0</v>
@@ -17323,7 +17323,7 @@
       </c>
       <c r="M248" s="8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N248" s="8">
         <v>0</v>
@@ -17428,7 +17428,7 @@
         <v>3</v>
       </c>
       <c r="N250" s="8">
-        <v>1442</v>
+        <v>1427</v>
       </c>
       <c r="O250" s="8"/>
       <c r="P250" s="8"/>
@@ -17479,7 +17479,7 @@
         <v>2</v>
       </c>
       <c r="N251" s="8">
-        <v>1240</v>
+        <v>1235</v>
       </c>
       <c r="O251" s="8"/>
       <c r="P251" s="8"/>
@@ -17530,7 +17530,7 @@
         <v>2</v>
       </c>
       <c r="N252" s="8">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="O252" s="8"/>
       <c r="P252" s="8"/>
@@ -17581,7 +17581,7 @@
         <v>2</v>
       </c>
       <c r="N253" s="8">
-        <v>1203</v>
+        <v>1195</v>
       </c>
       <c r="O253" s="8"/>
       <c r="P253" s="8"/>
@@ -17632,7 +17632,7 @@
         <v>2</v>
       </c>
       <c r="N254" s="8">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="O254" s="8"/>
       <c r="P254" s="8"/>
@@ -17683,7 +17683,7 @@
         <v>3</v>
       </c>
       <c r="N255" s="8">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="O255" s="8"/>
       <c r="P255" s="8"/>
@@ -17734,7 +17734,7 @@
         <v>1</v>
       </c>
       <c r="N256" s="8">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="O256" s="8"/>
       <c r="P256" s="8"/>
@@ -17785,7 +17785,7 @@
         <v>4</v>
       </c>
       <c r="N257" s="8">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="O257" s="8"/>
       <c r="P257" s="8"/>
@@ -17836,7 +17836,7 @@
         <v>2</v>
       </c>
       <c r="N258" s="8">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="O258" s="8"/>
       <c r="P258" s="8"/>
@@ -17887,7 +17887,7 @@
         <v>3</v>
       </c>
       <c r="N259" s="8">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O259" s="8"/>
       <c r="P259" s="8"/>
@@ -17938,7 +17938,7 @@
         <v>5</v>
       </c>
       <c r="N260" s="8">
-        <v>219</v>
+        <v>161</v>
       </c>
       <c r="O260" s="8"/>
       <c r="P260" s="8"/>
@@ -17973,7 +17973,7 @@
         <v>12</v>
       </c>
       <c r="I261" s="8">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J261" s="8">
         <v>0</v>
@@ -17986,10 +17986,10 @@
       </c>
       <c r="M261" s="8">
         <f t="shared" si="4"/>
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="N261" s="8">
-        <v>875</v>
+        <v>776</v>
       </c>
       <c r="O261" s="8"/>
       <c r="P261" s="8"/>
@@ -18024,7 +18024,7 @@
         <v>12</v>
       </c>
       <c r="I262" s="8">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J262" s="8">
         <v>0</v>
@@ -18037,10 +18037,10 @@
       </c>
       <c r="M262" s="8">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="N262" s="8">
-        <v>366</v>
+        <v>292</v>
       </c>
       <c r="O262" s="8"/>
       <c r="P262" s="8"/>
@@ -18075,7 +18075,7 @@
         <v>12</v>
       </c>
       <c r="I263" s="8">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J263" s="8">
         <v>0</v>
@@ -18084,14 +18084,14 @@
         <v>0</v>
       </c>
       <c r="L263" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M263" s="8">
         <f t="shared" si="4"/>
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N263" s="8">
-        <v>248</v>
+        <v>79</v>
       </c>
       <c r="O263" s="8"/>
       <c r="P263" s="8"/>
@@ -18142,7 +18142,7 @@
         <v>2</v>
       </c>
       <c r="N264" s="8">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="O264" s="8"/>
       <c r="P264" s="8"/>
@@ -18193,7 +18193,7 @@
         <v>2</v>
       </c>
       <c r="N265" s="8">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O265" s="8"/>
       <c r="P265" s="8"/>
@@ -18244,7 +18244,7 @@
         <v>3</v>
       </c>
       <c r="N266" s="8">
-        <v>1545</v>
+        <v>1540</v>
       </c>
       <c r="O266" s="8"/>
       <c r="P266" s="8"/>
@@ -18295,7 +18295,7 @@
         <v>3</v>
       </c>
       <c r="N267" s="8">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="O267" s="8"/>
       <c r="P267" s="8"/>
@@ -18330,7 +18330,7 @@
         <v>15</v>
       </c>
       <c r="I268" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J268" s="8">
         <v>0</v>
@@ -18343,7 +18343,7 @@
       </c>
       <c r="M268" s="8">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N268" s="8">
         <v>0</v>
@@ -18397,7 +18397,7 @@
         <v>4</v>
       </c>
       <c r="N269" s="8">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="O269" s="8"/>
       <c r="P269" s="8"/>
@@ -18534,7 +18534,7 @@
         <v>16</v>
       </c>
       <c r="I272" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J272" s="8">
         <v>0</v>
@@ -18547,7 +18547,7 @@
       </c>
       <c r="M272" s="8">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N272" s="8">
         <v>0</v>
@@ -18642,17 +18642,17 @@
         <v>0</v>
       </c>
       <c r="K274" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L274" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M274" s="8">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="N274" s="8">
-        <v>92</v>
+        <v>1</v>
       </c>
       <c r="O274" s="8"/>
       <c r="P274" s="8"/>
@@ -18687,7 +18687,7 @@
         <v>15</v>
       </c>
       <c r="I275" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J275" s="8">
         <v>0</v>
@@ -18700,10 +18700,10 @@
       </c>
       <c r="M275" s="8">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N275" s="8">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O275" s="8"/>
       <c r="P275" s="8"/>
@@ -18754,7 +18754,7 @@
         <v>3</v>
       </c>
       <c r="N276" s="8">
-        <v>292</v>
+        <v>221</v>
       </c>
       <c r="O276" s="8"/>
       <c r="P276" s="8"/>
@@ -18856,7 +18856,7 @@
         <v>9</v>
       </c>
       <c r="N278" s="8">
-        <v>1553</v>
+        <v>1354</v>
       </c>
       <c r="O278" s="8"/>
       <c r="P278" s="8"/>
@@ -18897,17 +18897,17 @@
         <v>0</v>
       </c>
       <c r="K279" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L279" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M279" s="8">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="N279" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O279" s="8"/>
       <c r="P279" s="8"/>
@@ -18958,7 +18958,7 @@
         <v>3</v>
       </c>
       <c r="N280" s="8">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O280" s="8"/>
       <c r="P280" s="8"/>
@@ -19009,7 +19009,7 @@
         <v>2</v>
       </c>
       <c r="N281" s="8">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O281" s="8"/>
       <c r="P281" s="8"/>
@@ -19095,7 +19095,7 @@
         <v>12</v>
       </c>
       <c r="I283" s="8">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J283" s="8">
         <v>0</v>
@@ -19108,10 +19108,10 @@
       </c>
       <c r="M283" s="8">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N283" s="8">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="O283" s="8"/>
       <c r="P283" s="8"/>
@@ -19146,7 +19146,7 @@
         <v>12</v>
       </c>
       <c r="I284" s="8">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="J284" s="8">
         <v>0</v>
@@ -19159,7 +19159,7 @@
       </c>
       <c r="M284" s="8">
         <f t="shared" si="4"/>
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="N284" s="8">
         <v>0</v>
@@ -19213,7 +19213,7 @@
         <v>3</v>
       </c>
       <c r="N285" s="8">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="O285" s="8"/>
       <c r="P285" s="8"/>
@@ -19264,7 +19264,7 @@
         <v>4</v>
       </c>
       <c r="N286" s="8">
-        <v>994</v>
+        <v>982</v>
       </c>
       <c r="O286" s="8"/>
       <c r="P286" s="8"/>
@@ -19315,7 +19315,7 @@
         <v>9</v>
       </c>
       <c r="N287" s="8">
-        <v>1142</v>
+        <v>1120</v>
       </c>
       <c r="O287" s="8"/>
       <c r="P287" s="8"/>
@@ -19366,7 +19366,7 @@
         <v>4</v>
       </c>
       <c r="N288" s="8">
-        <v>1476</v>
+        <v>1450</v>
       </c>
       <c r="O288" s="8"/>
       <c r="P288" s="8"/>
@@ -19410,14 +19410,14 @@
         <v>0</v>
       </c>
       <c r="L289" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M289" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N289" s="8">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O289" s="8"/>
       <c r="P289" s="8"/>
@@ -19468,7 +19468,7 @@
         <v>1</v>
       </c>
       <c r="N290" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O290" s="8"/>
       <c r="P290" s="8"/>
@@ -19503,7 +19503,7 @@
         <v>12</v>
       </c>
       <c r="I291" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J291" s="8">
         <v>0</v>
@@ -19516,10 +19516,10 @@
       </c>
       <c r="M291" s="8">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N291" s="8">
-        <v>2020</v>
+        <v>1791</v>
       </c>
       <c r="O291" s="8"/>
       <c r="P291" s="8"/>
@@ -19570,7 +19570,7 @@
         <v>3</v>
       </c>
       <c r="N292" s="8">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="O292" s="8"/>
       <c r="P292" s="8"/>
@@ -19656,23 +19656,23 @@
         <v>12</v>
       </c>
       <c r="I294" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J294" s="8">
         <v>0</v>
       </c>
       <c r="K294" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L294" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M294" s="8">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N294" s="8">
-        <v>1518</v>
+        <v>1484</v>
       </c>
       <c r="O294" s="8"/>
       <c r="P294" s="8"/>
@@ -19962,7 +19962,7 @@
         <v>13</v>
       </c>
       <c r="I300" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J300" s="8">
         <v>0</v>
@@ -19975,7 +19975,7 @@
       </c>
       <c r="M300" s="8">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N300" s="8">
         <v>0</v>
@@ -20029,7 +20029,7 @@
         <v>6</v>
       </c>
       <c r="N301" s="8">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O301" s="8"/>
       <c r="P301" s="8"/>
@@ -20080,7 +20080,7 @@
         <v>5</v>
       </c>
       <c r="N302" s="8">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="O302" s="8"/>
       <c r="P302" s="8"/>
@@ -20182,7 +20182,7 @@
         <v>4</v>
       </c>
       <c r="N304" s="8">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="O304" s="8"/>
       <c r="P304" s="8"/>
@@ -20233,7 +20233,7 @@
         <v>8</v>
       </c>
       <c r="N305" s="8">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="O305" s="8"/>
       <c r="P305" s="8"/>
@@ -20284,7 +20284,7 @@
         <v>9</v>
       </c>
       <c r="N306" s="8">
-        <v>1098</v>
+        <v>1057</v>
       </c>
       <c r="O306" s="8"/>
       <c r="P306" s="8"/>
@@ -20335,7 +20335,7 @@
         <v>11</v>
       </c>
       <c r="N307" s="8">
-        <v>1048</v>
+        <v>1027</v>
       </c>
       <c r="O307" s="8"/>
       <c r="P307" s="8"/>
@@ -20386,7 +20386,7 @@
         <v>11</v>
       </c>
       <c r="N308" s="8">
-        <v>1036</v>
+        <v>996</v>
       </c>
       <c r="O308" s="8"/>
       <c r="P308" s="8"/>
@@ -20437,7 +20437,7 @@
         <v>3</v>
       </c>
       <c r="N309" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O309" s="8"/>
       <c r="P309" s="8"/>
@@ -20488,7 +20488,7 @@
         <v>4</v>
       </c>
       <c r="N310" s="8">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="O310" s="8"/>
       <c r="P310" s="8"/>
@@ -20539,7 +20539,7 @@
         <v>2</v>
       </c>
       <c r="N311" s="8">
-        <v>186</v>
+        <v>156</v>
       </c>
       <c r="O311" s="8"/>
       <c r="P311" s="8"/>
@@ -20590,7 +20590,7 @@
         <v>6</v>
       </c>
       <c r="N312" s="8">
-        <v>126</v>
+        <v>60</v>
       </c>
       <c r="O312" s="8"/>
       <c r="P312" s="8"/>
@@ -20641,7 +20641,7 @@
         <v>2</v>
       </c>
       <c r="N313" s="8">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="O313" s="8"/>
       <c r="P313" s="8"/>
@@ -20676,7 +20676,7 @@
         <v>12</v>
       </c>
       <c r="I314" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J314" s="8">
         <v>0</v>
@@ -20685,14 +20685,14 @@
         <v>0</v>
       </c>
       <c r="L314" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M314" s="8">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N314" s="8">
-        <v>445</v>
+        <v>411</v>
       </c>
       <c r="O314" s="8"/>
       <c r="P314" s="8"/>
@@ -20743,7 +20743,7 @@
         <v>8</v>
       </c>
       <c r="N315" s="8">
-        <v>237</v>
+        <v>203</v>
       </c>
       <c r="O315" s="8"/>
       <c r="P315" s="8"/>
@@ -20794,7 +20794,7 @@
         <v>7</v>
       </c>
       <c r="N316" s="8">
-        <v>746</v>
+        <v>707</v>
       </c>
       <c r="O316" s="8"/>
       <c r="P316" s="8"/>
@@ -20829,23 +20829,23 @@
         <v>12</v>
       </c>
       <c r="I317" s="8">
+        <v>2</v>
+      </c>
+      <c r="J317" s="8">
+        <v>0</v>
+      </c>
+      <c r="K317" s="8">
+        <v>2</v>
+      </c>
+      <c r="L317" s="8">
         <v>3</v>
-      </c>
-      <c r="J317" s="8">
-        <v>0</v>
-      </c>
-      <c r="K317" s="8">
-        <v>0</v>
-      </c>
-      <c r="L317" s="8">
-        <v>2</v>
       </c>
       <c r="M317" s="8">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N317" s="8">
-        <v>389</v>
+        <v>299</v>
       </c>
       <c r="O317" s="8"/>
       <c r="P317" s="8"/>
@@ -20880,23 +20880,23 @@
         <v>12</v>
       </c>
       <c r="I318" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J318" s="8">
         <v>0</v>
       </c>
       <c r="K318" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L318" s="8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M318" s="8">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N318" s="8">
-        <v>951</v>
+        <v>798</v>
       </c>
       <c r="O318" s="8"/>
       <c r="P318" s="8"/>
@@ -20947,7 +20947,7 @@
         <v>4</v>
       </c>
       <c r="N319" s="8">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="O319" s="8"/>
       <c r="P319" s="8"/>
@@ -20998,7 +20998,7 @@
         <v>4</v>
       </c>
       <c r="N320" s="8">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="O320" s="8"/>
       <c r="P320" s="8"/>
@@ -21033,23 +21033,23 @@
         <v>14</v>
       </c>
       <c r="I321" s="8">
+        <v>0</v>
+      </c>
+      <c r="J321" s="8">
+        <v>0</v>
+      </c>
+      <c r="K321" s="8">
+        <v>0</v>
+      </c>
+      <c r="L321" s="8">
         <v>1</v>
-      </c>
-      <c r="J321" s="8">
-        <v>0</v>
-      </c>
-      <c r="K321" s="8">
-        <v>0</v>
-      </c>
-      <c r="L321" s="8">
-        <v>0</v>
       </c>
       <c r="M321" s="8">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="N321" s="8">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="O321" s="8"/>
       <c r="P321" s="8"/>
@@ -21100,7 +21100,7 @@
         <v>3</v>
       </c>
       <c r="N322" s="8">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="O322" s="8"/>
       <c r="P322" s="8"/>
@@ -21151,7 +21151,7 @@
         <v>4</v>
       </c>
       <c r="N323" s="8">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="O323" s="8"/>
       <c r="P323" s="8"/>
@@ -21195,11 +21195,11 @@
         <v>0</v>
       </c>
       <c r="L324" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M324" s="8">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N324" s="8">
         <v>0</v>
@@ -21253,7 +21253,7 @@
         <v>3</v>
       </c>
       <c r="N325" s="8">
-        <v>501</v>
+        <v>466</v>
       </c>
       <c r="O325" s="8"/>
       <c r="P325" s="8"/>
@@ -21304,7 +21304,7 @@
         <v>3</v>
       </c>
       <c r="N326" s="8">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="O326" s="8"/>
       <c r="P326" s="8"/>
@@ -21355,7 +21355,7 @@
         <v>3</v>
       </c>
       <c r="N327" s="8">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="O327" s="8"/>
       <c r="P327" s="8"/>
@@ -21406,7 +21406,7 @@
         <v>2</v>
       </c>
       <c r="N328" s="8">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="O328" s="8"/>
       <c r="P328" s="8"/>
@@ -21457,7 +21457,7 @@
         <v>4</v>
       </c>
       <c r="N329" s="8">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="O329" s="8"/>
       <c r="P329" s="8"/>
@@ -21508,7 +21508,7 @@
         <v>2</v>
       </c>
       <c r="N330" s="8">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O330" s="8"/>
       <c r="P330" s="8"/>
@@ -21661,7 +21661,7 @@
         <v>3</v>
       </c>
       <c r="N333" s="8">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="O333" s="8"/>
       <c r="P333" s="8"/>
@@ -21712,7 +21712,7 @@
         <v>4</v>
       </c>
       <c r="N334" s="8">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="O334" s="8"/>
       <c r="P334" s="8"/>
@@ -21753,17 +21753,17 @@
         <v>0</v>
       </c>
       <c r="K335" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L335" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M335" s="8">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="N335" s="8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O335" s="8"/>
       <c r="P335" s="8"/>
@@ -21814,7 +21814,7 @@
         <v>4</v>
       </c>
       <c r="N336" s="8">
-        <v>649</v>
+        <v>626</v>
       </c>
       <c r="O336" s="8"/>
       <c r="P336" s="8"/>
@@ -21849,7 +21849,7 @@
         <v>12</v>
       </c>
       <c r="I337" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J337" s="8">
         <v>0</v>
@@ -21862,10 +21862,10 @@
       </c>
       <c r="M337" s="8">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N337" s="8">
-        <v>1211</v>
+        <v>1202</v>
       </c>
       <c r="O337" s="8"/>
       <c r="P337" s="8"/>
@@ -21900,23 +21900,23 @@
         <v>12</v>
       </c>
       <c r="I338" s="8">
+        <v>1</v>
+      </c>
+      <c r="J338" s="8">
+        <v>0</v>
+      </c>
+      <c r="K338" s="8">
+        <v>6</v>
+      </c>
+      <c r="L338" s="8">
         <v>2</v>
-      </c>
-      <c r="J338" s="8">
-        <v>0</v>
-      </c>
-      <c r="K338" s="8">
-        <v>0</v>
-      </c>
-      <c r="L338" s="8">
-        <v>6</v>
       </c>
       <c r="M338" s="8">
         <f t="shared" si="5"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N338" s="8">
-        <v>1323</v>
+        <v>1267</v>
       </c>
       <c r="O338" s="8"/>
       <c r="P338" s="8"/>
@@ -21967,7 +21967,7 @@
         <v>3</v>
       </c>
       <c r="N339" s="8">
-        <v>874</v>
+        <v>858</v>
       </c>
       <c r="O339" s="8"/>
       <c r="P339" s="8"/>
@@ -22002,23 +22002,23 @@
         <v>14</v>
       </c>
       <c r="I340" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J340" s="8">
         <v>0</v>
       </c>
       <c r="K340" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L340" s="8">
         <v>5</v>
       </c>
       <c r="M340" s="8">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N340" s="8">
-        <v>842</v>
+        <v>794</v>
       </c>
       <c r="O340" s="8"/>
       <c r="P340" s="8"/>
@@ -22059,17 +22059,17 @@
         <v>0</v>
       </c>
       <c r="K341" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L341" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M341" s="8">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="N341" s="8">
-        <v>400</v>
+        <v>373</v>
       </c>
       <c r="O341" s="8"/>
       <c r="P341" s="8"/>
@@ -22120,7 +22120,7 @@
         <v>4</v>
       </c>
       <c r="N342" s="8">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O342" s="8"/>
       <c r="P342" s="8"/>
@@ -22206,7 +22206,7 @@
         <v>12</v>
       </c>
       <c r="I344" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J344" s="8">
         <v>0</v>
@@ -22219,7 +22219,7 @@
       </c>
       <c r="M344" s="8">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N344" s="8">
         <v>0</v>
@@ -22257,7 +22257,7 @@
         <v>12</v>
       </c>
       <c r="I345" s="8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J345" s="8">
         <v>0</v>
@@ -22270,7 +22270,7 @@
       </c>
       <c r="M345" s="8">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N345" s="8">
         <v>0</v>
@@ -22359,23 +22359,23 @@
         <v>13</v>
       </c>
       <c r="I347" s="8">
+        <v>11</v>
+      </c>
+      <c r="J347" s="8">
+        <v>0</v>
+      </c>
+      <c r="K347" s="8">
         <v>12</v>
       </c>
-      <c r="J347" s="8">
-        <v>0</v>
-      </c>
-      <c r="K347" s="8">
-        <v>0</v>
-      </c>
       <c r="L347" s="8">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M347" s="8">
         <f t="shared" si="5"/>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N347" s="8">
-        <v>675</v>
+        <v>588</v>
       </c>
       <c r="O347" s="8"/>
       <c r="P347" s="9"/>
@@ -22426,7 +22426,7 @@
         <v>81</v>
       </c>
       <c r="N348" s="8">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="O348" s="8"/>
       <c r="P348" s="9"/>
@@ -22630,7 +22630,7 @@
         <v>2</v>
       </c>
       <c r="N352" s="8">
-        <v>494</v>
+        <v>480</v>
       </c>
       <c r="O352" s="8"/>
       <c r="P352" s="9"/>
@@ -22885,7 +22885,7 @@
         <v>0</v>
       </c>
       <c r="N357" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O357" s="8"/>
       <c r="P357" s="9"/>
@@ -23175,20 +23175,20 @@
         <v>12</v>
       </c>
       <c r="I363" s="8">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="J363" s="8">
         <v>0</v>
       </c>
       <c r="K363" s="8">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="L363" s="8">
         <v>0</v>
       </c>
       <c r="M363" s="8">
         <f t="shared" si="5"/>
-        <v>633</v>
+        <v>620</v>
       </c>
       <c r="N363" s="8">
         <v>1318</v>
@@ -23344,7 +23344,7 @@
         <v>2</v>
       </c>
       <c r="N366" s="8">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="O366" s="8"/>
       <c r="P366" s="9"/>
@@ -23379,7 +23379,7 @@
         <v>12</v>
       </c>
       <c r="I367" s="8">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="J367" s="8">
         <v>0</v>
@@ -23392,7 +23392,7 @@
       </c>
       <c r="M367" s="8">
         <f t="shared" si="5"/>
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="N367" s="8">
         <v>0</v>
@@ -23436,17 +23436,17 @@
         <v>0</v>
       </c>
       <c r="K368" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L368" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M368" s="8">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="N368" s="8">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="O368" s="8"/>
       <c r="P368" s="9"/>
@@ -23481,7 +23481,7 @@
         <v>15</v>
       </c>
       <c r="I369" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J369" s="8">
         <v>0</v>
@@ -23494,7 +23494,7 @@
       </c>
       <c r="M369" s="8">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N369" s="8">
         <v>0</v>
@@ -23548,7 +23548,7 @@
         <v>2</v>
       </c>
       <c r="N370" s="8">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="O370" s="8"/>
       <c r="P370" s="9"/>
@@ -23685,7 +23685,7 @@
         <v>14</v>
       </c>
       <c r="I373" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J373" s="8">
         <v>0</v>
@@ -23698,10 +23698,10 @@
       </c>
       <c r="M373" s="8">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N373" s="8">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O373" s="8"/>
       <c r="P373" s="9"/>
@@ -24144,7 +24144,7 @@
         <v>13</v>
       </c>
       <c r="I382" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J382" s="8">
         <v>0</v>
@@ -24157,7 +24157,7 @@
       </c>
       <c r="M382" s="8">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N382" s="8">
         <v>0</v>
@@ -24246,7 +24246,7 @@
         <v>12</v>
       </c>
       <c r="I384" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J384" s="8">
         <v>0</v>
@@ -24259,10 +24259,10 @@
       </c>
       <c r="M384" s="8">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N384" s="8">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="O384" s="8"/>
       <c r="P384" s="9"/>
@@ -24297,7 +24297,7 @@
         <v>12</v>
       </c>
       <c r="I385" s="8">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="J385" s="8">
         <v>0</v>
@@ -24310,7 +24310,7 @@
       </c>
       <c r="M385" s="8">
         <f t="shared" si="5"/>
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="N385" s="8">
         <v>257</v>
@@ -24552,7 +24552,7 @@
         <v>12</v>
       </c>
       <c r="I390" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J390" s="8">
         <v>0</v>
@@ -24561,14 +24561,14 @@
         <v>0</v>
       </c>
       <c r="L390" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M390" s="8">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="N390" s="8">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="O390" s="8"/>
       <c r="P390" s="7"/>
@@ -24966,17 +24966,17 @@
         <v>0</v>
       </c>
       <c r="K398" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L398" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M398" s="8">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N398" s="8">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="O398" s="7"/>
       <c r="P398" s="7"/>
@@ -25272,17 +25272,17 @@
         <v>0</v>
       </c>
       <c r="K404" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L404" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M404" s="8">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="N404" s="8">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="O404" s="7"/>
       <c r="P404" s="7"/>
@@ -25323,17 +25323,17 @@
         <v>0</v>
       </c>
       <c r="K405" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L405" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M405" s="8">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="N405" s="8">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="O405" s="7"/>
       <c r="P405" s="7"/>
@@ -25374,10 +25374,10 @@
         <v>0</v>
       </c>
       <c r="K406" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L406" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M406" s="8">
         <f t="shared" si="7"/>
@@ -25428,11 +25428,11 @@
         <v>0</v>
       </c>
       <c r="L407" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M407" s="8">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N407" s="8">
         <v>0</v>
@@ -25476,17 +25476,17 @@
         <v>0</v>
       </c>
       <c r="K408" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L408" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M408" s="8">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="N408" s="8">
-        <v>19</v>
+        <v>297</v>
       </c>
       <c r="O408" s="7"/>
       <c r="P408" s="7"/>
@@ -25527,17 +25527,17 @@
         <v>0</v>
       </c>
       <c r="K409" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L409" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M409" s="8">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="N409" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O409" s="7"/>
       <c r="P409" s="7"/>
@@ -25578,17 +25578,17 @@
         <v>0</v>
       </c>
       <c r="K410" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L410" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M410" s="8">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="N410" s="8">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="O410" s="7"/>
       <c r="P410" s="7"/>
@@ -25629,17 +25629,17 @@
         <v>0</v>
       </c>
       <c r="K411" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L411" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M411" s="8">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="N411" s="8">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O411" s="7"/>
       <c r="P411" s="7"/>
@@ -25680,17 +25680,17 @@
         <v>0</v>
       </c>
       <c r="K412" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L412" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M412" s="8">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="N412" s="8">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="O412" s="7"/>
       <c r="P412" s="7"/>
@@ -25731,17 +25731,17 @@
         <v>0</v>
       </c>
       <c r="K413" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L413" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M413" s="8">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="N413" s="8">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="O413" s="7"/>
       <c r="P413" s="7"/>
@@ -25785,14 +25785,14 @@
         <v>0</v>
       </c>
       <c r="L414" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M414" s="8">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N414" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O414" s="7"/>
       <c r="P414" s="7"/>
@@ -25836,14 +25836,14 @@
         <v>0</v>
       </c>
       <c r="L415" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M415" s="8">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N415" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O415" s="7"/>
       <c r="P415" s="7"/>
@@ -25884,17 +25884,17 @@
         <v>0</v>
       </c>
       <c r="K416" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L416" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M416" s="8">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="N416" s="8">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="O416" s="7"/>
       <c r="P416" s="7"/>
@@ -25935,17 +25935,17 @@
         <v>0</v>
       </c>
       <c r="K417" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L417" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M417" s="8">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="N417" s="8">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="O417" s="7"/>
       <c r="P417" s="7"/>
@@ -25986,17 +25986,17 @@
         <v>0</v>
       </c>
       <c r="K418" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L418" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M418" s="8">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="N418" s="8">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="O418" s="7"/>
       <c r="P418" s="7"/>
@@ -26037,17 +26037,17 @@
         <v>0</v>
       </c>
       <c r="K419" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L419" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M419" s="8">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="N419" s="8">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O419" s="7"/>
       <c r="P419" s="7"/>
@@ -26088,17 +26088,17 @@
         <v>0</v>
       </c>
       <c r="K420" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L420" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M420" s="8">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="N420" s="8">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="O420" s="7"/>
       <c r="P420" s="7"/>
@@ -26139,17 +26139,17 @@
         <v>0</v>
       </c>
       <c r="K421" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L421" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M421" s="8">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="N421" s="8">
-        <v>458</v>
+        <v>433</v>
       </c>
       <c r="O421" s="7"/>
       <c r="P421" s="7"/>
@@ -26190,17 +26190,17 @@
         <v>0</v>
       </c>
       <c r="K422" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L422" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M422" s="8">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="N422" s="8">
-        <v>284</v>
+        <v>257</v>
       </c>
       <c r="O422" s="7"/>
       <c r="P422" s="7"/>
@@ -26241,17 +26241,17 @@
         <v>0</v>
       </c>
       <c r="K423" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L423" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M423" s="8">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="N423" s="8">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O423" s="7"/>
       <c r="P423" s="7"/>
@@ -26292,17 +26292,17 @@
         <v>0</v>
       </c>
       <c r="K424" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L424" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M424" s="8">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="N424" s="8">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="O424" s="7"/>
       <c r="P424" s="7"/>
@@ -26343,17 +26343,17 @@
         <v>0</v>
       </c>
       <c r="K425" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L425" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M425" s="8">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="N425" s="8">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O425" s="7"/>
       <c r="P425" s="7"/>
@@ -26394,17 +26394,17 @@
         <v>0</v>
       </c>
       <c r="K426" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L426" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M426" s="8">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="N426" s="8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O426" s="7"/>
       <c r="P426" s="7"/>
@@ -26445,17 +26445,17 @@
         <v>0</v>
       </c>
       <c r="K427" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L427" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M427" s="8">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="N427" s="8">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O427" s="7"/>
       <c r="P427" s="7"/>
@@ -26506,7 +26506,7 @@
         <v>0</v>
       </c>
       <c r="N428" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O428" s="7"/>
       <c r="P428" s="7"/>
@@ -26608,7 +26608,7 @@
         <v>0</v>
       </c>
       <c r="N430" s="8">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="O430" s="7"/>
       <c r="P430" s="7"/>
@@ -26659,7 +26659,7 @@
         <v>0</v>
       </c>
       <c r="N431" s="8">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="O431" s="7"/>
       <c r="P431" s="7"/>
@@ -26761,7 +26761,7 @@
         <v>0</v>
       </c>
       <c r="N433" s="8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O433" s="7"/>
       <c r="P433" s="7"/>

--- a/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
+++ b/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\Fossil Replenishment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C5A942F-14CB-4363-A063-10D05F099FA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6492CF69-64E1-486E-8DA8-E80C960992B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6662473D-6E1F-42FD-999B-28162E22D4B5}"/>
   </bookViews>
@@ -4764,7 +4764,7 @@
         <v>12</v>
       </c>
       <c r="I2" s="8">
-        <v>741</v>
+        <v>724</v>
       </c>
       <c r="J2" s="8">
         <v>0</v>
@@ -4773,11 +4773,11 @@
         <v>18</v>
       </c>
       <c r="L2" s="8">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="M2" s="8">
         <f>I2+J2+K2+L2</f>
-        <v>759</v>
+        <v>846</v>
       </c>
       <c r="N2" s="8">
         <v>1385</v>
@@ -4866,7 +4866,7 @@
         <v>12</v>
       </c>
       <c r="I4" s="8">
-        <v>183</v>
+        <v>275</v>
       </c>
       <c r="J4" s="8">
         <v>0</v>
@@ -4879,7 +4879,7 @@
       </c>
       <c r="M4" s="8">
         <f t="shared" si="0"/>
-        <v>183</v>
+        <v>275</v>
       </c>
       <c r="N4" s="8">
         <v>0</v>
@@ -4917,7 +4917,7 @@
         <v>12</v>
       </c>
       <c r="I5" s="8">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="J5" s="8">
         <v>0</v>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="M5" s="8">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="N5" s="8">
         <v>0</v>
@@ -4968,7 +4968,7 @@
         <v>12</v>
       </c>
       <c r="I6" s="8">
-        <v>792</v>
+        <v>758</v>
       </c>
       <c r="J6" s="8">
         <v>0</v>
@@ -4977,11 +4977,11 @@
         <v>16</v>
       </c>
       <c r="L6" s="8">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M6" s="8">
         <f t="shared" si="0"/>
-        <v>808</v>
+        <v>846</v>
       </c>
       <c r="N6" s="8">
         <v>1658</v>
@@ -5019,7 +5019,7 @@
         <v>12</v>
       </c>
       <c r="I7" s="8">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="J7" s="8">
         <v>0</v>
@@ -5032,10 +5032,10 @@
       </c>
       <c r="M7" s="8">
         <f t="shared" si="0"/>
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="N7" s="8">
-        <v>515</v>
+        <v>1028</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
@@ -5070,7 +5070,7 @@
         <v>12</v>
       </c>
       <c r="I8" s="8">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="J8" s="8">
         <v>0</v>
@@ -5083,10 +5083,10 @@
       </c>
       <c r="M8" s="8">
         <f t="shared" si="0"/>
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="N8" s="8">
-        <v>575</v>
+        <v>482</v>
       </c>
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
@@ -5121,23 +5121,23 @@
         <v>12</v>
       </c>
       <c r="I9" s="8">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="J9" s="8">
         <v>0</v>
       </c>
       <c r="K9" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L9" s="8">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="M9" s="8">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="N9" s="8">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
@@ -5172,20 +5172,20 @@
         <v>12</v>
       </c>
       <c r="I10" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J10" s="8">
         <v>0</v>
       </c>
       <c r="K10" s="8">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L10" s="8">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M10" s="8">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="N10" s="8">
         <v>0</v>
@@ -5223,23 +5223,23 @@
         <v>12</v>
       </c>
       <c r="I11" s="8">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="J11" s="8">
         <v>0</v>
       </c>
       <c r="K11" s="8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L11" s="8">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="M11" s="8">
         <f t="shared" si="0"/>
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="N11" s="8">
-        <v>172</v>
+        <v>7</v>
       </c>
       <c r="O11" s="8"/>
       <c r="P11" s="8"/>
@@ -5274,7 +5274,7 @@
         <v>12</v>
       </c>
       <c r="I12" s="8">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J12" s="8">
         <v>0</v>
@@ -5287,7 +5287,7 @@
       </c>
       <c r="M12" s="8">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="N12" s="8">
         <v>0</v>
@@ -5325,7 +5325,7 @@
         <v>12</v>
       </c>
       <c r="I13" s="8">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="J13" s="8">
         <v>0</v>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="M13" s="8">
         <f t="shared" si="0"/>
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="N13" s="8">
         <v>858</v>
@@ -5376,7 +5376,7 @@
         <v>12</v>
       </c>
       <c r="I14" s="8">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J14" s="8">
         <v>0</v>
@@ -5389,10 +5389,10 @@
       </c>
       <c r="M14" s="8">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="N14" s="8">
-        <v>739</v>
+        <v>697</v>
       </c>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
@@ -5427,20 +5427,20 @@
         <v>12</v>
       </c>
       <c r="I15" s="8">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J15" s="8">
         <v>0</v>
       </c>
       <c r="K15" s="8">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L15" s="8">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M15" s="8">
         <f t="shared" si="0"/>
-        <v>129</v>
+        <v>15</v>
       </c>
       <c r="N15" s="8">
         <v>0</v>
@@ -5478,23 +5478,23 @@
         <v>12</v>
       </c>
       <c r="I16" s="8">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="J16" s="8">
         <v>0</v>
       </c>
       <c r="K16" s="8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L16" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M16" s="8">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N16" s="8">
-        <v>664</v>
+        <v>603</v>
       </c>
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
@@ -5529,7 +5529,7 @@
         <v>12</v>
       </c>
       <c r="I17" s="8">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="J17" s="8">
         <v>0</v>
@@ -5542,10 +5542,10 @@
       </c>
       <c r="M17" s="8">
         <f t="shared" si="0"/>
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="N17" s="8">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="O17" s="8"/>
       <c r="P17" s="8"/>
@@ -5580,20 +5580,20 @@
         <v>12</v>
       </c>
       <c r="I18" s="8">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J18" s="8">
         <v>0</v>
       </c>
       <c r="K18" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" s="8">
         <v>0</v>
       </c>
       <c r="M18" s="8">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="N18" s="8">
         <v>0</v>
@@ -5640,14 +5640,14 @@
         <v>0</v>
       </c>
       <c r="L19" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M19" s="8">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="N19" s="8">
-        <v>809</v>
+        <v>612</v>
       </c>
       <c r="O19" s="8"/>
       <c r="P19" s="8"/>
@@ -5682,7 +5682,7 @@
         <v>14</v>
       </c>
       <c r="I20" s="8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J20" s="8">
         <v>0</v>
@@ -5695,10 +5695,10 @@
       </c>
       <c r="M20" s="8">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N20" s="8">
-        <v>491</v>
+        <v>107</v>
       </c>
       <c r="O20" s="8"/>
       <c r="P20" s="8"/>
@@ -5733,20 +5733,20 @@
         <v>13</v>
       </c>
       <c r="I21" s="8">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="J21" s="8">
         <v>0</v>
       </c>
       <c r="K21" s="8">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="L21" s="8">
         <v>0</v>
       </c>
       <c r="M21" s="8">
         <f t="shared" si="0"/>
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="N21" s="8">
         <v>0</v>
@@ -5835,23 +5835,23 @@
         <v>12</v>
       </c>
       <c r="I23" s="8">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J23" s="8">
         <v>0</v>
       </c>
       <c r="K23" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L23" s="8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M23" s="8">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="N23" s="8">
-        <v>116</v>
+        <v>8</v>
       </c>
       <c r="O23" s="8"/>
       <c r="P23" s="8"/>
@@ -5886,7 +5886,7 @@
         <v>14</v>
       </c>
       <c r="I24" s="8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J24" s="8">
         <v>0</v>
@@ -5899,10 +5899,10 @@
       </c>
       <c r="M24" s="8">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N24" s="8">
-        <v>571</v>
+        <v>537</v>
       </c>
       <c r="O24" s="8"/>
       <c r="P24" s="8"/>
@@ -5988,23 +5988,23 @@
         <v>12</v>
       </c>
       <c r="I26" s="8">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J26" s="8">
         <v>0</v>
       </c>
       <c r="K26" s="8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L26" s="8">
         <v>0</v>
       </c>
       <c r="M26" s="8">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="N26" s="8">
-        <v>477</v>
+        <v>358</v>
       </c>
       <c r="O26" s="8"/>
       <c r="P26" s="8"/>
@@ -6055,7 +6055,7 @@
         <v>22</v>
       </c>
       <c r="N27" s="8">
-        <v>957</v>
+        <v>897</v>
       </c>
       <c r="O27" s="8"/>
       <c r="P27" s="8"/>
@@ -6090,7 +6090,7 @@
         <v>12</v>
       </c>
       <c r="I28" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J28" s="8">
         <v>0</v>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="M28" s="8">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N28" s="8">
         <v>0</v>
@@ -6192,23 +6192,23 @@
         <v>14</v>
       </c>
       <c r="I30" s="8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J30" s="8">
         <v>0</v>
       </c>
       <c r="K30" s="8">
+        <v>0</v>
+      </c>
+      <c r="L30" s="8">
         <v>1</v>
-      </c>
-      <c r="L30" s="8">
-        <v>0</v>
       </c>
       <c r="M30" s="8">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N30" s="8">
-        <v>1277</v>
+        <v>1351</v>
       </c>
       <c r="O30" s="8"/>
       <c r="P30" s="8"/>
@@ -6294,23 +6294,23 @@
         <v>12</v>
       </c>
       <c r="I32" s="8">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J32" s="8">
         <v>0</v>
       </c>
       <c r="K32" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L32" s="8">
         <v>0</v>
       </c>
       <c r="M32" s="8">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N32" s="8">
-        <v>649</v>
+        <v>613</v>
       </c>
       <c r="O32" s="8"/>
       <c r="P32" s="8"/>
@@ -6345,7 +6345,7 @@
         <v>12</v>
       </c>
       <c r="I33" s="8">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J33" s="8">
         <v>0</v>
@@ -6358,10 +6358,10 @@
       </c>
       <c r="M33" s="8">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="N33" s="8">
-        <v>959</v>
+        <v>915</v>
       </c>
       <c r="O33" s="8"/>
       <c r="P33" s="8"/>
@@ -6412,7 +6412,7 @@
         <v>18</v>
       </c>
       <c r="N34" s="8">
-        <v>952</v>
+        <v>930</v>
       </c>
       <c r="O34" s="8"/>
       <c r="P34" s="8"/>
@@ -6447,7 +6447,7 @@
         <v>12</v>
       </c>
       <c r="I35" s="8">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J35" s="8">
         <v>0</v>
@@ -6460,10 +6460,10 @@
       </c>
       <c r="M35" s="8">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N35" s="8">
-        <v>733</v>
+        <v>724</v>
       </c>
       <c r="O35" s="8"/>
       <c r="P35" s="8"/>
@@ -6498,7 +6498,7 @@
         <v>13</v>
       </c>
       <c r="I36" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J36" s="8">
         <v>0</v>
@@ -6511,10 +6511,10 @@
       </c>
       <c r="M36" s="8">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N36" s="8">
-        <v>673</v>
+        <v>637</v>
       </c>
       <c r="O36" s="8"/>
       <c r="P36" s="8"/>
@@ -6549,7 +6549,7 @@
         <v>13</v>
       </c>
       <c r="I37" s="8">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J37" s="8">
         <v>0</v>
@@ -6562,10 +6562,10 @@
       </c>
       <c r="M37" s="8">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N37" s="8">
-        <v>1211</v>
+        <v>1148</v>
       </c>
       <c r="O37" s="8"/>
       <c r="P37" s="8"/>
@@ -6600,7 +6600,7 @@
         <v>12</v>
       </c>
       <c r="I38" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J38" s="8">
         <v>0</v>
@@ -6613,7 +6613,7 @@
       </c>
       <c r="M38" s="8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N38" s="8">
         <v>0</v>
@@ -6651,7 +6651,7 @@
         <v>12</v>
       </c>
       <c r="I39" s="8">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J39" s="8">
         <v>0</v>
@@ -6664,10 +6664,10 @@
       </c>
       <c r="M39" s="8">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N39" s="8">
-        <v>1837</v>
+        <v>1905</v>
       </c>
       <c r="O39" s="8"/>
       <c r="P39" s="8"/>
@@ -6702,7 +6702,7 @@
         <v>12</v>
       </c>
       <c r="I40" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J40" s="8">
         <v>0</v>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="M40" s="8">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N40" s="8">
         <v>0</v>
@@ -6753,7 +6753,7 @@
         <v>12</v>
       </c>
       <c r="I41" s="8">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J41" s="8">
         <v>0</v>
@@ -6762,14 +6762,14 @@
         <v>0</v>
       </c>
       <c r="L41" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M41" s="8">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="N41" s="8">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="O41" s="8"/>
       <c r="P41" s="8"/>
@@ -6804,7 +6804,7 @@
         <v>13</v>
       </c>
       <c r="I42" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J42" s="8">
         <v>0</v>
@@ -6817,10 +6817,10 @@
       </c>
       <c r="M42" s="8">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N42" s="8">
-        <v>1358</v>
+        <v>1300</v>
       </c>
       <c r="O42" s="8"/>
       <c r="P42" s="8"/>
@@ -6855,7 +6855,7 @@
         <v>12</v>
       </c>
       <c r="I43" s="8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J43" s="8">
         <v>0</v>
@@ -6864,14 +6864,14 @@
         <v>0</v>
       </c>
       <c r="L43" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" s="8">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N43" s="8">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="O43" s="8"/>
       <c r="P43" s="8"/>
@@ -6906,23 +6906,23 @@
         <v>12</v>
       </c>
       <c r="I44" s="8">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J44" s="8">
         <v>0</v>
       </c>
       <c r="K44" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L44" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M44" s="8">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N44" s="8">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="O44" s="8"/>
       <c r="P44" s="8"/>
@@ -6973,7 +6973,7 @@
         <v>13</v>
       </c>
       <c r="N45" s="8">
-        <v>659</v>
+        <v>633</v>
       </c>
       <c r="O45" s="8"/>
       <c r="P45" s="8"/>
@@ -7017,14 +7017,14 @@
         <v>0</v>
       </c>
       <c r="L46" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" s="8">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N46" s="8">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="O46" s="8"/>
       <c r="P46" s="8"/>
@@ -7075,7 +7075,7 @@
         <v>9</v>
       </c>
       <c r="N47" s="8">
-        <v>898</v>
+        <v>842</v>
       </c>
       <c r="O47" s="8"/>
       <c r="P47" s="8"/>
@@ -7110,7 +7110,7 @@
         <v>12</v>
       </c>
       <c r="I48" s="8">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J48" s="8">
         <v>0</v>
@@ -7123,10 +7123,10 @@
       </c>
       <c r="M48" s="8">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="N48" s="8">
-        <v>1805</v>
+        <v>1689</v>
       </c>
       <c r="O48" s="8"/>
       <c r="P48" s="8"/>
@@ -7161,7 +7161,7 @@
         <v>12</v>
       </c>
       <c r="I49" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J49" s="8">
         <v>0</v>
@@ -7174,10 +7174,10 @@
       </c>
       <c r="M49" s="8">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N49" s="8">
-        <v>854</v>
+        <v>823</v>
       </c>
       <c r="O49" s="8"/>
       <c r="P49" s="8"/>
@@ -7212,7 +7212,7 @@
         <v>15</v>
       </c>
       <c r="I50" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J50" s="8">
         <v>0</v>
@@ -7225,10 +7225,10 @@
       </c>
       <c r="M50" s="8">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N50" s="8">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="O50" s="8"/>
       <c r="P50" s="8"/>
@@ -7279,7 +7279,7 @@
         <v>24</v>
       </c>
       <c r="N51" s="8">
-        <v>346</v>
+        <v>320</v>
       </c>
       <c r="O51" s="8"/>
       <c r="P51" s="8"/>
@@ -7314,7 +7314,7 @@
         <v>12</v>
       </c>
       <c r="I52" s="8">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="J52" s="8">
         <v>0</v>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="M52" s="8">
         <f t="shared" si="0"/>
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="N52" s="8">
         <v>0</v>
@@ -7374,14 +7374,14 @@
         <v>0</v>
       </c>
       <c r="L53" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M53" s="8">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N53" s="8">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="O53" s="8"/>
       <c r="P53" s="8"/>
@@ -7422,17 +7422,17 @@
         <v>0</v>
       </c>
       <c r="K54" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54" s="8">
         <v>0</v>
       </c>
       <c r="M54" s="8">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N54" s="8">
-        <v>120</v>
+        <v>483</v>
       </c>
       <c r="O54" s="8"/>
       <c r="P54" s="8"/>
@@ -7467,20 +7467,20 @@
         <v>12</v>
       </c>
       <c r="I55" s="8">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J55" s="8">
         <v>0</v>
       </c>
       <c r="K55" s="8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L55" s="8">
         <v>0</v>
       </c>
       <c r="M55" s="8">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N55" s="8">
         <v>0</v>
@@ -7518,7 +7518,7 @@
         <v>14</v>
       </c>
       <c r="I56" s="8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J56" s="8">
         <v>0</v>
@@ -7531,10 +7531,10 @@
       </c>
       <c r="M56" s="8">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N56" s="8">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="O56" s="8"/>
       <c r="P56" s="8"/>
@@ -7569,23 +7569,23 @@
         <v>12</v>
       </c>
       <c r="I57" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J57" s="8">
         <v>0</v>
       </c>
       <c r="K57" s="8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L57" s="8">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M57" s="8">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="N57" s="8">
-        <v>504</v>
+        <v>127</v>
       </c>
       <c r="O57" s="8"/>
       <c r="P57" s="8"/>
@@ -7636,7 +7636,7 @@
         <v>3</v>
       </c>
       <c r="N58" s="8">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="O58" s="8"/>
       <c r="P58" s="8"/>
@@ -7687,7 +7687,7 @@
         <v>6</v>
       </c>
       <c r="N59" s="8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O59" s="8"/>
       <c r="P59" s="8"/>
@@ -7738,7 +7738,7 @@
         <v>5</v>
       </c>
       <c r="N60" s="8">
-        <v>574</v>
+        <v>541</v>
       </c>
       <c r="O60" s="8"/>
       <c r="P60" s="8"/>
@@ -7773,7 +7773,7 @@
         <v>12</v>
       </c>
       <c r="I61" s="8">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J61" s="8">
         <v>0</v>
@@ -7786,10 +7786,10 @@
       </c>
       <c r="M61" s="8">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N61" s="8">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="O61" s="8"/>
       <c r="P61" s="8"/>
@@ -7840,7 +7840,7 @@
         <v>8</v>
       </c>
       <c r="N62" s="8">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="O62" s="8"/>
       <c r="P62" s="8"/>
@@ -7891,7 +7891,7 @@
         <v>4</v>
       </c>
       <c r="N63" s="8">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="O63" s="8"/>
       <c r="P63" s="8"/>
@@ -7932,17 +7932,17 @@
         <v>0</v>
       </c>
       <c r="K64" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="8">
         <v>2</v>
       </c>
       <c r="M64" s="8">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N64" s="8">
-        <v>333</v>
+        <v>314</v>
       </c>
       <c r="O64" s="8"/>
       <c r="P64" s="8"/>
@@ -7977,7 +7977,7 @@
         <v>12</v>
       </c>
       <c r="I65" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J65" s="8">
         <v>0</v>
@@ -7990,10 +7990,10 @@
       </c>
       <c r="M65" s="8">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N65" s="8">
-        <v>897</v>
+        <v>876</v>
       </c>
       <c r="O65" s="8"/>
       <c r="P65" s="8"/>
@@ -8044,7 +8044,7 @@
         <v>4</v>
       </c>
       <c r="N66" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O66" s="8"/>
       <c r="P66" s="8"/>
@@ -8079,7 +8079,7 @@
         <v>12</v>
       </c>
       <c r="I67" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J67" s="8">
         <v>0</v>
@@ -8092,7 +8092,7 @@
       </c>
       <c r="M67" s="8">
         <f t="shared" ref="M67:M130" si="1">I67+J67+K67+L67</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N67" s="8">
         <v>0</v>
@@ -8130,7 +8130,7 @@
         <v>12</v>
       </c>
       <c r="I68" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J68" s="8">
         <v>0</v>
@@ -8143,10 +8143,10 @@
       </c>
       <c r="M68" s="8">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N68" s="8">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="O68" s="8"/>
       <c r="P68" s="8"/>
@@ -8181,7 +8181,7 @@
         <v>12</v>
       </c>
       <c r="I69" s="8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J69" s="8">
         <v>0</v>
@@ -8190,14 +8190,14 @@
         <v>0</v>
       </c>
       <c r="L69" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M69" s="8">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="N69" s="8">
-        <v>274</v>
+        <v>237</v>
       </c>
       <c r="O69" s="8"/>
       <c r="P69" s="8"/>
@@ -8241,14 +8241,14 @@
         <v>0</v>
       </c>
       <c r="L70" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N70" s="8">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="O70" s="8"/>
       <c r="P70" s="8"/>
@@ -8283,7 +8283,7 @@
         <v>12</v>
       </c>
       <c r="I71" s="8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J71" s="8">
         <v>0</v>
@@ -8296,7 +8296,7 @@
       </c>
       <c r="M71" s="8">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N71" s="8">
         <v>0</v>
@@ -8334,7 +8334,7 @@
         <v>12</v>
       </c>
       <c r="I72" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J72" s="8">
         <v>0</v>
@@ -8347,10 +8347,10 @@
       </c>
       <c r="M72" s="8">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N72" s="8">
-        <v>584</v>
+        <v>560</v>
       </c>
       <c r="O72" s="8"/>
       <c r="P72" s="8"/>
@@ -8385,23 +8385,23 @@
         <v>12</v>
       </c>
       <c r="I73" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J73" s="8">
         <v>0</v>
       </c>
       <c r="K73" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M73" s="8">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N73" s="8">
-        <v>746</v>
+        <v>232</v>
       </c>
       <c r="O73" s="8"/>
       <c r="P73" s="8"/>
@@ -8442,17 +8442,17 @@
         <v>0</v>
       </c>
       <c r="K74" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L74" s="8">
         <v>0</v>
       </c>
       <c r="M74" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N74" s="8">
-        <v>256</v>
+        <v>164</v>
       </c>
       <c r="O74" s="8"/>
       <c r="P74" s="8"/>
@@ -8487,7 +8487,7 @@
         <v>13</v>
       </c>
       <c r="I75" s="8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J75" s="8">
         <v>0</v>
@@ -8500,7 +8500,7 @@
       </c>
       <c r="M75" s="8">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N75" s="8">
         <v>31</v>
@@ -8554,7 +8554,7 @@
         <v>3</v>
       </c>
       <c r="N76" s="8">
-        <v>940</v>
+        <v>875</v>
       </c>
       <c r="O76" s="8"/>
       <c r="P76" s="8"/>
@@ -8605,7 +8605,7 @@
         <v>5</v>
       </c>
       <c r="N77" s="8">
-        <v>661</v>
+        <v>603</v>
       </c>
       <c r="O77" s="8"/>
       <c r="P77" s="8"/>
@@ -8640,23 +8640,23 @@
         <v>12</v>
       </c>
       <c r="I78" s="8">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J78" s="8">
         <v>0</v>
       </c>
       <c r="K78" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M78" s="8">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N78" s="8">
-        <v>405</v>
+        <v>376</v>
       </c>
       <c r="O78" s="8"/>
       <c r="P78" s="8"/>
@@ -8691,7 +8691,7 @@
         <v>13</v>
       </c>
       <c r="I79" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J79" s="8">
         <v>0</v>
@@ -8704,10 +8704,10 @@
       </c>
       <c r="M79" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N79" s="8">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="O79" s="8"/>
       <c r="P79" s="8"/>
@@ -8860,7 +8860,7 @@
         <v>5</v>
       </c>
       <c r="N82" s="8">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="O82" s="8"/>
       <c r="P82" s="8"/>
@@ -8911,7 +8911,7 @@
         <v>4</v>
       </c>
       <c r="N83" s="8">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="O83" s="8"/>
       <c r="P83" s="8"/>
@@ -9048,23 +9048,23 @@
         <v>12</v>
       </c>
       <c r="I86" s="8">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J86" s="8">
         <v>0</v>
       </c>
       <c r="K86" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L86" s="8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M86" s="8">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N86" s="8">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="O86" s="8"/>
       <c r="P86" s="8"/>
@@ -9166,7 +9166,7 @@
         <v>12</v>
       </c>
       <c r="N88" s="8">
-        <v>386</v>
+        <v>326</v>
       </c>
       <c r="O88" s="8"/>
       <c r="P88" s="8"/>
@@ -9201,7 +9201,7 @@
         <v>12</v>
       </c>
       <c r="I89" s="8">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J89" s="8">
         <v>0</v>
@@ -9210,14 +9210,14 @@
         <v>0</v>
       </c>
       <c r="L89" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M89" s="8">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="N89" s="8">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="O89" s="8"/>
       <c r="P89" s="8"/>
@@ -9268,7 +9268,7 @@
         <v>5</v>
       </c>
       <c r="N90" s="8">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O90" s="8"/>
       <c r="P90" s="8"/>
@@ -9303,7 +9303,7 @@
         <v>12</v>
       </c>
       <c r="I91" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J91" s="8">
         <v>0</v>
@@ -9312,14 +9312,14 @@
         <v>0</v>
       </c>
       <c r="L91" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M91" s="8">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N91" s="8">
-        <v>1033</v>
+        <v>983</v>
       </c>
       <c r="O91" s="8"/>
       <c r="P91" s="8"/>
@@ -9360,17 +9360,17 @@
         <v>0</v>
       </c>
       <c r="K92" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L92" s="8">
         <v>0</v>
       </c>
       <c r="M92" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N92" s="8">
-        <v>171</v>
+        <v>135</v>
       </c>
       <c r="O92" s="8"/>
       <c r="P92" s="8"/>
@@ -9405,23 +9405,23 @@
         <v>13</v>
       </c>
       <c r="I93" s="8">
+        <v>5</v>
+      </c>
+      <c r="J93" s="8">
+        <v>0</v>
+      </c>
+      <c r="K93" s="8">
+        <v>1</v>
+      </c>
+      <c r="L93" s="8">
         <v>6</v>
-      </c>
-      <c r="J93" s="8">
-        <v>0</v>
-      </c>
-      <c r="K93" s="8">
-        <v>0</v>
-      </c>
-      <c r="L93" s="8">
-        <v>4</v>
       </c>
       <c r="M93" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N93" s="8">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O93" s="8"/>
       <c r="P93" s="8"/>
@@ -9456,7 +9456,7 @@
         <v>12</v>
       </c>
       <c r="I94" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J94" s="8">
         <v>0</v>
@@ -9469,7 +9469,7 @@
       </c>
       <c r="M94" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N94" s="8">
         <v>0</v>
@@ -9523,7 +9523,7 @@
         <v>6</v>
       </c>
       <c r="N95" s="8">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="O95" s="8"/>
       <c r="P95" s="8"/>
@@ -9574,7 +9574,7 @@
         <v>7</v>
       </c>
       <c r="N96" s="8">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="O96" s="8"/>
       <c r="P96" s="8"/>
@@ -9609,23 +9609,23 @@
         <v>14</v>
       </c>
       <c r="I97" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J97" s="8">
         <v>0</v>
       </c>
       <c r="K97" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L97" s="8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M97" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N97" s="8">
-        <v>219</v>
+        <v>172</v>
       </c>
       <c r="O97" s="8"/>
       <c r="P97" s="8"/>
@@ -9660,7 +9660,7 @@
         <v>12</v>
       </c>
       <c r="I98" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J98" s="8">
         <v>0</v>
@@ -9673,7 +9673,7 @@
       </c>
       <c r="M98" s="8">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N98" s="8">
         <v>0</v>
@@ -9762,7 +9762,7 @@
         <v>15</v>
       </c>
       <c r="I100" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J100" s="8">
         <v>0</v>
@@ -9775,7 +9775,7 @@
       </c>
       <c r="M100" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N100" s="8">
         <v>0</v>
@@ -9829,7 +9829,7 @@
         <v>2</v>
       </c>
       <c r="N101" s="8">
-        <v>328</v>
+        <v>249</v>
       </c>
       <c r="O101" s="8"/>
       <c r="P101" s="8"/>
@@ -9864,23 +9864,23 @@
         <v>14</v>
       </c>
       <c r="I102" s="8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J102" s="8">
         <v>0</v>
       </c>
       <c r="K102" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L102" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M102" s="8">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N102" s="8">
-        <v>477</v>
+        <v>411</v>
       </c>
       <c r="O102" s="8"/>
       <c r="P102" s="8"/>
@@ -9915,23 +9915,23 @@
         <v>15</v>
       </c>
       <c r="I103" s="8">
+        <v>0</v>
+      </c>
+      <c r="J103" s="8">
+        <v>0</v>
+      </c>
+      <c r="K103" s="8">
+        <v>0</v>
+      </c>
+      <c r="L103" s="8">
         <v>1</v>
-      </c>
-      <c r="J103" s="8">
-        <v>0</v>
-      </c>
-      <c r="K103" s="8">
-        <v>2</v>
-      </c>
-      <c r="L103" s="8">
-        <v>0</v>
       </c>
       <c r="M103" s="8">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N103" s="8">
-        <v>437</v>
+        <v>358</v>
       </c>
       <c r="O103" s="8"/>
       <c r="P103" s="8"/>
@@ -10017,7 +10017,7 @@
         <v>12</v>
       </c>
       <c r="I105" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J105" s="8">
         <v>0</v>
@@ -10030,10 +10030,10 @@
       </c>
       <c r="M105" s="8">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N105" s="8">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="O105" s="8"/>
       <c r="P105" s="8"/>
@@ -10221,7 +10221,7 @@
         <v>13</v>
       </c>
       <c r="I109" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J109" s="8">
         <v>0</v>
@@ -10234,10 +10234,10 @@
       </c>
       <c r="M109" s="8">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N109" s="8">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="O109" s="8"/>
       <c r="P109" s="8"/>
@@ -10288,7 +10288,7 @@
         <v>11</v>
       </c>
       <c r="N110" s="8">
-        <v>541</v>
+        <v>520</v>
       </c>
       <c r="O110" s="8"/>
       <c r="P110" s="8"/>
@@ -10374,23 +10374,23 @@
         <v>12</v>
       </c>
       <c r="I112" s="8">
-        <v>48</v>
+        <v>152</v>
       </c>
       <c r="J112" s="8">
         <v>0</v>
       </c>
       <c r="K112" s="8">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L112" s="8">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="M112" s="8">
         <f t="shared" si="1"/>
-        <v>198</v>
+        <v>259</v>
       </c>
       <c r="N112" s="8">
-        <v>284</v>
+        <v>63</v>
       </c>
       <c r="O112" s="8"/>
       <c r="P112" s="8"/>
@@ -10425,7 +10425,7 @@
         <v>12</v>
       </c>
       <c r="I113" s="8">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J113" s="8">
         <v>0</v>
@@ -10438,10 +10438,10 @@
       </c>
       <c r="M113" s="8">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N113" s="8">
-        <v>822</v>
+        <v>783</v>
       </c>
       <c r="O113" s="8"/>
       <c r="P113" s="8"/>
@@ -10492,7 +10492,7 @@
         <v>9</v>
       </c>
       <c r="N114" s="8">
-        <v>666</v>
+        <v>593</v>
       </c>
       <c r="O114" s="8"/>
       <c r="P114" s="8"/>
@@ -10527,7 +10527,7 @@
         <v>13</v>
       </c>
       <c r="I115" s="8">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J115" s="8">
         <v>0</v>
@@ -10540,10 +10540,10 @@
       </c>
       <c r="M115" s="8">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="N115" s="8">
-        <v>536</v>
+        <v>518</v>
       </c>
       <c r="O115" s="8"/>
       <c r="P115" s="8"/>
@@ -10584,17 +10584,17 @@
         <v>0</v>
       </c>
       <c r="K116" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L116" s="8">
         <v>0</v>
       </c>
       <c r="M116" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N116" s="8">
-        <v>730</v>
+        <v>685</v>
       </c>
       <c r="O116" s="8"/>
       <c r="P116" s="8"/>
@@ -10629,7 +10629,7 @@
         <v>12</v>
       </c>
       <c r="I117" s="8">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J117" s="8">
         <v>0</v>
@@ -10638,14 +10638,14 @@
         <v>0</v>
       </c>
       <c r="L117" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M117" s="8">
         <f t="shared" si="1"/>
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="N117" s="8">
-        <v>266</v>
+        <v>219</v>
       </c>
       <c r="O117" s="8"/>
       <c r="P117" s="8"/>
@@ -10680,7 +10680,7 @@
         <v>13</v>
       </c>
       <c r="I118" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J118" s="8">
         <v>0</v>
@@ -10693,10 +10693,10 @@
       </c>
       <c r="M118" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N118" s="8">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="O118" s="8"/>
       <c r="P118" s="8"/>
@@ -10731,7 +10731,7 @@
         <v>14</v>
       </c>
       <c r="I119" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J119" s="8">
         <v>0</v>
@@ -10744,10 +10744,10 @@
       </c>
       <c r="M119" s="8">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N119" s="8">
-        <v>505</v>
+        <v>494</v>
       </c>
       <c r="O119" s="8"/>
       <c r="P119" s="8"/>
@@ -10782,7 +10782,7 @@
         <v>14</v>
       </c>
       <c r="I120" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J120" s="8">
         <v>0</v>
@@ -10795,10 +10795,10 @@
       </c>
       <c r="M120" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N120" s="8">
-        <v>1</v>
+        <v>220</v>
       </c>
       <c r="O120" s="8"/>
       <c r="P120" s="8"/>
@@ -10833,7 +10833,7 @@
         <v>15</v>
       </c>
       <c r="I121" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J121" s="8">
         <v>0</v>
@@ -10846,7 +10846,7 @@
       </c>
       <c r="M121" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N121" s="8">
         <v>0</v>
@@ -10900,7 +10900,7 @@
         <v>2</v>
       </c>
       <c r="N122" s="8">
-        <v>989</v>
+        <v>963</v>
       </c>
       <c r="O122" s="8"/>
       <c r="P122" s="8"/>
@@ -11037,7 +11037,7 @@
         <v>13</v>
       </c>
       <c r="I125" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J125" s="8">
         <v>0</v>
@@ -11050,10 +11050,10 @@
       </c>
       <c r="M125" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N125" s="8">
-        <v>186</v>
+        <v>156</v>
       </c>
       <c r="O125" s="8"/>
       <c r="P125" s="8"/>
@@ -11190,7 +11190,7 @@
         <v>12</v>
       </c>
       <c r="I128" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J128" s="8">
         <v>0</v>
@@ -11203,10 +11203,10 @@
       </c>
       <c r="M128" s="8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N128" s="8">
-        <v>814</v>
+        <v>808</v>
       </c>
       <c r="O128" s="8"/>
       <c r="P128" s="8"/>
@@ -11241,7 +11241,7 @@
         <v>15</v>
       </c>
       <c r="I129" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J129" s="8">
         <v>0</v>
@@ -11254,7 +11254,7 @@
       </c>
       <c r="M129" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N129" s="8">
         <v>0</v>
@@ -11292,23 +11292,23 @@
         <v>12</v>
       </c>
       <c r="I130" s="8">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J130" s="8">
         <v>0</v>
       </c>
       <c r="K130" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L130" s="8">
         <v>0</v>
       </c>
       <c r="M130" s="8">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N130" s="8">
-        <v>314</v>
+        <v>109</v>
       </c>
       <c r="O130" s="8"/>
       <c r="P130" s="8"/>
@@ -11394,7 +11394,7 @@
         <v>12</v>
       </c>
       <c r="I132" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J132" s="8">
         <v>0</v>
@@ -11407,10 +11407,10 @@
       </c>
       <c r="M132" s="8">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N132" s="8">
-        <v>844</v>
+        <v>839</v>
       </c>
       <c r="O132" s="8"/>
       <c r="P132" s="8"/>
@@ -11445,7 +11445,7 @@
         <v>12</v>
       </c>
       <c r="I133" s="8">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J133" s="8">
         <v>0</v>
@@ -11458,10 +11458,10 @@
       </c>
       <c r="M133" s="8">
         <f t="shared" si="2"/>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N133" s="8">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O133" s="8"/>
       <c r="P133" s="8"/>
@@ -11512,7 +11512,7 @@
         <v>4</v>
       </c>
       <c r="N134" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O134" s="8"/>
       <c r="P134" s="8"/>
@@ -11553,17 +11553,17 @@
         <v>0</v>
       </c>
       <c r="K135" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L135" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M135" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N135" s="8">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="O135" s="8"/>
       <c r="P135" s="8"/>
@@ -11598,7 +11598,7 @@
         <v>14</v>
       </c>
       <c r="I136" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J136" s="8">
         <v>0</v>
@@ -11607,14 +11607,14 @@
         <v>0</v>
       </c>
       <c r="L136" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M136" s="8">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N136" s="8">
-        <v>462</v>
+        <v>398</v>
       </c>
       <c r="O136" s="8"/>
       <c r="P136" s="8"/>
@@ -11665,7 +11665,7 @@
         <v>3</v>
       </c>
       <c r="N137" s="8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O137" s="8"/>
       <c r="P137" s="8"/>
@@ -11716,7 +11716,7 @@
         <v>3</v>
       </c>
       <c r="N138" s="8">
-        <v>1044</v>
+        <v>975</v>
       </c>
       <c r="O138" s="8"/>
       <c r="P138" s="8"/>
@@ -11818,7 +11818,7 @@
         <v>1</v>
       </c>
       <c r="N140" s="8">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O140" s="8"/>
       <c r="P140" s="8"/>
@@ -11853,7 +11853,7 @@
         <v>13</v>
       </c>
       <c r="I141" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J141" s="8">
         <v>0</v>
@@ -11862,14 +11862,14 @@
         <v>0</v>
       </c>
       <c r="L141" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M141" s="8">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N141" s="8">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O141" s="8"/>
       <c r="P141" s="8"/>
@@ -11971,7 +11971,7 @@
         <v>1</v>
       </c>
       <c r="N143" s="8">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O143" s="8"/>
       <c r="P143" s="8"/>
@@ -12073,7 +12073,7 @@
         <v>4</v>
       </c>
       <c r="N145" s="8">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="O145" s="8"/>
       <c r="P145" s="8"/>
@@ -12108,7 +12108,7 @@
         <v>16</v>
       </c>
       <c r="I146" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J146" s="8">
         <v>0</v>
@@ -12121,7 +12121,7 @@
       </c>
       <c r="M146" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N146" s="8">
         <v>0</v>
@@ -12175,7 +12175,7 @@
         <v>2</v>
       </c>
       <c r="N147" s="8">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="O147" s="8"/>
       <c r="P147" s="8"/>
@@ -12270,14 +12270,14 @@
         <v>0</v>
       </c>
       <c r="L149" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M149" s="8">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N149" s="8">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="O149" s="8"/>
       <c r="P149" s="8"/>
@@ -12328,7 +12328,7 @@
         <v>3</v>
       </c>
       <c r="N150" s="8">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="O150" s="8"/>
       <c r="P150" s="8"/>
@@ -12379,7 +12379,7 @@
         <v>3</v>
       </c>
       <c r="N151" s="8">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O151" s="8"/>
       <c r="P151" s="8"/>
@@ -12414,7 +12414,7 @@
         <v>15</v>
       </c>
       <c r="I152" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J152" s="8">
         <v>0</v>
@@ -12427,10 +12427,10 @@
       </c>
       <c r="M152" s="8">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N152" s="8">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="O152" s="8"/>
       <c r="P152" s="8"/>
@@ -12465,23 +12465,23 @@
         <v>13</v>
       </c>
       <c r="I153" s="8">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J153" s="8">
         <v>0</v>
       </c>
       <c r="K153" s="8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L153" s="8">
         <v>0</v>
       </c>
       <c r="M153" s="8">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="N153" s="8">
-        <v>529</v>
+        <v>0</v>
       </c>
       <c r="O153" s="8"/>
       <c r="P153" s="8"/>
@@ -12516,7 +12516,7 @@
         <v>15</v>
       </c>
       <c r="I154" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J154" s="8">
         <v>0</v>
@@ -12529,10 +12529,10 @@
       </c>
       <c r="M154" s="8">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N154" s="8">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O154" s="8"/>
       <c r="P154" s="8"/>
@@ -12618,7 +12618,7 @@
         <v>15</v>
       </c>
       <c r="I156" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J156" s="8">
         <v>0</v>
@@ -12631,7 +12631,7 @@
       </c>
       <c r="M156" s="8">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N156" s="8">
         <v>0</v>
@@ -12771,7 +12771,7 @@
         <v>15</v>
       </c>
       <c r="I159" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J159" s="8">
         <v>0</v>
@@ -12780,14 +12780,14 @@
         <v>0</v>
       </c>
       <c r="L159" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M159" s="8">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N159" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O159" s="8"/>
       <c r="P159" s="8"/>
@@ -12838,7 +12838,7 @@
         <v>3</v>
       </c>
       <c r="N160" s="8">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="O160" s="8"/>
       <c r="P160" s="8"/>
@@ -12889,7 +12889,7 @@
         <v>6</v>
       </c>
       <c r="N161" s="8">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="O161" s="8"/>
       <c r="P161" s="8"/>
@@ -12924,7 +12924,7 @@
         <v>13</v>
       </c>
       <c r="I162" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J162" s="8">
         <v>0</v>
@@ -12937,10 +12937,10 @@
       </c>
       <c r="M162" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N162" s="8">
-        <v>189</v>
+        <v>159</v>
       </c>
       <c r="O162" s="8"/>
       <c r="P162" s="8"/>
@@ -13026,7 +13026,7 @@
         <v>16</v>
       </c>
       <c r="I164" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J164" s="8">
         <v>0</v>
@@ -13039,10 +13039,10 @@
       </c>
       <c r="M164" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N164" s="8">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="O164" s="8"/>
       <c r="P164" s="8"/>
@@ -13093,7 +13093,7 @@
         <v>10</v>
       </c>
       <c r="N165" s="8">
-        <v>1237</v>
+        <v>1209</v>
       </c>
       <c r="O165" s="8"/>
       <c r="P165" s="8"/>
@@ -13128,7 +13128,7 @@
         <v>14</v>
       </c>
       <c r="I166" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J166" s="8">
         <v>0</v>
@@ -13141,10 +13141,10 @@
       </c>
       <c r="M166" s="8">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N166" s="8">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="O166" s="8"/>
       <c r="P166" s="8"/>
@@ -13236,17 +13236,17 @@
         <v>0</v>
       </c>
       <c r="K168" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L168" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M168" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N168" s="8">
-        <v>361</v>
+        <v>206</v>
       </c>
       <c r="O168" s="8"/>
       <c r="P168" s="8"/>
@@ -13281,7 +13281,7 @@
         <v>16</v>
       </c>
       <c r="I169" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J169" s="8">
         <v>0</v>
@@ -13294,7 +13294,7 @@
       </c>
       <c r="M169" s="8">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N169" s="8">
         <v>0</v>
@@ -13332,7 +13332,7 @@
         <v>14</v>
       </c>
       <c r="I170" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J170" s="8">
         <v>0</v>
@@ -13345,10 +13345,10 @@
       </c>
       <c r="M170" s="8">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N170" s="8">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="O170" s="8"/>
       <c r="P170" s="8"/>
@@ -13501,7 +13501,7 @@
         <v>2</v>
       </c>
       <c r="N173" s="8">
-        <v>618</v>
+        <v>599</v>
       </c>
       <c r="O173" s="8"/>
       <c r="P173" s="8"/>
@@ -13654,7 +13654,7 @@
         <v>2</v>
       </c>
       <c r="N176" s="8">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="O176" s="8"/>
       <c r="P176" s="8"/>
@@ -13807,7 +13807,7 @@
         <v>2</v>
       </c>
       <c r="N179" s="8">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="O179" s="8"/>
       <c r="P179" s="8"/>
@@ -13858,7 +13858,7 @@
         <v>6</v>
       </c>
       <c r="N180" s="8">
-        <v>496</v>
+        <v>467</v>
       </c>
       <c r="O180" s="8"/>
       <c r="P180" s="8"/>
@@ -13893,23 +13893,23 @@
         <v>15</v>
       </c>
       <c r="I181" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J181" s="8">
         <v>0</v>
       </c>
       <c r="K181" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L181" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M181" s="8">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="N181" s="8">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="O181" s="8"/>
       <c r="P181" s="8"/>
@@ -14011,7 +14011,7 @@
         <v>6</v>
       </c>
       <c r="N183" s="8">
-        <v>336</v>
+        <v>300</v>
       </c>
       <c r="O183" s="8"/>
       <c r="P183" s="8"/>
@@ -14097,7 +14097,7 @@
         <v>12</v>
       </c>
       <c r="I185" s="8">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="J185" s="8">
         <v>0</v>
@@ -14106,11 +14106,11 @@
         <v>15</v>
       </c>
       <c r="L185" s="8">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="M185" s="8">
         <f t="shared" si="2"/>
-        <v>429</v>
+        <v>504</v>
       </c>
       <c r="N185" s="8">
         <v>1743</v>
@@ -14148,7 +14148,7 @@
         <v>12</v>
       </c>
       <c r="I186" s="8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J186" s="8">
         <v>0</v>
@@ -14157,14 +14157,14 @@
         <v>0</v>
       </c>
       <c r="L186" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M186" s="8">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="N186" s="8">
-        <v>876</v>
+        <v>841</v>
       </c>
       <c r="O186" s="8"/>
       <c r="P186" s="8"/>
@@ -14215,7 +14215,7 @@
         <v>2</v>
       </c>
       <c r="N187" s="8">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="O187" s="8"/>
       <c r="P187" s="8"/>
@@ -14266,7 +14266,7 @@
         <v>5</v>
       </c>
       <c r="N188" s="8">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="O188" s="8"/>
       <c r="P188" s="8"/>
@@ -14352,13 +14352,13 @@
         <v>12</v>
       </c>
       <c r="I190" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J190" s="8">
         <v>0</v>
       </c>
       <c r="K190" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L190" s="8">
         <v>0</v>
@@ -14368,7 +14368,7 @@
         <v>17</v>
       </c>
       <c r="N190" s="8">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="O190" s="8"/>
       <c r="P190" s="8"/>
@@ -14419,7 +14419,7 @@
         <v>8</v>
       </c>
       <c r="N191" s="8">
-        <v>797</v>
+        <v>736</v>
       </c>
       <c r="O191" s="8"/>
       <c r="P191" s="8"/>
@@ -14454,7 +14454,7 @@
         <v>12</v>
       </c>
       <c r="I192" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J192" s="8">
         <v>0</v>
@@ -14467,7 +14467,7 @@
       </c>
       <c r="M192" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N192" s="8">
         <v>0</v>
@@ -14521,7 +14521,7 @@
         <v>3</v>
       </c>
       <c r="N193" s="8">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="O193" s="8"/>
       <c r="P193" s="8"/>
@@ -14556,7 +14556,7 @@
         <v>15</v>
       </c>
       <c r="I194" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J194" s="8">
         <v>0</v>
@@ -14569,10 +14569,10 @@
       </c>
       <c r="M194" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N194" s="8">
-        <v>254</v>
+        <v>213</v>
       </c>
       <c r="O194" s="8"/>
       <c r="P194" s="8"/>
@@ -14725,7 +14725,7 @@
         <v>3</v>
       </c>
       <c r="N197" s="8">
-        <v>549</v>
+        <v>509</v>
       </c>
       <c r="O197" s="8"/>
       <c r="P197" s="8"/>
@@ -15235,7 +15235,7 @@
         <v>5</v>
       </c>
       <c r="N207" s="8">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="O207" s="8"/>
       <c r="P207" s="8"/>
@@ -15286,7 +15286,7 @@
         <v>3</v>
       </c>
       <c r="N208" s="8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O208" s="8"/>
       <c r="P208" s="8"/>
@@ -15321,7 +15321,7 @@
         <v>12</v>
       </c>
       <c r="I209" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J209" s="8">
         <v>0</v>
@@ -15334,10 +15334,10 @@
       </c>
       <c r="M209" s="8">
         <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="N209" s="8">
         <v>1</v>
-      </c>
-      <c r="N209" s="8">
-        <v>6</v>
       </c>
       <c r="O209" s="8"/>
       <c r="P209" s="8"/>
@@ -15432,14 +15432,14 @@
         <v>0</v>
       </c>
       <c r="L211" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M211" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N211" s="8">
-        <v>728</v>
+        <v>719</v>
       </c>
       <c r="O211" s="8"/>
       <c r="P211" s="8"/>
@@ -15643,7 +15643,7 @@
         <v>3</v>
       </c>
       <c r="N215" s="8">
-        <v>703</v>
+        <v>649</v>
       </c>
       <c r="O215" s="8"/>
       <c r="P215" s="8"/>
@@ -15678,7 +15678,7 @@
         <v>14</v>
       </c>
       <c r="I216" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J216" s="8">
         <v>0</v>
@@ -15691,7 +15691,7 @@
       </c>
       <c r="M216" s="8">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N216" s="8">
         <v>0</v>
@@ -15745,7 +15745,7 @@
         <v>3</v>
       </c>
       <c r="N217" s="8">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O217" s="8"/>
       <c r="P217" s="8"/>
@@ -15780,7 +15780,7 @@
         <v>13</v>
       </c>
       <c r="I218" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J218" s="8">
         <v>0</v>
@@ -15793,7 +15793,7 @@
       </c>
       <c r="M218" s="8">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N218" s="8">
         <v>239</v>
@@ -15831,7 +15831,7 @@
         <v>13</v>
       </c>
       <c r="I219" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J219" s="8">
         <v>0</v>
@@ -15844,10 +15844,10 @@
       </c>
       <c r="M219" s="8">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N219" s="8">
-        <v>393</v>
+        <v>380</v>
       </c>
       <c r="O219" s="8"/>
       <c r="P219" s="8"/>
@@ -15949,7 +15949,7 @@
         <v>2</v>
       </c>
       <c r="N221" s="8">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="O221" s="8"/>
       <c r="P221" s="8"/>
@@ -15984,23 +15984,23 @@
         <v>16</v>
       </c>
       <c r="I222" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J222" s="8">
         <v>0</v>
       </c>
       <c r="K222" s="8">
+        <v>0</v>
+      </c>
+      <c r="L222" s="8">
         <v>1</v>
-      </c>
-      <c r="L222" s="8">
-        <v>0</v>
       </c>
       <c r="M222" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N222" s="8">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="O222" s="8"/>
       <c r="P222" s="8"/>
@@ -16044,14 +16044,14 @@
         <v>0</v>
       </c>
       <c r="L223" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M223" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N223" s="8">
-        <v>184</v>
+        <v>151</v>
       </c>
       <c r="O223" s="8"/>
       <c r="P223" s="8"/>
@@ -16102,7 +16102,7 @@
         <v>2</v>
       </c>
       <c r="N224" s="8">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="O224" s="8"/>
       <c r="P224" s="8"/>
@@ -16153,7 +16153,7 @@
         <v>3</v>
       </c>
       <c r="N225" s="8">
-        <v>552</v>
+        <v>518</v>
       </c>
       <c r="O225" s="8"/>
       <c r="P225" s="8"/>
@@ -16204,7 +16204,7 @@
         <v>0</v>
       </c>
       <c r="N226" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O226" s="8"/>
       <c r="P226" s="8"/>
@@ -16299,14 +16299,14 @@
         <v>0</v>
       </c>
       <c r="L228" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M228" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N228" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O228" s="8"/>
       <c r="P228" s="8"/>
@@ -16341,7 +16341,7 @@
         <v>15</v>
       </c>
       <c r="I229" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J229" s="8">
         <v>0</v>
@@ -16354,10 +16354,10 @@
       </c>
       <c r="M229" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N229" s="8">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="O229" s="8"/>
       <c r="P229" s="8"/>
@@ -16392,7 +16392,7 @@
         <v>15</v>
       </c>
       <c r="I230" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J230" s="8">
         <v>0</v>
@@ -16401,14 +16401,14 @@
         <v>0</v>
       </c>
       <c r="L230" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M230" s="8">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="N230" s="8">
-        <v>93</v>
+        <v>337</v>
       </c>
       <c r="O230" s="8"/>
       <c r="P230" s="8"/>
@@ -16494,7 +16494,7 @@
         <v>12</v>
       </c>
       <c r="I232" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J232" s="8">
         <v>0</v>
@@ -16507,10 +16507,10 @@
       </c>
       <c r="M232" s="8">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N232" s="8">
-        <v>518</v>
+        <v>452</v>
       </c>
       <c r="O232" s="8"/>
       <c r="P232" s="8"/>
@@ -16545,7 +16545,7 @@
         <v>15</v>
       </c>
       <c r="I233" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J233" s="8">
         <v>0</v>
@@ -16554,14 +16554,14 @@
         <v>0</v>
       </c>
       <c r="L233" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M233" s="8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N233" s="8">
-        <v>588</v>
+        <v>562</v>
       </c>
       <c r="O233" s="8"/>
       <c r="P233" s="8"/>
@@ -16612,7 +16612,7 @@
         <v>2</v>
       </c>
       <c r="N234" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O234" s="8"/>
       <c r="P234" s="8"/>
@@ -16663,7 +16663,7 @@
         <v>3</v>
       </c>
       <c r="N235" s="8">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="O235" s="8"/>
       <c r="P235" s="8"/>
@@ -16749,7 +16749,7 @@
         <v>12</v>
       </c>
       <c r="I237" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J237" s="8">
         <v>0</v>
@@ -16762,10 +16762,10 @@
       </c>
       <c r="M237" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N237" s="8">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="O237" s="8"/>
       <c r="P237" s="8"/>
@@ -16800,7 +16800,7 @@
         <v>14</v>
       </c>
       <c r="I238" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J238" s="8">
         <v>0</v>
@@ -16813,10 +16813,10 @@
       </c>
       <c r="M238" s="8">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N238" s="8">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="O238" s="8"/>
       <c r="P238" s="8"/>
@@ -16867,7 +16867,7 @@
         <v>3</v>
       </c>
       <c r="N239" s="8">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="O239" s="8"/>
       <c r="P239" s="8"/>
@@ -16902,23 +16902,23 @@
         <v>13</v>
       </c>
       <c r="I240" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J240" s="8">
         <v>0</v>
       </c>
       <c r="K240" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L240" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M240" s="8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N240" s="8">
-        <v>367</v>
+        <v>330</v>
       </c>
       <c r="O240" s="8"/>
       <c r="P240" s="8"/>
@@ -16969,7 +16969,7 @@
         <v>3</v>
       </c>
       <c r="N241" s="8">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="O241" s="8"/>
       <c r="P241" s="8"/>
@@ -17020,7 +17020,7 @@
         <v>3</v>
       </c>
       <c r="N242" s="8">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="O242" s="8"/>
       <c r="P242" s="8"/>
@@ -17055,23 +17055,23 @@
         <v>15</v>
       </c>
       <c r="I243" s="8">
+        <v>4</v>
+      </c>
+      <c r="J243" s="8">
+        <v>0</v>
+      </c>
+      <c r="K243" s="8">
         <v>1</v>
       </c>
-      <c r="J243" s="8">
-        <v>0</v>
-      </c>
-      <c r="K243" s="8">
-        <v>2</v>
-      </c>
       <c r="L243" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M243" s="8">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N243" s="8">
-        <v>156</v>
+        <v>76</v>
       </c>
       <c r="O243" s="8"/>
       <c r="P243" s="8"/>
@@ -17224,7 +17224,7 @@
         <v>3</v>
       </c>
       <c r="N246" s="8">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="O246" s="8"/>
       <c r="P246" s="8"/>
@@ -17268,14 +17268,14 @@
         <v>0</v>
       </c>
       <c r="L247" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M247" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N247" s="8">
-        <v>340</v>
+        <v>285</v>
       </c>
       <c r="O247" s="8"/>
       <c r="P247" s="8"/>
@@ -17428,7 +17428,7 @@
         <v>3</v>
       </c>
       <c r="N250" s="8">
-        <v>1427</v>
+        <v>1394</v>
       </c>
       <c r="O250" s="8"/>
       <c r="P250" s="8"/>
@@ -17479,7 +17479,7 @@
         <v>2</v>
       </c>
       <c r="N251" s="8">
-        <v>1235</v>
+        <v>1218</v>
       </c>
       <c r="O251" s="8"/>
       <c r="P251" s="8"/>
@@ -17581,7 +17581,7 @@
         <v>2</v>
       </c>
       <c r="N253" s="8">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="O253" s="8"/>
       <c r="P253" s="8"/>
@@ -17632,7 +17632,7 @@
         <v>2</v>
       </c>
       <c r="N254" s="8">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="O254" s="8"/>
       <c r="P254" s="8"/>
@@ -17683,7 +17683,7 @@
         <v>3</v>
       </c>
       <c r="N255" s="8">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O255" s="8"/>
       <c r="P255" s="8"/>
@@ -17718,23 +17718,23 @@
         <v>14</v>
       </c>
       <c r="I256" s="8">
+        <v>2</v>
+      </c>
+      <c r="J256" s="8">
+        <v>0</v>
+      </c>
+      <c r="K256" s="8">
+        <v>0</v>
+      </c>
+      <c r="L256" s="8">
         <v>1</v>
-      </c>
-      <c r="J256" s="8">
-        <v>0</v>
-      </c>
-      <c r="K256" s="8">
-        <v>0</v>
-      </c>
-      <c r="L256" s="8">
-        <v>0</v>
       </c>
       <c r="M256" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N256" s="8">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="O256" s="8"/>
       <c r="P256" s="8"/>
@@ -17785,7 +17785,7 @@
         <v>4</v>
       </c>
       <c r="N257" s="8">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O257" s="8"/>
       <c r="P257" s="8"/>
@@ -17820,7 +17820,7 @@
         <v>16</v>
       </c>
       <c r="I258" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J258" s="8">
         <v>0</v>
@@ -17833,10 +17833,10 @@
       </c>
       <c r="M258" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N258" s="8">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O258" s="8"/>
       <c r="P258" s="8"/>
@@ -17922,7 +17922,7 @@
         <v>13</v>
       </c>
       <c r="I260" s="8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J260" s="8">
         <v>0</v>
@@ -17935,10 +17935,10 @@
       </c>
       <c r="M260" s="8">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N260" s="8">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="O260" s="8"/>
       <c r="P260" s="8"/>
@@ -17973,7 +17973,7 @@
         <v>12</v>
       </c>
       <c r="I261" s="8">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J261" s="8">
         <v>0</v>
@@ -17986,10 +17986,10 @@
       </c>
       <c r="M261" s="8">
         <f t="shared" si="4"/>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N261" s="8">
-        <v>776</v>
+        <v>694</v>
       </c>
       <c r="O261" s="8"/>
       <c r="P261" s="8"/>
@@ -18033,14 +18033,14 @@
         <v>0</v>
       </c>
       <c r="L262" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M262" s="8">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N262" s="8">
-        <v>292</v>
+        <v>255</v>
       </c>
       <c r="O262" s="8"/>
       <c r="P262" s="8"/>
@@ -18075,23 +18075,23 @@
         <v>12</v>
       </c>
       <c r="I263" s="8">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J263" s="8">
         <v>0</v>
       </c>
       <c r="K263" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L263" s="8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M263" s="8">
         <f t="shared" si="4"/>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N263" s="8">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="O263" s="8"/>
       <c r="P263" s="8"/>
@@ -18142,7 +18142,7 @@
         <v>2</v>
       </c>
       <c r="N264" s="8">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="O264" s="8"/>
       <c r="P264" s="8"/>
@@ -18177,7 +18177,7 @@
         <v>14</v>
       </c>
       <c r="I265" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J265" s="8">
         <v>0</v>
@@ -18190,7 +18190,7 @@
       </c>
       <c r="M265" s="8">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N265" s="8">
         <v>40</v>
@@ -18244,7 +18244,7 @@
         <v>3</v>
       </c>
       <c r="N266" s="8">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="O266" s="8"/>
       <c r="P266" s="8"/>
@@ -18295,7 +18295,7 @@
         <v>3</v>
       </c>
       <c r="N267" s="8">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="O267" s="8"/>
       <c r="P267" s="8"/>
@@ -18381,7 +18381,7 @@
         <v>15</v>
       </c>
       <c r="I269" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J269" s="8">
         <v>0</v>
@@ -18394,7 +18394,7 @@
       </c>
       <c r="M269" s="8">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N269" s="8">
         <v>0</v>
@@ -18642,17 +18642,17 @@
         <v>0</v>
       </c>
       <c r="K274" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L274" s="8">
         <v>0</v>
       </c>
       <c r="M274" s="8">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N274" s="8">
-        <v>1</v>
+        <v>487</v>
       </c>
       <c r="O274" s="8"/>
       <c r="P274" s="8"/>
@@ -18703,7 +18703,7 @@
         <v>3</v>
       </c>
       <c r="N275" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O275" s="8"/>
       <c r="P275" s="8"/>
@@ -18754,7 +18754,7 @@
         <v>3</v>
       </c>
       <c r="N276" s="8">
-        <v>221</v>
+        <v>181</v>
       </c>
       <c r="O276" s="8"/>
       <c r="P276" s="8"/>
@@ -18840,7 +18840,7 @@
         <v>12</v>
       </c>
       <c r="I278" s="8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J278" s="8">
         <v>0</v>
@@ -18853,10 +18853,10 @@
       </c>
       <c r="M278" s="8">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N278" s="8">
-        <v>1354</v>
+        <v>1260</v>
       </c>
       <c r="O278" s="8"/>
       <c r="P278" s="8"/>
@@ -18897,14 +18897,14 @@
         <v>0</v>
       </c>
       <c r="K279" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L279" s="8">
         <v>0</v>
       </c>
       <c r="M279" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N279" s="8">
         <v>0</v>
@@ -18942,7 +18942,7 @@
         <v>16</v>
       </c>
       <c r="I280" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J280" s="8">
         <v>0</v>
@@ -18955,7 +18955,7 @@
       </c>
       <c r="M280" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N280" s="8">
         <v>67</v>
@@ -19095,7 +19095,7 @@
         <v>12</v>
       </c>
       <c r="I283" s="8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J283" s="8">
         <v>0</v>
@@ -19104,14 +19104,14 @@
         <v>0</v>
       </c>
       <c r="L283" s="8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M283" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="N283" s="8">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O283" s="8"/>
       <c r="P283" s="8"/>
@@ -19146,7 +19146,7 @@
         <v>12</v>
       </c>
       <c r="I284" s="8">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="J284" s="8">
         <v>0</v>
@@ -19159,7 +19159,7 @@
       </c>
       <c r="M284" s="8">
         <f t="shared" si="4"/>
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="N284" s="8">
         <v>0</v>
@@ -19213,7 +19213,7 @@
         <v>3</v>
       </c>
       <c r="N285" s="8">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="O285" s="8"/>
       <c r="P285" s="8"/>
@@ -19264,7 +19264,7 @@
         <v>4</v>
       </c>
       <c r="N286" s="8">
-        <v>982</v>
+        <v>974</v>
       </c>
       <c r="O286" s="8"/>
       <c r="P286" s="8"/>
@@ -19315,7 +19315,7 @@
         <v>9</v>
       </c>
       <c r="N287" s="8">
-        <v>1120</v>
+        <v>1114</v>
       </c>
       <c r="O287" s="8"/>
       <c r="P287" s="8"/>
@@ -19366,7 +19366,7 @@
         <v>4</v>
       </c>
       <c r="N288" s="8">
-        <v>1450</v>
+        <v>1444</v>
       </c>
       <c r="O288" s="8"/>
       <c r="P288" s="8"/>
@@ -19468,7 +19468,7 @@
         <v>1</v>
       </c>
       <c r="N290" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O290" s="8"/>
       <c r="P290" s="8"/>
@@ -19503,7 +19503,7 @@
         <v>12</v>
       </c>
       <c r="I291" s="8">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J291" s="8">
         <v>0</v>
@@ -19512,14 +19512,14 @@
         <v>0</v>
       </c>
       <c r="L291" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M291" s="8">
         <f t="shared" si="4"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N291" s="8">
-        <v>1791</v>
+        <v>1686</v>
       </c>
       <c r="O291" s="8"/>
       <c r="P291" s="8"/>
@@ -19570,7 +19570,7 @@
         <v>3</v>
       </c>
       <c r="N292" s="8">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="O292" s="8"/>
       <c r="P292" s="8"/>
@@ -19656,23 +19656,23 @@
         <v>12</v>
       </c>
       <c r="I294" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J294" s="8">
         <v>0</v>
       </c>
       <c r="K294" s="8">
+        <v>1</v>
+      </c>
+      <c r="L294" s="8">
         <v>5</v>
-      </c>
-      <c r="L294" s="8">
-        <v>4</v>
       </c>
       <c r="M294" s="8">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="N294" s="8">
-        <v>1484</v>
+        <v>1385</v>
       </c>
       <c r="O294" s="8"/>
       <c r="P294" s="8"/>
@@ -19962,7 +19962,7 @@
         <v>13</v>
       </c>
       <c r="I300" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J300" s="8">
         <v>0</v>
@@ -19975,7 +19975,7 @@
       </c>
       <c r="M300" s="8">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N300" s="8">
         <v>0</v>
@@ -20029,7 +20029,7 @@
         <v>6</v>
       </c>
       <c r="N301" s="8">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="O301" s="8"/>
       <c r="P301" s="8"/>
@@ -20080,7 +20080,7 @@
         <v>5</v>
       </c>
       <c r="N302" s="8">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="O302" s="8"/>
       <c r="P302" s="8"/>
@@ -20115,7 +20115,7 @@
         <v>13</v>
       </c>
       <c r="I303" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J303" s="8">
         <v>0</v>
@@ -20128,10 +20128,10 @@
       </c>
       <c r="M303" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N303" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O303" s="8"/>
       <c r="P303" s="8"/>
@@ -20166,7 +20166,7 @@
         <v>13</v>
       </c>
       <c r="I304" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J304" s="8">
         <v>0</v>
@@ -20179,10 +20179,10 @@
       </c>
       <c r="M304" s="8">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N304" s="8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O304" s="8"/>
       <c r="P304" s="8"/>
@@ -20233,7 +20233,7 @@
         <v>8</v>
       </c>
       <c r="N305" s="8">
-        <v>511</v>
+        <v>498</v>
       </c>
       <c r="O305" s="8"/>
       <c r="P305" s="8"/>
@@ -20284,7 +20284,7 @@
         <v>9</v>
       </c>
       <c r="N306" s="8">
-        <v>1057</v>
+        <v>1026</v>
       </c>
       <c r="O306" s="8"/>
       <c r="P306" s="8"/>
@@ -20335,7 +20335,7 @@
         <v>11</v>
       </c>
       <c r="N307" s="8">
-        <v>1027</v>
+        <v>1011</v>
       </c>
       <c r="O307" s="8"/>
       <c r="P307" s="8"/>
@@ -20386,7 +20386,7 @@
         <v>11</v>
       </c>
       <c r="N308" s="8">
-        <v>996</v>
+        <v>951</v>
       </c>
       <c r="O308" s="8"/>
       <c r="P308" s="8"/>
@@ -20437,7 +20437,7 @@
         <v>3</v>
       </c>
       <c r="N309" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O309" s="8"/>
       <c r="P309" s="8"/>
@@ -20472,7 +20472,7 @@
         <v>16</v>
       </c>
       <c r="I310" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J310" s="8">
         <v>0</v>
@@ -20485,7 +20485,7 @@
       </c>
       <c r="M310" s="8">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N310" s="8">
         <v>258</v>
@@ -20539,7 +20539,7 @@
         <v>2</v>
       </c>
       <c r="N311" s="8">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="O311" s="8"/>
       <c r="P311" s="8"/>
@@ -20590,7 +20590,7 @@
         <v>6</v>
       </c>
       <c r="N312" s="8">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="O312" s="8"/>
       <c r="P312" s="8"/>
@@ -20625,7 +20625,7 @@
         <v>13</v>
       </c>
       <c r="I313" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J313" s="8">
         <v>0</v>
@@ -20638,10 +20638,10 @@
       </c>
       <c r="M313" s="8">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N313" s="8">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="O313" s="8"/>
       <c r="P313" s="8"/>
@@ -20676,7 +20676,7 @@
         <v>12</v>
       </c>
       <c r="I314" s="8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J314" s="8">
         <v>0</v>
@@ -20689,10 +20689,10 @@
       </c>
       <c r="M314" s="8">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N314" s="8">
-        <v>411</v>
+        <v>395</v>
       </c>
       <c r="O314" s="8"/>
       <c r="P314" s="8"/>
@@ -20743,7 +20743,7 @@
         <v>8</v>
       </c>
       <c r="N315" s="8">
-        <v>203</v>
+        <v>169</v>
       </c>
       <c r="O315" s="8"/>
       <c r="P315" s="8"/>
@@ -20778,7 +20778,7 @@
         <v>12</v>
       </c>
       <c r="I316" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J316" s="8">
         <v>0</v>
@@ -20791,10 +20791,10 @@
       </c>
       <c r="M316" s="8">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N316" s="8">
-        <v>707</v>
+        <v>689</v>
       </c>
       <c r="O316" s="8"/>
       <c r="P316" s="8"/>
@@ -20829,7 +20829,7 @@
         <v>12</v>
       </c>
       <c r="I317" s="8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J317" s="8">
         <v>0</v>
@@ -20838,14 +20838,14 @@
         <v>2</v>
       </c>
       <c r="L317" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M317" s="8">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N317" s="8">
-        <v>299</v>
+        <v>270</v>
       </c>
       <c r="O317" s="8"/>
       <c r="P317" s="8"/>
@@ -20880,23 +20880,23 @@
         <v>12</v>
       </c>
       <c r="I318" s="8">
+        <v>9</v>
+      </c>
+      <c r="J318" s="8">
+        <v>0</v>
+      </c>
+      <c r="K318" s="8">
+        <v>0</v>
+      </c>
+      <c r="L318" s="8">
         <v>3</v>
-      </c>
-      <c r="J318" s="8">
-        <v>0</v>
-      </c>
-      <c r="K318" s="8">
-        <v>7</v>
-      </c>
-      <c r="L318" s="8">
-        <v>0</v>
       </c>
       <c r="M318" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N318" s="8">
-        <v>798</v>
+        <v>678</v>
       </c>
       <c r="O318" s="8"/>
       <c r="P318" s="8"/>
@@ -20947,7 +20947,7 @@
         <v>4</v>
       </c>
       <c r="N319" s="8">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="O319" s="8"/>
       <c r="P319" s="8"/>
@@ -20998,7 +20998,7 @@
         <v>4</v>
       </c>
       <c r="N320" s="8">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="O320" s="8"/>
       <c r="P320" s="8"/>
@@ -21033,7 +21033,7 @@
         <v>14</v>
       </c>
       <c r="I321" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J321" s="8">
         <v>0</v>
@@ -21042,14 +21042,14 @@
         <v>0</v>
       </c>
       <c r="L321" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M321" s="8">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N321" s="8">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="O321" s="8"/>
       <c r="P321" s="8"/>
@@ -21100,7 +21100,7 @@
         <v>3</v>
       </c>
       <c r="N322" s="8">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="O322" s="8"/>
       <c r="P322" s="8"/>
@@ -21151,7 +21151,7 @@
         <v>4</v>
       </c>
       <c r="N323" s="8">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="O323" s="8"/>
       <c r="P323" s="8"/>
@@ -21253,7 +21253,7 @@
         <v>3</v>
       </c>
       <c r="N325" s="8">
-        <v>466</v>
+        <v>449</v>
       </c>
       <c r="O325" s="8"/>
       <c r="P325" s="8"/>
@@ -21304,7 +21304,7 @@
         <v>3</v>
       </c>
       <c r="N326" s="8">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="O326" s="8"/>
       <c r="P326" s="8"/>
@@ -21339,7 +21339,7 @@
         <v>16</v>
       </c>
       <c r="I327" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J327" s="8">
         <v>0</v>
@@ -21352,10 +21352,10 @@
       </c>
       <c r="M327" s="8">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N327" s="8">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O327" s="8"/>
       <c r="P327" s="8"/>
@@ -21406,7 +21406,7 @@
         <v>2</v>
       </c>
       <c r="N328" s="8">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O328" s="8"/>
       <c r="P328" s="8"/>
@@ -21457,7 +21457,7 @@
         <v>4</v>
       </c>
       <c r="N329" s="8">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="O329" s="8"/>
       <c r="P329" s="8"/>
@@ -21661,7 +21661,7 @@
         <v>3</v>
       </c>
       <c r="N333" s="8">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="O333" s="8"/>
       <c r="P333" s="8"/>
@@ -21712,7 +21712,7 @@
         <v>4</v>
       </c>
       <c r="N334" s="8">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="O334" s="8"/>
       <c r="P334" s="8"/>
@@ -21747,13 +21747,13 @@
         <v>13</v>
       </c>
       <c r="I335" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J335" s="8">
         <v>0</v>
       </c>
       <c r="K335" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L335" s="8">
         <v>0</v>
@@ -21814,7 +21814,7 @@
         <v>4</v>
       </c>
       <c r="N336" s="8">
-        <v>626</v>
+        <v>598</v>
       </c>
       <c r="O336" s="8"/>
       <c r="P336" s="8"/>
@@ -21849,7 +21849,7 @@
         <v>12</v>
       </c>
       <c r="I337" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J337" s="8">
         <v>0</v>
@@ -21862,10 +21862,10 @@
       </c>
       <c r="M337" s="8">
         <f t="shared" si="5"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N337" s="8">
-        <v>1202</v>
+        <v>1194</v>
       </c>
       <c r="O337" s="8"/>
       <c r="P337" s="8"/>
@@ -21900,23 +21900,23 @@
         <v>12</v>
       </c>
       <c r="I338" s="8">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J338" s="8">
         <v>0</v>
       </c>
       <c r="K338" s="8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L338" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M338" s="8">
         <f t="shared" si="5"/>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="N338" s="8">
-        <v>1267</v>
+        <v>1227</v>
       </c>
       <c r="O338" s="8"/>
       <c r="P338" s="8"/>
@@ -21967,7 +21967,7 @@
         <v>3</v>
       </c>
       <c r="N339" s="8">
-        <v>858</v>
+        <v>851</v>
       </c>
       <c r="O339" s="8"/>
       <c r="P339" s="8"/>
@@ -22002,23 +22002,23 @@
         <v>14</v>
       </c>
       <c r="I340" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J340" s="8">
         <v>0</v>
       </c>
       <c r="K340" s="8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L340" s="8">
         <v>5</v>
       </c>
       <c r="M340" s="8">
         <f t="shared" si="5"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="N340" s="8">
-        <v>794</v>
+        <v>743</v>
       </c>
       <c r="O340" s="8"/>
       <c r="P340" s="8"/>
@@ -22053,13 +22053,13 @@
         <v>14</v>
       </c>
       <c r="I341" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J341" s="8">
         <v>0</v>
       </c>
       <c r="K341" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L341" s="8">
         <v>0</v>
@@ -22069,7 +22069,7 @@
         <v>3</v>
       </c>
       <c r="N341" s="8">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="O341" s="8"/>
       <c r="P341" s="8"/>
@@ -22120,7 +22120,7 @@
         <v>4</v>
       </c>
       <c r="N342" s="8">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="O342" s="8"/>
       <c r="P342" s="8"/>
@@ -22257,7 +22257,7 @@
         <v>12</v>
       </c>
       <c r="I345" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J345" s="8">
         <v>0</v>
@@ -22270,7 +22270,7 @@
       </c>
       <c r="M345" s="8">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N345" s="8">
         <v>0</v>
@@ -22359,23 +22359,23 @@
         <v>13</v>
       </c>
       <c r="I347" s="8">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J347" s="8">
         <v>0</v>
       </c>
       <c r="K347" s="8">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L347" s="8">
         <v>0</v>
       </c>
       <c r="M347" s="8">
         <f t="shared" si="5"/>
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="N347" s="8">
-        <v>588</v>
+        <v>523</v>
       </c>
       <c r="O347" s="8"/>
       <c r="P347" s="9"/>
@@ -22630,7 +22630,7 @@
         <v>2</v>
       </c>
       <c r="N352" s="8">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="O352" s="8"/>
       <c r="P352" s="9"/>
@@ -22776,14 +22776,14 @@
         <v>0</v>
       </c>
       <c r="L355" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M355" s="8">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N355" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O355" s="8"/>
       <c r="P355" s="9"/>
@@ -23175,7 +23175,7 @@
         <v>12</v>
       </c>
       <c r="I363" s="8">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="J363" s="8">
         <v>0</v>
@@ -23188,7 +23188,7 @@
       </c>
       <c r="M363" s="8">
         <f t="shared" si="5"/>
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="N363" s="8">
         <v>1318</v>
@@ -23344,7 +23344,7 @@
         <v>2</v>
       </c>
       <c r="N366" s="8">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="O366" s="8"/>
       <c r="P366" s="9"/>
@@ -23379,7 +23379,7 @@
         <v>12</v>
       </c>
       <c r="I367" s="8">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="J367" s="8">
         <v>0</v>
@@ -23392,7 +23392,7 @@
       </c>
       <c r="M367" s="8">
         <f t="shared" si="5"/>
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="N367" s="8">
         <v>0</v>
@@ -23430,13 +23430,13 @@
         <v>12</v>
       </c>
       <c r="I368" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J368" s="8">
         <v>0</v>
       </c>
       <c r="K368" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L368" s="8">
         <v>0</v>
@@ -23446,7 +23446,7 @@
         <v>5</v>
       </c>
       <c r="N368" s="8">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O368" s="8"/>
       <c r="P368" s="9"/>
@@ -23481,7 +23481,7 @@
         <v>15</v>
       </c>
       <c r="I369" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J369" s="8">
         <v>0</v>
@@ -23494,7 +23494,7 @@
       </c>
       <c r="M369" s="8">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N369" s="8">
         <v>0</v>
@@ -23548,7 +23548,7 @@
         <v>2</v>
       </c>
       <c r="N370" s="8">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="O370" s="8"/>
       <c r="P370" s="9"/>
@@ -23701,7 +23701,7 @@
         <v>4</v>
       </c>
       <c r="N373" s="8">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O373" s="8"/>
       <c r="P373" s="9"/>
@@ -24255,14 +24255,14 @@
         <v>0</v>
       </c>
       <c r="L384" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M384" s="8">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N384" s="8">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="O384" s="8"/>
       <c r="P384" s="9"/>
@@ -24552,23 +24552,23 @@
         <v>12</v>
       </c>
       <c r="I390" s="8">
+        <v>4</v>
+      </c>
+      <c r="J390" s="8">
+        <v>0</v>
+      </c>
+      <c r="K390" s="8">
+        <v>0</v>
+      </c>
+      <c r="L390" s="8">
         <v>2</v>
-      </c>
-      <c r="J390" s="8">
-        <v>0</v>
-      </c>
-      <c r="K390" s="8">
-        <v>0</v>
-      </c>
-      <c r="L390" s="8">
-        <v>1</v>
       </c>
       <c r="M390" s="8">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N390" s="8">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="O390" s="8"/>
       <c r="P390" s="7"/>
@@ -24960,23 +24960,23 @@
         <v>15</v>
       </c>
       <c r="I398" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J398" s="8">
         <v>0</v>
       </c>
       <c r="K398" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L398" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M398" s="8">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N398" s="8">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="O398" s="7"/>
       <c r="P398" s="7"/>
@@ -25266,13 +25266,13 @@
         <v>15</v>
       </c>
       <c r="I404" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J404" s="8">
         <v>0</v>
       </c>
       <c r="K404" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L404" s="8">
         <v>0</v>
@@ -25282,7 +25282,7 @@
         <v>2</v>
       </c>
       <c r="N404" s="8">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="O404" s="7"/>
       <c r="P404" s="7"/>
@@ -25317,13 +25317,13 @@
         <v>15</v>
       </c>
       <c r="I405" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J405" s="8">
         <v>0</v>
       </c>
       <c r="K405" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L405" s="8">
         <v>0</v>
@@ -25333,7 +25333,7 @@
         <v>2</v>
       </c>
       <c r="N405" s="8">
-        <v>426</v>
+        <v>409</v>
       </c>
       <c r="O405" s="7"/>
       <c r="P405" s="7"/>
@@ -25368,13 +25368,13 @@
         <v>15</v>
       </c>
       <c r="I406" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J406" s="8">
         <v>0</v>
       </c>
       <c r="K406" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L406" s="8">
         <v>0</v>
@@ -25470,13 +25470,13 @@
         <v>13</v>
       </c>
       <c r="I408" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J408" s="8">
         <v>0</v>
       </c>
       <c r="K408" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L408" s="8">
         <v>0</v>
@@ -25486,7 +25486,7 @@
         <v>2</v>
       </c>
       <c r="N408" s="8">
-        <v>297</v>
+        <v>471</v>
       </c>
       <c r="O408" s="7"/>
       <c r="P408" s="7"/>
@@ -25521,13 +25521,13 @@
         <v>13</v>
       </c>
       <c r="I409" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J409" s="8">
         <v>0</v>
       </c>
       <c r="K409" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L409" s="8">
         <v>0</v>
@@ -25537,7 +25537,7 @@
         <v>2</v>
       </c>
       <c r="N409" s="8">
-        <v>9</v>
+        <v>87</v>
       </c>
       <c r="O409" s="7"/>
       <c r="P409" s="7"/>
@@ -25572,13 +25572,13 @@
         <v>16</v>
       </c>
       <c r="I410" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J410" s="8">
         <v>0</v>
       </c>
       <c r="K410" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L410" s="8">
         <v>0</v>
@@ -25588,7 +25588,7 @@
         <v>2</v>
       </c>
       <c r="N410" s="8">
-        <v>87</v>
+        <v>150</v>
       </c>
       <c r="O410" s="7"/>
       <c r="P410" s="7"/>
@@ -25623,13 +25623,13 @@
         <v>16</v>
       </c>
       <c r="I411" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J411" s="8">
         <v>0</v>
       </c>
       <c r="K411" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L411" s="8">
         <v>0</v>
@@ -25639,7 +25639,7 @@
         <v>2</v>
       </c>
       <c r="N411" s="8">
-        <v>95</v>
+        <v>219</v>
       </c>
       <c r="O411" s="7"/>
       <c r="P411" s="7"/>
@@ -25674,13 +25674,13 @@
         <v>16</v>
       </c>
       <c r="I412" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J412" s="8">
         <v>0</v>
       </c>
       <c r="K412" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L412" s="8">
         <v>0</v>
@@ -25690,7 +25690,7 @@
         <v>2</v>
       </c>
       <c r="N412" s="8">
-        <v>76</v>
+        <v>287</v>
       </c>
       <c r="O412" s="7"/>
       <c r="P412" s="7"/>
@@ -25725,13 +25725,13 @@
         <v>16</v>
       </c>
       <c r="I413" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J413" s="8">
         <v>0</v>
       </c>
       <c r="K413" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L413" s="8">
         <v>0</v>
@@ -25741,7 +25741,7 @@
         <v>2</v>
       </c>
       <c r="N413" s="8">
-        <v>154</v>
+        <v>220</v>
       </c>
       <c r="O413" s="7"/>
       <c r="P413" s="7"/>
@@ -25785,14 +25785,14 @@
         <v>0</v>
       </c>
       <c r="L414" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M414" s="8">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N414" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O414" s="7"/>
       <c r="P414" s="7"/>
@@ -25836,14 +25836,14 @@
         <v>0</v>
       </c>
       <c r="L415" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M415" s="8">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N415" s="8">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="O415" s="7"/>
       <c r="P415" s="7"/>
@@ -25878,13 +25878,13 @@
         <v>12</v>
       </c>
       <c r="I416" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J416" s="8">
         <v>0</v>
       </c>
       <c r="K416" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L416" s="8">
         <v>0</v>
@@ -25894,7 +25894,7 @@
         <v>3</v>
       </c>
       <c r="N416" s="8">
-        <v>17</v>
+        <v>262</v>
       </c>
       <c r="O416" s="7"/>
       <c r="P416" s="7"/>
@@ -25929,13 +25929,13 @@
         <v>12</v>
       </c>
       <c r="I417" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J417" s="8">
         <v>0</v>
       </c>
       <c r="K417" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L417" s="8">
         <v>0</v>
@@ -25945,7 +25945,7 @@
         <v>3</v>
       </c>
       <c r="N417" s="8">
-        <v>22</v>
+        <v>230</v>
       </c>
       <c r="O417" s="7"/>
       <c r="P417" s="7"/>
@@ -25980,13 +25980,13 @@
         <v>12</v>
       </c>
       <c r="I418" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J418" s="8">
         <v>0</v>
       </c>
       <c r="K418" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L418" s="8">
         <v>0</v>
@@ -25996,7 +25996,7 @@
         <v>3</v>
       </c>
       <c r="N418" s="8">
-        <v>22</v>
+        <v>186</v>
       </c>
       <c r="O418" s="7"/>
       <c r="P418" s="7"/>
@@ -26031,13 +26031,13 @@
         <v>14</v>
       </c>
       <c r="I419" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J419" s="8">
         <v>0</v>
       </c>
       <c r="K419" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L419" s="8">
         <v>0</v>
@@ -26082,13 +26082,13 @@
         <v>14</v>
       </c>
       <c r="I420" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J420" s="8">
         <v>0</v>
       </c>
       <c r="K420" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L420" s="8">
         <v>0</v>
@@ -26098,7 +26098,7 @@
         <v>3</v>
       </c>
       <c r="N420" s="8">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="O420" s="7"/>
       <c r="P420" s="7"/>
@@ -26133,13 +26133,13 @@
         <v>14</v>
       </c>
       <c r="I421" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J421" s="8">
         <v>0</v>
       </c>
       <c r="K421" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L421" s="8">
         <v>0</v>
@@ -26149,7 +26149,7 @@
         <v>2</v>
       </c>
       <c r="N421" s="8">
-        <v>433</v>
+        <v>858</v>
       </c>
       <c r="O421" s="7"/>
       <c r="P421" s="7"/>
@@ -26184,13 +26184,13 @@
         <v>14</v>
       </c>
       <c r="I422" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J422" s="8">
         <v>0</v>
       </c>
       <c r="K422" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L422" s="8">
         <v>0</v>
@@ -26200,7 +26200,7 @@
         <v>2</v>
       </c>
       <c r="N422" s="8">
-        <v>257</v>
+        <v>322</v>
       </c>
       <c r="O422" s="7"/>
       <c r="P422" s="7"/>
@@ -26235,13 +26235,13 @@
         <v>14</v>
       </c>
       <c r="I423" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J423" s="8">
         <v>0</v>
       </c>
       <c r="K423" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L423" s="8">
         <v>0</v>
@@ -26251,7 +26251,7 @@
         <v>2</v>
       </c>
       <c r="N423" s="8">
-        <v>53</v>
+        <v>597</v>
       </c>
       <c r="O423" s="7"/>
       <c r="P423" s="7"/>
@@ -26286,13 +26286,13 @@
         <v>14</v>
       </c>
       <c r="I424" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J424" s="8">
         <v>0</v>
       </c>
       <c r="K424" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L424" s="8">
         <v>0</v>
@@ -26302,7 +26302,7 @@
         <v>2</v>
       </c>
       <c r="N424" s="8">
-        <v>44</v>
+        <v>415</v>
       </c>
       <c r="O424" s="7"/>
       <c r="P424" s="7"/>
@@ -26337,13 +26337,13 @@
         <v>14</v>
       </c>
       <c r="I425" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J425" s="8">
         <v>0</v>
       </c>
       <c r="K425" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L425" s="8">
         <v>0</v>
@@ -26353,7 +26353,7 @@
         <v>2</v>
       </c>
       <c r="N425" s="8">
-        <v>12</v>
+        <v>115</v>
       </c>
       <c r="O425" s="7"/>
       <c r="P425" s="7"/>
@@ -26388,13 +26388,13 @@
         <v>14</v>
       </c>
       <c r="I426" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J426" s="8">
         <v>0</v>
       </c>
       <c r="K426" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L426" s="8">
         <v>0</v>
@@ -26404,7 +26404,7 @@
         <v>2</v>
       </c>
       <c r="N426" s="8">
-        <v>3</v>
+        <v>76</v>
       </c>
       <c r="O426" s="7"/>
       <c r="P426" s="7"/>
@@ -26439,13 +26439,13 @@
         <v>14</v>
       </c>
       <c r="I427" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J427" s="8">
         <v>0</v>
       </c>
       <c r="K427" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L427" s="8">
         <v>0</v>
@@ -26608,7 +26608,7 @@
         <v>0</v>
       </c>
       <c r="N430" s="8">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O430" s="7"/>
       <c r="P430" s="7"/>
@@ -26659,7 +26659,7 @@
         <v>0</v>
       </c>
       <c r="N431" s="8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O431" s="7"/>
       <c r="P431" s="7"/>
@@ -26710,7 +26710,7 @@
         <v>0</v>
       </c>
       <c r="N432" s="8">
-        <v>12</v>
+        <v>180</v>
       </c>
       <c r="O432" s="7"/>
       <c r="P432" s="7"/>
@@ -26761,7 +26761,7 @@
         <v>0</v>
       </c>
       <c r="N433" s="8">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O433" s="7"/>
       <c r="P433" s="7"/>

--- a/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
+++ b/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\Fossil Replenishment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6492CF69-64E1-486E-8DA8-E80C960992B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8929BEAF-4619-46DF-A9E7-18BE2D268631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6662473D-6E1F-42FD-999B-28162E22D4B5}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3476" uniqueCount="1343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3484" uniqueCount="1346">
   <si>
     <t>In Transit PO</t>
   </si>
@@ -4066,6 +4066,15 @@
   </si>
   <si>
     <t>FBA80242</t>
+  </si>
+  <si>
+    <t>AR11615</t>
+  </si>
+  <si>
+    <t>B0DB1JQS43</t>
+  </si>
+  <si>
+    <t>FBA79494</t>
   </si>
 </sst>
 </file>
@@ -4764,23 +4773,23 @@
         <v>12</v>
       </c>
       <c r="I2" s="8">
-        <v>724</v>
+        <v>794</v>
       </c>
       <c r="J2" s="8">
         <v>0</v>
       </c>
       <c r="K2" s="8">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="L2" s="8">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="M2" s="8">
         <f>I2+J2+K2+L2</f>
-        <v>846</v>
+        <v>837</v>
       </c>
       <c r="N2" s="8">
-        <v>1385</v>
+        <v>1281</v>
       </c>
       <c r="O2" s="8"/>
       <c r="P2" s="8"/>
@@ -4815,7 +4824,7 @@
         <v>12</v>
       </c>
       <c r="I3" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3" s="8">
         <v>0</v>
@@ -4828,7 +4837,7 @@
       </c>
       <c r="M3" s="8">
         <f t="shared" ref="M3:M66" si="0">I3+J3+K3+L3</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N3" s="8">
         <v>0</v>
@@ -4917,7 +4926,7 @@
         <v>12</v>
       </c>
       <c r="I5" s="8">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="J5" s="8">
         <v>0</v>
@@ -4930,7 +4939,7 @@
       </c>
       <c r="M5" s="8">
         <f t="shared" si="0"/>
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="N5" s="8">
         <v>0</v>
@@ -4968,23 +4977,23 @@
         <v>12</v>
       </c>
       <c r="I6" s="8">
-        <v>758</v>
+        <v>795</v>
       </c>
       <c r="J6" s="8">
         <v>0</v>
       </c>
       <c r="K6" s="8">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="L6" s="8">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M6" s="8">
         <f t="shared" si="0"/>
-        <v>846</v>
+        <v>825</v>
       </c>
       <c r="N6" s="8">
-        <v>1658</v>
+        <v>1586</v>
       </c>
       <c r="O6" s="8"/>
       <c r="P6" s="8"/>
@@ -5019,7 +5028,7 @@
         <v>12</v>
       </c>
       <c r="I7" s="8">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="J7" s="8">
         <v>0</v>
@@ -5032,10 +5041,10 @@
       </c>
       <c r="M7" s="8">
         <f t="shared" si="0"/>
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="N7" s="8">
-        <v>1028</v>
+        <v>864</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
@@ -5070,23 +5079,23 @@
         <v>12</v>
       </c>
       <c r="I8" s="8">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="J8" s="8">
         <v>0</v>
       </c>
       <c r="K8" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="8">
         <v>0</v>
       </c>
       <c r="M8" s="8">
         <f t="shared" si="0"/>
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="N8" s="8">
-        <v>482</v>
+        <v>373</v>
       </c>
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
@@ -5121,7 +5130,7 @@
         <v>12</v>
       </c>
       <c r="I9" s="8">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J9" s="8">
         <v>0</v>
@@ -5130,11 +5139,11 @@
         <v>0</v>
       </c>
       <c r="L9" s="8">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M9" s="8">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="N9" s="8">
         <v>0</v>
@@ -5172,7 +5181,7 @@
         <v>12</v>
       </c>
       <c r="I10" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J10" s="8">
         <v>0</v>
@@ -5185,7 +5194,7 @@
       </c>
       <c r="M10" s="8">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N10" s="8">
         <v>0</v>
@@ -5223,23 +5232,23 @@
         <v>12</v>
       </c>
       <c r="I11" s="8">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="J11" s="8">
         <v>0</v>
       </c>
       <c r="K11" s="8">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="L11" s="8">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="M11" s="8">
         <f t="shared" si="0"/>
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="N11" s="8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O11" s="8"/>
       <c r="P11" s="8"/>
@@ -5325,20 +5334,20 @@
         <v>12</v>
       </c>
       <c r="I13" s="8">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="J13" s="8">
         <v>0</v>
       </c>
       <c r="K13" s="8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L13" s="8">
         <v>0</v>
       </c>
       <c r="M13" s="8">
         <f t="shared" si="0"/>
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="N13" s="8">
         <v>858</v>
@@ -5376,13 +5385,13 @@
         <v>12</v>
       </c>
       <c r="I14" s="8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J14" s="8">
         <v>0</v>
       </c>
       <c r="K14" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="8">
         <v>0</v>
@@ -5392,7 +5401,7 @@
         <v>22</v>
       </c>
       <c r="N14" s="8">
-        <v>697</v>
+        <v>647</v>
       </c>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
@@ -5427,7 +5436,7 @@
         <v>12</v>
       </c>
       <c r="I15" s="8">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="J15" s="8">
         <v>0</v>
@@ -5440,7 +5449,7 @@
       </c>
       <c r="M15" s="8">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="N15" s="8">
         <v>0</v>
@@ -5478,7 +5487,7 @@
         <v>12</v>
       </c>
       <c r="I16" s="8">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J16" s="8">
         <v>0</v>
@@ -5491,10 +5500,10 @@
       </c>
       <c r="M16" s="8">
         <f t="shared" si="0"/>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N16" s="8">
-        <v>603</v>
+        <v>545</v>
       </c>
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
@@ -5529,7 +5538,7 @@
         <v>12</v>
       </c>
       <c r="I17" s="8">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J17" s="8">
         <v>0</v>
@@ -5542,10 +5551,10 @@
       </c>
       <c r="M17" s="8">
         <f t="shared" si="0"/>
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="N17" s="8">
-        <v>357</v>
+        <v>341</v>
       </c>
       <c r="O17" s="8"/>
       <c r="P17" s="8"/>
@@ -5580,7 +5589,7 @@
         <v>12</v>
       </c>
       <c r="I18" s="8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J18" s="8">
         <v>0</v>
@@ -5593,7 +5602,7 @@
       </c>
       <c r="M18" s="8">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N18" s="8">
         <v>0</v>
@@ -5631,23 +5640,23 @@
         <v>13</v>
       </c>
       <c r="I19" s="8">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J19" s="8">
         <v>0</v>
       </c>
       <c r="K19" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M19" s="8">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N19" s="8">
-        <v>612</v>
+        <v>484</v>
       </c>
       <c r="O19" s="8"/>
       <c r="P19" s="8"/>
@@ -5682,7 +5691,7 @@
         <v>14</v>
       </c>
       <c r="I20" s="8">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J20" s="8">
         <v>0</v>
@@ -5695,10 +5704,10 @@
       </c>
       <c r="M20" s="8">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="N20" s="8">
-        <v>107</v>
+        <v>2</v>
       </c>
       <c r="O20" s="8"/>
       <c r="P20" s="8"/>
@@ -5733,7 +5742,7 @@
         <v>13</v>
       </c>
       <c r="I21" s="8">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J21" s="8">
         <v>0</v>
@@ -5746,7 +5755,7 @@
       </c>
       <c r="M21" s="8">
         <f t="shared" si="0"/>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N21" s="8">
         <v>0</v>
@@ -5835,23 +5844,23 @@
         <v>12</v>
       </c>
       <c r="I23" s="8">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J23" s="8">
         <v>0</v>
       </c>
       <c r="K23" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L23" s="8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M23" s="8">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N23" s="8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O23" s="8"/>
       <c r="P23" s="8"/>
@@ -5886,7 +5895,7 @@
         <v>14</v>
       </c>
       <c r="I24" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J24" s="8">
         <v>0</v>
@@ -5899,10 +5908,10 @@
       </c>
       <c r="M24" s="8">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N24" s="8">
-        <v>537</v>
+        <v>428</v>
       </c>
       <c r="O24" s="8"/>
       <c r="P24" s="8"/>
@@ -5988,7 +5997,7 @@
         <v>12</v>
       </c>
       <c r="I26" s="8">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J26" s="8">
         <v>0</v>
@@ -6001,10 +6010,10 @@
       </c>
       <c r="M26" s="8">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N26" s="8">
-        <v>358</v>
+        <v>203</v>
       </c>
       <c r="O26" s="8"/>
       <c r="P26" s="8"/>
@@ -6039,7 +6048,7 @@
         <v>12</v>
       </c>
       <c r="I27" s="8">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J27" s="8">
         <v>0</v>
@@ -6052,10 +6061,10 @@
       </c>
       <c r="M27" s="8">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N27" s="8">
-        <v>897</v>
+        <v>858</v>
       </c>
       <c r="O27" s="8"/>
       <c r="P27" s="8"/>
@@ -6198,17 +6207,17 @@
         <v>0</v>
       </c>
       <c r="K30" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L30" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="8">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N30" s="8">
-        <v>1351</v>
+        <v>1316</v>
       </c>
       <c r="O30" s="8"/>
       <c r="P30" s="8"/>
@@ -6243,7 +6252,7 @@
         <v>13</v>
       </c>
       <c r="I31" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" s="8">
         <v>0</v>
@@ -6256,7 +6265,7 @@
       </c>
       <c r="M31" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" s="8">
         <v>0</v>
@@ -6294,7 +6303,7 @@
         <v>12</v>
       </c>
       <c r="I32" s="8">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J32" s="8">
         <v>0</v>
@@ -6307,10 +6316,10 @@
       </c>
       <c r="M32" s="8">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="N32" s="8">
-        <v>613</v>
+        <v>585</v>
       </c>
       <c r="O32" s="8"/>
       <c r="P32" s="8"/>
@@ -6351,17 +6360,17 @@
         <v>0</v>
       </c>
       <c r="K33" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L33" s="8">
         <v>0</v>
       </c>
       <c r="M33" s="8">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="N33" s="8">
-        <v>915</v>
+        <v>852</v>
       </c>
       <c r="O33" s="8"/>
       <c r="P33" s="8"/>
@@ -6396,7 +6405,7 @@
         <v>12</v>
       </c>
       <c r="I34" s="8">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J34" s="8">
         <v>0</v>
@@ -6409,10 +6418,10 @@
       </c>
       <c r="M34" s="8">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N34" s="8">
-        <v>930</v>
+        <v>904</v>
       </c>
       <c r="O34" s="8"/>
       <c r="P34" s="8"/>
@@ -6463,7 +6472,7 @@
         <v>12</v>
       </c>
       <c r="N35" s="8">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="O35" s="8"/>
       <c r="P35" s="8"/>
@@ -6498,7 +6507,7 @@
         <v>13</v>
       </c>
       <c r="I36" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J36" s="8">
         <v>0</v>
@@ -6511,10 +6520,10 @@
       </c>
       <c r="M36" s="8">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N36" s="8">
-        <v>637</v>
+        <v>623</v>
       </c>
       <c r="O36" s="8"/>
       <c r="P36" s="8"/>
@@ -6565,7 +6574,7 @@
         <v>30</v>
       </c>
       <c r="N37" s="8">
-        <v>1148</v>
+        <v>1031</v>
       </c>
       <c r="O37" s="8"/>
       <c r="P37" s="8"/>
@@ -6651,23 +6660,23 @@
         <v>12</v>
       </c>
       <c r="I39" s="8">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J39" s="8">
         <v>0</v>
       </c>
       <c r="K39" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L39" s="8">
         <v>0</v>
       </c>
       <c r="M39" s="8">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="N39" s="8">
-        <v>1905</v>
+        <v>2702</v>
       </c>
       <c r="O39" s="8"/>
       <c r="P39" s="8"/>
@@ -6753,23 +6762,23 @@
         <v>12</v>
       </c>
       <c r="I41" s="8">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J41" s="8">
         <v>0</v>
       </c>
       <c r="K41" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L41" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M41" s="8">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N41" s="8">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="O41" s="8"/>
       <c r="P41" s="8"/>
@@ -6804,7 +6813,7 @@
         <v>13</v>
       </c>
       <c r="I42" s="8">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J42" s="8">
         <v>0</v>
@@ -6817,10 +6826,10 @@
       </c>
       <c r="M42" s="8">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N42" s="8">
-        <v>1300</v>
+        <v>1206</v>
       </c>
       <c r="O42" s="8"/>
       <c r="P42" s="8"/>
@@ -6855,7 +6864,7 @@
         <v>12</v>
       </c>
       <c r="I43" s="8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J43" s="8">
         <v>0</v>
@@ -6864,11 +6873,11 @@
         <v>0</v>
       </c>
       <c r="L43" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" s="8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N43" s="8">
         <v>0</v>
@@ -6906,7 +6915,7 @@
         <v>12</v>
       </c>
       <c r="I44" s="8">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J44" s="8">
         <v>0</v>
@@ -6915,14 +6924,14 @@
         <v>0</v>
       </c>
       <c r="L44" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M44" s="8">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N44" s="8">
-        <v>264</v>
+        <v>226</v>
       </c>
       <c r="O44" s="8"/>
       <c r="P44" s="8"/>
@@ -6973,7 +6982,7 @@
         <v>13</v>
       </c>
       <c r="N45" s="8">
-        <v>633</v>
+        <v>606</v>
       </c>
       <c r="O45" s="8"/>
       <c r="P45" s="8"/>
@@ -7008,7 +7017,7 @@
         <v>12</v>
       </c>
       <c r="I46" s="8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J46" s="8">
         <v>0</v>
@@ -7017,14 +7026,14 @@
         <v>0</v>
       </c>
       <c r="L46" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" s="8">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="N46" s="8">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="O46" s="8"/>
       <c r="P46" s="8"/>
@@ -7059,7 +7068,7 @@
         <v>13</v>
       </c>
       <c r="I47" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J47" s="8">
         <v>0</v>
@@ -7072,10 +7081,10 @@
       </c>
       <c r="M47" s="8">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N47" s="8">
-        <v>842</v>
+        <v>770</v>
       </c>
       <c r="O47" s="8"/>
       <c r="P47" s="8"/>
@@ -7116,17 +7125,17 @@
         <v>0</v>
       </c>
       <c r="K48" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="8">
         <v>0</v>
       </c>
       <c r="M48" s="8">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N48" s="8">
-        <v>1689</v>
+        <v>1592</v>
       </c>
       <c r="O48" s="8"/>
       <c r="P48" s="8"/>
@@ -7161,7 +7170,7 @@
         <v>12</v>
       </c>
       <c r="I49" s="8">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J49" s="8">
         <v>0</v>
@@ -7174,10 +7183,10 @@
       </c>
       <c r="M49" s="8">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N49" s="8">
-        <v>823</v>
+        <v>770</v>
       </c>
       <c r="O49" s="8"/>
       <c r="P49" s="8"/>
@@ -7228,7 +7237,7 @@
         <v>4</v>
       </c>
       <c r="N50" s="8">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="O50" s="8"/>
       <c r="P50" s="8"/>
@@ -7279,7 +7288,7 @@
         <v>24</v>
       </c>
       <c r="N51" s="8">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="O51" s="8"/>
       <c r="P51" s="8"/>
@@ -7314,7 +7323,7 @@
         <v>12</v>
       </c>
       <c r="I52" s="8">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="J52" s="8">
         <v>0</v>
@@ -7327,7 +7336,7 @@
       </c>
       <c r="M52" s="8">
         <f t="shared" si="0"/>
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="N52" s="8">
         <v>0</v>
@@ -7365,7 +7374,7 @@
         <v>12</v>
       </c>
       <c r="I53" s="8">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J53" s="8">
         <v>0</v>
@@ -7374,14 +7383,14 @@
         <v>0</v>
       </c>
       <c r="L53" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M53" s="8">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="N53" s="8">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="O53" s="8"/>
       <c r="P53" s="8"/>
@@ -7422,17 +7431,17 @@
         <v>0</v>
       </c>
       <c r="K54" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="8">
         <v>0</v>
       </c>
       <c r="M54" s="8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N54" s="8">
-        <v>483</v>
+        <v>441</v>
       </c>
       <c r="O54" s="8"/>
       <c r="P54" s="8"/>
@@ -7467,7 +7476,7 @@
         <v>12</v>
       </c>
       <c r="I55" s="8">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J55" s="8">
         <v>0</v>
@@ -7480,7 +7489,7 @@
       </c>
       <c r="M55" s="8">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="N55" s="8">
         <v>0</v>
@@ -7534,7 +7543,7 @@
         <v>4</v>
       </c>
       <c r="N56" s="8">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O56" s="8"/>
       <c r="P56" s="8"/>
@@ -7569,23 +7578,23 @@
         <v>12</v>
       </c>
       <c r="I57" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J57" s="8">
         <v>0</v>
       </c>
       <c r="K57" s="8">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="L57" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M57" s="8">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N57" s="8">
-        <v>127</v>
+        <v>55</v>
       </c>
       <c r="O57" s="8"/>
       <c r="P57" s="8"/>
@@ -7620,13 +7629,13 @@
         <v>12</v>
       </c>
       <c r="I58" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J58" s="8">
         <v>0</v>
       </c>
       <c r="K58" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="8">
         <v>0</v>
@@ -7636,7 +7645,7 @@
         <v>3</v>
       </c>
       <c r="N58" s="8">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="O58" s="8"/>
       <c r="P58" s="8"/>
@@ -7671,7 +7680,7 @@
         <v>13</v>
       </c>
       <c r="I59" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J59" s="8">
         <v>0</v>
@@ -7684,7 +7693,7 @@
       </c>
       <c r="M59" s="8">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N59" s="8">
         <v>0</v>
@@ -7722,7 +7731,7 @@
         <v>12</v>
       </c>
       <c r="I60" s="8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J60" s="8">
         <v>0</v>
@@ -7735,10 +7744,10 @@
       </c>
       <c r="M60" s="8">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N60" s="8">
-        <v>541</v>
+        <v>491</v>
       </c>
       <c r="O60" s="8"/>
       <c r="P60" s="8"/>
@@ -7773,7 +7782,7 @@
         <v>12</v>
       </c>
       <c r="I61" s="8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J61" s="8">
         <v>0</v>
@@ -7786,7 +7795,7 @@
       </c>
       <c r="M61" s="8">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N61" s="8">
         <v>0</v>
@@ -7824,7 +7833,7 @@
         <v>12</v>
       </c>
       <c r="I62" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J62" s="8">
         <v>0</v>
@@ -7837,10 +7846,10 @@
       </c>
       <c r="M62" s="8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N62" s="8">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="O62" s="8"/>
       <c r="P62" s="8"/>
@@ -7891,7 +7900,7 @@
         <v>4</v>
       </c>
       <c r="N63" s="8">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="O63" s="8"/>
       <c r="P63" s="8"/>
@@ -7926,7 +7935,7 @@
         <v>13</v>
       </c>
       <c r="I64" s="8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J64" s="8">
         <v>0</v>
@@ -7935,14 +7944,14 @@
         <v>1</v>
       </c>
       <c r="L64" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M64" s="8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N64" s="8">
-        <v>314</v>
+        <v>251</v>
       </c>
       <c r="O64" s="8"/>
       <c r="P64" s="8"/>
@@ -7983,17 +7992,17 @@
         <v>0</v>
       </c>
       <c r="K65" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" s="8">
         <v>0</v>
       </c>
       <c r="M65" s="8">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N65" s="8">
-        <v>876</v>
+        <v>861</v>
       </c>
       <c r="O65" s="8"/>
       <c r="P65" s="8"/>
@@ -8130,7 +8139,7 @@
         <v>12</v>
       </c>
       <c r="I68" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J68" s="8">
         <v>0</v>
@@ -8143,10 +8152,10 @@
       </c>
       <c r="M68" s="8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N68" s="8">
-        <v>907</v>
+        <v>891</v>
       </c>
       <c r="O68" s="8"/>
       <c r="P68" s="8"/>
@@ -8181,7 +8190,7 @@
         <v>12</v>
       </c>
       <c r="I69" s="8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J69" s="8">
         <v>0</v>
@@ -8194,10 +8203,10 @@
       </c>
       <c r="M69" s="8">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N69" s="8">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="O69" s="8"/>
       <c r="P69" s="8"/>
@@ -8232,7 +8241,7 @@
         <v>16</v>
       </c>
       <c r="I70" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J70" s="8">
         <v>0</v>
@@ -8241,14 +8250,14 @@
         <v>0</v>
       </c>
       <c r="L70" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70" s="8">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="N70" s="8">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="O70" s="8"/>
       <c r="P70" s="8"/>
@@ -8283,7 +8292,7 @@
         <v>12</v>
       </c>
       <c r="I71" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J71" s="8">
         <v>0</v>
@@ -8296,7 +8305,7 @@
       </c>
       <c r="M71" s="8">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N71" s="8">
         <v>0</v>
@@ -8350,7 +8359,7 @@
         <v>7</v>
       </c>
       <c r="N72" s="8">
-        <v>560</v>
+        <v>536</v>
       </c>
       <c r="O72" s="8"/>
       <c r="P72" s="8"/>
@@ -8391,17 +8400,17 @@
         <v>0</v>
       </c>
       <c r="K73" s="8">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L73" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M73" s="8">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N73" s="8">
-        <v>232</v>
+        <v>174</v>
       </c>
       <c r="O73" s="8"/>
       <c r="P73" s="8"/>
@@ -8442,17 +8451,17 @@
         <v>0</v>
       </c>
       <c r="K74" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L74" s="8">
         <v>0</v>
       </c>
       <c r="M74" s="8">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N74" s="8">
-        <v>164</v>
+        <v>137</v>
       </c>
       <c r="O74" s="8"/>
       <c r="P74" s="8"/>
@@ -8554,7 +8563,7 @@
         <v>3</v>
       </c>
       <c r="N76" s="8">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="O76" s="8"/>
       <c r="P76" s="8"/>
@@ -8589,7 +8598,7 @@
         <v>12</v>
       </c>
       <c r="I77" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J77" s="8">
         <v>0</v>
@@ -8602,10 +8611,10 @@
       </c>
       <c r="M77" s="8">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N77" s="8">
-        <v>603</v>
+        <v>507</v>
       </c>
       <c r="O77" s="8"/>
       <c r="P77" s="8"/>
@@ -8640,23 +8649,23 @@
         <v>12</v>
       </c>
       <c r="I78" s="8">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J78" s="8">
         <v>0</v>
       </c>
       <c r="K78" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L78" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M78" s="8">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N78" s="8">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="O78" s="8"/>
       <c r="P78" s="8"/>
@@ -8691,7 +8700,7 @@
         <v>13</v>
       </c>
       <c r="I79" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J79" s="8">
         <v>0</v>
@@ -8704,10 +8713,10 @@
       </c>
       <c r="M79" s="8">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N79" s="8">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O79" s="8"/>
       <c r="P79" s="8"/>
@@ -8742,7 +8751,7 @@
         <v>13</v>
       </c>
       <c r="I80" s="8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J80" s="8">
         <v>0</v>
@@ -8755,7 +8764,7 @@
       </c>
       <c r="M80" s="8">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N80" s="8">
         <v>0</v>
@@ -8860,7 +8869,7 @@
         <v>5</v>
       </c>
       <c r="N82" s="8">
-        <v>251</v>
+        <v>225</v>
       </c>
       <c r="O82" s="8"/>
       <c r="P82" s="8"/>
@@ -8911,7 +8920,7 @@
         <v>4</v>
       </c>
       <c r="N83" s="8">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="O83" s="8"/>
       <c r="P83" s="8"/>
@@ -8997,7 +9006,7 @@
         <v>14</v>
       </c>
       <c r="I85" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J85" s="8">
         <v>0</v>
@@ -9010,7 +9019,7 @@
       </c>
       <c r="M85" s="8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N85" s="8">
         <v>524</v>
@@ -9048,23 +9057,23 @@
         <v>12</v>
       </c>
       <c r="I86" s="8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J86" s="8">
         <v>0</v>
       </c>
       <c r="K86" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L86" s="8">
         <v>0</v>
       </c>
       <c r="M86" s="8">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N86" s="8">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="O86" s="8"/>
       <c r="P86" s="8"/>
@@ -9166,7 +9175,7 @@
         <v>12</v>
       </c>
       <c r="N88" s="8">
-        <v>326</v>
+        <v>260</v>
       </c>
       <c r="O88" s="8"/>
       <c r="P88" s="8"/>
@@ -9201,23 +9210,23 @@
         <v>12</v>
       </c>
       <c r="I89" s="8">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J89" s="8">
         <v>0</v>
       </c>
       <c r="K89" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L89" s="8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M89" s="8">
         <f t="shared" si="1"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N89" s="8">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O89" s="8"/>
       <c r="P89" s="8"/>
@@ -9303,7 +9312,7 @@
         <v>12</v>
       </c>
       <c r="I91" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J91" s="8">
         <v>0</v>
@@ -9316,10 +9325,10 @@
       </c>
       <c r="M91" s="8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N91" s="8">
-        <v>983</v>
+        <v>946</v>
       </c>
       <c r="O91" s="8"/>
       <c r="P91" s="8"/>
@@ -9370,7 +9379,7 @@
         <v>5</v>
       </c>
       <c r="N92" s="8">
-        <v>135</v>
+        <v>42</v>
       </c>
       <c r="O92" s="8"/>
       <c r="P92" s="8"/>
@@ -9405,20 +9414,20 @@
         <v>13</v>
       </c>
       <c r="I93" s="8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J93" s="8">
         <v>0</v>
       </c>
       <c r="K93" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L93" s="8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M93" s="8">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="N93" s="8">
         <v>0</v>
@@ -9523,7 +9532,7 @@
         <v>6</v>
       </c>
       <c r="N95" s="8">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="O95" s="8"/>
       <c r="P95" s="8"/>
@@ -9574,7 +9583,7 @@
         <v>7</v>
       </c>
       <c r="N96" s="8">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="O96" s="8"/>
       <c r="P96" s="8"/>
@@ -9609,23 +9618,23 @@
         <v>14</v>
       </c>
       <c r="I97" s="8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J97" s="8">
         <v>0</v>
       </c>
       <c r="K97" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L97" s="8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M97" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N97" s="8">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="O97" s="8"/>
       <c r="P97" s="8"/>
@@ -9660,7 +9669,7 @@
         <v>12</v>
       </c>
       <c r="I98" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J98" s="8">
         <v>0</v>
@@ -9673,7 +9682,7 @@
       </c>
       <c r="M98" s="8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N98" s="8">
         <v>0</v>
@@ -9762,7 +9771,7 @@
         <v>15</v>
       </c>
       <c r="I100" s="8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J100" s="8">
         <v>0</v>
@@ -9775,7 +9784,7 @@
       </c>
       <c r="M100" s="8">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N100" s="8">
         <v>0</v>
@@ -9829,7 +9838,7 @@
         <v>2</v>
       </c>
       <c r="N101" s="8">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="O101" s="8"/>
       <c r="P101" s="8"/>
@@ -9864,23 +9873,23 @@
         <v>14</v>
       </c>
       <c r="I102" s="8">
+        <v>0</v>
+      </c>
+      <c r="J102" s="8">
+        <v>0</v>
+      </c>
+      <c r="K102" s="8">
         <v>5</v>
       </c>
-      <c r="J102" s="8">
-        <v>0</v>
-      </c>
-      <c r="K102" s="8">
-        <v>0</v>
-      </c>
       <c r="L102" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M102" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N102" s="8">
-        <v>411</v>
+        <v>391</v>
       </c>
       <c r="O102" s="8"/>
       <c r="P102" s="8"/>
@@ -9915,23 +9924,23 @@
         <v>15</v>
       </c>
       <c r="I103" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J103" s="8">
         <v>0</v>
       </c>
       <c r="K103" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L103" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M103" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N103" s="8">
-        <v>358</v>
+        <v>340</v>
       </c>
       <c r="O103" s="8"/>
       <c r="P103" s="8"/>
@@ -10017,7 +10026,7 @@
         <v>12</v>
       </c>
       <c r="I105" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J105" s="8">
         <v>0</v>
@@ -10030,10 +10039,10 @@
       </c>
       <c r="M105" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N105" s="8">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="O105" s="8"/>
       <c r="P105" s="8"/>
@@ -10374,23 +10383,23 @@
         <v>12</v>
       </c>
       <c r="I112" s="8">
-        <v>152</v>
+        <v>219</v>
       </c>
       <c r="J112" s="8">
         <v>0</v>
       </c>
       <c r="K112" s="8">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L112" s="8">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="M112" s="8">
         <f t="shared" si="1"/>
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="N112" s="8">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="O112" s="8"/>
       <c r="P112" s="8"/>
@@ -10431,17 +10440,17 @@
         <v>0</v>
       </c>
       <c r="K113" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L113" s="8">
         <v>0</v>
       </c>
       <c r="M113" s="8">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N113" s="8">
-        <v>783</v>
+        <v>725</v>
       </c>
       <c r="O113" s="8"/>
       <c r="P113" s="8"/>
@@ -10476,7 +10485,7 @@
         <v>13</v>
       </c>
       <c r="I114" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J114" s="8">
         <v>0</v>
@@ -10489,10 +10498,10 @@
       </c>
       <c r="M114" s="8">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N114" s="8">
-        <v>593</v>
+        <v>486</v>
       </c>
       <c r="O114" s="8"/>
       <c r="P114" s="8"/>
@@ -10543,7 +10552,7 @@
         <v>9</v>
       </c>
       <c r="N115" s="8">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="O115" s="8"/>
       <c r="P115" s="8"/>
@@ -10594,7 +10603,7 @@
         <v>6</v>
       </c>
       <c r="N116" s="8">
-        <v>685</v>
+        <v>651</v>
       </c>
       <c r="O116" s="8"/>
       <c r="P116" s="8"/>
@@ -10629,23 +10638,23 @@
         <v>12</v>
       </c>
       <c r="I117" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J117" s="8">
         <v>0</v>
       </c>
       <c r="K117" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L117" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M117" s="8">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="N117" s="8">
-        <v>219</v>
+        <v>136</v>
       </c>
       <c r="O117" s="8"/>
       <c r="P117" s="8"/>
@@ -10696,7 +10705,7 @@
         <v>6</v>
       </c>
       <c r="N118" s="8">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="O118" s="8"/>
       <c r="P118" s="8"/>
@@ -10747,7 +10756,7 @@
         <v>7</v>
       </c>
       <c r="N119" s="8">
-        <v>494</v>
+        <v>467</v>
       </c>
       <c r="O119" s="8"/>
       <c r="P119" s="8"/>
@@ -10782,7 +10791,7 @@
         <v>14</v>
       </c>
       <c r="I120" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J120" s="8">
         <v>0</v>
@@ -10795,10 +10804,10 @@
       </c>
       <c r="M120" s="8">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N120" s="8">
-        <v>220</v>
+        <v>79</v>
       </c>
       <c r="O120" s="8"/>
       <c r="P120" s="8"/>
@@ -10833,7 +10842,7 @@
         <v>15</v>
       </c>
       <c r="I121" s="8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J121" s="8">
         <v>0</v>
@@ -10846,7 +10855,7 @@
       </c>
       <c r="M121" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N121" s="8">
         <v>0</v>
@@ -10900,7 +10909,7 @@
         <v>2</v>
       </c>
       <c r="N122" s="8">
-        <v>963</v>
+        <v>954</v>
       </c>
       <c r="O122" s="8"/>
       <c r="P122" s="8"/>
@@ -11053,7 +11062,7 @@
         <v>6</v>
       </c>
       <c r="N125" s="8">
-        <v>156</v>
+        <v>93</v>
       </c>
       <c r="O125" s="8"/>
       <c r="P125" s="8"/>
@@ -11206,7 +11215,7 @@
         <v>3</v>
       </c>
       <c r="N128" s="8">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="O128" s="8"/>
       <c r="P128" s="8"/>
@@ -11298,17 +11307,17 @@
         <v>0</v>
       </c>
       <c r="K130" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L130" s="8">
         <v>0</v>
       </c>
       <c r="M130" s="8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N130" s="8">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="O130" s="8"/>
       <c r="P130" s="8"/>
@@ -11343,7 +11352,7 @@
         <v>14</v>
       </c>
       <c r="I131" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J131" s="8">
         <v>0</v>
@@ -11356,10 +11365,10 @@
       </c>
       <c r="M131" s="8">
         <f t="shared" ref="M131:M194" si="2">I131+J131+K131+L131</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N131" s="8">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="O131" s="8"/>
       <c r="P131" s="8"/>
@@ -11394,7 +11403,7 @@
         <v>12</v>
       </c>
       <c r="I132" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J132" s="8">
         <v>0</v>
@@ -11403,14 +11412,14 @@
         <v>0</v>
       </c>
       <c r="L132" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M132" s="8">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="N132" s="8">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="O132" s="8"/>
       <c r="P132" s="8"/>
@@ -11445,7 +11454,7 @@
         <v>12</v>
       </c>
       <c r="I133" s="8">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J133" s="8">
         <v>0</v>
@@ -11458,10 +11467,10 @@
       </c>
       <c r="M133" s="8">
         <f t="shared" si="2"/>
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="N133" s="8">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="O133" s="8"/>
       <c r="P133" s="8"/>
@@ -11547,23 +11556,23 @@
         <v>15</v>
       </c>
       <c r="I135" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J135" s="8">
         <v>0</v>
       </c>
       <c r="K135" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L135" s="8">
         <v>0</v>
       </c>
       <c r="M135" s="8">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N135" s="8">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="O135" s="8"/>
       <c r="P135" s="8"/>
@@ -11598,23 +11607,23 @@
         <v>14</v>
       </c>
       <c r="I136" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J136" s="8">
         <v>0</v>
       </c>
       <c r="K136" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L136" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M136" s="8">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N136" s="8">
-        <v>398</v>
+        <v>363</v>
       </c>
       <c r="O136" s="8"/>
       <c r="P136" s="8"/>
@@ -11700,7 +11709,7 @@
         <v>12</v>
       </c>
       <c r="I138" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J138" s="8">
         <v>0</v>
@@ -11713,10 +11722,10 @@
       </c>
       <c r="M138" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N138" s="8">
-        <v>975</v>
+        <v>966</v>
       </c>
       <c r="O138" s="8"/>
       <c r="P138" s="8"/>
@@ -11808,17 +11817,17 @@
         <v>0</v>
       </c>
       <c r="K140" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L140" s="8">
         <v>0</v>
       </c>
       <c r="M140" s="8">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N140" s="8">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="O140" s="8"/>
       <c r="P140" s="8"/>
@@ -11862,14 +11871,14 @@
         <v>0</v>
       </c>
       <c r="L141" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M141" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N141" s="8">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O141" s="8"/>
       <c r="P141" s="8"/>
@@ -11964,14 +11973,14 @@
         <v>0</v>
       </c>
       <c r="L143" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M143" s="8">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N143" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O143" s="8"/>
       <c r="P143" s="8"/>
@@ -12073,7 +12082,7 @@
         <v>4</v>
       </c>
       <c r="N145" s="8">
-        <v>834</v>
+        <v>821</v>
       </c>
       <c r="O145" s="8"/>
       <c r="P145" s="8"/>
@@ -12108,7 +12117,7 @@
         <v>16</v>
       </c>
       <c r="I146" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J146" s="8">
         <v>0</v>
@@ -12121,7 +12130,7 @@
       </c>
       <c r="M146" s="8">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N146" s="8">
         <v>0</v>
@@ -12175,7 +12184,7 @@
         <v>2</v>
       </c>
       <c r="N147" s="8">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O147" s="8"/>
       <c r="P147" s="8"/>
@@ -12267,17 +12276,17 @@
         <v>0</v>
       </c>
       <c r="K149" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L149" s="8">
         <v>0</v>
       </c>
       <c r="M149" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N149" s="8">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="O149" s="8"/>
       <c r="P149" s="8"/>
@@ -12312,7 +12321,7 @@
         <v>12</v>
       </c>
       <c r="I150" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J150" s="8">
         <v>0</v>
@@ -12325,10 +12334,10 @@
       </c>
       <c r="M150" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N150" s="8">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="O150" s="8"/>
       <c r="P150" s="8"/>
@@ -12379,7 +12388,7 @@
         <v>3</v>
       </c>
       <c r="N151" s="8">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="O151" s="8"/>
       <c r="P151" s="8"/>
@@ -12430,7 +12439,7 @@
         <v>3</v>
       </c>
       <c r="N152" s="8">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O152" s="8"/>
       <c r="P152" s="8"/>
@@ -12465,7 +12474,7 @@
         <v>13</v>
       </c>
       <c r="I153" s="8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J153" s="8">
         <v>0</v>
@@ -12478,10 +12487,10 @@
       </c>
       <c r="M153" s="8">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N153" s="8">
-        <v>0</v>
+        <v>529</v>
       </c>
       <c r="O153" s="8"/>
       <c r="P153" s="8"/>
@@ -12532,7 +12541,7 @@
         <v>2</v>
       </c>
       <c r="N154" s="8">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="O154" s="8"/>
       <c r="P154" s="8"/>
@@ -12618,7 +12627,7 @@
         <v>15</v>
       </c>
       <c r="I156" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J156" s="8">
         <v>0</v>
@@ -12631,7 +12640,7 @@
       </c>
       <c r="M156" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N156" s="8">
         <v>0</v>
@@ -12780,11 +12789,11 @@
         <v>0</v>
       </c>
       <c r="L159" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M159" s="8">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N159" s="8">
         <v>0</v>
@@ -12873,7 +12882,7 @@
         <v>13</v>
       </c>
       <c r="I161" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J161" s="8">
         <v>0</v>
@@ -12886,10 +12895,10 @@
       </c>
       <c r="M161" s="8">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N161" s="8">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="O161" s="8"/>
       <c r="P161" s="8"/>
@@ -12924,7 +12933,7 @@
         <v>13</v>
       </c>
       <c r="I162" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J162" s="8">
         <v>0</v>
@@ -12933,14 +12942,14 @@
         <v>0</v>
       </c>
       <c r="L162" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M162" s="8">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="N162" s="8">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="O162" s="8"/>
       <c r="P162" s="8"/>
@@ -13042,7 +13051,7 @@
         <v>2</v>
       </c>
       <c r="N164" s="8">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="O164" s="8"/>
       <c r="P164" s="8"/>
@@ -13093,7 +13102,7 @@
         <v>10</v>
       </c>
       <c r="N165" s="8">
-        <v>1209</v>
+        <v>1157</v>
       </c>
       <c r="O165" s="8"/>
       <c r="P165" s="8"/>
@@ -13239,14 +13248,14 @@
         <v>1</v>
       </c>
       <c r="L168" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M168" s="8">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N168" s="8">
-        <v>206</v>
+        <v>177</v>
       </c>
       <c r="O168" s="8"/>
       <c r="P168" s="8"/>
@@ -13281,7 +13290,7 @@
         <v>16</v>
       </c>
       <c r="I169" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J169" s="8">
         <v>0</v>
@@ -13294,7 +13303,7 @@
       </c>
       <c r="M169" s="8">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N169" s="8">
         <v>0</v>
@@ -13348,7 +13357,7 @@
         <v>2</v>
       </c>
       <c r="N170" s="8">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="O170" s="8"/>
       <c r="P170" s="8"/>
@@ -13501,7 +13510,7 @@
         <v>2</v>
       </c>
       <c r="N173" s="8">
-        <v>599</v>
+        <v>552</v>
       </c>
       <c r="O173" s="8"/>
       <c r="P173" s="8"/>
@@ -13654,7 +13663,7 @@
         <v>2</v>
       </c>
       <c r="N176" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O176" s="8"/>
       <c r="P176" s="8"/>
@@ -13807,7 +13816,7 @@
         <v>2</v>
       </c>
       <c r="N179" s="8">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="O179" s="8"/>
       <c r="P179" s="8"/>
@@ -13842,7 +13851,7 @@
         <v>13</v>
       </c>
       <c r="I180" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J180" s="8">
         <v>0</v>
@@ -13855,10 +13864,10 @@
       </c>
       <c r="M180" s="8">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N180" s="8">
-        <v>467</v>
+        <v>439</v>
       </c>
       <c r="O180" s="8"/>
       <c r="P180" s="8"/>
@@ -13909,7 +13918,7 @@
         <v>3</v>
       </c>
       <c r="N181" s="8">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="O181" s="8"/>
       <c r="P181" s="8"/>
@@ -14011,7 +14020,7 @@
         <v>6</v>
       </c>
       <c r="N183" s="8">
-        <v>300</v>
+        <v>395</v>
       </c>
       <c r="O183" s="8"/>
       <c r="P183" s="8"/>
@@ -14097,23 +14106,23 @@
         <v>12</v>
       </c>
       <c r="I185" s="8">
-        <v>405</v>
+        <v>448</v>
       </c>
       <c r="J185" s="8">
         <v>0</v>
       </c>
       <c r="K185" s="8">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="L185" s="8">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="M185" s="8">
         <f t="shared" si="2"/>
-        <v>504</v>
+        <v>482</v>
       </c>
       <c r="N185" s="8">
-        <v>1743</v>
+        <v>1659</v>
       </c>
       <c r="O185" s="8"/>
       <c r="P185" s="8"/>
@@ -14164,7 +14173,7 @@
         <v>7</v>
       </c>
       <c r="N186" s="8">
-        <v>841</v>
+        <v>797</v>
       </c>
       <c r="O186" s="8"/>
       <c r="P186" s="8"/>
@@ -14199,7 +14208,7 @@
         <v>14</v>
       </c>
       <c r="I187" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J187" s="8">
         <v>0</v>
@@ -14212,10 +14221,10 @@
       </c>
       <c r="M187" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N187" s="8">
-        <v>36</v>
+        <v>135</v>
       </c>
       <c r="O187" s="8"/>
       <c r="P187" s="8"/>
@@ -14266,7 +14275,7 @@
         <v>5</v>
       </c>
       <c r="N188" s="8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O188" s="8"/>
       <c r="P188" s="8"/>
@@ -14368,7 +14377,7 @@
         <v>17</v>
       </c>
       <c r="N190" s="8">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="O190" s="8"/>
       <c r="P190" s="8"/>
@@ -14403,7 +14412,7 @@
         <v>12</v>
       </c>
       <c r="I191" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J191" s="8">
         <v>0</v>
@@ -14416,10 +14425,10 @@
       </c>
       <c r="M191" s="8">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N191" s="8">
-        <v>736</v>
+        <v>683</v>
       </c>
       <c r="O191" s="8"/>
       <c r="P191" s="8"/>
@@ -14562,17 +14571,17 @@
         <v>0</v>
       </c>
       <c r="K194" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L194" s="8">
         <v>0</v>
       </c>
       <c r="M194" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N194" s="8">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="O194" s="8"/>
       <c r="P194" s="8"/>
@@ -14709,7 +14718,7 @@
         <v>12</v>
       </c>
       <c r="I197" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J197" s="8">
         <v>0</v>
@@ -14722,10 +14731,10 @@
       </c>
       <c r="M197" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N197" s="8">
-        <v>509</v>
+        <v>445</v>
       </c>
       <c r="O197" s="8"/>
       <c r="P197" s="8"/>
@@ -15219,7 +15228,7 @@
         <v>14</v>
       </c>
       <c r="I207" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J207" s="8">
         <v>0</v>
@@ -15232,10 +15241,10 @@
       </c>
       <c r="M207" s="8">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N207" s="8">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="O207" s="8"/>
       <c r="P207" s="8"/>
@@ -15270,7 +15279,7 @@
         <v>14</v>
       </c>
       <c r="I208" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J208" s="8">
         <v>0</v>
@@ -15283,7 +15292,7 @@
       </c>
       <c r="M208" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N208" s="8">
         <v>19</v>
@@ -15327,17 +15336,17 @@
         <v>0</v>
       </c>
       <c r="K209" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L209" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M209" s="8">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="N209" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O209" s="8"/>
       <c r="P209" s="8"/>
@@ -15423,7 +15432,7 @@
         <v>12</v>
       </c>
       <c r="I211" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J211" s="8">
         <v>0</v>
@@ -15432,14 +15441,14 @@
         <v>0</v>
       </c>
       <c r="L211" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M211" s="8">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="N211" s="8">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="O211" s="8"/>
       <c r="P211" s="8"/>
@@ -15582,17 +15591,17 @@
         <v>0</v>
       </c>
       <c r="K214" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L214" s="8">
         <v>0</v>
       </c>
       <c r="M214" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N214" s="8">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="O214" s="8"/>
       <c r="P214" s="8"/>
@@ -15643,7 +15652,7 @@
         <v>3</v>
       </c>
       <c r="N215" s="8">
-        <v>649</v>
+        <v>638</v>
       </c>
       <c r="O215" s="8"/>
       <c r="P215" s="8"/>
@@ -15678,7 +15687,7 @@
         <v>14</v>
       </c>
       <c r="I216" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J216" s="8">
         <v>0</v>
@@ -15691,7 +15700,7 @@
       </c>
       <c r="M216" s="8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N216" s="8">
         <v>0</v>
@@ -15780,7 +15789,7 @@
         <v>13</v>
       </c>
       <c r="I218" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J218" s="8">
         <v>0</v>
@@ -15793,7 +15802,7 @@
       </c>
       <c r="M218" s="8">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N218" s="8">
         <v>239</v>
@@ -15831,7 +15840,7 @@
         <v>13</v>
       </c>
       <c r="I219" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J219" s="8">
         <v>0</v>
@@ -15844,10 +15853,10 @@
       </c>
       <c r="M219" s="8">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N219" s="8">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="O219" s="8"/>
       <c r="P219" s="8"/>
@@ -15990,10 +15999,10 @@
         <v>0</v>
       </c>
       <c r="K222" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L222" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M222" s="8">
         <f t="shared" si="3"/>
@@ -16035,23 +16044,23 @@
         <v>15</v>
       </c>
       <c r="I223" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J223" s="8">
         <v>0</v>
       </c>
       <c r="K223" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L223" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M223" s="8">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="N223" s="8">
-        <v>151</v>
+        <v>122</v>
       </c>
       <c r="O223" s="8"/>
       <c r="P223" s="8"/>
@@ -16086,7 +16095,7 @@
         <v>13</v>
       </c>
       <c r="I224" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J224" s="8">
         <v>0</v>
@@ -16099,7 +16108,7 @@
       </c>
       <c r="M224" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N224" s="8">
         <v>175</v>
@@ -16153,7 +16162,7 @@
         <v>3</v>
       </c>
       <c r="N225" s="8">
-        <v>518</v>
+        <v>477</v>
       </c>
       <c r="O225" s="8"/>
       <c r="P225" s="8"/>
@@ -16204,7 +16213,7 @@
         <v>0</v>
       </c>
       <c r="N226" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O226" s="8"/>
       <c r="P226" s="8"/>
@@ -16306,7 +16315,7 @@
         <v>2</v>
       </c>
       <c r="N228" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O228" s="8"/>
       <c r="P228" s="8"/>
@@ -16347,17 +16356,17 @@
         <v>0</v>
       </c>
       <c r="K229" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L229" s="8">
         <v>0</v>
       </c>
       <c r="M229" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N229" s="8">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O229" s="8"/>
       <c r="P229" s="8"/>
@@ -16408,7 +16417,7 @@
         <v>3</v>
       </c>
       <c r="N230" s="8">
-        <v>337</v>
+        <v>139</v>
       </c>
       <c r="O230" s="8"/>
       <c r="P230" s="8"/>
@@ -16494,7 +16503,7 @@
         <v>12</v>
       </c>
       <c r="I232" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J232" s="8">
         <v>0</v>
@@ -16507,10 +16516,10 @@
       </c>
       <c r="M232" s="8">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N232" s="8">
-        <v>452</v>
+        <v>401</v>
       </c>
       <c r="O232" s="8"/>
       <c r="P232" s="8"/>
@@ -16545,23 +16554,23 @@
         <v>15</v>
       </c>
       <c r="I233" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J233" s="8">
         <v>0</v>
       </c>
       <c r="K233" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L233" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M233" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N233" s="8">
-        <v>562</v>
+        <v>524</v>
       </c>
       <c r="O233" s="8"/>
       <c r="P233" s="8"/>
@@ -16612,7 +16621,7 @@
         <v>2</v>
       </c>
       <c r="N234" s="8">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O234" s="8"/>
       <c r="P234" s="8"/>
@@ -16647,7 +16656,7 @@
         <v>14</v>
       </c>
       <c r="I235" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J235" s="8">
         <v>0</v>
@@ -16660,7 +16669,7 @@
       </c>
       <c r="M235" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N235" s="8">
         <v>0</v>
@@ -16749,7 +16758,7 @@
         <v>12</v>
       </c>
       <c r="I237" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J237" s="8">
         <v>0</v>
@@ -16762,10 +16771,10 @@
       </c>
       <c r="M237" s="8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N237" s="8">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="O237" s="8"/>
       <c r="P237" s="8"/>
@@ -16816,7 +16825,7 @@
         <v>5</v>
       </c>
       <c r="N238" s="8">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="O238" s="8"/>
       <c r="P238" s="8"/>
@@ -16867,7 +16876,7 @@
         <v>3</v>
       </c>
       <c r="N239" s="8">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="O239" s="8"/>
       <c r="P239" s="8"/>
@@ -16902,23 +16911,23 @@
         <v>13</v>
       </c>
       <c r="I240" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J240" s="8">
         <v>0</v>
       </c>
       <c r="K240" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L240" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M240" s="8">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="N240" s="8">
-        <v>330</v>
+        <v>306</v>
       </c>
       <c r="O240" s="8"/>
       <c r="P240" s="8"/>
@@ -16969,7 +16978,7 @@
         <v>3</v>
       </c>
       <c r="N241" s="8">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="O241" s="8"/>
       <c r="P241" s="8"/>
@@ -17020,7 +17029,7 @@
         <v>3</v>
       </c>
       <c r="N242" s="8">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="O242" s="8"/>
       <c r="P242" s="8"/>
@@ -17055,23 +17064,23 @@
         <v>15</v>
       </c>
       <c r="I243" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J243" s="8">
         <v>0</v>
       </c>
       <c r="K243" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L243" s="8">
         <v>0</v>
       </c>
       <c r="M243" s="8">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N243" s="8">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="O243" s="8"/>
       <c r="P243" s="8"/>
@@ -17157,7 +17166,7 @@
         <v>15</v>
       </c>
       <c r="I245" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J245" s="8">
         <v>0</v>
@@ -17170,7 +17179,7 @@
       </c>
       <c r="M245" s="8">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N245" s="8">
         <v>0</v>
@@ -17224,7 +17233,7 @@
         <v>3</v>
       </c>
       <c r="N246" s="8">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="O246" s="8"/>
       <c r="P246" s="8"/>
@@ -17265,17 +17274,17 @@
         <v>0</v>
       </c>
       <c r="K247" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L247" s="8">
         <v>0</v>
       </c>
       <c r="M247" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N247" s="8">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="O247" s="8"/>
       <c r="P247" s="8"/>
@@ -17310,7 +17319,7 @@
         <v>12</v>
       </c>
       <c r="I248" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J248" s="8">
         <v>0</v>
@@ -17323,7 +17332,7 @@
       </c>
       <c r="M248" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N248" s="8">
         <v>0</v>
@@ -17428,7 +17437,7 @@
         <v>3</v>
       </c>
       <c r="N250" s="8">
-        <v>1394</v>
+        <v>1384</v>
       </c>
       <c r="O250" s="8"/>
       <c r="P250" s="8"/>
@@ -17479,7 +17488,7 @@
         <v>2</v>
       </c>
       <c r="N251" s="8">
-        <v>1218</v>
+        <v>1212</v>
       </c>
       <c r="O251" s="8"/>
       <c r="P251" s="8"/>
@@ -17581,7 +17590,7 @@
         <v>2</v>
       </c>
       <c r="N253" s="8">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="O253" s="8"/>
       <c r="P253" s="8"/>
@@ -17718,7 +17727,7 @@
         <v>14</v>
       </c>
       <c r="I256" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J256" s="8">
         <v>0</v>
@@ -17727,14 +17736,14 @@
         <v>0</v>
       </c>
       <c r="L256" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M256" s="8">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="N256" s="8">
-        <v>1037</v>
+        <v>1031</v>
       </c>
       <c r="O256" s="8"/>
       <c r="P256" s="8"/>
@@ -17785,7 +17794,7 @@
         <v>4</v>
       </c>
       <c r="N257" s="8">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="O257" s="8"/>
       <c r="P257" s="8"/>
@@ -17826,17 +17835,17 @@
         <v>0</v>
       </c>
       <c r="K258" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L258" s="8">
         <v>0</v>
       </c>
       <c r="M258" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N258" s="8">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O258" s="8"/>
       <c r="P258" s="8"/>
@@ -17887,7 +17896,7 @@
         <v>3</v>
       </c>
       <c r="N259" s="8">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="O259" s="8"/>
       <c r="P259" s="8"/>
@@ -17928,17 +17937,17 @@
         <v>0</v>
       </c>
       <c r="K260" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L260" s="8">
         <v>0</v>
       </c>
       <c r="M260" s="8">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N260" s="8">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="O260" s="8"/>
       <c r="P260" s="8"/>
@@ -17973,7 +17982,7 @@
         <v>12</v>
       </c>
       <c r="I261" s="8">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J261" s="8">
         <v>0</v>
@@ -17986,10 +17995,10 @@
       </c>
       <c r="M261" s="8">
         <f t="shared" si="4"/>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N261" s="8">
-        <v>694</v>
+        <v>558</v>
       </c>
       <c r="O261" s="8"/>
       <c r="P261" s="8"/>
@@ -18033,14 +18042,14 @@
         <v>0</v>
       </c>
       <c r="L262" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M262" s="8">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N262" s="8">
-        <v>255</v>
+        <v>195</v>
       </c>
       <c r="O262" s="8"/>
       <c r="P262" s="8"/>
@@ -18075,20 +18084,20 @@
         <v>12</v>
       </c>
       <c r="I263" s="8">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J263" s="8">
         <v>0</v>
       </c>
       <c r="K263" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L263" s="8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M263" s="8">
         <f t="shared" si="4"/>
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="N263" s="8">
         <v>0</v>
@@ -18142,7 +18151,7 @@
         <v>2</v>
       </c>
       <c r="N264" s="8">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="O264" s="8"/>
       <c r="P264" s="8"/>
@@ -18177,7 +18186,7 @@
         <v>14</v>
       </c>
       <c r="I265" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J265" s="8">
         <v>0</v>
@@ -18190,7 +18199,7 @@
       </c>
       <c r="M265" s="8">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N265" s="8">
         <v>40</v>
@@ -18244,7 +18253,7 @@
         <v>3</v>
       </c>
       <c r="N266" s="8">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="O266" s="8"/>
       <c r="P266" s="8"/>
@@ -18483,7 +18492,7 @@
         <v>16</v>
       </c>
       <c r="I271" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J271" s="8">
         <v>0</v>
@@ -18496,7 +18505,7 @@
       </c>
       <c r="M271" s="8">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N271" s="8">
         <v>0</v>
@@ -18642,17 +18651,17 @@
         <v>0</v>
       </c>
       <c r="K274" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L274" s="8">
         <v>0</v>
       </c>
       <c r="M274" s="8">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N274" s="8">
-        <v>487</v>
+        <v>472</v>
       </c>
       <c r="O274" s="8"/>
       <c r="P274" s="8"/>
@@ -18687,7 +18696,7 @@
         <v>15</v>
       </c>
       <c r="I275" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J275" s="8">
         <v>0</v>
@@ -18700,10 +18709,10 @@
       </c>
       <c r="M275" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N275" s="8">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O275" s="8"/>
       <c r="P275" s="8"/>
@@ -18754,7 +18763,7 @@
         <v>3</v>
       </c>
       <c r="N276" s="8">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="O276" s="8"/>
       <c r="P276" s="8"/>
@@ -18846,17 +18855,17 @@
         <v>0</v>
       </c>
       <c r="K278" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L278" s="8">
         <v>0</v>
       </c>
       <c r="M278" s="8">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N278" s="8">
-        <v>1260</v>
+        <v>1310</v>
       </c>
       <c r="O278" s="8"/>
       <c r="P278" s="8"/>
@@ -19095,7 +19104,7 @@
         <v>12</v>
       </c>
       <c r="I283" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J283" s="8">
         <v>0</v>
@@ -19104,11 +19113,11 @@
         <v>0</v>
       </c>
       <c r="L283" s="8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M283" s="8">
         <f t="shared" si="4"/>
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="N283" s="8">
         <v>0</v>
@@ -19146,7 +19155,7 @@
         <v>12</v>
       </c>
       <c r="I284" s="8">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="J284" s="8">
         <v>0</v>
@@ -19159,7 +19168,7 @@
       </c>
       <c r="M284" s="8">
         <f t="shared" si="4"/>
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="N284" s="8">
         <v>0</v>
@@ -19197,7 +19206,7 @@
         <v>13</v>
       </c>
       <c r="I285" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J285" s="8">
         <v>0</v>
@@ -19210,10 +19219,10 @@
       </c>
       <c r="M285" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N285" s="8">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O285" s="8"/>
       <c r="P285" s="8"/>
@@ -19264,7 +19273,7 @@
         <v>4</v>
       </c>
       <c r="N286" s="8">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="O286" s="8"/>
       <c r="P286" s="8"/>
@@ -19315,7 +19324,7 @@
         <v>9</v>
       </c>
       <c r="N287" s="8">
-        <v>1114</v>
+        <v>1110</v>
       </c>
       <c r="O287" s="8"/>
       <c r="P287" s="8"/>
@@ -19366,7 +19375,7 @@
         <v>4</v>
       </c>
       <c r="N288" s="8">
-        <v>1444</v>
+        <v>1397</v>
       </c>
       <c r="O288" s="8"/>
       <c r="P288" s="8"/>
@@ -19452,7 +19461,7 @@
         <v>14</v>
       </c>
       <c r="I290" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J290" s="8">
         <v>0</v>
@@ -19465,7 +19474,7 @@
       </c>
       <c r="M290" s="8">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N290" s="8">
         <v>0</v>
@@ -19503,23 +19512,23 @@
         <v>12</v>
       </c>
       <c r="I291" s="8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J291" s="8">
         <v>0</v>
       </c>
       <c r="K291" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L291" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M291" s="8">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N291" s="8">
-        <v>1686</v>
+        <v>1565</v>
       </c>
       <c r="O291" s="8"/>
       <c r="P291" s="8"/>
@@ -19554,7 +19563,7 @@
         <v>16</v>
       </c>
       <c r="I292" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J292" s="8">
         <v>0</v>
@@ -19567,7 +19576,7 @@
       </c>
       <c r="M292" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N292" s="8">
         <v>201</v>
@@ -19656,23 +19665,23 @@
         <v>12</v>
       </c>
       <c r="I294" s="8">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J294" s="8">
         <v>0</v>
       </c>
       <c r="K294" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L294" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M294" s="8">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N294" s="8">
-        <v>1385</v>
+        <v>1349</v>
       </c>
       <c r="O294" s="8"/>
       <c r="P294" s="8"/>
@@ -19962,7 +19971,7 @@
         <v>13</v>
       </c>
       <c r="I300" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J300" s="8">
         <v>0</v>
@@ -19975,7 +19984,7 @@
       </c>
       <c r="M300" s="8">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N300" s="8">
         <v>0</v>
@@ -20029,7 +20038,7 @@
         <v>6</v>
       </c>
       <c r="N301" s="8">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O301" s="8"/>
       <c r="P301" s="8"/>
@@ -20080,7 +20089,7 @@
         <v>5</v>
       </c>
       <c r="N302" s="8">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="O302" s="8"/>
       <c r="P302" s="8"/>
@@ -20233,7 +20242,7 @@
         <v>8</v>
       </c>
       <c r="N305" s="8">
-        <v>498</v>
+        <v>483</v>
       </c>
       <c r="O305" s="8"/>
       <c r="P305" s="8"/>
@@ -20284,7 +20293,7 @@
         <v>9</v>
       </c>
       <c r="N306" s="8">
-        <v>1026</v>
+        <v>1004</v>
       </c>
       <c r="O306" s="8"/>
       <c r="P306" s="8"/>
@@ -20335,7 +20344,7 @@
         <v>11</v>
       </c>
       <c r="N307" s="8">
-        <v>1011</v>
+        <v>997</v>
       </c>
       <c r="O307" s="8"/>
       <c r="P307" s="8"/>
@@ -20370,7 +20379,7 @@
         <v>13</v>
       </c>
       <c r="I308" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J308" s="8">
         <v>0</v>
@@ -20383,10 +20392,10 @@
       </c>
       <c r="M308" s="8">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N308" s="8">
-        <v>951</v>
+        <v>917</v>
       </c>
       <c r="O308" s="8"/>
       <c r="P308" s="8"/>
@@ -20539,7 +20548,7 @@
         <v>2</v>
       </c>
       <c r="N311" s="8">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O311" s="8"/>
       <c r="P311" s="8"/>
@@ -20590,7 +20599,7 @@
         <v>6</v>
       </c>
       <c r="N312" s="8">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="O312" s="8"/>
       <c r="P312" s="8"/>
@@ -20641,7 +20650,7 @@
         <v>3</v>
       </c>
       <c r="N313" s="8">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="O313" s="8"/>
       <c r="P313" s="8"/>
@@ -20676,23 +20685,23 @@
         <v>12</v>
       </c>
       <c r="I314" s="8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J314" s="8">
         <v>0</v>
       </c>
       <c r="K314" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L314" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M314" s="8">
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
       <c r="N314" s="8">
-        <v>395</v>
+        <v>381</v>
       </c>
       <c r="O314" s="8"/>
       <c r="P314" s="8"/>
@@ -20743,7 +20752,7 @@
         <v>8</v>
       </c>
       <c r="N315" s="8">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="O315" s="8"/>
       <c r="P315" s="8"/>
@@ -20794,7 +20803,7 @@
         <v>6</v>
       </c>
       <c r="N316" s="8">
-        <v>689</v>
+        <v>673</v>
       </c>
       <c r="O316" s="8"/>
       <c r="P316" s="8"/>
@@ -20835,17 +20844,17 @@
         <v>0</v>
       </c>
       <c r="K317" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L317" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M317" s="8">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N317" s="8">
-        <v>270</v>
+        <v>247</v>
       </c>
       <c r="O317" s="8"/>
       <c r="P317" s="8"/>
@@ -20880,23 +20889,23 @@
         <v>12</v>
       </c>
       <c r="I318" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J318" s="8">
         <v>0</v>
       </c>
       <c r="K318" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L318" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M318" s="8">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="N318" s="8">
-        <v>678</v>
+        <v>536</v>
       </c>
       <c r="O318" s="8"/>
       <c r="P318" s="8"/>
@@ -20947,7 +20956,7 @@
         <v>4</v>
       </c>
       <c r="N319" s="8">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="O319" s="8"/>
       <c r="P319" s="8"/>
@@ -20998,7 +21007,7 @@
         <v>4</v>
       </c>
       <c r="N320" s="8">
-        <v>677</v>
+        <v>663</v>
       </c>
       <c r="O320" s="8"/>
       <c r="P320" s="8"/>
@@ -21033,7 +21042,7 @@
         <v>14</v>
       </c>
       <c r="I321" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J321" s="8">
         <v>0</v>
@@ -21042,14 +21051,14 @@
         <v>0</v>
       </c>
       <c r="L321" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M321" s="8">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="N321" s="8">
-        <v>558</v>
+        <v>539</v>
       </c>
       <c r="O321" s="8"/>
       <c r="P321" s="8"/>
@@ -21100,7 +21109,7 @@
         <v>3</v>
       </c>
       <c r="N322" s="8">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="O322" s="8"/>
       <c r="P322" s="8"/>
@@ -21253,7 +21262,7 @@
         <v>3</v>
       </c>
       <c r="N325" s="8">
-        <v>449</v>
+        <v>423</v>
       </c>
       <c r="O325" s="8"/>
       <c r="P325" s="8"/>
@@ -21304,7 +21313,7 @@
         <v>3</v>
       </c>
       <c r="N326" s="8">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="O326" s="8"/>
       <c r="P326" s="8"/>
@@ -21355,7 +21364,7 @@
         <v>2</v>
       </c>
       <c r="N327" s="8">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O327" s="8"/>
       <c r="P327" s="8"/>
@@ -21406,7 +21415,7 @@
         <v>2</v>
       </c>
       <c r="N328" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O328" s="8"/>
       <c r="P328" s="8"/>
@@ -21457,7 +21466,7 @@
         <v>4</v>
       </c>
       <c r="N329" s="8">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="O329" s="8"/>
       <c r="P329" s="8"/>
@@ -21508,7 +21517,7 @@
         <v>2</v>
       </c>
       <c r="N330" s="8">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O330" s="8"/>
       <c r="P330" s="8"/>
@@ -21661,7 +21670,7 @@
         <v>3</v>
       </c>
       <c r="N333" s="8">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="O333" s="8"/>
       <c r="P333" s="8"/>
@@ -21712,7 +21721,7 @@
         <v>4</v>
       </c>
       <c r="N334" s="8">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="O334" s="8"/>
       <c r="P334" s="8"/>
@@ -21763,7 +21772,7 @@
         <v>2</v>
       </c>
       <c r="N335" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O335" s="8"/>
       <c r="P335" s="8"/>
@@ -21814,7 +21823,7 @@
         <v>4</v>
       </c>
       <c r="N336" s="8">
-        <v>598</v>
+        <v>567</v>
       </c>
       <c r="O336" s="8"/>
       <c r="P336" s="8"/>
@@ -21849,13 +21858,13 @@
         <v>12</v>
       </c>
       <c r="I337" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J337" s="8">
         <v>0</v>
       </c>
       <c r="K337" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L337" s="8">
         <v>0</v>
@@ -21865,7 +21874,7 @@
         <v>11</v>
       </c>
       <c r="N337" s="8">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="O337" s="8"/>
       <c r="P337" s="8"/>
@@ -21900,23 +21909,23 @@
         <v>12</v>
       </c>
       <c r="I338" s="8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J338" s="8">
         <v>0</v>
       </c>
       <c r="K338" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L338" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M338" s="8">
         <f t="shared" si="5"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N338" s="8">
-        <v>1227</v>
+        <v>1208</v>
       </c>
       <c r="O338" s="8"/>
       <c r="P338" s="8"/>
@@ -21967,7 +21976,7 @@
         <v>3</v>
       </c>
       <c r="N339" s="8">
-        <v>851</v>
+        <v>840</v>
       </c>
       <c r="O339" s="8"/>
       <c r="P339" s="8"/>
@@ -22008,17 +22017,17 @@
         <v>0</v>
       </c>
       <c r="K340" s="8">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L340" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M340" s="8">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N340" s="8">
-        <v>743</v>
+        <v>692</v>
       </c>
       <c r="O340" s="8"/>
       <c r="P340" s="8"/>
@@ -22069,7 +22078,7 @@
         <v>3</v>
       </c>
       <c r="N341" s="8">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="O341" s="8"/>
       <c r="P341" s="8"/>
@@ -22206,7 +22215,7 @@
         <v>12</v>
       </c>
       <c r="I344" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J344" s="8">
         <v>0</v>
@@ -22219,7 +22228,7 @@
       </c>
       <c r="M344" s="8">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N344" s="8">
         <v>0</v>
@@ -22359,23 +22368,23 @@
         <v>13</v>
       </c>
       <c r="I347" s="8">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J347" s="8">
         <v>0</v>
       </c>
       <c r="K347" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L347" s="8">
         <v>0</v>
       </c>
       <c r="M347" s="8">
         <f t="shared" si="5"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N347" s="8">
-        <v>523</v>
+        <v>483</v>
       </c>
       <c r="O347" s="8"/>
       <c r="P347" s="9"/>
@@ -22614,7 +22623,7 @@
         <v>14</v>
       </c>
       <c r="I352" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J352" s="8">
         <v>0</v>
@@ -22627,10 +22636,10 @@
       </c>
       <c r="M352" s="8">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N352" s="8">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="O352" s="8"/>
       <c r="P352" s="9"/>
@@ -22767,23 +22776,23 @@
         <v>16</v>
       </c>
       <c r="I355" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J355" s="8">
         <v>0</v>
       </c>
       <c r="K355" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L355" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M355" s="8">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N355" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O355" s="8"/>
       <c r="P355" s="9"/>
@@ -23175,7 +23184,7 @@
         <v>12</v>
       </c>
       <c r="I363" s="8">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="J363" s="8">
         <v>0</v>
@@ -23188,7 +23197,7 @@
       </c>
       <c r="M363" s="8">
         <f t="shared" si="5"/>
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="N363" s="8">
         <v>1318</v>
@@ -23379,7 +23388,7 @@
         <v>12</v>
       </c>
       <c r="I367" s="8">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J367" s="8">
         <v>0</v>
@@ -23392,7 +23401,7 @@
       </c>
       <c r="M367" s="8">
         <f t="shared" si="5"/>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="N367" s="8">
         <v>0</v>
@@ -23430,23 +23439,23 @@
         <v>12</v>
       </c>
       <c r="I368" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J368" s="8">
         <v>0</v>
       </c>
       <c r="K368" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L368" s="8">
         <v>0</v>
       </c>
       <c r="M368" s="8">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N368" s="8">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O368" s="8"/>
       <c r="P368" s="9"/>
@@ -23599,7 +23608,7 @@
         <v>3</v>
       </c>
       <c r="N371" s="8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O371" s="8"/>
       <c r="P371" s="9"/>
@@ -24144,7 +24153,7 @@
         <v>13</v>
       </c>
       <c r="I382" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J382" s="8">
         <v>0</v>
@@ -24157,7 +24166,7 @@
       </c>
       <c r="M382" s="8">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N382" s="8">
         <v>0</v>
@@ -24246,7 +24255,7 @@
         <v>12</v>
       </c>
       <c r="I384" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J384" s="8">
         <v>0</v>
@@ -24255,14 +24264,14 @@
         <v>0</v>
       </c>
       <c r="L384" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M384" s="8">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N384" s="8">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="O384" s="8"/>
       <c r="P384" s="9"/>
@@ -24297,7 +24306,7 @@
         <v>12</v>
       </c>
       <c r="I385" s="8">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="J385" s="8">
         <v>0</v>
@@ -24310,7 +24319,7 @@
       </c>
       <c r="M385" s="8">
         <f t="shared" si="5"/>
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="N385" s="8">
         <v>257</v>
@@ -24552,7 +24561,7 @@
         <v>12</v>
       </c>
       <c r="I390" s="8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J390" s="8">
         <v>0</v>
@@ -24561,14 +24570,14 @@
         <v>0</v>
       </c>
       <c r="L390" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M390" s="8">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
       <c r="N390" s="8">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="O390" s="8"/>
       <c r="P390" s="7"/>
@@ -24976,7 +24985,7 @@
         <v>1</v>
       </c>
       <c r="N398" s="8">
-        <v>0</v>
+        <v>567</v>
       </c>
       <c r="O398" s="7"/>
       <c r="P398" s="7"/>
@@ -25282,7 +25291,7 @@
         <v>2</v>
       </c>
       <c r="N404" s="8">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="O404" s="7"/>
       <c r="P404" s="7"/>
@@ -25333,7 +25342,7 @@
         <v>2</v>
       </c>
       <c r="N405" s="8">
-        <v>409</v>
+        <v>396</v>
       </c>
       <c r="O405" s="7"/>
       <c r="P405" s="7"/>
@@ -25486,7 +25495,7 @@
         <v>2</v>
       </c>
       <c r="N408" s="8">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O408" s="7"/>
       <c r="P408" s="7"/>
@@ -25537,7 +25546,7 @@
         <v>2</v>
       </c>
       <c r="N409" s="8">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="O409" s="7"/>
       <c r="P409" s="7"/>
@@ -25690,7 +25699,7 @@
         <v>2</v>
       </c>
       <c r="N412" s="8">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="O412" s="7"/>
       <c r="P412" s="7"/>
@@ -25741,7 +25750,7 @@
         <v>2</v>
       </c>
       <c r="N413" s="8">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O413" s="7"/>
       <c r="P413" s="7"/>
@@ -25776,7 +25785,7 @@
         <v>12</v>
       </c>
       <c r="I414" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J414" s="8">
         <v>0</v>
@@ -25785,14 +25794,14 @@
         <v>0</v>
       </c>
       <c r="L414" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M414" s="8">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="N414" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O414" s="7"/>
       <c r="P414" s="7"/>
@@ -25827,7 +25836,7 @@
         <v>12</v>
       </c>
       <c r="I415" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J415" s="8">
         <v>0</v>
@@ -25836,14 +25845,14 @@
         <v>0</v>
       </c>
       <c r="L415" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M415" s="8">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="N415" s="8">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="O415" s="7"/>
       <c r="P415" s="7"/>
@@ -25894,7 +25903,7 @@
         <v>3</v>
       </c>
       <c r="N416" s="8">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="O416" s="7"/>
       <c r="P416" s="7"/>
@@ -25945,7 +25954,7 @@
         <v>3</v>
       </c>
       <c r="N417" s="8">
-        <v>230</v>
+        <v>205</v>
       </c>
       <c r="O417" s="7"/>
       <c r="P417" s="7"/>
@@ -25980,7 +25989,7 @@
         <v>12</v>
       </c>
       <c r="I418" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J418" s="8">
         <v>0</v>
@@ -25993,10 +26002,10 @@
       </c>
       <c r="M418" s="8">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N418" s="8">
-        <v>186</v>
+        <v>153</v>
       </c>
       <c r="O418" s="7"/>
       <c r="P418" s="7"/>
@@ -26047,7 +26056,7 @@
         <v>3</v>
       </c>
       <c r="N419" s="8">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="O419" s="7"/>
       <c r="P419" s="7"/>
@@ -26098,7 +26107,7 @@
         <v>3</v>
       </c>
       <c r="N420" s="8">
-        <v>443</v>
+        <v>415</v>
       </c>
       <c r="O420" s="7"/>
       <c r="P420" s="7"/>
@@ -26149,7 +26158,7 @@
         <v>2</v>
       </c>
       <c r="N421" s="8">
-        <v>858</v>
+        <v>808</v>
       </c>
       <c r="O421" s="7"/>
       <c r="P421" s="7"/>
@@ -26200,7 +26209,7 @@
         <v>2</v>
       </c>
       <c r="N422" s="8">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="O422" s="7"/>
       <c r="P422" s="7"/>
@@ -26251,7 +26260,7 @@
         <v>2</v>
       </c>
       <c r="N423" s="8">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="O423" s="7"/>
       <c r="P423" s="7"/>
@@ -26302,7 +26311,7 @@
         <v>2</v>
       </c>
       <c r="N424" s="8">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="O424" s="7"/>
       <c r="P424" s="7"/>
@@ -26353,7 +26362,7 @@
         <v>2</v>
       </c>
       <c r="N425" s="8">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="O425" s="7"/>
       <c r="P425" s="7"/>
@@ -26404,7 +26413,7 @@
         <v>2</v>
       </c>
       <c r="N426" s="8">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O426" s="7"/>
       <c r="P426" s="7"/>
@@ -26608,7 +26617,7 @@
         <v>0</v>
       </c>
       <c r="N430" s="8">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="O430" s="7"/>
       <c r="P430" s="7"/>
@@ -26710,7 +26719,7 @@
         <v>0</v>
       </c>
       <c r="N432" s="8">
-        <v>180</v>
+        <v>143</v>
       </c>
       <c r="O432" s="7"/>
       <c r="P432" s="7"/>
@@ -26761,7 +26770,7 @@
         <v>0</v>
       </c>
       <c r="N433" s="8">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="O433" s="7"/>
       <c r="P433" s="7"/>
@@ -26771,20 +26780,49 @@
       <c r="T433" s="7"/>
     </row>
     <row r="434" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A434" s="7"/>
-      <c r="B434" s="7"/>
-      <c r="C434" s="7"/>
-      <c r="D434" s="7"/>
-      <c r="E434" s="7"/>
-      <c r="F434" s="7"/>
-      <c r="G434" s="7"/>
-      <c r="H434" s="7"/>
-      <c r="I434" s="7"/>
-      <c r="J434" s="7"/>
-      <c r="K434" s="7"/>
-      <c r="L434" s="7"/>
-      <c r="M434" s="7"/>
-      <c r="N434" s="7"/>
+      <c r="A434" s="7" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B434" s="7" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C434" s="7" t="s">
+        <v>1343</v>
+      </c>
+      <c r="D434" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E434" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F434" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G434" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H434" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I434" s="8">
+        <v>0</v>
+      </c>
+      <c r="J434" s="8">
+        <v>0</v>
+      </c>
+      <c r="K434" s="8">
+        <v>0</v>
+      </c>
+      <c r="L434" s="8">
+        <v>0</v>
+      </c>
+      <c r="M434" s="8">
+        <f t="shared" ref="M434" si="8">I434+J434+K434+L434</f>
+        <v>0</v>
+      </c>
+      <c r="N434" s="7">
+        <v>197</v>
+      </c>
       <c r="O434" s="7"/>
       <c r="P434" s="7"/>
       <c r="Q434" s="7"/>

--- a/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
+++ b/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\Fossil Replenishment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8929BEAF-4619-46DF-A9E7-18BE2D268631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92EC844A-B609-4DB7-80EA-459B18E8AE5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6662473D-6E1F-42FD-999B-28162E22D4B5}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$T$433</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$T$439</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3484" uniqueCount="1346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3519" uniqueCount="1360">
   <si>
     <t>In Transit PO</t>
   </si>
@@ -3438,9 +3438,6 @@
     <t>B0CZSF6LVY</t>
   </si>
   <si>
-    <t>N</t>
-  </si>
-  <si>
     <t>FS5164</t>
   </si>
   <si>
@@ -4075,6 +4072,51 @@
   </si>
   <si>
     <t>FBA79494</t>
+  </si>
+  <si>
+    <t>CH2600</t>
+  </si>
+  <si>
+    <t>MK7473</t>
+  </si>
+  <si>
+    <t>BQ3377</t>
+  </si>
+  <si>
+    <t>MK9118</t>
+  </si>
+  <si>
+    <t>ES5401</t>
+  </si>
+  <si>
+    <t>B004LPOYRA</t>
+  </si>
+  <si>
+    <t>B0CRD5XBPH</t>
+  </si>
+  <si>
+    <t>B07H4ZMTML</t>
+  </si>
+  <si>
+    <t>B0C7WL5TJY</t>
+  </si>
+  <si>
+    <t>B0DSBQMHMD</t>
+  </si>
+  <si>
+    <t>FBA66629</t>
+  </si>
+  <si>
+    <t>FBA79309</t>
+  </si>
+  <si>
+    <t>FBA74719</t>
+  </si>
+  <si>
+    <t>FBA79387</t>
+  </si>
+  <si>
+    <t>FBA79744</t>
   </si>
 </sst>
 </file>
@@ -4209,7 +4251,47 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="16">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -4773,23 +4855,23 @@
         <v>12</v>
       </c>
       <c r="I2" s="8">
-        <v>794</v>
+        <v>826</v>
       </c>
       <c r="J2" s="8">
         <v>0</v>
       </c>
       <c r="K2" s="8">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="L2" s="8">
         <v>0</v>
       </c>
       <c r="M2" s="8">
         <f>I2+J2+K2+L2</f>
-        <v>837</v>
+        <v>898</v>
       </c>
       <c r="N2" s="8">
-        <v>1281</v>
+        <v>1209</v>
       </c>
       <c r="O2" s="8"/>
       <c r="P2" s="8"/>
@@ -4824,7 +4906,7 @@
         <v>12</v>
       </c>
       <c r="I3" s="8">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J3" s="8">
         <v>0</v>
@@ -4837,7 +4919,7 @@
       </c>
       <c r="M3" s="8">
         <f t="shared" ref="M3:M66" si="0">I3+J3+K3+L3</f>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="N3" s="8">
         <v>0</v>
@@ -4875,7 +4957,7 @@
         <v>12</v>
       </c>
       <c r="I4" s="8">
-        <v>275</v>
+        <v>231</v>
       </c>
       <c r="J4" s="8">
         <v>0</v>
@@ -4888,7 +4970,7 @@
       </c>
       <c r="M4" s="8">
         <f t="shared" si="0"/>
-        <v>275</v>
+        <v>231</v>
       </c>
       <c r="N4" s="8">
         <v>0</v>
@@ -4926,7 +5008,7 @@
         <v>12</v>
       </c>
       <c r="I5" s="8">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="J5" s="8">
         <v>0</v>
@@ -4939,10 +5021,10 @@
       </c>
       <c r="M5" s="8">
         <f t="shared" si="0"/>
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="N5" s="8">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="O5" s="8"/>
       <c r="P5" s="8"/>
@@ -4977,23 +5059,23 @@
         <v>12</v>
       </c>
       <c r="I6" s="8">
-        <v>795</v>
+        <v>869</v>
       </c>
       <c r="J6" s="8">
         <v>0</v>
       </c>
       <c r="K6" s="8">
-        <v>30</v>
+        <v>96</v>
       </c>
       <c r="L6" s="8">
         <v>0</v>
       </c>
       <c r="M6" s="8">
         <f t="shared" si="0"/>
-        <v>825</v>
+        <v>965</v>
       </c>
       <c r="N6" s="8">
-        <v>1586</v>
+        <v>1490</v>
       </c>
       <c r="O6" s="8"/>
       <c r="P6" s="8"/>
@@ -5028,7 +5110,7 @@
         <v>12</v>
       </c>
       <c r="I7" s="8">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J7" s="8">
         <v>0</v>
@@ -5041,10 +5123,10 @@
       </c>
       <c r="M7" s="8">
         <f t="shared" si="0"/>
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="N7" s="8">
-        <v>864</v>
+        <v>869</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
@@ -5079,23 +5161,23 @@
         <v>12</v>
       </c>
       <c r="I8" s="8">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J8" s="8">
         <v>0</v>
       </c>
       <c r="K8" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="8">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="M8" s="8">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="N8" s="8">
-        <v>373</v>
+        <v>318</v>
       </c>
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
@@ -5121,7 +5203,7 @@
         <v>19</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>1062</v>
@@ -5130,7 +5212,7 @@
         <v>12</v>
       </c>
       <c r="I9" s="8">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J9" s="8">
         <v>0</v>
@@ -5143,7 +5225,7 @@
       </c>
       <c r="M9" s="8">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N9" s="8">
         <v>0</v>
@@ -5172,7 +5254,7 @@
         <v>19</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>1062</v>
@@ -5181,7 +5263,7 @@
         <v>12</v>
       </c>
       <c r="I10" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="8">
         <v>0</v>
@@ -5194,7 +5276,7 @@
       </c>
       <c r="M10" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" s="8">
         <v>0</v>
@@ -5232,20 +5314,20 @@
         <v>12</v>
       </c>
       <c r="I11" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J11" s="8">
         <v>0</v>
       </c>
       <c r="K11" s="8">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L11" s="8">
         <v>0</v>
       </c>
       <c r="M11" s="8">
         <f t="shared" si="0"/>
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="N11" s="8">
         <v>0</v>
@@ -5283,7 +5365,7 @@
         <v>12</v>
       </c>
       <c r="I12" s="8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J12" s="8">
         <v>0</v>
@@ -5296,7 +5378,7 @@
       </c>
       <c r="M12" s="8">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N12" s="8">
         <v>0</v>
@@ -5334,23 +5416,23 @@
         <v>12</v>
       </c>
       <c r="I13" s="8">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J13" s="8">
         <v>0</v>
       </c>
       <c r="K13" s="8">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="L13" s="8">
         <v>0</v>
       </c>
       <c r="M13" s="8">
         <f t="shared" si="0"/>
-        <v>228</v>
+        <v>277</v>
       </c>
       <c r="N13" s="8">
-        <v>858</v>
+        <v>810</v>
       </c>
       <c r="O13" s="8"/>
       <c r="P13" s="8"/>
@@ -5385,23 +5467,23 @@
         <v>12</v>
       </c>
       <c r="I14" s="8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J14" s="8">
         <v>0</v>
       </c>
       <c r="K14" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" s="8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M14" s="8">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="N14" s="8">
-        <v>647</v>
+        <v>626</v>
       </c>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
@@ -5496,14 +5578,14 @@
         <v>0</v>
       </c>
       <c r="L16" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M16" s="8">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="N16" s="8">
-        <v>545</v>
+        <v>533</v>
       </c>
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
@@ -5538,7 +5620,7 @@
         <v>12</v>
       </c>
       <c r="I17" s="8">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="J17" s="8">
         <v>0</v>
@@ -5551,10 +5633,10 @@
       </c>
       <c r="M17" s="8">
         <f t="shared" si="0"/>
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="N17" s="8">
-        <v>341</v>
+        <v>315</v>
       </c>
       <c r="O17" s="8"/>
       <c r="P17" s="8"/>
@@ -5646,17 +5728,17 @@
         <v>0</v>
       </c>
       <c r="K19" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" s="8">
         <v>0</v>
       </c>
       <c r="M19" s="8">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N19" s="8">
-        <v>484</v>
+        <v>405</v>
       </c>
       <c r="O19" s="8"/>
       <c r="P19" s="8"/>
@@ -5691,7 +5773,7 @@
         <v>14</v>
       </c>
       <c r="I20" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J20" s="8">
         <v>0</v>
@@ -5700,14 +5782,14 @@
         <v>0</v>
       </c>
       <c r="L20" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M20" s="8">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="N20" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O20" s="8"/>
       <c r="P20" s="8"/>
@@ -5742,7 +5824,7 @@
         <v>13</v>
       </c>
       <c r="I21" s="8">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="J21" s="8">
         <v>0</v>
@@ -5755,7 +5837,7 @@
       </c>
       <c r="M21" s="8">
         <f t="shared" si="0"/>
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="N21" s="8">
         <v>0</v>
@@ -5793,7 +5875,7 @@
         <v>12</v>
       </c>
       <c r="I22" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" s="8">
         <v>0</v>
@@ -5806,7 +5888,7 @@
       </c>
       <c r="M22" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" s="8">
         <v>0</v>
@@ -5844,20 +5926,20 @@
         <v>12</v>
       </c>
       <c r="I23" s="8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J23" s="8">
         <v>0</v>
       </c>
       <c r="K23" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L23" s="8">
         <v>0</v>
       </c>
       <c r="M23" s="8">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="N23" s="8">
         <v>0</v>
@@ -5911,7 +5993,7 @@
         <v>10</v>
       </c>
       <c r="N24" s="8">
-        <v>428</v>
+        <v>411</v>
       </c>
       <c r="O24" s="8"/>
       <c r="P24" s="8"/>
@@ -5997,7 +6079,7 @@
         <v>12</v>
       </c>
       <c r="I26" s="8">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J26" s="8">
         <v>0</v>
@@ -6006,14 +6088,14 @@
         <v>0</v>
       </c>
       <c r="L26" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M26" s="8">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N26" s="8">
-        <v>203</v>
+        <v>154</v>
       </c>
       <c r="O26" s="8"/>
       <c r="P26" s="8"/>
@@ -6048,7 +6130,7 @@
         <v>12</v>
       </c>
       <c r="I27" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J27" s="8">
         <v>0</v>
@@ -6061,10 +6143,10 @@
       </c>
       <c r="M27" s="8">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N27" s="8">
-        <v>858</v>
+        <v>849</v>
       </c>
       <c r="O27" s="8"/>
       <c r="P27" s="8"/>
@@ -6099,7 +6181,7 @@
         <v>12</v>
       </c>
       <c r="I28" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J28" s="8">
         <v>0</v>
@@ -6112,7 +6194,7 @@
       </c>
       <c r="M28" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N28" s="8">
         <v>0</v>
@@ -6150,7 +6232,7 @@
         <v>13</v>
       </c>
       <c r="I29" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J29" s="8">
         <v>0</v>
@@ -6163,7 +6245,7 @@
       </c>
       <c r="M29" s="8">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N29" s="8">
         <v>0</v>
@@ -6201,23 +6283,23 @@
         <v>14</v>
       </c>
       <c r="I30" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J30" s="8">
         <v>0</v>
       </c>
       <c r="K30" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L30" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M30" s="8">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N30" s="8">
-        <v>1316</v>
+        <v>1307</v>
       </c>
       <c r="O30" s="8"/>
       <c r="P30" s="8"/>
@@ -6252,7 +6334,7 @@
         <v>13</v>
       </c>
       <c r="I31" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J31" s="8">
         <v>0</v>
@@ -6265,7 +6347,7 @@
       </c>
       <c r="M31" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N31" s="8">
         <v>0</v>
@@ -6303,7 +6385,7 @@
         <v>12</v>
       </c>
       <c r="I32" s="8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J32" s="8">
         <v>0</v>
@@ -6316,10 +6398,10 @@
       </c>
       <c r="M32" s="8">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N32" s="8">
-        <v>585</v>
+        <v>575</v>
       </c>
       <c r="O32" s="8"/>
       <c r="P32" s="8"/>
@@ -6360,17 +6442,17 @@
         <v>0</v>
       </c>
       <c r="K33" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L33" s="8">
         <v>0</v>
       </c>
       <c r="M33" s="8">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="N33" s="8">
-        <v>852</v>
+        <v>842</v>
       </c>
       <c r="O33" s="8"/>
       <c r="P33" s="8"/>
@@ -6405,7 +6487,7 @@
         <v>12</v>
       </c>
       <c r="I34" s="8">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J34" s="8">
         <v>0</v>
@@ -6418,10 +6500,10 @@
       </c>
       <c r="M34" s="8">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N34" s="8">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="O34" s="8"/>
       <c r="P34" s="8"/>
@@ -6456,7 +6538,7 @@
         <v>12</v>
       </c>
       <c r="I35" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J35" s="8">
         <v>0</v>
@@ -6469,10 +6551,10 @@
       </c>
       <c r="M35" s="8">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N35" s="8">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="O35" s="8"/>
       <c r="P35" s="8"/>
@@ -6523,7 +6605,7 @@
         <v>7</v>
       </c>
       <c r="N36" s="8">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="O36" s="8"/>
       <c r="P36" s="8"/>
@@ -6574,7 +6656,7 @@
         <v>30</v>
       </c>
       <c r="N37" s="8">
-        <v>1031</v>
+        <v>991</v>
       </c>
       <c r="O37" s="8"/>
       <c r="P37" s="8"/>
@@ -6600,7 +6682,7 @@
         <v>19</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G38" s="8" t="s">
         <v>1062</v>
@@ -6660,23 +6742,23 @@
         <v>12</v>
       </c>
       <c r="I39" s="8">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J39" s="8">
         <v>0</v>
       </c>
       <c r="K39" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L39" s="8">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M39" s="8">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="N39" s="8">
-        <v>2702</v>
+        <v>2680</v>
       </c>
       <c r="O39" s="8"/>
       <c r="P39" s="8"/>
@@ -6762,13 +6844,13 @@
         <v>12</v>
       </c>
       <c r="I41" s="8">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J41" s="8">
         <v>0</v>
       </c>
       <c r="K41" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L41" s="8">
         <v>0</v>
@@ -6778,7 +6860,7 @@
         <v>20</v>
       </c>
       <c r="N41" s="8">
-        <v>186</v>
+        <v>250</v>
       </c>
       <c r="O41" s="8"/>
       <c r="P41" s="8"/>
@@ -6822,14 +6904,14 @@
         <v>0</v>
       </c>
       <c r="L42" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M42" s="8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="N42" s="8">
-        <v>1206</v>
+        <v>1165</v>
       </c>
       <c r="O42" s="8"/>
       <c r="P42" s="8"/>
@@ -6915,7 +6997,7 @@
         <v>12</v>
       </c>
       <c r="I44" s="8">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J44" s="8">
         <v>0</v>
@@ -6928,10 +7010,10 @@
       </c>
       <c r="M44" s="8">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N44" s="8">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="O44" s="8"/>
       <c r="P44" s="8"/>
@@ -6982,7 +7064,7 @@
         <v>13</v>
       </c>
       <c r="N45" s="8">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="O45" s="8"/>
       <c r="P45" s="8"/>
@@ -7033,7 +7115,7 @@
         <v>12</v>
       </c>
       <c r="N46" s="8">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O46" s="8"/>
       <c r="P46" s="8"/>
@@ -7068,7 +7150,7 @@
         <v>13</v>
       </c>
       <c r="I47" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J47" s="8">
         <v>0</v>
@@ -7081,10 +7163,10 @@
       </c>
       <c r="M47" s="8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N47" s="8">
-        <v>770</v>
+        <v>755</v>
       </c>
       <c r="O47" s="8"/>
       <c r="P47" s="8"/>
@@ -7119,23 +7201,23 @@
         <v>12</v>
       </c>
       <c r="I48" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J48" s="8">
         <v>0</v>
       </c>
       <c r="K48" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" s="8">
         <v>0</v>
       </c>
       <c r="M48" s="8">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N48" s="8">
-        <v>1592</v>
+        <v>1500</v>
       </c>
       <c r="O48" s="8"/>
       <c r="P48" s="8"/>
@@ -7186,7 +7268,7 @@
         <v>10</v>
       </c>
       <c r="N49" s="8">
-        <v>770</v>
+        <v>757</v>
       </c>
       <c r="O49" s="8"/>
       <c r="P49" s="8"/>
@@ -7288,7 +7370,7 @@
         <v>24</v>
       </c>
       <c r="N51" s="8">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="O51" s="8"/>
       <c r="P51" s="8"/>
@@ -7390,7 +7472,7 @@
         <v>9</v>
       </c>
       <c r="N53" s="8">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="O53" s="8"/>
       <c r="P53" s="8"/>
@@ -7425,23 +7507,23 @@
         <v>12</v>
       </c>
       <c r="I54" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J54" s="8">
         <v>0</v>
       </c>
       <c r="K54" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54" s="8">
         <v>0</v>
       </c>
       <c r="M54" s="8">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N54" s="8">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="O54" s="8"/>
       <c r="P54" s="8"/>
@@ -7476,7 +7558,7 @@
         <v>12</v>
       </c>
       <c r="I55" s="8">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J55" s="8">
         <v>0</v>
@@ -7489,7 +7571,7 @@
       </c>
       <c r="M55" s="8">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="N55" s="8">
         <v>0</v>
@@ -7527,7 +7609,7 @@
         <v>14</v>
       </c>
       <c r="I56" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J56" s="8">
         <v>0</v>
@@ -7540,10 +7622,10 @@
       </c>
       <c r="M56" s="8">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N56" s="8">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O56" s="8"/>
       <c r="P56" s="8"/>
@@ -7578,23 +7660,23 @@
         <v>12</v>
       </c>
       <c r="I57" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J57" s="8">
         <v>0</v>
       </c>
       <c r="K57" s="8">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L57" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M57" s="8">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="N57" s="8">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O57" s="8"/>
       <c r="P57" s="8"/>
@@ -7629,23 +7711,23 @@
         <v>12</v>
       </c>
       <c r="I58" s="8">
+        <v>1</v>
+      </c>
+      <c r="J58" s="8">
+        <v>0</v>
+      </c>
+      <c r="K58" s="8">
+        <v>0</v>
+      </c>
+      <c r="L58" s="8">
         <v>2</v>
-      </c>
-      <c r="J58" s="8">
-        <v>0</v>
-      </c>
-      <c r="K58" s="8">
-        <v>1</v>
-      </c>
-      <c r="L58" s="8">
-        <v>0</v>
       </c>
       <c r="M58" s="8">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="N58" s="8">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="O58" s="8"/>
       <c r="P58" s="8"/>
@@ -7671,7 +7753,7 @@
         <v>19</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G59" s="8" t="s">
         <v>1062</v>
@@ -7731,7 +7813,7 @@
         <v>12</v>
       </c>
       <c r="I60" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J60" s="8">
         <v>0</v>
@@ -7744,10 +7826,10 @@
       </c>
       <c r="M60" s="8">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N60" s="8">
-        <v>491</v>
+        <v>474</v>
       </c>
       <c r="O60" s="8"/>
       <c r="P60" s="8"/>
@@ -7782,7 +7864,7 @@
         <v>12</v>
       </c>
       <c r="I61" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J61" s="8">
         <v>0</v>
@@ -7795,7 +7877,7 @@
       </c>
       <c r="M61" s="8">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N61" s="8">
         <v>0</v>
@@ -7849,7 +7931,7 @@
         <v>7</v>
       </c>
       <c r="N62" s="8">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="O62" s="8"/>
       <c r="P62" s="8"/>
@@ -7884,7 +7966,7 @@
         <v>12</v>
       </c>
       <c r="I63" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J63" s="8">
         <v>0</v>
@@ -7897,10 +7979,10 @@
       </c>
       <c r="M63" s="8">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N63" s="8">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="O63" s="8"/>
       <c r="P63" s="8"/>
@@ -7935,23 +8017,23 @@
         <v>13</v>
       </c>
       <c r="I64" s="8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J64" s="8">
         <v>0</v>
       </c>
       <c r="K64" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M64" s="8">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N64" s="8">
-        <v>251</v>
+        <v>222</v>
       </c>
       <c r="O64" s="8"/>
       <c r="P64" s="8"/>
@@ -7977,7 +8059,7 @@
         <v>19</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="G65" s="8" t="s">
         <v>1062</v>
@@ -7992,17 +8074,17 @@
         <v>0</v>
       </c>
       <c r="K65" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" s="8">
         <v>0</v>
       </c>
       <c r="M65" s="8">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N65" s="8">
-        <v>861</v>
+        <v>848</v>
       </c>
       <c r="O65" s="8"/>
       <c r="P65" s="8"/>
@@ -8104,7 +8186,7 @@
         <v>3</v>
       </c>
       <c r="N67" s="8">
-        <v>0</v>
+        <v>664</v>
       </c>
       <c r="O67" s="8"/>
       <c r="P67" s="8"/>
@@ -8139,7 +8221,7 @@
         <v>12</v>
       </c>
       <c r="I68" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J68" s="8">
         <v>0</v>
@@ -8148,14 +8230,14 @@
         <v>0</v>
       </c>
       <c r="L68" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M68" s="8">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N68" s="8">
-        <v>891</v>
+        <v>886</v>
       </c>
       <c r="O68" s="8"/>
       <c r="P68" s="8"/>
@@ -8206,7 +8288,7 @@
         <v>10</v>
       </c>
       <c r="N69" s="8">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="O69" s="8"/>
       <c r="P69" s="8"/>
@@ -8257,7 +8339,7 @@
         <v>2</v>
       </c>
       <c r="N70" s="8">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="O70" s="8"/>
       <c r="P70" s="8"/>
@@ -8359,7 +8441,7 @@
         <v>7</v>
       </c>
       <c r="N72" s="8">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="O72" s="8"/>
       <c r="P72" s="8"/>
@@ -8394,23 +8476,23 @@
         <v>12</v>
       </c>
       <c r="I73" s="8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J73" s="8">
         <v>0</v>
       </c>
       <c r="K73" s="8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L73" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M73" s="8">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="N73" s="8">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="O73" s="8"/>
       <c r="P73" s="8"/>
@@ -8445,23 +8527,23 @@
         <v>14</v>
       </c>
       <c r="I74" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J74" s="8">
         <v>0</v>
       </c>
       <c r="K74" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L74" s="8">
         <v>0</v>
       </c>
       <c r="M74" s="8">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N74" s="8">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O74" s="8"/>
       <c r="P74" s="8"/>
@@ -8487,7 +8569,7 @@
         <v>19</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G75" s="8" t="s">
         <v>1062</v>
@@ -8512,7 +8594,7 @@
         <v>6</v>
       </c>
       <c r="N75" s="8">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O75" s="8"/>
       <c r="P75" s="8"/>
@@ -8538,7 +8620,7 @@
         <v>19</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="G76" s="8" t="s">
         <v>1062</v>
@@ -8598,7 +8680,7 @@
         <v>12</v>
       </c>
       <c r="I77" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J77" s="8">
         <v>0</v>
@@ -8611,10 +8693,10 @@
       </c>
       <c r="M77" s="8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N77" s="8">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="O77" s="8"/>
       <c r="P77" s="8"/>
@@ -8649,23 +8731,23 @@
         <v>12</v>
       </c>
       <c r="I78" s="8">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J78" s="8">
         <v>0</v>
       </c>
       <c r="K78" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L78" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M78" s="8">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="N78" s="8">
-        <v>324</v>
+        <v>300</v>
       </c>
       <c r="O78" s="8"/>
       <c r="P78" s="8"/>
@@ -8716,7 +8798,7 @@
         <v>4</v>
       </c>
       <c r="N79" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O79" s="8"/>
       <c r="P79" s="8"/>
@@ -8767,7 +8849,7 @@
         <v>3</v>
       </c>
       <c r="N80" s="8">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="O80" s="8"/>
       <c r="P80" s="8"/>
@@ -8869,7 +8951,7 @@
         <v>5</v>
       </c>
       <c r="N82" s="8">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="O82" s="8"/>
       <c r="P82" s="8"/>
@@ -8920,7 +9002,7 @@
         <v>4</v>
       </c>
       <c r="N83" s="8">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="O83" s="8"/>
       <c r="P83" s="8"/>
@@ -8955,7 +9037,7 @@
         <v>13</v>
       </c>
       <c r="I84" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J84" s="8">
         <v>0</v>
@@ -8968,7 +9050,7 @@
       </c>
       <c r="M84" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N84" s="8">
         <v>0</v>
@@ -8997,7 +9079,7 @@
         <v>19</v>
       </c>
       <c r="F85" s="8" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="G85" s="8" t="s">
         <v>1061</v>
@@ -9006,7 +9088,7 @@
         <v>14</v>
       </c>
       <c r="I85" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J85" s="8">
         <v>0</v>
@@ -9019,7 +9101,7 @@
       </c>
       <c r="M85" s="8">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N85" s="8">
         <v>524</v>
@@ -9048,7 +9130,7 @@
         <v>19</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G86" s="8" t="s">
         <v>1062</v>
@@ -9057,7 +9139,7 @@
         <v>12</v>
       </c>
       <c r="I86" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J86" s="8">
         <v>0</v>
@@ -9070,10 +9152,10 @@
       </c>
       <c r="M86" s="8">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N86" s="8">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="O86" s="8"/>
       <c r="P86" s="8"/>
@@ -9175,7 +9257,7 @@
         <v>12</v>
       </c>
       <c r="N88" s="8">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="O88" s="8"/>
       <c r="P88" s="8"/>
@@ -9210,20 +9292,20 @@
         <v>12</v>
       </c>
       <c r="I89" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J89" s="8">
         <v>0</v>
       </c>
       <c r="K89" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L89" s="8">
         <v>0</v>
       </c>
       <c r="M89" s="8">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N89" s="8">
         <v>0</v>
@@ -9277,7 +9359,7 @@
         <v>5</v>
       </c>
       <c r="N90" s="8">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O90" s="8"/>
       <c r="P90" s="8"/>
@@ -9303,7 +9385,7 @@
         <v>19</v>
       </c>
       <c r="F91" s="8" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="G91" s="8" t="s">
         <v>1062</v>
@@ -9321,14 +9403,14 @@
         <v>0</v>
       </c>
       <c r="L91" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" s="8">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N91" s="8">
-        <v>946</v>
+        <v>938</v>
       </c>
       <c r="O91" s="8"/>
       <c r="P91" s="8"/>
@@ -9363,7 +9445,7 @@
         <v>12</v>
       </c>
       <c r="I92" s="8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J92" s="8">
         <v>0</v>
@@ -9376,10 +9458,10 @@
       </c>
       <c r="M92" s="8">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N92" s="8">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="O92" s="8"/>
       <c r="P92" s="8"/>
@@ -9405,7 +9487,7 @@
         <v>19</v>
       </c>
       <c r="F93" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G93" s="8" t="s">
         <v>1062</v>
@@ -9414,7 +9496,7 @@
         <v>13</v>
       </c>
       <c r="I93" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J93" s="8">
         <v>0</v>
@@ -9427,7 +9509,7 @@
       </c>
       <c r="M93" s="8">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N93" s="8">
         <v>0</v>
@@ -9456,7 +9538,7 @@
         <v>19</v>
       </c>
       <c r="F94" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G94" s="8" t="s">
         <v>1062</v>
@@ -9532,7 +9614,7 @@
         <v>6</v>
       </c>
       <c r="N95" s="8">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="O95" s="8"/>
       <c r="P95" s="8"/>
@@ -9583,7 +9665,7 @@
         <v>7</v>
       </c>
       <c r="N96" s="8">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O96" s="8"/>
       <c r="P96" s="8"/>
@@ -9618,23 +9700,23 @@
         <v>14</v>
       </c>
       <c r="I97" s="8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J97" s="8">
         <v>0</v>
       </c>
       <c r="K97" s="8">
+        <v>0</v>
+      </c>
+      <c r="L97" s="8">
         <v>3</v>
-      </c>
-      <c r="L97" s="8">
-        <v>0</v>
       </c>
       <c r="M97" s="8">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N97" s="8">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="O97" s="8"/>
       <c r="P97" s="8"/>
@@ -9822,7 +9904,7 @@
         <v>15</v>
       </c>
       <c r="I101" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J101" s="8">
         <v>0</v>
@@ -9835,10 +9917,10 @@
       </c>
       <c r="M101" s="8">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N101" s="8">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="O101" s="8"/>
       <c r="P101" s="8"/>
@@ -9873,23 +9955,23 @@
         <v>14</v>
       </c>
       <c r="I102" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J102" s="8">
         <v>0</v>
       </c>
       <c r="K102" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L102" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M102" s="8">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N102" s="8">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="O102" s="8"/>
       <c r="P102" s="8"/>
@@ -9915,7 +9997,7 @@
         <v>19</v>
       </c>
       <c r="F103" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G103" s="8" t="s">
         <v>1062</v>
@@ -9924,23 +10006,23 @@
         <v>15</v>
       </c>
       <c r="I103" s="8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J103" s="8">
         <v>0</v>
       </c>
       <c r="K103" s="8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L103" s="8">
         <v>0</v>
       </c>
       <c r="M103" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N103" s="8">
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="O103" s="8"/>
       <c r="P103" s="8"/>
@@ -10042,7 +10124,7 @@
         <v>6</v>
       </c>
       <c r="N105" s="8">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O105" s="8"/>
       <c r="P105" s="8"/>
@@ -10179,7 +10261,7 @@
         <v>15</v>
       </c>
       <c r="I108" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J108" s="8">
         <v>0</v>
@@ -10192,7 +10274,7 @@
       </c>
       <c r="M108" s="8">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N108" s="8">
         <v>0</v>
@@ -10246,7 +10328,7 @@
         <v>4</v>
       </c>
       <c r="N109" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O109" s="8"/>
       <c r="P109" s="8"/>
@@ -10272,7 +10354,7 @@
         <v>19</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="G110" s="8" t="s">
         <v>1061</v>
@@ -10332,7 +10414,7 @@
         <v>13</v>
       </c>
       <c r="I111" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J111" s="8">
         <v>0</v>
@@ -10345,7 +10427,7 @@
       </c>
       <c r="M111" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N111" s="8">
         <v>0</v>
@@ -10383,20 +10465,20 @@
         <v>12</v>
       </c>
       <c r="I112" s="8">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="J112" s="8">
         <v>0</v>
       </c>
       <c r="K112" s="8">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="L112" s="8">
         <v>0</v>
       </c>
       <c r="M112" s="8">
         <f t="shared" si="1"/>
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="N112" s="8">
         <v>0</v>
@@ -10434,23 +10516,23 @@
         <v>12</v>
       </c>
       <c r="I113" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J113" s="8">
         <v>0</v>
       </c>
       <c r="K113" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L113" s="8">
         <v>0</v>
       </c>
       <c r="M113" s="8">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="N113" s="8">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="O113" s="8"/>
       <c r="P113" s="8"/>
@@ -10485,7 +10567,7 @@
         <v>13</v>
       </c>
       <c r="I114" s="8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J114" s="8">
         <v>0</v>
@@ -10498,10 +10580,10 @@
       </c>
       <c r="M114" s="8">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N114" s="8">
-        <v>486</v>
+        <v>531</v>
       </c>
       <c r="O114" s="8"/>
       <c r="P114" s="8"/>
@@ -10552,7 +10634,7 @@
         <v>9</v>
       </c>
       <c r="N115" s="8">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="O115" s="8"/>
       <c r="P115" s="8"/>
@@ -10603,7 +10685,7 @@
         <v>6</v>
       </c>
       <c r="N116" s="8">
-        <v>651</v>
+        <v>633</v>
       </c>
       <c r="O116" s="8"/>
       <c r="P116" s="8"/>
@@ -10644,17 +10726,17 @@
         <v>0</v>
       </c>
       <c r="K117" s="8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L117" s="8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M117" s="8">
         <f t="shared" si="1"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N117" s="8">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="O117" s="8"/>
       <c r="P117" s="8"/>
@@ -10705,7 +10787,7 @@
         <v>6</v>
       </c>
       <c r="N118" s="8">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O118" s="8"/>
       <c r="P118" s="8"/>
@@ -10740,7 +10822,7 @@
         <v>14</v>
       </c>
       <c r="I119" s="8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J119" s="8">
         <v>0</v>
@@ -10753,10 +10835,10 @@
       </c>
       <c r="M119" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N119" s="8">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="O119" s="8"/>
       <c r="P119" s="8"/>
@@ -10791,7 +10873,7 @@
         <v>14</v>
       </c>
       <c r="I120" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J120" s="8">
         <v>0</v>
@@ -10804,10 +10886,10 @@
       </c>
       <c r="M120" s="8">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N120" s="8">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="O120" s="8"/>
       <c r="P120" s="8"/>
@@ -10909,7 +10991,7 @@
         <v>2</v>
       </c>
       <c r="N122" s="8">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="O122" s="8"/>
       <c r="P122" s="8"/>
@@ -10935,7 +11017,7 @@
         <v>19</v>
       </c>
       <c r="F123" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G123" s="8" t="s">
         <v>1062</v>
@@ -11062,7 +11144,7 @@
         <v>6</v>
       </c>
       <c r="N125" s="8">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="O125" s="8"/>
       <c r="P125" s="8"/>
@@ -11088,7 +11170,7 @@
         <v>19</v>
       </c>
       <c r="F126" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G126" s="8" t="s">
         <v>1062</v>
@@ -11215,7 +11297,7 @@
         <v>3</v>
       </c>
       <c r="N128" s="8">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="O128" s="8"/>
       <c r="P128" s="8"/>
@@ -11307,17 +11389,17 @@
         <v>0</v>
       </c>
       <c r="K130" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L130" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M130" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N130" s="8">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="O130" s="8"/>
       <c r="P130" s="8"/>
@@ -11343,7 +11425,7 @@
         <v>19</v>
       </c>
       <c r="F131" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G131" s="8" t="s">
         <v>1062</v>
@@ -11368,7 +11450,7 @@
         <v>2</v>
       </c>
       <c r="N131" s="8">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="O131" s="8"/>
       <c r="P131" s="8"/>
@@ -11419,7 +11501,7 @@
         <v>7</v>
       </c>
       <c r="N132" s="8">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="O132" s="8"/>
       <c r="P132" s="8"/>
@@ -11454,7 +11536,7 @@
         <v>12</v>
       </c>
       <c r="I133" s="8">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J133" s="8">
         <v>0</v>
@@ -11463,14 +11545,14 @@
         <v>0</v>
       </c>
       <c r="L133" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M133" s="8">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
       <c r="N133" s="8">
-        <v>119</v>
+        <v>295</v>
       </c>
       <c r="O133" s="8"/>
       <c r="P133" s="8"/>
@@ -11521,7 +11603,7 @@
         <v>4</v>
       </c>
       <c r="N134" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O134" s="8"/>
       <c r="P134" s="8"/>
@@ -11547,7 +11629,7 @@
         <v>19</v>
       </c>
       <c r="F135" s="8" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="G135" s="8" t="s">
         <v>1062</v>
@@ -11562,17 +11644,17 @@
         <v>0</v>
       </c>
       <c r="K135" s="8">
+        <v>0</v>
+      </c>
+      <c r="L135" s="8">
         <v>2</v>
-      </c>
-      <c r="L135" s="8">
-        <v>0</v>
       </c>
       <c r="M135" s="8">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="N135" s="8">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="O135" s="8"/>
       <c r="P135" s="8"/>
@@ -11607,23 +11689,23 @@
         <v>14</v>
       </c>
       <c r="I136" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J136" s="8">
         <v>0</v>
       </c>
       <c r="K136" s="8">
+        <v>0</v>
+      </c>
+      <c r="L136" s="8">
         <v>3</v>
-      </c>
-      <c r="L136" s="8">
-        <v>0</v>
       </c>
       <c r="M136" s="8">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N136" s="8">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="O136" s="8"/>
       <c r="P136" s="8"/>
@@ -11658,7 +11740,7 @@
         <v>15</v>
       </c>
       <c r="I137" s="8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J137" s="8">
         <v>0</v>
@@ -11671,10 +11753,10 @@
       </c>
       <c r="M137" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N137" s="8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O137" s="8"/>
       <c r="P137" s="8"/>
@@ -11718,14 +11800,14 @@
         <v>0</v>
       </c>
       <c r="L138" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M138" s="8">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N138" s="8">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="O138" s="8"/>
       <c r="P138" s="8"/>
@@ -11751,7 +11833,7 @@
         <v>19</v>
       </c>
       <c r="F139" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G139" s="8" t="s">
         <v>1062</v>
@@ -11760,7 +11842,7 @@
         <v>15</v>
       </c>
       <c r="I139" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J139" s="8">
         <v>0</v>
@@ -11773,10 +11855,10 @@
       </c>
       <c r="M139" s="8">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N139" s="8">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O139" s="8"/>
       <c r="P139" s="8"/>
@@ -11802,7 +11884,7 @@
         <v>19</v>
       </c>
       <c r="F140" s="8" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="G140" s="8" t="s">
         <v>1062</v>
@@ -11817,17 +11899,17 @@
         <v>0</v>
       </c>
       <c r="K140" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L140" s="8">
         <v>0</v>
       </c>
       <c r="M140" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N140" s="8">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="O140" s="8"/>
       <c r="P140" s="8"/>
@@ -11871,14 +11953,14 @@
         <v>0</v>
       </c>
       <c r="L141" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M141" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N141" s="8">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O141" s="8"/>
       <c r="P141" s="8"/>
@@ -11929,7 +12011,7 @@
         <v>2</v>
       </c>
       <c r="N142" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O142" s="8"/>
       <c r="P142" s="8"/>
@@ -11973,14 +12055,14 @@
         <v>0</v>
       </c>
       <c r="L143" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M143" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N143" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O143" s="8"/>
       <c r="P143" s="8"/>
@@ -12082,7 +12164,7 @@
         <v>4</v>
       </c>
       <c r="N145" s="8">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="O145" s="8"/>
       <c r="P145" s="8"/>
@@ -12184,7 +12266,7 @@
         <v>2</v>
       </c>
       <c r="N147" s="8">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O147" s="8"/>
       <c r="P147" s="8"/>
@@ -12219,7 +12301,7 @@
         <v>15</v>
       </c>
       <c r="I148" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J148" s="8">
         <v>0</v>
@@ -12232,7 +12314,7 @@
       </c>
       <c r="M148" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N148" s="8">
         <v>344</v>
@@ -12261,7 +12343,7 @@
         <v>19</v>
       </c>
       <c r="F149" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G149" s="8" t="s">
         <v>1062</v>
@@ -12270,23 +12352,23 @@
         <v>12</v>
       </c>
       <c r="I149" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J149" s="8">
         <v>0</v>
       </c>
       <c r="K149" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L149" s="8">
         <v>0</v>
       </c>
       <c r="M149" s="8">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N149" s="8">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="O149" s="8"/>
       <c r="P149" s="8"/>
@@ -12312,7 +12394,7 @@
         <v>19</v>
       </c>
       <c r="F150" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G150" s="8" t="s">
         <v>1062</v>
@@ -12330,14 +12412,14 @@
         <v>0</v>
       </c>
       <c r="L150" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M150" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N150" s="8">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="O150" s="8"/>
       <c r="P150" s="8"/>
@@ -12388,7 +12470,7 @@
         <v>3</v>
       </c>
       <c r="N151" s="8">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O151" s="8"/>
       <c r="P151" s="8"/>
@@ -12439,7 +12521,7 @@
         <v>3</v>
       </c>
       <c r="N152" s="8">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O152" s="8"/>
       <c r="P152" s="8"/>
@@ -12465,7 +12547,7 @@
         <v>19</v>
       </c>
       <c r="F153" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G153" s="8" t="s">
         <v>1062</v>
@@ -12483,14 +12565,14 @@
         <v>0</v>
       </c>
       <c r="L153" s="8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M153" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N153" s="8">
-        <v>529</v>
+        <v>0</v>
       </c>
       <c r="O153" s="8"/>
       <c r="P153" s="8"/>
@@ -12541,7 +12623,7 @@
         <v>2</v>
       </c>
       <c r="N154" s="8">
-        <v>487</v>
+        <v>0</v>
       </c>
       <c r="O154" s="8"/>
       <c r="P154" s="8"/>
@@ -12618,7 +12700,7 @@
         <v>19</v>
       </c>
       <c r="F156" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G156" s="8" t="s">
         <v>1062</v>
@@ -12771,7 +12853,7 @@
         <v>19</v>
       </c>
       <c r="F159" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G159" s="8" t="s">
         <v>1062</v>
@@ -12847,7 +12929,7 @@
         <v>3</v>
       </c>
       <c r="N160" s="8">
-        <v>517</v>
+        <v>0</v>
       </c>
       <c r="O160" s="8"/>
       <c r="P160" s="8"/>
@@ -12898,7 +12980,7 @@
         <v>5</v>
       </c>
       <c r="N161" s="8">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="O161" s="8"/>
       <c r="P161" s="8"/>
@@ -12924,7 +13006,7 @@
         <v>19</v>
       </c>
       <c r="F162" s="8" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="G162" s="8" t="s">
         <v>1062</v>
@@ -12933,7 +13015,7 @@
         <v>13</v>
       </c>
       <c r="I162" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J162" s="8">
         <v>0</v>
@@ -12946,10 +13028,10 @@
       </c>
       <c r="M162" s="8">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N162" s="8">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="O162" s="8"/>
       <c r="P162" s="8"/>
@@ -13000,7 +13082,7 @@
         <v>4</v>
       </c>
       <c r="N163" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O163" s="8"/>
       <c r="P163" s="8"/>
@@ -13086,7 +13168,7 @@
         <v>12</v>
       </c>
       <c r="I165" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J165" s="8">
         <v>0</v>
@@ -13099,10 +13181,10 @@
       </c>
       <c r="M165" s="8">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N165" s="8">
-        <v>1157</v>
+        <v>1152</v>
       </c>
       <c r="O165" s="8"/>
       <c r="P165" s="8"/>
@@ -13128,7 +13210,7 @@
         <v>19</v>
       </c>
       <c r="F166" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G166" s="8" t="s">
         <v>1062</v>
@@ -13239,23 +13321,23 @@
         <v>14</v>
       </c>
       <c r="I168" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J168" s="8">
         <v>0</v>
       </c>
       <c r="K168" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L168" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M168" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N168" s="8">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="O168" s="8"/>
       <c r="P168" s="8"/>
@@ -13332,7 +13414,7 @@
         <v>19</v>
       </c>
       <c r="F170" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G170" s="8" t="s">
         <v>1062</v>
@@ -13341,7 +13423,7 @@
         <v>14</v>
       </c>
       <c r="I170" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J170" s="8">
         <v>0</v>
@@ -13354,10 +13436,10 @@
       </c>
       <c r="M170" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N170" s="8">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="O170" s="8"/>
       <c r="P170" s="8"/>
@@ -13443,7 +13525,7 @@
         <v>14</v>
       </c>
       <c r="I172" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J172" s="8">
         <v>0</v>
@@ -13456,10 +13538,10 @@
       </c>
       <c r="M172" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N172" s="8">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O172" s="8"/>
       <c r="P172" s="8"/>
@@ -13494,7 +13576,7 @@
         <v>14</v>
       </c>
       <c r="I173" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J173" s="8">
         <v>0</v>
@@ -13507,7 +13589,7 @@
       </c>
       <c r="M173" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N173" s="8">
         <v>552</v>
@@ -13663,7 +13745,7 @@
         <v>2</v>
       </c>
       <c r="N176" s="8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O176" s="8"/>
       <c r="P176" s="8"/>
@@ -13816,7 +13898,7 @@
         <v>2</v>
       </c>
       <c r="N179" s="8">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="O179" s="8"/>
       <c r="P179" s="8"/>
@@ -13860,14 +13942,14 @@
         <v>0</v>
       </c>
       <c r="L180" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M180" s="8">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N180" s="8">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="O180" s="8"/>
       <c r="P180" s="8"/>
@@ -13918,7 +14000,7 @@
         <v>3</v>
       </c>
       <c r="N181" s="8">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O181" s="8"/>
       <c r="P181" s="8"/>
@@ -14004,7 +14086,7 @@
         <v>12</v>
       </c>
       <c r="I183" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J183" s="8">
         <v>0</v>
@@ -14017,10 +14099,10 @@
       </c>
       <c r="M183" s="8">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N183" s="8">
-        <v>395</v>
+        <v>420</v>
       </c>
       <c r="O183" s="8"/>
       <c r="P183" s="8"/>
@@ -14106,20 +14188,20 @@
         <v>12</v>
       </c>
       <c r="I185" s="8">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="J185" s="8">
         <v>0</v>
       </c>
       <c r="K185" s="8">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="L185" s="8">
         <v>0</v>
       </c>
       <c r="M185" s="8">
         <f t="shared" si="2"/>
-        <v>482</v>
+        <v>460</v>
       </c>
       <c r="N185" s="8">
         <v>1659</v>
@@ -14157,7 +14239,7 @@
         <v>12</v>
       </c>
       <c r="I186" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J186" s="8">
         <v>0</v>
@@ -14170,10 +14252,10 @@
       </c>
       <c r="M186" s="8">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N186" s="8">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="O186" s="8"/>
       <c r="P186" s="8"/>
@@ -14224,7 +14306,7 @@
         <v>1</v>
       </c>
       <c r="N187" s="8">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O187" s="8"/>
       <c r="P187" s="8"/>
@@ -14275,7 +14357,7 @@
         <v>5</v>
       </c>
       <c r="N188" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O188" s="8"/>
       <c r="P188" s="8"/>
@@ -14361,7 +14443,7 @@
         <v>12</v>
       </c>
       <c r="I190" s="8">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J190" s="8">
         <v>0</v>
@@ -14374,10 +14456,10 @@
       </c>
       <c r="M190" s="8">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N190" s="8">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="O190" s="8"/>
       <c r="P190" s="8"/>
@@ -14428,7 +14510,7 @@
         <v>7</v>
       </c>
       <c r="N191" s="8">
-        <v>683</v>
+        <v>671</v>
       </c>
       <c r="O191" s="8"/>
       <c r="P191" s="8"/>
@@ -14530,7 +14612,7 @@
         <v>3</v>
       </c>
       <c r="N193" s="8">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="O193" s="8"/>
       <c r="P193" s="8"/>
@@ -14565,23 +14647,23 @@
         <v>15</v>
       </c>
       <c r="I194" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J194" s="8">
         <v>0</v>
       </c>
       <c r="K194" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L194" s="8">
         <v>0</v>
       </c>
       <c r="M194" s="8">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N194" s="8">
-        <v>204</v>
+        <v>250</v>
       </c>
       <c r="O194" s="8"/>
       <c r="P194" s="8"/>
@@ -14718,7 +14800,7 @@
         <v>12</v>
       </c>
       <c r="I197" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J197" s="8">
         <v>0</v>
@@ -14727,14 +14809,14 @@
         <v>0</v>
       </c>
       <c r="L197" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M197" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N197" s="8">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="O197" s="8"/>
       <c r="P197" s="8"/>
@@ -14811,7 +14893,7 @@
         <v>19</v>
       </c>
       <c r="F199" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G199" s="8" t="s">
         <v>1062</v>
@@ -14913,7 +14995,7 @@
         <v>19</v>
       </c>
       <c r="F201" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G201" s="8" t="s">
         <v>1062</v>
@@ -15066,7 +15148,7 @@
         <v>19</v>
       </c>
       <c r="F204" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G204" s="8" t="s">
         <v>1062</v>
@@ -15075,7 +15157,7 @@
         <v>13</v>
       </c>
       <c r="I204" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J204" s="8">
         <v>0</v>
@@ -15088,7 +15170,7 @@
       </c>
       <c r="M204" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N204" s="8">
         <v>0</v>
@@ -15117,7 +15199,7 @@
         <v>19</v>
       </c>
       <c r="F205" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G205" s="8" t="s">
         <v>1062</v>
@@ -15244,7 +15326,7 @@
         <v>4</v>
       </c>
       <c r="N207" s="8">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="O207" s="8"/>
       <c r="P207" s="8"/>
@@ -15288,14 +15370,14 @@
         <v>0</v>
       </c>
       <c r="L208" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M208" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N208" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O208" s="8"/>
       <c r="P208" s="8"/>
@@ -15321,7 +15403,7 @@
         <v>19</v>
       </c>
       <c r="F209" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G209" s="8" t="s">
         <v>1062</v>
@@ -15330,13 +15412,13 @@
         <v>12</v>
       </c>
       <c r="I209" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J209" s="8">
         <v>0</v>
       </c>
       <c r="K209" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L209" s="8">
         <v>0</v>
@@ -15372,7 +15454,7 @@
         <v>19</v>
       </c>
       <c r="F210" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G210" s="8" t="s">
         <v>1062</v>
@@ -15423,7 +15505,7 @@
         <v>19</v>
       </c>
       <c r="F211" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G211" s="8" t="s">
         <v>1062</v>
@@ -15448,7 +15530,7 @@
         <v>3</v>
       </c>
       <c r="N211" s="8">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="O211" s="8"/>
       <c r="P211" s="8"/>
@@ -15585,23 +15667,23 @@
         <v>14</v>
       </c>
       <c r="I214" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J214" s="8">
         <v>0</v>
       </c>
       <c r="K214" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L214" s="8">
         <v>0</v>
       </c>
       <c r="M214" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N214" s="8">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="O214" s="8"/>
       <c r="P214" s="8"/>
@@ -15754,7 +15836,7 @@
         <v>3</v>
       </c>
       <c r="N217" s="8">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="O217" s="8"/>
       <c r="P217" s="8"/>
@@ -15805,7 +15887,7 @@
         <v>4</v>
       </c>
       <c r="N218" s="8">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="O218" s="8"/>
       <c r="P218" s="8"/>
@@ -15856,7 +15938,7 @@
         <v>4</v>
       </c>
       <c r="N219" s="8">
-        <v>377</v>
+        <v>0</v>
       </c>
       <c r="O219" s="8"/>
       <c r="P219" s="8"/>
@@ -15882,7 +15964,7 @@
         <v>19</v>
       </c>
       <c r="F220" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G220" s="8" t="s">
         <v>1062</v>
@@ -15993,13 +16075,13 @@
         <v>16</v>
       </c>
       <c r="I222" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J222" s="8">
         <v>0</v>
       </c>
       <c r="K222" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L222" s="8">
         <v>0</v>
@@ -16009,7 +16091,7 @@
         <v>2</v>
       </c>
       <c r="N222" s="8">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O222" s="8"/>
       <c r="P222" s="8"/>
@@ -16044,23 +16126,23 @@
         <v>15</v>
       </c>
       <c r="I223" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J223" s="8">
         <v>0</v>
       </c>
       <c r="K223" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L223" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M223" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N223" s="8">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="O223" s="8"/>
       <c r="P223" s="8"/>
@@ -16086,7 +16168,7 @@
         <v>19</v>
       </c>
       <c r="F224" s="8" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="G224" s="8" t="s">
         <v>1062</v>
@@ -16104,14 +16186,14 @@
         <v>0</v>
       </c>
       <c r="L224" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M224" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N224" s="8">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O224" s="8"/>
       <c r="P224" s="8"/>
@@ -16162,7 +16244,7 @@
         <v>3</v>
       </c>
       <c r="N225" s="8">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="O225" s="8"/>
       <c r="P225" s="8"/>
@@ -16213,7 +16295,7 @@
         <v>0</v>
       </c>
       <c r="N226" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O226" s="8"/>
       <c r="P226" s="8"/>
@@ -16341,7 +16423,7 @@
         <v>19</v>
       </c>
       <c r="F229" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G229" s="8" t="s">
         <v>1062</v>
@@ -16356,17 +16438,17 @@
         <v>0</v>
       </c>
       <c r="K229" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L229" s="8">
         <v>0</v>
       </c>
       <c r="M229" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N229" s="8">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="O229" s="8"/>
       <c r="P229" s="8"/>
@@ -16410,14 +16492,14 @@
         <v>0</v>
       </c>
       <c r="L230" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M230" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N230" s="8">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="O230" s="8"/>
       <c r="P230" s="8"/>
@@ -16519,7 +16601,7 @@
         <v>7</v>
       </c>
       <c r="N232" s="8">
-        <v>401</v>
+        <v>383</v>
       </c>
       <c r="O232" s="8"/>
       <c r="P232" s="8"/>
@@ -16560,17 +16642,17 @@
         <v>0</v>
       </c>
       <c r="K233" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L233" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M233" s="8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N233" s="8">
-        <v>524</v>
+        <v>0</v>
       </c>
       <c r="O233" s="8"/>
       <c r="P233" s="8"/>
@@ -16596,7 +16678,7 @@
         <v>19</v>
       </c>
       <c r="F234" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G234" s="8" t="s">
         <v>1062</v>
@@ -16621,7 +16703,7 @@
         <v>2</v>
       </c>
       <c r="N234" s="8">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O234" s="8"/>
       <c r="P234" s="8"/>
@@ -16672,7 +16754,7 @@
         <v>2</v>
       </c>
       <c r="N235" s="8">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="O235" s="8"/>
       <c r="P235" s="8"/>
@@ -16749,7 +16831,7 @@
         <v>19</v>
       </c>
       <c r="F237" s="8" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="G237" s="8" t="s">
         <v>1062</v>
@@ -16758,7 +16840,7 @@
         <v>12</v>
       </c>
       <c r="I237" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J237" s="8">
         <v>0</v>
@@ -16767,14 +16849,14 @@
         <v>0</v>
       </c>
       <c r="L237" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M237" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N237" s="8">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="O237" s="8"/>
       <c r="P237" s="8"/>
@@ -16809,7 +16891,7 @@
         <v>14</v>
       </c>
       <c r="I238" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J238" s="8">
         <v>0</v>
@@ -16822,10 +16904,10 @@
       </c>
       <c r="M238" s="8">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N238" s="8">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="O238" s="8"/>
       <c r="P238" s="8"/>
@@ -16851,7 +16933,7 @@
         <v>19</v>
       </c>
       <c r="F239" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G239" s="8" t="s">
         <v>1062</v>
@@ -16876,7 +16958,7 @@
         <v>3</v>
       </c>
       <c r="N239" s="8">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O239" s="8"/>
       <c r="P239" s="8"/>
@@ -16917,17 +16999,17 @@
         <v>0</v>
       </c>
       <c r="K240" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L240" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M240" s="8">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N240" s="8">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="O240" s="8"/>
       <c r="P240" s="8"/>
@@ -16978,7 +17060,7 @@
         <v>3</v>
       </c>
       <c r="N241" s="8">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="O241" s="8"/>
       <c r="P241" s="8"/>
@@ -17004,7 +17086,7 @@
         <v>19</v>
       </c>
       <c r="F242" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G242" s="8" t="s">
         <v>1062</v>
@@ -17029,7 +17111,7 @@
         <v>3</v>
       </c>
       <c r="N242" s="8">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="O242" s="8"/>
       <c r="P242" s="8"/>
@@ -17055,7 +17137,7 @@
         <v>19</v>
       </c>
       <c r="F243" s="8" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="G243" s="8" t="s">
         <v>1062</v>
@@ -17064,23 +17146,23 @@
         <v>15</v>
       </c>
       <c r="I243" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J243" s="8">
         <v>0</v>
       </c>
       <c r="K243" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L243" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M243" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N243" s="8">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="O243" s="8"/>
       <c r="P243" s="8"/>
@@ -17233,7 +17315,7 @@
         <v>3</v>
       </c>
       <c r="N246" s="8">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="O246" s="8"/>
       <c r="P246" s="8"/>
@@ -17259,7 +17341,7 @@
         <v>19</v>
       </c>
       <c r="F247" s="8" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="G247" s="8" t="s">
         <v>1062</v>
@@ -17274,14 +17356,14 @@
         <v>0</v>
       </c>
       <c r="K247" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L247" s="8">
         <v>0</v>
       </c>
       <c r="M247" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N247" s="8">
         <v>274</v>
@@ -17319,7 +17401,7 @@
         <v>12</v>
       </c>
       <c r="I248" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J248" s="8">
         <v>0</v>
@@ -17332,7 +17414,7 @@
       </c>
       <c r="M248" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N248" s="8">
         <v>0</v>
@@ -17412,7 +17494,7 @@
         <v>19</v>
       </c>
       <c r="F250" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G250" s="8" t="s">
         <v>1062</v>
@@ -17421,7 +17503,7 @@
         <v>12</v>
       </c>
       <c r="I250" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J250" s="8">
         <v>0</v>
@@ -17434,10 +17516,10 @@
       </c>
       <c r="M250" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N250" s="8">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="O250" s="8"/>
       <c r="P250" s="8"/>
@@ -17463,7 +17545,7 @@
         <v>19</v>
       </c>
       <c r="F251" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G251" s="8" t="s">
         <v>1062</v>
@@ -17514,7 +17596,7 @@
         <v>19</v>
       </c>
       <c r="F252" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G252" s="8" t="s">
         <v>1062</v>
@@ -17565,7 +17647,7 @@
         <v>19</v>
       </c>
       <c r="F253" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G253" s="8" t="s">
         <v>1062</v>
@@ -17590,7 +17672,7 @@
         <v>2</v>
       </c>
       <c r="N253" s="8">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="O253" s="8"/>
       <c r="P253" s="8"/>
@@ -17616,7 +17698,7 @@
         <v>19</v>
       </c>
       <c r="F254" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G254" s="8" t="s">
         <v>1062</v>
@@ -17641,7 +17723,7 @@
         <v>2</v>
       </c>
       <c r="N254" s="8">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O254" s="8"/>
       <c r="P254" s="8"/>
@@ -17692,7 +17774,7 @@
         <v>3</v>
       </c>
       <c r="N255" s="8">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="O255" s="8"/>
       <c r="P255" s="8"/>
@@ -17743,7 +17825,7 @@
         <v>3</v>
       </c>
       <c r="N256" s="8">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="O256" s="8"/>
       <c r="P256" s="8"/>
@@ -17794,7 +17876,7 @@
         <v>4</v>
       </c>
       <c r="N257" s="8">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="O257" s="8"/>
       <c r="P257" s="8"/>
@@ -17835,14 +17917,14 @@
         <v>0</v>
       </c>
       <c r="K258" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L258" s="8">
         <v>0</v>
       </c>
       <c r="M258" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N258" s="8">
         <v>66</v>
@@ -17896,7 +17978,7 @@
         <v>3</v>
       </c>
       <c r="N259" s="8">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="O259" s="8"/>
       <c r="P259" s="8"/>
@@ -17931,23 +18013,23 @@
         <v>13</v>
       </c>
       <c r="I260" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J260" s="8">
         <v>0</v>
       </c>
       <c r="K260" s="8">
+        <v>0</v>
+      </c>
+      <c r="L260" s="8">
         <v>3</v>
-      </c>
-      <c r="L260" s="8">
-        <v>0</v>
       </c>
       <c r="M260" s="8">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N260" s="8">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="O260" s="8"/>
       <c r="P260" s="8"/>
@@ -17982,7 +18064,7 @@
         <v>12</v>
       </c>
       <c r="I261" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J261" s="8">
         <v>0</v>
@@ -17991,14 +18073,14 @@
         <v>0</v>
       </c>
       <c r="L261" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M261" s="8">
         <f t="shared" si="4"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="N261" s="8">
-        <v>558</v>
+        <v>533</v>
       </c>
       <c r="O261" s="8"/>
       <c r="P261" s="8"/>
@@ -18042,14 +18124,14 @@
         <v>0</v>
       </c>
       <c r="L262" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M262" s="8">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N262" s="8">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="O262" s="8"/>
       <c r="P262" s="8"/>
@@ -18084,7 +18166,7 @@
         <v>12</v>
       </c>
       <c r="I263" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J263" s="8">
         <v>0</v>
@@ -18097,10 +18179,10 @@
       </c>
       <c r="M263" s="8">
         <f t="shared" si="4"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N263" s="8">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="O263" s="8"/>
       <c r="P263" s="8"/>
@@ -18202,7 +18284,7 @@
         <v>0</v>
       </c>
       <c r="N265" s="8">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O265" s="8"/>
       <c r="P265" s="8"/>
@@ -18228,7 +18310,7 @@
         <v>19</v>
       </c>
       <c r="F266" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G266" s="8" t="s">
         <v>1062</v>
@@ -18645,13 +18727,13 @@
         <v>16</v>
       </c>
       <c r="I274" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J274" s="8">
         <v>0</v>
       </c>
       <c r="K274" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L274" s="8">
         <v>0</v>
@@ -18661,7 +18743,7 @@
         <v>3</v>
       </c>
       <c r="N274" s="8">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="O274" s="8"/>
       <c r="P274" s="8"/>
@@ -18712,7 +18794,7 @@
         <v>2</v>
       </c>
       <c r="N275" s="8">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O275" s="8"/>
       <c r="P275" s="8"/>
@@ -18763,7 +18845,7 @@
         <v>3</v>
       </c>
       <c r="N276" s="8">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="O276" s="8"/>
       <c r="P276" s="8"/>
@@ -18789,7 +18871,7 @@
         <v>19</v>
       </c>
       <c r="F277" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G277" s="8" t="s">
         <v>1062</v>
@@ -18849,23 +18931,23 @@
         <v>12</v>
       </c>
       <c r="I278" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J278" s="8">
         <v>0</v>
       </c>
       <c r="K278" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L278" s="8">
         <v>0</v>
       </c>
       <c r="M278" s="8">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N278" s="8">
-        <v>1310</v>
+        <v>1283</v>
       </c>
       <c r="O278" s="8"/>
       <c r="P278" s="8"/>
@@ -18891,7 +18973,7 @@
         <v>19</v>
       </c>
       <c r="F279" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G279" s="8" t="s">
         <v>1062</v>
@@ -18900,7 +18982,7 @@
         <v>13</v>
       </c>
       <c r="I279" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J279" s="8">
         <v>0</v>
@@ -18913,7 +18995,7 @@
       </c>
       <c r="M279" s="8">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N279" s="8">
         <v>0</v>
@@ -18951,7 +19033,7 @@
         <v>16</v>
       </c>
       <c r="I280" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J280" s="8">
         <v>0</v>
@@ -18964,7 +19046,7 @@
       </c>
       <c r="M280" s="8">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N280" s="8">
         <v>67</v>
@@ -19018,7 +19100,7 @@
         <v>2</v>
       </c>
       <c r="N281" s="8">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="O281" s="8"/>
       <c r="P281" s="8"/>
@@ -19104,7 +19186,7 @@
         <v>12</v>
       </c>
       <c r="I283" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J283" s="8">
         <v>0</v>
@@ -19117,7 +19199,7 @@
       </c>
       <c r="M283" s="8">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N283" s="8">
         <v>0</v>
@@ -19155,7 +19237,7 @@
         <v>12</v>
       </c>
       <c r="I284" s="8">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="J284" s="8">
         <v>0</v>
@@ -19168,7 +19250,7 @@
       </c>
       <c r="M284" s="8">
         <f t="shared" si="4"/>
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="N284" s="8">
         <v>0</v>
@@ -19222,7 +19304,7 @@
         <v>2</v>
       </c>
       <c r="N285" s="8">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="O285" s="8"/>
       <c r="P285" s="8"/>
@@ -19273,7 +19355,7 @@
         <v>4</v>
       </c>
       <c r="N286" s="8">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="O286" s="8"/>
       <c r="P286" s="8"/>
@@ -19324,7 +19406,7 @@
         <v>9</v>
       </c>
       <c r="N287" s="8">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="O287" s="8"/>
       <c r="P287" s="8"/>
@@ -19375,7 +19457,7 @@
         <v>4</v>
       </c>
       <c r="N288" s="8">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="O288" s="8"/>
       <c r="P288" s="8"/>
@@ -19410,7 +19492,7 @@
         <v>14</v>
       </c>
       <c r="I289" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J289" s="8">
         <v>0</v>
@@ -19423,10 +19505,10 @@
       </c>
       <c r="M289" s="8">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N289" s="8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O289" s="8"/>
       <c r="P289" s="8"/>
@@ -19452,7 +19534,7 @@
         <v>19</v>
       </c>
       <c r="F290" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G290" s="8" t="s">
         <v>1062</v>
@@ -19477,7 +19559,7 @@
         <v>0</v>
       </c>
       <c r="N290" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O290" s="8"/>
       <c r="P290" s="8"/>
@@ -19512,23 +19594,23 @@
         <v>12</v>
       </c>
       <c r="I291" s="8">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J291" s="8">
         <v>0</v>
       </c>
       <c r="K291" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L291" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M291" s="8">
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
       <c r="N291" s="8">
-        <v>1565</v>
+        <v>1451</v>
       </c>
       <c r="O291" s="8"/>
       <c r="P291" s="8"/>
@@ -19579,7 +19661,7 @@
         <v>2</v>
       </c>
       <c r="N292" s="8">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O292" s="8"/>
       <c r="P292" s="8"/>
@@ -19605,7 +19687,7 @@
         <v>19</v>
       </c>
       <c r="F293" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G293" s="8" t="s">
         <v>1062</v>
@@ -19656,7 +19738,7 @@
         <v>19</v>
       </c>
       <c r="F294" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G294" s="8" t="s">
         <v>1062</v>
@@ -19665,23 +19747,23 @@
         <v>12</v>
       </c>
       <c r="I294" s="8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J294" s="8">
         <v>0</v>
       </c>
       <c r="K294" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L294" s="8">
         <v>0</v>
       </c>
       <c r="M294" s="8">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N294" s="8">
-        <v>1349</v>
+        <v>1333</v>
       </c>
       <c r="O294" s="8"/>
       <c r="P294" s="8"/>
@@ -19809,7 +19891,7 @@
         <v>19</v>
       </c>
       <c r="F297" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G297" s="8" t="s">
         <v>1062</v>
@@ -19860,7 +19942,7 @@
         <v>19</v>
       </c>
       <c r="F298" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G298" s="8" t="s">
         <v>1062</v>
@@ -19971,7 +20053,7 @@
         <v>13</v>
       </c>
       <c r="I300" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J300" s="8">
         <v>0</v>
@@ -19984,7 +20066,7 @@
       </c>
       <c r="M300" s="8">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N300" s="8">
         <v>0</v>
@@ -20133,14 +20215,14 @@
         <v>0</v>
       </c>
       <c r="L303" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M303" s="8">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N303" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O303" s="8"/>
       <c r="P303" s="8"/>
@@ -20175,7 +20257,7 @@
         <v>13</v>
       </c>
       <c r="I304" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J304" s="8">
         <v>0</v>
@@ -20188,7 +20270,7 @@
       </c>
       <c r="M304" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N304" s="8">
         <v>8</v>
@@ -20242,7 +20324,7 @@
         <v>8</v>
       </c>
       <c r="N305" s="8">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="O305" s="8"/>
       <c r="P305" s="8"/>
@@ -20293,7 +20375,7 @@
         <v>9</v>
       </c>
       <c r="N306" s="8">
-        <v>1004</v>
+        <v>985</v>
       </c>
       <c r="O306" s="8"/>
       <c r="P306" s="8"/>
@@ -20344,7 +20426,7 @@
         <v>11</v>
       </c>
       <c r="N307" s="8">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="O307" s="8"/>
       <c r="P307" s="8"/>
@@ -20395,7 +20477,7 @@
         <v>10</v>
       </c>
       <c r="N308" s="8">
-        <v>917</v>
+        <v>904</v>
       </c>
       <c r="O308" s="8"/>
       <c r="P308" s="8"/>
@@ -20650,7 +20732,7 @@
         <v>3</v>
       </c>
       <c r="N313" s="8">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="O313" s="8"/>
       <c r="P313" s="8"/>
@@ -20685,13 +20767,13 @@
         <v>12</v>
       </c>
       <c r="I314" s="8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J314" s="8">
         <v>0</v>
       </c>
       <c r="K314" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L314" s="8">
         <v>0</v>
@@ -20701,7 +20783,7 @@
         <v>11</v>
       </c>
       <c r="N314" s="8">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="O314" s="8"/>
       <c r="P314" s="8"/>
@@ -20752,7 +20834,7 @@
         <v>8</v>
       </c>
       <c r="N315" s="8">
-        <v>139</v>
+        <v>344</v>
       </c>
       <c r="O315" s="8"/>
       <c r="P315" s="8"/>
@@ -20803,7 +20885,7 @@
         <v>6</v>
       </c>
       <c r="N316" s="8">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="O316" s="8"/>
       <c r="P316" s="8"/>
@@ -20829,7 +20911,7 @@
         <v>19</v>
       </c>
       <c r="F317" s="8" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G317" s="8" t="s">
         <v>1062</v>
@@ -20838,23 +20920,23 @@
         <v>12</v>
       </c>
       <c r="I317" s="8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J317" s="8">
         <v>0</v>
       </c>
       <c r="K317" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L317" s="8">
         <v>0</v>
       </c>
       <c r="M317" s="8">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N317" s="8">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="O317" s="8"/>
       <c r="P317" s="8"/>
@@ -20895,17 +20977,17 @@
         <v>0</v>
       </c>
       <c r="K318" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L318" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M318" s="8">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="N318" s="8">
-        <v>536</v>
+        <v>470</v>
       </c>
       <c r="O318" s="8"/>
       <c r="P318" s="8"/>
@@ -20956,7 +21038,7 @@
         <v>4</v>
       </c>
       <c r="N319" s="8">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="O319" s="8"/>
       <c r="P319" s="8"/>
@@ -21007,7 +21089,7 @@
         <v>4</v>
       </c>
       <c r="N320" s="8">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="O320" s="8"/>
       <c r="P320" s="8"/>
@@ -21051,14 +21133,14 @@
         <v>0</v>
       </c>
       <c r="L321" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M321" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N321" s="8">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="O321" s="8"/>
       <c r="P321" s="8"/>
@@ -21262,7 +21344,7 @@
         <v>3</v>
       </c>
       <c r="N325" s="8">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="O325" s="8"/>
       <c r="P325" s="8"/>
@@ -21313,7 +21395,7 @@
         <v>3</v>
       </c>
       <c r="N326" s="8">
-        <v>1003</v>
+        <v>998</v>
       </c>
       <c r="O326" s="8"/>
       <c r="P326" s="8"/>
@@ -21415,7 +21497,7 @@
         <v>2</v>
       </c>
       <c r="N328" s="8">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O328" s="8"/>
       <c r="P328" s="8"/>
@@ -21466,7 +21548,7 @@
         <v>4</v>
       </c>
       <c r="N329" s="8">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="O329" s="8"/>
       <c r="P329" s="8"/>
@@ -21517,7 +21599,7 @@
         <v>2</v>
       </c>
       <c r="N330" s="8">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="O330" s="8"/>
       <c r="P330" s="8"/>
@@ -21670,7 +21752,7 @@
         <v>3</v>
       </c>
       <c r="N333" s="8">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="O333" s="8"/>
       <c r="P333" s="8"/>
@@ -21705,7 +21787,7 @@
         <v>13</v>
       </c>
       <c r="I334" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J334" s="8">
         <v>0</v>
@@ -21718,10 +21800,10 @@
       </c>
       <c r="M334" s="8">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N334" s="8">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="O334" s="8"/>
       <c r="P334" s="8"/>
@@ -21772,7 +21854,7 @@
         <v>2</v>
       </c>
       <c r="N335" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O335" s="8"/>
       <c r="P335" s="8"/>
@@ -21823,7 +21905,7 @@
         <v>4</v>
       </c>
       <c r="N336" s="8">
-        <v>567</v>
+        <v>0</v>
       </c>
       <c r="O336" s="8"/>
       <c r="P336" s="8"/>
@@ -21864,17 +21946,17 @@
         <v>0</v>
       </c>
       <c r="K337" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L337" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M337" s="8">
         <f t="shared" si="5"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N337" s="8">
-        <v>1192</v>
+        <v>1187</v>
       </c>
       <c r="O337" s="8"/>
       <c r="P337" s="8"/>
@@ -21909,13 +21991,13 @@
         <v>12</v>
       </c>
       <c r="I338" s="8">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J338" s="8">
         <v>0</v>
       </c>
       <c r="K338" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L338" s="8">
         <v>0</v>
@@ -21925,7 +22007,7 @@
         <v>13</v>
       </c>
       <c r="N338" s="8">
-        <v>1208</v>
+        <v>1197</v>
       </c>
       <c r="O338" s="8"/>
       <c r="P338" s="8"/>
@@ -21976,7 +22058,7 @@
         <v>3</v>
       </c>
       <c r="N339" s="8">
-        <v>840</v>
+        <v>827</v>
       </c>
       <c r="O339" s="8"/>
       <c r="P339" s="8"/>
@@ -22011,23 +22093,23 @@
         <v>14</v>
       </c>
       <c r="I340" s="8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J340" s="8">
         <v>0</v>
       </c>
       <c r="K340" s="8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L340" s="8">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M340" s="8">
         <f t="shared" si="5"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="N340" s="8">
-        <v>692</v>
+        <v>662</v>
       </c>
       <c r="O340" s="8"/>
       <c r="P340" s="8"/>
@@ -22191,7 +22273,7 @@
     </row>
     <row r="344" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="9" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B344" s="9" t="s">
         <v>1102</v>
@@ -22215,7 +22297,7 @@
         <v>12</v>
       </c>
       <c r="I344" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J344" s="8">
         <v>0</v>
@@ -22228,7 +22310,7 @@
       </c>
       <c r="M344" s="8">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N344" s="8">
         <v>0</v>
@@ -22242,7 +22324,7 @@
     </row>
     <row r="345" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="9" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="B345" s="9" t="s">
         <v>1103</v>
@@ -22266,7 +22348,7 @@
         <v>12</v>
       </c>
       <c r="I345" s="8">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="J345" s="8">
         <v>0</v>
@@ -22279,7 +22361,7 @@
       </c>
       <c r="M345" s="8">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="N345" s="8">
         <v>0</v>
@@ -22293,7 +22375,7 @@
     </row>
     <row r="346" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="9" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="B346" s="9" t="s">
         <v>1104</v>
@@ -22344,7 +22426,7 @@
     </row>
     <row r="347" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="9" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="B347" s="9" t="s">
         <v>1105</v>
@@ -22368,23 +22450,23 @@
         <v>13</v>
       </c>
       <c r="I347" s="8">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J347" s="8">
         <v>0</v>
       </c>
       <c r="K347" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L347" s="8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M347" s="8">
         <f t="shared" si="5"/>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N347" s="8">
-        <v>483</v>
+        <v>465</v>
       </c>
       <c r="O347" s="8"/>
       <c r="P347" s="9"/>
@@ -22395,7 +22477,7 @@
     </row>
     <row r="348" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="9" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="B348" s="9" t="s">
         <v>1106</v>
@@ -22446,7 +22528,7 @@
     </row>
     <row r="349" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="9" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B349" s="9" t="s">
         <v>1107</v>
@@ -22497,7 +22579,7 @@
     </row>
     <row r="350" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="9" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B350" s="9" t="s">
         <v>1108</v>
@@ -22512,7 +22594,7 @@
         <v>19</v>
       </c>
       <c r="F350" s="9" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G350" s="8" t="s">
         <v>1062</v>
@@ -22548,7 +22630,7 @@
     </row>
     <row r="351" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="9" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="B351" s="9" t="s">
         <v>1109</v>
@@ -22563,7 +22645,7 @@
         <v>19</v>
       </c>
       <c r="F351" s="9" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G351" s="8" t="s">
         <v>1062</v>
@@ -22599,7 +22681,7 @@
     </row>
     <row r="352" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="9" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="B352" s="9" t="s">
         <v>1110</v>
@@ -22639,7 +22721,7 @@
         <v>1</v>
       </c>
       <c r="N352" s="8">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="O352" s="8"/>
       <c r="P352" s="9"/>
@@ -22650,7 +22732,7 @@
     </row>
     <row r="353" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="9" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B353" s="9" t="s">
         <v>1111</v>
@@ -22701,7 +22783,7 @@
     </row>
     <row r="354" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="9" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B354" s="9" t="s">
         <v>1112</v>
@@ -22752,7 +22834,7 @@
     </row>
     <row r="355" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="9" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B355" s="9" t="s">
         <v>1113</v>
@@ -22782,14 +22864,14 @@
         <v>0</v>
       </c>
       <c r="K355" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L355" s="8">
         <v>0</v>
       </c>
       <c r="M355" s="8">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N355" s="8">
         <v>0</v>
@@ -22803,7 +22885,7 @@
     </row>
     <row r="356" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="9" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="B356" s="9" t="s">
         <v>1114</v>
@@ -22854,7 +22936,7 @@
     </row>
     <row r="357" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="9" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="B357" s="9" t="s">
         <v>1115</v>
@@ -22905,7 +22987,7 @@
     </row>
     <row r="358" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="9" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="B358" s="9" t="s">
         <v>1116</v>
@@ -22920,7 +23002,7 @@
         <v>19</v>
       </c>
       <c r="F358" s="9" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G358" s="8" t="s">
         <v>1062</v>
@@ -22956,7 +23038,7 @@
     </row>
     <row r="359" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="9" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B359" s="9" t="s">
         <v>1117</v>
@@ -23007,7 +23089,7 @@
     </row>
     <row r="360" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="9" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="B360" s="9" t="s">
         <v>1118</v>
@@ -23058,7 +23140,7 @@
     </row>
     <row r="361" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="9" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="B361" s="9" t="s">
         <v>1119</v>
@@ -23109,7 +23191,7 @@
     </row>
     <row r="362" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="9" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="B362" s="9" t="s">
         <v>1120</v>
@@ -23160,7 +23242,7 @@
     </row>
     <row r="363" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="9" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="B363" s="9" t="s">
         <v>1121</v>
@@ -23184,7 +23266,7 @@
         <v>12</v>
       </c>
       <c r="I363" s="8">
-        <v>611</v>
+        <v>598</v>
       </c>
       <c r="J363" s="8">
         <v>0</v>
@@ -23197,7 +23279,7 @@
       </c>
       <c r="M363" s="8">
         <f t="shared" si="5"/>
-        <v>611</v>
+        <v>598</v>
       </c>
       <c r="N363" s="8">
         <v>1318</v>
@@ -23211,7 +23293,7 @@
     </row>
     <row r="364" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="9" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="B364" s="9" t="s">
         <v>1122</v>
@@ -23262,7 +23344,7 @@
     </row>
     <row r="365" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="9" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="B365" s="9" t="s">
         <v>1123</v>
@@ -23277,7 +23359,7 @@
         <v>19</v>
       </c>
       <c r="F365" s="9" t="s">
-        <v>1133</v>
+        <v>1068</v>
       </c>
       <c r="G365" s="8" t="s">
         <v>1061</v>
@@ -23313,7 +23395,7 @@
     </row>
     <row r="366" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="9" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="B366" s="9" t="s">
         <v>1124</v>
@@ -23364,7 +23446,7 @@
     </row>
     <row r="367" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" s="9" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B367" s="9" t="s">
         <v>1125</v>
@@ -23388,7 +23470,7 @@
         <v>12</v>
       </c>
       <c r="I367" s="8">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J367" s="8">
         <v>0</v>
@@ -23401,7 +23483,7 @@
       </c>
       <c r="M367" s="8">
         <f t="shared" si="5"/>
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="N367" s="8">
         <v>0</v>
@@ -23415,7 +23497,7 @@
     </row>
     <row r="368" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A368" s="9" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B368" s="9" t="s">
         <v>1126</v>
@@ -23445,17 +23527,17 @@
         <v>0</v>
       </c>
       <c r="K368" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L368" s="8">
         <v>0</v>
       </c>
       <c r="M368" s="8">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N368" s="8">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O368" s="8"/>
       <c r="P368" s="9"/>
@@ -23466,7 +23548,7 @@
     </row>
     <row r="369" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A369" s="9" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="B369" s="9" t="s">
         <v>1127</v>
@@ -23517,7 +23599,7 @@
     </row>
     <row r="370" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A370" s="9" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B370" s="9" t="s">
         <v>1128</v>
@@ -23568,7 +23650,7 @@
     </row>
     <row r="371" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A371" s="9" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B371" s="9" t="s">
         <v>1129</v>
@@ -23608,7 +23690,7 @@
         <v>3</v>
       </c>
       <c r="N371" s="8">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="O371" s="8"/>
       <c r="P371" s="9"/>
@@ -23619,7 +23701,7 @@
     </row>
     <row r="372" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A372" s="9" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="B372" s="9" t="s">
         <v>1130</v>
@@ -23670,7 +23752,7 @@
     </row>
     <row r="373" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A373" s="9" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="B373" s="9" t="s">
         <v>1131</v>
@@ -23721,7 +23803,7 @@
     </row>
     <row r="374" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A374" s="9" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="B374" s="9" t="s">
         <v>1132</v>
@@ -23772,13 +23854,13 @@
     </row>
     <row r="375" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A375" s="9" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="B375" s="9" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="C375" s="9" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="D375" s="8" t="s">
         <v>20</v>
@@ -23823,13 +23905,13 @@
     </row>
     <row r="376" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A376" s="9" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="B376" s="9" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="C376" s="9" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="D376" s="8" t="s">
         <v>20</v>
@@ -23874,13 +23956,13 @@
     </row>
     <row r="377" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A377" s="9" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="B377" s="9" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="C377" s="9" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="D377" s="8" t="s">
         <v>30</v>
@@ -23925,13 +24007,13 @@
     </row>
     <row r="378" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A378" s="9" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B378" s="9" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="C378" s="9" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="D378" s="8" t="s">
         <v>30</v>
@@ -23976,13 +24058,13 @@
     </row>
     <row r="379" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A379" s="9" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="B379" s="9" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="C379" s="9" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="D379" s="8" t="s">
         <v>75</v>
@@ -24027,13 +24109,13 @@
     </row>
     <row r="380" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A380" s="9" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="B380" s="9" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="C380" s="9" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="D380" s="8" t="s">
         <v>30</v>
@@ -24042,7 +24124,7 @@
         <v>19</v>
       </c>
       <c r="F380" s="9" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G380" s="8" t="s">
         <v>1062</v>
@@ -24078,13 +24160,13 @@
     </row>
     <row r="381" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A381" s="9" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="B381" s="9" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="C381" s="9" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="D381" s="8" t="s">
         <v>30</v>
@@ -24093,7 +24175,7 @@
         <v>19</v>
       </c>
       <c r="F381" s="9" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G381" s="8" t="s">
         <v>1062</v>
@@ -24129,13 +24211,13 @@
     </row>
     <row r="382" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A382" s="9" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="B382" s="9" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="C382" s="9" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="D382" s="8" t="s">
         <v>52</v>
@@ -24180,13 +24262,13 @@
     </row>
     <row r="383" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A383" s="9" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B383" s="9" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="C383" s="9" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="D383" s="8" t="s">
         <v>52</v>
@@ -24231,13 +24313,13 @@
     </row>
     <row r="384" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A384" s="9" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="B384" s="9" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="C384" s="9" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="D384" s="8" t="s">
         <v>418</v>
@@ -24255,7 +24337,7 @@
         <v>12</v>
       </c>
       <c r="I384" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J384" s="8">
         <v>0</v>
@@ -24264,14 +24346,14 @@
         <v>0</v>
       </c>
       <c r="L384" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M384" s="8">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N384" s="8">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="O384" s="8"/>
       <c r="P384" s="9"/>
@@ -24282,13 +24364,13 @@
     </row>
     <row r="385" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A385" s="7" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="B385" s="7" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="C385" s="7" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="D385" s="7" t="s">
         <v>20</v>
@@ -24306,7 +24388,7 @@
         <v>12</v>
       </c>
       <c r="I385" s="8">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J385" s="8">
         <v>0</v>
@@ -24319,7 +24401,7 @@
       </c>
       <c r="M385" s="8">
         <f t="shared" si="5"/>
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N385" s="8">
         <v>257</v>
@@ -24333,13 +24415,13 @@
     </row>
     <row r="386" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A386" s="7" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="B386" s="7" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="C386" s="7" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="D386" s="7" t="s">
         <v>418</v>
@@ -24384,13 +24466,13 @@
     </row>
     <row r="387" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A387" s="7" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="B387" s="7" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="C387" s="7" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="D387" s="7" t="s">
         <v>62</v>
@@ -24435,13 +24517,13 @@
     </row>
     <row r="388" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A388" s="7" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="B388" s="7" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C388" s="7" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D388" s="7" t="s">
         <v>62</v>
@@ -24486,13 +24568,13 @@
     </row>
     <row r="389" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A389" s="7" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="B389" s="7" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="C389" s="7" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D389" s="7" t="s">
         <v>52</v>
@@ -24501,7 +24583,7 @@
         <v>19</v>
       </c>
       <c r="F389" s="9" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G389" s="8" t="s">
         <v>1062</v>
@@ -24537,13 +24619,13 @@
     </row>
     <row r="390" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A390" s="7" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="B390" s="7" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="C390" s="7" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="D390" s="10" t="s">
         <v>921</v>
@@ -24577,7 +24659,7 @@
         <v>6</v>
       </c>
       <c r="N390" s="8">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O390" s="8"/>
       <c r="P390" s="7"/>
@@ -24588,13 +24670,13 @@
     </row>
     <row r="391" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A391" s="6" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="B391" s="7" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="C391" s="7" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D391" s="7" t="s">
         <v>20</v>
@@ -24612,7 +24694,7 @@
         <v>12</v>
       </c>
       <c r="I391" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J391" s="8">
         <v>0</v>
@@ -24625,7 +24707,7 @@
       </c>
       <c r="M391" s="8">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N391" s="8">
         <v>0</v>
@@ -24639,13 +24721,13 @@
     </row>
     <row r="392" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A392" s="6" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="B392" s="7" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="C392" s="7" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D392" s="7" t="s">
         <v>20</v>
@@ -24690,13 +24772,13 @@
     </row>
     <row r="393" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A393" s="6" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="B393" s="7" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C393" s="7" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="D393" s="7" t="s">
         <v>30</v>
@@ -24741,13 +24823,13 @@
     </row>
     <row r="394" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A394" s="6" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="B394" s="7" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C394" s="7" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="D394" s="7" t="s">
         <v>30</v>
@@ -24765,7 +24847,7 @@
         <v>12</v>
       </c>
       <c r="I394" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J394" s="8">
         <v>0</v>
@@ -24778,7 +24860,7 @@
       </c>
       <c r="M394" s="8">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N394" s="8">
         <v>0</v>
@@ -24792,13 +24874,13 @@
     </row>
     <row r="395" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A395" s="6" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="B395" s="7" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="C395" s="7" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="D395" s="7" t="s">
         <v>30</v>
@@ -24843,13 +24925,13 @@
     </row>
     <row r="396" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A396" s="6" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="B396" s="7" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="C396" s="7" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="D396" s="7" t="s">
         <v>418</v>
@@ -24867,7 +24949,7 @@
         <v>12</v>
       </c>
       <c r="I396" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J396" s="8">
         <v>0</v>
@@ -24880,7 +24962,7 @@
       </c>
       <c r="M396" s="8">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N396" s="8">
         <v>0</v>
@@ -24894,13 +24976,13 @@
     </row>
     <row r="397" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A397" s="6" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="B397" s="7" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="C397" s="7" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="D397" s="7" t="s">
         <v>418</v>
@@ -24945,13 +25027,13 @@
     </row>
     <row r="398" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A398" s="6" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="B398" s="7" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C398" s="7" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="D398" s="7" t="s">
         <v>418</v>
@@ -24960,7 +25042,7 @@
         <v>19</v>
       </c>
       <c r="F398" s="7" t="s">
-        <v>418</v>
+        <v>1070</v>
       </c>
       <c r="G398" s="7" t="s">
         <v>1062</v>
@@ -24978,14 +25060,14 @@
         <v>0</v>
       </c>
       <c r="L398" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M398" s="8">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N398" s="8">
-        <v>567</v>
+        <v>0</v>
       </c>
       <c r="O398" s="7"/>
       <c r="P398" s="7"/>
@@ -24996,13 +25078,13 @@
     </row>
     <row r="399" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A399" s="7" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="B399" s="7" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C399" s="7" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="D399" s="7" t="s">
         <v>418</v>
@@ -25047,13 +25129,13 @@
     </row>
     <row r="400" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A400" s="7" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="B400" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="C400" s="7" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="D400" s="7" t="s">
         <v>418</v>
@@ -25098,13 +25180,13 @@
     </row>
     <row r="401" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A401" s="7" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="B401" s="7" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="C401" s="7" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="D401" s="7" t="s">
         <v>52</v>
@@ -25113,7 +25195,7 @@
         <v>19</v>
       </c>
       <c r="F401" s="7" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G401" s="8" t="s">
         <v>1062</v>
@@ -25149,13 +25231,13 @@
     </row>
     <row r="402" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A402" s="7" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B402" s="7" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="C402" s="10" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="D402" s="10" t="s">
         <v>701</v>
@@ -25200,13 +25282,13 @@
     </row>
     <row r="403" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A403" s="11" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B403" s="7" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="C403" s="10" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="D403" s="7" t="s">
         <v>127</v>
@@ -25215,10 +25297,10 @@
         <v>19</v>
       </c>
       <c r="F403" s="7" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G403" s="7" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H403" s="7" t="s">
         <v>13</v>
@@ -25251,16 +25333,16 @@
     </row>
     <row r="404" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A404" s="6" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="B404" s="7" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="C404" s="7" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="D404" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E404" s="8" t="s">
         <v>19</v>
@@ -25291,7 +25373,7 @@
         <v>2</v>
       </c>
       <c r="N404" s="8">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="O404" s="7"/>
       <c r="P404" s="7"/>
@@ -25302,16 +25384,16 @@
     </row>
     <row r="405" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A405" s="6" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="B405" s="7" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="C405" s="7" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="D405" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E405" s="8" t="s">
         <v>19</v>
@@ -25342,7 +25424,7 @@
         <v>2</v>
       </c>
       <c r="N405" s="8">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="O405" s="7"/>
       <c r="P405" s="7"/>
@@ -25353,16 +25435,16 @@
     </row>
     <row r="406" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A406" s="6" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="B406" s="7" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="C406" s="7" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="D406" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E406" s="8" t="s">
         <v>19</v>
@@ -25404,16 +25486,16 @@
     </row>
     <row r="407" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A407" s="6" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="B407" s="7" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="C407" s="7" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="D407" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E407" s="8" t="s">
         <v>19</v>
@@ -25455,16 +25537,16 @@
     </row>
     <row r="408" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A408" s="6" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="B408" s="7" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="C408" s="7" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="D408" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E408" s="8" t="s">
         <v>19</v>
@@ -25495,7 +25577,7 @@
         <v>2</v>
       </c>
       <c r="N408" s="8">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="O408" s="7"/>
       <c r="P408" s="7"/>
@@ -25506,16 +25588,16 @@
     </row>
     <row r="409" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A409" s="6" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B409" s="7" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="C409" s="7" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="D409" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E409" s="8" t="s">
         <v>19</v>
@@ -25546,7 +25628,7 @@
         <v>2</v>
       </c>
       <c r="N409" s="8">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="O409" s="7"/>
       <c r="P409" s="7"/>
@@ -25557,16 +25639,16 @@
     </row>
     <row r="410" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A410" s="6" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="B410" s="7" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="C410" s="7" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="D410" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E410" s="8" t="s">
         <v>19</v>
@@ -25597,7 +25679,7 @@
         <v>2</v>
       </c>
       <c r="N410" s="8">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O410" s="7"/>
       <c r="P410" s="7"/>
@@ -25608,16 +25690,16 @@
     </row>
     <row r="411" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A411" s="6" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="B411" s="7" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="C411" s="7" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="D411" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E411" s="8" t="s">
         <v>19</v>
@@ -25648,7 +25730,7 @@
         <v>2</v>
       </c>
       <c r="N411" s="8">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="O411" s="7"/>
       <c r="P411" s="7"/>
@@ -25659,16 +25741,16 @@
     </row>
     <row r="412" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A412" s="6" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="B412" s="7" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="C412" s="7" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="D412" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E412" s="8" t="s">
         <v>19</v>
@@ -25699,7 +25781,7 @@
         <v>2</v>
       </c>
       <c r="N412" s="8">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="O412" s="7"/>
       <c r="P412" s="7"/>
@@ -25710,16 +25792,16 @@
     </row>
     <row r="413" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A413" s="6" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="B413" s="7" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="C413" s="7" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="D413" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E413" s="8" t="s">
         <v>19</v>
@@ -25750,7 +25832,7 @@
         <v>2</v>
       </c>
       <c r="N413" s="8">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="O413" s="7"/>
       <c r="P413" s="7"/>
@@ -25761,16 +25843,16 @@
     </row>
     <row r="414" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A414" s="6" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="B414" s="7" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="C414" s="7" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="D414" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E414" s="8" t="s">
         <v>19</v>
@@ -25801,7 +25883,7 @@
         <v>1</v>
       </c>
       <c r="N414" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O414" s="7"/>
       <c r="P414" s="7"/>
@@ -25812,16 +25894,16 @@
     </row>
     <row r="415" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A415" s="6" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="B415" s="7" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="C415" s="7" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="D415" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E415" s="8" t="s">
         <v>19</v>
@@ -25852,7 +25934,7 @@
         <v>1</v>
       </c>
       <c r="N415" s="8">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="O415" s="7"/>
       <c r="P415" s="7"/>
@@ -25863,16 +25945,16 @@
     </row>
     <row r="416" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A416" s="6" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="B416" s="7" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="C416" s="7" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="D416" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E416" s="8" t="s">
         <v>19</v>
@@ -25914,16 +25996,16 @@
     </row>
     <row r="417" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A417" s="6" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="B417" s="7" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="C417" s="7" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="D417" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E417" s="8" t="s">
         <v>19</v>
@@ -25954,7 +26036,7 @@
         <v>3</v>
       </c>
       <c r="N417" s="8">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="O417" s="7"/>
       <c r="P417" s="7"/>
@@ -25965,16 +26047,16 @@
     </row>
     <row r="418" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A418" s="6" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="B418" s="7" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="C418" s="7" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="D418" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E418" s="8" t="s">
         <v>19</v>
@@ -25989,7 +26071,7 @@
         <v>12</v>
       </c>
       <c r="I418" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J418" s="8">
         <v>0</v>
@@ -25998,14 +26080,14 @@
         <v>0</v>
       </c>
       <c r="L418" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M418" s="8">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N418" s="8">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="O418" s="7"/>
       <c r="P418" s="7"/>
@@ -26016,16 +26098,16 @@
     </row>
     <row r="419" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A419" s="6" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="B419" s="7" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="C419" s="7" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="D419" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E419" s="8" t="s">
         <v>19</v>
@@ -26056,7 +26138,7 @@
         <v>3</v>
       </c>
       <c r="N419" s="8">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O419" s="7"/>
       <c r="P419" s="7"/>
@@ -26067,16 +26149,16 @@
     </row>
     <row r="420" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A420" s="6" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="B420" s="7" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="C420" s="7" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="D420" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E420" s="8" t="s">
         <v>19</v>
@@ -26107,7 +26189,7 @@
         <v>3</v>
       </c>
       <c r="N420" s="8">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="O420" s="7"/>
       <c r="P420" s="7"/>
@@ -26118,16 +26200,16 @@
     </row>
     <row r="421" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A421" s="6" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="B421" s="7" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="C421" s="7" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="D421" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E421" s="8" t="s">
         <v>19</v>
@@ -26158,7 +26240,7 @@
         <v>2</v>
       </c>
       <c r="N421" s="8">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="O421" s="7"/>
       <c r="P421" s="7"/>
@@ -26169,16 +26251,16 @@
     </row>
     <row r="422" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A422" s="6" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="B422" s="7" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="C422" s="7" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="D422" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E422" s="8" t="s">
         <v>19</v>
@@ -26209,7 +26291,7 @@
         <v>2</v>
       </c>
       <c r="N422" s="8">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="O422" s="7"/>
       <c r="P422" s="7"/>
@@ -26220,16 +26302,16 @@
     </row>
     <row r="423" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A423" s="6" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="B423" s="7" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="C423" s="7" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="D423" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E423" s="8" t="s">
         <v>19</v>
@@ -26260,7 +26342,7 @@
         <v>2</v>
       </c>
       <c r="N423" s="8">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="O423" s="7"/>
       <c r="P423" s="7"/>
@@ -26271,16 +26353,16 @@
     </row>
     <row r="424" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A424" s="6" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="B424" s="7" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="C424" s="7" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="D424" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E424" s="8" t="s">
         <v>19</v>
@@ -26311,7 +26393,7 @@
         <v>2</v>
       </c>
       <c r="N424" s="8">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="O424" s="7"/>
       <c r="P424" s="7"/>
@@ -26322,16 +26404,16 @@
     </row>
     <row r="425" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A425" s="6" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="B425" s="7" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="C425" s="7" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="D425" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E425" s="8" t="s">
         <v>19</v>
@@ -26362,7 +26444,7 @@
         <v>2</v>
       </c>
       <c r="N425" s="8">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="O425" s="7"/>
       <c r="P425" s="7"/>
@@ -26373,16 +26455,16 @@
     </row>
     <row r="426" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A426" s="6" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="B426" s="7" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="C426" s="7" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="D426" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E426" s="8" t="s">
         <v>19</v>
@@ -26413,7 +26495,7 @@
         <v>2</v>
       </c>
       <c r="N426" s="8">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="O426" s="7"/>
       <c r="P426" s="7"/>
@@ -26424,16 +26506,16 @@
     </row>
     <row r="427" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A427" s="6" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="B427" s="7" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="C427" s="7" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="D427" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E427" s="8" t="s">
         <v>19</v>
@@ -26475,16 +26557,16 @@
     </row>
     <row r="428" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A428" s="6" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="B428" s="7" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="C428" s="7" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="D428" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E428" s="8" t="s">
         <v>19</v>
@@ -26526,16 +26608,16 @@
     </row>
     <row r="429" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A429" s="6" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="B429" s="7" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="C429" s="7" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="D429" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E429" s="8" t="s">
         <v>19</v>
@@ -26577,16 +26659,16 @@
     </row>
     <row r="430" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A430" s="6" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="B430" s="7" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="C430" s="7" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="D430" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E430" s="8" t="s">
         <v>19</v>
@@ -26617,7 +26699,7 @@
         <v>0</v>
       </c>
       <c r="N430" s="8">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="O430" s="7"/>
       <c r="P430" s="7"/>
@@ -26628,16 +26710,16 @@
     </row>
     <row r="431" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A431" s="6" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="B431" s="7" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="C431" s="7" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="D431" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E431" s="8" t="s">
         <v>19</v>
@@ -26668,7 +26750,7 @@
         <v>0</v>
       </c>
       <c r="N431" s="8">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="O431" s="7"/>
       <c r="P431" s="7"/>
@@ -26679,16 +26761,16 @@
     </row>
     <row r="432" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A432" s="6" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="B432" s="7" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="C432" s="7" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="D432" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E432" s="8" t="s">
         <v>19</v>
@@ -26719,7 +26801,7 @@
         <v>0</v>
       </c>
       <c r="N432" s="8">
-        <v>143</v>
+        <v>235</v>
       </c>
       <c r="O432" s="7"/>
       <c r="P432" s="7"/>
@@ -26730,16 +26812,16 @@
     </row>
     <row r="433" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A433" s="6" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="B433" s="7" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C433" s="7" t="s">
+        <v>1309</v>
+      </c>
+      <c r="D433" s="7" t="s">
         <v>1311</v>
-      </c>
-      <c r="C433" s="7" t="s">
-        <v>1310</v>
-      </c>
-      <c r="D433" s="7" t="s">
-        <v>1312</v>
       </c>
       <c r="E433" s="8" t="s">
         <v>19</v>
@@ -26781,25 +26863,25 @@
     </row>
     <row r="434" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A434" s="7" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="B434" s="7" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="C434" s="7" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D434" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E434" s="8" t="s">
         <v>19</v>
       </c>
       <c r="F434" s="7" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G434" s="7" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H434" s="7" t="s">
         <v>15</v>
@@ -26814,14 +26896,14 @@
         <v>0</v>
       </c>
       <c r="L434" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M434" s="8">
         <f t="shared" ref="M434" si="8">I434+J434+K434+L434</f>
-        <v>0</v>
-      </c>
-      <c r="N434" s="7">
-        <v>197</v>
+        <v>2</v>
+      </c>
+      <c r="N434" s="8">
+        <v>0</v>
       </c>
       <c r="O434" s="7"/>
       <c r="P434" s="7"/>
@@ -26831,20 +26913,47 @@
       <c r="T434" s="7"/>
     </row>
     <row r="435" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A435" s="7"/>
-      <c r="B435" s="7"/>
-      <c r="C435" s="7"/>
+      <c r="A435" s="7" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B435" s="7" t="s">
+        <v>1350</v>
+      </c>
+      <c r="C435" s="10" t="s">
+        <v>1345</v>
+      </c>
       <c r="D435" s="7"/>
-      <c r="E435" s="7"/>
-      <c r="F435" s="7"/>
-      <c r="G435" s="7"/>
-      <c r="H435" s="7"/>
-      <c r="I435" s="7"/>
-      <c r="J435" s="7"/>
-      <c r="K435" s="7"/>
-      <c r="L435" s="7"/>
-      <c r="M435" s="7"/>
-      <c r="N435" s="7"/>
+      <c r="E435" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F435" s="7" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G435" s="7" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H435" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I435" s="8">
+        <v>1</v>
+      </c>
+      <c r="J435" s="8">
+        <v>0</v>
+      </c>
+      <c r="K435" s="8">
+        <v>0</v>
+      </c>
+      <c r="L435" s="8">
+        <v>0</v>
+      </c>
+      <c r="M435" s="8">
+        <f t="shared" ref="M435:M439" si="9">I435+J435+K435+L435</f>
+        <v>1</v>
+      </c>
+      <c r="N435" s="8">
+        <v>0</v>
+      </c>
       <c r="O435" s="7"/>
       <c r="P435" s="7"/>
       <c r="Q435" s="7"/>
@@ -26853,20 +26962,47 @@
       <c r="T435" s="7"/>
     </row>
     <row r="436" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A436" s="7"/>
-      <c r="B436" s="7"/>
-      <c r="C436" s="7"/>
+      <c r="A436" s="7" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B436" s="7" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C436" s="10" t="s">
+        <v>1346</v>
+      </c>
       <c r="D436" s="7"/>
-      <c r="E436" s="7"/>
-      <c r="F436" s="7"/>
-      <c r="G436" s="7"/>
-      <c r="H436" s="7"/>
-      <c r="I436" s="7"/>
-      <c r="J436" s="7"/>
-      <c r="K436" s="7"/>
-      <c r="L436" s="7"/>
-      <c r="M436" s="7"/>
-      <c r="N436" s="7"/>
+      <c r="E436" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F436" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G436" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H436" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I436" s="8">
+        <v>2</v>
+      </c>
+      <c r="J436" s="8">
+        <v>0</v>
+      </c>
+      <c r="K436" s="8">
+        <v>0</v>
+      </c>
+      <c r="L436" s="8">
+        <v>0</v>
+      </c>
+      <c r="M436" s="8">
+        <f t="shared" si="9"/>
+        <v>2</v>
+      </c>
+      <c r="N436" s="8">
+        <v>0</v>
+      </c>
       <c r="O436" s="7"/>
       <c r="P436" s="7"/>
       <c r="Q436" s="7"/>
@@ -26875,20 +27011,47 @@
       <c r="T436" s="7"/>
     </row>
     <row r="437" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A437" s="7"/>
-      <c r="B437" s="7"/>
-      <c r="C437" s="7"/>
+      <c r="A437" s="7" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B437" s="7" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C437" s="10" t="s">
+        <v>1347</v>
+      </c>
       <c r="D437" s="7"/>
-      <c r="E437" s="7"/>
-      <c r="F437" s="7"/>
-      <c r="G437" s="7"/>
-      <c r="H437" s="7"/>
-      <c r="I437" s="7"/>
-      <c r="J437" s="7"/>
-      <c r="K437" s="7"/>
-      <c r="L437" s="7"/>
-      <c r="M437" s="7"/>
-      <c r="N437" s="7"/>
+      <c r="E437" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F437" s="7" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G437" s="7" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H437" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I437" s="8">
+        <v>1</v>
+      </c>
+      <c r="J437" s="8">
+        <v>0</v>
+      </c>
+      <c r="K437" s="8">
+        <v>0</v>
+      </c>
+      <c r="L437" s="8">
+        <v>0</v>
+      </c>
+      <c r="M437" s="8">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="N437" s="8">
+        <v>0</v>
+      </c>
       <c r="O437" s="7"/>
       <c r="P437" s="7"/>
       <c r="Q437" s="7"/>
@@ -26897,20 +27060,47 @@
       <c r="T437" s="7"/>
     </row>
     <row r="438" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A438" s="7"/>
-      <c r="B438" s="7"/>
-      <c r="C438" s="7"/>
+      <c r="A438" s="7" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B438" s="7" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C438" s="10" t="s">
+        <v>1348</v>
+      </c>
       <c r="D438" s="7"/>
-      <c r="E438" s="7"/>
-      <c r="F438" s="7"/>
-      <c r="G438" s="7"/>
-      <c r="H438" s="7"/>
-      <c r="I438" s="7"/>
-      <c r="J438" s="7"/>
-      <c r="K438" s="7"/>
-      <c r="L438" s="7"/>
-      <c r="M438" s="7"/>
-      <c r="N438" s="7"/>
+      <c r="E438" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F438" s="7" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G438" s="7" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H438" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I438" s="8">
+        <v>0</v>
+      </c>
+      <c r="J438" s="8">
+        <v>0</v>
+      </c>
+      <c r="K438" s="8">
+        <v>0</v>
+      </c>
+      <c r="L438" s="8">
+        <v>0</v>
+      </c>
+      <c r="M438" s="8">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="N438" s="8">
+        <v>1</v>
+      </c>
       <c r="O438" s="7"/>
       <c r="P438" s="7"/>
       <c r="Q438" s="7"/>
@@ -26919,20 +27109,47 @@
       <c r="T438" s="7"/>
     </row>
     <row r="439" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A439" s="7"/>
-      <c r="B439" s="7"/>
-      <c r="C439" s="7"/>
+      <c r="A439" s="7" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B439" s="7" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C439" s="10" t="s">
+        <v>1349</v>
+      </c>
       <c r="D439" s="7"/>
-      <c r="E439" s="7"/>
-      <c r="F439" s="7"/>
-      <c r="G439" s="7"/>
-      <c r="H439" s="7"/>
-      <c r="I439" s="7"/>
-      <c r="J439" s="7"/>
-      <c r="K439" s="7"/>
-      <c r="L439" s="7"/>
-      <c r="M439" s="7"/>
-      <c r="N439" s="7"/>
+      <c r="E439" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F439" s="7" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G439" s="7" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H439" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I439" s="8">
+        <v>0</v>
+      </c>
+      <c r="J439" s="8">
+        <v>0</v>
+      </c>
+      <c r="K439" s="8">
+        <v>0</v>
+      </c>
+      <c r="L439" s="8">
+        <v>0</v>
+      </c>
+      <c r="M439" s="8">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="N439" s="8">
+        <v>2</v>
+      </c>
       <c r="O439" s="7"/>
       <c r="P439" s="7"/>
       <c r="Q439" s="7"/>
@@ -34069,26 +34286,32 @@
       <c r="T763" s="7"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T433" xr:uid="{AF55B7BF-85DC-4082-9A73-200B4D79A598}"/>
+  <autoFilter ref="A1:T439" xr:uid="{AF55B7BF-85DC-4082-9A73-200B4D79A598}"/>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="11" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="9" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C402">
-    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C403">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C435:C439">
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
+++ b/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\Fossil Replenishment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92EC844A-B609-4DB7-80EA-459B18E8AE5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA74F32B-9212-4C83-B1CD-CD460BB95FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6662473D-6E1F-42FD-999B-28162E22D4B5}"/>
   </bookViews>
@@ -4855,23 +4855,23 @@
         <v>12</v>
       </c>
       <c r="I2" s="8">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="J2" s="8">
         <v>0</v>
       </c>
       <c r="K2" s="8">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="L2" s="8">
         <v>0</v>
       </c>
       <c r="M2" s="8">
         <f>I2+J2+K2+L2</f>
-        <v>898</v>
+        <v>827</v>
       </c>
       <c r="N2" s="8">
-        <v>1209</v>
+        <v>2191</v>
       </c>
       <c r="O2" s="8"/>
       <c r="P2" s="8"/>
@@ -4906,7 +4906,7 @@
         <v>12</v>
       </c>
       <c r="I3" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J3" s="8">
         <v>0</v>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="M3" s="8">
         <f t="shared" ref="M3:M66" si="0">I3+J3+K3+L3</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N3" s="8">
         <v>0</v>
@@ -4957,7 +4957,7 @@
         <v>12</v>
       </c>
       <c r="I4" s="8">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="J4" s="8">
         <v>0</v>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="M4" s="8">
         <f t="shared" si="0"/>
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="N4" s="8">
         <v>0</v>
@@ -5008,7 +5008,7 @@
         <v>12</v>
       </c>
       <c r="I5" s="8">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="J5" s="8">
         <v>0</v>
@@ -5017,14 +5017,14 @@
         <v>0</v>
       </c>
       <c r="L5" s="8">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="M5" s="8">
         <f t="shared" si="0"/>
-        <v>37</v>
+        <v>189</v>
       </c>
       <c r="N5" s="8">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="O5" s="8"/>
       <c r="P5" s="8"/>
@@ -5059,20 +5059,20 @@
         <v>12</v>
       </c>
       <c r="I6" s="8">
-        <v>869</v>
+        <v>887</v>
       </c>
       <c r="J6" s="8">
         <v>0</v>
       </c>
       <c r="K6" s="8">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="L6" s="8">
         <v>0</v>
       </c>
       <c r="M6" s="8">
         <f t="shared" si="0"/>
-        <v>965</v>
+        <v>887</v>
       </c>
       <c r="N6" s="8">
         <v>1490</v>
@@ -5110,7 +5110,7 @@
         <v>12</v>
       </c>
       <c r="I7" s="8">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="J7" s="8">
         <v>0</v>
@@ -5123,10 +5123,10 @@
       </c>
       <c r="M7" s="8">
         <f t="shared" si="0"/>
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="N7" s="8">
-        <v>869</v>
+        <v>575</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
@@ -5161,23 +5161,23 @@
         <v>12</v>
       </c>
       <c r="I8" s="8">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="J8" s="8">
         <v>0</v>
       </c>
       <c r="K8" s="8">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="L8" s="8">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="M8" s="8">
         <f t="shared" si="0"/>
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="N8" s="8">
-        <v>318</v>
+        <v>100</v>
       </c>
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
@@ -5212,7 +5212,7 @@
         <v>12</v>
       </c>
       <c r="I9" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" s="8">
         <v>0</v>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="M9" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N9" s="8">
         <v>0</v>
@@ -5314,7 +5314,7 @@
         <v>12</v>
       </c>
       <c r="I11" s="8">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="J11" s="8">
         <v>0</v>
@@ -5327,7 +5327,7 @@
       </c>
       <c r="M11" s="8">
         <f t="shared" si="0"/>
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="N11" s="8">
         <v>0</v>
@@ -5365,7 +5365,7 @@
         <v>12</v>
       </c>
       <c r="I12" s="8">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J12" s="8">
         <v>0</v>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="M12" s="8">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N12" s="8">
         <v>0</v>
@@ -5416,20 +5416,20 @@
         <v>12</v>
       </c>
       <c r="I13" s="8">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="J13" s="8">
         <v>0</v>
       </c>
       <c r="K13" s="8">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L13" s="8">
         <v>0</v>
       </c>
       <c r="M13" s="8">
         <f t="shared" si="0"/>
-        <v>277</v>
+        <v>246</v>
       </c>
       <c r="N13" s="8">
         <v>810</v>
@@ -5467,23 +5467,23 @@
         <v>12</v>
       </c>
       <c r="I14" s="8">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J14" s="8">
         <v>0</v>
       </c>
       <c r="K14" s="8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L14" s="8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M14" s="8">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N14" s="8">
-        <v>626</v>
+        <v>557</v>
       </c>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
@@ -5569,23 +5569,23 @@
         <v>12</v>
       </c>
       <c r="I16" s="8">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J16" s="8">
         <v>0</v>
       </c>
       <c r="K16" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L16" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M16" s="8">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N16" s="8">
-        <v>533</v>
+        <v>377</v>
       </c>
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
@@ -5636,7 +5636,7 @@
         <v>64</v>
       </c>
       <c r="N17" s="8">
-        <v>315</v>
+        <v>285</v>
       </c>
       <c r="O17" s="8"/>
       <c r="P17" s="8"/>
@@ -5671,7 +5671,7 @@
         <v>12</v>
       </c>
       <c r="I18" s="8">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J18" s="8">
         <v>0</v>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M18" s="8">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N18" s="8">
         <v>0</v>
@@ -5722,7 +5722,7 @@
         <v>13</v>
       </c>
       <c r="I19" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J19" s="8">
         <v>0</v>
@@ -5735,10 +5735,10 @@
       </c>
       <c r="M19" s="8">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N19" s="8">
-        <v>405</v>
+        <v>270</v>
       </c>
       <c r="O19" s="8"/>
       <c r="P19" s="8"/>
@@ -5773,7 +5773,7 @@
         <v>14</v>
       </c>
       <c r="I20" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J20" s="8">
         <v>0</v>
@@ -5782,11 +5782,11 @@
         <v>0</v>
       </c>
       <c r="L20" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M20" s="8">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="N20" s="8">
         <v>0</v>
@@ -5824,7 +5824,7 @@
         <v>13</v>
       </c>
       <c r="I21" s="8">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="J21" s="8">
         <v>0</v>
@@ -5837,7 +5837,7 @@
       </c>
       <c r="M21" s="8">
         <f t="shared" si="0"/>
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="N21" s="8">
         <v>0</v>
@@ -5926,7 +5926,7 @@
         <v>12</v>
       </c>
       <c r="I23" s="8">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J23" s="8">
         <v>0</v>
@@ -5939,7 +5939,7 @@
       </c>
       <c r="M23" s="8">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="N23" s="8">
         <v>0</v>
@@ -5977,7 +5977,7 @@
         <v>14</v>
       </c>
       <c r="I24" s="8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J24" s="8">
         <v>0</v>
@@ -5990,10 +5990,10 @@
       </c>
       <c r="M24" s="8">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N24" s="8">
-        <v>411</v>
+        <v>256</v>
       </c>
       <c r="O24" s="8"/>
       <c r="P24" s="8"/>
@@ -6085,17 +6085,17 @@
         <v>0</v>
       </c>
       <c r="K26" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L26" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M26" s="8">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="N26" s="8">
-        <v>154</v>
+        <v>200</v>
       </c>
       <c r="O26" s="8"/>
       <c r="P26" s="8"/>
@@ -6130,7 +6130,7 @@
         <v>12</v>
       </c>
       <c r="I27" s="8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J27" s="8">
         <v>0</v>
@@ -6143,10 +6143,10 @@
       </c>
       <c r="M27" s="8">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N27" s="8">
-        <v>849</v>
+        <v>713</v>
       </c>
       <c r="O27" s="8"/>
       <c r="P27" s="8"/>
@@ -6181,7 +6181,7 @@
         <v>12</v>
       </c>
       <c r="I28" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J28" s="8">
         <v>0</v>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="M28" s="8">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N28" s="8">
         <v>0</v>
@@ -6232,7 +6232,7 @@
         <v>13</v>
       </c>
       <c r="I29" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J29" s="8">
         <v>0</v>
@@ -6245,7 +6245,7 @@
       </c>
       <c r="M29" s="8">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="N29" s="8">
         <v>0</v>
@@ -6283,23 +6283,23 @@
         <v>14</v>
       </c>
       <c r="I30" s="8">
+        <v>6</v>
+      </c>
+      <c r="J30" s="8">
+        <v>0</v>
+      </c>
+      <c r="K30" s="8">
+        <v>3</v>
+      </c>
+      <c r="L30" s="8">
         <v>4</v>
-      </c>
-      <c r="J30" s="8">
-        <v>0</v>
-      </c>
-      <c r="K30" s="8">
-        <v>0</v>
-      </c>
-      <c r="L30" s="8">
-        <v>3</v>
       </c>
       <c r="M30" s="8">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="N30" s="8">
-        <v>1307</v>
+        <v>1213</v>
       </c>
       <c r="O30" s="8"/>
       <c r="P30" s="8"/>
@@ -6385,7 +6385,7 @@
         <v>12</v>
       </c>
       <c r="I32" s="8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J32" s="8">
         <v>0</v>
@@ -6398,10 +6398,10 @@
       </c>
       <c r="M32" s="8">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N32" s="8">
-        <v>575</v>
+        <v>517</v>
       </c>
       <c r="O32" s="8"/>
       <c r="P32" s="8"/>
@@ -6436,7 +6436,7 @@
         <v>12</v>
       </c>
       <c r="I33" s="8">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J33" s="8">
         <v>0</v>
@@ -6445,14 +6445,14 @@
         <v>0</v>
       </c>
       <c r="L33" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M33" s="8">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="N33" s="8">
-        <v>842</v>
+        <v>733</v>
       </c>
       <c r="O33" s="8"/>
       <c r="P33" s="8"/>
@@ -6487,7 +6487,7 @@
         <v>12</v>
       </c>
       <c r="I34" s="8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J34" s="8">
         <v>0</v>
@@ -6500,10 +6500,10 @@
       </c>
       <c r="M34" s="8">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N34" s="8">
-        <v>899</v>
+        <v>820</v>
       </c>
       <c r="O34" s="8"/>
       <c r="P34" s="8"/>
@@ -6538,7 +6538,7 @@
         <v>12</v>
       </c>
       <c r="I35" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J35" s="8">
         <v>0</v>
@@ -6551,10 +6551,10 @@
       </c>
       <c r="M35" s="8">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N35" s="8">
-        <v>715</v>
+        <v>703</v>
       </c>
       <c r="O35" s="8"/>
       <c r="P35" s="8"/>
@@ -6605,7 +6605,7 @@
         <v>7</v>
       </c>
       <c r="N36" s="8">
-        <v>616</v>
+        <v>574</v>
       </c>
       <c r="O36" s="8"/>
       <c r="P36" s="8"/>
@@ -6640,7 +6640,7 @@
         <v>13</v>
       </c>
       <c r="I37" s="8">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J37" s="8">
         <v>0</v>
@@ -6653,10 +6653,10 @@
       </c>
       <c r="M37" s="8">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N37" s="8">
-        <v>991</v>
+        <v>875</v>
       </c>
       <c r="O37" s="8"/>
       <c r="P37" s="8"/>
@@ -6691,7 +6691,7 @@
         <v>12</v>
       </c>
       <c r="I38" s="8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J38" s="8">
         <v>0</v>
@@ -6704,7 +6704,7 @@
       </c>
       <c r="M38" s="8">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N38" s="8">
         <v>0</v>
@@ -6742,23 +6742,23 @@
         <v>12</v>
       </c>
       <c r="I39" s="8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J39" s="8">
         <v>0</v>
       </c>
       <c r="K39" s="8">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L39" s="8">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M39" s="8">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N39" s="8">
-        <v>2680</v>
+        <v>2669</v>
       </c>
       <c r="O39" s="8"/>
       <c r="P39" s="8"/>
@@ -6793,7 +6793,7 @@
         <v>12</v>
       </c>
       <c r="I40" s="8">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J40" s="8">
         <v>0</v>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="M40" s="8">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N40" s="8">
         <v>0</v>
@@ -6844,7 +6844,7 @@
         <v>12</v>
       </c>
       <c r="I41" s="8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J41" s="8">
         <v>0</v>
@@ -6857,10 +6857,10 @@
       </c>
       <c r="M41" s="8">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N41" s="8">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="O41" s="8"/>
       <c r="P41" s="8"/>
@@ -6901,17 +6901,17 @@
         <v>0</v>
       </c>
       <c r="K42" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L42" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M42" s="8">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="N42" s="8">
-        <v>1165</v>
+        <v>979</v>
       </c>
       <c r="O42" s="8"/>
       <c r="P42" s="8"/>
@@ -6946,7 +6946,7 @@
         <v>12</v>
       </c>
       <c r="I43" s="8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J43" s="8">
         <v>0</v>
@@ -6959,7 +6959,7 @@
       </c>
       <c r="M43" s="8">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N43" s="8">
         <v>0</v>
@@ -6997,7 +6997,7 @@
         <v>12</v>
       </c>
       <c r="I44" s="8">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J44" s="8">
         <v>0</v>
@@ -7010,10 +7010,10 @@
       </c>
       <c r="M44" s="8">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N44" s="8">
-        <v>222</v>
+        <v>165</v>
       </c>
       <c r="O44" s="8"/>
       <c r="P44" s="8"/>
@@ -7064,7 +7064,7 @@
         <v>13</v>
       </c>
       <c r="N45" s="8">
-        <v>600</v>
+        <v>549</v>
       </c>
       <c r="O45" s="8"/>
       <c r="P45" s="8"/>
@@ -7099,7 +7099,7 @@
         <v>12</v>
       </c>
       <c r="I46" s="8">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J46" s="8">
         <v>0</v>
@@ -7112,10 +7112,10 @@
       </c>
       <c r="M46" s="8">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="N46" s="8">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="O46" s="8"/>
       <c r="P46" s="8"/>
@@ -7166,7 +7166,7 @@
         <v>7</v>
       </c>
       <c r="N47" s="8">
-        <v>755</v>
+        <v>594</v>
       </c>
       <c r="O47" s="8"/>
       <c r="P47" s="8"/>
@@ -7201,7 +7201,7 @@
         <v>12</v>
       </c>
       <c r="I48" s="8">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J48" s="8">
         <v>0</v>
@@ -7210,14 +7210,14 @@
         <v>0</v>
       </c>
       <c r="L48" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M48" s="8">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="N48" s="8">
-        <v>1500</v>
+        <v>1114</v>
       </c>
       <c r="O48" s="8"/>
       <c r="P48" s="8"/>
@@ -7252,7 +7252,7 @@
         <v>12</v>
       </c>
       <c r="I49" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J49" s="8">
         <v>0</v>
@@ -7265,10 +7265,10 @@
       </c>
       <c r="M49" s="8">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N49" s="8">
-        <v>757</v>
+        <v>603</v>
       </c>
       <c r="O49" s="8"/>
       <c r="P49" s="8"/>
@@ -7319,7 +7319,7 @@
         <v>4</v>
       </c>
       <c r="N50" s="8">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="O50" s="8"/>
       <c r="P50" s="8"/>
@@ -7370,7 +7370,7 @@
         <v>24</v>
       </c>
       <c r="N51" s="8">
-        <v>301</v>
+        <v>263</v>
       </c>
       <c r="O51" s="8"/>
       <c r="P51" s="8"/>
@@ -7405,7 +7405,7 @@
         <v>12</v>
       </c>
       <c r="I52" s="8">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="J52" s="8">
         <v>0</v>
@@ -7418,7 +7418,7 @@
       </c>
       <c r="M52" s="8">
         <f t="shared" si="0"/>
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="N52" s="8">
         <v>0</v>
@@ -7472,7 +7472,7 @@
         <v>9</v>
       </c>
       <c r="N53" s="8">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="O53" s="8"/>
       <c r="P53" s="8"/>
@@ -7523,7 +7523,7 @@
         <v>7</v>
       </c>
       <c r="N54" s="8">
-        <v>433</v>
+        <v>292</v>
       </c>
       <c r="O54" s="8"/>
       <c r="P54" s="8"/>
@@ -7558,7 +7558,7 @@
         <v>12</v>
       </c>
       <c r="I55" s="8">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J55" s="8">
         <v>0</v>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="M55" s="8">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N55" s="8">
         <v>0</v>
@@ -7618,14 +7618,14 @@
         <v>0</v>
       </c>
       <c r="L56" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" s="8">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N56" s="8">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="O56" s="8"/>
       <c r="P56" s="8"/>
@@ -7660,23 +7660,23 @@
         <v>12</v>
       </c>
       <c r="I57" s="8">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J57" s="8">
         <v>0</v>
       </c>
       <c r="K57" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L57" s="8">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M57" s="8">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="N57" s="8">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="O57" s="8"/>
       <c r="P57" s="8"/>
@@ -7711,23 +7711,23 @@
         <v>12</v>
       </c>
       <c r="I58" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J58" s="8">
         <v>0</v>
       </c>
       <c r="K58" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L58" s="8">
         <v>2</v>
       </c>
       <c r="M58" s="8">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N58" s="8">
-        <v>603</v>
+        <v>587</v>
       </c>
       <c r="O58" s="8"/>
       <c r="P58" s="8"/>
@@ -7813,7 +7813,7 @@
         <v>12</v>
       </c>
       <c r="I60" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J60" s="8">
         <v>0</v>
@@ -7822,14 +7822,14 @@
         <v>0</v>
       </c>
       <c r="L60" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" s="8">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N60" s="8">
-        <v>474</v>
+        <v>354</v>
       </c>
       <c r="O60" s="8"/>
       <c r="P60" s="8"/>
@@ -7864,7 +7864,7 @@
         <v>12</v>
       </c>
       <c r="I61" s="8">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J61" s="8">
         <v>0</v>
@@ -7877,7 +7877,7 @@
       </c>
       <c r="M61" s="8">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="N61" s="8">
         <v>0</v>
@@ -7915,7 +7915,7 @@
         <v>12</v>
       </c>
       <c r="I62" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J62" s="8">
         <v>0</v>
@@ -7928,10 +7928,10 @@
       </c>
       <c r="M62" s="8">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N62" s="8">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="O62" s="8"/>
       <c r="P62" s="8"/>
@@ -7966,7 +7966,7 @@
         <v>12</v>
       </c>
       <c r="I63" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J63" s="8">
         <v>0</v>
@@ -7979,10 +7979,10 @@
       </c>
       <c r="M63" s="8">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N63" s="8">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="O63" s="8"/>
       <c r="P63" s="8"/>
@@ -8017,23 +8017,23 @@
         <v>13</v>
       </c>
       <c r="I64" s="8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J64" s="8">
         <v>0</v>
       </c>
       <c r="K64" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L64" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M64" s="8">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N64" s="8">
-        <v>222</v>
+        <v>411</v>
       </c>
       <c r="O64" s="8"/>
       <c r="P64" s="8"/>
@@ -8068,7 +8068,7 @@
         <v>12</v>
       </c>
       <c r="I65" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J65" s="8">
         <v>0</v>
@@ -8081,10 +8081,10 @@
       </c>
       <c r="M65" s="8">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N65" s="8">
-        <v>848</v>
+        <v>820</v>
       </c>
       <c r="O65" s="8"/>
       <c r="P65" s="8"/>
@@ -8135,7 +8135,7 @@
         <v>4</v>
       </c>
       <c r="N66" s="8">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="O66" s="8"/>
       <c r="P66" s="8"/>
@@ -8186,7 +8186,7 @@
         <v>3</v>
       </c>
       <c r="N67" s="8">
-        <v>664</v>
+        <v>604</v>
       </c>
       <c r="O67" s="8"/>
       <c r="P67" s="8"/>
@@ -8227,17 +8227,17 @@
         <v>0</v>
       </c>
       <c r="K68" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L68" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M68" s="8">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="N68" s="8">
-        <v>886</v>
+        <v>862</v>
       </c>
       <c r="O68" s="8"/>
       <c r="P68" s="8"/>
@@ -8288,7 +8288,7 @@
         <v>10</v>
       </c>
       <c r="N69" s="8">
-        <v>221</v>
+        <v>132</v>
       </c>
       <c r="O69" s="8"/>
       <c r="P69" s="8"/>
@@ -8323,7 +8323,7 @@
         <v>16</v>
       </c>
       <c r="I70" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J70" s="8">
         <v>0</v>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="M70" s="8">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N70" s="8">
         <v>543</v>
@@ -8374,7 +8374,7 @@
         <v>12</v>
       </c>
       <c r="I71" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J71" s="8">
         <v>0</v>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="M71" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N71" s="8">
         <v>0</v>
@@ -8425,7 +8425,7 @@
         <v>12</v>
       </c>
       <c r="I72" s="8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J72" s="8">
         <v>0</v>
@@ -8438,10 +8438,10 @@
       </c>
       <c r="M72" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N72" s="8">
-        <v>528</v>
+        <v>470</v>
       </c>
       <c r="O72" s="8"/>
       <c r="P72" s="8"/>
@@ -8482,14 +8482,14 @@
         <v>0</v>
       </c>
       <c r="K73" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L73" s="8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M73" s="8">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="N73" s="8">
         <v>169</v>
@@ -8543,7 +8543,7 @@
         <v>6</v>
       </c>
       <c r="N74" s="8">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="O74" s="8"/>
       <c r="P74" s="8"/>
@@ -8629,7 +8629,7 @@
         <v>13</v>
       </c>
       <c r="I76" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J76" s="8">
         <v>0</v>
@@ -8642,10 +8642,10 @@
       </c>
       <c r="M76" s="8">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N76" s="8">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="O76" s="8"/>
       <c r="P76" s="8"/>
@@ -8696,7 +8696,7 @@
         <v>5</v>
       </c>
       <c r="N77" s="8">
-        <v>509</v>
+        <v>387</v>
       </c>
       <c r="O77" s="8"/>
       <c r="P77" s="8"/>
@@ -8731,23 +8731,23 @@
         <v>12</v>
       </c>
       <c r="I78" s="8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J78" s="8">
         <v>0</v>
       </c>
       <c r="K78" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L78" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M78" s="8">
         <f t="shared" si="1"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N78" s="8">
-        <v>300</v>
+        <v>221</v>
       </c>
       <c r="O78" s="8"/>
       <c r="P78" s="8"/>
@@ -8849,7 +8849,7 @@
         <v>3</v>
       </c>
       <c r="N80" s="8">
-        <v>346</v>
+        <v>239</v>
       </c>
       <c r="O80" s="8"/>
       <c r="P80" s="8"/>
@@ -8951,7 +8951,7 @@
         <v>5</v>
       </c>
       <c r="N82" s="8">
-        <v>222</v>
+        <v>172</v>
       </c>
       <c r="O82" s="8"/>
       <c r="P82" s="8"/>
@@ -9002,7 +9002,7 @@
         <v>4</v>
       </c>
       <c r="N83" s="8">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="O83" s="8"/>
       <c r="P83" s="8"/>
@@ -9088,7 +9088,7 @@
         <v>14</v>
       </c>
       <c r="I85" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J85" s="8">
         <v>0</v>
@@ -9101,10 +9101,10 @@
       </c>
       <c r="M85" s="8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N85" s="8">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="O85" s="8"/>
       <c r="P85" s="8"/>
@@ -9139,7 +9139,7 @@
         <v>12</v>
       </c>
       <c r="I86" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J86" s="8">
         <v>0</v>
@@ -9152,10 +9152,10 @@
       </c>
       <c r="M86" s="8">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N86" s="8">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="O86" s="8"/>
       <c r="P86" s="8"/>
@@ -9241,7 +9241,7 @@
         <v>12</v>
       </c>
       <c r="I88" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J88" s="8">
         <v>0</v>
@@ -9254,10 +9254,10 @@
       </c>
       <c r="M88" s="8">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N88" s="8">
-        <v>258</v>
+        <v>155</v>
       </c>
       <c r="O88" s="8"/>
       <c r="P88" s="8"/>
@@ -9292,7 +9292,7 @@
         <v>12</v>
       </c>
       <c r="I89" s="8">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J89" s="8">
         <v>0</v>
@@ -9305,10 +9305,10 @@
       </c>
       <c r="M89" s="8">
         <f t="shared" si="1"/>
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N89" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O89" s="8"/>
       <c r="P89" s="8"/>
@@ -9359,7 +9359,7 @@
         <v>5</v>
       </c>
       <c r="N90" s="8">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O90" s="8"/>
       <c r="P90" s="8"/>
@@ -9400,17 +9400,17 @@
         <v>0</v>
       </c>
       <c r="K91" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M91" s="8">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="N91" s="8">
-        <v>938</v>
+        <v>864</v>
       </c>
       <c r="O91" s="8"/>
       <c r="P91" s="8"/>
@@ -9454,14 +9454,14 @@
         <v>0</v>
       </c>
       <c r="L92" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M92" s="8">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N92" s="8">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="O92" s="8"/>
       <c r="P92" s="8"/>
@@ -9614,7 +9614,7 @@
         <v>6</v>
       </c>
       <c r="N95" s="8">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O95" s="8"/>
       <c r="P95" s="8"/>
@@ -9649,7 +9649,7 @@
         <v>13</v>
       </c>
       <c r="I96" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J96" s="8">
         <v>0</v>
@@ -9662,10 +9662,10 @@
       </c>
       <c r="M96" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N96" s="8">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="O96" s="8"/>
       <c r="P96" s="8"/>
@@ -9700,23 +9700,23 @@
         <v>14</v>
       </c>
       <c r="I97" s="8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J97" s="8">
         <v>0</v>
       </c>
       <c r="K97" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L97" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M97" s="8">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N97" s="8">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="O97" s="8"/>
       <c r="P97" s="8"/>
@@ -9904,23 +9904,23 @@
         <v>15</v>
       </c>
       <c r="I101" s="8">
+        <v>2</v>
+      </c>
+      <c r="J101" s="8">
+        <v>0</v>
+      </c>
+      <c r="K101" s="8">
+        <v>0</v>
+      </c>
+      <c r="L101" s="8">
         <v>1</v>
-      </c>
-      <c r="J101" s="8">
-        <v>0</v>
-      </c>
-      <c r="K101" s="8">
-        <v>0</v>
-      </c>
-      <c r="L101" s="8">
-        <v>0</v>
       </c>
       <c r="M101" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N101" s="8">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O101" s="8"/>
       <c r="P101" s="8"/>
@@ -9955,23 +9955,23 @@
         <v>14</v>
       </c>
       <c r="I102" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J102" s="8">
         <v>0</v>
       </c>
       <c r="K102" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L102" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M102" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N102" s="8">
-        <v>385</v>
+        <v>369</v>
       </c>
       <c r="O102" s="8"/>
       <c r="P102" s="8"/>
@@ -10022,7 +10022,7 @@
         <v>5</v>
       </c>
       <c r="N103" s="8">
-        <v>0</v>
+        <v>284</v>
       </c>
       <c r="O103" s="8"/>
       <c r="P103" s="8"/>
@@ -10108,7 +10108,7 @@
         <v>12</v>
       </c>
       <c r="I105" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J105" s="8">
         <v>0</v>
@@ -10121,10 +10121,10 @@
       </c>
       <c r="M105" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N105" s="8">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="O105" s="8"/>
       <c r="P105" s="8"/>
@@ -10328,7 +10328,7 @@
         <v>4</v>
       </c>
       <c r="N109" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O109" s="8"/>
       <c r="P109" s="8"/>
@@ -10363,7 +10363,7 @@
         <v>13</v>
       </c>
       <c r="I110" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J110" s="8">
         <v>0</v>
@@ -10376,10 +10376,10 @@
       </c>
       <c r="M110" s="8">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N110" s="8">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="O110" s="8"/>
       <c r="P110" s="8"/>
@@ -10465,7 +10465,7 @@
         <v>12</v>
       </c>
       <c r="I112" s="8">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="J112" s="8">
         <v>0</v>
@@ -10478,10 +10478,10 @@
       </c>
       <c r="M112" s="8">
         <f t="shared" si="1"/>
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="N112" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O112" s="8"/>
       <c r="P112" s="8"/>
@@ -10525,14 +10525,14 @@
         <v>0</v>
       </c>
       <c r="L113" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M113" s="8">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N113" s="8">
-        <v>733</v>
+        <v>653</v>
       </c>
       <c r="O113" s="8"/>
       <c r="P113" s="8"/>
@@ -10583,7 +10583,7 @@
         <v>6</v>
       </c>
       <c r="N114" s="8">
-        <v>531</v>
+        <v>357</v>
       </c>
       <c r="O114" s="8"/>
       <c r="P114" s="8"/>
@@ -10634,7 +10634,7 @@
         <v>9</v>
       </c>
       <c r="N115" s="8">
-        <v>507</v>
+        <v>484</v>
       </c>
       <c r="O115" s="8"/>
       <c r="P115" s="8"/>
@@ -10669,7 +10669,7 @@
         <v>12</v>
       </c>
       <c r="I116" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J116" s="8">
         <v>0</v>
@@ -10682,10 +10682,10 @@
       </c>
       <c r="M116" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N116" s="8">
-        <v>633</v>
+        <v>534</v>
       </c>
       <c r="O116" s="8"/>
       <c r="P116" s="8"/>
@@ -10720,23 +10720,23 @@
         <v>12</v>
       </c>
       <c r="I117" s="8">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J117" s="8">
         <v>0</v>
       </c>
       <c r="K117" s="8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L117" s="8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M117" s="8">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="N117" s="8">
-        <v>111</v>
+        <v>10</v>
       </c>
       <c r="O117" s="8"/>
       <c r="P117" s="8"/>
@@ -10787,7 +10787,7 @@
         <v>6</v>
       </c>
       <c r="N118" s="8">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="O118" s="8"/>
       <c r="P118" s="8"/>
@@ -10838,7 +10838,7 @@
         <v>8</v>
       </c>
       <c r="N119" s="8">
-        <v>461</v>
+        <v>435</v>
       </c>
       <c r="O119" s="8"/>
       <c r="P119" s="8"/>
@@ -10873,7 +10873,7 @@
         <v>14</v>
       </c>
       <c r="I120" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J120" s="8">
         <v>0</v>
@@ -10886,10 +10886,10 @@
       </c>
       <c r="M120" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N120" s="8">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="O120" s="8"/>
       <c r="P120" s="8"/>
@@ -10991,7 +10991,7 @@
         <v>2</v>
       </c>
       <c r="N122" s="8">
-        <v>950</v>
+        <v>889</v>
       </c>
       <c r="O122" s="8"/>
       <c r="P122" s="8"/>
@@ -11144,7 +11144,7 @@
         <v>6</v>
       </c>
       <c r="N125" s="8">
-        <v>81</v>
+        <v>4</v>
       </c>
       <c r="O125" s="8"/>
       <c r="P125" s="8"/>
@@ -11297,7 +11297,7 @@
         <v>3</v>
       </c>
       <c r="N128" s="8">
-        <v>804</v>
+        <v>795</v>
       </c>
       <c r="O128" s="8"/>
       <c r="P128" s="8"/>
@@ -11383,23 +11383,23 @@
         <v>12</v>
       </c>
       <c r="I130" s="8">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J130" s="8">
         <v>0</v>
       </c>
       <c r="K130" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L130" s="8">
         <v>1</v>
       </c>
       <c r="M130" s="8">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N130" s="8">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="O130" s="8"/>
       <c r="P130" s="8"/>
@@ -11434,7 +11434,7 @@
         <v>14</v>
       </c>
       <c r="I131" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J131" s="8">
         <v>0</v>
@@ -11447,10 +11447,10 @@
       </c>
       <c r="M131" s="8">
         <f t="shared" ref="M131:M194" si="2">I131+J131+K131+L131</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N131" s="8">
-        <v>463</v>
+        <v>438</v>
       </c>
       <c r="O131" s="8"/>
       <c r="P131" s="8"/>
@@ -11485,7 +11485,7 @@
         <v>12</v>
       </c>
       <c r="I132" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J132" s="8">
         <v>0</v>
@@ -11498,10 +11498,10 @@
       </c>
       <c r="M132" s="8">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N132" s="8">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="O132" s="8"/>
       <c r="P132" s="8"/>
@@ -11536,23 +11536,23 @@
         <v>12</v>
       </c>
       <c r="I133" s="8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J133" s="8">
         <v>0</v>
       </c>
       <c r="K133" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L133" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M133" s="8">
         <f t="shared" si="2"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N133" s="8">
-        <v>295</v>
+        <v>8</v>
       </c>
       <c r="O133" s="8"/>
       <c r="P133" s="8"/>
@@ -11603,7 +11603,7 @@
         <v>4</v>
       </c>
       <c r="N134" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O134" s="8"/>
       <c r="P134" s="8"/>
@@ -11638,23 +11638,23 @@
         <v>15</v>
       </c>
       <c r="I135" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J135" s="8">
         <v>0</v>
       </c>
       <c r="K135" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L135" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M135" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N135" s="8">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="O135" s="8"/>
       <c r="P135" s="8"/>
@@ -11695,17 +11695,17 @@
         <v>0</v>
       </c>
       <c r="K136" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L136" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M136" s="8">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N136" s="8">
-        <v>350</v>
+        <v>292</v>
       </c>
       <c r="O136" s="8"/>
       <c r="P136" s="8"/>
@@ -11740,7 +11740,7 @@
         <v>15</v>
       </c>
       <c r="I137" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J137" s="8">
         <v>0</v>
@@ -11753,10 +11753,10 @@
       </c>
       <c r="M137" s="8">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N137" s="8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O137" s="8"/>
       <c r="P137" s="8"/>
@@ -11791,23 +11791,23 @@
         <v>12</v>
       </c>
       <c r="I138" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J138" s="8">
         <v>0</v>
       </c>
       <c r="K138" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L138" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M138" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N138" s="8">
-        <v>964</v>
+        <v>969</v>
       </c>
       <c r="O138" s="8"/>
       <c r="P138" s="8"/>
@@ -11851,14 +11851,14 @@
         <v>0</v>
       </c>
       <c r="L139" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M139" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N139" s="8">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O139" s="8"/>
       <c r="P139" s="8"/>
@@ -11893,7 +11893,7 @@
         <v>15</v>
       </c>
       <c r="I140" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J140" s="8">
         <v>0</v>
@@ -11906,10 +11906,10 @@
       </c>
       <c r="M140" s="8">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N140" s="8">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="O140" s="8"/>
       <c r="P140" s="8"/>
@@ -11953,11 +11953,11 @@
         <v>0</v>
       </c>
       <c r="L141" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M141" s="8">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N141" s="8">
         <v>0</v>
@@ -12055,11 +12055,11 @@
         <v>0</v>
       </c>
       <c r="L143" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M143" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N143" s="8">
         <v>0</v>
@@ -12164,7 +12164,7 @@
         <v>4</v>
       </c>
       <c r="N145" s="8">
-        <v>823</v>
+        <v>778</v>
       </c>
       <c r="O145" s="8"/>
       <c r="P145" s="8"/>
@@ -12199,7 +12199,7 @@
         <v>16</v>
       </c>
       <c r="I146" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J146" s="8">
         <v>0</v>
@@ -12212,7 +12212,7 @@
       </c>
       <c r="M146" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N146" s="8">
         <v>0</v>
@@ -12250,7 +12250,7 @@
         <v>14</v>
       </c>
       <c r="I147" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J147" s="8">
         <v>0</v>
@@ -12263,10 +12263,10 @@
       </c>
       <c r="M147" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N147" s="8">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="O147" s="8"/>
       <c r="P147" s="8"/>
@@ -12317,7 +12317,7 @@
         <v>2</v>
       </c>
       <c r="N148" s="8">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="O148" s="8"/>
       <c r="P148" s="8"/>
@@ -12361,14 +12361,14 @@
         <v>0</v>
       </c>
       <c r="L149" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M149" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N149" s="8">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="O149" s="8"/>
       <c r="P149" s="8"/>
@@ -12409,17 +12409,17 @@
         <v>0</v>
       </c>
       <c r="K150" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L150" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M150" s="8">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="N150" s="8">
-        <v>566</v>
+        <v>552</v>
       </c>
       <c r="O150" s="8"/>
       <c r="P150" s="8"/>
@@ -12470,7 +12470,7 @@
         <v>3</v>
       </c>
       <c r="N151" s="8">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O151" s="8"/>
       <c r="P151" s="8"/>
@@ -12521,7 +12521,7 @@
         <v>3</v>
       </c>
       <c r="N152" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O152" s="8"/>
       <c r="P152" s="8"/>
@@ -12565,11 +12565,11 @@
         <v>0</v>
       </c>
       <c r="L153" s="8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M153" s="8">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N153" s="8">
         <v>0</v>
@@ -12623,7 +12623,7 @@
         <v>2</v>
       </c>
       <c r="N154" s="8">
-        <v>0</v>
+        <v>454</v>
       </c>
       <c r="O154" s="8"/>
       <c r="P154" s="8"/>
@@ -12929,7 +12929,7 @@
         <v>3</v>
       </c>
       <c r="N160" s="8">
-        <v>0</v>
+        <v>445</v>
       </c>
       <c r="O160" s="8"/>
       <c r="P160" s="8"/>
@@ -12980,7 +12980,7 @@
         <v>5</v>
       </c>
       <c r="N161" s="8">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="O161" s="8"/>
       <c r="P161" s="8"/>
@@ -13015,7 +13015,7 @@
         <v>13</v>
       </c>
       <c r="I162" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J162" s="8">
         <v>0</v>
@@ -13028,10 +13028,10 @@
       </c>
       <c r="M162" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N162" s="8">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="O162" s="8"/>
       <c r="P162" s="8"/>
@@ -13082,7 +13082,7 @@
         <v>4</v>
       </c>
       <c r="N163" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O163" s="8"/>
       <c r="P163" s="8"/>
@@ -13133,7 +13133,7 @@
         <v>2</v>
       </c>
       <c r="N164" s="8">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="O164" s="8"/>
       <c r="P164" s="8"/>
@@ -13184,7 +13184,7 @@
         <v>9</v>
       </c>
       <c r="N165" s="8">
-        <v>1152</v>
+        <v>1070</v>
       </c>
       <c r="O165" s="8"/>
       <c r="P165" s="8"/>
@@ -13235,7 +13235,7 @@
         <v>2</v>
       </c>
       <c r="N166" s="8">
-        <v>883</v>
+        <v>0</v>
       </c>
       <c r="O166" s="8"/>
       <c r="P166" s="8"/>
@@ -13321,23 +13321,23 @@
         <v>14</v>
       </c>
       <c r="I168" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J168" s="8">
         <v>0</v>
       </c>
       <c r="K168" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L168" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M168" s="8">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N168" s="8">
-        <v>173</v>
+        <v>124</v>
       </c>
       <c r="O168" s="8"/>
       <c r="P168" s="8"/>
@@ -13439,7 +13439,7 @@
         <v>1</v>
       </c>
       <c r="N170" s="8">
-        <v>652</v>
+        <v>640</v>
       </c>
       <c r="O170" s="8"/>
       <c r="P170" s="8"/>
@@ -13541,7 +13541,7 @@
         <v>1</v>
       </c>
       <c r="N172" s="8">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="O172" s="8"/>
       <c r="P172" s="8"/>
@@ -13585,14 +13585,14 @@
         <v>0</v>
       </c>
       <c r="L173" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M173" s="8">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N173" s="8">
-        <v>552</v>
+        <v>529</v>
       </c>
       <c r="O173" s="8"/>
       <c r="P173" s="8"/>
@@ -13898,7 +13898,7 @@
         <v>2</v>
       </c>
       <c r="N179" s="8">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O179" s="8"/>
       <c r="P179" s="8"/>
@@ -13933,23 +13933,23 @@
         <v>13</v>
       </c>
       <c r="I180" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J180" s="8">
         <v>0</v>
       </c>
       <c r="K180" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L180" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M180" s="8">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N180" s="8">
-        <v>451</v>
+        <v>379</v>
       </c>
       <c r="O180" s="8"/>
       <c r="P180" s="8"/>
@@ -14000,7 +14000,7 @@
         <v>3</v>
       </c>
       <c r="N181" s="8">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="O181" s="8"/>
       <c r="P181" s="8"/>
@@ -14086,7 +14086,7 @@
         <v>12</v>
       </c>
       <c r="I183" s="8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J183" s="8">
         <v>0</v>
@@ -14099,10 +14099,10 @@
       </c>
       <c r="M183" s="8">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N183" s="8">
-        <v>420</v>
+        <v>377</v>
       </c>
       <c r="O183" s="8"/>
       <c r="P183" s="8"/>
@@ -14188,7 +14188,7 @@
         <v>12</v>
       </c>
       <c r="I185" s="8">
-        <v>460</v>
+        <v>379</v>
       </c>
       <c r="J185" s="8">
         <v>0</v>
@@ -14201,7 +14201,7 @@
       </c>
       <c r="M185" s="8">
         <f t="shared" si="2"/>
-        <v>460</v>
+        <v>379</v>
       </c>
       <c r="N185" s="8">
         <v>1659</v>
@@ -14255,7 +14255,7 @@
         <v>6</v>
       </c>
       <c r="N186" s="8">
-        <v>791</v>
+        <v>678</v>
       </c>
       <c r="O186" s="8"/>
       <c r="P186" s="8"/>
@@ -14306,7 +14306,7 @@
         <v>1</v>
       </c>
       <c r="N187" s="8">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="O187" s="8"/>
       <c r="P187" s="8"/>
@@ -14341,7 +14341,7 @@
         <v>15</v>
       </c>
       <c r="I188" s="8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J188" s="8">
         <v>0</v>
@@ -14354,10 +14354,10 @@
       </c>
       <c r="M188" s="8">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N188" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O188" s="8"/>
       <c r="P188" s="8"/>
@@ -14443,7 +14443,7 @@
         <v>12</v>
       </c>
       <c r="I190" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J190" s="8">
         <v>0</v>
@@ -14456,10 +14456,10 @@
       </c>
       <c r="M190" s="8">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N190" s="8">
-        <v>307</v>
+        <v>290</v>
       </c>
       <c r="O190" s="8"/>
       <c r="P190" s="8"/>
@@ -14494,7 +14494,7 @@
         <v>12</v>
       </c>
       <c r="I191" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J191" s="8">
         <v>0</v>
@@ -14507,10 +14507,10 @@
       </c>
       <c r="M191" s="8">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N191" s="8">
-        <v>671</v>
+        <v>525</v>
       </c>
       <c r="O191" s="8"/>
       <c r="P191" s="8"/>
@@ -14612,7 +14612,7 @@
         <v>3</v>
       </c>
       <c r="N193" s="8">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="O193" s="8"/>
       <c r="P193" s="8"/>
@@ -14647,7 +14647,7 @@
         <v>15</v>
       </c>
       <c r="I194" s="8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J194" s="8">
         <v>0</v>
@@ -14656,14 +14656,14 @@
         <v>0</v>
       </c>
       <c r="L194" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M194" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N194" s="8">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="O194" s="8"/>
       <c r="P194" s="8"/>
@@ -14806,17 +14806,17 @@
         <v>0</v>
       </c>
       <c r="K197" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L197" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M197" s="8">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="N197" s="8">
-        <v>439</v>
+        <v>323</v>
       </c>
       <c r="O197" s="8"/>
       <c r="P197" s="8"/>
@@ -15122,7 +15122,7 @@
         <v>2</v>
       </c>
       <c r="N203" s="8">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O203" s="8"/>
       <c r="P203" s="8"/>
@@ -15326,7 +15326,7 @@
         <v>4</v>
       </c>
       <c r="N207" s="8">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="O207" s="8"/>
       <c r="P207" s="8"/>
@@ -15361,23 +15361,23 @@
         <v>14</v>
       </c>
       <c r="I208" s="8">
+        <v>1</v>
+      </c>
+      <c r="J208" s="8">
+        <v>0</v>
+      </c>
+      <c r="K208" s="8">
         <v>2</v>
       </c>
-      <c r="J208" s="8">
-        <v>0</v>
-      </c>
-      <c r="K208" s="8">
-        <v>0</v>
-      </c>
       <c r="L208" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M208" s="8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N208" s="8">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="O208" s="8"/>
       <c r="P208" s="8"/>
@@ -15530,7 +15530,7 @@
         <v>3</v>
       </c>
       <c r="N211" s="8">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="O211" s="8"/>
       <c r="P211" s="8"/>
@@ -15565,7 +15565,7 @@
         <v>14</v>
       </c>
       <c r="I212" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J212" s="8">
         <v>0</v>
@@ -15578,7 +15578,7 @@
       </c>
       <c r="M212" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N212" s="8">
         <v>0</v>
@@ -15667,23 +15667,23 @@
         <v>14</v>
       </c>
       <c r="I214" s="8">
+        <v>2</v>
+      </c>
+      <c r="J214" s="8">
+        <v>0</v>
+      </c>
+      <c r="K214" s="8">
+        <v>0</v>
+      </c>
+      <c r="L214" s="8">
         <v>1</v>
-      </c>
-      <c r="J214" s="8">
-        <v>0</v>
-      </c>
-      <c r="K214" s="8">
-        <v>0</v>
-      </c>
-      <c r="L214" s="8">
-        <v>0</v>
       </c>
       <c r="M214" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N214" s="8">
-        <v>454</v>
+        <v>435</v>
       </c>
       <c r="O214" s="8"/>
       <c r="P214" s="8"/>
@@ -15718,7 +15718,7 @@
         <v>14</v>
       </c>
       <c r="I215" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J215" s="8">
         <v>0</v>
@@ -15731,10 +15731,10 @@
       </c>
       <c r="M215" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N215" s="8">
-        <v>638</v>
+        <v>614</v>
       </c>
       <c r="O215" s="8"/>
       <c r="P215" s="8"/>
@@ -15836,7 +15836,7 @@
         <v>3</v>
       </c>
       <c r="N217" s="8">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="O217" s="8"/>
       <c r="P217" s="8"/>
@@ -15887,7 +15887,7 @@
         <v>4</v>
       </c>
       <c r="N218" s="8">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="O218" s="8"/>
       <c r="P218" s="8"/>
@@ -15938,7 +15938,7 @@
         <v>4</v>
       </c>
       <c r="N219" s="8">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="O219" s="8"/>
       <c r="P219" s="8"/>
@@ -16040,7 +16040,7 @@
         <v>2</v>
       </c>
       <c r="N221" s="8">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O221" s="8"/>
       <c r="P221" s="8"/>
@@ -16126,20 +16126,20 @@
         <v>15</v>
       </c>
       <c r="I223" s="8">
+        <v>1</v>
+      </c>
+      <c r="J223" s="8">
+        <v>0</v>
+      </c>
+      <c r="K223" s="8">
         <v>2</v>
       </c>
-      <c r="J223" s="8">
-        <v>0</v>
-      </c>
-      <c r="K223" s="8">
-        <v>0</v>
-      </c>
       <c r="L223" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M223" s="8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N223" s="8">
         <v>0</v>
@@ -16177,20 +16177,20 @@
         <v>13</v>
       </c>
       <c r="I224" s="8">
+        <v>2</v>
+      </c>
+      <c r="J224" s="8">
+        <v>0</v>
+      </c>
+      <c r="K224" s="8">
         <v>1</v>
       </c>
-      <c r="J224" s="8">
-        <v>0</v>
-      </c>
-      <c r="K224" s="8">
-        <v>0</v>
-      </c>
       <c r="L224" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M224" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N224" s="8">
         <v>174</v>
@@ -16244,7 +16244,7 @@
         <v>3</v>
       </c>
       <c r="N225" s="8">
-        <v>467</v>
+        <v>422</v>
       </c>
       <c r="O225" s="8"/>
       <c r="P225" s="8"/>
@@ -16295,7 +16295,7 @@
         <v>0</v>
       </c>
       <c r="N226" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O226" s="8"/>
       <c r="P226" s="8"/>
@@ -16397,7 +16397,7 @@
         <v>2</v>
       </c>
       <c r="N228" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O228" s="8"/>
       <c r="P228" s="8"/>
@@ -16432,7 +16432,7 @@
         <v>15</v>
       </c>
       <c r="I229" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J229" s="8">
         <v>0</v>
@@ -16445,10 +16445,10 @@
       </c>
       <c r="M229" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N229" s="8">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="O229" s="8"/>
       <c r="P229" s="8"/>
@@ -16489,10 +16489,10 @@
         <v>0</v>
       </c>
       <c r="K230" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L230" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M230" s="8">
         <f t="shared" si="3"/>
@@ -16585,7 +16585,7 @@
         <v>12</v>
       </c>
       <c r="I232" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J232" s="8">
         <v>0</v>
@@ -16598,10 +16598,10 @@
       </c>
       <c r="M232" s="8">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N232" s="8">
-        <v>383</v>
+        <v>316</v>
       </c>
       <c r="O232" s="8"/>
       <c r="P232" s="8"/>
@@ -16636,23 +16636,23 @@
         <v>15</v>
       </c>
       <c r="I233" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J233" s="8">
         <v>0</v>
       </c>
       <c r="K233" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L233" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M233" s="8">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N233" s="8">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="O233" s="8"/>
       <c r="P233" s="8"/>
@@ -16687,7 +16687,7 @@
         <v>15</v>
       </c>
       <c r="I234" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J234" s="8">
         <v>0</v>
@@ -16700,10 +16700,10 @@
       </c>
       <c r="M234" s="8">
         <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="N234" s="8">
         <v>2</v>
-      </c>
-      <c r="N234" s="8">
-        <v>0</v>
       </c>
       <c r="O234" s="8"/>
       <c r="P234" s="8"/>
@@ -16754,7 +16754,7 @@
         <v>2</v>
       </c>
       <c r="N235" s="8">
-        <v>182</v>
+        <v>37</v>
       </c>
       <c r="O235" s="8"/>
       <c r="P235" s="8"/>
@@ -16846,17 +16846,17 @@
         <v>0</v>
       </c>
       <c r="K237" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L237" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M237" s="8">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="N237" s="8">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="O237" s="8"/>
       <c r="P237" s="8"/>
@@ -16907,7 +16907,7 @@
         <v>4</v>
       </c>
       <c r="N238" s="8">
-        <v>430</v>
+        <v>413</v>
       </c>
       <c r="O238" s="8"/>
       <c r="P238" s="8"/>
@@ -16958,7 +16958,7 @@
         <v>3</v>
       </c>
       <c r="N239" s="8">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="O239" s="8"/>
       <c r="P239" s="8"/>
@@ -16999,17 +16999,17 @@
         <v>0</v>
       </c>
       <c r="K240" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L240" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M240" s="8">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N240" s="8">
-        <v>295</v>
+        <v>242</v>
       </c>
       <c r="O240" s="8"/>
       <c r="P240" s="8"/>
@@ -17060,7 +17060,7 @@
         <v>3</v>
       </c>
       <c r="N241" s="8">
-        <v>248</v>
+        <v>215</v>
       </c>
       <c r="O241" s="8"/>
       <c r="P241" s="8"/>
@@ -17095,7 +17095,7 @@
         <v>12</v>
       </c>
       <c r="I242" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J242" s="8">
         <v>0</v>
@@ -17108,10 +17108,10 @@
       </c>
       <c r="M242" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N242" s="8">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="O242" s="8"/>
       <c r="P242" s="8"/>
@@ -17146,23 +17146,23 @@
         <v>15</v>
       </c>
       <c r="I243" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J243" s="8">
         <v>0</v>
       </c>
       <c r="K243" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L243" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M243" s="8">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N243" s="8">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="O243" s="8"/>
       <c r="P243" s="8"/>
@@ -17315,7 +17315,7 @@
         <v>3</v>
       </c>
       <c r="N246" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O246" s="8"/>
       <c r="P246" s="8"/>
@@ -17350,7 +17350,7 @@
         <v>13</v>
       </c>
       <c r="I247" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J247" s="8">
         <v>0</v>
@@ -17363,10 +17363,10 @@
       </c>
       <c r="M247" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N247" s="8">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="O247" s="8"/>
       <c r="P247" s="8"/>
@@ -17452,7 +17452,7 @@
         <v>13</v>
       </c>
       <c r="I249" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J249" s="8">
         <v>0</v>
@@ -17465,7 +17465,7 @@
       </c>
       <c r="M249" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N249" s="8">
         <v>0</v>
@@ -17503,7 +17503,7 @@
         <v>12</v>
       </c>
       <c r="I250" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J250" s="8">
         <v>0</v>
@@ -17516,10 +17516,10 @@
       </c>
       <c r="M250" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N250" s="8">
-        <v>1383</v>
+        <v>1374</v>
       </c>
       <c r="O250" s="8"/>
       <c r="P250" s="8"/>
@@ -17570,7 +17570,7 @@
         <v>2</v>
       </c>
       <c r="N251" s="8">
-        <v>1212</v>
+        <v>1199</v>
       </c>
       <c r="O251" s="8"/>
       <c r="P251" s="8"/>
@@ -17656,7 +17656,7 @@
         <v>14</v>
       </c>
       <c r="I253" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J253" s="8">
         <v>0</v>
@@ -17669,7 +17669,7 @@
       </c>
       <c r="M253" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N253" s="8">
         <v>1196</v>
@@ -17707,7 +17707,7 @@
         <v>14</v>
       </c>
       <c r="I254" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J254" s="8">
         <v>0</v>
@@ -17720,7 +17720,7 @@
       </c>
       <c r="M254" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N254" s="8">
         <v>519</v>
@@ -17774,7 +17774,7 @@
         <v>3</v>
       </c>
       <c r="N255" s="8">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="O255" s="8"/>
       <c r="P255" s="8"/>
@@ -17825,7 +17825,7 @@
         <v>3</v>
       </c>
       <c r="N256" s="8">
-        <v>1030</v>
+        <v>1023</v>
       </c>
       <c r="O256" s="8"/>
       <c r="P256" s="8"/>
@@ -17876,7 +17876,7 @@
         <v>4</v>
       </c>
       <c r="N257" s="8">
-        <v>331</v>
+        <v>311</v>
       </c>
       <c r="O257" s="8"/>
       <c r="P257" s="8"/>
@@ -17911,7 +17911,7 @@
         <v>16</v>
       </c>
       <c r="I258" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J258" s="8">
         <v>0</v>
@@ -17924,10 +17924,10 @@
       </c>
       <c r="M258" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N258" s="8">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="O258" s="8"/>
       <c r="P258" s="8"/>
@@ -17978,7 +17978,7 @@
         <v>3</v>
       </c>
       <c r="N259" s="8">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="O259" s="8"/>
       <c r="P259" s="8"/>
@@ -18013,23 +18013,23 @@
         <v>13</v>
       </c>
       <c r="I260" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J260" s="8">
         <v>0</v>
       </c>
       <c r="K260" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L260" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M260" s="8">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N260" s="8">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="O260" s="8"/>
       <c r="P260" s="8"/>
@@ -18064,23 +18064,23 @@
         <v>12</v>
       </c>
       <c r="I261" s="8">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J261" s="8">
         <v>0</v>
       </c>
       <c r="K261" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L261" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M261" s="8">
         <f t="shared" si="4"/>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N261" s="8">
-        <v>533</v>
+        <v>312</v>
       </c>
       <c r="O261" s="8"/>
       <c r="P261" s="8"/>
@@ -18121,17 +18121,17 @@
         <v>0</v>
       </c>
       <c r="K262" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L262" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M262" s="8">
         <f t="shared" si="4"/>
         <v>15</v>
       </c>
       <c r="N262" s="8">
-        <v>171</v>
+        <v>89</v>
       </c>
       <c r="O262" s="8"/>
       <c r="P262" s="8"/>
@@ -18166,7 +18166,7 @@
         <v>12</v>
       </c>
       <c r="I263" s="8">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J263" s="8">
         <v>0</v>
@@ -18175,14 +18175,14 @@
         <v>0</v>
       </c>
       <c r="L263" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M263" s="8">
         <f t="shared" si="4"/>
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="N263" s="8">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="O263" s="8"/>
       <c r="P263" s="8"/>
@@ -18233,7 +18233,7 @@
         <v>2</v>
       </c>
       <c r="N264" s="8">
-        <v>1011</v>
+        <v>1006</v>
       </c>
       <c r="O264" s="8"/>
       <c r="P264" s="8"/>
@@ -18277,14 +18277,14 @@
         <v>0</v>
       </c>
       <c r="L265" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M265" s="8">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N265" s="8">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="O265" s="8"/>
       <c r="P265" s="8"/>
@@ -18335,7 +18335,7 @@
         <v>3</v>
       </c>
       <c r="N266" s="8">
-        <v>1536</v>
+        <v>1532</v>
       </c>
       <c r="O266" s="8"/>
       <c r="P266" s="8"/>
@@ -18386,7 +18386,7 @@
         <v>3</v>
       </c>
       <c r="N267" s="8">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O267" s="8"/>
       <c r="P267" s="8"/>
@@ -18743,7 +18743,7 @@
         <v>3</v>
       </c>
       <c r="N274" s="8">
-        <v>474</v>
+        <v>461</v>
       </c>
       <c r="O274" s="8"/>
       <c r="P274" s="8"/>
@@ -18829,7 +18829,7 @@
         <v>15</v>
       </c>
       <c r="I276" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J276" s="8">
         <v>0</v>
@@ -18842,7 +18842,7 @@
       </c>
       <c r="M276" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N276" s="8">
         <v>0</v>
@@ -18940,14 +18940,14 @@
         <v>0</v>
       </c>
       <c r="L278" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M278" s="8">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N278" s="8">
-        <v>1283</v>
+        <v>1010</v>
       </c>
       <c r="O278" s="8"/>
       <c r="P278" s="8"/>
@@ -18982,7 +18982,7 @@
         <v>13</v>
       </c>
       <c r="I279" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J279" s="8">
         <v>0</v>
@@ -18995,7 +18995,7 @@
       </c>
       <c r="M279" s="8">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N279" s="8">
         <v>0</v>
@@ -19186,7 +19186,7 @@
         <v>12</v>
       </c>
       <c r="I283" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J283" s="8">
         <v>0</v>
@@ -19199,7 +19199,7 @@
       </c>
       <c r="M283" s="8">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N283" s="8">
         <v>0</v>
@@ -19237,7 +19237,7 @@
         <v>12</v>
       </c>
       <c r="I284" s="8">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J284" s="8">
         <v>0</v>
@@ -19250,7 +19250,7 @@
       </c>
       <c r="M284" s="8">
         <f t="shared" si="4"/>
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="N284" s="8">
         <v>0</v>
@@ -19304,7 +19304,7 @@
         <v>2</v>
       </c>
       <c r="N285" s="8">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="O285" s="8"/>
       <c r="P285" s="8"/>
@@ -19339,7 +19339,7 @@
         <v>12</v>
       </c>
       <c r="I286" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J286" s="8">
         <v>0</v>
@@ -19352,10 +19352,10 @@
       </c>
       <c r="M286" s="8">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N286" s="8">
-        <v>967</v>
+        <v>959</v>
       </c>
       <c r="O286" s="8"/>
       <c r="P286" s="8"/>
@@ -19406,7 +19406,7 @@
         <v>9</v>
       </c>
       <c r="N287" s="8">
-        <v>1109</v>
+        <v>1104</v>
       </c>
       <c r="O287" s="8"/>
       <c r="P287" s="8"/>
@@ -19457,7 +19457,7 @@
         <v>4</v>
       </c>
       <c r="N288" s="8">
-        <v>1399</v>
+        <v>1369</v>
       </c>
       <c r="O288" s="8"/>
       <c r="P288" s="8"/>
@@ -19492,23 +19492,23 @@
         <v>14</v>
       </c>
       <c r="I289" s="8">
+        <v>2</v>
+      </c>
+      <c r="J289" s="8">
+        <v>0</v>
+      </c>
+      <c r="K289" s="8">
+        <v>0</v>
+      </c>
+      <c r="L289" s="8">
         <v>1</v>
-      </c>
-      <c r="J289" s="8">
-        <v>0</v>
-      </c>
-      <c r="K289" s="8">
-        <v>0</v>
-      </c>
-      <c r="L289" s="8">
-        <v>0</v>
       </c>
       <c r="M289" s="8">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N289" s="8">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O289" s="8"/>
       <c r="P289" s="8"/>
@@ -19552,14 +19552,14 @@
         <v>0</v>
       </c>
       <c r="L290" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M290" s="8">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N290" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O290" s="8"/>
       <c r="P290" s="8"/>
@@ -19594,23 +19594,23 @@
         <v>12</v>
       </c>
       <c r="I291" s="8">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J291" s="8">
         <v>0</v>
       </c>
       <c r="K291" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L291" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M291" s="8">
         <f t="shared" si="4"/>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="N291" s="8">
-        <v>1451</v>
+        <v>1169</v>
       </c>
       <c r="O291" s="8"/>
       <c r="P291" s="8"/>
@@ -19661,7 +19661,7 @@
         <v>2</v>
       </c>
       <c r="N292" s="8">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="O292" s="8"/>
       <c r="P292" s="8"/>
@@ -19747,7 +19747,7 @@
         <v>12</v>
       </c>
       <c r="I294" s="8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J294" s="8">
         <v>0</v>
@@ -19760,10 +19760,10 @@
       </c>
       <c r="M294" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N294" s="8">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="O294" s="8"/>
       <c r="P294" s="8"/>
@@ -20053,7 +20053,7 @@
         <v>13</v>
       </c>
       <c r="I300" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J300" s="8">
         <v>0</v>
@@ -20066,7 +20066,7 @@
       </c>
       <c r="M300" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N300" s="8">
         <v>0</v>
@@ -20120,7 +20120,7 @@
         <v>6</v>
       </c>
       <c r="N301" s="8">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O301" s="8"/>
       <c r="P301" s="8"/>
@@ -20171,7 +20171,7 @@
         <v>5</v>
       </c>
       <c r="N302" s="8">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O302" s="8"/>
       <c r="P302" s="8"/>
@@ -20215,11 +20215,11 @@
         <v>0</v>
       </c>
       <c r="L303" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M303" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N303" s="8">
         <v>0</v>
@@ -20324,7 +20324,7 @@
         <v>8</v>
       </c>
       <c r="N305" s="8">
-        <v>476</v>
+        <v>446</v>
       </c>
       <c r="O305" s="8"/>
       <c r="P305" s="8"/>
@@ -20375,7 +20375,7 @@
         <v>9</v>
       </c>
       <c r="N306" s="8">
-        <v>985</v>
+        <v>927</v>
       </c>
       <c r="O306" s="8"/>
       <c r="P306" s="8"/>
@@ -20426,7 +20426,7 @@
         <v>11</v>
       </c>
       <c r="N307" s="8">
-        <v>993</v>
+        <v>951</v>
       </c>
       <c r="O307" s="8"/>
       <c r="P307" s="8"/>
@@ -20477,7 +20477,7 @@
         <v>10</v>
       </c>
       <c r="N308" s="8">
-        <v>904</v>
+        <v>812</v>
       </c>
       <c r="O308" s="8"/>
       <c r="P308" s="8"/>
@@ -20614,7 +20614,7 @@
         <v>16</v>
       </c>
       <c r="I311" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J311" s="8">
         <v>0</v>
@@ -20627,10 +20627,10 @@
       </c>
       <c r="M311" s="8">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N311" s="8">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="O311" s="8"/>
       <c r="P311" s="8"/>
@@ -20681,7 +20681,7 @@
         <v>6</v>
       </c>
       <c r="N312" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O312" s="8"/>
       <c r="P312" s="8"/>
@@ -20732,7 +20732,7 @@
         <v>3</v>
       </c>
       <c r="N313" s="8">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="O313" s="8"/>
       <c r="P313" s="8"/>
@@ -20783,7 +20783,7 @@
         <v>11</v>
       </c>
       <c r="N314" s="8">
-        <v>383</v>
+        <v>335</v>
       </c>
       <c r="O314" s="8"/>
       <c r="P314" s="8"/>
@@ -20834,7 +20834,7 @@
         <v>8</v>
       </c>
       <c r="N315" s="8">
-        <v>344</v>
+        <v>286</v>
       </c>
       <c r="O315" s="8"/>
       <c r="P315" s="8"/>
@@ -20869,7 +20869,7 @@
         <v>12</v>
       </c>
       <c r="I316" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J316" s="8">
         <v>0</v>
@@ -20882,10 +20882,10 @@
       </c>
       <c r="M316" s="8">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N316" s="8">
-        <v>672</v>
+        <v>653</v>
       </c>
       <c r="O316" s="8"/>
       <c r="P316" s="8"/>
@@ -20936,7 +20936,7 @@
         <v>9</v>
       </c>
       <c r="N317" s="8">
-        <v>238</v>
+        <v>208</v>
       </c>
       <c r="O317" s="8"/>
       <c r="P317" s="8"/>
@@ -20971,23 +20971,23 @@
         <v>12</v>
       </c>
       <c r="I318" s="8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J318" s="8">
         <v>0</v>
       </c>
       <c r="K318" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L318" s="8">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M318" s="8">
         <f t="shared" si="4"/>
         <v>14</v>
       </c>
       <c r="N318" s="8">
-        <v>470</v>
+        <v>218</v>
       </c>
       <c r="O318" s="8"/>
       <c r="P318" s="8"/>
@@ -21038,7 +21038,7 @@
         <v>4</v>
       </c>
       <c r="N319" s="8">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="O319" s="8"/>
       <c r="P319" s="8"/>
@@ -21089,7 +21089,7 @@
         <v>4</v>
       </c>
       <c r="N320" s="8">
-        <v>661</v>
+        <v>634</v>
       </c>
       <c r="O320" s="8"/>
       <c r="P320" s="8"/>
@@ -21124,23 +21124,23 @@
         <v>14</v>
       </c>
       <c r="I321" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J321" s="8">
         <v>0</v>
       </c>
       <c r="K321" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L321" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M321" s="8">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N321" s="8">
-        <v>535</v>
+        <v>497</v>
       </c>
       <c r="O321" s="8"/>
       <c r="P321" s="8"/>
@@ -21191,7 +21191,7 @@
         <v>3</v>
       </c>
       <c r="N322" s="8">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="O322" s="8"/>
       <c r="P322" s="8"/>
@@ -21242,7 +21242,7 @@
         <v>4</v>
       </c>
       <c r="N323" s="8">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O323" s="8"/>
       <c r="P323" s="8"/>
@@ -21344,7 +21344,7 @@
         <v>3</v>
       </c>
       <c r="N325" s="8">
-        <v>415</v>
+        <v>341</v>
       </c>
       <c r="O325" s="8"/>
       <c r="P325" s="8"/>
@@ -21395,7 +21395,7 @@
         <v>3</v>
       </c>
       <c r="N326" s="8">
-        <v>998</v>
+        <v>990</v>
       </c>
       <c r="O326" s="8"/>
       <c r="P326" s="8"/>
@@ -21430,7 +21430,7 @@
         <v>16</v>
       </c>
       <c r="I327" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J327" s="8">
         <v>0</v>
@@ -21443,10 +21443,10 @@
       </c>
       <c r="M327" s="8">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N327" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O327" s="8"/>
       <c r="P327" s="8"/>
@@ -21497,7 +21497,7 @@
         <v>2</v>
       </c>
       <c r="N328" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O328" s="8"/>
       <c r="P328" s="8"/>
@@ -21548,7 +21548,7 @@
         <v>4</v>
       </c>
       <c r="N329" s="8">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="O329" s="8"/>
       <c r="P329" s="8"/>
@@ -21599,7 +21599,7 @@
         <v>2</v>
       </c>
       <c r="N330" s="8">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="O330" s="8"/>
       <c r="P330" s="8"/>
@@ -21752,7 +21752,7 @@
         <v>3</v>
       </c>
       <c r="N333" s="8">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="O333" s="8"/>
       <c r="P333" s="8"/>
@@ -21787,7 +21787,7 @@
         <v>13</v>
       </c>
       <c r="I334" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J334" s="8">
         <v>0</v>
@@ -21800,10 +21800,10 @@
       </c>
       <c r="M334" s="8">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N334" s="8">
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="O334" s="8"/>
       <c r="P334" s="8"/>
@@ -21854,7 +21854,7 @@
         <v>2</v>
       </c>
       <c r="N335" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O335" s="8"/>
       <c r="P335" s="8"/>
@@ -21905,7 +21905,7 @@
         <v>4</v>
       </c>
       <c r="N336" s="8">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="O336" s="8"/>
       <c r="P336" s="8"/>
@@ -21940,23 +21940,23 @@
         <v>12</v>
       </c>
       <c r="I337" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J337" s="8">
         <v>0</v>
       </c>
       <c r="K337" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L337" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M337" s="8">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N337" s="8">
-        <v>1187</v>
+        <v>1173</v>
       </c>
       <c r="O337" s="8"/>
       <c r="P337" s="8"/>
@@ -22007,7 +22007,7 @@
         <v>13</v>
       </c>
       <c r="N338" s="8">
-        <v>1197</v>
+        <v>1127</v>
       </c>
       <c r="O338" s="8"/>
       <c r="P338" s="8"/>
@@ -22058,7 +22058,7 @@
         <v>3</v>
       </c>
       <c r="N339" s="8">
-        <v>827</v>
+        <v>809</v>
       </c>
       <c r="O339" s="8"/>
       <c r="P339" s="8"/>
@@ -22093,23 +22093,23 @@
         <v>14</v>
       </c>
       <c r="I340" s="8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J340" s="8">
         <v>0</v>
       </c>
       <c r="K340" s="8">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L340" s="8">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M340" s="8">
         <f t="shared" si="5"/>
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="N340" s="8">
-        <v>662</v>
+        <v>552</v>
       </c>
       <c r="O340" s="8"/>
       <c r="P340" s="8"/>
@@ -22144,7 +22144,7 @@
         <v>14</v>
       </c>
       <c r="I341" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J341" s="8">
         <v>0</v>
@@ -22157,10 +22157,10 @@
       </c>
       <c r="M341" s="8">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N341" s="8">
-        <v>359</v>
+        <v>339</v>
       </c>
       <c r="O341" s="8"/>
       <c r="P341" s="8"/>
@@ -22211,7 +22211,7 @@
         <v>4</v>
       </c>
       <c r="N342" s="8">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O342" s="8"/>
       <c r="P342" s="8"/>
@@ -22348,7 +22348,7 @@
         <v>12</v>
       </c>
       <c r="I345" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J345" s="8">
         <v>0</v>
@@ -22361,7 +22361,7 @@
       </c>
       <c r="M345" s="8">
         <f t="shared" si="5"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N345" s="8">
         <v>0</v>
@@ -22450,23 +22450,23 @@
         <v>13</v>
       </c>
       <c r="I347" s="8">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J347" s="8">
         <v>0</v>
       </c>
       <c r="K347" s="8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L347" s="8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M347" s="8">
         <f t="shared" si="5"/>
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N347" s="8">
-        <v>465</v>
+        <v>381</v>
       </c>
       <c r="O347" s="8"/>
       <c r="P347" s="9"/>
@@ -22501,7 +22501,7 @@
         <v>12</v>
       </c>
       <c r="I348" s="8">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J348" s="8">
         <v>0</v>
@@ -22514,7 +22514,7 @@
       </c>
       <c r="M348" s="8">
         <f t="shared" si="5"/>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N348" s="8">
         <v>0</v>
@@ -22714,14 +22714,14 @@
         <v>0</v>
       </c>
       <c r="L352" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M352" s="8">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N352" s="8">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="O352" s="8"/>
       <c r="P352" s="9"/>
@@ -23078,7 +23078,7 @@
         <v>3</v>
       </c>
       <c r="N359" s="8">
-        <v>0</v>
+        <v>991</v>
       </c>
       <c r="O359" s="8"/>
       <c r="P359" s="9"/>
@@ -23266,7 +23266,7 @@
         <v>12</v>
       </c>
       <c r="I363" s="8">
-        <v>598</v>
+        <v>573</v>
       </c>
       <c r="J363" s="8">
         <v>0</v>
@@ -23279,7 +23279,7 @@
       </c>
       <c r="M363" s="8">
         <f t="shared" si="5"/>
-        <v>598</v>
+        <v>573</v>
       </c>
       <c r="N363" s="8">
         <v>1318</v>
@@ -23435,7 +23435,7 @@
         <v>2</v>
       </c>
       <c r="N366" s="8">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O366" s="8"/>
       <c r="P366" s="9"/>
@@ -23470,7 +23470,7 @@
         <v>12</v>
       </c>
       <c r="I367" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J367" s="8">
         <v>0</v>
@@ -23483,7 +23483,7 @@
       </c>
       <c r="M367" s="8">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N367" s="8">
         <v>0</v>
@@ -23521,7 +23521,7 @@
         <v>12</v>
       </c>
       <c r="I368" s="8">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J368" s="8">
         <v>0</v>
@@ -23530,14 +23530,14 @@
         <v>0</v>
       </c>
       <c r="L368" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M368" s="8">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N368" s="8">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="O368" s="8"/>
       <c r="P368" s="9"/>
@@ -23639,7 +23639,7 @@
         <v>2</v>
       </c>
       <c r="N370" s="8">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="O370" s="8"/>
       <c r="P370" s="9"/>
@@ -23674,7 +23674,7 @@
         <v>13</v>
       </c>
       <c r="I371" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J371" s="8">
         <v>0</v>
@@ -23687,10 +23687,10 @@
       </c>
       <c r="M371" s="8">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N371" s="8">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O371" s="8"/>
       <c r="P371" s="9"/>
@@ -23792,7 +23792,7 @@
         <v>4</v>
       </c>
       <c r="N373" s="8">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O373" s="8"/>
       <c r="P373" s="9"/>
@@ -24235,7 +24235,7 @@
         <v>13</v>
       </c>
       <c r="I382" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J382" s="8">
         <v>0</v>
@@ -24248,7 +24248,7 @@
       </c>
       <c r="M382" s="8">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N382" s="8">
         <v>0</v>
@@ -24343,17 +24343,17 @@
         <v>0</v>
       </c>
       <c r="K384" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L384" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M384" s="8">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
       <c r="N384" s="8">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="O384" s="8"/>
       <c r="P384" s="9"/>
@@ -24388,7 +24388,7 @@
         <v>12</v>
       </c>
       <c r="I385" s="8">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="J385" s="8">
         <v>0</v>
@@ -24401,7 +24401,7 @@
       </c>
       <c r="M385" s="8">
         <f t="shared" si="5"/>
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="N385" s="8">
         <v>257</v>
@@ -24643,7 +24643,7 @@
         <v>12</v>
       </c>
       <c r="I390" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J390" s="8">
         <v>0</v>
@@ -24652,14 +24652,14 @@
         <v>0</v>
       </c>
       <c r="L390" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M390" s="8">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
       <c r="N390" s="8">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="O390" s="8"/>
       <c r="P390" s="7"/>
@@ -25051,7 +25051,7 @@
         <v>15</v>
       </c>
       <c r="I398" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J398" s="8">
         <v>0</v>
@@ -25060,11 +25060,11 @@
         <v>0</v>
       </c>
       <c r="L398" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M398" s="8">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N398" s="8">
         <v>0</v>
@@ -25373,7 +25373,7 @@
         <v>2</v>
       </c>
       <c r="N404" s="8">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="O404" s="7"/>
       <c r="P404" s="7"/>
@@ -25424,7 +25424,7 @@
         <v>2</v>
       </c>
       <c r="N405" s="8">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="O405" s="7"/>
       <c r="P405" s="7"/>
@@ -25577,7 +25577,7 @@
         <v>2</v>
       </c>
       <c r="N408" s="8">
-        <v>469</v>
+        <v>452</v>
       </c>
       <c r="O408" s="7"/>
       <c r="P408" s="7"/>
@@ -25612,7 +25612,7 @@
         <v>13</v>
       </c>
       <c r="I409" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J409" s="8">
         <v>0</v>
@@ -25625,10 +25625,10 @@
       </c>
       <c r="M409" s="8">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N409" s="8">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="O409" s="7"/>
       <c r="P409" s="7"/>
@@ -25679,7 +25679,7 @@
         <v>2</v>
       </c>
       <c r="N410" s="8">
-        <v>147</v>
+        <v>242</v>
       </c>
       <c r="O410" s="7"/>
       <c r="P410" s="7"/>
@@ -25730,7 +25730,7 @@
         <v>2</v>
       </c>
       <c r="N411" s="8">
-        <v>215</v>
+        <v>288</v>
       </c>
       <c r="O411" s="7"/>
       <c r="P411" s="7"/>
@@ -25781,7 +25781,7 @@
         <v>2</v>
       </c>
       <c r="N412" s="8">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="O412" s="7"/>
       <c r="P412" s="7"/>
@@ -25832,7 +25832,7 @@
         <v>2</v>
       </c>
       <c r="N413" s="8">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="O413" s="7"/>
       <c r="P413" s="7"/>
@@ -25918,7 +25918,7 @@
         <v>12</v>
       </c>
       <c r="I415" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J415" s="8">
         <v>0</v>
@@ -25931,10 +25931,10 @@
       </c>
       <c r="M415" s="8">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N415" s="8">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="O415" s="7"/>
       <c r="P415" s="7"/>
@@ -25985,7 +25985,7 @@
         <v>3</v>
       </c>
       <c r="N416" s="8">
-        <v>249</v>
+        <v>192</v>
       </c>
       <c r="O416" s="7"/>
       <c r="P416" s="7"/>
@@ -26036,7 +26036,7 @@
         <v>3</v>
       </c>
       <c r="N417" s="8">
-        <v>200</v>
+        <v>153</v>
       </c>
       <c r="O417" s="7"/>
       <c r="P417" s="7"/>
@@ -26077,17 +26077,17 @@
         <v>0</v>
       </c>
       <c r="K418" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L418" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M418" s="8">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="N418" s="8">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="O418" s="7"/>
       <c r="P418" s="7"/>
@@ -26138,7 +26138,7 @@
         <v>3</v>
       </c>
       <c r="N419" s="8">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O419" s="7"/>
       <c r="P419" s="7"/>
@@ -26189,7 +26189,7 @@
         <v>3</v>
       </c>
       <c r="N420" s="8">
-        <v>414</v>
+        <v>399</v>
       </c>
       <c r="O420" s="7"/>
       <c r="P420" s="7"/>
@@ -26240,7 +26240,7 @@
         <v>2</v>
       </c>
       <c r="N421" s="8">
-        <v>807</v>
+        <v>708</v>
       </c>
       <c r="O421" s="7"/>
       <c r="P421" s="7"/>
@@ -26291,7 +26291,7 @@
         <v>2</v>
       </c>
       <c r="N422" s="8">
-        <v>317</v>
+        <v>282</v>
       </c>
       <c r="O422" s="7"/>
       <c r="P422" s="7"/>
@@ -26342,7 +26342,7 @@
         <v>2</v>
       </c>
       <c r="N423" s="8">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="O423" s="7"/>
       <c r="P423" s="7"/>
@@ -26393,7 +26393,7 @@
         <v>2</v>
       </c>
       <c r="N424" s="8">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O424" s="7"/>
       <c r="P424" s="7"/>
@@ -26444,7 +26444,7 @@
         <v>2</v>
       </c>
       <c r="N425" s="8">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="O425" s="7"/>
       <c r="P425" s="7"/>
@@ -26495,7 +26495,7 @@
         <v>2</v>
       </c>
       <c r="N426" s="8">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="O426" s="7"/>
       <c r="P426" s="7"/>
@@ -26546,7 +26546,7 @@
         <v>2</v>
       </c>
       <c r="N427" s="8">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="O427" s="7"/>
       <c r="P427" s="7"/>
@@ -26699,7 +26699,7 @@
         <v>0</v>
       </c>
       <c r="N430" s="8">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="O430" s="7"/>
       <c r="P430" s="7"/>
@@ -26750,7 +26750,7 @@
         <v>0</v>
       </c>
       <c r="N431" s="8">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="O431" s="7"/>
       <c r="P431" s="7"/>
@@ -26801,7 +26801,7 @@
         <v>0</v>
       </c>
       <c r="N432" s="8">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="O432" s="7"/>
       <c r="P432" s="7"/>
@@ -26852,7 +26852,7 @@
         <v>0</v>
       </c>
       <c r="N433" s="8">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="O433" s="7"/>
       <c r="P433" s="7"/>
@@ -26896,11 +26896,11 @@
         <v>0</v>
       </c>
       <c r="L434" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M434" s="8">
         <f t="shared" ref="M434" si="8">I434+J434+K434+L434</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N434" s="8">
         <v>0</v>
@@ -27099,7 +27099,7 @@
         <v>0</v>
       </c>
       <c r="N438" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O438" s="7"/>
       <c r="P438" s="7"/>
@@ -27148,7 +27148,7 @@
         <v>0</v>
       </c>
       <c r="N439" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O439" s="7"/>
       <c r="P439" s="7"/>
@@ -34286,7 +34286,6 @@
       <c r="T763" s="7"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T439" xr:uid="{AF55B7BF-85DC-4082-9A73-200B4D79A598}"/>
   <conditionalFormatting sqref="A1:B1">
     <cfRule type="duplicateValues" dxfId="15" priority="23"/>
     <cfRule type="duplicateValues" dxfId="14" priority="24"/>

--- a/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
+++ b/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\Fossil Replenishment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA74F32B-9212-4C83-B1CD-CD460BB95FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFC13321-91EC-435E-8E47-1F5EA290C36D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6662473D-6E1F-42FD-999B-28162E22D4B5}"/>
   </bookViews>
@@ -4855,7 +4855,7 @@
         <v>12</v>
       </c>
       <c r="I2" s="8">
-        <v>827</v>
+        <v>702</v>
       </c>
       <c r="J2" s="8">
         <v>0</v>
@@ -4864,14 +4864,14 @@
         <v>0</v>
       </c>
       <c r="L2" s="8">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M2" s="8">
         <f>I2+J2+K2+L2</f>
-        <v>827</v>
+        <v>798</v>
       </c>
       <c r="N2" s="8">
-        <v>2191</v>
+        <v>2108</v>
       </c>
       <c r="O2" s="8"/>
       <c r="P2" s="8"/>
@@ -5008,7 +5008,7 @@
         <v>12</v>
       </c>
       <c r="I5" s="8">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J5" s="8">
         <v>0</v>
@@ -5017,11 +5017,11 @@
         <v>0</v>
       </c>
       <c r="L5" s="8">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="M5" s="8">
         <f t="shared" si="0"/>
-        <v>189</v>
+        <v>11</v>
       </c>
       <c r="N5" s="8">
         <v>0</v>
@@ -5059,7 +5059,7 @@
         <v>12</v>
       </c>
       <c r="I6" s="8">
-        <v>887</v>
+        <v>793</v>
       </c>
       <c r="J6" s="8">
         <v>0</v>
@@ -5068,14 +5068,14 @@
         <v>0</v>
       </c>
       <c r="L6" s="8">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M6" s="8">
         <f t="shared" si="0"/>
-        <v>887</v>
+        <v>913</v>
       </c>
       <c r="N6" s="8">
-        <v>1490</v>
+        <v>1370</v>
       </c>
       <c r="O6" s="8"/>
       <c r="P6" s="8"/>
@@ -5110,7 +5110,7 @@
         <v>12</v>
       </c>
       <c r="I7" s="8">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="J7" s="8">
         <v>0</v>
@@ -5123,10 +5123,10 @@
       </c>
       <c r="M7" s="8">
         <f t="shared" si="0"/>
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="N7" s="8">
-        <v>575</v>
+        <v>434</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
@@ -5161,23 +5161,23 @@
         <v>12</v>
       </c>
       <c r="I8" s="8">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J8" s="8">
         <v>0</v>
       </c>
       <c r="K8" s="8">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="L8" s="8">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M8" s="8">
         <f t="shared" si="0"/>
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N8" s="8">
-        <v>100</v>
+        <v>437</v>
       </c>
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
@@ -5212,7 +5212,7 @@
         <v>12</v>
       </c>
       <c r="I9" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J9" s="8">
         <v>0</v>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="M9" s="8">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N9" s="8">
         <v>0</v>
@@ -5263,7 +5263,7 @@
         <v>12</v>
       </c>
       <c r="I10" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" s="8">
         <v>0</v>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="M10" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" s="8">
         <v>0</v>
@@ -5314,7 +5314,7 @@
         <v>12</v>
       </c>
       <c r="I11" s="8">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="J11" s="8">
         <v>0</v>
@@ -5327,7 +5327,7 @@
       </c>
       <c r="M11" s="8">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N11" s="8">
         <v>0</v>
@@ -5365,7 +5365,7 @@
         <v>12</v>
       </c>
       <c r="I12" s="8">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J12" s="8">
         <v>0</v>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="M12" s="8">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="N12" s="8">
         <v>0</v>
@@ -5416,7 +5416,7 @@
         <v>12</v>
       </c>
       <c r="I13" s="8">
-        <v>246</v>
+        <v>188</v>
       </c>
       <c r="J13" s="8">
         <v>0</v>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="M13" s="8">
         <f t="shared" si="0"/>
-        <v>246</v>
+        <v>188</v>
       </c>
       <c r="N13" s="8">
         <v>810</v>
@@ -5467,23 +5467,23 @@
         <v>12</v>
       </c>
       <c r="I14" s="8">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J14" s="8">
         <v>0</v>
       </c>
       <c r="K14" s="8">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L14" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M14" s="8">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="N14" s="8">
-        <v>557</v>
+        <v>532</v>
       </c>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
@@ -5575,17 +5575,17 @@
         <v>0</v>
       </c>
       <c r="K16" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L16" s="8">
         <v>0</v>
       </c>
       <c r="M16" s="8">
         <f t="shared" si="0"/>
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N16" s="8">
-        <v>377</v>
+        <v>333</v>
       </c>
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
@@ -5620,7 +5620,7 @@
         <v>12</v>
       </c>
       <c r="I17" s="8">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="J17" s="8">
         <v>0</v>
@@ -5633,10 +5633,10 @@
       </c>
       <c r="M17" s="8">
         <f t="shared" si="0"/>
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="N17" s="8">
-        <v>285</v>
+        <v>251</v>
       </c>
       <c r="O17" s="8"/>
       <c r="P17" s="8"/>
@@ -5687,7 +5687,7 @@
         <v>21</v>
       </c>
       <c r="N18" s="8">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="O18" s="8"/>
       <c r="P18" s="8"/>
@@ -5738,7 +5738,7 @@
         <v>14</v>
       </c>
       <c r="N19" s="8">
-        <v>270</v>
+        <v>56</v>
       </c>
       <c r="O19" s="8"/>
       <c r="P19" s="8"/>
@@ -5773,7 +5773,7 @@
         <v>14</v>
       </c>
       <c r="I20" s="8">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J20" s="8">
         <v>0</v>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="M20" s="8">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N20" s="8">
         <v>0</v>
@@ -5824,7 +5824,7 @@
         <v>13</v>
       </c>
       <c r="I21" s="8">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J21" s="8">
         <v>0</v>
@@ -5837,7 +5837,7 @@
       </c>
       <c r="M21" s="8">
         <f t="shared" si="0"/>
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="N21" s="8">
         <v>0</v>
@@ -5926,7 +5926,7 @@
         <v>12</v>
       </c>
       <c r="I23" s="8">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J23" s="8">
         <v>0</v>
@@ -5939,10 +5939,10 @@
       </c>
       <c r="M23" s="8">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="N23" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" s="8"/>
       <c r="P23" s="8"/>
@@ -5993,7 +5993,7 @@
         <v>11</v>
       </c>
       <c r="N24" s="8">
-        <v>256</v>
+        <v>595</v>
       </c>
       <c r="O24" s="8"/>
       <c r="P24" s="8"/>
@@ -6079,23 +6079,23 @@
         <v>12</v>
       </c>
       <c r="I26" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J26" s="8">
         <v>0</v>
       </c>
       <c r="K26" s="8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L26" s="8">
         <v>0</v>
       </c>
       <c r="M26" s="8">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N26" s="8">
-        <v>200</v>
+        <v>26</v>
       </c>
       <c r="O26" s="8"/>
       <c r="P26" s="8"/>
@@ -6130,7 +6130,7 @@
         <v>12</v>
       </c>
       <c r="I27" s="8">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J27" s="8">
         <v>0</v>
@@ -6143,10 +6143,10 @@
       </c>
       <c r="M27" s="8">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N27" s="8">
-        <v>713</v>
+        <v>667</v>
       </c>
       <c r="O27" s="8"/>
       <c r="P27" s="8"/>
@@ -6181,7 +6181,7 @@
         <v>12</v>
       </c>
       <c r="I28" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J28" s="8">
         <v>0</v>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="M28" s="8">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N28" s="8">
         <v>0</v>
@@ -6232,7 +6232,7 @@
         <v>13</v>
       </c>
       <c r="I29" s="8">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J29" s="8">
         <v>0</v>
@@ -6245,7 +6245,7 @@
       </c>
       <c r="M29" s="8">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="N29" s="8">
         <v>0</v>
@@ -6283,7 +6283,7 @@
         <v>14</v>
       </c>
       <c r="I30" s="8">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J30" s="8">
         <v>0</v>
@@ -6292,14 +6292,14 @@
         <v>3</v>
       </c>
       <c r="L30" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M30" s="8">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N30" s="8">
-        <v>1213</v>
+        <v>1184</v>
       </c>
       <c r="O30" s="8"/>
       <c r="P30" s="8"/>
@@ -6385,7 +6385,7 @@
         <v>12</v>
       </c>
       <c r="I32" s="8">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J32" s="8">
         <v>0</v>
@@ -6398,10 +6398,10 @@
       </c>
       <c r="M32" s="8">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N32" s="8">
-        <v>517</v>
+        <v>499</v>
       </c>
       <c r="O32" s="8"/>
       <c r="P32" s="8"/>
@@ -6436,23 +6436,23 @@
         <v>12</v>
       </c>
       <c r="I33" s="8">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J33" s="8">
         <v>0</v>
       </c>
       <c r="K33" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M33" s="8">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="N33" s="8">
-        <v>733</v>
+        <v>631</v>
       </c>
       <c r="O33" s="8"/>
       <c r="P33" s="8"/>
@@ -6503,7 +6503,7 @@
         <v>15</v>
       </c>
       <c r="N34" s="8">
-        <v>820</v>
+        <v>0</v>
       </c>
       <c r="O34" s="8"/>
       <c r="P34" s="8"/>
@@ -6538,7 +6538,7 @@
         <v>12</v>
       </c>
       <c r="I35" s="8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J35" s="8">
         <v>0</v>
@@ -6551,10 +6551,10 @@
       </c>
       <c r="M35" s="8">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N35" s="8">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="O35" s="8"/>
       <c r="P35" s="8"/>
@@ -6589,7 +6589,7 @@
         <v>13</v>
       </c>
       <c r="I36" s="8">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J36" s="8">
         <v>0</v>
@@ -6602,10 +6602,10 @@
       </c>
       <c r="M36" s="8">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="N36" s="8">
-        <v>574</v>
+        <v>563</v>
       </c>
       <c r="O36" s="8"/>
       <c r="P36" s="8"/>
@@ -6640,7 +6640,7 @@
         <v>13</v>
       </c>
       <c r="I37" s="8">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J37" s="8">
         <v>0</v>
@@ -6653,10 +6653,10 @@
       </c>
       <c r="M37" s="8">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N37" s="8">
-        <v>875</v>
+        <v>769</v>
       </c>
       <c r="O37" s="8"/>
       <c r="P37" s="8"/>
@@ -6691,7 +6691,7 @@
         <v>12</v>
       </c>
       <c r="I38" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J38" s="8">
         <v>0</v>
@@ -6704,7 +6704,7 @@
       </c>
       <c r="M38" s="8">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N38" s="8">
         <v>0</v>
@@ -6742,23 +6742,23 @@
         <v>12</v>
       </c>
       <c r="I39" s="8">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J39" s="8">
         <v>0</v>
       </c>
       <c r="K39" s="8">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L39" s="8">
         <v>0</v>
       </c>
       <c r="M39" s="8">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="N39" s="8">
-        <v>2669</v>
+        <v>2597</v>
       </c>
       <c r="O39" s="8"/>
       <c r="P39" s="8"/>
@@ -6793,7 +6793,7 @@
         <v>12</v>
       </c>
       <c r="I40" s="8">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J40" s="8">
         <v>0</v>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="M40" s="8">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="N40" s="8">
         <v>0</v>
@@ -6860,7 +6860,7 @@
         <v>19</v>
       </c>
       <c r="N41" s="8">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="O41" s="8"/>
       <c r="P41" s="8"/>
@@ -6895,13 +6895,13 @@
         <v>13</v>
       </c>
       <c r="I42" s="8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J42" s="8">
         <v>0</v>
       </c>
       <c r="K42" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L42" s="8">
         <v>0</v>
@@ -6911,7 +6911,7 @@
         <v>12</v>
       </c>
       <c r="N42" s="8">
-        <v>979</v>
+        <v>861</v>
       </c>
       <c r="O42" s="8"/>
       <c r="P42" s="8"/>
@@ -6946,7 +6946,7 @@
         <v>12</v>
       </c>
       <c r="I43" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J43" s="8">
         <v>0</v>
@@ -6959,7 +6959,7 @@
       </c>
       <c r="M43" s="8">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N43" s="8">
         <v>0</v>
@@ -6997,7 +6997,7 @@
         <v>12</v>
       </c>
       <c r="I44" s="8">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J44" s="8">
         <v>0</v>
@@ -7010,10 +7010,10 @@
       </c>
       <c r="M44" s="8">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="N44" s="8">
-        <v>165</v>
+        <v>434</v>
       </c>
       <c r="O44" s="8"/>
       <c r="P44" s="8"/>
@@ -7048,7 +7048,7 @@
         <v>12</v>
       </c>
       <c r="I45" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J45" s="8">
         <v>0</v>
@@ -7061,10 +7061,10 @@
       </c>
       <c r="M45" s="8">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N45" s="8">
-        <v>549</v>
+        <v>809</v>
       </c>
       <c r="O45" s="8"/>
       <c r="P45" s="8"/>
@@ -7099,7 +7099,7 @@
         <v>12</v>
       </c>
       <c r="I46" s="8">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J46" s="8">
         <v>0</v>
@@ -7112,7 +7112,7 @@
       </c>
       <c r="M46" s="8">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N46" s="8">
         <v>0</v>
@@ -7150,7 +7150,7 @@
         <v>13</v>
       </c>
       <c r="I47" s="8">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J47" s="8">
         <v>0</v>
@@ -7163,10 +7163,10 @@
       </c>
       <c r="M47" s="8">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N47" s="8">
-        <v>594</v>
+        <v>516</v>
       </c>
       <c r="O47" s="8"/>
       <c r="P47" s="8"/>
@@ -7201,23 +7201,23 @@
         <v>12</v>
       </c>
       <c r="I48" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J48" s="8">
         <v>0</v>
       </c>
       <c r="K48" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L48" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M48" s="8">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N48" s="8">
-        <v>1114</v>
+        <v>962</v>
       </c>
       <c r="O48" s="8"/>
       <c r="P48" s="8"/>
@@ -7252,7 +7252,7 @@
         <v>12</v>
       </c>
       <c r="I49" s="8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J49" s="8">
         <v>0</v>
@@ -7261,14 +7261,14 @@
         <v>0</v>
       </c>
       <c r="L49" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" s="8">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N49" s="8">
-        <v>603</v>
+        <v>568</v>
       </c>
       <c r="O49" s="8"/>
       <c r="P49" s="8"/>
@@ -7354,7 +7354,7 @@
         <v>12</v>
       </c>
       <c r="I51" s="8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J51" s="8">
         <v>0</v>
@@ -7367,10 +7367,10 @@
       </c>
       <c r="M51" s="8">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N51" s="8">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="O51" s="8"/>
       <c r="P51" s="8"/>
@@ -7405,7 +7405,7 @@
         <v>12</v>
       </c>
       <c r="I52" s="8">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="J52" s="8">
         <v>0</v>
@@ -7418,7 +7418,7 @@
       </c>
       <c r="M52" s="8">
         <f t="shared" si="0"/>
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="N52" s="8">
         <v>0</v>
@@ -7456,7 +7456,7 @@
         <v>12</v>
       </c>
       <c r="I53" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J53" s="8">
         <v>0</v>
@@ -7469,10 +7469,10 @@
       </c>
       <c r="M53" s="8">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N53" s="8">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O53" s="8"/>
       <c r="P53" s="8"/>
@@ -7507,7 +7507,7 @@
         <v>12</v>
       </c>
       <c r="I54" s="8">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J54" s="8">
         <v>0</v>
@@ -7520,10 +7520,10 @@
       </c>
       <c r="M54" s="8">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N54" s="8">
-        <v>292</v>
+        <v>235</v>
       </c>
       <c r="O54" s="8"/>
       <c r="P54" s="8"/>
@@ -7558,7 +7558,7 @@
         <v>12</v>
       </c>
       <c r="I55" s="8">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J55" s="8">
         <v>0</v>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="M55" s="8">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N55" s="8">
         <v>0</v>
@@ -7615,17 +7615,17 @@
         <v>0</v>
       </c>
       <c r="K56" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="8">
         <v>1</v>
       </c>
       <c r="M56" s="8">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N56" s="8">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="O56" s="8"/>
       <c r="P56" s="8"/>
@@ -7660,23 +7660,23 @@
         <v>12</v>
       </c>
       <c r="I57" s="8">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J57" s="8">
         <v>0</v>
       </c>
       <c r="K57" s="8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L57" s="8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M57" s="8">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="N57" s="8">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="O57" s="8"/>
       <c r="P57" s="8"/>
@@ -7711,23 +7711,23 @@
         <v>12</v>
       </c>
       <c r="I58" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J58" s="8">
         <v>0</v>
       </c>
       <c r="K58" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L58" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M58" s="8">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N58" s="8">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="O58" s="8"/>
       <c r="P58" s="8"/>
@@ -7762,7 +7762,7 @@
         <v>13</v>
       </c>
       <c r="I59" s="8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J59" s="8">
         <v>0</v>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="M59" s="8">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N59" s="8">
         <v>0</v>
@@ -7813,23 +7813,23 @@
         <v>12</v>
       </c>
       <c r="I60" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J60" s="8">
         <v>0</v>
       </c>
       <c r="K60" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60" s="8">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N60" s="8">
-        <v>354</v>
+        <v>322</v>
       </c>
       <c r="O60" s="8"/>
       <c r="P60" s="8"/>
@@ -7864,7 +7864,7 @@
         <v>12</v>
       </c>
       <c r="I61" s="8">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J61" s="8">
         <v>0</v>
@@ -7877,10 +7877,10 @@
       </c>
       <c r="M61" s="8">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N61" s="8">
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="O61" s="8"/>
       <c r="P61" s="8"/>
@@ -7915,7 +7915,7 @@
         <v>12</v>
       </c>
       <c r="I62" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J62" s="8">
         <v>0</v>
@@ -7928,10 +7928,10 @@
       </c>
       <c r="M62" s="8">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N62" s="8">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="O62" s="8"/>
       <c r="P62" s="8"/>
@@ -7966,7 +7966,7 @@
         <v>12</v>
       </c>
       <c r="I63" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J63" s="8">
         <v>0</v>
@@ -7975,14 +7975,14 @@
         <v>0</v>
       </c>
       <c r="L63" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M63" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N63" s="8">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="O63" s="8"/>
       <c r="P63" s="8"/>
@@ -8023,17 +8023,17 @@
         <v>0</v>
       </c>
       <c r="K64" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L64" s="8">
         <v>0</v>
       </c>
       <c r="M64" s="8">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N64" s="8">
-        <v>411</v>
+        <v>643</v>
       </c>
       <c r="O64" s="8"/>
       <c r="P64" s="8"/>
@@ -8077,14 +8077,14 @@
         <v>0</v>
       </c>
       <c r="L65" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" s="8">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N65" s="8">
-        <v>820</v>
+        <v>803</v>
       </c>
       <c r="O65" s="8"/>
       <c r="P65" s="8"/>
@@ -8186,7 +8186,7 @@
         <v>3</v>
       </c>
       <c r="N67" s="8">
-        <v>604</v>
+        <v>0</v>
       </c>
       <c r="O67" s="8"/>
       <c r="P67" s="8"/>
@@ -8221,23 +8221,23 @@
         <v>12</v>
       </c>
       <c r="I68" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J68" s="8">
         <v>0</v>
       </c>
       <c r="K68" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L68" s="8">
         <v>0</v>
       </c>
       <c r="M68" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N68" s="8">
-        <v>862</v>
+        <v>852</v>
       </c>
       <c r="O68" s="8"/>
       <c r="P68" s="8"/>
@@ -8288,7 +8288,7 @@
         <v>10</v>
       </c>
       <c r="N69" s="8">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="O69" s="8"/>
       <c r="P69" s="8"/>
@@ -8332,14 +8332,14 @@
         <v>0</v>
       </c>
       <c r="L70" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N70" s="8">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="O70" s="8"/>
       <c r="P70" s="8"/>
@@ -8425,7 +8425,7 @@
         <v>12</v>
       </c>
       <c r="I72" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J72" s="8">
         <v>0</v>
@@ -8434,14 +8434,14 @@
         <v>0</v>
       </c>
       <c r="L72" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M72" s="8">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N72" s="8">
-        <v>470</v>
+        <v>927</v>
       </c>
       <c r="O72" s="8"/>
       <c r="P72" s="8"/>
@@ -8476,23 +8476,23 @@
         <v>12</v>
       </c>
       <c r="I73" s="8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J73" s="8">
         <v>0</v>
       </c>
       <c r="K73" s="8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L73" s="8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M73" s="8">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="N73" s="8">
-        <v>169</v>
+        <v>129</v>
       </c>
       <c r="O73" s="8"/>
       <c r="P73" s="8"/>
@@ -8527,7 +8527,7 @@
         <v>14</v>
       </c>
       <c r="I74" s="8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J74" s="8">
         <v>0</v>
@@ -8540,10 +8540,10 @@
       </c>
       <c r="M74" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N74" s="8">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="O74" s="8"/>
       <c r="P74" s="8"/>
@@ -8578,7 +8578,7 @@
         <v>13</v>
       </c>
       <c r="I75" s="8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J75" s="8">
         <v>0</v>
@@ -8591,10 +8591,10 @@
       </c>
       <c r="M75" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N75" s="8">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="O75" s="8"/>
       <c r="P75" s="8"/>
@@ -8629,23 +8629,23 @@
         <v>13</v>
       </c>
       <c r="I76" s="8">
+        <v>2</v>
+      </c>
+      <c r="J76" s="8">
+        <v>0</v>
+      </c>
+      <c r="K76" s="8">
+        <v>0</v>
+      </c>
+      <c r="L76" s="8">
         <v>1</v>
-      </c>
-      <c r="J76" s="8">
-        <v>0</v>
-      </c>
-      <c r="K76" s="8">
-        <v>0</v>
-      </c>
-      <c r="L76" s="8">
-        <v>0</v>
       </c>
       <c r="M76" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N76" s="8">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="O76" s="8"/>
       <c r="P76" s="8"/>
@@ -8696,7 +8696,7 @@
         <v>5</v>
       </c>
       <c r="N77" s="8">
-        <v>387</v>
+        <v>305</v>
       </c>
       <c r="O77" s="8"/>
       <c r="P77" s="8"/>
@@ -8731,23 +8731,23 @@
         <v>12</v>
       </c>
       <c r="I78" s="8">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J78" s="8">
         <v>0</v>
       </c>
       <c r="K78" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L78" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M78" s="8">
         <f t="shared" si="1"/>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N78" s="8">
-        <v>221</v>
+        <v>162</v>
       </c>
       <c r="O78" s="8"/>
       <c r="P78" s="8"/>
@@ -8782,7 +8782,7 @@
         <v>13</v>
       </c>
       <c r="I79" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J79" s="8">
         <v>0</v>
@@ -8795,7 +8795,7 @@
       </c>
       <c r="M79" s="8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N79" s="8">
         <v>0</v>
@@ -8833,7 +8833,7 @@
         <v>13</v>
       </c>
       <c r="I80" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J80" s="8">
         <v>0</v>
@@ -8846,10 +8846,10 @@
       </c>
       <c r="M80" s="8">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N80" s="8">
-        <v>239</v>
+        <v>185</v>
       </c>
       <c r="O80" s="8"/>
       <c r="P80" s="8"/>
@@ -8935,7 +8935,7 @@
         <v>15</v>
       </c>
       <c r="I82" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J82" s="8">
         <v>0</v>
@@ -8948,10 +8948,10 @@
       </c>
       <c r="M82" s="8">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N82" s="8">
-        <v>172</v>
+        <v>145</v>
       </c>
       <c r="O82" s="8"/>
       <c r="P82" s="8"/>
@@ -8986,7 +8986,7 @@
         <v>15</v>
       </c>
       <c r="I83" s="8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J83" s="8">
         <v>0</v>
@@ -8999,10 +8999,10 @@
       </c>
       <c r="M83" s="8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N83" s="8">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="O83" s="8"/>
       <c r="P83" s="8"/>
@@ -9088,7 +9088,7 @@
         <v>14</v>
       </c>
       <c r="I85" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J85" s="8">
         <v>0</v>
@@ -9097,14 +9097,14 @@
         <v>0</v>
       </c>
       <c r="L85" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M85" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N85" s="8">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="O85" s="8"/>
       <c r="P85" s="8"/>
@@ -9139,7 +9139,7 @@
         <v>12</v>
       </c>
       <c r="I86" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J86" s="8">
         <v>0</v>
@@ -9152,7 +9152,7 @@
       </c>
       <c r="M86" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N86" s="8">
         <v>0</v>
@@ -9257,7 +9257,7 @@
         <v>11</v>
       </c>
       <c r="N88" s="8">
-        <v>155</v>
+        <v>103</v>
       </c>
       <c r="O88" s="8"/>
       <c r="P88" s="8"/>
@@ -9292,7 +9292,7 @@
         <v>12</v>
       </c>
       <c r="I89" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J89" s="8">
         <v>0</v>
@@ -9305,10 +9305,10 @@
       </c>
       <c r="M89" s="8">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N89" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O89" s="8"/>
       <c r="P89" s="8"/>
@@ -9343,7 +9343,7 @@
         <v>12</v>
       </c>
       <c r="I90" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J90" s="8">
         <v>0</v>
@@ -9356,10 +9356,10 @@
       </c>
       <c r="M90" s="8">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N90" s="8">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="O90" s="8"/>
       <c r="P90" s="8"/>
@@ -9394,13 +9394,13 @@
         <v>12</v>
       </c>
       <c r="I91" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J91" s="8">
         <v>0</v>
       </c>
       <c r="K91" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L91" s="8">
         <v>0</v>
@@ -9410,7 +9410,7 @@
         <v>4</v>
       </c>
       <c r="N91" s="8">
-        <v>864</v>
+        <v>839</v>
       </c>
       <c r="O91" s="8"/>
       <c r="P91" s="8"/>
@@ -9445,20 +9445,20 @@
         <v>12</v>
       </c>
       <c r="I92" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J92" s="8">
         <v>0</v>
       </c>
       <c r="K92" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L92" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M92" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N92" s="8">
         <v>0</v>
@@ -9614,7 +9614,7 @@
         <v>6</v>
       </c>
       <c r="N95" s="8">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="O95" s="8"/>
       <c r="P95" s="8"/>
@@ -9665,7 +9665,7 @@
         <v>6</v>
       </c>
       <c r="N96" s="8">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="O96" s="8"/>
       <c r="P96" s="8"/>
@@ -9706,17 +9706,17 @@
         <v>0</v>
       </c>
       <c r="K97" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L97" s="8">
         <v>0</v>
       </c>
       <c r="M97" s="8">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N97" s="8">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="O97" s="8"/>
       <c r="P97" s="8"/>
@@ -9751,7 +9751,7 @@
         <v>12</v>
       </c>
       <c r="I98" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J98" s="8">
         <v>0</v>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="M98" s="8">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N98" s="8">
         <v>0</v>
@@ -9904,20 +9904,20 @@
         <v>15</v>
       </c>
       <c r="I101" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J101" s="8">
         <v>0</v>
       </c>
       <c r="K101" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M101" s="8">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N101" s="8">
         <v>253</v>
@@ -9955,23 +9955,23 @@
         <v>14</v>
       </c>
       <c r="I102" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J102" s="8">
         <v>0</v>
       </c>
       <c r="K102" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L102" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M102" s="8">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="N102" s="8">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="O102" s="8"/>
       <c r="P102" s="8"/>
@@ -10006,7 +10006,7 @@
         <v>15</v>
       </c>
       <c r="I103" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J103" s="8">
         <v>0</v>
@@ -10019,10 +10019,10 @@
       </c>
       <c r="M103" s="8">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N103" s="8">
-        <v>284</v>
+        <v>0</v>
       </c>
       <c r="O103" s="8"/>
       <c r="P103" s="8"/>
@@ -10124,7 +10124,7 @@
         <v>5</v>
       </c>
       <c r="N105" s="8">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="O105" s="8"/>
       <c r="P105" s="8"/>
@@ -10159,7 +10159,7 @@
         <v>15</v>
       </c>
       <c r="I106" s="8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J106" s="8">
         <v>0</v>
@@ -10172,7 +10172,7 @@
       </c>
       <c r="M106" s="8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N106" s="8">
         <v>0</v>
@@ -10261,7 +10261,7 @@
         <v>15</v>
       </c>
       <c r="I108" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J108" s="8">
         <v>0</v>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="M108" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N108" s="8">
         <v>0</v>
@@ -10465,7 +10465,7 @@
         <v>12</v>
       </c>
       <c r="I112" s="8">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="J112" s="8">
         <v>0</v>
@@ -10474,14 +10474,14 @@
         <v>0</v>
       </c>
       <c r="L112" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M112" s="8">
         <f t="shared" si="1"/>
-        <v>224</v>
+        <v>201</v>
       </c>
       <c r="N112" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O112" s="8"/>
       <c r="P112" s="8"/>
@@ -10532,7 +10532,7 @@
         <v>12</v>
       </c>
       <c r="N113" s="8">
-        <v>653</v>
+        <v>616</v>
       </c>
       <c r="O113" s="8"/>
       <c r="P113" s="8"/>
@@ -10583,7 +10583,7 @@
         <v>6</v>
       </c>
       <c r="N114" s="8">
-        <v>357</v>
+        <v>221</v>
       </c>
       <c r="O114" s="8"/>
       <c r="P114" s="8"/>
@@ -10634,7 +10634,7 @@
         <v>9</v>
       </c>
       <c r="N115" s="8">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="O115" s="8"/>
       <c r="P115" s="8"/>
@@ -10685,7 +10685,7 @@
         <v>5</v>
       </c>
       <c r="N116" s="8">
-        <v>534</v>
+        <v>510</v>
       </c>
       <c r="O116" s="8"/>
       <c r="P116" s="8"/>
@@ -10720,7 +10720,7 @@
         <v>12</v>
       </c>
       <c r="I117" s="8">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J117" s="8">
         <v>0</v>
@@ -10729,14 +10729,14 @@
         <v>8</v>
       </c>
       <c r="L117" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M117" s="8">
         <f t="shared" si="1"/>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N117" s="8">
-        <v>10</v>
+        <v>192</v>
       </c>
       <c r="O117" s="8"/>
       <c r="P117" s="8"/>
@@ -10787,7 +10787,7 @@
         <v>6</v>
       </c>
       <c r="N118" s="8">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="O118" s="8"/>
       <c r="P118" s="8"/>
@@ -10838,7 +10838,7 @@
         <v>8</v>
       </c>
       <c r="N119" s="8">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="O119" s="8"/>
       <c r="P119" s="8"/>
@@ -10873,7 +10873,7 @@
         <v>14</v>
       </c>
       <c r="I120" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J120" s="8">
         <v>0</v>
@@ -10886,10 +10886,10 @@
       </c>
       <c r="M120" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N120" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O120" s="8"/>
       <c r="P120" s="8"/>
@@ -10924,7 +10924,7 @@
         <v>15</v>
       </c>
       <c r="I121" s="8">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J121" s="8">
         <v>0</v>
@@ -10937,10 +10937,10 @@
       </c>
       <c r="M121" s="8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N121" s="8">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O121" s="8"/>
       <c r="P121" s="8"/>
@@ -10975,7 +10975,7 @@
         <v>13</v>
       </c>
       <c r="I122" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J122" s="8">
         <v>0</v>
@@ -10988,10 +10988,10 @@
       </c>
       <c r="M122" s="8">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N122" s="8">
-        <v>889</v>
+        <v>871</v>
       </c>
       <c r="O122" s="8"/>
       <c r="P122" s="8"/>
@@ -11042,7 +11042,7 @@
         <v>3</v>
       </c>
       <c r="N123" s="8">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="O123" s="8"/>
       <c r="P123" s="8"/>
@@ -11128,7 +11128,7 @@
         <v>13</v>
       </c>
       <c r="I125" s="8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J125" s="8">
         <v>0</v>
@@ -11141,10 +11141,10 @@
       </c>
       <c r="M125" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N125" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O125" s="8"/>
       <c r="P125" s="8"/>
@@ -11297,7 +11297,7 @@
         <v>3</v>
       </c>
       <c r="N128" s="8">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="O128" s="8"/>
       <c r="P128" s="8"/>
@@ -11383,7 +11383,7 @@
         <v>12</v>
       </c>
       <c r="I130" s="8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J130" s="8">
         <v>0</v>
@@ -11392,11 +11392,11 @@
         <v>1</v>
       </c>
       <c r="L130" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M130" s="8">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N130" s="8">
         <v>94</v>
@@ -11443,14 +11443,14 @@
         <v>0</v>
       </c>
       <c r="L131" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M131" s="8">
         <f t="shared" ref="M131:M194" si="2">I131+J131+K131+L131</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N131" s="8">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="O131" s="8"/>
       <c r="P131" s="8"/>
@@ -11501,7 +11501,7 @@
         <v>6</v>
       </c>
       <c r="N132" s="8">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="O132" s="8"/>
       <c r="P132" s="8"/>
@@ -11536,23 +11536,23 @@
         <v>12</v>
       </c>
       <c r="I133" s="8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J133" s="8">
         <v>0</v>
       </c>
       <c r="K133" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L133" s="8">
         <v>0</v>
       </c>
       <c r="M133" s="8">
         <f t="shared" si="2"/>
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N133" s="8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O133" s="8"/>
       <c r="P133" s="8"/>
@@ -11603,7 +11603,7 @@
         <v>4</v>
       </c>
       <c r="N134" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O134" s="8"/>
       <c r="P134" s="8"/>
@@ -11638,23 +11638,23 @@
         <v>15</v>
       </c>
       <c r="I135" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J135" s="8">
         <v>0</v>
       </c>
       <c r="K135" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L135" s="8">
         <v>0</v>
       </c>
       <c r="M135" s="8">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N135" s="8">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="O135" s="8"/>
       <c r="P135" s="8"/>
@@ -11695,17 +11695,17 @@
         <v>0</v>
       </c>
       <c r="K136" s="8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L136" s="8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M136" s="8">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N136" s="8">
-        <v>292</v>
+        <v>251</v>
       </c>
       <c r="O136" s="8"/>
       <c r="P136" s="8"/>
@@ -11740,7 +11740,7 @@
         <v>15</v>
       </c>
       <c r="I137" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J137" s="8">
         <v>0</v>
@@ -11753,10 +11753,10 @@
       </c>
       <c r="M137" s="8">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N137" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O137" s="8"/>
       <c r="P137" s="8"/>
@@ -11791,13 +11791,13 @@
         <v>12</v>
       </c>
       <c r="I138" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J138" s="8">
         <v>0</v>
       </c>
       <c r="K138" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L138" s="8">
         <v>0</v>
@@ -11807,7 +11807,7 @@
         <v>4</v>
       </c>
       <c r="N138" s="8">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="O138" s="8"/>
       <c r="P138" s="8"/>
@@ -11848,17 +11848,17 @@
         <v>0</v>
       </c>
       <c r="K139" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L139" s="8">
         <v>1</v>
       </c>
       <c r="M139" s="8">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N139" s="8">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O139" s="8"/>
       <c r="P139" s="8"/>
@@ -11893,7 +11893,7 @@
         <v>15</v>
       </c>
       <c r="I140" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J140" s="8">
         <v>0</v>
@@ -11906,10 +11906,10 @@
       </c>
       <c r="M140" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N140" s="8">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="O140" s="8"/>
       <c r="P140" s="8"/>
@@ -12164,7 +12164,7 @@
         <v>4</v>
       </c>
       <c r="N145" s="8">
-        <v>778</v>
+        <v>752</v>
       </c>
       <c r="O145" s="8"/>
       <c r="P145" s="8"/>
@@ -12259,14 +12259,14 @@
         <v>0</v>
       </c>
       <c r="L147" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M147" s="8">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N147" s="8">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="O147" s="8"/>
       <c r="P147" s="8"/>
@@ -12301,7 +12301,7 @@
         <v>15</v>
       </c>
       <c r="I148" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J148" s="8">
         <v>0</v>
@@ -12314,10 +12314,10 @@
       </c>
       <c r="M148" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N148" s="8">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="O148" s="8"/>
       <c r="P148" s="8"/>
@@ -12358,17 +12358,17 @@
         <v>0</v>
       </c>
       <c r="K149" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L149" s="8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M149" s="8">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N149" s="8">
-        <v>139</v>
+        <v>108</v>
       </c>
       <c r="O149" s="8"/>
       <c r="P149" s="8"/>
@@ -12403,7 +12403,7 @@
         <v>12</v>
       </c>
       <c r="I150" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J150" s="8">
         <v>0</v>
@@ -12416,10 +12416,10 @@
       </c>
       <c r="M150" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N150" s="8">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="O150" s="8"/>
       <c r="P150" s="8"/>
@@ -12454,7 +12454,7 @@
         <v>13</v>
       </c>
       <c r="I151" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J151" s="8">
         <v>0</v>
@@ -12467,7 +12467,7 @@
       </c>
       <c r="M151" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N151" s="8">
         <v>198</v>
@@ -12505,7 +12505,7 @@
         <v>15</v>
       </c>
       <c r="I152" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J152" s="8">
         <v>0</v>
@@ -12518,10 +12518,10 @@
       </c>
       <c r="M152" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N152" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O152" s="8"/>
       <c r="P152" s="8"/>
@@ -12607,7 +12607,7 @@
         <v>15</v>
       </c>
       <c r="I154" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J154" s="8">
         <v>0</v>
@@ -12620,10 +12620,10 @@
       </c>
       <c r="M154" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N154" s="8">
-        <v>454</v>
+        <v>0</v>
       </c>
       <c r="O154" s="8"/>
       <c r="P154" s="8"/>
@@ -12709,7 +12709,7 @@
         <v>15</v>
       </c>
       <c r="I156" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J156" s="8">
         <v>0</v>
@@ -12722,7 +12722,7 @@
       </c>
       <c r="M156" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N156" s="8">
         <v>0</v>
@@ -12862,7 +12862,7 @@
         <v>15</v>
       </c>
       <c r="I159" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J159" s="8">
         <v>0</v>
@@ -12875,7 +12875,7 @@
       </c>
       <c r="M159" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N159" s="8">
         <v>0</v>
@@ -12913,7 +12913,7 @@
         <v>15</v>
       </c>
       <c r="I160" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J160" s="8">
         <v>0</v>
@@ -12926,10 +12926,10 @@
       </c>
       <c r="M160" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N160" s="8">
-        <v>445</v>
+        <v>0</v>
       </c>
       <c r="O160" s="8"/>
       <c r="P160" s="8"/>
@@ -12980,7 +12980,7 @@
         <v>5</v>
       </c>
       <c r="N161" s="8">
-        <v>386</v>
+        <v>353</v>
       </c>
       <c r="O161" s="8"/>
       <c r="P161" s="8"/>
@@ -13024,14 +13024,14 @@
         <v>0</v>
       </c>
       <c r="L162" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M162" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N162" s="8">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="O162" s="8"/>
       <c r="P162" s="8"/>
@@ -13066,7 +13066,7 @@
         <v>16</v>
       </c>
       <c r="I163" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J163" s="8">
         <v>0</v>
@@ -13079,7 +13079,7 @@
       </c>
       <c r="M163" s="8">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N163" s="8">
         <v>0</v>
@@ -13117,7 +13117,7 @@
         <v>16</v>
       </c>
       <c r="I164" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J164" s="8">
         <v>0</v>
@@ -13130,10 +13130,10 @@
       </c>
       <c r="M164" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N164" s="8">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="O164" s="8"/>
       <c r="P164" s="8"/>
@@ -13184,7 +13184,7 @@
         <v>9</v>
       </c>
       <c r="N165" s="8">
-        <v>1070</v>
+        <v>1045</v>
       </c>
       <c r="O165" s="8"/>
       <c r="P165" s="8"/>
@@ -13219,7 +13219,7 @@
         <v>14</v>
       </c>
       <c r="I166" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J166" s="8">
         <v>0</v>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="M166" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N166" s="8">
         <v>0</v>
@@ -13321,23 +13321,23 @@
         <v>14</v>
       </c>
       <c r="I168" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J168" s="8">
         <v>0</v>
       </c>
       <c r="K168" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L168" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M168" s="8">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N168" s="8">
-        <v>124</v>
+        <v>93</v>
       </c>
       <c r="O168" s="8"/>
       <c r="P168" s="8"/>
@@ -13372,7 +13372,7 @@
         <v>16</v>
       </c>
       <c r="I169" s="8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J169" s="8">
         <v>0</v>
@@ -13385,7 +13385,7 @@
       </c>
       <c r="M169" s="8">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N169" s="8">
         <v>0</v>
@@ -13423,7 +13423,7 @@
         <v>14</v>
       </c>
       <c r="I170" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J170" s="8">
         <v>0</v>
@@ -13436,10 +13436,10 @@
       </c>
       <c r="M170" s="8">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N170" s="8">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="O170" s="8"/>
       <c r="P170" s="8"/>
@@ -13525,7 +13525,7 @@
         <v>14</v>
       </c>
       <c r="I172" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J172" s="8">
         <v>0</v>
@@ -13538,7 +13538,7 @@
       </c>
       <c r="M172" s="8">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N172" s="8">
         <v>52</v>
@@ -13582,17 +13582,17 @@
         <v>0</v>
       </c>
       <c r="K173" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L173" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M173" s="8">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="N173" s="8">
-        <v>529</v>
+        <v>498</v>
       </c>
       <c r="O173" s="8"/>
       <c r="P173" s="8"/>
@@ -13678,7 +13678,7 @@
         <v>14</v>
       </c>
       <c r="I175" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J175" s="8">
         <v>0</v>
@@ -13691,7 +13691,7 @@
       </c>
       <c r="M175" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N175" s="8">
         <v>0</v>
@@ -13898,7 +13898,7 @@
         <v>2</v>
       </c>
       <c r="N179" s="8">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O179" s="8"/>
       <c r="P179" s="8"/>
@@ -13939,17 +13939,17 @@
         <v>0</v>
       </c>
       <c r="K180" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L180" s="8">
         <v>0</v>
       </c>
       <c r="M180" s="8">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N180" s="8">
-        <v>379</v>
+        <v>329</v>
       </c>
       <c r="O180" s="8"/>
       <c r="P180" s="8"/>
@@ -14000,7 +14000,7 @@
         <v>3</v>
       </c>
       <c r="N181" s="8">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O181" s="8"/>
       <c r="P181" s="8"/>
@@ -14095,14 +14095,14 @@
         <v>0</v>
       </c>
       <c r="L183" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M183" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N183" s="8">
-        <v>377</v>
+        <v>356</v>
       </c>
       <c r="O183" s="8"/>
       <c r="P183" s="8"/>
@@ -14188,7 +14188,7 @@
         <v>12</v>
       </c>
       <c r="I185" s="8">
-        <v>379</v>
+        <v>321</v>
       </c>
       <c r="J185" s="8">
         <v>0</v>
@@ -14201,7 +14201,7 @@
       </c>
       <c r="M185" s="8">
         <f t="shared" si="2"/>
-        <v>379</v>
+        <v>321</v>
       </c>
       <c r="N185" s="8">
         <v>1659</v>
@@ -14255,7 +14255,7 @@
         <v>6</v>
       </c>
       <c r="N186" s="8">
-        <v>678</v>
+        <v>660</v>
       </c>
       <c r="O186" s="8"/>
       <c r="P186" s="8"/>
@@ -14290,7 +14290,7 @@
         <v>14</v>
       </c>
       <c r="I187" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J187" s="8">
         <v>0</v>
@@ -14303,10 +14303,10 @@
       </c>
       <c r="M187" s="8">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N187" s="8">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="O187" s="8"/>
       <c r="P187" s="8"/>
@@ -14357,7 +14357,7 @@
         <v>3</v>
       </c>
       <c r="N188" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O188" s="8"/>
       <c r="P188" s="8"/>
@@ -14443,7 +14443,7 @@
         <v>12</v>
       </c>
       <c r="I190" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J190" s="8">
         <v>0</v>
@@ -14456,10 +14456,10 @@
       </c>
       <c r="M190" s="8">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N190" s="8">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="O190" s="8"/>
       <c r="P190" s="8"/>
@@ -14494,7 +14494,7 @@
         <v>12</v>
       </c>
       <c r="I191" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J191" s="8">
         <v>0</v>
@@ -14507,10 +14507,10 @@
       </c>
       <c r="M191" s="8">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N191" s="8">
-        <v>525</v>
+        <v>486</v>
       </c>
       <c r="O191" s="8"/>
       <c r="P191" s="8"/>
@@ -14545,7 +14545,7 @@
         <v>12</v>
       </c>
       <c r="I192" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J192" s="8">
         <v>0</v>
@@ -14558,7 +14558,7 @@
       </c>
       <c r="M192" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N192" s="8">
         <v>0</v>
@@ -14647,20 +14647,20 @@
         <v>15</v>
       </c>
       <c r="I194" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J194" s="8">
         <v>0</v>
       </c>
       <c r="K194" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L194" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M194" s="8">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N194" s="8">
         <v>264</v>
@@ -14800,23 +14800,23 @@
         <v>12</v>
       </c>
       <c r="I197" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J197" s="8">
         <v>0</v>
       </c>
       <c r="K197" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L197" s="8">
         <v>0</v>
       </c>
       <c r="M197" s="8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N197" s="8">
-        <v>323</v>
+        <v>544</v>
       </c>
       <c r="O197" s="8"/>
       <c r="P197" s="8"/>
@@ -14953,7 +14953,7 @@
         <v>14</v>
       </c>
       <c r="I200" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J200" s="8">
         <v>0</v>
@@ -14966,7 +14966,7 @@
       </c>
       <c r="M200" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N200" s="8">
         <v>0</v>
@@ -15055,7 +15055,7 @@
         <v>16</v>
       </c>
       <c r="I202" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J202" s="8">
         <v>0</v>
@@ -15068,10 +15068,10 @@
       </c>
       <c r="M202" s="8">
         <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="N202" s="8">
         <v>3</v>
-      </c>
-      <c r="N202" s="8">
-        <v>0</v>
       </c>
       <c r="O202" s="8"/>
       <c r="P202" s="8"/>
@@ -15106,7 +15106,7 @@
         <v>15</v>
       </c>
       <c r="I203" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J203" s="8">
         <v>0</v>
@@ -15119,10 +15119,10 @@
       </c>
       <c r="M203" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N203" s="8">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O203" s="8"/>
       <c r="P203" s="8"/>
@@ -15310,7 +15310,7 @@
         <v>14</v>
       </c>
       <c r="I207" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J207" s="8">
         <v>0</v>
@@ -15323,10 +15323,10 @@
       </c>
       <c r="M207" s="8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N207" s="8">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="O207" s="8"/>
       <c r="P207" s="8"/>
@@ -15361,7 +15361,7 @@
         <v>14</v>
       </c>
       <c r="I208" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J208" s="8">
         <v>0</v>
@@ -15374,10 +15374,10 @@
       </c>
       <c r="M208" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N208" s="8">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="O208" s="8"/>
       <c r="P208" s="8"/>
@@ -15412,7 +15412,7 @@
         <v>12</v>
       </c>
       <c r="I209" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J209" s="8">
         <v>0</v>
@@ -15425,7 +15425,7 @@
       </c>
       <c r="M209" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N209" s="8">
         <v>0</v>
@@ -15514,7 +15514,7 @@
         <v>12</v>
       </c>
       <c r="I211" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J211" s="8">
         <v>0</v>
@@ -15527,10 +15527,10 @@
       </c>
       <c r="M211" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N211" s="8">
-        <v>703</v>
+        <v>690</v>
       </c>
       <c r="O211" s="8"/>
       <c r="P211" s="8"/>
@@ -15667,23 +15667,23 @@
         <v>14</v>
       </c>
       <c r="I214" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J214" s="8">
         <v>0</v>
       </c>
       <c r="K214" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L214" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M214" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N214" s="8">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="O214" s="8"/>
       <c r="P214" s="8"/>
@@ -15727,14 +15727,14 @@
         <v>0</v>
       </c>
       <c r="L215" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M215" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N215" s="8">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="O215" s="8"/>
       <c r="P215" s="8"/>
@@ -15769,7 +15769,7 @@
         <v>14</v>
       </c>
       <c r="I216" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J216" s="8">
         <v>0</v>
@@ -15782,7 +15782,7 @@
       </c>
       <c r="M216" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N216" s="8">
         <v>0</v>
@@ -15820,7 +15820,7 @@
         <v>13</v>
       </c>
       <c r="I217" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J217" s="8">
         <v>0</v>
@@ -15833,10 +15833,10 @@
       </c>
       <c r="M217" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N217" s="8">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="O217" s="8"/>
       <c r="P217" s="8"/>
@@ -15871,7 +15871,7 @@
         <v>13</v>
       </c>
       <c r="I218" s="8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J218" s="8">
         <v>0</v>
@@ -15884,10 +15884,10 @@
       </c>
       <c r="M218" s="8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N218" s="8">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="O218" s="8"/>
       <c r="P218" s="8"/>
@@ -15922,7 +15922,7 @@
         <v>13</v>
       </c>
       <c r="I219" s="8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J219" s="8">
         <v>0</v>
@@ -15935,10 +15935,10 @@
       </c>
       <c r="M219" s="8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N219" s="8">
-        <v>256</v>
+        <v>0</v>
       </c>
       <c r="O219" s="8"/>
       <c r="P219" s="8"/>
@@ -15973,7 +15973,7 @@
         <v>16</v>
       </c>
       <c r="I220" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J220" s="8">
         <v>0</v>
@@ -15986,7 +15986,7 @@
       </c>
       <c r="M220" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N220" s="8">
         <v>0</v>
@@ -16024,7 +16024,7 @@
         <v>16</v>
       </c>
       <c r="I221" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J221" s="8">
         <v>0</v>
@@ -16037,10 +16037,10 @@
       </c>
       <c r="M221" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N221" s="8">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="O221" s="8"/>
       <c r="P221" s="8"/>
@@ -16091,7 +16091,7 @@
         <v>2</v>
       </c>
       <c r="N222" s="8">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="O222" s="8"/>
       <c r="P222" s="8"/>
@@ -16126,7 +16126,7 @@
         <v>15</v>
       </c>
       <c r="I223" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J223" s="8">
         <v>0</v>
@@ -16139,7 +16139,7 @@
       </c>
       <c r="M223" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N223" s="8">
         <v>0</v>
@@ -16177,13 +16177,13 @@
         <v>13</v>
       </c>
       <c r="I224" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J224" s="8">
         <v>0</v>
       </c>
       <c r="K224" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L224" s="8">
         <v>0</v>
@@ -16244,7 +16244,7 @@
         <v>3</v>
       </c>
       <c r="N225" s="8">
-        <v>422</v>
+        <v>0</v>
       </c>
       <c r="O225" s="8"/>
       <c r="P225" s="8"/>
@@ -16397,7 +16397,7 @@
         <v>2</v>
       </c>
       <c r="N228" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O228" s="8"/>
       <c r="P228" s="8"/>
@@ -16441,14 +16441,14 @@
         <v>0</v>
       </c>
       <c r="L229" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M229" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N229" s="8">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="O229" s="8"/>
       <c r="P229" s="8"/>
@@ -16483,13 +16483,13 @@
         <v>15</v>
       </c>
       <c r="I230" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J230" s="8">
         <v>0</v>
       </c>
       <c r="K230" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L230" s="8">
         <v>0</v>
@@ -16585,7 +16585,7 @@
         <v>12</v>
       </c>
       <c r="I232" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J232" s="8">
         <v>0</v>
@@ -16594,14 +16594,14 @@
         <v>0</v>
       </c>
       <c r="L232" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M232" s="8">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N232" s="8">
-        <v>316</v>
+        <v>459</v>
       </c>
       <c r="O232" s="8"/>
       <c r="P232" s="8"/>
@@ -16636,23 +16636,23 @@
         <v>15</v>
       </c>
       <c r="I233" s="8">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J233" s="8">
         <v>0</v>
       </c>
       <c r="K233" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L233" s="8">
         <v>0</v>
       </c>
       <c r="M233" s="8">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N233" s="8">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="O233" s="8"/>
       <c r="P233" s="8"/>
@@ -16696,14 +16696,14 @@
         <v>0</v>
       </c>
       <c r="L234" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M234" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N234" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O234" s="8"/>
       <c r="P234" s="8"/>
@@ -16754,7 +16754,7 @@
         <v>2</v>
       </c>
       <c r="N235" s="8">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="O235" s="8"/>
       <c r="P235" s="8"/>
@@ -16856,7 +16856,7 @@
         <v>5</v>
       </c>
       <c r="N237" s="8">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="O237" s="8"/>
       <c r="P237" s="8"/>
@@ -16891,7 +16891,7 @@
         <v>14</v>
       </c>
       <c r="I238" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J238" s="8">
         <v>0</v>
@@ -16900,14 +16900,14 @@
         <v>0</v>
       </c>
       <c r="L238" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M238" s="8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N238" s="8">
-        <v>413</v>
+        <v>397</v>
       </c>
       <c r="O238" s="8"/>
       <c r="P238" s="8"/>
@@ -16958,7 +16958,7 @@
         <v>3</v>
       </c>
       <c r="N239" s="8">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="O239" s="8"/>
       <c r="P239" s="8"/>
@@ -16993,23 +16993,23 @@
         <v>13</v>
       </c>
       <c r="I240" s="8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J240" s="8">
         <v>0</v>
       </c>
       <c r="K240" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L240" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M240" s="8">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N240" s="8">
-        <v>242</v>
+        <v>134</v>
       </c>
       <c r="O240" s="8"/>
       <c r="P240" s="8"/>
@@ -17060,7 +17060,7 @@
         <v>3</v>
       </c>
       <c r="N241" s="8">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="O241" s="8"/>
       <c r="P241" s="8"/>
@@ -17111,7 +17111,7 @@
         <v>2</v>
       </c>
       <c r="N242" s="8">
-        <v>663</v>
+        <v>649</v>
       </c>
       <c r="O242" s="8"/>
       <c r="P242" s="8"/>
@@ -17146,23 +17146,23 @@
         <v>15</v>
       </c>
       <c r="I243" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J243" s="8">
         <v>0</v>
       </c>
       <c r="K243" s="8">
+        <v>2</v>
+      </c>
+      <c r="L243" s="8">
         <v>4</v>
-      </c>
-      <c r="L243" s="8">
-        <v>0</v>
       </c>
       <c r="M243" s="8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="N243" s="8">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O243" s="8"/>
       <c r="P243" s="8"/>
@@ -17315,7 +17315,7 @@
         <v>3</v>
       </c>
       <c r="N246" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O246" s="8"/>
       <c r="P246" s="8"/>
@@ -17350,7 +17350,7 @@
         <v>13</v>
       </c>
       <c r="I247" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J247" s="8">
         <v>0</v>
@@ -17363,7 +17363,7 @@
       </c>
       <c r="M247" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N247" s="8">
         <v>283</v>
@@ -17503,7 +17503,7 @@
         <v>12</v>
       </c>
       <c r="I250" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J250" s="8">
         <v>0</v>
@@ -17512,14 +17512,14 @@
         <v>0</v>
       </c>
       <c r="L250" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M250" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N250" s="8">
-        <v>1374</v>
+        <v>1369</v>
       </c>
       <c r="O250" s="8"/>
       <c r="P250" s="8"/>
@@ -17554,7 +17554,7 @@
         <v>14</v>
       </c>
       <c r="I251" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J251" s="8">
         <v>0</v>
@@ -17567,10 +17567,10 @@
       </c>
       <c r="M251" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N251" s="8">
-        <v>1199</v>
+        <v>1196</v>
       </c>
       <c r="O251" s="8"/>
       <c r="P251" s="8"/>
@@ -17605,7 +17605,7 @@
         <v>14</v>
       </c>
       <c r="I252" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J252" s="8">
         <v>0</v>
@@ -17618,7 +17618,7 @@
       </c>
       <c r="M252" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N252" s="8">
         <v>187</v>
@@ -17656,23 +17656,23 @@
         <v>14</v>
       </c>
       <c r="I253" s="8">
+        <v>2</v>
+      </c>
+      <c r="J253" s="8">
+        <v>0</v>
+      </c>
+      <c r="K253" s="8">
+        <v>0</v>
+      </c>
+      <c r="L253" s="8">
         <v>1</v>
-      </c>
-      <c r="J253" s="8">
-        <v>0</v>
-      </c>
-      <c r="K253" s="8">
-        <v>0</v>
-      </c>
-      <c r="L253" s="8">
-        <v>0</v>
       </c>
       <c r="M253" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N253" s="8">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="O253" s="8"/>
       <c r="P253" s="8"/>
@@ -17707,23 +17707,23 @@
         <v>14</v>
       </c>
       <c r="I254" s="8">
+        <v>2</v>
+      </c>
+      <c r="J254" s="8">
+        <v>0</v>
+      </c>
+      <c r="K254" s="8">
+        <v>0</v>
+      </c>
+      <c r="L254" s="8">
         <v>1</v>
-      </c>
-      <c r="J254" s="8">
-        <v>0</v>
-      </c>
-      <c r="K254" s="8">
-        <v>0</v>
-      </c>
-      <c r="L254" s="8">
-        <v>0</v>
       </c>
       <c r="M254" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N254" s="8">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="O254" s="8"/>
       <c r="P254" s="8"/>
@@ -17758,7 +17758,7 @@
         <v>14</v>
       </c>
       <c r="I255" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J255" s="8">
         <v>0</v>
@@ -17771,10 +17771,10 @@
       </c>
       <c r="M255" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N255" s="8">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="O255" s="8"/>
       <c r="P255" s="8"/>
@@ -17825,7 +17825,7 @@
         <v>3</v>
       </c>
       <c r="N256" s="8">
-        <v>1023</v>
+        <v>1019</v>
       </c>
       <c r="O256" s="8"/>
       <c r="P256" s="8"/>
@@ -17876,7 +17876,7 @@
         <v>4</v>
       </c>
       <c r="N257" s="8">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="O257" s="8"/>
       <c r="P257" s="8"/>
@@ -17911,7 +17911,7 @@
         <v>16</v>
       </c>
       <c r="I258" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J258" s="8">
         <v>0</v>
@@ -17924,7 +17924,7 @@
       </c>
       <c r="M258" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N258" s="8">
         <v>68</v>
@@ -17978,7 +17978,7 @@
         <v>3</v>
       </c>
       <c r="N259" s="8">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="O259" s="8"/>
       <c r="P259" s="8"/>
@@ -18019,17 +18019,17 @@
         <v>0</v>
       </c>
       <c r="K260" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L260" s="8">
         <v>0</v>
       </c>
       <c r="M260" s="8">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N260" s="8">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="O260" s="8"/>
       <c r="P260" s="8"/>
@@ -18064,23 +18064,23 @@
         <v>12</v>
       </c>
       <c r="I261" s="8">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J261" s="8">
         <v>0</v>
       </c>
       <c r="K261" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L261" s="8">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="M261" s="8">
         <f t="shared" si="4"/>
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="N261" s="8">
-        <v>312</v>
+        <v>135</v>
       </c>
       <c r="O261" s="8"/>
       <c r="P261" s="8"/>
@@ -18121,17 +18121,17 @@
         <v>0</v>
       </c>
       <c r="K262" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L262" s="8">
         <v>0</v>
       </c>
       <c r="M262" s="8">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N262" s="8">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="O262" s="8"/>
       <c r="P262" s="8"/>
@@ -18166,7 +18166,7 @@
         <v>12</v>
       </c>
       <c r="I263" s="8">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="J263" s="8">
         <v>0</v>
@@ -18175,11 +18175,11 @@
         <v>0</v>
       </c>
       <c r="L263" s="8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M263" s="8">
         <f t="shared" si="4"/>
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="N263" s="8">
         <v>0</v>
@@ -18233,7 +18233,7 @@
         <v>2</v>
       </c>
       <c r="N264" s="8">
-        <v>1006</v>
+        <v>1195</v>
       </c>
       <c r="O264" s="8"/>
       <c r="P264" s="8"/>
@@ -18268,23 +18268,23 @@
         <v>14</v>
       </c>
       <c r="I265" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J265" s="8">
         <v>0</v>
       </c>
       <c r="K265" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L265" s="8">
         <v>1</v>
       </c>
       <c r="M265" s="8">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N265" s="8">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="O265" s="8"/>
       <c r="P265" s="8"/>
@@ -18335,7 +18335,7 @@
         <v>3</v>
       </c>
       <c r="N266" s="8">
-        <v>1532</v>
+        <v>1527</v>
       </c>
       <c r="O266" s="8"/>
       <c r="P266" s="8"/>
@@ -18370,7 +18370,7 @@
         <v>14</v>
       </c>
       <c r="I267" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J267" s="8">
         <v>0</v>
@@ -18383,7 +18383,7 @@
       </c>
       <c r="M267" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N267" s="8">
         <v>51</v>
@@ -18437,7 +18437,7 @@
         <v>3</v>
       </c>
       <c r="N268" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O268" s="8"/>
       <c r="P268" s="8"/>
@@ -18743,7 +18743,7 @@
         <v>3</v>
       </c>
       <c r="N274" s="8">
-        <v>461</v>
+        <v>428</v>
       </c>
       <c r="O274" s="8"/>
       <c r="P274" s="8"/>
@@ -18778,7 +18778,7 @@
         <v>15</v>
       </c>
       <c r="I275" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J275" s="8">
         <v>0</v>
@@ -18791,7 +18791,7 @@
       </c>
       <c r="M275" s="8">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N275" s="8">
         <v>0</v>
@@ -18931,23 +18931,23 @@
         <v>12</v>
       </c>
       <c r="I278" s="8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J278" s="8">
         <v>0</v>
       </c>
       <c r="K278" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L278" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M278" s="8">
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="N278" s="8">
-        <v>1010</v>
+        <v>891</v>
       </c>
       <c r="O278" s="8"/>
       <c r="P278" s="8"/>
@@ -18982,7 +18982,7 @@
         <v>13</v>
       </c>
       <c r="I279" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J279" s="8">
         <v>0</v>
@@ -18995,7 +18995,7 @@
       </c>
       <c r="M279" s="8">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N279" s="8">
         <v>0</v>
@@ -19033,7 +19033,7 @@
         <v>16</v>
       </c>
       <c r="I280" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J280" s="8">
         <v>0</v>
@@ -19046,7 +19046,7 @@
       </c>
       <c r="M280" s="8">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N280" s="8">
         <v>67</v>
@@ -19186,7 +19186,7 @@
         <v>12</v>
       </c>
       <c r="I283" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J283" s="8">
         <v>0</v>
@@ -19199,7 +19199,7 @@
       </c>
       <c r="M283" s="8">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N283" s="8">
         <v>0</v>
@@ -19237,7 +19237,7 @@
         <v>12</v>
       </c>
       <c r="I284" s="8">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="J284" s="8">
         <v>0</v>
@@ -19250,7 +19250,7 @@
       </c>
       <c r="M284" s="8">
         <f t="shared" si="4"/>
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="N284" s="8">
         <v>0</v>
@@ -19304,7 +19304,7 @@
         <v>2</v>
       </c>
       <c r="N285" s="8">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="O285" s="8"/>
       <c r="P285" s="8"/>
@@ -19355,7 +19355,7 @@
         <v>3</v>
       </c>
       <c r="N286" s="8">
-        <v>959</v>
+        <v>950</v>
       </c>
       <c r="O286" s="8"/>
       <c r="P286" s="8"/>
@@ -19390,7 +19390,7 @@
         <v>12</v>
       </c>
       <c r="I287" s="8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J287" s="8">
         <v>0</v>
@@ -19403,10 +19403,10 @@
       </c>
       <c r="M287" s="8">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N287" s="8">
-        <v>1104</v>
+        <v>1094</v>
       </c>
       <c r="O287" s="8"/>
       <c r="P287" s="8"/>
@@ -19441,7 +19441,7 @@
         <v>14</v>
       </c>
       <c r="I288" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J288" s="8">
         <v>0</v>
@@ -19454,10 +19454,10 @@
       </c>
       <c r="M288" s="8">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N288" s="8">
-        <v>1369</v>
+        <v>1336</v>
       </c>
       <c r="O288" s="8"/>
       <c r="P288" s="8"/>
@@ -19492,7 +19492,7 @@
         <v>14</v>
       </c>
       <c r="I289" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J289" s="8">
         <v>0</v>
@@ -19501,14 +19501,14 @@
         <v>0</v>
       </c>
       <c r="L289" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M289" s="8">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="N289" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O289" s="8"/>
       <c r="P289" s="8"/>
@@ -19552,11 +19552,11 @@
         <v>0</v>
       </c>
       <c r="L290" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M290" s="8">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N290" s="8">
         <v>0</v>
@@ -19594,7 +19594,7 @@
         <v>12</v>
       </c>
       <c r="I291" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J291" s="8">
         <v>0</v>
@@ -19603,14 +19603,14 @@
         <v>3</v>
       </c>
       <c r="L291" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M291" s="8">
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="N291" s="8">
-        <v>1169</v>
+        <v>1013</v>
       </c>
       <c r="O291" s="8"/>
       <c r="P291" s="8"/>
@@ -19747,7 +19747,7 @@
         <v>12</v>
       </c>
       <c r="I294" s="8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J294" s="8">
         <v>0</v>
@@ -19756,14 +19756,14 @@
         <v>0</v>
       </c>
       <c r="L294" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M294" s="8">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="N294" s="8">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="O294" s="8"/>
       <c r="P294" s="8"/>
@@ -20053,7 +20053,7 @@
         <v>13</v>
       </c>
       <c r="I300" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J300" s="8">
         <v>0</v>
@@ -20066,7 +20066,7 @@
       </c>
       <c r="M300" s="8">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N300" s="8">
         <v>0</v>
@@ -20206,7 +20206,7 @@
         <v>13</v>
       </c>
       <c r="I303" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J303" s="8">
         <v>0</v>
@@ -20219,7 +20219,7 @@
       </c>
       <c r="M303" s="8">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N303" s="8">
         <v>0</v>
@@ -20324,7 +20324,7 @@
         <v>8</v>
       </c>
       <c r="N305" s="8">
-        <v>446</v>
+        <v>415</v>
       </c>
       <c r="O305" s="8"/>
       <c r="P305" s="8"/>
@@ -20375,7 +20375,7 @@
         <v>9</v>
       </c>
       <c r="N306" s="8">
-        <v>927</v>
+        <v>879</v>
       </c>
       <c r="O306" s="8"/>
       <c r="P306" s="8"/>
@@ -20410,7 +20410,7 @@
         <v>13</v>
       </c>
       <c r="I307" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J307" s="8">
         <v>0</v>
@@ -20423,10 +20423,10 @@
       </c>
       <c r="M307" s="8">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N307" s="8">
-        <v>951</v>
+        <v>923</v>
       </c>
       <c r="O307" s="8"/>
       <c r="P307" s="8"/>
@@ -20477,7 +20477,7 @@
         <v>10</v>
       </c>
       <c r="N308" s="8">
-        <v>812</v>
+        <v>769</v>
       </c>
       <c r="O308" s="8"/>
       <c r="P308" s="8"/>
@@ -20681,7 +20681,7 @@
         <v>6</v>
       </c>
       <c r="N312" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O312" s="8"/>
       <c r="P312" s="8"/>
@@ -20732,7 +20732,7 @@
         <v>3</v>
       </c>
       <c r="N313" s="8">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="O313" s="8"/>
       <c r="P313" s="8"/>
@@ -20783,7 +20783,7 @@
         <v>11</v>
       </c>
       <c r="N314" s="8">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="O314" s="8"/>
       <c r="P314" s="8"/>
@@ -20834,7 +20834,7 @@
         <v>8</v>
       </c>
       <c r="N315" s="8">
-        <v>286</v>
+        <v>218</v>
       </c>
       <c r="O315" s="8"/>
       <c r="P315" s="8"/>
@@ -20885,7 +20885,7 @@
         <v>5</v>
       </c>
       <c r="N316" s="8">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="O316" s="8"/>
       <c r="P316" s="8"/>
@@ -20920,7 +20920,7 @@
         <v>12</v>
       </c>
       <c r="I317" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J317" s="8">
         <v>0</v>
@@ -20933,10 +20933,10 @@
       </c>
       <c r="M317" s="8">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N317" s="8">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="O317" s="8"/>
       <c r="P317" s="8"/>
@@ -20971,23 +20971,23 @@
         <v>12</v>
       </c>
       <c r="I318" s="8">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J318" s="8">
         <v>0</v>
       </c>
       <c r="K318" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L318" s="8">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M318" s="8">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="N318" s="8">
-        <v>218</v>
+        <v>99</v>
       </c>
       <c r="O318" s="8"/>
       <c r="P318" s="8"/>
@@ -21038,7 +21038,7 @@
         <v>4</v>
       </c>
       <c r="N319" s="8">
-        <v>396</v>
+        <v>369</v>
       </c>
       <c r="O319" s="8"/>
       <c r="P319" s="8"/>
@@ -21089,7 +21089,7 @@
         <v>4</v>
       </c>
       <c r="N320" s="8">
-        <v>634</v>
+        <v>622</v>
       </c>
       <c r="O320" s="8"/>
       <c r="P320" s="8"/>
@@ -21140,7 +21140,7 @@
         <v>3</v>
       </c>
       <c r="N321" s="8">
-        <v>497</v>
+        <v>464</v>
       </c>
       <c r="O321" s="8"/>
       <c r="P321" s="8"/>
@@ -21191,7 +21191,7 @@
         <v>3</v>
       </c>
       <c r="N322" s="8">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="O322" s="8"/>
       <c r="P322" s="8"/>
@@ -21344,7 +21344,7 @@
         <v>3</v>
       </c>
       <c r="N325" s="8">
-        <v>341</v>
+        <v>283</v>
       </c>
       <c r="O325" s="8"/>
       <c r="P325" s="8"/>
@@ -21395,7 +21395,7 @@
         <v>3</v>
       </c>
       <c r="N326" s="8">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="O326" s="8"/>
       <c r="P326" s="8"/>
@@ -21439,14 +21439,14 @@
         <v>0</v>
       </c>
       <c r="L327" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M327" s="8">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N327" s="8">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O327" s="8"/>
       <c r="P327" s="8"/>
@@ -21497,7 +21497,7 @@
         <v>2</v>
       </c>
       <c r="N328" s="8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O328" s="8"/>
       <c r="P328" s="8"/>
@@ -21548,7 +21548,7 @@
         <v>4</v>
       </c>
       <c r="N329" s="8">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="O329" s="8"/>
       <c r="P329" s="8"/>
@@ -21599,7 +21599,7 @@
         <v>2</v>
       </c>
       <c r="N330" s="8">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="O330" s="8"/>
       <c r="P330" s="8"/>
@@ -21634,7 +21634,7 @@
         <v>13</v>
       </c>
       <c r="I331" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J331" s="8">
         <v>0</v>
@@ -21647,7 +21647,7 @@
       </c>
       <c r="M331" s="8">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N331" s="8">
         <v>0</v>
@@ -21752,7 +21752,7 @@
         <v>3</v>
       </c>
       <c r="N333" s="8">
-        <v>285</v>
+        <v>0</v>
       </c>
       <c r="O333" s="8"/>
       <c r="P333" s="8"/>
@@ -21803,7 +21803,7 @@
         <v>4</v>
       </c>
       <c r="N334" s="8">
-        <v>312</v>
+        <v>0</v>
       </c>
       <c r="O334" s="8"/>
       <c r="P334" s="8"/>
@@ -21854,7 +21854,7 @@
         <v>2</v>
       </c>
       <c r="N335" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O335" s="8"/>
       <c r="P335" s="8"/>
@@ -21905,7 +21905,7 @@
         <v>4</v>
       </c>
       <c r="N336" s="8">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="O336" s="8"/>
       <c r="P336" s="8"/>
@@ -21940,13 +21940,13 @@
         <v>12</v>
       </c>
       <c r="I337" s="8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J337" s="8">
         <v>0</v>
       </c>
       <c r="K337" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L337" s="8">
         <v>0</v>
@@ -21956,7 +21956,7 @@
         <v>12</v>
       </c>
       <c r="N337" s="8">
-        <v>1173</v>
+        <v>1168</v>
       </c>
       <c r="O337" s="8"/>
       <c r="P337" s="8"/>
@@ -21991,7 +21991,7 @@
         <v>12</v>
       </c>
       <c r="I338" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J338" s="8">
         <v>0</v>
@@ -22004,10 +22004,10 @@
       </c>
       <c r="M338" s="8">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N338" s="8">
-        <v>1127</v>
+        <v>1080</v>
       </c>
       <c r="O338" s="8"/>
       <c r="P338" s="8"/>
@@ -22058,7 +22058,7 @@
         <v>3</v>
       </c>
       <c r="N339" s="8">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="O339" s="8"/>
       <c r="P339" s="8"/>
@@ -22093,23 +22093,23 @@
         <v>14</v>
       </c>
       <c r="I340" s="8">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J340" s="8">
         <v>0</v>
       </c>
       <c r="K340" s="8">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L340" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M340" s="8">
         <f t="shared" si="5"/>
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="N340" s="8">
-        <v>552</v>
+        <v>496</v>
       </c>
       <c r="O340" s="8"/>
       <c r="P340" s="8"/>
@@ -22144,7 +22144,7 @@
         <v>14</v>
       </c>
       <c r="I341" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J341" s="8">
         <v>0</v>
@@ -22157,10 +22157,10 @@
       </c>
       <c r="M341" s="8">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N341" s="8">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="O341" s="8"/>
       <c r="P341" s="8"/>
@@ -22195,7 +22195,7 @@
         <v>14</v>
       </c>
       <c r="I342" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J342" s="8">
         <v>0</v>
@@ -22208,7 +22208,7 @@
       </c>
       <c r="M342" s="8">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N342" s="8">
         <v>323</v>
@@ -22348,7 +22348,7 @@
         <v>12</v>
       </c>
       <c r="I345" s="8">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J345" s="8">
         <v>0</v>
@@ -22361,7 +22361,7 @@
       </c>
       <c r="M345" s="8">
         <f t="shared" si="5"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N345" s="8">
         <v>0</v>
@@ -22450,23 +22450,23 @@
         <v>13</v>
       </c>
       <c r="I347" s="8">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J347" s="8">
         <v>0</v>
       </c>
       <c r="K347" s="8">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L347" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M347" s="8">
         <f t="shared" si="5"/>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N347" s="8">
-        <v>381</v>
+        <v>315</v>
       </c>
       <c r="O347" s="8"/>
       <c r="P347" s="9"/>
@@ -22501,7 +22501,7 @@
         <v>12</v>
       </c>
       <c r="I348" s="8">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="J348" s="8">
         <v>0</v>
@@ -22514,7 +22514,7 @@
       </c>
       <c r="M348" s="8">
         <f t="shared" si="5"/>
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="N348" s="8">
         <v>0</v>
@@ -22711,17 +22711,17 @@
         <v>0</v>
       </c>
       <c r="K352" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L352" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M352" s="8">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="N352" s="8">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="O352" s="8"/>
       <c r="P352" s="9"/>
@@ -23078,7 +23078,7 @@
         <v>3</v>
       </c>
       <c r="N359" s="8">
-        <v>991</v>
+        <v>980</v>
       </c>
       <c r="O359" s="8"/>
       <c r="P359" s="9"/>
@@ -23266,7 +23266,7 @@
         <v>12</v>
       </c>
       <c r="I363" s="8">
-        <v>573</v>
+        <v>542</v>
       </c>
       <c r="J363" s="8">
         <v>0</v>
@@ -23279,7 +23279,7 @@
       </c>
       <c r="M363" s="8">
         <f t="shared" si="5"/>
-        <v>573</v>
+        <v>542</v>
       </c>
       <c r="N363" s="8">
         <v>1318</v>
@@ -23368,7 +23368,7 @@
         <v>13</v>
       </c>
       <c r="I365" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J365" s="8">
         <v>0</v>
@@ -23381,7 +23381,7 @@
       </c>
       <c r="M365" s="8">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N365" s="8">
         <v>0</v>
@@ -23435,7 +23435,7 @@
         <v>2</v>
       </c>
       <c r="N366" s="8">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="O366" s="8"/>
       <c r="P366" s="9"/>
@@ -23521,7 +23521,7 @@
         <v>12</v>
       </c>
       <c r="I368" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J368" s="8">
         <v>0</v>
@@ -23530,14 +23530,14 @@
         <v>0</v>
       </c>
       <c r="L368" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M368" s="8">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N368" s="8">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="O368" s="8"/>
       <c r="P368" s="9"/>
@@ -23572,7 +23572,7 @@
         <v>15</v>
       </c>
       <c r="I369" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J369" s="8">
         <v>0</v>
@@ -23585,7 +23585,7 @@
       </c>
       <c r="M369" s="8">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N369" s="8">
         <v>0</v>
@@ -23690,7 +23690,7 @@
         <v>2</v>
       </c>
       <c r="N371" s="8">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O371" s="8"/>
       <c r="P371" s="9"/>
@@ -23776,7 +23776,7 @@
         <v>14</v>
       </c>
       <c r="I373" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J373" s="8">
         <v>0</v>
@@ -23789,10 +23789,10 @@
       </c>
       <c r="M373" s="8">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N373" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O373" s="8"/>
       <c r="P373" s="9"/>
@@ -24337,7 +24337,7 @@
         <v>12</v>
       </c>
       <c r="I384" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J384" s="8">
         <v>0</v>
@@ -24350,10 +24350,10 @@
       </c>
       <c r="M384" s="8">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N384" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="O384" s="8"/>
       <c r="P384" s="9"/>
@@ -24388,7 +24388,7 @@
         <v>12</v>
       </c>
       <c r="I385" s="8">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="J385" s="8">
         <v>0</v>
@@ -24401,7 +24401,7 @@
       </c>
       <c r="M385" s="8">
         <f t="shared" si="5"/>
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="N385" s="8">
         <v>257</v>
@@ -24643,7 +24643,7 @@
         <v>12</v>
       </c>
       <c r="I390" s="8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J390" s="8">
         <v>0</v>
@@ -24652,14 +24652,14 @@
         <v>0</v>
       </c>
       <c r="L390" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M390" s="8">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N390" s="8">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="O390" s="8"/>
       <c r="P390" s="7"/>
@@ -25373,7 +25373,7 @@
         <v>2</v>
       </c>
       <c r="N404" s="8">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="O404" s="7"/>
       <c r="P404" s="7"/>
@@ -25424,7 +25424,7 @@
         <v>2</v>
       </c>
       <c r="N405" s="8">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="O405" s="7"/>
       <c r="P405" s="7"/>
@@ -25577,7 +25577,7 @@
         <v>2</v>
       </c>
       <c r="N408" s="8">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="O408" s="7"/>
       <c r="P408" s="7"/>
@@ -25612,7 +25612,7 @@
         <v>13</v>
       </c>
       <c r="I409" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J409" s="8">
         <v>0</v>
@@ -25625,10 +25625,10 @@
       </c>
       <c r="M409" s="8">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N409" s="8">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="O409" s="7"/>
       <c r="P409" s="7"/>
@@ -25679,7 +25679,7 @@
         <v>2</v>
       </c>
       <c r="N410" s="8">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="O410" s="7"/>
       <c r="P410" s="7"/>
@@ -25730,7 +25730,7 @@
         <v>2</v>
       </c>
       <c r="N411" s="8">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="O411" s="7"/>
       <c r="P411" s="7"/>
@@ -25781,7 +25781,7 @@
         <v>2</v>
       </c>
       <c r="N412" s="8">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O412" s="7"/>
       <c r="P412" s="7"/>
@@ -25832,7 +25832,7 @@
         <v>2</v>
       </c>
       <c r="N413" s="8">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O413" s="7"/>
       <c r="P413" s="7"/>
@@ -25867,7 +25867,7 @@
         <v>12</v>
       </c>
       <c r="I414" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J414" s="8">
         <v>0</v>
@@ -25880,7 +25880,7 @@
       </c>
       <c r="M414" s="8">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N414" s="8">
         <v>0</v>
@@ -25927,14 +25927,14 @@
         <v>0</v>
       </c>
       <c r="L415" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M415" s="8">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N415" s="8">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="O415" s="7"/>
       <c r="P415" s="7"/>
@@ -25985,7 +25985,7 @@
         <v>3</v>
       </c>
       <c r="N416" s="8">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="O416" s="7"/>
       <c r="P416" s="7"/>
@@ -26036,7 +26036,7 @@
         <v>3</v>
       </c>
       <c r="N417" s="8">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="O417" s="7"/>
       <c r="P417" s="7"/>
@@ -26087,7 +26087,7 @@
         <v>4</v>
       </c>
       <c r="N418" s="8">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="O418" s="7"/>
       <c r="P418" s="7"/>
@@ -26138,7 +26138,7 @@
         <v>3</v>
       </c>
       <c r="N419" s="8">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="O419" s="7"/>
       <c r="P419" s="7"/>
@@ -26189,7 +26189,7 @@
         <v>3</v>
       </c>
       <c r="N420" s="8">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="O420" s="7"/>
       <c r="P420" s="7"/>
@@ -26240,7 +26240,7 @@
         <v>2</v>
       </c>
       <c r="N421" s="8">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="O421" s="7"/>
       <c r="P421" s="7"/>
@@ -26291,7 +26291,7 @@
         <v>2</v>
       </c>
       <c r="N422" s="8">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="O422" s="7"/>
       <c r="P422" s="7"/>
@@ -26342,7 +26342,7 @@
         <v>2</v>
       </c>
       <c r="N423" s="8">
-        <v>588</v>
+        <v>514</v>
       </c>
       <c r="O423" s="7"/>
       <c r="P423" s="7"/>
@@ -26393,7 +26393,7 @@
         <v>2</v>
       </c>
       <c r="N424" s="8">
-        <v>411</v>
+        <v>338</v>
       </c>
       <c r="O424" s="7"/>
       <c r="P424" s="7"/>
@@ -26444,7 +26444,7 @@
         <v>2</v>
       </c>
       <c r="N425" s="8">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="O425" s="7"/>
       <c r="P425" s="7"/>
@@ -26495,7 +26495,7 @@
         <v>2</v>
       </c>
       <c r="N426" s="8">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="O426" s="7"/>
       <c r="P426" s="7"/>
@@ -26546,7 +26546,7 @@
         <v>2</v>
       </c>
       <c r="N427" s="8">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O427" s="7"/>
       <c r="P427" s="7"/>
@@ -26699,7 +26699,7 @@
         <v>0</v>
       </c>
       <c r="N430" s="8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O430" s="7"/>
       <c r="P430" s="7"/>
@@ -26750,7 +26750,7 @@
         <v>0</v>
       </c>
       <c r="N431" s="8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O431" s="7"/>
       <c r="P431" s="7"/>
@@ -26801,7 +26801,7 @@
         <v>0</v>
       </c>
       <c r="N432" s="8">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O432" s="7"/>
       <c r="P432" s="7"/>
@@ -27099,7 +27099,7 @@
         <v>0</v>
       </c>
       <c r="N438" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O438" s="7"/>
       <c r="P438" s="7"/>

--- a/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
+++ b/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\Fossil Replenishment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFC13321-91EC-435E-8E47-1F5EA290C36D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54779161-AED0-4BA2-BA42-A6A0C770BA7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6662473D-6E1F-42FD-999B-28162E22D4B5}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$T$439</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3519" uniqueCount="1360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3519" uniqueCount="1359">
   <si>
     <t>In Transit PO</t>
   </si>
@@ -3244,9 +3244,6 @@
   </si>
   <si>
     <t>Y</t>
-  </si>
-  <si>
-    <t>Y-Pulse</t>
   </si>
   <si>
     <t>Y-Liq</t>
@@ -5203,7 +5200,7 @@
         <v>19</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>1062</v>
@@ -5254,7 +5251,7 @@
         <v>19</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>1062</v>
@@ -5305,7 +5302,7 @@
         <v>19</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>1062</v>
@@ -6019,7 +6016,7 @@
         <v>19</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G25" s="8" t="s">
         <v>1062</v>
@@ -6172,7 +6169,7 @@
         <v>19</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G28" s="8" t="s">
         <v>1062</v>
@@ -6682,7 +6679,7 @@
         <v>19</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G38" s="8" t="s">
         <v>1062</v>
@@ -6784,10 +6781,10 @@
         <v>19</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H40" s="8" t="s">
         <v>12</v>
@@ -6937,7 +6934,7 @@
         <v>19</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G43" s="8" t="s">
         <v>1062</v>
@@ -7294,7 +7291,7 @@
         <v>19</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G50" s="8" t="s">
         <v>1062</v>
@@ -7651,7 +7648,7 @@
         <v>19</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G57" s="8" t="s">
         <v>1062</v>
@@ -7753,7 +7750,7 @@
         <v>19</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G59" s="8" t="s">
         <v>1062</v>
@@ -8059,10 +8056,10 @@
         <v>19</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="H65" s="8" t="s">
         <v>12</v>
@@ -8110,7 +8107,7 @@
         <v>19</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G66" s="8" t="s">
         <v>1062</v>
@@ -8467,7 +8464,7 @@
         <v>19</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G73" s="8" t="s">
         <v>1062</v>
@@ -8518,7 +8515,7 @@
         <v>19</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G74" s="8" t="s">
         <v>1062</v>
@@ -8569,7 +8566,7 @@
         <v>19</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G75" s="8" t="s">
         <v>1062</v>
@@ -8620,7 +8617,7 @@
         <v>19</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G76" s="8" t="s">
         <v>1062</v>
@@ -8977,10 +8974,10 @@
         <v>19</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H83" s="8" t="s">
         <v>15</v>
@@ -9028,7 +9025,7 @@
         <v>19</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G84" s="8" t="s">
         <v>1062</v>
@@ -9082,7 +9079,7 @@
         <v>1069</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H85" s="8" t="s">
         <v>14</v>
@@ -9130,10 +9127,10 @@
         <v>19</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="H86" s="8" t="s">
         <v>12</v>
@@ -9181,10 +9178,10 @@
         <v>19</v>
       </c>
       <c r="F87" s="8" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H87" s="8" t="s">
         <v>13</v>
@@ -9385,10 +9382,10 @@
         <v>19</v>
       </c>
       <c r="F91" s="8" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="G91" s="8" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="H91" s="8" t="s">
         <v>12</v>
@@ -9487,7 +9484,7 @@
         <v>19</v>
       </c>
       <c r="F93" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G93" s="8" t="s">
         <v>1062</v>
@@ -9538,7 +9535,7 @@
         <v>19</v>
       </c>
       <c r="F94" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G94" s="8" t="s">
         <v>1062</v>
@@ -9691,7 +9688,7 @@
         <v>19</v>
       </c>
       <c r="F97" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G97" s="8" t="s">
         <v>1062</v>
@@ -9742,7 +9739,7 @@
         <v>19</v>
       </c>
       <c r="F98" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G98" s="8" t="s">
         <v>1062</v>
@@ -9793,7 +9790,7 @@
         <v>19</v>
       </c>
       <c r="F99" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G99" s="8" t="s">
         <v>1062</v>
@@ -9844,10 +9841,10 @@
         <v>19</v>
       </c>
       <c r="F100" s="8" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="G100" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H100" s="8" t="s">
         <v>15</v>
@@ -9895,7 +9892,7 @@
         <v>19</v>
       </c>
       <c r="F101" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G101" s="8" t="s">
         <v>1062</v>
@@ -9946,7 +9943,7 @@
         <v>19</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G102" s="8" t="s">
         <v>1062</v>
@@ -9997,7 +9994,7 @@
         <v>19</v>
       </c>
       <c r="F103" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G103" s="8" t="s">
         <v>1062</v>
@@ -10048,7 +10045,7 @@
         <v>19</v>
       </c>
       <c r="F104" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G104" s="8" t="s">
         <v>1062</v>
@@ -10150,10 +10147,10 @@
         <v>19</v>
       </c>
       <c r="F106" s="8" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="G106" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H106" s="8" t="s">
         <v>15</v>
@@ -10252,10 +10249,10 @@
         <v>19</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="G108" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H108" s="8" t="s">
         <v>15</v>
@@ -10303,7 +10300,7 @@
         <v>19</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G109" s="8" t="s">
         <v>1062</v>
@@ -10354,10 +10351,10 @@
         <v>19</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H110" s="8" t="s">
         <v>13</v>
@@ -10405,7 +10402,7 @@
         <v>19</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G111" s="8" t="s">
         <v>1062</v>
@@ -11017,7 +11014,7 @@
         <v>19</v>
       </c>
       <c r="F123" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G123" s="8" t="s">
         <v>1062</v>
@@ -11068,7 +11065,7 @@
         <v>19</v>
       </c>
       <c r="F124" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G124" s="8" t="s">
         <v>1062</v>
@@ -11170,7 +11167,7 @@
         <v>19</v>
       </c>
       <c r="F126" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G126" s="8" t="s">
         <v>1062</v>
@@ -11221,7 +11218,7 @@
         <v>19</v>
       </c>
       <c r="F127" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G127" s="8" t="s">
         <v>1062</v>
@@ -11323,7 +11320,7 @@
         <v>19</v>
       </c>
       <c r="F129" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G129" s="8" t="s">
         <v>1062</v>
@@ -11374,7 +11371,7 @@
         <v>19</v>
       </c>
       <c r="F130" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G130" s="8" t="s">
         <v>1062</v>
@@ -11425,7 +11422,7 @@
         <v>19</v>
       </c>
       <c r="F131" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G131" s="8" t="s">
         <v>1062</v>
@@ -11629,7 +11626,7 @@
         <v>19</v>
       </c>
       <c r="F135" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G135" s="8" t="s">
         <v>1062</v>
@@ -11680,7 +11677,7 @@
         <v>19</v>
       </c>
       <c r="F136" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G136" s="8" t="s">
         <v>1062</v>
@@ -11731,7 +11728,7 @@
         <v>19</v>
       </c>
       <c r="F137" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G137" s="8" t="s">
         <v>1062</v>
@@ -11782,7 +11779,7 @@
         <v>19</v>
       </c>
       <c r="F138" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G138" s="8" t="s">
         <v>1062</v>
@@ -11833,7 +11830,7 @@
         <v>19</v>
       </c>
       <c r="F139" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G139" s="8" t="s">
         <v>1062</v>
@@ -11884,7 +11881,7 @@
         <v>19</v>
       </c>
       <c r="F140" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G140" s="8" t="s">
         <v>1062</v>
@@ -11935,7 +11932,7 @@
         <v>19</v>
       </c>
       <c r="F141" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G141" s="8" t="s">
         <v>1062</v>
@@ -11986,7 +11983,7 @@
         <v>19</v>
       </c>
       <c r="F142" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G142" s="8" t="s">
         <v>1062</v>
@@ -12037,7 +12034,7 @@
         <v>19</v>
       </c>
       <c r="F143" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G143" s="8" t="s">
         <v>1062</v>
@@ -12088,7 +12085,7 @@
         <v>19</v>
       </c>
       <c r="F144" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G144" s="8" t="s">
         <v>1062</v>
@@ -12190,7 +12187,7 @@
         <v>19</v>
       </c>
       <c r="F146" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G146" s="8" t="s">
         <v>1062</v>
@@ -12292,7 +12289,7 @@
         <v>19</v>
       </c>
       <c r="F148" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G148" s="8" t="s">
         <v>1062</v>
@@ -12343,7 +12340,7 @@
         <v>19</v>
       </c>
       <c r="F149" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G149" s="8" t="s">
         <v>1062</v>
@@ -12394,7 +12391,7 @@
         <v>19</v>
       </c>
       <c r="F150" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G150" s="8" t="s">
         <v>1062</v>
@@ -12445,7 +12442,7 @@
         <v>19</v>
       </c>
       <c r="F151" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G151" s="8" t="s">
         <v>1062</v>
@@ -12547,7 +12544,7 @@
         <v>19</v>
       </c>
       <c r="F153" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G153" s="8" t="s">
         <v>1062</v>
@@ -12649,7 +12646,7 @@
         <v>19</v>
       </c>
       <c r="F155" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G155" s="8" t="s">
         <v>1062</v>
@@ -12700,7 +12697,7 @@
         <v>19</v>
       </c>
       <c r="F156" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G156" s="8" t="s">
         <v>1062</v>
@@ -12751,7 +12748,7 @@
         <v>19</v>
       </c>
       <c r="F157" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G157" s="8" t="s">
         <v>1062</v>
@@ -12802,7 +12799,7 @@
         <v>19</v>
       </c>
       <c r="F158" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G158" s="8" t="s">
         <v>1062</v>
@@ -12853,7 +12850,7 @@
         <v>19</v>
       </c>
       <c r="F159" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G159" s="8" t="s">
         <v>1062</v>
@@ -13006,7 +13003,7 @@
         <v>19</v>
       </c>
       <c r="F162" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G162" s="8" t="s">
         <v>1062</v>
@@ -13057,7 +13054,7 @@
         <v>19</v>
       </c>
       <c r="F163" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G163" s="8" t="s">
         <v>1062</v>
@@ -13108,7 +13105,7 @@
         <v>19</v>
       </c>
       <c r="F164" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G164" s="8" t="s">
         <v>1062</v>
@@ -13210,10 +13207,10 @@
         <v>19</v>
       </c>
       <c r="F166" s="8" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="G166" s="8" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="H166" s="8" t="s">
         <v>14</v>
@@ -13261,7 +13258,7 @@
         <v>19</v>
       </c>
       <c r="F167" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G167" s="8" t="s">
         <v>1062</v>
@@ -13312,7 +13309,7 @@
         <v>19</v>
       </c>
       <c r="F168" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G168" s="8" t="s">
         <v>1062</v>
@@ -13363,7 +13360,7 @@
         <v>19</v>
       </c>
       <c r="F169" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G169" s="8" t="s">
         <v>1062</v>
@@ -13414,10 +13411,10 @@
         <v>19</v>
       </c>
       <c r="F170" s="8" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="G170" s="8" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="H170" s="8" t="s">
         <v>14</v>
@@ -13465,7 +13462,7 @@
         <v>19</v>
       </c>
       <c r="F171" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G171" s="8" t="s">
         <v>1062</v>
@@ -13516,7 +13513,7 @@
         <v>19</v>
       </c>
       <c r="F172" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G172" s="8" t="s">
         <v>1062</v>
@@ -13618,7 +13615,7 @@
         <v>19</v>
       </c>
       <c r="F174" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G174" s="8" t="s">
         <v>1062</v>
@@ -13669,7 +13666,7 @@
         <v>19</v>
       </c>
       <c r="F175" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G175" s="8" t="s">
         <v>1062</v>
@@ -13771,7 +13768,7 @@
         <v>19</v>
       </c>
       <c r="F177" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G177" s="8" t="s">
         <v>1062</v>
@@ -13822,10 +13819,10 @@
         <v>19</v>
       </c>
       <c r="F178" s="8" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="G178" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H178" s="8" t="s">
         <v>12</v>
@@ -14026,7 +14023,7 @@
         <v>19</v>
       </c>
       <c r="F182" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G182" s="8" t="s">
         <v>1062</v>
@@ -14332,7 +14329,7 @@
         <v>19</v>
       </c>
       <c r="F188" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G188" s="8" t="s">
         <v>1062</v>
@@ -14383,7 +14380,7 @@
         <v>19</v>
       </c>
       <c r="F189" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G189" s="8" t="s">
         <v>1062</v>
@@ -14587,10 +14584,10 @@
         <v>19</v>
       </c>
       <c r="F193" s="8" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="G193" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H193" s="8" t="s">
         <v>14</v>
@@ -14638,7 +14635,7 @@
         <v>19</v>
       </c>
       <c r="F194" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G194" s="8" t="s">
         <v>1062</v>
@@ -14689,7 +14686,7 @@
         <v>19</v>
       </c>
       <c r="F195" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G195" s="8" t="s">
         <v>1062</v>
@@ -14740,7 +14737,7 @@
         <v>19</v>
       </c>
       <c r="F196" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G196" s="8" t="s">
         <v>1062</v>
@@ -14842,7 +14839,7 @@
         <v>19</v>
       </c>
       <c r="F198" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G198" s="8" t="s">
         <v>1062</v>
@@ -14893,7 +14890,7 @@
         <v>19</v>
       </c>
       <c r="F199" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G199" s="8" t="s">
         <v>1062</v>
@@ -14944,7 +14941,7 @@
         <v>19</v>
       </c>
       <c r="F200" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G200" s="8" t="s">
         <v>1062</v>
@@ -14995,10 +14992,10 @@
         <v>19</v>
       </c>
       <c r="F201" s="8" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="G201" s="8" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="H201" s="8" t="s">
         <v>12</v>
@@ -15148,7 +15145,7 @@
         <v>19</v>
       </c>
       <c r="F204" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G204" s="8" t="s">
         <v>1062</v>
@@ -15199,7 +15196,7 @@
         <v>19</v>
       </c>
       <c r="F205" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G205" s="8" t="s">
         <v>1062</v>
@@ -15250,7 +15247,7 @@
         <v>19</v>
       </c>
       <c r="F206" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G206" s="8" t="s">
         <v>1062</v>
@@ -15403,10 +15400,10 @@
         <v>19</v>
       </c>
       <c r="F209" s="8" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="G209" s="8" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="H209" s="8" t="s">
         <v>12</v>
@@ -15454,7 +15451,7 @@
         <v>19</v>
       </c>
       <c r="F210" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G210" s="8" t="s">
         <v>1062</v>
@@ -15505,7 +15502,7 @@
         <v>19</v>
       </c>
       <c r="F211" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G211" s="8" t="s">
         <v>1062</v>
@@ -15556,7 +15553,7 @@
         <v>19</v>
       </c>
       <c r="F212" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G212" s="8" t="s">
         <v>1062</v>
@@ -15607,7 +15604,7 @@
         <v>19</v>
       </c>
       <c r="F213" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G213" s="8" t="s">
         <v>1062</v>
@@ -15658,7 +15655,7 @@
         <v>19</v>
       </c>
       <c r="F214" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G214" s="8" t="s">
         <v>1062</v>
@@ -15709,7 +15706,7 @@
         <v>19</v>
       </c>
       <c r="F215" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G215" s="8" t="s">
         <v>1062</v>
@@ -15760,7 +15757,7 @@
         <v>19</v>
       </c>
       <c r="F216" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G216" s="8" t="s">
         <v>1062</v>
@@ -15964,7 +15961,7 @@
         <v>19</v>
       </c>
       <c r="F220" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G220" s="8" t="s">
         <v>1062</v>
@@ -16015,7 +16012,7 @@
         <v>19</v>
       </c>
       <c r="F221" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G221" s="8" t="s">
         <v>1062</v>
@@ -16168,7 +16165,7 @@
         <v>19</v>
       </c>
       <c r="F224" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G224" s="8" t="s">
         <v>1062</v>
@@ -16270,7 +16267,7 @@
         <v>19</v>
       </c>
       <c r="F226" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G226" s="8" t="s">
         <v>1062</v>
@@ -16423,7 +16420,7 @@
         <v>19</v>
       </c>
       <c r="F229" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G229" s="8" t="s">
         <v>1062</v>
@@ -16525,10 +16522,10 @@
         <v>19</v>
       </c>
       <c r="F231" s="8" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="G231" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H231" s="8" t="s">
         <v>13</v>
@@ -16678,7 +16675,7 @@
         <v>19</v>
       </c>
       <c r="F234" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G234" s="8" t="s">
         <v>1062</v>
@@ -16780,10 +16777,10 @@
         <v>19</v>
       </c>
       <c r="F236" s="8" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="G236" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H236" s="8" t="s">
         <v>14</v>
@@ -16831,7 +16828,7 @@
         <v>19</v>
       </c>
       <c r="F237" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G237" s="8" t="s">
         <v>1062</v>
@@ -16933,7 +16930,7 @@
         <v>19</v>
       </c>
       <c r="F239" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G239" s="8" t="s">
         <v>1062</v>
@@ -17086,7 +17083,7 @@
         <v>19</v>
       </c>
       <c r="F242" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G242" s="8" t="s">
         <v>1062</v>
@@ -17137,7 +17134,7 @@
         <v>19</v>
       </c>
       <c r="F243" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G243" s="8" t="s">
         <v>1062</v>
@@ -17188,7 +17185,7 @@
         <v>19</v>
       </c>
       <c r="F244" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G244" s="8" t="s">
         <v>1062</v>
@@ -17341,7 +17338,7 @@
         <v>19</v>
       </c>
       <c r="F247" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G247" s="8" t="s">
         <v>1062</v>
@@ -17392,7 +17389,7 @@
         <v>19</v>
       </c>
       <c r="F248" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G248" s="8" t="s">
         <v>1062</v>
@@ -17443,10 +17440,10 @@
         <v>19</v>
       </c>
       <c r="F249" s="8" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="G249" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H249" s="8" t="s">
         <v>13</v>
@@ -17494,7 +17491,7 @@
         <v>19</v>
       </c>
       <c r="F250" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G250" s="8" t="s">
         <v>1062</v>
@@ -17545,10 +17542,10 @@
         <v>19</v>
       </c>
       <c r="F251" s="8" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="G251" s="8" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="H251" s="8" t="s">
         <v>14</v>
@@ -17596,7 +17593,7 @@
         <v>19</v>
       </c>
       <c r="F252" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G252" s="8" t="s">
         <v>1062</v>
@@ -17647,7 +17644,7 @@
         <v>19</v>
       </c>
       <c r="F253" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G253" s="8" t="s">
         <v>1062</v>
@@ -17698,7 +17695,7 @@
         <v>19</v>
       </c>
       <c r="F254" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G254" s="8" t="s">
         <v>1062</v>
@@ -17749,10 +17746,10 @@
         <v>19</v>
       </c>
       <c r="F255" s="8" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="G255" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H255" s="8" t="s">
         <v>14</v>
@@ -17902,10 +17899,10 @@
         <v>19</v>
       </c>
       <c r="F258" s="8" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="G258" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H258" s="8" t="s">
         <v>16</v>
@@ -18310,10 +18307,10 @@
         <v>19</v>
       </c>
       <c r="F266" s="8" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="G266" s="8" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="H266" s="8" t="s">
         <v>14</v>
@@ -18412,10 +18409,10 @@
         <v>19</v>
       </c>
       <c r="F268" s="8" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="G268" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H268" s="8" t="s">
         <v>15</v>
@@ -18565,7 +18562,7 @@
         <v>19</v>
       </c>
       <c r="F271" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G271" s="8" t="s">
         <v>1062</v>
@@ -18616,7 +18613,7 @@
         <v>19</v>
       </c>
       <c r="F272" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G272" s="8" t="s">
         <v>1062</v>
@@ -18667,10 +18664,10 @@
         <v>19</v>
       </c>
       <c r="F273" s="8" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="G273" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H273" s="8" t="s">
         <v>16</v>
@@ -18871,7 +18868,7 @@
         <v>19</v>
       </c>
       <c r="F277" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G277" s="8" t="s">
         <v>1062</v>
@@ -18973,7 +18970,7 @@
         <v>19</v>
       </c>
       <c r="F279" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G279" s="8" t="s">
         <v>1062</v>
@@ -19534,7 +19531,7 @@
         <v>19</v>
       </c>
       <c r="F290" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G290" s="8" t="s">
         <v>1062</v>
@@ -19687,7 +19684,7 @@
         <v>19</v>
       </c>
       <c r="F293" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G293" s="8" t="s">
         <v>1062</v>
@@ -19738,7 +19735,7 @@
         <v>19</v>
       </c>
       <c r="F294" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G294" s="8" t="s">
         <v>1062</v>
@@ -19840,10 +19837,10 @@
         <v>19</v>
       </c>
       <c r="F296" s="8" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="G296" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H296" s="8" t="s">
         <v>14</v>
@@ -19891,7 +19888,7 @@
         <v>19</v>
       </c>
       <c r="F297" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G297" s="8" t="s">
         <v>1062</v>
@@ -19942,7 +19939,7 @@
         <v>19</v>
       </c>
       <c r="F298" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G298" s="8" t="s">
         <v>1062</v>
@@ -20095,10 +20092,10 @@
         <v>19</v>
       </c>
       <c r="F301" s="8" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="G301" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H301" s="8" t="s">
         <v>13</v>
@@ -20146,10 +20143,10 @@
         <v>19</v>
       </c>
       <c r="F302" s="8" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="G302" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H302" s="8" t="s">
         <v>13</v>
@@ -20197,10 +20194,10 @@
         <v>19</v>
       </c>
       <c r="F303" s="8" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="G303" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H303" s="8" t="s">
         <v>13</v>
@@ -20248,10 +20245,10 @@
         <v>19</v>
       </c>
       <c r="F304" s="8" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="G304" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H304" s="8" t="s">
         <v>13</v>
@@ -20503,10 +20500,10 @@
         <v>19</v>
       </c>
       <c r="F309" s="8" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="G309" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H309" s="8" t="s">
         <v>13</v>
@@ -20911,10 +20908,10 @@
         <v>19</v>
       </c>
       <c r="F317" s="8" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="G317" s="8" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="H317" s="8" t="s">
         <v>12</v>
@@ -22237,10 +22234,10 @@
         <v>19</v>
       </c>
       <c r="F343" s="8" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="G343" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H343" s="8" t="s">
         <v>14</v>
@@ -22273,13 +22270,13 @@
     </row>
     <row r="344" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="9" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B344" s="9" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="C344" s="9" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="D344" s="8" t="s">
         <v>20</v>
@@ -22324,13 +22321,13 @@
     </row>
     <row r="345" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="9" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B345" s="9" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="C345" s="9" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="D345" s="8" t="s">
         <v>20</v>
@@ -22375,13 +22372,13 @@
     </row>
     <row r="346" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="9" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="B346" s="9" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="C346" s="9" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="D346" s="8" t="s">
         <v>20</v>
@@ -22426,13 +22423,13 @@
     </row>
     <row r="347" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="9" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="B347" s="9" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C347" s="9" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="D347" s="8" t="s">
         <v>701</v>
@@ -22477,13 +22474,13 @@
     </row>
     <row r="348" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="9" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="B348" s="9" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C348" s="9" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="D348" s="8" t="s">
         <v>701</v>
@@ -22528,13 +22525,13 @@
     </row>
     <row r="349" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="9" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="B349" s="9" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="C349" s="9" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="D349" s="8" t="s">
         <v>30</v>
@@ -22543,7 +22540,7 @@
         <v>19</v>
       </c>
       <c r="F349" s="9" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G349" s="8" t="s">
         <v>1062</v>
@@ -22579,13 +22576,13 @@
     </row>
     <row r="350" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="9" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B350" s="9" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="C350" s="9" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="D350" s="8" t="s">
         <v>75</v>
@@ -22594,7 +22591,7 @@
         <v>19</v>
       </c>
       <c r="F350" s="9" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G350" s="8" t="s">
         <v>1062</v>
@@ -22630,13 +22627,13 @@
     </row>
     <row r="351" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="9" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B351" s="9" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C351" s="9" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="D351" s="8" t="s">
         <v>75</v>
@@ -22645,7 +22642,7 @@
         <v>19</v>
       </c>
       <c r="F351" s="9" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G351" s="8" t="s">
         <v>1062</v>
@@ -22681,13 +22678,13 @@
     </row>
     <row r="352" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="9" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="B352" s="9" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="C352" s="9" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="D352" s="8" t="s">
         <v>75</v>
@@ -22732,13 +22729,13 @@
     </row>
     <row r="353" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="9" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="B353" s="9" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="C353" s="9" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="D353" s="8" t="s">
         <v>30</v>
@@ -22747,7 +22744,7 @@
         <v>19</v>
       </c>
       <c r="F353" s="9" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G353" s="8" t="s">
         <v>1062</v>
@@ -22783,13 +22780,13 @@
     </row>
     <row r="354" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="9" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B354" s="9" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="C354" s="9" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="D354" s="8" t="s">
         <v>75</v>
@@ -22798,7 +22795,7 @@
         <v>19</v>
       </c>
       <c r="F354" s="9" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G354" s="8" t="s">
         <v>1062</v>
@@ -22834,13 +22831,13 @@
     </row>
     <row r="355" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="9" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B355" s="9" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="C355" s="9" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="D355" s="8" t="s">
         <v>30</v>
@@ -22849,7 +22846,7 @@
         <v>19</v>
       </c>
       <c r="F355" s="9" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G355" s="8" t="s">
         <v>1062</v>
@@ -22885,13 +22882,13 @@
     </row>
     <row r="356" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="9" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B356" s="9" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="C356" s="9" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="D356" s="8" t="s">
         <v>75</v>
@@ -22900,7 +22897,7 @@
         <v>19</v>
       </c>
       <c r="F356" s="9" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G356" s="8" t="s">
         <v>1062</v>
@@ -22936,13 +22933,13 @@
     </row>
     <row r="357" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="9" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="B357" s="9" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="C357" s="9" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="D357" s="8" t="s">
         <v>75</v>
@@ -22951,7 +22948,7 @@
         <v>19</v>
       </c>
       <c r="F357" s="9" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G357" s="8" t="s">
         <v>1062</v>
@@ -22987,13 +22984,13 @@
     </row>
     <row r="358" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="9" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="B358" s="9" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C358" s="9" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="D358" s="8" t="s">
         <v>75</v>
@@ -23002,7 +22999,7 @@
         <v>19</v>
       </c>
       <c r="F358" s="9" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G358" s="8" t="s">
         <v>1062</v>
@@ -23038,13 +23035,13 @@
     </row>
     <row r="359" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="9" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="B359" s="9" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C359" s="9" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="D359" s="8" t="s">
         <v>75</v>
@@ -23089,13 +23086,13 @@
     </row>
     <row r="360" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="9" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B360" s="9" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C360" s="9" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="D360" s="8" t="s">
         <v>30</v>
@@ -23104,10 +23101,10 @@
         <v>19</v>
       </c>
       <c r="F360" s="9" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="G360" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H360" s="8" t="s">
         <v>14</v>
@@ -23140,13 +23137,13 @@
     </row>
     <row r="361" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="9" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="B361" s="9" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C361" s="9" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="D361" s="8" t="s">
         <v>75</v>
@@ -23155,7 +23152,7 @@
         <v>19</v>
       </c>
       <c r="F361" s="9" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G361" s="8" t="s">
         <v>1062</v>
@@ -23191,13 +23188,13 @@
     </row>
     <row r="362" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="9" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="B362" s="9" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C362" s="9" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="D362" s="8" t="s">
         <v>75</v>
@@ -23206,7 +23203,7 @@
         <v>19</v>
       </c>
       <c r="F362" s="9" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G362" s="8" t="s">
         <v>1062</v>
@@ -23242,13 +23239,13 @@
     </row>
     <row r="363" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="9" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="B363" s="9" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="C363" s="9" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="D363" s="8" t="s">
         <v>418</v>
@@ -23293,13 +23290,13 @@
     </row>
     <row r="364" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="9" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="B364" s="9" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="C364" s="9" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="D364" s="8" t="s">
         <v>418</v>
@@ -23308,7 +23305,7 @@
         <v>19</v>
       </c>
       <c r="F364" s="9" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G364" s="8" t="s">
         <v>1062</v>
@@ -23344,13 +23341,13 @@
     </row>
     <row r="365" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="9" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="B365" s="9" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C365" s="9" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="D365" s="8" t="s">
         <v>30</v>
@@ -23395,13 +23392,13 @@
     </row>
     <row r="366" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="9" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="B366" s="9" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="C366" s="9" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="D366" s="8" t="s">
         <v>127</v>
@@ -23446,13 +23443,13 @@
     </row>
     <row r="367" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" s="9" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="B367" s="9" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="C367" s="9" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="D367" s="8" t="s">
         <v>75</v>
@@ -23497,13 +23494,13 @@
     </row>
     <row r="368" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A368" s="9" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B368" s="9" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="C368" s="9" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="D368" s="8" t="s">
         <v>418</v>
@@ -23548,13 +23545,13 @@
     </row>
     <row r="369" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A369" s="9" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B369" s="9" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="C369" s="9" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="D369" s="8" t="s">
         <v>194</v>
@@ -23599,13 +23596,13 @@
     </row>
     <row r="370" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A370" s="9" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="B370" s="9" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="C370" s="9" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="D370" s="8" t="s">
         <v>921</v>
@@ -23650,13 +23647,13 @@
     </row>
     <row r="371" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A371" s="9" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B371" s="9" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="C371" s="9" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="D371" s="8" t="s">
         <v>921</v>
@@ -23701,13 +23698,13 @@
     </row>
     <row r="372" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A372" s="9" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B372" s="9" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="C372" s="9" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="D372" s="8" t="s">
         <v>921</v>
@@ -23716,10 +23713,10 @@
         <v>19</v>
       </c>
       <c r="F372" s="9" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="G372" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H372" s="8" t="s">
         <v>14</v>
@@ -23752,13 +23749,13 @@
     </row>
     <row r="373" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A373" s="9" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="B373" s="9" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="C373" s="9" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="D373" s="8" t="s">
         <v>921</v>
@@ -23803,13 +23800,13 @@
     </row>
     <row r="374" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A374" s="9" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="B374" s="9" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="C374" s="9" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="D374" s="8" t="s">
         <v>75</v>
@@ -23818,7 +23815,7 @@
         <v>19</v>
       </c>
       <c r="F374" s="9" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G374" s="8" t="s">
         <v>1062</v>
@@ -23854,13 +23851,13 @@
     </row>
     <row r="375" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A375" s="9" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="B375" s="9" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="C375" s="9" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="D375" s="8" t="s">
         <v>20</v>
@@ -23905,13 +23902,13 @@
     </row>
     <row r="376" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A376" s="9" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="B376" s="9" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="C376" s="9" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="D376" s="8" t="s">
         <v>20</v>
@@ -23956,13 +23953,13 @@
     </row>
     <row r="377" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A377" s="9" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="B377" s="9" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="C377" s="9" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="D377" s="8" t="s">
         <v>30</v>
@@ -23971,7 +23968,7 @@
         <v>19</v>
       </c>
       <c r="F377" s="9" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G377" s="8" t="s">
         <v>1062</v>
@@ -24007,13 +24004,13 @@
     </row>
     <row r="378" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A378" s="9" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="B378" s="9" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="C378" s="9" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="D378" s="8" t="s">
         <v>30</v>
@@ -24022,7 +24019,7 @@
         <v>19</v>
       </c>
       <c r="F378" s="9" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G378" s="8" t="s">
         <v>1062</v>
@@ -24058,13 +24055,13 @@
     </row>
     <row r="379" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A379" s="9" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B379" s="9" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="C379" s="9" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="D379" s="8" t="s">
         <v>75</v>
@@ -24073,7 +24070,7 @@
         <v>19</v>
       </c>
       <c r="F379" s="9" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G379" s="8" t="s">
         <v>1062</v>
@@ -24109,13 +24106,13 @@
     </row>
     <row r="380" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A380" s="9" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="B380" s="9" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="C380" s="9" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="D380" s="8" t="s">
         <v>30</v>
@@ -24124,10 +24121,10 @@
         <v>19</v>
       </c>
       <c r="F380" s="9" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="G380" s="8" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="H380" s="8" t="s">
         <v>12</v>
@@ -24160,13 +24157,13 @@
     </row>
     <row r="381" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A381" s="9" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="B381" s="9" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="C381" s="9" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="D381" s="8" t="s">
         <v>30</v>
@@ -24175,7 +24172,7 @@
         <v>19</v>
       </c>
       <c r="F381" s="9" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G381" s="8" t="s">
         <v>1062</v>
@@ -24211,13 +24208,13 @@
     </row>
     <row r="382" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A382" s="9" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="B382" s="9" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="C382" s="9" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="D382" s="8" t="s">
         <v>52</v>
@@ -24262,13 +24259,13 @@
     </row>
     <row r="383" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A383" s="9" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="B383" s="9" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="C383" s="9" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="D383" s="8" t="s">
         <v>52</v>
@@ -24277,7 +24274,7 @@
         <v>19</v>
       </c>
       <c r="F383" s="9" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G383" s="8" t="s">
         <v>1062</v>
@@ -24313,13 +24310,13 @@
     </row>
     <row r="384" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A384" s="9" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B384" s="9" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="C384" s="9" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="D384" s="8" t="s">
         <v>418</v>
@@ -24364,13 +24361,13 @@
     </row>
     <row r="385" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A385" s="7" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="B385" s="7" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="C385" s="7" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="D385" s="7" t="s">
         <v>20</v>
@@ -24415,13 +24412,13 @@
     </row>
     <row r="386" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A386" s="7" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="B386" s="7" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="C386" s="7" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="D386" s="7" t="s">
         <v>418</v>
@@ -24430,7 +24427,7 @@
         <v>19</v>
       </c>
       <c r="F386" s="9" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G386" s="8" t="s">
         <v>1062</v>
@@ -24466,13 +24463,13 @@
     </row>
     <row r="387" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A387" s="7" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="B387" s="7" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="C387" s="7" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="D387" s="7" t="s">
         <v>62</v>
@@ -24481,7 +24478,7 @@
         <v>19</v>
       </c>
       <c r="F387" s="9" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G387" s="8" t="s">
         <v>1062</v>
@@ -24517,13 +24514,13 @@
     </row>
     <row r="388" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A388" s="7" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="B388" s="7" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="C388" s="7" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="D388" s="7" t="s">
         <v>62</v>
@@ -24568,13 +24565,13 @@
     </row>
     <row r="389" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A389" s="7" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="B389" s="7" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C389" s="7" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D389" s="7" t="s">
         <v>52</v>
@@ -24583,7 +24580,7 @@
         <v>19</v>
       </c>
       <c r="F389" s="9" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G389" s="8" t="s">
         <v>1062</v>
@@ -24619,13 +24616,13 @@
     </row>
     <row r="390" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A390" s="7" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="B390" s="7" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="C390" s="7" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="D390" s="10" t="s">
         <v>921</v>
@@ -24670,13 +24667,13 @@
     </row>
     <row r="391" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A391" s="6" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="B391" s="7" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C391" s="7" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="D391" s="7" t="s">
         <v>20</v>
@@ -24721,13 +24718,13 @@
     </row>
     <row r="392" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A392" s="6" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="B392" s="7" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="C392" s="7" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D392" s="7" t="s">
         <v>20</v>
@@ -24772,13 +24769,13 @@
     </row>
     <row r="393" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A393" s="6" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="B393" s="7" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="C393" s="7" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D393" s="7" t="s">
         <v>30</v>
@@ -24787,7 +24784,7 @@
         <v>19</v>
       </c>
       <c r="F393" s="7" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G393" s="7" t="s">
         <v>1062</v>
@@ -24823,13 +24820,13 @@
     </row>
     <row r="394" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A394" s="6" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="B394" s="7" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C394" s="7" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="D394" s="7" t="s">
         <v>30</v>
@@ -24838,7 +24835,7 @@
         <v>19</v>
       </c>
       <c r="F394" s="7" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G394" s="7" t="s">
         <v>1062</v>
@@ -24874,13 +24871,13 @@
     </row>
     <row r="395" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A395" s="6" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="B395" s="7" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C395" s="7" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="D395" s="7" t="s">
         <v>30</v>
@@ -24889,10 +24886,10 @@
         <v>19</v>
       </c>
       <c r="F395" s="7" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="G395" s="7" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H395" s="7" t="s">
         <v>13</v>
@@ -24925,13 +24922,13 @@
     </row>
     <row r="396" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A396" s="6" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="B396" s="7" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="C396" s="7" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="D396" s="7" t="s">
         <v>418</v>
@@ -24940,7 +24937,7 @@
         <v>19</v>
       </c>
       <c r="F396" s="7" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G396" s="7" t="s">
         <v>1062</v>
@@ -24976,13 +24973,13 @@
     </row>
     <row r="397" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A397" s="6" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="B397" s="7" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="C397" s="7" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="D397" s="7" t="s">
         <v>418</v>
@@ -25027,13 +25024,13 @@
     </row>
     <row r="398" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A398" s="6" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="B398" s="7" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="C398" s="7" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="D398" s="7" t="s">
         <v>418</v>
@@ -25042,7 +25039,7 @@
         <v>19</v>
       </c>
       <c r="F398" s="7" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G398" s="7" t="s">
         <v>1062</v>
@@ -25078,13 +25075,13 @@
     </row>
     <row r="399" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A399" s="7" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="B399" s="7" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="C399" s="7" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="D399" s="7" t="s">
         <v>418</v>
@@ -25129,13 +25126,13 @@
     </row>
     <row r="400" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A400" s="7" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="B400" s="7" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C400" s="7" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="D400" s="7" t="s">
         <v>418</v>
@@ -25144,7 +25141,7 @@
         <v>19</v>
       </c>
       <c r="F400" s="7" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G400" s="7" t="s">
         <v>1062</v>
@@ -25180,13 +25177,13 @@
     </row>
     <row r="401" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A401" s="7" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="B401" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="C401" s="7" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="D401" s="7" t="s">
         <v>52</v>
@@ -25195,7 +25192,7 @@
         <v>19</v>
       </c>
       <c r="F401" s="7" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G401" s="8" t="s">
         <v>1062</v>
@@ -25231,13 +25228,13 @@
     </row>
     <row r="402" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A402" s="7" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="B402" s="7" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="C402" s="10" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="D402" s="10" t="s">
         <v>701</v>
@@ -25246,7 +25243,7 @@
         <v>19</v>
       </c>
       <c r="F402" s="7" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G402" s="7" t="s">
         <v>1062</v>
@@ -25282,13 +25279,13 @@
     </row>
     <row r="403" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A403" s="11" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="B403" s="7" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="C403" s="10" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="D403" s="7" t="s">
         <v>127</v>
@@ -25297,7 +25294,7 @@
         <v>19</v>
       </c>
       <c r="F403" s="7" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G403" s="7" t="s">
         <v>1062</v>
@@ -25333,16 +25330,16 @@
     </row>
     <row r="404" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A404" s="6" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="B404" s="7" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="C404" s="7" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="D404" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="E404" s="8" t="s">
         <v>19</v>
@@ -25384,16 +25381,16 @@
     </row>
     <row r="405" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A405" s="6" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="B405" s="7" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="C405" s="7" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="D405" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="E405" s="8" t="s">
         <v>19</v>
@@ -25435,16 +25432,16 @@
     </row>
     <row r="406" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A406" s="6" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="B406" s="7" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="C406" s="7" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="D406" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="E406" s="8" t="s">
         <v>19</v>
@@ -25486,16 +25483,16 @@
     </row>
     <row r="407" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A407" s="6" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="B407" s="7" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="C407" s="7" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="D407" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="E407" s="8" t="s">
         <v>19</v>
@@ -25537,16 +25534,16 @@
     </row>
     <row r="408" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A408" s="6" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="B408" s="7" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="C408" s="7" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="D408" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="E408" s="8" t="s">
         <v>19</v>
@@ -25588,16 +25585,16 @@
     </row>
     <row r="409" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A409" s="6" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="B409" s="7" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="C409" s="7" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="D409" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="E409" s="8" t="s">
         <v>19</v>
@@ -25639,16 +25636,16 @@
     </row>
     <row r="410" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A410" s="6" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B410" s="7" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="C410" s="7" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D410" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="E410" s="8" t="s">
         <v>19</v>
@@ -25690,16 +25687,16 @@
     </row>
     <row r="411" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A411" s="6" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="B411" s="7" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="C411" s="7" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="D411" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="E411" s="8" t="s">
         <v>19</v>
@@ -25741,16 +25738,16 @@
     </row>
     <row r="412" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A412" s="6" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="B412" s="7" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="C412" s="7" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="D412" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="E412" s="8" t="s">
         <v>19</v>
@@ -25792,16 +25789,16 @@
     </row>
     <row r="413" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A413" s="6" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="B413" s="7" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="C413" s="7" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="D413" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="E413" s="8" t="s">
         <v>19</v>
@@ -25843,16 +25840,16 @@
     </row>
     <row r="414" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A414" s="6" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="B414" s="7" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="C414" s="7" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="D414" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="E414" s="8" t="s">
         <v>19</v>
@@ -25894,16 +25891,16 @@
     </row>
     <row r="415" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A415" s="6" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="B415" s="7" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="C415" s="7" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="D415" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="E415" s="8" t="s">
         <v>19</v>
@@ -25945,16 +25942,16 @@
     </row>
     <row r="416" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A416" s="6" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="B416" s="7" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="C416" s="7" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="D416" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="E416" s="8" t="s">
         <v>19</v>
@@ -25996,16 +25993,16 @@
     </row>
     <row r="417" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A417" s="6" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="B417" s="7" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="C417" s="7" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="D417" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="E417" s="8" t="s">
         <v>19</v>
@@ -26047,16 +26044,16 @@
     </row>
     <row r="418" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A418" s="6" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="B418" s="7" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="C418" s="7" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="D418" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="E418" s="8" t="s">
         <v>19</v>
@@ -26098,16 +26095,16 @@
     </row>
     <row r="419" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A419" s="6" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="B419" s="7" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="C419" s="7" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="D419" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="E419" s="8" t="s">
         <v>19</v>
@@ -26149,16 +26146,16 @@
     </row>
     <row r="420" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A420" s="6" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="B420" s="7" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="C420" s="7" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="D420" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="E420" s="8" t="s">
         <v>19</v>
@@ -26200,16 +26197,16 @@
     </row>
     <row r="421" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A421" s="6" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="B421" s="7" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="C421" s="7" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="D421" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="E421" s="8" t="s">
         <v>19</v>
@@ -26251,16 +26248,16 @@
     </row>
     <row r="422" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A422" s="6" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="B422" s="7" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="C422" s="7" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D422" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="E422" s="8" t="s">
         <v>19</v>
@@ -26302,16 +26299,16 @@
     </row>
     <row r="423" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A423" s="6" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="B423" s="7" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="C423" s="7" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="D423" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="E423" s="8" t="s">
         <v>19</v>
@@ -26353,16 +26350,16 @@
     </row>
     <row r="424" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A424" s="6" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="B424" s="7" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="C424" s="7" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="D424" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="E424" s="8" t="s">
         <v>19</v>
@@ -26404,16 +26401,16 @@
     </row>
     <row r="425" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A425" s="6" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="B425" s="7" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="C425" s="7" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="D425" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="E425" s="8" t="s">
         <v>19</v>
@@ -26455,16 +26452,16 @@
     </row>
     <row r="426" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A426" s="6" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="B426" s="7" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="C426" s="7" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="D426" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="E426" s="8" t="s">
         <v>19</v>
@@ -26506,16 +26503,16 @@
     </row>
     <row r="427" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A427" s="6" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="B427" s="7" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="C427" s="7" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="D427" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="E427" s="8" t="s">
         <v>19</v>
@@ -26557,16 +26554,16 @@
     </row>
     <row r="428" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A428" s="6" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="B428" s="7" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="C428" s="7" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="D428" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="E428" s="8" t="s">
         <v>19</v>
@@ -26608,16 +26605,16 @@
     </row>
     <row r="429" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A429" s="6" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="B429" s="7" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="C429" s="7" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="D429" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="E429" s="8" t="s">
         <v>19</v>
@@ -26659,16 +26656,16 @@
     </row>
     <row r="430" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A430" s="6" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="B430" s="7" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="C430" s="7" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="D430" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="E430" s="8" t="s">
         <v>19</v>
@@ -26710,16 +26707,16 @@
     </row>
     <row r="431" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A431" s="6" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="B431" s="7" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="C431" s="7" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="D431" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="E431" s="8" t="s">
         <v>19</v>
@@ -26761,16 +26758,16 @@
     </row>
     <row r="432" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A432" s="6" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="B432" s="7" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="C432" s="7" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="D432" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="E432" s="8" t="s">
         <v>19</v>
@@ -26812,16 +26809,16 @@
     </row>
     <row r="433" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A433" s="6" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="B433" s="7" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C433" s="7" t="s">
+        <v>1308</v>
+      </c>
+      <c r="D433" s="7" t="s">
         <v>1310</v>
-      </c>
-      <c r="C433" s="7" t="s">
-        <v>1309</v>
-      </c>
-      <c r="D433" s="7" t="s">
-        <v>1311</v>
       </c>
       <c r="E433" s="8" t="s">
         <v>19</v>
@@ -26863,22 +26860,22 @@
     </row>
     <row r="434" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A434" s="7" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="B434" s="7" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="C434" s="7" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D434" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="E434" s="8" t="s">
         <v>19</v>
       </c>
       <c r="F434" s="7" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G434" s="7" t="s">
         <v>1062</v>
@@ -26914,20 +26911,20 @@
     </row>
     <row r="435" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A435" s="7" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="B435" s="7" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="C435" s="10" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="D435" s="7"/>
       <c r="E435" s="8" t="s">
         <v>19</v>
       </c>
       <c r="F435" s="7" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G435" s="7" t="s">
         <v>1062</v>
@@ -26963,13 +26960,13 @@
     </row>
     <row r="436" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A436" s="7" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="B436" s="7" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="C436" s="10" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D436" s="7"/>
       <c r="E436" s="8" t="s">
@@ -27012,20 +27009,20 @@
     </row>
     <row r="437" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A437" s="7" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="B437" s="7" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="C437" s="10" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D437" s="7"/>
       <c r="E437" s="8" t="s">
         <v>19</v>
       </c>
       <c r="F437" s="7" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G437" s="7" t="s">
         <v>1062</v>
@@ -27061,20 +27058,20 @@
     </row>
     <row r="438" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A438" s="7" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="B438" s="7" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="C438" s="10" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D438" s="7"/>
       <c r="E438" s="8" t="s">
         <v>19</v>
       </c>
       <c r="F438" s="7" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G438" s="7" t="s">
         <v>1062</v>
@@ -27110,20 +27107,20 @@
     </row>
     <row r="439" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A439" s="7" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="B439" s="7" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="C439" s="10" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="D439" s="7"/>
       <c r="E439" s="8" t="s">
         <v>19</v>
       </c>
       <c r="F439" s="7" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G439" s="7" t="s">
         <v>1062</v>
@@ -34286,31 +34283,32 @@
       <c r="T763" s="7"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:T439" xr:uid="{AF55B7BF-85DC-4082-9A73-200B4D79A598}"/>
   <conditionalFormatting sqref="A1:B1">
     <cfRule type="duplicateValues" dxfId="15" priority="23"/>
     <cfRule type="duplicateValues" dxfId="14" priority="24"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="13" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="40"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C402">
-    <cfRule type="duplicateValues" dxfId="9" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C403">
-    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C435:C439">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1">
+    <cfRule type="duplicateValues" dxfId="3" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
+++ b/data/input/Fossil Replenishment/Fossil Replenishment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\Fossil Replenishment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54779161-AED0-4BA2-BA42-A6A0C770BA7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3FC17A6-4A18-4FA0-AAF6-C6C235E5985C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6662473D-6E1F-42FD-999B-28162E22D4B5}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$T$439</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3519" uniqueCount="1359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3715" uniqueCount="1443">
   <si>
     <t>In Transit PO</t>
   </si>
@@ -4114,6 +4114,258 @@
   </si>
   <si>
     <t>FBA79744</t>
+  </si>
+  <si>
+    <t>AX2467</t>
+  </si>
+  <si>
+    <t>AX2468</t>
+  </si>
+  <si>
+    <t>AX2652</t>
+  </si>
+  <si>
+    <t>AX4409</t>
+  </si>
+  <si>
+    <t>AX4410</t>
+  </si>
+  <si>
+    <t>DZ4715</t>
+  </si>
+  <si>
+    <t>DZ4724</t>
+  </si>
+  <si>
+    <t>CE1135</t>
+  </si>
+  <si>
+    <t>CE1136</t>
+  </si>
+  <si>
+    <t>CE1137</t>
+  </si>
+  <si>
+    <t>ES5503</t>
+  </si>
+  <si>
+    <t>ES5504</t>
+  </si>
+  <si>
+    <t>ES5505</t>
+  </si>
+  <si>
+    <t>ES5512</t>
+  </si>
+  <si>
+    <t>FS6180</t>
+  </si>
+  <si>
+    <t>FS6181</t>
+  </si>
+  <si>
+    <t>FS6182</t>
+  </si>
+  <si>
+    <t>FS6189</t>
+  </si>
+  <si>
+    <t>FS6194</t>
+  </si>
+  <si>
+    <t>FS6198SET</t>
+  </si>
+  <si>
+    <t>FS6199SET</t>
+  </si>
+  <si>
+    <t>MK7618</t>
+  </si>
+  <si>
+    <t>MK7619</t>
+  </si>
+  <si>
+    <t>MK7620</t>
+  </si>
+  <si>
+    <t>MK7621</t>
+  </si>
+  <si>
+    <t>MK7641</t>
+  </si>
+  <si>
+    <t>MK9273</t>
+  </si>
+  <si>
+    <t>MK9277</t>
+  </si>
+  <si>
+    <t>B0H1K1XJBK</t>
+  </si>
+  <si>
+    <t>B0H1JTMVMW</t>
+  </si>
+  <si>
+    <t>B0H1K4MHH4</t>
+  </si>
+  <si>
+    <t>B0H1JZFQRZ</t>
+  </si>
+  <si>
+    <t>B0H1K1W6GJ</t>
+  </si>
+  <si>
+    <t>B0H44QP75W</t>
+  </si>
+  <si>
+    <t>B0H44XPFRC</t>
+  </si>
+  <si>
+    <t>B0H8XG2F43</t>
+  </si>
+  <si>
+    <t>B0H8XXYKBC</t>
+  </si>
+  <si>
+    <t>B0H8Y4Z1KK</t>
+  </si>
+  <si>
+    <t>B0H1K56S6V</t>
+  </si>
+  <si>
+    <t>B0H1K216VW</t>
+  </si>
+  <si>
+    <t>B0H1JTL93N</t>
+  </si>
+  <si>
+    <t>B0H8Y38KKY</t>
+  </si>
+  <si>
+    <t>B0H1K2HBC9</t>
+  </si>
+  <si>
+    <t>B0H1KB3F39</t>
+  </si>
+  <si>
+    <t>B0H1K5RK6V</t>
+  </si>
+  <si>
+    <t>B0H8XZ9N1P</t>
+  </si>
+  <si>
+    <t>B0H1K4MHGJ</t>
+  </si>
+  <si>
+    <t>B0H1JY5HK3</t>
+  </si>
+  <si>
+    <t>B0H1JN7L2Z</t>
+  </si>
+  <si>
+    <t>B0H2ZX1W6F</t>
+  </si>
+  <si>
+    <t>B0H2ZVD5RS</t>
+  </si>
+  <si>
+    <t>B0H312FS95</t>
+  </si>
+  <si>
+    <t>B0H2ZX6LSV</t>
+  </si>
+  <si>
+    <t>B0H2ZMP3LX</t>
+  </si>
+  <si>
+    <t>B0H2ZZQDC9</t>
+  </si>
+  <si>
+    <t>B0H2ZPG58N</t>
+  </si>
+  <si>
+    <t>FBA80257</t>
+  </si>
+  <si>
+    <t>FBA80258</t>
+  </si>
+  <si>
+    <t>FBA80259</t>
+  </si>
+  <si>
+    <t>FBA80262</t>
+  </si>
+  <si>
+    <t>FBA80263</t>
+  </si>
+  <si>
+    <t>FBA80265</t>
+  </si>
+  <si>
+    <t>FBA80266</t>
+  </si>
+  <si>
+    <t>FBA80268</t>
+  </si>
+  <si>
+    <t>FBA80269</t>
+  </si>
+  <si>
+    <t>FBA80270</t>
+  </si>
+  <si>
+    <t>FBA80271</t>
+  </si>
+  <si>
+    <t>FBA80272</t>
+  </si>
+  <si>
+    <t>FBA80273</t>
+  </si>
+  <si>
+    <t>FBA80274</t>
+  </si>
+  <si>
+    <t>FBA80275</t>
+  </si>
+  <si>
+    <t>FBA80276</t>
+  </si>
+  <si>
+    <t>FBA80277</t>
+  </si>
+  <si>
+    <t>FBA80278</t>
+  </si>
+  <si>
+    <t>FBA80279</t>
+  </si>
+  <si>
+    <t>FBA80280</t>
+  </si>
+  <si>
+    <t>FBA80281</t>
+  </si>
+  <si>
+    <t>FBA80282</t>
+  </si>
+  <si>
+    <t>FBA80283</t>
+  </si>
+  <si>
+    <t>FBA80284</t>
+  </si>
+  <si>
+    <t>FBA80285</t>
+  </si>
+  <si>
+    <t>FBA80288</t>
+  </si>
+  <si>
+    <t>FBA80290</t>
+  </si>
+  <si>
+    <t>FBA80292</t>
   </si>
 </sst>
 </file>
@@ -4852,23 +5104,23 @@
         <v>12</v>
       </c>
       <c r="I2" s="8">
-        <v>702</v>
+        <v>724</v>
       </c>
       <c r="J2" s="8">
         <v>0</v>
       </c>
       <c r="K2" s="8">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="L2" s="8">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="M2" s="8">
         <f>I2+J2+K2+L2</f>
-        <v>798</v>
+        <v>892</v>
       </c>
       <c r="N2" s="8">
-        <v>2108</v>
+        <v>1992</v>
       </c>
       <c r="O2" s="8"/>
       <c r="P2" s="8"/>
@@ -4903,7 +5155,7 @@
         <v>12</v>
       </c>
       <c r="I3" s="8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J3" s="8">
         <v>0</v>
@@ -4916,7 +5168,7 @@
       </c>
       <c r="M3" s="8">
         <f t="shared" ref="M3:M66" si="0">I3+J3+K3+L3</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N3" s="8">
         <v>0</v>
@@ -4954,7 +5206,7 @@
         <v>12</v>
       </c>
       <c r="I4" s="8">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J4" s="8">
         <v>0</v>
@@ -4967,7 +5219,7 @@
       </c>
       <c r="M4" s="8">
         <f t="shared" si="0"/>
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="N4" s="8">
         <v>0</v>
@@ -5005,7 +5257,7 @@
         <v>12</v>
       </c>
       <c r="I5" s="8">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J5" s="8">
         <v>0</v>
@@ -5018,10 +5270,10 @@
       </c>
       <c r="M5" s="8">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N5" s="8">
-        <v>0</v>
+        <v>457</v>
       </c>
       <c r="O5" s="8"/>
       <c r="P5" s="8"/>
@@ -5056,23 +5308,23 @@
         <v>12</v>
       </c>
       <c r="I6" s="8">
-        <v>793</v>
+        <v>816</v>
       </c>
       <c r="J6" s="8">
         <v>0</v>
       </c>
       <c r="K6" s="8">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="L6" s="8">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="M6" s="8">
         <f t="shared" si="0"/>
-        <v>913</v>
+        <v>972</v>
       </c>
       <c r="N6" s="8">
-        <v>1370</v>
+        <v>2238</v>
       </c>
       <c r="O6" s="8"/>
       <c r="P6" s="8"/>
@@ -5107,7 +5359,7 @@
         <v>12</v>
       </c>
       <c r="I7" s="8">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="J7" s="8">
         <v>0</v>
@@ -5120,10 +5372,10 @@
       </c>
       <c r="M7" s="8">
         <f t="shared" si="0"/>
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="N7" s="8">
-        <v>434</v>
+        <v>398</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
@@ -5158,23 +5410,23 @@
         <v>12</v>
       </c>
       <c r="I8" s="8">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J8" s="8">
         <v>0</v>
       </c>
       <c r="K8" s="8">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L8" s="8">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M8" s="8">
         <f t="shared" si="0"/>
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="N8" s="8">
-        <v>437</v>
+        <v>457</v>
       </c>
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
@@ -5276,7 +5528,7 @@
         <v>0</v>
       </c>
       <c r="N10" s="8">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="O10" s="8"/>
       <c r="P10" s="8"/>
@@ -5311,7 +5563,7 @@
         <v>12</v>
       </c>
       <c r="I11" s="8">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="J11" s="8">
         <v>0</v>
@@ -5324,7 +5576,7 @@
       </c>
       <c r="M11" s="8">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="N11" s="8">
         <v>0</v>
@@ -5362,7 +5614,7 @@
         <v>12</v>
       </c>
       <c r="I12" s="8">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J12" s="8">
         <v>0</v>
@@ -5375,7 +5627,7 @@
       </c>
       <c r="M12" s="8">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="N12" s="8">
         <v>0</v>
@@ -5413,23 +5665,23 @@
         <v>12</v>
       </c>
       <c r="I13" s="8">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="J13" s="8">
         <v>0</v>
       </c>
       <c r="K13" s="8">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="L13" s="8">
         <v>0</v>
       </c>
       <c r="M13" s="8">
         <f t="shared" si="0"/>
-        <v>188</v>
+        <v>220</v>
       </c>
       <c r="N13" s="8">
-        <v>810</v>
+        <v>762</v>
       </c>
       <c r="O13" s="8"/>
       <c r="P13" s="8"/>
@@ -5464,23 +5716,23 @@
         <v>12</v>
       </c>
       <c r="I14" s="8">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J14" s="8">
         <v>0</v>
       </c>
       <c r="K14" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L14" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M14" s="8">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="N14" s="8">
-        <v>532</v>
+        <v>519</v>
       </c>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
@@ -5531,7 +5783,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="8">
-        <v>0</v>
+        <v>2116</v>
       </c>
       <c r="O15" s="8"/>
       <c r="P15" s="8"/>
@@ -5566,23 +5818,23 @@
         <v>12</v>
       </c>
       <c r="I16" s="8">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J16" s="8">
         <v>0</v>
       </c>
       <c r="K16" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" s="8">
         <v>0</v>
       </c>
       <c r="M16" s="8">
         <f t="shared" si="0"/>
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="N16" s="8">
-        <v>333</v>
+        <v>306</v>
       </c>
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
@@ -5617,7 +5869,7 @@
         <v>12</v>
       </c>
       <c r="I17" s="8">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="J17" s="8">
         <v>0</v>
@@ -5630,10 +5882,10 @@
       </c>
       <c r="M17" s="8">
         <f t="shared" si="0"/>
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="N17" s="8">
-        <v>251</v>
+        <v>294</v>
       </c>
       <c r="O17" s="8"/>
       <c r="P17" s="8"/>
@@ -5674,17 +5926,17 @@
         <v>0</v>
       </c>
       <c r="K18" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L18" s="8">
         <v>0</v>
       </c>
       <c r="M18" s="8">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N18" s="8">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="O18" s="8"/>
       <c r="P18" s="8"/>
@@ -5719,7 +5971,7 @@
         <v>13</v>
       </c>
       <c r="I19" s="8">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J19" s="8">
         <v>0</v>
@@ -5732,10 +5984,10 @@
       </c>
       <c r="M19" s="8">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="N19" s="8">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="O19" s="8"/>
       <c r="P19" s="8"/>
@@ -5770,7 +6022,7 @@
         <v>14</v>
       </c>
       <c r="I20" s="8">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J20" s="8">
         <v>0</v>
@@ -5783,7 +6035,7 @@
       </c>
       <c r="M20" s="8">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N20" s="8">
         <v>0</v>
@@ -5821,7 +6073,7 @@
         <v>13</v>
       </c>
       <c r="I21" s="8">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="J21" s="8">
         <v>0</v>
@@ -5834,7 +6086,7 @@
       </c>
       <c r="M21" s="8">
         <f t="shared" si="0"/>
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="N21" s="8">
         <v>0</v>
@@ -5872,7 +6124,7 @@
         <v>12</v>
       </c>
       <c r="I22" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" s="8">
         <v>0</v>
@@ -5885,7 +6137,7 @@
       </c>
       <c r="M22" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" s="8">
         <v>0</v>
@@ -5923,7 +6175,7 @@
         <v>12</v>
       </c>
       <c r="I23" s="8">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J23" s="8">
         <v>0</v>
@@ -5936,10 +6188,10 @@
       </c>
       <c r="M23" s="8">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N23" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" s="8"/>
       <c r="P23" s="8"/>
@@ -5990,7 +6242,7 @@
         <v>11</v>
       </c>
       <c r="N24" s="8">
-        <v>595</v>
+        <v>496</v>
       </c>
       <c r="O24" s="8"/>
       <c r="P24" s="8"/>
@@ -6076,13 +6328,13 @@
         <v>12</v>
       </c>
       <c r="I26" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J26" s="8">
         <v>0</v>
       </c>
       <c r="K26" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L26" s="8">
         <v>0</v>
@@ -6092,7 +6344,7 @@
         <v>19</v>
       </c>
       <c r="N26" s="8">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O26" s="8"/>
       <c r="P26" s="8"/>
@@ -6127,7 +6379,7 @@
         <v>12</v>
       </c>
       <c r="I27" s="8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J27" s="8">
         <v>0</v>
@@ -6140,10 +6392,10 @@
       </c>
       <c r="M27" s="8">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N27" s="8">
-        <v>667</v>
+        <v>652</v>
       </c>
       <c r="O27" s="8"/>
       <c r="P27" s="8"/>
@@ -6178,7 +6430,7 @@
         <v>12</v>
       </c>
       <c r="I28" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J28" s="8">
         <v>0</v>
@@ -6191,7 +6443,7 @@
       </c>
       <c r="M28" s="8">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N28" s="8">
         <v>0</v>
@@ -6229,7 +6481,7 @@
         <v>13</v>
       </c>
       <c r="I29" s="8">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J29" s="8">
         <v>0</v>
@@ -6242,7 +6494,7 @@
       </c>
       <c r="M29" s="8">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N29" s="8">
         <v>0</v>
@@ -6280,23 +6532,23 @@
         <v>14</v>
       </c>
       <c r="I30" s="8">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J30" s="8">
         <v>0</v>
       </c>
       <c r="K30" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L30" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M30" s="8">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N30" s="8">
-        <v>1184</v>
+        <v>1175</v>
       </c>
       <c r="O30" s="8"/>
       <c r="P30" s="8"/>
@@ -6382,7 +6634,7 @@
         <v>12</v>
       </c>
       <c r="I32" s="8">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J32" s="8">
         <v>0</v>
@@ -6395,10 +6647,10 @@
       </c>
       <c r="M32" s="8">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N32" s="8">
-        <v>499</v>
+        <v>482</v>
       </c>
       <c r="O32" s="8"/>
       <c r="P32" s="8"/>
@@ -6433,23 +6685,23 @@
         <v>12</v>
       </c>
       <c r="I33" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J33" s="8">
         <v>0</v>
       </c>
       <c r="K33" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L33" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" s="8">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="N33" s="8">
-        <v>631</v>
+        <v>620</v>
       </c>
       <c r="O33" s="8"/>
       <c r="P33" s="8"/>
@@ -6535,7 +6787,7 @@
         <v>12</v>
       </c>
       <c r="I35" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J35" s="8">
         <v>0</v>
@@ -6548,10 +6800,10 @@
       </c>
       <c r="M35" s="8">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N35" s="8">
-        <v>693</v>
+        <v>686</v>
       </c>
       <c r="O35" s="8"/>
       <c r="P35" s="8"/>
@@ -6602,7 +6854,7 @@
         <v>15</v>
       </c>
       <c r="N36" s="8">
-        <v>563</v>
+        <v>550</v>
       </c>
       <c r="O36" s="8"/>
       <c r="P36" s="8"/>
@@ -6637,7 +6889,7 @@
         <v>13</v>
       </c>
       <c r="I37" s="8">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J37" s="8">
         <v>0</v>
@@ -6650,10 +6902,10 @@
       </c>
       <c r="M37" s="8">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N37" s="8">
-        <v>769</v>
+        <v>711</v>
       </c>
       <c r="O37" s="8"/>
       <c r="P37" s="8"/>
@@ -6688,7 +6940,7 @@
         <v>12</v>
       </c>
       <c r="I38" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J38" s="8">
         <v>0</v>
@@ -6701,7 +6953,7 @@
       </c>
       <c r="M38" s="8">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N38" s="8">
         <v>0</v>
@@ -6739,23 +6991,23 @@
         <v>12</v>
       </c>
       <c r="I39" s="8">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J39" s="8">
         <v>0</v>
       </c>
       <c r="K39" s="8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L39" s="8">
         <v>0</v>
       </c>
       <c r="M39" s="8">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="N39" s="8">
-        <v>2597</v>
+        <v>2470</v>
       </c>
       <c r="O39" s="8"/>
       <c r="P39" s="8"/>
@@ -6790,7 +7042,7 @@
         <v>12</v>
       </c>
       <c r="I40" s="8">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J40" s="8">
         <v>0</v>
@@ -6803,7 +7055,7 @@
       </c>
       <c r="M40" s="8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N40" s="8">
         <v>0</v>
@@ -6841,7 +7093,7 @@
         <v>12</v>
       </c>
       <c r="I41" s="8">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J41" s="8">
         <v>0</v>
@@ -6854,10 +7106,10 @@
       </c>
       <c r="M41" s="8">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N41" s="8">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="O41" s="8"/>
       <c r="P41" s="8"/>
@@ -6892,23 +7144,23 @@
         <v>13</v>
       </c>
       <c r="I42" s="8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J42" s="8">
         <v>0</v>
       </c>
       <c r="K42" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L42" s="8">
         <v>0</v>
       </c>
       <c r="M42" s="8">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N42" s="8">
-        <v>861</v>
+        <v>798</v>
       </c>
       <c r="O42" s="8"/>
       <c r="P42" s="8"/>
@@ -6943,7 +7195,7 @@
         <v>12</v>
       </c>
       <c r="I43" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J43" s="8">
         <v>0</v>
@@ -6956,7 +7208,7 @@
       </c>
       <c r="M43" s="8">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N43" s="8">
         <v>0</v>
@@ -6994,23 +7246,23 @@
         <v>12</v>
       </c>
       <c r="I44" s="8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J44" s="8">
         <v>0</v>
       </c>
       <c r="K44" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L44" s="8">
         <v>0</v>
       </c>
       <c r="M44" s="8">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="N44" s="8">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="O44" s="8"/>
       <c r="P44" s="8"/>
@@ -7045,7 +7297,7 @@
         <v>12</v>
       </c>
       <c r="I45" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J45" s="8">
         <v>0</v>
@@ -7058,7 +7310,7 @@
       </c>
       <c r="M45" s="8">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N45" s="8">
         <v>809</v>
@@ -7096,7 +7348,7 @@
         <v>12</v>
       </c>
       <c r="I46" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J46" s="8">
         <v>0</v>
@@ -7109,10 +7361,10 @@
       </c>
       <c r="M46" s="8">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N46" s="8">
-        <v>0</v>
+        <v>286</v>
       </c>
       <c r="O46" s="8"/>
       <c r="P46" s="8"/>
@@ -7147,23 +7399,23 @@
         <v>13</v>
       </c>
       <c r="I47" s="8">
+        <v>3</v>
+      </c>
+      <c r="J47" s="8">
+        <v>0</v>
+      </c>
+      <c r="K47" s="8">
         <v>4</v>
-      </c>
-      <c r="J47" s="8">
-        <v>0</v>
-      </c>
-      <c r="K47" s="8">
-        <v>0</v>
       </c>
       <c r="L47" s="8">
         <v>0</v>
       </c>
       <c r="M47" s="8">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N47" s="8">
-        <v>516</v>
+        <v>456</v>
       </c>
       <c r="O47" s="8"/>
       <c r="P47" s="8"/>
@@ -7198,13 +7450,13 @@
         <v>12</v>
       </c>
       <c r="I48" s="8">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J48" s="8">
         <v>0</v>
       </c>
       <c r="K48" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L48" s="8">
         <v>0</v>
@@ -7214,7 +7466,7 @@
         <v>15</v>
       </c>
       <c r="N48" s="8">
-        <v>962</v>
+        <v>905</v>
       </c>
       <c r="O48" s="8"/>
       <c r="P48" s="8"/>
@@ -7255,17 +7507,17 @@
         <v>0</v>
       </c>
       <c r="K49" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L49" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49" s="8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N49" s="8">
-        <v>568</v>
+        <v>549</v>
       </c>
       <c r="O49" s="8"/>
       <c r="P49" s="8"/>
@@ -7316,7 +7568,7 @@
         <v>4</v>
       </c>
       <c r="N50" s="8">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="O50" s="8"/>
       <c r="P50" s="8"/>
@@ -7351,7 +7603,7 @@
         <v>12</v>
       </c>
       <c r="I51" s="8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J51" s="8">
         <v>0</v>
@@ -7364,10 +7616,10 @@
       </c>
       <c r="M51" s="8">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N51" s="8">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="O51" s="8"/>
       <c r="P51" s="8"/>
@@ -7402,7 +7654,7 @@
         <v>12</v>
       </c>
       <c r="I52" s="8">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="J52" s="8">
         <v>0</v>
@@ -7415,7 +7667,7 @@
       </c>
       <c r="M52" s="8">
         <f t="shared" si="0"/>
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="N52" s="8">
         <v>0</v>
@@ -7504,23 +7756,23 @@
         <v>12</v>
       </c>
       <c r="I54" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J54" s="8">
         <v>0</v>
       </c>
       <c r="K54" s="8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L54" s="8">
         <v>0</v>
       </c>
       <c r="M54" s="8">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N54" s="8">
-        <v>235</v>
+        <v>180</v>
       </c>
       <c r="O54" s="8"/>
       <c r="P54" s="8"/>
@@ -7555,7 +7807,7 @@
         <v>12</v>
       </c>
       <c r="I55" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J55" s="8">
         <v>0</v>
@@ -7568,7 +7820,7 @@
       </c>
       <c r="M55" s="8">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N55" s="8">
         <v>0</v>
@@ -7606,7 +7858,7 @@
         <v>14</v>
       </c>
       <c r="I56" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J56" s="8">
         <v>0</v>
@@ -7615,14 +7867,14 @@
         <v>1</v>
       </c>
       <c r="L56" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" s="8">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="N56" s="8">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O56" s="8"/>
       <c r="P56" s="8"/>
@@ -7657,23 +7909,23 @@
         <v>12</v>
       </c>
       <c r="I57" s="8">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J57" s="8">
         <v>0</v>
       </c>
       <c r="K57" s="8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L57" s="8">
         <v>0</v>
       </c>
       <c r="M57" s="8">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="N57" s="8">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O57" s="8"/>
       <c r="P57" s="8"/>
@@ -7708,23 +7960,23 @@
         <v>12</v>
       </c>
       <c r="I58" s="8">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J58" s="8">
         <v>0</v>
       </c>
       <c r="K58" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L58" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" s="8">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N58" s="8">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="O58" s="8"/>
       <c r="P58" s="8"/>
@@ -7759,7 +8011,7 @@
         <v>13</v>
       </c>
       <c r="I59" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J59" s="8">
         <v>0</v>
@@ -7772,7 +8024,7 @@
       </c>
       <c r="M59" s="8">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N59" s="8">
         <v>0</v>
@@ -7810,23 +8062,23 @@
         <v>12</v>
       </c>
       <c r="I60" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J60" s="8">
         <v>0</v>
       </c>
       <c r="K60" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" s="8">
         <v>0</v>
       </c>
       <c r="M60" s="8">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N60" s="8">
-        <v>322</v>
+        <v>296</v>
       </c>
       <c r="O60" s="8"/>
       <c r="P60" s="8"/>
@@ -7861,23 +8113,23 @@
         <v>12</v>
       </c>
       <c r="I61" s="8">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J61" s="8">
         <v>0</v>
       </c>
       <c r="K61" s="8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L61" s="8">
         <v>0</v>
       </c>
       <c r="M61" s="8">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="N61" s="8">
-        <v>472</v>
+        <v>392</v>
       </c>
       <c r="O61" s="8"/>
       <c r="P61" s="8"/>
@@ -7928,7 +8180,7 @@
         <v>7</v>
       </c>
       <c r="N62" s="8">
-        <v>250</v>
+        <v>529</v>
       </c>
       <c r="O62" s="8"/>
       <c r="P62" s="8"/>
@@ -7963,23 +8215,23 @@
         <v>12</v>
       </c>
       <c r="I63" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J63" s="8">
         <v>0</v>
       </c>
       <c r="K63" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L63" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M63" s="8">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="N63" s="8">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="O63" s="8"/>
       <c r="P63" s="8"/>
@@ -8014,7 +8266,7 @@
         <v>13</v>
       </c>
       <c r="I64" s="8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J64" s="8">
         <v>0</v>
@@ -8027,10 +8279,10 @@
       </c>
       <c r="M64" s="8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N64" s="8">
-        <v>643</v>
+        <v>557</v>
       </c>
       <c r="O64" s="8"/>
       <c r="P64" s="8"/>
@@ -8065,23 +8317,23 @@
         <v>12</v>
       </c>
       <c r="I65" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J65" s="8">
         <v>0</v>
       </c>
       <c r="K65" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L65" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M65" s="8">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N65" s="8">
-        <v>803</v>
+        <v>774</v>
       </c>
       <c r="O65" s="8"/>
       <c r="P65" s="8"/>
@@ -8116,7 +8368,7 @@
         <v>14</v>
       </c>
       <c r="I66" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J66" s="8">
         <v>0</v>
@@ -8129,7 +8381,7 @@
       </c>
       <c r="M66" s="8">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N66" s="8">
         <v>45</v>
@@ -8218,7 +8470,7 @@
         <v>12</v>
       </c>
       <c r="I68" s="8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J68" s="8">
         <v>0</v>
@@ -8231,10 +8483,10 @@
       </c>
       <c r="M68" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N68" s="8">
-        <v>852</v>
+        <v>839</v>
       </c>
       <c r="O68" s="8"/>
       <c r="P68" s="8"/>
@@ -8269,7 +8521,7 @@
         <v>12</v>
       </c>
       <c r="I69" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J69" s="8">
         <v>0</v>
@@ -8282,10 +8534,10 @@
       </c>
       <c r="M69" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N69" s="8">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="O69" s="8"/>
       <c r="P69" s="8"/>
@@ -8329,14 +8581,14 @@
         <v>0</v>
       </c>
       <c r="L70" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70" s="8">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N70" s="8">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="O70" s="8"/>
       <c r="P70" s="8"/>
@@ -8428,17 +8680,17 @@
         <v>0</v>
       </c>
       <c r="K72" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L72" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M72" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N72" s="8">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="O72" s="8"/>
       <c r="P72" s="8"/>
@@ -8473,23 +8725,23 @@
         <v>12</v>
       </c>
       <c r="I73" s="8">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J73" s="8">
         <v>0</v>
       </c>
       <c r="K73" s="8">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L73" s="8">
         <v>0</v>
       </c>
       <c r="M73" s="8">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N73" s="8">
-        <v>129</v>
+        <v>90</v>
       </c>
       <c r="O73" s="8"/>
       <c r="P73" s="8"/>
@@ -8530,17 +8782,17 @@
         <v>0</v>
       </c>
       <c r="K74" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L74" s="8">
         <v>0</v>
       </c>
       <c r="M74" s="8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N74" s="8">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="O74" s="8"/>
       <c r="P74" s="8"/>
@@ -8591,7 +8843,7 @@
         <v>8</v>
       </c>
       <c r="N75" s="8">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="O75" s="8"/>
       <c r="P75" s="8"/>
@@ -8632,17 +8884,17 @@
         <v>0</v>
       </c>
       <c r="K76" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M76" s="8">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="N76" s="8">
-        <v>873</v>
+        <v>863</v>
       </c>
       <c r="O76" s="8"/>
       <c r="P76" s="8"/>
@@ -8693,7 +8945,7 @@
         <v>5</v>
       </c>
       <c r="N77" s="8">
-        <v>305</v>
+        <v>282</v>
       </c>
       <c r="O77" s="8"/>
       <c r="P77" s="8"/>
@@ -8728,23 +8980,23 @@
         <v>12</v>
       </c>
       <c r="I78" s="8">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J78" s="8">
         <v>0</v>
       </c>
       <c r="K78" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L78" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M78" s="8">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N78" s="8">
-        <v>162</v>
+        <v>127</v>
       </c>
       <c r="O78" s="8"/>
       <c r="P78" s="8"/>
@@ -8830,7 +9082,7 @@
         <v>13</v>
       </c>
       <c r="I80" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J80" s="8">
         <v>0</v>
@@ -8843,10 +9095,10 @@
       </c>
       <c r="M80" s="8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N80" s="8">
-        <v>185</v>
+        <v>157</v>
       </c>
       <c r="O80" s="8"/>
       <c r="P80" s="8"/>
@@ -8932,7 +9184,7 @@
         <v>15</v>
       </c>
       <c r="I82" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J82" s="8">
         <v>0</v>
@@ -8945,10 +9197,10 @@
       </c>
       <c r="M82" s="8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N82" s="8">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="O82" s="8"/>
       <c r="P82" s="8"/>
@@ -8999,7 +9251,7 @@
         <v>6</v>
       </c>
       <c r="N83" s="8">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="O83" s="8"/>
       <c r="P83" s="8"/>
@@ -9034,7 +9286,7 @@
         <v>13</v>
       </c>
       <c r="I84" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J84" s="8">
         <v>0</v>
@@ -9047,7 +9299,7 @@
       </c>
       <c r="M84" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N84" s="8">
         <v>0</v>
@@ -9085,20 +9337,20 @@
         <v>14</v>
       </c>
       <c r="I85" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J85" s="8">
         <v>0</v>
       </c>
       <c r="K85" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L85" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M85" s="8">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N85" s="8">
         <v>518</v>
@@ -9136,7 +9388,7 @@
         <v>12</v>
       </c>
       <c r="I86" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J86" s="8">
         <v>0</v>
@@ -9149,7 +9401,7 @@
       </c>
       <c r="M86" s="8">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N86" s="8">
         <v>0</v>
@@ -9187,7 +9439,7 @@
         <v>13</v>
       </c>
       <c r="I87" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J87" s="8">
         <v>0</v>
@@ -9200,7 +9452,7 @@
       </c>
       <c r="M87" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N87" s="8">
         <v>0</v>
@@ -9254,7 +9506,7 @@
         <v>11</v>
       </c>
       <c r="N88" s="8">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="O88" s="8"/>
       <c r="P88" s="8"/>
@@ -9289,7 +9541,7 @@
         <v>12</v>
       </c>
       <c r="I89" s="8">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J89" s="8">
         <v>0</v>
@@ -9302,10 +9554,10 @@
       </c>
       <c r="M89" s="8">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="N89" s="8">
-        <v>0</v>
+        <v>296</v>
       </c>
       <c r="O89" s="8"/>
       <c r="P89" s="8"/>
@@ -9397,17 +9649,17 @@
         <v>0</v>
       </c>
       <c r="K91" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L91" s="8">
         <v>0</v>
       </c>
       <c r="M91" s="8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N91" s="8">
-        <v>839</v>
+        <v>817</v>
       </c>
       <c r="O91" s="8"/>
       <c r="P91" s="8"/>
@@ -9442,13 +9694,13 @@
         <v>12</v>
       </c>
       <c r="I92" s="8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J92" s="8">
         <v>0</v>
       </c>
       <c r="K92" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L92" s="8">
         <v>0</v>
@@ -9458,7 +9710,7 @@
         <v>7</v>
       </c>
       <c r="N92" s="8">
-        <v>0</v>
+        <v>552</v>
       </c>
       <c r="O92" s="8"/>
       <c r="P92" s="8"/>
@@ -9493,7 +9745,7 @@
         <v>13</v>
       </c>
       <c r="I93" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J93" s="8">
         <v>0</v>
@@ -9506,7 +9758,7 @@
       </c>
       <c r="M93" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N93" s="8">
         <v>0</v>
@@ -9611,7 +9863,7 @@
         <v>6</v>
       </c>
       <c r="N95" s="8">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="O95" s="8"/>
       <c r="P95" s="8"/>
@@ -9662,7 +9914,7 @@
         <v>6</v>
       </c>
       <c r="N96" s="8">
-        <v>162</v>
+        <v>136</v>
       </c>
       <c r="O96" s="8"/>
       <c r="P96" s="8"/>
@@ -9697,23 +9949,23 @@
         <v>14</v>
       </c>
       <c r="I97" s="8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J97" s="8">
         <v>0</v>
       </c>
       <c r="K97" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L97" s="8">
         <v>0</v>
       </c>
       <c r="M97" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N97" s="8">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="O97" s="8"/>
       <c r="P97" s="8"/>
@@ -9850,7 +10102,7 @@
         <v>15</v>
       </c>
       <c r="I100" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J100" s="8">
         <v>0</v>
@@ -9863,7 +10115,7 @@
       </c>
       <c r="M100" s="8">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N100" s="8">
         <v>0</v>
@@ -9901,13 +10153,13 @@
         <v>15</v>
       </c>
       <c r="I101" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J101" s="8">
         <v>0</v>
       </c>
       <c r="K101" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L101" s="8">
         <v>0</v>
@@ -9917,7 +10169,7 @@
         <v>2</v>
       </c>
       <c r="N101" s="8">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="O101" s="8"/>
       <c r="P101" s="8"/>
@@ -9952,23 +10204,23 @@
         <v>14</v>
       </c>
       <c r="I102" s="8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J102" s="8">
         <v>0</v>
       </c>
       <c r="K102" s="8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L102" s="8">
         <v>0</v>
       </c>
       <c r="M102" s="8">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="N102" s="8">
-        <v>359</v>
+        <v>296</v>
       </c>
       <c r="O102" s="8"/>
       <c r="P102" s="8"/>
@@ -10003,7 +10255,7 @@
         <v>15</v>
       </c>
       <c r="I103" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J103" s="8">
         <v>0</v>
@@ -10016,10 +10268,10 @@
       </c>
       <c r="M103" s="8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N103" s="8">
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="O103" s="8"/>
       <c r="P103" s="8"/>
@@ -10105,7 +10357,7 @@
         <v>12</v>
       </c>
       <c r="I105" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J105" s="8">
         <v>0</v>
@@ -10118,10 +10370,10 @@
       </c>
       <c r="M105" s="8">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N105" s="8">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="O105" s="8"/>
       <c r="P105" s="8"/>
@@ -10258,7 +10510,7 @@
         <v>15</v>
       </c>
       <c r="I108" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J108" s="8">
         <v>0</v>
@@ -10271,7 +10523,7 @@
       </c>
       <c r="M108" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N108" s="8">
         <v>0</v>
@@ -10360,7 +10612,7 @@
         <v>13</v>
       </c>
       <c r="I110" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J110" s="8">
         <v>0</v>
@@ -10373,10 +10625,10 @@
       </c>
       <c r="M110" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N110" s="8">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="O110" s="8"/>
       <c r="P110" s="8"/>
@@ -10462,7 +10714,7 @@
         <v>12</v>
       </c>
       <c r="I112" s="8">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="J112" s="8">
         <v>0</v>
@@ -10471,11 +10723,11 @@
         <v>0</v>
       </c>
       <c r="L112" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M112" s="8">
         <f t="shared" si="1"/>
-        <v>201</v>
+        <v>182</v>
       </c>
       <c r="N112" s="8">
         <v>0</v>
@@ -10513,23 +10765,23 @@
         <v>12</v>
       </c>
       <c r="I113" s="8">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J113" s="8">
         <v>0</v>
       </c>
       <c r="K113" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L113" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M113" s="8">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N113" s="8">
-        <v>616</v>
+        <v>601</v>
       </c>
       <c r="O113" s="8"/>
       <c r="P113" s="8"/>
@@ -10580,7 +10832,7 @@
         <v>6</v>
       </c>
       <c r="N114" s="8">
-        <v>221</v>
+        <v>199</v>
       </c>
       <c r="O114" s="8"/>
       <c r="P114" s="8"/>
@@ -10631,7 +10883,7 @@
         <v>9</v>
       </c>
       <c r="N115" s="8">
-        <v>476</v>
+        <v>460</v>
       </c>
       <c r="O115" s="8"/>
       <c r="P115" s="8"/>
@@ -10672,17 +10924,17 @@
         <v>0</v>
       </c>
       <c r="K116" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L116" s="8">
         <v>0</v>
       </c>
       <c r="M116" s="8">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N116" s="8">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="O116" s="8"/>
       <c r="P116" s="8"/>
@@ -10717,23 +10969,23 @@
         <v>12</v>
       </c>
       <c r="I117" s="8">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J117" s="8">
         <v>0</v>
       </c>
       <c r="K117" s="8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L117" s="8">
         <v>0</v>
       </c>
       <c r="M117" s="8">
         <f t="shared" si="1"/>
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="N117" s="8">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="O117" s="8"/>
       <c r="P117" s="8"/>
@@ -10784,7 +11036,7 @@
         <v>6</v>
       </c>
       <c r="N118" s="8">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="O118" s="8"/>
       <c r="P118" s="8"/>
@@ -10819,7 +11071,7 @@
         <v>14</v>
       </c>
       <c r="I119" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J119" s="8">
         <v>0</v>
@@ -10832,10 +11084,10 @@
       </c>
       <c r="M119" s="8">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N119" s="8">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="O119" s="8"/>
       <c r="P119" s="8"/>
@@ -10870,7 +11122,7 @@
         <v>14</v>
       </c>
       <c r="I120" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J120" s="8">
         <v>0</v>
@@ -10883,7 +11135,7 @@
       </c>
       <c r="M120" s="8">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N120" s="8">
         <v>0</v>
@@ -10937,7 +11189,7 @@
         <v>7</v>
       </c>
       <c r="N121" s="8">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O121" s="8"/>
       <c r="P121" s="8"/>
@@ -10988,7 +11240,7 @@
         <v>3</v>
       </c>
       <c r="N122" s="8">
-        <v>871</v>
+        <v>848</v>
       </c>
       <c r="O122" s="8"/>
       <c r="P122" s="8"/>
@@ -11039,7 +11291,7 @@
         <v>3</v>
       </c>
       <c r="N123" s="8">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="O123" s="8"/>
       <c r="P123" s="8"/>
@@ -11125,7 +11377,7 @@
         <v>13</v>
       </c>
       <c r="I125" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J125" s="8">
         <v>0</v>
@@ -11138,7 +11390,7 @@
       </c>
       <c r="M125" s="8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N125" s="8">
         <v>0</v>
@@ -11227,7 +11479,7 @@
         <v>12</v>
       </c>
       <c r="I127" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J127" s="8">
         <v>0</v>
@@ -11240,7 +11492,7 @@
       </c>
       <c r="M127" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N127" s="8">
         <v>0</v>
@@ -11294,7 +11546,7 @@
         <v>3</v>
       </c>
       <c r="N128" s="8">
-        <v>793</v>
+        <v>786</v>
       </c>
       <c r="O128" s="8"/>
       <c r="P128" s="8"/>
@@ -11386,17 +11638,17 @@
         <v>0</v>
       </c>
       <c r="K130" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L130" s="8">
         <v>0</v>
       </c>
       <c r="M130" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N130" s="8">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="O130" s="8"/>
       <c r="P130" s="8"/>
@@ -11431,23 +11683,23 @@
         <v>14</v>
       </c>
       <c r="I131" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J131" s="8">
         <v>0</v>
       </c>
       <c r="K131" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L131" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M131" s="8">
         <f t="shared" ref="M131:M194" si="2">I131+J131+K131+L131</f>
         <v>2</v>
       </c>
       <c r="N131" s="8">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="O131" s="8"/>
       <c r="P131" s="8"/>
@@ -11482,7 +11734,7 @@
         <v>12</v>
       </c>
       <c r="I132" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J132" s="8">
         <v>0</v>
@@ -11495,10 +11747,10 @@
       </c>
       <c r="M132" s="8">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N132" s="8">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="O132" s="8"/>
       <c r="P132" s="8"/>
@@ -11533,20 +11785,20 @@
         <v>12</v>
       </c>
       <c r="I133" s="8">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J133" s="8">
         <v>0</v>
       </c>
       <c r="K133" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L133" s="8">
         <v>0</v>
       </c>
       <c r="M133" s="8">
         <f t="shared" si="2"/>
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="N133" s="8">
         <v>0</v>
@@ -11584,7 +11836,7 @@
         <v>15</v>
       </c>
       <c r="I134" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J134" s="8">
         <v>0</v>
@@ -11597,10 +11849,10 @@
       </c>
       <c r="M134" s="8">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N134" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O134" s="8"/>
       <c r="P134" s="8"/>
@@ -11641,17 +11893,17 @@
         <v>0</v>
       </c>
       <c r="K135" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L135" s="8">
         <v>0</v>
       </c>
       <c r="M135" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N135" s="8">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O135" s="8"/>
       <c r="P135" s="8"/>
@@ -11686,23 +11938,23 @@
         <v>14</v>
       </c>
       <c r="I136" s="8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J136" s="8">
         <v>0</v>
       </c>
       <c r="K136" s="8">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L136" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M136" s="8">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N136" s="8">
-        <v>251</v>
+        <v>224</v>
       </c>
       <c r="O136" s="8"/>
       <c r="P136" s="8"/>
@@ -11753,7 +12005,7 @@
         <v>6</v>
       </c>
       <c r="N137" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O137" s="8"/>
       <c r="P137" s="8"/>
@@ -11794,14 +12046,14 @@
         <v>0</v>
       </c>
       <c r="K138" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L138" s="8">
         <v>0</v>
       </c>
       <c r="M138" s="8">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N138" s="8">
         <v>967</v>
@@ -11839,23 +12091,23 @@
         <v>15</v>
       </c>
       <c r="I139" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J139" s="8">
         <v>0</v>
       </c>
       <c r="K139" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L139" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M139" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N139" s="8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O139" s="8"/>
       <c r="P139" s="8"/>
@@ -11890,7 +12142,7 @@
         <v>15</v>
       </c>
       <c r="I140" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J140" s="8">
         <v>0</v>
@@ -11903,10 +12155,10 @@
       </c>
       <c r="M140" s="8">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N140" s="8">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="O140" s="8"/>
       <c r="P140" s="8"/>
@@ -12008,7 +12260,7 @@
         <v>2</v>
       </c>
       <c r="N142" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O142" s="8"/>
       <c r="P142" s="8"/>
@@ -12161,7 +12413,7 @@
         <v>4</v>
       </c>
       <c r="N145" s="8">
-        <v>752</v>
+        <v>742</v>
       </c>
       <c r="O145" s="8"/>
       <c r="P145" s="8"/>
@@ -12196,7 +12448,7 @@
         <v>16</v>
       </c>
       <c r="I146" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J146" s="8">
         <v>0</v>
@@ -12209,7 +12461,7 @@
       </c>
       <c r="M146" s="8">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N146" s="8">
         <v>0</v>
@@ -12253,17 +12505,17 @@
         <v>0</v>
       </c>
       <c r="K147" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L147" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M147" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N147" s="8">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="O147" s="8"/>
       <c r="P147" s="8"/>
@@ -12304,17 +12556,17 @@
         <v>0</v>
       </c>
       <c r="K148" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L148" s="8">
         <v>0</v>
       </c>
       <c r="M148" s="8">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N148" s="8">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="O148" s="8"/>
       <c r="P148" s="8"/>
@@ -12349,23 +12601,23 @@
         <v>12</v>
       </c>
       <c r="I149" s="8">
+        <v>4</v>
+      </c>
+      <c r="J149" s="8">
+        <v>0</v>
+      </c>
+      <c r="K149" s="8">
         <v>2</v>
       </c>
-      <c r="J149" s="8">
-        <v>0</v>
-      </c>
-      <c r="K149" s="8">
-        <v>4</v>
-      </c>
       <c r="L149" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M149" s="8">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N149" s="8">
-        <v>108</v>
+        <v>46</v>
       </c>
       <c r="O149" s="8"/>
       <c r="P149" s="8"/>
@@ -12400,13 +12652,13 @@
         <v>12</v>
       </c>
       <c r="I150" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J150" s="8">
         <v>0</v>
       </c>
       <c r="K150" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L150" s="8">
         <v>0</v>
@@ -12416,7 +12668,7 @@
         <v>2</v>
       </c>
       <c r="N150" s="8">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="O150" s="8"/>
       <c r="P150" s="8"/>
@@ -12451,7 +12703,7 @@
         <v>13</v>
       </c>
       <c r="I151" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J151" s="8">
         <v>0</v>
@@ -12464,10 +12716,10 @@
       </c>
       <c r="M151" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N151" s="8">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="O151" s="8"/>
       <c r="P151" s="8"/>
@@ -12620,7 +12872,7 @@
         <v>5</v>
       </c>
       <c r="N154" s="8">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="O154" s="8"/>
       <c r="P154" s="8"/>
@@ -12706,7 +12958,7 @@
         <v>15</v>
       </c>
       <c r="I156" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J156" s="8">
         <v>0</v>
@@ -12719,7 +12971,7 @@
       </c>
       <c r="M156" s="8">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N156" s="8">
         <v>0</v>
@@ -12859,7 +13111,7 @@
         <v>15</v>
       </c>
       <c r="I159" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J159" s="8">
         <v>0</v>
@@ -12872,7 +13124,7 @@
       </c>
       <c r="M159" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N159" s="8">
         <v>0</v>
@@ -12926,7 +13178,7 @@
         <v>4</v>
       </c>
       <c r="N160" s="8">
-        <v>0</v>
+        <v>438</v>
       </c>
       <c r="O160" s="8"/>
       <c r="P160" s="8"/>
@@ -12977,7 +13229,7 @@
         <v>5</v>
       </c>
       <c r="N161" s="8">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="O161" s="8"/>
       <c r="P161" s="8"/>
@@ -13012,23 +13264,23 @@
         <v>13</v>
       </c>
       <c r="I162" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J162" s="8">
         <v>0</v>
       </c>
       <c r="K162" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L162" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M162" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N162" s="8">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="O162" s="8"/>
       <c r="P162" s="8"/>
@@ -13114,7 +13366,7 @@
         <v>16</v>
       </c>
       <c r="I164" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J164" s="8">
         <v>0</v>
@@ -13127,7 +13379,7 @@
       </c>
       <c r="M164" s="8">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N164" s="8">
         <v>13</v>
@@ -13181,7 +13433,7 @@
         <v>9</v>
       </c>
       <c r="N165" s="8">
-        <v>1045</v>
+        <v>1028</v>
       </c>
       <c r="O165" s="8"/>
       <c r="P165" s="8"/>
@@ -13324,17 +13576,17 @@
         <v>0</v>
       </c>
       <c r="K168" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L168" s="8">
         <v>0</v>
       </c>
       <c r="M168" s="8">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N168" s="8">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="O168" s="8"/>
       <c r="P168" s="8"/>
@@ -13573,13 +13825,13 @@
         <v>14</v>
       </c>
       <c r="I173" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J173" s="8">
         <v>0</v>
       </c>
       <c r="K173" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L173" s="8">
         <v>0</v>
@@ -13589,7 +13841,7 @@
         <v>2</v>
       </c>
       <c r="N173" s="8">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="O173" s="8"/>
       <c r="P173" s="8"/>
@@ -13895,7 +14147,7 @@
         <v>2</v>
       </c>
       <c r="N179" s="8">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="O179" s="8"/>
       <c r="P179" s="8"/>
@@ -13936,17 +14188,17 @@
         <v>0</v>
       </c>
       <c r="K180" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L180" s="8">
         <v>0</v>
       </c>
       <c r="M180" s="8">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N180" s="8">
-        <v>329</v>
+        <v>310</v>
       </c>
       <c r="O180" s="8"/>
       <c r="P180" s="8"/>
@@ -13997,7 +14249,7 @@
         <v>3</v>
       </c>
       <c r="N181" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O181" s="8"/>
       <c r="P181" s="8"/>
@@ -14083,23 +14335,23 @@
         <v>12</v>
       </c>
       <c r="I183" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J183" s="8">
         <v>0</v>
       </c>
       <c r="K183" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L183" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M183" s="8">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N183" s="8">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="O183" s="8"/>
       <c r="P183" s="8"/>
@@ -14185,23 +14437,23 @@
         <v>12</v>
       </c>
       <c r="I185" s="8">
-        <v>321</v>
+        <v>292</v>
       </c>
       <c r="J185" s="8">
         <v>0</v>
       </c>
       <c r="K185" s="8">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L185" s="8">
         <v>0</v>
       </c>
       <c r="M185" s="8">
         <f t="shared" si="2"/>
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="N185" s="8">
-        <v>1659</v>
+        <v>1635</v>
       </c>
       <c r="O185" s="8"/>
       <c r="P185" s="8"/>
@@ -14252,7 +14504,7 @@
         <v>6</v>
       </c>
       <c r="N186" s="8">
-        <v>660</v>
+        <v>1100</v>
       </c>
       <c r="O186" s="8"/>
       <c r="P186" s="8"/>
@@ -14303,7 +14555,7 @@
         <v>2</v>
       </c>
       <c r="N187" s="8">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="O187" s="8"/>
       <c r="P187" s="8"/>
@@ -14456,7 +14708,7 @@
         <v>16</v>
       </c>
       <c r="N190" s="8">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O190" s="8"/>
       <c r="P190" s="8"/>
@@ -14491,23 +14743,23 @@
         <v>12</v>
       </c>
       <c r="I191" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J191" s="8">
         <v>0</v>
       </c>
       <c r="K191" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L191" s="8">
         <v>0</v>
       </c>
       <c r="M191" s="8">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N191" s="8">
-        <v>486</v>
+        <v>463</v>
       </c>
       <c r="O191" s="8"/>
       <c r="P191" s="8"/>
@@ -14609,7 +14861,7 @@
         <v>3</v>
       </c>
       <c r="N193" s="8">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="O193" s="8"/>
       <c r="P193" s="8"/>
@@ -14644,13 +14896,13 @@
         <v>15</v>
       </c>
       <c r="I194" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J194" s="8">
         <v>0</v>
       </c>
       <c r="K194" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L194" s="8">
         <v>0</v>
@@ -14660,7 +14912,7 @@
         <v>6</v>
       </c>
       <c r="N194" s="8">
-        <v>264</v>
+        <v>203</v>
       </c>
       <c r="O194" s="8"/>
       <c r="P194" s="8"/>
@@ -14813,7 +15065,7 @@
         <v>5</v>
       </c>
       <c r="N197" s="8">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="O197" s="8"/>
       <c r="P197" s="8"/>
@@ -15068,7 +15320,7 @@
         <v>2</v>
       </c>
       <c r="N202" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O202" s="8"/>
       <c r="P202" s="8"/>
@@ -15103,7 +15355,7 @@
         <v>15</v>
       </c>
       <c r="I203" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J203" s="8">
         <v>0</v>
@@ -15116,10 +15368,10 @@
       </c>
       <c r="M203" s="8">
         <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="N203" s="8">
         <v>3</v>
-      </c>
-      <c r="N203" s="8">
-        <v>0</v>
       </c>
       <c r="O203" s="8"/>
       <c r="P203" s="8"/>
@@ -15205,7 +15457,7 @@
         <v>16</v>
       </c>
       <c r="I205" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J205" s="8">
         <v>0</v>
@@ -15218,7 +15470,7 @@
       </c>
       <c r="M205" s="8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N205" s="8">
         <v>0</v>
@@ -15313,17 +15565,17 @@
         <v>0</v>
       </c>
       <c r="K207" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L207" s="8">
         <v>0</v>
       </c>
       <c r="M207" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N207" s="8">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O207" s="8"/>
       <c r="P207" s="8"/>
@@ -15358,23 +15610,23 @@
         <v>14</v>
       </c>
       <c r="I208" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J208" s="8">
         <v>0</v>
       </c>
       <c r="K208" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L208" s="8">
         <v>0</v>
       </c>
       <c r="M208" s="8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N208" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O208" s="8"/>
       <c r="P208" s="8"/>
@@ -15511,23 +15763,23 @@
         <v>12</v>
       </c>
       <c r="I211" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J211" s="8">
         <v>0</v>
       </c>
       <c r="K211" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L211" s="8">
         <v>0</v>
       </c>
       <c r="M211" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N211" s="8">
-        <v>690</v>
+        <v>649</v>
       </c>
       <c r="O211" s="8"/>
       <c r="P211" s="8"/>
@@ -15562,7 +15814,7 @@
         <v>14</v>
       </c>
       <c r="I212" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J212" s="8">
         <v>0</v>
@@ -15575,7 +15827,7 @@
       </c>
       <c r="M212" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N212" s="8">
         <v>0</v>
@@ -15664,13 +15916,13 @@
         <v>14</v>
       </c>
       <c r="I214" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J214" s="8">
         <v>0</v>
       </c>
       <c r="K214" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L214" s="8">
         <v>0</v>
@@ -15680,7 +15932,7 @@
         <v>4</v>
       </c>
       <c r="N214" s="8">
-        <v>427</v>
+        <v>391</v>
       </c>
       <c r="O214" s="8"/>
       <c r="P214" s="8"/>
@@ -15721,17 +15973,17 @@
         <v>0</v>
       </c>
       <c r="K215" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L215" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M215" s="8">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="N215" s="8">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="O215" s="8"/>
       <c r="P215" s="8"/>
@@ -15833,7 +16085,7 @@
         <v>4</v>
       </c>
       <c r="N217" s="8">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="O217" s="8"/>
       <c r="P217" s="8"/>
@@ -15884,7 +16136,7 @@
         <v>6</v>
       </c>
       <c r="N218" s="8">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="O218" s="8"/>
       <c r="P218" s="8"/>
@@ -15919,7 +16171,7 @@
         <v>13</v>
       </c>
       <c r="I219" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J219" s="8">
         <v>0</v>
@@ -15932,10 +16184,10 @@
       </c>
       <c r="M219" s="8">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N219" s="8">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="O219" s="8"/>
       <c r="P219" s="8"/>
@@ -16037,7 +16289,7 @@
         <v>4</v>
       </c>
       <c r="N221" s="8">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O221" s="8"/>
       <c r="P221" s="8"/>
@@ -16088,7 +16340,7 @@
         <v>2</v>
       </c>
       <c r="N222" s="8">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="O222" s="8"/>
       <c r="P222" s="8"/>
@@ -16123,13 +16375,13 @@
         <v>15</v>
       </c>
       <c r="I223" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J223" s="8">
         <v>0</v>
       </c>
       <c r="K223" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L223" s="8">
         <v>0</v>
@@ -16139,7 +16391,7 @@
         <v>4</v>
       </c>
       <c r="N223" s="8">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="O223" s="8"/>
       <c r="P223" s="8"/>
@@ -16241,7 +16493,7 @@
         <v>3</v>
       </c>
       <c r="N225" s="8">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="O225" s="8"/>
       <c r="P225" s="8"/>
@@ -16435,17 +16687,17 @@
         <v>0</v>
       </c>
       <c r="K229" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L229" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M229" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N229" s="8">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="O229" s="8"/>
       <c r="P229" s="8"/>
@@ -16496,7 +16748,7 @@
         <v>4</v>
       </c>
       <c r="N230" s="8">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="O230" s="8"/>
       <c r="P230" s="8"/>
@@ -16582,23 +16834,23 @@
         <v>12</v>
       </c>
       <c r="I232" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J232" s="8">
         <v>0</v>
       </c>
       <c r="K232" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L232" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M232" s="8">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N232" s="8">
-        <v>459</v>
+        <v>441</v>
       </c>
       <c r="O232" s="8"/>
       <c r="P232" s="8"/>
@@ -16633,13 +16885,13 @@
         <v>15</v>
       </c>
       <c r="I233" s="8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J233" s="8">
         <v>0</v>
       </c>
       <c r="K233" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L233" s="8">
         <v>0</v>
@@ -16649,7 +16901,7 @@
         <v>9</v>
       </c>
       <c r="N233" s="8">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="O233" s="8"/>
       <c r="P233" s="8"/>
@@ -16690,17 +16942,17 @@
         <v>0</v>
       </c>
       <c r="K234" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L234" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M234" s="8">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="N234" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O234" s="8"/>
       <c r="P234" s="8"/>
@@ -16735,13 +16987,13 @@
         <v>14</v>
       </c>
       <c r="I235" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J235" s="8">
         <v>0</v>
       </c>
       <c r="K235" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L235" s="8">
         <v>0</v>
@@ -16751,7 +17003,7 @@
         <v>2</v>
       </c>
       <c r="N235" s="8">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O235" s="8"/>
       <c r="P235" s="8"/>
@@ -16843,14 +17095,14 @@
         <v>0</v>
       </c>
       <c r="K237" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L237" s="8">
         <v>0</v>
       </c>
       <c r="M237" s="8">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N237" s="8">
         <v>762</v>
@@ -16894,17 +17146,17 @@
         <v>0</v>
       </c>
       <c r="K238" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L238" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M238" s="8">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="N238" s="8">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="O238" s="8"/>
       <c r="P238" s="8"/>
@@ -16955,7 +17207,7 @@
         <v>3</v>
       </c>
       <c r="N239" s="8">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="O239" s="8"/>
       <c r="P239" s="8"/>
@@ -16990,13 +17242,13 @@
         <v>13</v>
       </c>
       <c r="I240" s="8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J240" s="8">
         <v>0</v>
       </c>
       <c r="K240" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L240" s="8">
         <v>0</v>
@@ -17006,7 +17258,7 @@
         <v>9</v>
       </c>
       <c r="N240" s="8">
-        <v>134</v>
+        <v>64</v>
       </c>
       <c r="O240" s="8"/>
       <c r="P240" s="8"/>
@@ -17057,7 +17309,7 @@
         <v>3</v>
       </c>
       <c r="N241" s="8">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="O241" s="8"/>
       <c r="P241" s="8"/>
@@ -17092,7 +17344,7 @@
         <v>12</v>
       </c>
       <c r="I242" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J242" s="8">
         <v>0</v>
@@ -17105,10 +17357,10 @@
       </c>
       <c r="M242" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N242" s="8">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="O242" s="8"/>
       <c r="P242" s="8"/>
@@ -17143,7 +17395,7 @@
         <v>15</v>
       </c>
       <c r="I243" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J243" s="8">
         <v>0</v>
@@ -17152,11 +17404,11 @@
         <v>2</v>
       </c>
       <c r="L243" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M243" s="8">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N243" s="8">
         <v>0</v>
@@ -17245,7 +17497,7 @@
         <v>15</v>
       </c>
       <c r="I245" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J245" s="8">
         <v>0</v>
@@ -17258,10 +17510,10 @@
       </c>
       <c r="M245" s="8">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N245" s="8">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="O245" s="8"/>
       <c r="P245" s="8"/>
@@ -17312,7 +17564,7 @@
         <v>3</v>
       </c>
       <c r="N246" s="8">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="O246" s="8"/>
       <c r="P246" s="8"/>
@@ -17363,7 +17615,7 @@
         <v>2</v>
       </c>
       <c r="N247" s="8">
-        <v>283</v>
+        <v>237</v>
       </c>
       <c r="O247" s="8"/>
       <c r="P247" s="8"/>
@@ -17398,7 +17650,7 @@
         <v>12</v>
       </c>
       <c r="I248" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J248" s="8">
         <v>0</v>
@@ -17411,7 +17663,7 @@
       </c>
       <c r="M248" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N248" s="8">
         <v>0</v>
@@ -17506,17 +17758,17 @@
         <v>0</v>
       </c>
       <c r="K250" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L250" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M250" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N250" s="8">
-        <v>1369</v>
+        <v>1313</v>
       </c>
       <c r="O250" s="8"/>
       <c r="P250" s="8"/>
@@ -17567,7 +17819,7 @@
         <v>3</v>
       </c>
       <c r="N251" s="8">
-        <v>1196</v>
+        <v>1189</v>
       </c>
       <c r="O251" s="8"/>
       <c r="P251" s="8"/>
@@ -17602,7 +17854,7 @@
         <v>14</v>
       </c>
       <c r="I252" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J252" s="8">
         <v>0</v>
@@ -17615,7 +17867,7 @@
       </c>
       <c r="M252" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N252" s="8">
         <v>187</v>
@@ -17653,7 +17905,7 @@
         <v>14</v>
       </c>
       <c r="I253" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J253" s="8">
         <v>0</v>
@@ -17662,11 +17914,11 @@
         <v>0</v>
       </c>
       <c r="L253" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M253" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N253" s="8">
         <v>1195</v>
@@ -17713,14 +17965,14 @@
         <v>0</v>
       </c>
       <c r="L254" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M254" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N254" s="8">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="O254" s="8"/>
       <c r="P254" s="8"/>
@@ -17822,7 +18074,7 @@
         <v>3</v>
       </c>
       <c r="N256" s="8">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="O256" s="8"/>
       <c r="P256" s="8"/>
@@ -17857,7 +18109,7 @@
         <v>14</v>
       </c>
       <c r="I257" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J257" s="8">
         <v>0</v>
@@ -17870,10 +18122,10 @@
       </c>
       <c r="M257" s="8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N257" s="8">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="O257" s="8"/>
       <c r="P257" s="8"/>
@@ -17975,7 +18227,7 @@
         <v>3</v>
       </c>
       <c r="N259" s="8">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O259" s="8"/>
       <c r="P259" s="8"/>
@@ -18010,23 +18262,23 @@
         <v>13</v>
       </c>
       <c r="I260" s="8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J260" s="8">
         <v>0</v>
       </c>
       <c r="K260" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L260" s="8">
         <v>0</v>
       </c>
       <c r="M260" s="8">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N260" s="8">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="O260" s="8"/>
       <c r="P260" s="8"/>
@@ -18061,23 +18313,23 @@
         <v>12</v>
       </c>
       <c r="I261" s="8">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J261" s="8">
         <v>0</v>
       </c>
       <c r="K261" s="8">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="L261" s="8">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M261" s="8">
         <f t="shared" si="4"/>
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="N261" s="8">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="O261" s="8"/>
       <c r="P261" s="8"/>
@@ -18112,23 +18364,23 @@
         <v>12</v>
       </c>
       <c r="I262" s="8">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J262" s="8">
         <v>0</v>
       </c>
       <c r="K262" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L262" s="8">
         <v>0</v>
       </c>
       <c r="M262" s="8">
         <f t="shared" si="4"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N262" s="8">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="O262" s="8"/>
       <c r="P262" s="8"/>
@@ -18163,7 +18415,7 @@
         <v>12</v>
       </c>
       <c r="I263" s="8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J263" s="8">
         <v>0</v>
@@ -18176,7 +18428,7 @@
       </c>
       <c r="M263" s="8">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N263" s="8">
         <v>0</v>
@@ -18230,7 +18482,7 @@
         <v>2</v>
       </c>
       <c r="N264" s="8">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="O264" s="8"/>
       <c r="P264" s="8"/>
@@ -18265,23 +18517,23 @@
         <v>14</v>
       </c>
       <c r="I265" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J265" s="8">
         <v>0</v>
       </c>
       <c r="K265" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L265" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M265" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N265" s="8">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="O265" s="8"/>
       <c r="P265" s="8"/>
@@ -18367,7 +18619,7 @@
         <v>14</v>
       </c>
       <c r="I267" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J267" s="8">
         <v>0</v>
@@ -18380,7 +18632,7 @@
       </c>
       <c r="M267" s="8">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N267" s="8">
         <v>51</v>
@@ -18434,7 +18686,7 @@
         <v>3</v>
       </c>
       <c r="N268" s="8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O268" s="8"/>
       <c r="P268" s="8"/>
@@ -18469,7 +18721,7 @@
         <v>15</v>
       </c>
       <c r="I269" s="8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J269" s="8">
         <v>0</v>
@@ -18482,7 +18734,7 @@
       </c>
       <c r="M269" s="8">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N269" s="8">
         <v>0</v>
@@ -18740,7 +18992,7 @@
         <v>3</v>
       </c>
       <c r="N274" s="8">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="O274" s="8"/>
       <c r="P274" s="8"/>
@@ -18791,7 +19043,7 @@
         <v>3</v>
       </c>
       <c r="N275" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O275" s="8"/>
       <c r="P275" s="8"/>
@@ -18826,7 +19078,7 @@
         <v>15</v>
       </c>
       <c r="I276" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J276" s="8">
         <v>0</v>
@@ -18839,10 +19091,10 @@
       </c>
       <c r="M276" s="8">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N276" s="8">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="O276" s="8"/>
       <c r="P276" s="8"/>
@@ -18928,23 +19180,23 @@
         <v>12</v>
       </c>
       <c r="I278" s="8">
+        <v>6</v>
+      </c>
+      <c r="J278" s="8">
+        <v>0</v>
+      </c>
+      <c r="K278" s="8">
         <v>4</v>
       </c>
-      <c r="J278" s="8">
-        <v>0</v>
-      </c>
-      <c r="K278" s="8">
-        <v>1</v>
-      </c>
       <c r="L278" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M278" s="8">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N278" s="8">
-        <v>891</v>
+        <v>843</v>
       </c>
       <c r="O278" s="8"/>
       <c r="P278" s="8"/>
@@ -19081,7 +19333,7 @@
         <v>16</v>
       </c>
       <c r="I281" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J281" s="8">
         <v>0</v>
@@ -19094,10 +19346,10 @@
       </c>
       <c r="M281" s="8">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N281" s="8">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="O281" s="8"/>
       <c r="P281" s="8"/>
@@ -19234,7 +19486,7 @@
         <v>12</v>
       </c>
       <c r="I284" s="8">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="J284" s="8">
         <v>0</v>
@@ -19247,7 +19499,7 @@
       </c>
       <c r="M284" s="8">
         <f t="shared" si="4"/>
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="N284" s="8">
         <v>0</v>
@@ -19301,7 +19553,7 @@
         <v>2</v>
       </c>
       <c r="N285" s="8">
-        <v>3</v>
+        <v>283</v>
       </c>
       <c r="O285" s="8"/>
       <c r="P285" s="8"/>
@@ -19352,7 +19604,7 @@
         <v>3</v>
       </c>
       <c r="N286" s="8">
-        <v>950</v>
+        <v>934</v>
       </c>
       <c r="O286" s="8"/>
       <c r="P286" s="8"/>
@@ -19403,7 +19655,7 @@
         <v>7</v>
       </c>
       <c r="N287" s="8">
-        <v>1094</v>
+        <v>1085</v>
       </c>
       <c r="O287" s="8"/>
       <c r="P287" s="8"/>
@@ -19438,7 +19690,7 @@
         <v>14</v>
       </c>
       <c r="I288" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J288" s="8">
         <v>0</v>
@@ -19451,10 +19703,10 @@
       </c>
       <c r="M288" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N288" s="8">
-        <v>1336</v>
+        <v>1325</v>
       </c>
       <c r="O288" s="8"/>
       <c r="P288" s="8"/>
@@ -19591,23 +19843,23 @@
         <v>12</v>
       </c>
       <c r="I291" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J291" s="8">
         <v>0</v>
       </c>
       <c r="K291" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L291" s="8">
         <v>0</v>
       </c>
       <c r="M291" s="8">
         <f t="shared" si="4"/>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N291" s="8">
-        <v>1013</v>
+        <v>938</v>
       </c>
       <c r="O291" s="8"/>
       <c r="P291" s="8"/>
@@ -19744,23 +19996,23 @@
         <v>12</v>
       </c>
       <c r="I294" s="8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J294" s="8">
         <v>0</v>
       </c>
       <c r="K294" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L294" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M294" s="8">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N294" s="8">
-        <v>1333</v>
+        <v>1264</v>
       </c>
       <c r="O294" s="8"/>
       <c r="P294" s="8"/>
@@ -20152,7 +20404,7 @@
         <v>13</v>
       </c>
       <c r="I302" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J302" s="8">
         <v>0</v>
@@ -20165,10 +20417,10 @@
       </c>
       <c r="M302" s="8">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N302" s="8">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="O302" s="8"/>
       <c r="P302" s="8"/>
@@ -20270,7 +20522,7 @@
         <v>4</v>
       </c>
       <c r="N304" s="8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O304" s="8"/>
       <c r="P304" s="8"/>
@@ -20321,7 +20573,7 @@
         <v>8</v>
       </c>
       <c r="N305" s="8">
-        <v>415</v>
+        <v>394</v>
       </c>
       <c r="O305" s="8"/>
       <c r="P305" s="8"/>
@@ -20372,7 +20624,7 @@
         <v>9</v>
       </c>
       <c r="N306" s="8">
-        <v>879</v>
+        <v>866</v>
       </c>
       <c r="O306" s="8"/>
       <c r="P306" s="8"/>
@@ -20423,7 +20675,7 @@
         <v>10</v>
       </c>
       <c r="N307" s="8">
-        <v>923</v>
+        <v>893</v>
       </c>
       <c r="O307" s="8"/>
       <c r="P307" s="8"/>
@@ -20458,7 +20710,7 @@
         <v>13</v>
       </c>
       <c r="I308" s="8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J308" s="8">
         <v>0</v>
@@ -20471,10 +20723,10 @@
       </c>
       <c r="M308" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N308" s="8">
-        <v>769</v>
+        <v>740</v>
       </c>
       <c r="O308" s="8"/>
       <c r="P308" s="8"/>
@@ -20509,7 +20761,7 @@
         <v>13</v>
       </c>
       <c r="I309" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J309" s="8">
         <v>0</v>
@@ -20522,7 +20774,7 @@
       </c>
       <c r="M309" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N309" s="8">
         <v>0</v>
@@ -20611,13 +20863,13 @@
         <v>16</v>
       </c>
       <c r="I311" s="8">
+        <v>0</v>
+      </c>
+      <c r="J311" s="8">
+        <v>0</v>
+      </c>
+      <c r="K311" s="8">
         <v>1</v>
-      </c>
-      <c r="J311" s="8">
-        <v>0</v>
-      </c>
-      <c r="K311" s="8">
-        <v>0</v>
       </c>
       <c r="L311" s="8">
         <v>0</v>
@@ -20627,7 +20879,7 @@
         <v>1</v>
       </c>
       <c r="N311" s="8">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="O311" s="8"/>
       <c r="P311" s="8"/>
@@ -20713,7 +20965,7 @@
         <v>13</v>
       </c>
       <c r="I313" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J313" s="8">
         <v>0</v>
@@ -20726,10 +20978,10 @@
       </c>
       <c r="M313" s="8">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N313" s="8">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="O313" s="8"/>
       <c r="P313" s="8"/>
@@ -20764,7 +21016,7 @@
         <v>12</v>
       </c>
       <c r="I314" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J314" s="8">
         <v>0</v>
@@ -20777,10 +21029,10 @@
       </c>
       <c r="M314" s="8">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N314" s="8">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="O314" s="8"/>
       <c r="P314" s="8"/>
@@ -20815,7 +21067,7 @@
         <v>12</v>
       </c>
       <c r="I315" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J315" s="8">
         <v>0</v>
@@ -20828,10 +21080,10 @@
       </c>
       <c r="M315" s="8">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N315" s="8">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="O315" s="8"/>
       <c r="P315" s="8"/>
@@ -20866,13 +21118,13 @@
         <v>12</v>
       </c>
       <c r="I316" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J316" s="8">
         <v>0</v>
       </c>
       <c r="K316" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L316" s="8">
         <v>0</v>
@@ -20882,7 +21134,7 @@
         <v>5</v>
       </c>
       <c r="N316" s="8">
-        <v>656</v>
+        <v>928</v>
       </c>
       <c r="O316" s="8"/>
       <c r="P316" s="8"/>
@@ -20923,17 +21175,17 @@
         <v>0</v>
       </c>
       <c r="K317" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L317" s="8">
         <v>0</v>
       </c>
       <c r="M317" s="8">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="N317" s="8">
-        <v>201</v>
+        <v>95</v>
       </c>
       <c r="O317" s="8"/>
       <c r="P317" s="8"/>
@@ -20968,23 +21220,23 @@
         <v>12</v>
       </c>
       <c r="I318" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J318" s="8">
         <v>0</v>
       </c>
       <c r="K318" s="8">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="L318" s="8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M318" s="8">
         <f t="shared" si="4"/>
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="N318" s="8">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="O318" s="8"/>
       <c r="P318" s="8"/>
@@ -21035,7 +21287,7 @@
         <v>4</v>
       </c>
       <c r="N319" s="8">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="O319" s="8"/>
       <c r="P319" s="8"/>
@@ -21086,7 +21338,7 @@
         <v>4</v>
       </c>
       <c r="N320" s="8">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="O320" s="8"/>
       <c r="P320" s="8"/>
@@ -21121,13 +21373,13 @@
         <v>14</v>
       </c>
       <c r="I321" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J321" s="8">
         <v>0</v>
       </c>
       <c r="K321" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L321" s="8">
         <v>0</v>
@@ -21137,7 +21389,7 @@
         <v>3</v>
       </c>
       <c r="N321" s="8">
-        <v>464</v>
+        <v>446</v>
       </c>
       <c r="O321" s="8"/>
       <c r="P321" s="8"/>
@@ -21188,7 +21440,7 @@
         <v>3</v>
       </c>
       <c r="N322" s="8">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="O322" s="8"/>
       <c r="P322" s="8"/>
@@ -21325,7 +21577,7 @@
         <v>14</v>
       </c>
       <c r="I325" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J325" s="8">
         <v>0</v>
@@ -21338,10 +21590,10 @@
       </c>
       <c r="M325" s="8">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N325" s="8">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="O325" s="8"/>
       <c r="P325" s="8"/>
@@ -21392,7 +21644,7 @@
         <v>3</v>
       </c>
       <c r="N326" s="8">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="O326" s="8"/>
       <c r="P326" s="8"/>
@@ -21433,17 +21685,17 @@
         <v>0</v>
       </c>
       <c r="K327" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L327" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M327" s="8">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="N327" s="8">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O327" s="8"/>
       <c r="P327" s="8"/>
@@ -21494,7 +21746,7 @@
         <v>2</v>
       </c>
       <c r="N328" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O328" s="8"/>
       <c r="P328" s="8"/>
@@ -21545,7 +21797,7 @@
         <v>4</v>
       </c>
       <c r="N329" s="8">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="O329" s="8"/>
       <c r="P329" s="8"/>
@@ -21580,7 +21832,7 @@
         <v>13</v>
       </c>
       <c r="I330" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J330" s="8">
         <v>0</v>
@@ -21593,10 +21845,10 @@
       </c>
       <c r="M330" s="8">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N330" s="8">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O330" s="8"/>
       <c r="P330" s="8"/>
@@ -21749,7 +22001,7 @@
         <v>3</v>
       </c>
       <c r="N333" s="8">
-        <v>0</v>
+        <v>286</v>
       </c>
       <c r="O333" s="8"/>
       <c r="P333" s="8"/>
@@ -21800,7 +22052,7 @@
         <v>4</v>
       </c>
       <c r="N334" s="8">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="O334" s="8"/>
       <c r="P334" s="8"/>
@@ -21835,7 +22087,7 @@
         <v>13</v>
       </c>
       <c r="I335" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J335" s="8">
         <v>0</v>
@@ -21848,7 +22100,7 @@
       </c>
       <c r="M335" s="8">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N335" s="8">
         <v>0</v>
@@ -21902,7 +22154,7 @@
         <v>4</v>
       </c>
       <c r="N336" s="8">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="O336" s="8"/>
       <c r="P336" s="8"/>
@@ -21943,17 +22195,17 @@
         <v>0</v>
       </c>
       <c r="K337" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L337" s="8">
         <v>0</v>
       </c>
       <c r="M337" s="8">
         <f t="shared" si="5"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N337" s="8">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="O337" s="8"/>
       <c r="P337" s="8"/>
@@ -21988,7 +22240,7 @@
         <v>12</v>
       </c>
       <c r="I338" s="8">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J338" s="8">
         <v>0</v>
@@ -22001,10 +22253,10 @@
       </c>
       <c r="M338" s="8">
         <f t="shared" si="5"/>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="N338" s="8">
-        <v>1080</v>
+        <v>1052</v>
       </c>
       <c r="O338" s="8"/>
       <c r="P338" s="8"/>
@@ -22039,7 +22291,7 @@
         <v>14</v>
       </c>
       <c r="I339" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J339" s="8">
         <v>0</v>
@@ -22052,10 +22304,10 @@
       </c>
       <c r="M339" s="8">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N339" s="8">
-        <v>803</v>
+        <v>797</v>
       </c>
       <c r="O339" s="8"/>
       <c r="P339" s="8"/>
@@ -22090,23 +22342,23 @@
         <v>14</v>
       </c>
       <c r="I340" s="8">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J340" s="8">
         <v>0</v>
       </c>
       <c r="K340" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L340" s="8">
         <v>0</v>
       </c>
       <c r="M340" s="8">
         <f t="shared" si="5"/>
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="N340" s="8">
-        <v>496</v>
+        <v>441</v>
       </c>
       <c r="O340" s="8"/>
       <c r="P340" s="8"/>
@@ -22147,17 +22399,17 @@
         <v>0</v>
       </c>
       <c r="K341" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L341" s="8">
         <v>0</v>
       </c>
       <c r="M341" s="8">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N341" s="8">
-        <v>327</v>
+        <v>313</v>
       </c>
       <c r="O341" s="8"/>
       <c r="P341" s="8"/>
@@ -22192,7 +22444,7 @@
         <v>14</v>
       </c>
       <c r="I342" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J342" s="8">
         <v>0</v>
@@ -22205,7 +22457,7 @@
       </c>
       <c r="M342" s="8">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N342" s="8">
         <v>323</v>
@@ -22259,7 +22511,7 @@
         <v>4</v>
       </c>
       <c r="N343" s="8">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="O343" s="8"/>
       <c r="P343" s="8"/>
@@ -22345,7 +22597,7 @@
         <v>12</v>
       </c>
       <c r="I345" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J345" s="8">
         <v>0</v>
@@ -22358,7 +22610,7 @@
       </c>
       <c r="M345" s="8">
         <f t="shared" si="5"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N345" s="8">
         <v>0</v>
@@ -22447,23 +22699,23 @@
         <v>13</v>
       </c>
       <c r="I347" s="8">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J347" s="8">
         <v>0</v>
       </c>
       <c r="K347" s="8">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L347" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M347" s="8">
         <f t="shared" si="5"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N347" s="8">
-        <v>315</v>
+        <v>272</v>
       </c>
       <c r="O347" s="8"/>
       <c r="P347" s="9"/>
@@ -22498,7 +22750,7 @@
         <v>12</v>
       </c>
       <c r="I348" s="8">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J348" s="8">
         <v>0</v>
@@ -22511,7 +22763,7 @@
       </c>
       <c r="M348" s="8">
         <f t="shared" si="5"/>
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N348" s="8">
         <v>0</v>
@@ -22702,13 +22954,13 @@
         <v>14</v>
       </c>
       <c r="I352" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J352" s="8">
         <v>0</v>
       </c>
       <c r="K352" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L352" s="8">
         <v>0</v>
@@ -22718,7 +22970,7 @@
         <v>2</v>
       </c>
       <c r="N352" s="8">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="O352" s="8"/>
       <c r="P352" s="9"/>
@@ -22855,7 +23107,7 @@
         <v>16</v>
       </c>
       <c r="I355" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J355" s="8">
         <v>0</v>
@@ -22868,7 +23120,7 @@
       </c>
       <c r="M355" s="8">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N355" s="8">
         <v>0</v>
@@ -23075,7 +23327,7 @@
         <v>3</v>
       </c>
       <c r="N359" s="8">
-        <v>980</v>
+        <v>986</v>
       </c>
       <c r="O359" s="8"/>
       <c r="P359" s="9"/>
@@ -23263,23 +23515,23 @@
         <v>12</v>
       </c>
       <c r="I363" s="8">
-        <v>542</v>
+        <v>522</v>
       </c>
       <c r="J363" s="8">
         <v>0</v>
       </c>
       <c r="K363" s="8">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="L363" s="8">
         <v>0</v>
       </c>
       <c r="M363" s="8">
         <f t="shared" si="5"/>
-        <v>542</v>
+        <v>642</v>
       </c>
       <c r="N363" s="8">
-        <v>1318</v>
+        <v>1198</v>
       </c>
       <c r="O363" s="8"/>
       <c r="P363" s="9"/>
@@ -23518,23 +23770,23 @@
         <v>12</v>
       </c>
       <c r="I368" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J368" s="8">
         <v>0</v>
       </c>
       <c r="K368" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L368" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M368" s="8">
         <f t="shared" si="5"/>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N368" s="8">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="O368" s="8"/>
       <c r="P368" s="9"/>
@@ -23585,7 +23837,7 @@
         <v>0</v>
       </c>
       <c r="N369" s="8">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="O369" s="8"/>
       <c r="P369" s="9"/>
@@ -23687,7 +23939,7 @@
         <v>2</v>
       </c>
       <c r="N371" s="8">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O371" s="8"/>
       <c r="P371" s="9"/>
@@ -23773,7 +24025,7 @@
         <v>14</v>
       </c>
       <c r="I373" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J373" s="8">
         <v>0</v>
@@ -23786,7 +24038,7 @@
       </c>
       <c r="M373" s="8">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N373" s="8">
         <v>0</v>
@@ -24334,13 +24586,13 @@
         <v>12</v>
       </c>
       <c r="I384" s="8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J384" s="8">
         <v>0</v>
       </c>
       <c r="K384" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L384" s="8">
         <v>0</v>
@@ -24350,7 +24602,7 @@
         <v>6</v>
       </c>
       <c r="N384" s="8">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="O384" s="8"/>
       <c r="P384" s="9"/>
@@ -24385,23 +24637,23 @@
         <v>12</v>
       </c>
       <c r="I385" s="8">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="J385" s="8">
         <v>0</v>
       </c>
       <c r="K385" s="8">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="L385" s="8">
         <v>0</v>
       </c>
       <c r="M385" s="8">
         <f t="shared" si="5"/>
-        <v>158</v>
+        <v>271</v>
       </c>
       <c r="N385" s="8">
-        <v>257</v>
+        <v>137</v>
       </c>
       <c r="O385" s="8"/>
       <c r="P385" s="7"/>
@@ -24656,7 +24908,7 @@
         <v>7</v>
       </c>
       <c r="N390" s="8">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="O390" s="8"/>
       <c r="P390" s="7"/>
@@ -24691,7 +24943,7 @@
         <v>12</v>
       </c>
       <c r="I391" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J391" s="8">
         <v>0</v>
@@ -24704,7 +24956,7 @@
       </c>
       <c r="M391" s="8">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N391" s="8">
         <v>0</v>
@@ -24946,7 +25198,7 @@
         <v>12</v>
       </c>
       <c r="I396" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J396" s="8">
         <v>0</v>
@@ -24959,7 +25211,7 @@
       </c>
       <c r="M396" s="8">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N396" s="8">
         <v>0</v>
@@ -25370,7 +25622,7 @@
         <v>2</v>
       </c>
       <c r="N404" s="8">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="O404" s="7"/>
       <c r="P404" s="7"/>
@@ -25421,7 +25673,7 @@
         <v>2</v>
       </c>
       <c r="N405" s="8">
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="O405" s="7"/>
       <c r="P405" s="7"/>
@@ -25558,7 +25810,7 @@
         <v>13</v>
       </c>
       <c r="I408" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J408" s="8">
         <v>0</v>
@@ -25571,10 +25823,10 @@
       </c>
       <c r="M408" s="8">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N408" s="8">
-        <v>446</v>
+        <v>416</v>
       </c>
       <c r="O408" s="7"/>
       <c r="P408" s="7"/>
@@ -25609,7 +25861,7 @@
         <v>13</v>
       </c>
       <c r="I409" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J409" s="8">
         <v>0</v>
@@ -25622,10 +25874,10 @@
       </c>
       <c r="M409" s="8">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N409" s="8">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="O409" s="7"/>
       <c r="P409" s="7"/>
@@ -25676,7 +25928,7 @@
         <v>2</v>
       </c>
       <c r="N410" s="8">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O410" s="7"/>
       <c r="P410" s="7"/>
@@ -25727,7 +25979,7 @@
         <v>2</v>
       </c>
       <c r="N411" s="8">
-        <v>290</v>
+        <v>313</v>
       </c>
       <c r="O411" s="7"/>
       <c r="P411" s="7"/>
@@ -25829,7 +26081,7 @@
         <v>2</v>
       </c>
       <c r="N413" s="8">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="O413" s="7"/>
       <c r="P413" s="7"/>
@@ -25921,17 +26173,17 @@
         <v>0</v>
       </c>
       <c r="K415" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L415" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M415" s="8">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N415" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O415" s="7"/>
       <c r="P415" s="7"/>
@@ -25982,7 +26234,7 @@
         <v>3</v>
       </c>
       <c r="N416" s="8">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="O416" s="7"/>
       <c r="P416" s="7"/>
@@ -26017,23 +26269,23 @@
         <v>12</v>
       </c>
       <c r="I417" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J417" s="8">
         <v>0</v>
       </c>
       <c r="K417" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L417" s="8">
         <v>0</v>
       </c>
       <c r="M417" s="8">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N417" s="8">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="O417" s="7"/>
       <c r="P417" s="7"/>
@@ -26068,13 +26320,13 @@
         <v>12</v>
       </c>
       <c r="I418" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J418" s="8">
         <v>0</v>
       </c>
       <c r="K418" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L418" s="8">
         <v>0</v>
@@ -26084,7 +26336,7 @@
         <v>4</v>
       </c>
       <c r="N418" s="8">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="O418" s="7"/>
       <c r="P418" s="7"/>
@@ -26186,7 +26438,7 @@
         <v>3</v>
       </c>
       <c r="N420" s="8">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="O420" s="7"/>
       <c r="P420" s="7"/>
@@ -26237,7 +26489,7 @@
         <v>2</v>
       </c>
       <c r="N421" s="8">
-        <v>704</v>
+        <v>691</v>
       </c>
       <c r="O421" s="7"/>
       <c r="P421" s="7"/>
@@ -26288,7 +26540,7 @@
         <v>2</v>
       </c>
       <c r="N422" s="8">
-        <v>275</v>
+        <v>252</v>
       </c>
       <c r="O422" s="7"/>
       <c r="P422" s="7"/>
@@ -26339,7 +26591,7 @@
         <v>2</v>
       </c>
       <c r="N423" s="8">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="O423" s="7"/>
       <c r="P423" s="7"/>
@@ -26441,7 +26693,7 @@
         <v>2</v>
       </c>
       <c r="N425" s="8">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O425" s="7"/>
       <c r="P425" s="7"/>
@@ -26492,7 +26744,7 @@
         <v>2</v>
       </c>
       <c r="N426" s="8">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="O426" s="7"/>
       <c r="P426" s="7"/>
@@ -26645,7 +26897,7 @@
         <v>0</v>
       </c>
       <c r="N429" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O429" s="7"/>
       <c r="P429" s="7"/>
@@ -26798,7 +27050,7 @@
         <v>0</v>
       </c>
       <c r="N432" s="8">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="O432" s="7"/>
       <c r="P432" s="7"/>
@@ -26945,7 +27197,7 @@
         <v>0</v>
       </c>
       <c r="M435" s="8">
-        <f t="shared" ref="M435:M439" si="9">I435+J435+K435+L435</f>
+        <f t="shared" ref="M435:M467" si="9">I435+J435+K435+L435</f>
         <v>1</v>
       </c>
       <c r="N435" s="8">
@@ -27086,17 +27338,17 @@
         <v>0</v>
       </c>
       <c r="K438" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L438" s="8">
         <v>0</v>
       </c>
       <c r="M438" s="8">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N438" s="8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O438" s="7"/>
       <c r="P438" s="7"/>
@@ -27155,20 +27407,47 @@
       <c r="T439" s="7"/>
     </row>
     <row r="440" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A440" s="7"/>
-      <c r="B440" s="7"/>
-      <c r="C440" s="7"/>
+      <c r="A440" s="7" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B440" s="7" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C440" s="7" t="s">
+        <v>1359</v>
+      </c>
       <c r="D440" s="7"/>
-      <c r="E440" s="7"/>
-      <c r="F440" s="7"/>
-      <c r="G440" s="7"/>
-      <c r="H440" s="7"/>
-      <c r="I440" s="7"/>
-      <c r="J440" s="7"/>
-      <c r="K440" s="7"/>
-      <c r="L440" s="7"/>
-      <c r="M440" s="7"/>
-      <c r="N440" s="7"/>
+      <c r="E440" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F440" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G440" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H440" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="I440" s="7">
+        <v>0</v>
+      </c>
+      <c r="J440" s="8">
+        <v>0</v>
+      </c>
+      <c r="K440" s="8">
+        <v>0</v>
+      </c>
+      <c r="L440" s="7">
+        <v>10</v>
+      </c>
+      <c r="M440" s="8">
+        <f t="shared" si="9"/>
+        <v>10</v>
+      </c>
+      <c r="N440" s="7">
+        <v>0</v>
+      </c>
       <c r="O440" s="7"/>
       <c r="P440" s="7"/>
       <c r="Q440" s="7"/>
@@ -27177,20 +27456,47 @@
       <c r="T440" s="7"/>
     </row>
     <row r="441" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A441" s="7"/>
-      <c r="B441" s="7"/>
-      <c r="C441" s="7"/>
+      <c r="A441" s="7" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B441" s="7" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C441" s="7" t="s">
+        <v>1360</v>
+      </c>
       <c r="D441" s="7"/>
-      <c r="E441" s="7"/>
-      <c r="F441" s="7"/>
-      <c r="G441" s="7"/>
-      <c r="H441" s="7"/>
-      <c r="I441" s="7"/>
-      <c r="J441" s="7"/>
-      <c r="K441" s="7"/>
-      <c r="L441" s="7"/>
-      <c r="M441" s="7"/>
-      <c r="N441" s="7"/>
+      <c r="E441" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F441" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G441" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H441" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="I441" s="7">
+        <v>0</v>
+      </c>
+      <c r="J441" s="8">
+        <v>0</v>
+      </c>
+      <c r="K441" s="8">
+        <v>0</v>
+      </c>
+      <c r="L441" s="7">
+        <v>5</v>
+      </c>
+      <c r="M441" s="8">
+        <f t="shared" si="9"/>
+        <v>5</v>
+      </c>
+      <c r="N441" s="7">
+        <v>0</v>
+      </c>
       <c r="O441" s="7"/>
       <c r="P441" s="7"/>
       <c r="Q441" s="7"/>
@@ -27199,20 +27505,47 @@
       <c r="T441" s="7"/>
     </row>
     <row r="442" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A442" s="7"/>
-      <c r="B442" s="7"/>
-      <c r="C442" s="7"/>
+      <c r="A442" s="7" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B442" s="7" t="s">
+        <v>1389</v>
+      </c>
+      <c r="C442" s="7" t="s">
+        <v>1361</v>
+      </c>
       <c r="D442" s="7"/>
-      <c r="E442" s="7"/>
-      <c r="F442" s="7"/>
-      <c r="G442" s="7"/>
-      <c r="H442" s="7"/>
-      <c r="I442" s="7"/>
-      <c r="J442" s="7"/>
-      <c r="K442" s="7"/>
-      <c r="L442" s="7"/>
-      <c r="M442" s="7"/>
-      <c r="N442" s="7"/>
+      <c r="E442" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F442" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G442" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H442" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="I442" s="7">
+        <v>0</v>
+      </c>
+      <c r="J442" s="8">
+        <v>0</v>
+      </c>
+      <c r="K442" s="8">
+        <v>0</v>
+      </c>
+      <c r="L442" s="7">
+        <v>3</v>
+      </c>
+      <c r="M442" s="8">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="N442" s="7">
+        <v>0</v>
+      </c>
       <c r="O442" s="7"/>
       <c r="P442" s="7"/>
       <c r="Q442" s="7"/>
@@ -27221,20 +27554,47 @@
       <c r="T442" s="7"/>
     </row>
     <row r="443" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A443" s="7"/>
-      <c r="B443" s="7"/>
-      <c r="C443" s="7"/>
+      <c r="A443" s="7" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B443" s="7" t="s">
+        <v>1390</v>
+      </c>
+      <c r="C443" s="7" t="s">
+        <v>1362</v>
+      </c>
       <c r="D443" s="7"/>
-      <c r="E443" s="7"/>
-      <c r="F443" s="7"/>
-      <c r="G443" s="7"/>
-      <c r="H443" s="7"/>
-      <c r="I443" s="7"/>
-      <c r="J443" s="7"/>
-      <c r="K443" s="7"/>
-      <c r="L443" s="7"/>
-      <c r="M443" s="7"/>
-      <c r="N443" s="7"/>
+      <c r="E443" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F443" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G443" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H443" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="I443" s="7">
+        <v>0</v>
+      </c>
+      <c r="J443" s="8">
+        <v>0</v>
+      </c>
+      <c r="K443" s="8">
+        <v>0</v>
+      </c>
+      <c r="L443" s="7">
+        <v>10</v>
+      </c>
+      <c r="M443" s="8">
+        <f t="shared" si="9"/>
+        <v>10</v>
+      </c>
+      <c r="N443" s="7">
+        <v>0</v>
+      </c>
       <c r="O443" s="7"/>
       <c r="P443" s="7"/>
       <c r="Q443" s="7"/>
@@ -27243,20 +27603,47 @@
       <c r="T443" s="7"/>
     </row>
     <row r="444" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A444" s="7"/>
-      <c r="B444" s="7"/>
-      <c r="C444" s="7"/>
+      <c r="A444" s="7" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B444" s="7" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C444" s="7" t="s">
+        <v>1363</v>
+      </c>
       <c r="D444" s="7"/>
-      <c r="E444" s="7"/>
-      <c r="F444" s="7"/>
-      <c r="G444" s="7"/>
-      <c r="H444" s="7"/>
-      <c r="I444" s="7"/>
-      <c r="J444" s="7"/>
-      <c r="K444" s="7"/>
-      <c r="L444" s="7"/>
-      <c r="M444" s="7"/>
-      <c r="N444" s="7"/>
+      <c r="E444" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F444" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G444" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H444" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="I444" s="7">
+        <v>0</v>
+      </c>
+      <c r="J444" s="8">
+        <v>0</v>
+      </c>
+      <c r="K444" s="8">
+        <v>0</v>
+      </c>
+      <c r="L444" s="7">
+        <v>3</v>
+      </c>
+      <c r="M444" s="8">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="N444" s="7">
+        <v>0</v>
+      </c>
       <c r="O444" s="7"/>
       <c r="P444" s="7"/>
       <c r="Q444" s="7"/>
@@ -27265,20 +27652,47 @@
       <c r="T444" s="7"/>
     </row>
     <row r="445" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A445" s="7"/>
-      <c r="B445" s="7"/>
-      <c r="C445" s="7"/>
+      <c r="A445" s="7" t="s">
+        <v>1420</v>
+      </c>
+      <c r="B445" s="7" t="s">
+        <v>1392</v>
+      </c>
+      <c r="C445" s="7" t="s">
+        <v>1364</v>
+      </c>
       <c r="D445" s="7"/>
-      <c r="E445" s="7"/>
-      <c r="F445" s="7"/>
-      <c r="G445" s="7"/>
-      <c r="H445" s="7"/>
-      <c r="I445" s="7"/>
-      <c r="J445" s="7"/>
-      <c r="K445" s="7"/>
-      <c r="L445" s="7"/>
-      <c r="M445" s="7"/>
-      <c r="N445" s="7"/>
+      <c r="E445" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F445" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G445" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H445" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I445" s="7">
+        <v>0</v>
+      </c>
+      <c r="J445" s="8">
+        <v>0</v>
+      </c>
+      <c r="K445" s="8">
+        <v>0</v>
+      </c>
+      <c r="L445" s="7">
+        <v>2</v>
+      </c>
+      <c r="M445" s="8">
+        <f t="shared" si="9"/>
+        <v>2</v>
+      </c>
+      <c r="N445" s="7">
+        <v>0</v>
+      </c>
       <c r="O445" s="7"/>
       <c r="P445" s="7"/>
       <c r="Q445" s="7"/>
@@ -27287,20 +27701,47 @@
       <c r="T445" s="7"/>
     </row>
     <row r="446" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A446" s="7"/>
-      <c r="B446" s="7"/>
-      <c r="C446" s="7"/>
+      <c r="A446" s="7" t="s">
+        <v>1421</v>
+      </c>
+      <c r="B446" s="7" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C446" s="7" t="s">
+        <v>1365</v>
+      </c>
       <c r="D446" s="7"/>
-      <c r="E446" s="7"/>
-      <c r="F446" s="7"/>
-      <c r="G446" s="7"/>
-      <c r="H446" s="7"/>
-      <c r="I446" s="7"/>
-      <c r="J446" s="7"/>
-      <c r="K446" s="7"/>
-      <c r="L446" s="7"/>
-      <c r="M446" s="7"/>
-      <c r="N446" s="7"/>
+      <c r="E446" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F446" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G446" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H446" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I446" s="7">
+        <v>0</v>
+      </c>
+      <c r="J446" s="8">
+        <v>0</v>
+      </c>
+      <c r="K446" s="8">
+        <v>0</v>
+      </c>
+      <c r="L446" s="7">
+        <v>2</v>
+      </c>
+      <c r="M446" s="8">
+        <f t="shared" si="9"/>
+        <v>2</v>
+      </c>
+      <c r="N446" s="7">
+        <v>0</v>
+      </c>
       <c r="O446" s="7"/>
       <c r="P446" s="7"/>
       <c r="Q446" s="7"/>
@@ -27309,20 +27750,47 @@
       <c r="T446" s="7"/>
     </row>
     <row r="447" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A447" s="7"/>
-      <c r="B447" s="7"/>
-      <c r="C447" s="7"/>
+      <c r="A447" s="7" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B447" s="7" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C447" s="7" t="s">
+        <v>1366</v>
+      </c>
       <c r="D447" s="7"/>
-      <c r="E447" s="7"/>
-      <c r="F447" s="7"/>
-      <c r="G447" s="7"/>
-      <c r="H447" s="7"/>
-      <c r="I447" s="7"/>
-      <c r="J447" s="7"/>
-      <c r="K447" s="7"/>
-      <c r="L447" s="7"/>
-      <c r="M447" s="7"/>
-      <c r="N447" s="7"/>
+      <c r="E447" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F447" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G447" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H447" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I447" s="7">
+        <v>0</v>
+      </c>
+      <c r="J447" s="8">
+        <v>0</v>
+      </c>
+      <c r="K447" s="8">
+        <v>0</v>
+      </c>
+      <c r="L447" s="7">
+        <v>3</v>
+      </c>
+      <c r="M447" s="8">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="N447" s="7">
+        <v>2</v>
+      </c>
       <c r="O447" s="7"/>
       <c r="P447" s="7"/>
       <c r="Q447" s="7"/>
@@ -27331,20 +27799,47 @@
       <c r="T447" s="7"/>
     </row>
     <row r="448" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A448" s="7"/>
-      <c r="B448" s="7"/>
-      <c r="C448" s="7"/>
+      <c r="A448" s="7" t="s">
+        <v>1423</v>
+      </c>
+      <c r="B448" s="7" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C448" s="7" t="s">
+        <v>1367</v>
+      </c>
       <c r="D448" s="7"/>
-      <c r="E448" s="7"/>
-      <c r="F448" s="7"/>
-      <c r="G448" s="7"/>
-      <c r="H448" s="7"/>
-      <c r="I448" s="7"/>
-      <c r="J448" s="7"/>
-      <c r="K448" s="7"/>
-      <c r="L448" s="7"/>
-      <c r="M448" s="7"/>
-      <c r="N448" s="7"/>
+      <c r="E448" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F448" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G448" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H448" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I448" s="7">
+        <v>0</v>
+      </c>
+      <c r="J448" s="8">
+        <v>0</v>
+      </c>
+      <c r="K448" s="8">
+        <v>0</v>
+      </c>
+      <c r="L448" s="7">
+        <v>3</v>
+      </c>
+      <c r="M448" s="8">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="N448" s="7">
+        <v>0</v>
+      </c>
       <c r="O448" s="7"/>
       <c r="P448" s="7"/>
       <c r="Q448" s="7"/>
@@ -27353,20 +27848,47 @@
       <c r="T448" s="7"/>
     </row>
     <row r="449" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A449" s="7"/>
-      <c r="B449" s="7"/>
-      <c r="C449" s="7"/>
+      <c r="A449" s="7" t="s">
+        <v>1424</v>
+      </c>
+      <c r="B449" s="7" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C449" s="7" t="s">
+        <v>1368</v>
+      </c>
       <c r="D449" s="7"/>
-      <c r="E449" s="7"/>
-      <c r="F449" s="7"/>
-      <c r="G449" s="7"/>
-      <c r="H449" s="7"/>
-      <c r="I449" s="7"/>
-      <c r="J449" s="7"/>
-      <c r="K449" s="7"/>
-      <c r="L449" s="7"/>
-      <c r="M449" s="7"/>
-      <c r="N449" s="7"/>
+      <c r="E449" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F449" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G449" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H449" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I449" s="7">
+        <v>0</v>
+      </c>
+      <c r="J449" s="8">
+        <v>0</v>
+      </c>
+      <c r="K449" s="8">
+        <v>0</v>
+      </c>
+      <c r="L449" s="7">
+        <v>3</v>
+      </c>
+      <c r="M449" s="8">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="N449" s="7">
+        <v>9</v>
+      </c>
       <c r="O449" s="7"/>
       <c r="P449" s="7"/>
       <c r="Q449" s="7"/>
@@ -27375,20 +27897,47 @@
       <c r="T449" s="7"/>
     </row>
     <row r="450" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A450" s="7"/>
-      <c r="B450" s="7"/>
-      <c r="C450" s="7"/>
+      <c r="A450" s="7" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B450" s="7" t="s">
+        <v>1397</v>
+      </c>
+      <c r="C450" s="7" t="s">
+        <v>1369</v>
+      </c>
       <c r="D450" s="7"/>
-      <c r="E450" s="7"/>
-      <c r="F450" s="7"/>
-      <c r="G450" s="7"/>
-      <c r="H450" s="7"/>
-      <c r="I450" s="7"/>
-      <c r="J450" s="7"/>
-      <c r="K450" s="7"/>
-      <c r="L450" s="7"/>
-      <c r="M450" s="7"/>
-      <c r="N450" s="7"/>
+      <c r="E450" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F450" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G450" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H450" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I450" s="7">
+        <v>0</v>
+      </c>
+      <c r="J450" s="8">
+        <v>0</v>
+      </c>
+      <c r="K450" s="8">
+        <v>0</v>
+      </c>
+      <c r="L450" s="7">
+        <v>3</v>
+      </c>
+      <c r="M450" s="8">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="N450" s="7">
+        <v>0</v>
+      </c>
       <c r="O450" s="7"/>
       <c r="P450" s="7"/>
       <c r="Q450" s="7"/>
@@ -27397,20 +27946,47 @@
       <c r="T450" s="7"/>
     </row>
     <row r="451" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A451" s="7"/>
-      <c r="B451" s="7"/>
-      <c r="C451" s="7"/>
+      <c r="A451" s="7" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B451" s="7" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C451" s="7" t="s">
+        <v>1370</v>
+      </c>
       <c r="D451" s="7"/>
-      <c r="E451" s="7"/>
-      <c r="F451" s="7"/>
-      <c r="G451" s="7"/>
-      <c r="H451" s="7"/>
-      <c r="I451" s="7"/>
-      <c r="J451" s="7"/>
-      <c r="K451" s="7"/>
-      <c r="L451" s="7"/>
-      <c r="M451" s="7"/>
-      <c r="N451" s="7"/>
+      <c r="E451" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F451" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G451" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H451" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I451" s="7">
+        <v>0</v>
+      </c>
+      <c r="J451" s="8">
+        <v>0</v>
+      </c>
+      <c r="K451" s="8">
+        <v>0</v>
+      </c>
+      <c r="L451" s="7">
+        <v>5</v>
+      </c>
+      <c r="M451" s="8">
+        <f t="shared" si="9"/>
+        <v>5</v>
+      </c>
+      <c r="N451" s="7">
+        <v>2</v>
+      </c>
       <c r="O451" s="7"/>
       <c r="P451" s="7"/>
       <c r="Q451" s="7"/>
@@ -27419,20 +27995,47 @@
       <c r="T451" s="7"/>
     </row>
     <row r="452" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A452" s="7"/>
-      <c r="B452" s="7"/>
-      <c r="C452" s="7"/>
+      <c r="A452" s="7" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B452" s="7" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C452" s="7" t="s">
+        <v>1371</v>
+      </c>
       <c r="D452" s="7"/>
-      <c r="E452" s="7"/>
-      <c r="F452" s="7"/>
-      <c r="G452" s="7"/>
-      <c r="H452" s="7"/>
-      <c r="I452" s="7"/>
-      <c r="J452" s="7"/>
-      <c r="K452" s="7"/>
-      <c r="L452" s="7"/>
-      <c r="M452" s="7"/>
-      <c r="N452" s="7"/>
+      <c r="E452" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F452" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G452" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H452" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I452" s="7">
+        <v>0</v>
+      </c>
+      <c r="J452" s="8">
+        <v>0</v>
+      </c>
+      <c r="K452" s="8">
+        <v>0</v>
+      </c>
+      <c r="L452" s="7">
+        <v>2</v>
+      </c>
+      <c r="M452" s="8">
+        <f t="shared" si="9"/>
+        <v>2</v>
+      </c>
+      <c r="N452" s="7">
+        <v>1</v>
+      </c>
       <c r="O452" s="7"/>
       <c r="P452" s="7"/>
       <c r="Q452" s="7"/>
@@ -27441,20 +28044,47 @@
       <c r="T452" s="7"/>
     </row>
     <row r="453" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A453" s="7"/>
-      <c r="B453" s="7"/>
-      <c r="C453" s="7"/>
+      <c r="A453" s="7" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B453" s="7" t="s">
+        <v>1400</v>
+      </c>
+      <c r="C453" s="7" t="s">
+        <v>1372</v>
+      </c>
       <c r="D453" s="7"/>
-      <c r="E453" s="7"/>
-      <c r="F453" s="7"/>
-      <c r="G453" s="7"/>
-      <c r="H453" s="7"/>
-      <c r="I453" s="7"/>
-      <c r="J453" s="7"/>
-      <c r="K453" s="7"/>
-      <c r="L453" s="7"/>
-      <c r="M453" s="7"/>
-      <c r="N453" s="7"/>
+      <c r="E453" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F453" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G453" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H453" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I453" s="7">
+        <v>0</v>
+      </c>
+      <c r="J453" s="8">
+        <v>0</v>
+      </c>
+      <c r="K453" s="8">
+        <v>0</v>
+      </c>
+      <c r="L453" s="7">
+        <v>4</v>
+      </c>
+      <c r="M453" s="8">
+        <f t="shared" si="9"/>
+        <v>4</v>
+      </c>
+      <c r="N453" s="7">
+        <v>0</v>
+      </c>
       <c r="O453" s="7"/>
       <c r="P453" s="7"/>
       <c r="Q453" s="7"/>
@@ -27463,20 +28093,47 @@
       <c r="T453" s="7"/>
     </row>
     <row r="454" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A454" s="7"/>
-      <c r="B454" s="7"/>
-      <c r="C454" s="7"/>
+      <c r="A454" s="7" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B454" s="7" t="s">
+        <v>1401</v>
+      </c>
+      <c r="C454" s="7" t="s">
+        <v>1373</v>
+      </c>
       <c r="D454" s="7"/>
-      <c r="E454" s="7"/>
-      <c r="F454" s="7"/>
-      <c r="G454" s="7"/>
-      <c r="H454" s="7"/>
-      <c r="I454" s="7"/>
-      <c r="J454" s="7"/>
-      <c r="K454" s="7"/>
-      <c r="L454" s="7"/>
-      <c r="M454" s="7"/>
-      <c r="N454" s="7"/>
+      <c r="E454" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F454" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G454" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H454" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I454" s="7">
+        <v>0</v>
+      </c>
+      <c r="J454" s="8">
+        <v>0</v>
+      </c>
+      <c r="K454" s="8">
+        <v>0</v>
+      </c>
+      <c r="L454" s="7">
+        <v>3</v>
+      </c>
+      <c r="M454" s="8">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="N454" s="7">
+        <v>14</v>
+      </c>
       <c r="O454" s="7"/>
       <c r="P454" s="7"/>
       <c r="Q454" s="7"/>
@@ -27485,20 +28142,47 @@
       <c r="T454" s="7"/>
     </row>
     <row r="455" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A455" s="7"/>
-      <c r="B455" s="7"/>
-      <c r="C455" s="7"/>
+      <c r="A455" s="7" t="s">
+        <v>1430</v>
+      </c>
+      <c r="B455" s="7" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C455" s="7" t="s">
+        <v>1374</v>
+      </c>
       <c r="D455" s="7"/>
-      <c r="E455" s="7"/>
-      <c r="F455" s="7"/>
-      <c r="G455" s="7"/>
-      <c r="H455" s="7"/>
-      <c r="I455" s="7"/>
-      <c r="J455" s="7"/>
-      <c r="K455" s="7"/>
-      <c r="L455" s="7"/>
-      <c r="M455" s="7"/>
-      <c r="N455" s="7"/>
+      <c r="E455" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F455" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G455" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H455" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I455" s="7">
+        <v>0</v>
+      </c>
+      <c r="J455" s="8">
+        <v>0</v>
+      </c>
+      <c r="K455" s="8">
+        <v>0</v>
+      </c>
+      <c r="L455" s="7">
+        <v>3</v>
+      </c>
+      <c r="M455" s="8">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="N455" s="7">
+        <v>0</v>
+      </c>
       <c r="O455" s="7"/>
       <c r="P455" s="7"/>
       <c r="Q455" s="7"/>
@@ -27507,20 +28191,47 @@
       <c r="T455" s="7"/>
     </row>
     <row r="456" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A456" s="7"/>
-      <c r="B456" s="7"/>
-      <c r="C456" s="7"/>
+      <c r="A456" s="7" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B456" s="7" t="s">
+        <v>1403</v>
+      </c>
+      <c r="C456" s="7" t="s">
+        <v>1375</v>
+      </c>
       <c r="D456" s="7"/>
-      <c r="E456" s="7"/>
-      <c r="F456" s="7"/>
-      <c r="G456" s="7"/>
-      <c r="H456" s="7"/>
-      <c r="I456" s="7"/>
-      <c r="J456" s="7"/>
-      <c r="K456" s="7"/>
-      <c r="L456" s="7"/>
-      <c r="M456" s="7"/>
-      <c r="N456" s="7"/>
+      <c r="E456" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F456" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G456" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H456" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I456" s="7">
+        <v>0</v>
+      </c>
+      <c r="J456" s="8">
+        <v>0</v>
+      </c>
+      <c r="K456" s="8">
+        <v>0</v>
+      </c>
+      <c r="L456" s="7">
+        <v>5</v>
+      </c>
+      <c r="M456" s="8">
+        <f t="shared" si="9"/>
+        <v>5</v>
+      </c>
+      <c r="N456" s="7">
+        <v>0</v>
+      </c>
       <c r="O456" s="7"/>
       <c r="P456" s="7"/>
       <c r="Q456" s="7"/>
@@ -27529,20 +28240,47 @@
       <c r="T456" s="7"/>
     </row>
     <row r="457" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A457" s="7"/>
-      <c r="B457" s="7"/>
-      <c r="C457" s="7"/>
+      <c r="A457" s="7" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B457" s="7" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C457" s="7" t="s">
+        <v>1376</v>
+      </c>
       <c r="D457" s="7"/>
-      <c r="E457" s="7"/>
-      <c r="F457" s="7"/>
-      <c r="G457" s="7"/>
-      <c r="H457" s="7"/>
-      <c r="I457" s="7"/>
-      <c r="J457" s="7"/>
-      <c r="K457" s="7"/>
-      <c r="L457" s="7"/>
-      <c r="M457" s="7"/>
-      <c r="N457" s="7"/>
+      <c r="E457" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F457" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G457" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H457" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I457" s="7">
+        <v>0</v>
+      </c>
+      <c r="J457" s="8">
+        <v>0</v>
+      </c>
+      <c r="K457" s="8">
+        <v>0</v>
+      </c>
+      <c r="L457" s="7">
+        <v>4</v>
+      </c>
+      <c r="M457" s="8">
+        <f t="shared" si="9"/>
+        <v>4</v>
+      </c>
+      <c r="N457" s="7">
+        <v>0</v>
+      </c>
       <c r="O457" s="7"/>
       <c r="P457" s="7"/>
       <c r="Q457" s="7"/>
@@ -27551,20 +28289,47 @@
       <c r="T457" s="7"/>
     </row>
     <row r="458" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A458" s="7"/>
-      <c r="B458" s="7"/>
-      <c r="C458" s="7"/>
+      <c r="A458" s="7" t="s">
+        <v>1433</v>
+      </c>
+      <c r="B458" s="7" t="s">
+        <v>1405</v>
+      </c>
+      <c r="C458" s="7" t="s">
+        <v>1377</v>
+      </c>
       <c r="D458" s="7"/>
-      <c r="E458" s="7"/>
-      <c r="F458" s="7"/>
-      <c r="G458" s="7"/>
-      <c r="H458" s="7"/>
-      <c r="I458" s="7"/>
-      <c r="J458" s="7"/>
-      <c r="K458" s="7"/>
-      <c r="L458" s="7"/>
-      <c r="M458" s="7"/>
-      <c r="N458" s="7"/>
+      <c r="E458" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F458" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G458" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H458" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I458" s="7">
+        <v>0</v>
+      </c>
+      <c r="J458" s="8">
+        <v>0</v>
+      </c>
+      <c r="K458" s="8">
+        <v>0</v>
+      </c>
+      <c r="L458" s="7">
+        <v>2</v>
+      </c>
+      <c r="M458" s="8">
+        <f t="shared" si="9"/>
+        <v>2</v>
+      </c>
+      <c r="N458" s="7">
+        <v>1</v>
+      </c>
       <c r="O458" s="7"/>
       <c r="P458" s="7"/>
       <c r="Q458" s="7"/>
@@ -27573,20 +28338,47 @@
       <c r="T458" s="7"/>
     </row>
     <row r="459" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A459" s="7"/>
-      <c r="B459" s="7"/>
-      <c r="C459" s="7"/>
+      <c r="A459" s="7" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B459" s="7" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C459" s="7" t="s">
+        <v>1378</v>
+      </c>
       <c r="D459" s="7"/>
-      <c r="E459" s="7"/>
-      <c r="F459" s="7"/>
-      <c r="G459" s="7"/>
-      <c r="H459" s="7"/>
-      <c r="I459" s="7"/>
-      <c r="J459" s="7"/>
-      <c r="K459" s="7"/>
-      <c r="L459" s="7"/>
-      <c r="M459" s="7"/>
-      <c r="N459" s="7"/>
+      <c r="E459" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F459" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G459" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H459" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I459" s="7">
+        <v>0</v>
+      </c>
+      <c r="J459" s="8">
+        <v>0</v>
+      </c>
+      <c r="K459" s="8">
+        <v>0</v>
+      </c>
+      <c r="L459" s="7">
+        <v>3</v>
+      </c>
+      <c r="M459" s="8">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="N459" s="7">
+        <v>0</v>
+      </c>
       <c r="O459" s="7"/>
       <c r="P459" s="7"/>
       <c r="Q459" s="7"/>
@@ -27595,20 +28387,47 @@
       <c r="T459" s="7"/>
     </row>
     <row r="460" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A460" s="7"/>
-      <c r="B460" s="7"/>
-      <c r="C460" s="7"/>
+      <c r="A460" s="7" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B460" s="7" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C460" s="7" t="s">
+        <v>1379</v>
+      </c>
       <c r="D460" s="7"/>
-      <c r="E460" s="7"/>
-      <c r="F460" s="7"/>
-      <c r="G460" s="7"/>
-      <c r="H460" s="7"/>
-      <c r="I460" s="7"/>
-      <c r="J460" s="7"/>
-      <c r="K460" s="7"/>
-      <c r="L460" s="7"/>
-      <c r="M460" s="7"/>
-      <c r="N460" s="7"/>
+      <c r="E460" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F460" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G460" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H460" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I460" s="7">
+        <v>0</v>
+      </c>
+      <c r="J460" s="8">
+        <v>0</v>
+      </c>
+      <c r="K460" s="8">
+        <v>0</v>
+      </c>
+      <c r="L460" s="7">
+        <v>3</v>
+      </c>
+      <c r="M460" s="8">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="N460" s="7">
+        <v>0</v>
+      </c>
       <c r="O460" s="7"/>
       <c r="P460" s="7"/>
       <c r="Q460" s="7"/>
@@ -27617,20 +28436,47 @@
       <c r="T460" s="7"/>
     </row>
     <row r="461" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A461" s="7"/>
-      <c r="B461" s="7"/>
-      <c r="C461" s="7"/>
+      <c r="A461" s="7" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B461" s="7" t="s">
+        <v>1408</v>
+      </c>
+      <c r="C461" s="7" t="s">
+        <v>1380</v>
+      </c>
       <c r="D461" s="7"/>
-      <c r="E461" s="7"/>
-      <c r="F461" s="7"/>
-      <c r="G461" s="7"/>
-      <c r="H461" s="7"/>
-      <c r="I461" s="7"/>
-      <c r="J461" s="7"/>
-      <c r="K461" s="7"/>
-      <c r="L461" s="7"/>
-      <c r="M461" s="7"/>
-      <c r="N461" s="7"/>
+      <c r="E461" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F461" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G461" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H461" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I461" s="7">
+        <v>0</v>
+      </c>
+      <c r="J461" s="8">
+        <v>0</v>
+      </c>
+      <c r="K461" s="8">
+        <v>0</v>
+      </c>
+      <c r="L461" s="7">
+        <v>3</v>
+      </c>
+      <c r="M461" s="8">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="N461" s="7">
+        <v>29</v>
+      </c>
       <c r="O461" s="7"/>
       <c r="P461" s="7"/>
       <c r="Q461" s="7"/>
@@ -27639,20 +28485,47 @@
       <c r="T461" s="7"/>
     </row>
     <row r="462" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A462" s="7"/>
-      <c r="B462" s="7"/>
-      <c r="C462" s="7"/>
+      <c r="A462" s="7" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B462" s="7" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C462" s="7" t="s">
+        <v>1381</v>
+      </c>
       <c r="D462" s="7"/>
-      <c r="E462" s="7"/>
-      <c r="F462" s="7"/>
-      <c r="G462" s="7"/>
-      <c r="H462" s="7"/>
-      <c r="I462" s="7"/>
-      <c r="J462" s="7"/>
-      <c r="K462" s="7"/>
-      <c r="L462" s="7"/>
-      <c r="M462" s="7"/>
-      <c r="N462" s="7"/>
+      <c r="E462" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F462" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G462" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H462" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I462" s="7">
+        <v>0</v>
+      </c>
+      <c r="J462" s="8">
+        <v>0</v>
+      </c>
+      <c r="K462" s="8">
+        <v>0</v>
+      </c>
+      <c r="L462" s="7">
+        <v>3</v>
+      </c>
+      <c r="M462" s="8">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="N462" s="7">
+        <v>0</v>
+      </c>
       <c r="O462" s="7"/>
       <c r="P462" s="7"/>
       <c r="Q462" s="7"/>
@@ -27661,20 +28534,47 @@
       <c r="T462" s="7"/>
     </row>
     <row r="463" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A463" s="7"/>
-      <c r="B463" s="7"/>
-      <c r="C463" s="7"/>
+      <c r="A463" s="7" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B463" s="7" t="s">
+        <v>1410</v>
+      </c>
+      <c r="C463" s="7" t="s">
+        <v>1382</v>
+      </c>
       <c r="D463" s="7"/>
-      <c r="E463" s="7"/>
-      <c r="F463" s="7"/>
-      <c r="G463" s="7"/>
-      <c r="H463" s="7"/>
-      <c r="I463" s="7"/>
-      <c r="J463" s="7"/>
-      <c r="K463" s="7"/>
-      <c r="L463" s="7"/>
-      <c r="M463" s="7"/>
-      <c r="N463" s="7"/>
+      <c r="E463" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F463" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G463" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H463" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I463" s="7">
+        <v>0</v>
+      </c>
+      <c r="J463" s="8">
+        <v>0</v>
+      </c>
+      <c r="K463" s="8">
+        <v>0</v>
+      </c>
+      <c r="L463" s="7">
+        <v>3</v>
+      </c>
+      <c r="M463" s="8">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="N463" s="7">
+        <v>33</v>
+      </c>
       <c r="O463" s="7"/>
       <c r="P463" s="7"/>
       <c r="Q463" s="7"/>
@@ -27683,20 +28583,47 @@
       <c r="T463" s="7"/>
     </row>
     <row r="464" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A464" s="7"/>
-      <c r="B464" s="7"/>
-      <c r="C464" s="7"/>
+      <c r="A464" s="7" t="s">
+        <v>1439</v>
+      </c>
+      <c r="B464" s="7" t="s">
+        <v>1411</v>
+      </c>
+      <c r="C464" s="7" t="s">
+        <v>1383</v>
+      </c>
       <c r="D464" s="7"/>
-      <c r="E464" s="7"/>
-      <c r="F464" s="7"/>
-      <c r="G464" s="7"/>
-      <c r="H464" s="7"/>
-      <c r="I464" s="7"/>
-      <c r="J464" s="7"/>
-      <c r="K464" s="7"/>
-      <c r="L464" s="7"/>
-      <c r="M464" s="7"/>
-      <c r="N464" s="7"/>
+      <c r="E464" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F464" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G464" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H464" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I464" s="7">
+        <v>0</v>
+      </c>
+      <c r="J464" s="8">
+        <v>0</v>
+      </c>
+      <c r="K464" s="8">
+        <v>0</v>
+      </c>
+      <c r="L464" s="7">
+        <v>1</v>
+      </c>
+      <c r="M464" s="8">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="N464" s="7">
+        <v>2</v>
+      </c>
       <c r="O464" s="7"/>
       <c r="P464" s="7"/>
       <c r="Q464" s="7"/>
@@ -27705,20 +28632,47 @@
       <c r="T464" s="7"/>
     </row>
     <row r="465" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A465" s="7"/>
-      <c r="B465" s="7"/>
-      <c r="C465" s="7"/>
+      <c r="A465" s="7" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B465" s="7" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C465" s="7" t="s">
+        <v>1384</v>
+      </c>
       <c r="D465" s="7"/>
-      <c r="E465" s="7"/>
-      <c r="F465" s="7"/>
-      <c r="G465" s="7"/>
-      <c r="H465" s="7"/>
-      <c r="I465" s="7"/>
-      <c r="J465" s="7"/>
-      <c r="K465" s="7"/>
-      <c r="L465" s="7"/>
-      <c r="M465" s="7"/>
-      <c r="N465" s="7"/>
+      <c r="E465" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F465" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G465" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H465" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I465" s="7">
+        <v>0</v>
+      </c>
+      <c r="J465" s="8">
+        <v>0</v>
+      </c>
+      <c r="K465" s="8">
+        <v>0</v>
+      </c>
+      <c r="L465" s="7">
+        <v>1</v>
+      </c>
+      <c r="M465" s="8">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="N465" s="7">
+        <v>4</v>
+      </c>
       <c r="O465" s="7"/>
       <c r="P465" s="7"/>
       <c r="Q465" s="7"/>
@@ -27727,20 +28681,47 @@
       <c r="T465" s="7"/>
     </row>
     <row r="466" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A466" s="7"/>
-      <c r="B466" s="7"/>
-      <c r="C466" s="7"/>
+      <c r="A466" s="7" t="s">
+        <v>1441</v>
+      </c>
+      <c r="B466" s="7" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C466" s="7" t="s">
+        <v>1385</v>
+      </c>
       <c r="D466" s="7"/>
-      <c r="E466" s="7"/>
-      <c r="F466" s="7"/>
-      <c r="G466" s="7"/>
-      <c r="H466" s="7"/>
-      <c r="I466" s="7"/>
-      <c r="J466" s="7"/>
-      <c r="K466" s="7"/>
-      <c r="L466" s="7"/>
-      <c r="M466" s="7"/>
-      <c r="N466" s="7"/>
+      <c r="E466" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F466" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G466" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H466" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I466" s="7">
+        <v>0</v>
+      </c>
+      <c r="J466" s="8">
+        <v>0</v>
+      </c>
+      <c r="K466" s="8">
+        <v>0</v>
+      </c>
+      <c r="L466" s="7">
+        <v>1</v>
+      </c>
+      <c r="M466" s="8">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="N466" s="7">
+        <v>1</v>
+      </c>
       <c r="O466" s="7"/>
       <c r="P466" s="7"/>
       <c r="Q466" s="7"/>
@@ -27749,20 +28730,47 @@
       <c r="T466" s="7"/>
     </row>
     <row r="467" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A467" s="7"/>
-      <c r="B467" s="7"/>
-      <c r="C467" s="7"/>
+      <c r="A467" s="7" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B467" s="7" t="s">
+        <v>1414</v>
+      </c>
+      <c r="C467" s="7" t="s">
+        <v>1386</v>
+      </c>
       <c r="D467" s="7"/>
-      <c r="E467" s="7"/>
-      <c r="F467" s="7"/>
-      <c r="G467" s="7"/>
-      <c r="H467" s="7"/>
-      <c r="I467" s="7"/>
-      <c r="J467" s="7"/>
-      <c r="K467" s="7"/>
-      <c r="L467" s="7"/>
-      <c r="M467" s="7"/>
-      <c r="N467" s="7"/>
+      <c r="E467" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F467" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G467" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H467" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I467" s="7">
+        <v>0</v>
+      </c>
+      <c r="J467" s="8">
+        <v>0</v>
+      </c>
+      <c r="K467" s="8">
+        <v>0</v>
+      </c>
+      <c r="L467" s="7">
+        <v>5</v>
+      </c>
+      <c r="M467" s="8">
+        <f t="shared" si="9"/>
+        <v>5</v>
+      </c>
+      <c r="N467" s="7">
+       